--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_7E57064139D4AD56E0136A7F0DCDB38FD164FAA1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_5161D2470C0771BF7ABEB4345A4C9F872E0144CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1830" yWindow="1425" windowWidth="36435" windowHeight="19425" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="1296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1315">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -103,10 +103,10 @@
     <t>주당 환산 161세트</t>
   </si>
   <si>
-    <t>164세트</t>
-  </si>
-  <si>
-    <t>주 4회 140에서 올렸다. 유지선은 75. 늘린 곳은 현장 일 보정이 사라진 자리들이다</t>
+    <t>168세트</t>
+  </si>
+  <si>
+    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 둘(원 레그 컬 · 발 높은 레그 프레스)</t>
   </si>
   <si>
     <t>증량 방식</t>
@@ -244,7 +244,7 @@
     <t>· 2순위 — 목 2종목(6). 2026-10-02 신설이라 되돌려도 잃을 적응이 없다.</t>
   </si>
   <si>
-    <t>· 3순위 — 시티드 레그 컬 3 · 카프 2종 중 하나 3 · 라잉 레그 레이즈 3. 고립이라 메인 리프트 진행에 영향이 없다.</t>
+    <t>· 3순위 — 레그 익스텐션 3 · 카프 2종 중 하나 3 · 라잉 레그 레이즈 3. 고립이라 메인 리프트 진행에 영향이 없다. 레그 익스텐션은 수요일 레그 프레스가 사두에 간접을 얹어 줘 값이 가장 싸졌다.</t>
   </si>
   <si>
     <t>· 마지막까지 지키는 것은 스쿼트 · 벤치 · 오버헤드 프레스 · 데드 톱세트와 가슴 · 등 · 어깨 볼륨이다.</t>
@@ -2809,10 +2809,10 @@
     <t>하체 전면(사두) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 83분</t>
-  </si>
-  <si>
-    <t>스쿼트 5×5가 앞, 어깨 블록이 4~6번. 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 이너 · 아우터 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다</t>
+    <t>약 92분</t>
+  </si>
+  <si>
+    <t>스쿼트 5×5가 앞, 어깨 블록이 4~6번. 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 이너 · 아우터 · 원 레그 컬 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다</t>
   </si>
   <si>
     <t>일</t>
@@ -2869,10 +2869,10 @@
     <t>하체 후면(햄 · 둔) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 82분</t>
-  </si>
-  <si>
-    <t>데드 톱1 + 백오프2. 스미스 오버헤드 프레스가 어깨 블록 첫 종목 — 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다</t>
+    <t>약 87분</t>
+  </si>
+  <si>
+    <t>데드 톱1 + 백오프2 · 레그 프레스는 발을 발판 위쪽에(둔근). 스미스 오버헤드 프레스가 어깨 블록 첫 종목 — 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다</t>
   </si>
   <si>
     <t>목</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 400분 (6시간 40분)</t>
+    <t>약 413분 (6시간 53분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -2911,7 +2911,10 @@
     <t>· 큰 부위 셋을 둘로 쪼갰다 — 하체는 전면(토) / 후면(수), 등은 광배(일) / 승모 · 능형(목), 가슴은 상부(월) / 중하부(목).</t>
   </si>
   <si>
-    <t>· 쪼갠 축은 근육군이지 움직임 평면이 아니다. 2026-09-04에 '주동근은 그립 폭이 아니라 팔꿈치 경로가 정한다'로 바꾼 그 원칙을 그대로 쓴다. 그래서 수평 당기기인 원암 케이블 로우가 광배 날(일)에 있다.</t>
+    <t>· 쪼갠 축은 근육군이지 움직임 평면이 아니다. 2026-09-04에 '주동근은 그립 폭이 아니라 팔꿈치 경로가 정한다'로 바꾼 그 원칙을 그대로 쓴다. 그래서 수평 당기기인 원암 케이블 로우가 광배 날(일)에 있고, 발 높은 레그 프레스가 햄스트링이 아니라 둔근으로 계상된다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 보강] 햄스트링도 주 2회로 쪼갰다 — 수요일 7(루마니안 3 · 레그 컬 4) + 토요일 3(원 레그 컬). 사두만 주 1회로 남는데 스쿼트 5×5가 한 날을 다 쓰기 때문이다. 대신 수요일 레그 프레스가 사두에 간접 1.5세트치를 얹어 노출은 주 2회가 됐다.</t>
   </si>
   <si>
     <t>· 금요일만 쉰다. 쉬는 날을 스쿼트 앞에 두는 것이 여섯 날 중 가장 값이 큰 자리다.</t>
@@ -2920,12 +2923,15 @@
     <t>[빈도를 올리고 볼륨은 조금만 올렸다 — 2026-10-02]</t>
   </si>
   <si>
-    <t>· 주 4회 140세트 → 주 6회 164세트. 세트는 17% 늘었고 가슴 · 등 · 하체 빈도가 주 1회 → 2회로 올랐다.</t>
+    <t>· 주 4회 140세트 → 주 6회 168세트. 세트는 20% 늘었고 가슴 · 등 · 하체 · 햄스트링 빈도가 주 1회 → 2회로 올랐다.</t>
   </si>
   <si>
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
   </si>
   <si>
+    <t>· [2026-10-02 사용자 추가 둘] 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량을 10으로 유지했다. 164 → 168.</t>
+  </si>
+  <si>
     <t>· 유지한 곳 — 흉근 24 · 승모 중부 10 · 삼각 측면 10 · 후면 10 · 사두 12 · 햄스트링 10 · 내전근 4. 이미 성장 구간 상단이라 세트는 그대로 두고 빈도만 올렸다.</t>
   </si>
   <si>
@@ -2971,16 +2977,16 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 토 34세트 83분 · 수 31세트 82분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
-  </si>
-  <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 22를 빼면 실질 12, 수요일은 19를 빼면 12, 월요일은 6을 빼면 16이다.</t>
+    <t>· 토 37세트 92분 · 수 32세트 87분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 25를 빼면 실질 12, 수요일은 19를 빼면 13, 월요일은 6을 빼면 16이다.</t>
   </si>
   <si>
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 주 400분 = 6시간 40분. 주 4회 370분에서 30분 늘었다 — 세트가 17% 늘었는데 시간은 8%만 늘어난 것은 늘린 자리가 전부 휴식 60~75초짜리 고립이기 때문이다.</t>
+    <t>· 주 413분 = 6시간 53분. 주 4회 370분에서 43분 늘었다. 토(92) · 수(87)가 가장 크지만 주 4회 시절 토(107) · 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>[몸 상태가 안 좋으면]</t>
@@ -3049,6 +3055,12 @@
     <t>힙 어브덕션 머신 (겸용 머신이 없을 때) / 케이블 힙 외전</t>
   </si>
   <si>
+    <t>[2026-10-02 추가 — 사용자 지적] 전면 하체만 12세트인 날에 햄스트링이 0이었다. 이 3세트로 햄스트링이 주 1회 → 2회가 된다(수요일 7 + 여기 3) — 가슴 · 등처럼 빈도를 쪼갠 셈이다. 편측이라 좌우 차가 드러나고, 사두로만 때린 날의 무릎 균형도 맞춘다.</t>
+  </si>
+  <si>
+    <t>라잉 / 시티드 레그 컬 (양측) / 노르딕 햄 컬 (맨몸)</t>
+  </si>
+  <si>
     <t>앉아서 하는 쪽 — 무릎이 굽어 가자미근 비중이 커진다. 수요일 스탠딩과 각도를 나눈다.</t>
   </si>
   <si>
@@ -3064,13 +3076,19 @@
     <t>· 하체를 전면 · 후면으로 갈라 토요일이 사두 전담이 됐다. 스쿼트 · 레그 프레스 · 익스텐션 12세트로 사두 주간 세트가 한 날에 다 들어간다.</t>
   </si>
   <si>
-    <t>· 어깨 블록을 4~6번에 둔 이유 — 이너 · 아우터 타이와 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 11세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
+    <t>· 어깨 블록을 4~6번에 둔 이유 — 이너 · 아우터 타이와 원 레그 컬 · 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 14세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
   </si>
   <si>
     <t>· 토요일에 어깨 세 방향(전 · 측 · 후)을 다 넣는 것이 사용자 지정이다. 전면은 머신 숄더, 측면은 덤벨 레터럴, 후면은 리버스 펙덱.</t>
   </si>
   <si>
-    <t>· 34세트 · 약 83분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 이너 · 아우터 · 카프 22세트)은 예외로 본다 — 실질 12세트다.</t>
+    <t>· [2026-10-02] 원 레그 컬 3을 더했다. 사두는 스쿼트 5×5 때문에 쪼갤 수 없어 주 1회지만 햄스트링은 쪼갤 수 있고, 전면 하체 날에 햄스트링이 0이면 무릎을 한쪽으로만 때리는 날이 된다.</t>
+  </si>
+  <si>
+    <t>· 37세트 · 약 92분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 이너 · 아우터 · 원 레그 컬 · 카프 25세트)은 예외로 본다 — 실질 12세트다.</t>
+  </si>
+  <si>
+    <t>· 여섯 날 중 가장 크다. 그래도 주 4회 시절 토요일(43세트 · 107분)보다는 작다.</t>
   </si>
   <si>
     <t>· 웜업은 별도다. 스쿼트가 있는 날이므로 10~15분을 더 잡는다.</t>
@@ -3088,7 +3106,7 @@
     <t>· N열 '드롭(초)'는 마지막 세트에 더해지는 시간이다. I열 종목 분에 합산되고, 앱 타이머는 마지막 세트를 그만큼 늘린 뒤 '드롭세트'라고 읊는다. E열 세트 수와 복귀_세트검산은 건드리지 않는다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고</t>
+    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???</t>
   </si>
   <si>
     <t>일요일 — 등(광배) · 팔</t>
@@ -3430,45 +3448,45 @@
     <t>덤벨 루마니안 데드 (허리 부담 ↓ · 좌우 균형) / 케이블 풀스루</t>
   </si>
   <si>
-    <t>무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 라잉으로 하면 고관절이 펴져 짧아진 구간에서 훈련된다.</t>
-  </si>
-  <si>
-    <t>라잉 레그 컬 / 노르딕 햄 컬 (맨몸)</t>
-  </si>
-  <si>
-    <t>시티드 레그 컬</t>
-  </si>
-  <si>
-    <t>[2026-10-02 신설] 고관절이 굽어 햄스트링이 늘어난 구간에서 훈련된다 — 라잉과 각도를 나눈다. 같은 중량이 안 나오는 것이 정상이다.</t>
-  </si>
-  <si>
-    <t>라잉 레그 컬 (각도가 겹친다 — 머신이 하나뿐일 때) / 케이블 레그 컬</t>
-  </si>
-  <si>
-    <t>둔근 직접. 짧아진 구간에서 최대 장력이 걸려 데드 · 루마니안(늘어난 구간)과 갈린다.</t>
+    <t>레그 프레스 (발 높게)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 둔다 — 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라간다. 근육군은 둔근으로 잡았다: 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀌고, 능동 단축이 작으면 자극도 작다. 그래서 사두 0.33 · 햄스트링 0.2를 간접으로 계상했다. 중량은 토요일(125)보다 낮게 잡았다 — 발 위치가 바뀌면 같은 중량이 안 나온다. 더블 프로그레션으로 맞춘다.</t>
+  </si>
+  <si>
+    <t>와이드 스탠스 레그 프레스 (발 높게) / 45도 레그 프레스 (발 높게) / 스미스 스쿼트 (발 앞쪽)</t>
+  </si>
+  <si>
+    <t>무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 라잉으로 하면 고관절이 펴져 짧아진 구간에서 훈련된다. 토요일 원 레그 컬과 같은 기능이지만 이쪽은 양측 · 고중량이다.</t>
+  </si>
+  <si>
+    <t>시티드 레그 컬 (고관절이 굽어 늘어난 구간) / 라잉 레그 컬 / 노르딕 햄 컬 (맨몸)</t>
+  </si>
+  <si>
+    <t>스미스 오버헤드 프레스</t>
+  </si>
+  <si>
+    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 14세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
+  </si>
+  <si>
+    <t>머신 숄더 프레스 (완전 머신을 원할 때 — 단 증량 추적은 이쪽으로 옮긴다) / 덤벨 숄더 프레스</t>
+  </si>
+  <si>
+    <t>프레스 직후라 측면 삼각이 이미 1.5세트치 간접을 받았다. 중량을 토요일보다 낮춰 잡는 것이 정상이다.</t>
+  </si>
+  <si>
+    <t>머신이라 상체 각도가 고정된다 — 데드 뒤에 기립근으로 버티지 않아도 되는 후면 삼각 종목이 이것뿐이다.</t>
+  </si>
+  <si>
+    <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 리버스 펙덱</t>
+  </si>
+  <si>
+    <t>둔근 직접. 짧아진 구간에서 최대 장력이 걸려 데드 · 루마니안(늘어난 구간)과 갈린다. 어깨와 경쟁하지 않는 고관절 종목이라 어깨 블록 뒤로 보냈다 — 그만큼 오버헤드 프레스 앞 누적이 줄었다.</t>
   </si>
   <si>
     <t>머신 힙 쓰러스트 / 글루트 브릿지 / 케이블 풀스루</t>
   </si>
   <si>
-    <t>스미스 오버헤드 프레스</t>
-  </si>
-  <si>
-    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 13세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
-  </si>
-  <si>
-    <t>머신 숄더 프레스 (완전 머신을 원할 때 — 단 증량 추적은 이쪽으로 옮긴다) / 덤벨 숄더 프레스</t>
-  </si>
-  <si>
-    <t>프레스 직후라 측면 삼각이 이미 1.5세트치 간접을 받았다. 중량을 토요일보다 낮춰 잡는 것이 정상이다.</t>
-  </si>
-  <si>
-    <t>머신이라 상체 각도가 고정된다 — 데드 뒤에 기립근으로 버티지 않아도 되는 후면 삼각 종목이 이것뿐이다.</t>
-  </si>
-  <si>
-    <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 리버스 펙덱</t>
-  </si>
-  <si>
     <t>어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤로 보냈다. 토요일 아우터 타이와 합쳐 주 7세트.</t>
   </si>
   <si>
@@ -3493,22 +3511,46 @@
     <t>· 토요일(하체 전면) 뒤 — 중간이다. 전면 삼각 · 삼두는 온전하나 스쿼트 5×5의 전신 피로가 가장 크다.</t>
   </si>
   <si>
-    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 13세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
+    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 14세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
   </si>
   <si>
     <t>· 그래서 토요일 전면은 머신 숄더 프레스(볼륨용)이고, 증량을 추적하는 쪽은 이 날이다.</t>
   </si>
   <si>
+    <t>· 힙 쓰러스트 · 힙 외전 · 카프를 어깨 뒤로 보내 프레스 앞 누적을 14세트로 묶었다. 레그 프레스가 들어오며 17이 될 수 있었던 자리다.</t>
+  </si>
+  <si>
     <t>[하체 후면을 한 날에 모은 이유]</t>
   </si>
   <si>
     <t>· 데드 · 루마니안 데드는 둘 다 고관절 힌지다. 주에 흩어 두면 기립근이 회복할 72시간을 못 받는다 — 같은 패턴은 한 날에 모은다.</t>
   </si>
   <si>
-    <t>· 굴곡(레그 컬 7)과 신전(데드 3 · 루마니안 3)을 같이 둬 햄스트링 두 기능을 다 쓴다. 햄스트링 주 10세트가 전부 이 날이다.</t>
-  </si>
-  <si>
-    <t>· 토요일(사두 12) · 수요일(후면 13)로 갈라 하체 빈도가 주 2회가 됐다. 세트 총량은 25 → 25로 같고 빈도만 올랐다.</t>
+    <t>· 고관절 신전 넷(데드 3 · 루마니안 3 · 레그 프레스 발 높게 4 · 힙 쓰러스트 3)과 무릎 굴곡(레그 컬 4)을 같이 둬 햄스트링 · 둔근의 두 기능을 다 쓴다.</t>
+  </si>
+  <si>
+    <t>· 햄스트링 주 10세트 중 7이 이 날이고 3은 토요일 원 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다.</t>
+  </si>
+  <si>
+    <t>· 토요일(사두 12 + 햄 3) · 수요일(후면 14 + 중둔근 3 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
+  </si>
+  <si>
+    <t>[레그 프레스를 발 높게 — 2026-10-02 사용자 지정]</t>
+  </si>
+  <si>
+    <t>· 발을 발판 가장 위쪽에 둔다. 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라가고, 무릎 신전 범위는 줄어든다.</t>
+  </si>
+  <si>
+    <t>· 다만 햄스트링 종목은 아니다 — 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀐다. 능동 단축이 작으면 자극도 작다.</t>
+  </si>
+  <si>
+    <t>· 그래서 주동근은 둔근으로 잡고 사두 0.33 · 햄스트링 0.2 · 내전근 0.2를 간접으로 계상했다. 후면을 노린다는 의도는 둔근 직접 4세트로 실현된다.</t>
+  </si>
+  <si>
+    <t>· 햄스트링 쪽을 직접 때리는 것은 루마니안 데드(늘어난 구간) · 레그 컬(짧아진 구간) · 토요일 원 레그 컬(편측)이다.</t>
+  </si>
+  <si>
+    <t>· 토요일 레그 프레스(발 낮게 · 사두)와 같은 종목 다른 자리다. 사두에도 간접 1.5세트치가 붙어 사두가 주 1회에서 '주 1회 + 간접 1회'가 됐다.</t>
   </si>
   <si>
     <t>[데드리프트 운용 규칙]</t>
@@ -3523,19 +3565,19 @@
     <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
   </si>
   <si>
-    <t>· 31세트 · 약 82분. 여섯 날 중 둘째로 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
-  </si>
-  <si>
-    <t>· 고립 19세트를 빼면 실질 12세트다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
+    <t>· 32세트 · 약 87분. 여섯 날 중 둘째로 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
+  </si>
+  <si>
+    <t>· 고립 19세트를 빼면 실질 13세트다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
   </si>
   <si>
     <t>· 레그 컬 +75초 · 레터럴 +60초. 마지막 세트에만 2단.</t>
   </si>
   <si>
-    <t>· 데드 · 백오프 · 루마니안에는 걸지 않는다 — 척추가 버티는 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고</t>
+    <t>· 데드 · 백오프 · 루마니안 · 레그 프레스에는 걸지 않는다 — 척추가 버티거나 중량이 큰 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고  /  수 하체에는 레그 프레스 넣어주고, 수요일에 하는 레그 프레스는 발을 발판의 가장 위쪽에 두어서 햄스트링 후면을 타겟하도록 할거야. 동시에 사두도 좀 타겟되겠지만.</t>
   </si>
   <si>
     <t>목요일 — 등(승모·능형) · 가슴 · 팔</t>
@@ -3712,6 +3754,9 @@
     <t>머리 위 프레스 중 측면삼각 능동 외전</t>
   </si>
   <si>
+    <t>발을 발판 위쪽에 둬도 무릎 신전은 남는다 — 부분 협력. 사두 직접은 토요일에 12세트가 있고 이 줄 덕에 사두 노출이 주 2회가 된다 (2026-10-02)</t>
+  </si>
+  <si>
     <t>넓은 그립 로우의 광배 관여 — 주동근(능형 · 중부승모)은 직접으로 센다 (2026-09-04 전환)</t>
   </si>
   <si>
@@ -3778,9 +3823,15 @@
     <t>톱세트와 같은 동작 (2026-10-02 백오프 복귀)</t>
   </si>
   <si>
+    <t>발을 높이면 고관절 신전 비중이 오르지만 무릎도 같이 펴진다 — 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 햄스트링 길이가 거의 안 바뀌고, 능동 단축이 작으면 자극도 작다. 그래서 주동근은 둔근이고 햄스트링은 약관여다 (2026-10-02 사용자 지정 종목)</t>
+  </si>
+  <si>
     <t>벌어진 스탠스 구간 약관여</t>
   </si>
   <si>
+    <t>벌어진 스탠스 구간 약관여 — 토요일 레그 프레스와 같은 등급 (2026-10-02)</t>
+  </si>
+  <si>
     <t>복귀_화_팔</t>
   </si>
   <si>
@@ -3844,16 +3895,16 @@
     <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 출처 없음 — 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블로 저항곡선을 갈랐다</t>
   </si>
   <si>
-    <t>직접 12세트: 토요일 스쿼트 5 · 레그 프레스 4 · 레그 익스텐션 3. 간접 출처 없음. 전면 하체가 한 날에 다 들어가 주 1회다 — 스쿼트 5×5가 있어 쪼갤 자리가 없다</t>
+    <t>직접 12세트: 토요일 스쿼트 5 · 레그 프레스 4 · 레그 익스텐션 3. 간접 1.3 — 수요일 레그 프레스(발 높게) 0.33×4. 직접은 주 1회다(스쿼트 5×5가 한 날을 다 쓴다) — 다만 수요일 간접 덕에 자극 노출은 주 2회가 됐다 (2026-10-02)</t>
   </si>
   <si>
     <t>하체 합산(대퇴 · 햄 · 종아리)</t>
   </si>
   <si>
-    <t>직접 10세트: 수요일 루마니안 데드 3 · 레그 컬 4 · 시티드 레그 컬 3. 간접 3.0 — 힙 쓰러스트 0.5×3 + 데드 0.5×1 + 백오프 0.5×2. 굴곡(컬 7)과 신전(힌지 3)을 같이 둬 두 기능을 다 쓴다</t>
-  </si>
-  <si>
-    <t>직접 3세트: 수요일 힙 쓰러스트 3. 간접 6.8 — 스쿼트 0.5×5 + 루마니안 0.5×3 + 데드 0.5×1 + 백오프 0.5×2 + 레그 프레스 0.33×4. 간접이 두 배라 직접 3으로 충분하다</t>
+    <t>직접 10세트: 수요일 루마니안 데드 3 · 레그 컬 4 + 토요일 원 레그 컬 3(편측). 간접 3.8 — 힙 쓰러스트 0.5×3 + 백오프 0.5×2 + 데드 0.5×1 + 레그 프레스(발 높게) 0.2×4. [2026-10-02 사용자 지적] 전면 하체 날에 햄스트링이 0이라 원 레그 컬 3을 토요일로 옮겨 빈도를 주 2회로 쪼갰다 — 총량 10은 그대로다(내가 넣었던 시티드 레그 컬 3을 뺐다)</t>
+  </si>
+  <si>
+    <t>직접 7세트: 수요일 레그 프레스(발 높게) 4 · 힙 쓰러스트 3 (3 → 7). 간접 6.8 — 스쿼트 0.5×5 + 루마니안 0.5×3 + 데드 0.5×1 + 백오프 0.5×2 + 토요일 레그 프레스 0.33×4. [2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 두면 고관절 굽힘 범위가 커져 고관절 신전 비중이 오르고, 둔근이 그 동작의 주동근이다. 햄스트링은 무릎이 같이 펴져 길이가 거의 안 바뀌므로 약관여(0.2)로 뒀다</t>
   </si>
   <si>
     <t>직접 7세트: 토요일 아우터 타이 4 · 수요일 케이블 힙 외전 3. 간접 출처 없음 — 스쿼트 · 레그 프레스는 양측 지지라 계수가 없다. 8 → 7은 날을 가르며 생긴 차이이고 빈도는 1 → 2회가 됐다</t>
@@ -3874,7 +3925,7 @@
     <t>직접 6세트: 화요일 중량 크런치 3 · 라잉 레그 레이즈 3 (3 → 6). 간접 출처 없음 — 스쿼트 · 데드의 브레이싱은 등척성이라 0. 현장 일이 코어를 버티게만 하던 것이 끝나 직접 굴곡을 늘렸다</t>
   </si>
   <si>
-    <t>직접 4세트: 토요일 이너 타이 4 (아우터와 슈퍼세트). 간접 1.8 — 스쿼트 0.2×5 + 레그 프레스 0.2×4. 복귀판 초안에 통째로 비어 있던 자리이고 2026-09-13에 되살렸다</t>
+    <t>직접 4세트: 토요일 이너 타이 4 (아우터와 슈퍼세트). 간접 2.6 — 스쿼트 0.2×5 + 레그 프레스 2종 각 0.2×4 (토 발 낮게 · 수 발 높게). 복귀판 초안에 통째로 비어 있던 자리이고 2026-09-13에 되살렸다</t>
   </si>
   <si>
     <t>직접 6세트: 화요일 넥 익스텐션 3 · 넥 플렉션 3. 2026-10-02 신설 — 사용자 요청으로 화요일 구성에 들어 있었다. 간접 출처 없음. 데드 · 슈러그의 목 지지는 등척성이라 계수를 주지 않는다. 첫 2주는 무게 없이 가동범위만</t>
@@ -3925,6 +3976,9 @@
     <t>· 중둔근 7.0 — 하한 근처다. 유지는 되나 성장 여지는 없다. 아우터 타이를 5세트로 되돌리면 8이 된다.</t>
   </si>
   <si>
+    <t>· 둔근 14.0 · 햄스트링 14.0 — 2026-10-02에 둘 다 올라왔다(둔근 10 → 14 · 햄 13 → 14). 수요일이 고관절 신전 넷(데드 · 루마니안 · 발 높은 레그 프레스 · 힙 쓰러스트)을 다 가진 날이 됐기 때문이다. 둘 다 성장 구간 안이고 천장까지 여유가 있다.</t>
+  </si>
+  <si>
     <t>· 삼각근 측면 11.5 · 후면 10.0 — 셋으로 나눠 주 3회 빈도가 됐다. 세트는 그대로인데 자극 빈도만 올랐다.</t>
   </si>
   <si>
@@ -3940,7 +3994,10 @@
     <t>· 다시 걸고 싶으면 J2에 수를, K3에 '상태'를 되살리면 시트와 앱이 그대로 돌아온다.</t>
   </si>
   <si>
-    <t>· 상한 이력 — 2026-09-13 최초 136 · 09-14 145 · 09-14 제거(당시 147) · 10-02 주 6회 개편으로 164.</t>
+    <t>· 상한 이력 — 2026-09-13 최초 136 · 09-14 145 · 09-14 제거(당시 147) · 10-02 주 6회 개편으로 164 → 같은 날 사용자 추가 둘(원 레그 컬 3 · 발 높은 레그 프레스 4, 시티드 레그 컬 −3)로 168.</t>
+  </si>
+  <si>
+    <t>· 168은 사용자가 고른 밴드(155~165)를 3 넘는다. 상한이 없으므로 금지는 아니고 기록이다 — 밴드로 되돌리려면 레그 익스텐션 3 → 2(수요일 레그 프레스가 사두 간접을 얹어 줬다) 또는 힙 쓰러스트 3 → 2(둔근 직접이 4 더 생겼다)가 가장 값이 싸다.</t>
   </si>
   <si>
     <t>· 세트를 계수로 일괄 조정하지 않는다. 늘릴 때도 줄일 때도 종목 단위로, 근거를 F열에 달아 움직인다.</t>
@@ -10885,7 +10942,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10949,8 +11006,8 @@
         <v>916</v>
       </c>
       <c r="E6" s="121">
-        <f>복귀_토_하체전면!$E$23</f>
-        <v>34</v>
+        <f>복귀_토_하체전면!$E$24</f>
+        <v>37</v>
       </c>
       <c r="F6" s="113" t="s">
         <v>917</v>
@@ -11046,7 +11103,7 @@
       </c>
       <c r="E10" s="121">
         <f>복귀_수_하체후면!$E$33</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="113" t="s">
         <v>937</v>
@@ -11111,7 +11168,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="115">
         <f>SUM(E6:E12)</f>
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F13" s="115" t="s">
         <v>946</v>
@@ -11148,13 +11205,13 @@
         <v>952</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="107" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="123" t="s">
         <v>953</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="107" t="s">
         <v>954</v>
       </c>
     </row>
@@ -11178,18 +11235,18 @@
         <v>958</v>
       </c>
     </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="123" t="s">
+        <v>959</v>
+      </c>
+    </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="107" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="123" t="s">
+      <c r="A29" s="123" t="s">
         <v>960</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="123" t="s">
+      <c r="A31" s="107" t="s">
         <v>961</v>
       </c>
     </row>
@@ -11203,18 +11260,18 @@
         <v>963</v>
       </c>
     </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="123" t="s">
+        <v>964</v>
+      </c>
+    </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="107" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="123" t="s">
+      <c r="A35" s="123" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="123" t="s">
+      <c r="A37" s="107" t="s">
         <v>966</v>
       </c>
     </row>
@@ -11233,18 +11290,18 @@
         <v>969</v>
       </c>
     </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="123" t="s">
+        <v>970</v>
+      </c>
+    </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="107" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="123" t="s">
+      <c r="A42" s="123" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="123" t="s">
+      <c r="A44" s="107" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11258,18 +11315,18 @@
         <v>974</v>
       </c>
     </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="123" t="s">
+        <v>975</v>
+      </c>
+    </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="107" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="123" t="s">
+      <c r="A48" s="123" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="123" t="s">
+      <c r="A50" s="107" t="s">
         <v>977</v>
       </c>
     </row>
@@ -11281,6 +11338,16 @@
     <row r="52" spans="1:1">
       <c r="A52" s="123" t="s">
         <v>979</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="123" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="123" t="s">
+        <v>981</v>
       </c>
     </row>
   </sheetData>
@@ -11291,7 +11358,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -11311,7 +11378,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -11466,14 +11533,14 @@
         <v>180</v>
       </c>
       <c r="I14" s="111">
-        <f t="shared" ref="I14:I22" si="0">IF(E14=0,0,ROUND((E14*(G14+H14)+N14)/60,1))</f>
+        <f t="shared" ref="I14:I23" si="0">IF(E14=0,0,ROUND((E14*(G14+H14)+N14)/60,1))</f>
         <v>17.5</v>
       </c>
       <c r="J14" s="112" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="K14" s="112" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="L14" s="111" t="s">
         <v>356</v>
@@ -11511,10 +11578,10 @@
         <v>13</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -11550,10 +11617,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -11591,7 +11658,7 @@
         <v>8</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="K17" s="114" t="s">
         <v>597</v>
@@ -11630,10 +11697,10 @@
         <v>7.7</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -11646,7 +11713,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="114" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C19" s="113" t="s">
         <v>372</v>
@@ -11671,10 +11738,10 @@
         <v>7.7</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -11712,10 +11779,10 @@
         <v>3.3</v>
       </c>
       <c r="J20" s="114" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="K20" s="114" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="L20" s="113"/>
       <c r="M20" s="113" t="s">
@@ -11753,10 +11820,10 @@
         <v>10.7</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="K21" s="114" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="L21" s="113"/>
       <c r="M21" s="113" t="s">
@@ -11769,122 +11836,171 @@
         <v>9</v>
       </c>
       <c r="B22" s="114" t="s">
-        <v>502</v>
+        <v>576</v>
       </c>
       <c r="C22" s="113" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="D22" s="113">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E22" s="113">
         <v>3</v>
       </c>
-      <c r="F22" s="113" t="s">
-        <v>303</v>
+      <c r="F22" s="113">
+        <v>10</v>
       </c>
       <c r="G22" s="113">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H22" s="113">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="I22" s="113">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="114" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K22" s="114" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="L22" s="113"/>
       <c r="M22" s="113"/>
       <c r="N22" s="113"/>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="115"/>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115" t="s">
+    <row r="23" spans="1:14" ht="30" customHeight="1">
+      <c r="A23" s="113">
+        <v>10</v>
+      </c>
+      <c r="B23" s="114" t="s">
+        <v>502</v>
+      </c>
+      <c r="C23" s="113" t="s">
+        <v>322</v>
+      </c>
+      <c r="D23" s="113">
+        <v>8</v>
+      </c>
+      <c r="E23" s="113">
+        <v>3</v>
+      </c>
+      <c r="F23" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="G23" s="113">
+        <v>40</v>
+      </c>
+      <c r="H23" s="113">
+        <v>75</v>
+      </c>
+      <c r="I23" s="113">
+        <f t="shared" si="0"/>
+        <v>5.8</v>
+      </c>
+      <c r="J23" s="114" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K23" s="114" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L23" s="113"/>
+      <c r="M23" s="113"/>
+      <c r="N23" s="113"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="115"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="115" t="s">
         <v>335</v>
       </c>
-      <c r="E23" s="115">
-        <f>SUM(E14:E22)</f>
-        <v>34</v>
-      </c>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115">
-        <f>ROUND(SUM(I14:I22),0)</f>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="107" t="s">
-        <v>999</v>
+      <c r="E24" s="115">
+        <f>SUM(E14:E23)</f>
+        <v>37</v>
+      </c>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="115">
+        <f>ROUND(SUM(I14:I23),0)</f>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="116" t="s">
-        <v>1000</v>
+      <c r="A26" s="107" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1003</v>
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="116" t="s">
+        <v>1007</v>
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="107" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="116" t="s">
-        <v>1004</v>
+      <c r="A31" s="116" t="s">
+        <v>1008</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="116" t="s">
-        <v>1005</v>
+      <c r="A33" s="107" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="116" t="s">
+        <v>1009</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="107" t="s">
-        <v>1006</v>
+      <c r="A35" s="116" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="116" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="116" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="116" t="s">
-        <v>1009</v>
+      <c r="A38" s="107" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="116" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="C40" s="117" t="s">
-        <v>1010</v>
+      <c r="A40" s="116" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="116" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="C43" s="117" t="s">
+        <v>1016</v>
       </c>
     </row>
   </sheetData>
@@ -11915,27 +12031,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="118" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12017,13 +12133,13 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="L11" s="113" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="M11" s="113"/>
       <c r="N11" s="113"/>
@@ -12033,7 +12149,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="114" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C12" s="113" t="s">
         <v>281</v>
@@ -12058,10 +12174,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -12072,7 +12188,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C13" s="113" t="s">
         <v>281</v>
@@ -12097,10 +12213,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -12138,10 +12254,10 @@
         <v>9</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -12177,10 +12293,10 @@
         <v>5.8</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -12216,10 +12332,10 @@
         <v>6.8</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -12257,10 +12373,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -12289,92 +12405,92 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="116" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="116" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="C41" s="117" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
@@ -12405,7 +12521,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12491,7 +12607,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="118" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12579,10 +12695,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="112" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="K18" s="112" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="L18" s="111" t="s">
         <v>356</v>
@@ -12620,10 +12736,10 @@
         <v>12.7</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -12659,10 +12775,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J20" s="114" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="K20" s="114" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="L20" s="113"/>
       <c r="M20" s="113"/>
@@ -12698,13 +12814,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="K21" s="114" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="L21" s="113" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="M21" s="113"/>
       <c r="N21" s="113"/>
@@ -12714,13 +12830,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="114" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C22" s="113" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="113" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="E22" s="113">
         <v>3</v>
@@ -12739,10 +12855,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="114" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="K22" s="114" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="L22" s="113"/>
       <c r="M22" s="113"/>
@@ -12759,7 +12875,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="113" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="E23" s="113">
         <v>3</v>
@@ -12778,10 +12894,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -12808,77 +12924,77 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="116" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="116" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="117" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
   </sheetData>
@@ -12909,22 +13025,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13011,10 +13127,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="L11" s="113"/>
       <c r="M11" s="113"/>
@@ -13052,10 +13168,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -13091,10 +13207,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -13105,7 +13221,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>309</v>
@@ -13130,10 +13246,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -13169,10 +13285,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -13183,7 +13299,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="114" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>939</v>
@@ -13208,10 +13324,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -13222,7 +13338,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="114" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>939</v>
@@ -13247,10 +13363,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -13286,10 +13402,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -13325,10 +13441,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -13355,87 +13471,87 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="116" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="116" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="C42" s="117" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -14127,7 +14243,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -14147,7 +14263,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14228,7 +14344,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14382,10 +14498,10 @@
         <v>3.5</v>
       </c>
       <c r="J22" s="112" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="K22" s="112" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="L22" s="111"/>
       <c r="M22" s="111"/>
@@ -14396,7 +14512,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="114" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="C23" s="113" t="s">
         <v>327</v>
@@ -14422,10 +14538,10 @@
         <v>7</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -14442,7 +14558,7 @@
         <v>398</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="E24" s="113">
         <v>3</v>
@@ -14461,10 +14577,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J24" s="114" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="K24" s="114" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="L24" s="113"/>
       <c r="M24" s="113"/>
@@ -14475,57 +14591,55 @@
         <v>4</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>397</v>
+        <v>1130</v>
       </c>
       <c r="C25" s="113" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D25" s="113">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="E25" s="113">
         <v>4</v>
       </c>
       <c r="F25" s="113" t="s">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="G25" s="113">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H25" s="113">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I25" s="113">
         <f t="shared" si="0"/>
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="J25" s="114" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="K25" s="114" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="L25" s="113"/>
       <c r="M25" s="113"/>
-      <c r="N25" s="113">
-        <v>75</v>
-      </c>
+      <c r="N25" s="113"/>
     </row>
     <row r="26" spans="1:14" ht="30" customHeight="1">
       <c r="A26" s="113">
         <v>5</v>
       </c>
       <c r="B26" s="114" t="s">
-        <v>1126</v>
+        <v>397</v>
       </c>
       <c r="C26" s="113" t="s">
         <v>398</v>
       </c>
       <c r="D26" s="113">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E26" s="113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="113" t="s">
         <v>364</v>
@@ -14538,111 +14652,115 @@
       </c>
       <c r="I26" s="113">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11.9</v>
       </c>
       <c r="J26" s="114" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="K26" s="114" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="L26" s="113"/>
       <c r="M26" s="113"/>
-      <c r="N26" s="113"/>
+      <c r="N26" s="113">
+        <v>75</v>
+      </c>
     </row>
     <row r="27" spans="1:14" ht="30" customHeight="1">
-      <c r="A27" s="113">
+      <c r="A27" s="111">
         <v>6</v>
       </c>
-      <c r="B27" s="114" t="s">
-        <v>570</v>
-      </c>
-      <c r="C27" s="113" t="s">
-        <v>389</v>
-      </c>
-      <c r="D27" s="113">
-        <v>25</v>
-      </c>
-      <c r="E27" s="113">
-        <v>3</v>
-      </c>
-      <c r="F27" s="113" t="s">
-        <v>364</v>
-      </c>
-      <c r="G27" s="113">
-        <v>40</v>
-      </c>
-      <c r="H27" s="113">
-        <v>120</v>
-      </c>
-      <c r="I27" s="113">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="J27" s="114" t="s">
-        <v>1129</v>
-      </c>
-      <c r="K27" s="114" t="s">
-        <v>1130</v>
-      </c>
-      <c r="L27" s="113"/>
-      <c r="M27" s="113"/>
-      <c r="N27" s="113"/>
-    </row>
-    <row r="28" spans="1:14" ht="30" customHeight="1">
-      <c r="A28" s="111">
-        <v>7</v>
-      </c>
-      <c r="B28" s="112" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C28" s="111" t="s">
+      <c r="B27" s="112" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C27" s="111" t="s">
         <v>443</v>
       </c>
-      <c r="D28" s="111">
+      <c r="D27" s="111">
         <f>시작중량_설정!$E$10</f>
         <v>26</v>
       </c>
-      <c r="E28" s="111">
+      <c r="E27" s="111">
         <v>3</v>
       </c>
-      <c r="F28" s="111">
+      <c r="F27" s="111">
         <v>5</v>
       </c>
-      <c r="G28" s="111">
+      <c r="G27" s="111">
         <v>30</v>
       </c>
-      <c r="H28" s="111">
+      <c r="H27" s="111">
         <v>180</v>
       </c>
-      <c r="I28" s="111">
+      <c r="I27" s="111">
         <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
-      <c r="J28" s="112" t="s">
-        <v>1132</v>
-      </c>
-      <c r="K28" s="112" t="s">
-        <v>1133</v>
-      </c>
-      <c r="L28" s="111" t="s">
+      <c r="J27" s="112" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K27" s="112" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L27" s="111" t="s">
         <v>521</v>
       </c>
-      <c r="M28" s="111"/>
-      <c r="N28" s="111"/>
+      <c r="M27" s="111"/>
+      <c r="N27" s="111"/>
+    </row>
+    <row r="28" spans="1:14" ht="30" customHeight="1">
+      <c r="A28" s="113">
+        <v>7</v>
+      </c>
+      <c r="B28" s="114" t="s">
+        <v>367</v>
+      </c>
+      <c r="C28" s="113" t="s">
+        <v>368</v>
+      </c>
+      <c r="D28" s="113">
+        <v>8</v>
+      </c>
+      <c r="E28" s="113">
+        <v>3</v>
+      </c>
+      <c r="F28" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="G28" s="113">
+        <v>40</v>
+      </c>
+      <c r="H28" s="113">
+        <v>60</v>
+      </c>
+      <c r="I28" s="113">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="J28" s="114" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K28" s="114" t="s">
+        <v>991</v>
+      </c>
+      <c r="L28" s="113"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="113">
+        <v>60</v>
+      </c>
     </row>
     <row r="29" spans="1:14" ht="30" customHeight="1">
       <c r="A29" s="113">
         <v>8</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>367</v>
+        <v>537</v>
       </c>
       <c r="C29" s="113" t="s">
-        <v>368</v>
-      </c>
-      <c r="D29" s="113">
-        <v>8</v>
+        <v>372</v>
+      </c>
+      <c r="D29" s="113" t="s">
+        <v>298</v>
       </c>
       <c r="E29" s="113">
         <v>3</v>
@@ -14658,54 +14776,52 @@
       </c>
       <c r="I29" s="113">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J29" s="114" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="K29" s="114" t="s">
-        <v>989</v>
+        <v>1140</v>
       </c>
       <c r="L29" s="113"/>
       <c r="M29" s="113"/>
-      <c r="N29" s="113">
-        <v>60</v>
-      </c>
+      <c r="N29" s="113"/>
     </row>
     <row r="30" spans="1:14" ht="30" customHeight="1">
       <c r="A30" s="113">
         <v>9</v>
       </c>
       <c r="B30" s="114" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="C30" s="113" t="s">
-        <v>372</v>
-      </c>
-      <c r="D30" s="113" t="s">
-        <v>298</v>
+        <v>389</v>
+      </c>
+      <c r="D30" s="113">
+        <v>25</v>
       </c>
       <c r="E30" s="113">
         <v>3</v>
       </c>
       <c r="F30" s="113" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="G30" s="113">
         <v>40</v>
       </c>
       <c r="H30" s="113">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I30" s="113">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J30" s="114" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="K30" s="114" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="L30" s="113"/>
       <c r="M30" s="113"/>
@@ -14741,10 +14857,10 @@
         <v>6.8</v>
       </c>
       <c r="J31" s="114" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="K31" s="114" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="L31" s="113"/>
       <c r="M31" s="113"/>
@@ -14780,10 +14896,10 @@
         <v>5.8</v>
       </c>
       <c r="J32" s="114" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="K32" s="114" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="L32" s="113"/>
       <c r="M32" s="113"/>
@@ -14798,124 +14914,164 @@
       </c>
       <c r="E33" s="115">
         <f>SUM(E22:E32)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F33" s="115"/>
       <c r="G33" s="115"/>
       <c r="H33" s="115"/>
       <c r="I33" s="115">
         <f>ROUND(SUM(I22:I32),0)</f>
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="107" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="116" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="116" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="116" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="116" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="116" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="107" t="s">
-        <v>1147</v>
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="116" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="116" t="s">
-        <v>1148</v>
+      <c r="A43" s="107" t="s">
+        <v>1154</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="116" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="116" t="s">
-        <v>1150</v>
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="116" t="s">
+        <v>1157</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="107" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="116" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="116" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="A47" s="116" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="107" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
       <c r="A50" s="116" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="107" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="116" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="116" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
       <c r="A53" s="116" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
       <c r="A54" s="116" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
       <c r="A56" s="107" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
       <c r="A57" s="116" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
       <c r="A58" s="116" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
       <c r="A59" s="116" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="C61" s="117" t="s">
-        <v>1159</v>
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="107" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="116" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="116" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="107" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="116" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="116" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="116" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="C70" s="117" t="s">
+        <v>1173</v>
       </c>
     </row>
   </sheetData>
@@ -14946,27 +15102,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1160</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1161</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="118" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15023,7 +15179,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="114" t="s">
-        <v>1162</v>
+        <v>1176</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>296</v>
@@ -15048,13 +15204,13 @@
         <v>12.7</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1163</v>
+        <v>1177</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1164</v>
+        <v>1178</v>
       </c>
       <c r="L11" s="113" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="M11" s="113"/>
       <c r="N11" s="113"/>
@@ -15089,10 +15245,10 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1165</v>
+        <v>1179</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1166</v>
+        <v>1180</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -15128,10 +15284,10 @@
         <v>6.8</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1167</v>
+        <v>1181</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -15169,10 +15325,10 @@
         <v>6.5</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1169</v>
+        <v>1183</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1170</v>
+        <v>1184</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -15208,10 +15364,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1171</v>
+        <v>1185</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1172</v>
+        <v>1186</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -15247,10 +15403,10 @@
         <v>10.7</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1173</v>
+        <v>1187</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1174</v>
+        <v>1188</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -15263,7 +15419,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="114" t="s">
-        <v>1175</v>
+        <v>1189</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>359</v>
@@ -15288,10 +15444,10 @@
         <v>5.5</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1176</v>
+        <v>1190</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1177</v>
+        <v>1191</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -15302,7 +15458,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="114" t="s">
-        <v>1178</v>
+        <v>1192</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>283</v>
@@ -15327,10 +15483,10 @@
         <v>5.8</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>1179</v>
+        <v>1193</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>1180</v>
+        <v>1194</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -15357,87 +15513,87 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="107" t="s">
-        <v>1181</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="116" t="s">
-        <v>1182</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1183</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1184</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1185</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1186</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1187</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="107" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="116" t="s">
-        <v>1189</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1190</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="107" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="116" t="s">
-        <v>1191</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1192</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1193</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="C41" s="117" t="s">
-        <v>1194</v>
+        <v>1208</v>
       </c>
     </row>
   </sheetData>
@@ -15824,7 +15980,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -15838,12 +15994,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1195</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1196</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -15857,12 +16013,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1197</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="110" t="s">
-        <v>1198</v>
+        <v>1212</v>
       </c>
       <c r="B6" s="110" t="s">
         <v>652</v>
@@ -15888,7 +16044,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B7" s="114" t="s">
         <v>97</v>
@@ -15911,12 +16067,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="114" t="s">
-        <v>1200</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B8" s="114" t="s">
         <v>531</v>
@@ -15939,12 +16095,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="114" t="s">
-        <v>1200</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B9" s="114" t="s">
         <v>357</v>
@@ -15967,12 +16123,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="114" t="s">
-        <v>1201</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="113" t="s">
-        <v>1202</v>
+        <v>1216</v>
       </c>
       <c r="B10" s="114" t="s">
         <v>522</v>
@@ -15995,15 +16151,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="114" t="s">
-        <v>1200</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="113" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B11" s="114" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>359</v>
@@ -16023,12 +16179,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="114" t="s">
-        <v>1200</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="113" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="B12" s="114" t="s">
         <v>280</v>
@@ -16051,15 +16207,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="114" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="113" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C13" s="113" t="s">
         <v>283</v>
@@ -16079,15 +16235,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="114" t="s">
-        <v>1206</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="113" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>283</v>
@@ -16107,12 +16263,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="114" t="s">
-        <v>1207</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="113" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="B15" s="114" t="s">
         <v>486</v>
@@ -16135,15 +16291,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="114" t="s">
-        <v>1208</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="113" t="s">
-        <v>1209</v>
+        <v>1223</v>
       </c>
       <c r="B16" s="114" t="s">
-        <v>1162</v>
+        <v>1176</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>283</v>
@@ -16163,12 +16319,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="114" t="s">
-        <v>1210</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="113" t="s">
-        <v>1209</v>
+        <v>1223</v>
       </c>
       <c r="B17" s="114" t="s">
         <v>479</v>
@@ -16191,12 +16347,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="114" t="s">
-        <v>1211</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B18" s="114" t="s">
         <v>97</v>
@@ -16219,12 +16375,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="114" t="s">
-        <v>1212</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B19" s="114" t="s">
         <v>531</v>
@@ -16247,12 +16403,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="114" t="s">
-        <v>1213</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B20" s="114" t="s">
         <v>357</v>
@@ -16275,12 +16431,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="114" t="s">
-        <v>1214</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B21" s="114" t="s">
         <v>600</v>
@@ -16303,12 +16459,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="114" t="s">
-        <v>1215</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="113" t="s">
-        <v>1209</v>
+        <v>1223</v>
       </c>
       <c r="B22" s="114" t="s">
         <v>441</v>
@@ -16331,15 +16487,15 @@
         <v>673</v>
       </c>
       <c r="H22" s="114" t="s">
-        <v>1216</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="113" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B23" s="114" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C23" s="113" t="s">
         <v>368</v>
@@ -16359,21 +16515,21 @@
         <v>673</v>
       </c>
       <c r="H23" s="114" t="s">
-        <v>1217</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="113" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="B24" s="114" t="s">
-        <v>1162</v>
+        <v>1130</v>
       </c>
       <c r="C24" s="113" t="s">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="D24" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E24" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16381,21 +16537,21 @@
       </c>
       <c r="F24" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="G24" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H24" s="114" t="s">
-        <v>1218</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5">
       <c r="A25" s="113" t="s">
-        <v>1209</v>
+        <v>1223</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>479</v>
+        <v>1176</v>
       </c>
       <c r="C25" s="113" t="s">
         <v>281</v>
@@ -16405,81 +16561,81 @@
       </c>
       <c r="E25" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G25" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H25" s="114" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="113" t="s">
-        <v>1203</v>
+        <v>1223</v>
       </c>
       <c r="B26" s="114" t="s">
-        <v>95</v>
+        <v>479</v>
       </c>
       <c r="C26" s="113" t="s">
         <v>281</v>
       </c>
       <c r="D26" s="113">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G26" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H26" s="114" t="s">
-        <v>1219</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="113" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B27" s="114" t="s">
-        <v>1131</v>
+        <v>95</v>
       </c>
       <c r="C27" s="113" t="s">
-        <v>421</v>
+        <v>281</v>
       </c>
       <c r="D27" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G27" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H27" s="114" t="s">
-        <v>1220</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="113" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="B28" s="114" t="s">
-        <v>1162</v>
+        <v>1135</v>
       </c>
       <c r="C28" s="113" t="s">
         <v>421</v>
@@ -16489,25 +16645,25 @@
       </c>
       <c r="E28" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G28" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H28" s="114" t="s">
-        <v>1221</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="113" t="s">
-        <v>1203</v>
+        <v>1223</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>95</v>
+        <v>1176</v>
       </c>
       <c r="C29" s="113" t="s">
         <v>421</v>
@@ -16517,53 +16673,53 @@
       </c>
       <c r="E29" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G29" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H29" s="114" t="s">
-        <v>1222</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="113" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="B30" s="114" t="s">
-        <v>280</v>
+        <v>95</v>
       </c>
       <c r="C30" s="113" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D30" s="113">
         <v>0.2</v>
       </c>
       <c r="E30" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="G30" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H30" s="114" t="s">
-        <v>1223</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="113" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="B31" s="114" t="s">
-        <v>1022</v>
+        <v>280</v>
       </c>
       <c r="C31" s="113" t="s">
         <v>432</v>
@@ -16573,25 +16729,25 @@
       </c>
       <c r="E31" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H31" s="114" t="s">
-        <v>1224</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="113" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="B32" s="114" t="s">
-        <v>1019</v>
+        <v>1028</v>
       </c>
       <c r="C32" s="113" t="s">
         <v>432</v>
@@ -16601,59 +16757,59 @@
       </c>
       <c r="E32" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G32" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H32" s="114" t="s">
-        <v>1225</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="113" t="s">
-        <v>1199</v>
+        <v>1218</v>
       </c>
       <c r="B33" s="114" t="s">
-        <v>424</v>
+        <v>1025</v>
       </c>
       <c r="C33" s="113" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="D33" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E33" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G33" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H33" s="114" t="s">
-        <v>1226</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="113" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
       <c r="B34" s="114" t="s">
-        <v>537</v>
+        <v>424</v>
       </c>
       <c r="C34" s="113" t="s">
         <v>296</v>
       </c>
       <c r="D34" s="113">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16661,21 +16817,21 @@
       </c>
       <c r="F34" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G34" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H34" s="114" t="s">
-        <v>1227</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="113" t="s">
-        <v>1202</v>
+        <v>1217</v>
       </c>
       <c r="B35" s="114" t="s">
-        <v>990</v>
+        <v>537</v>
       </c>
       <c r="C35" s="113" t="s">
         <v>296</v>
@@ -16685,81 +16841,81 @@
       </c>
       <c r="E35" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="G35" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H35" s="114" t="s">
-        <v>1227</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="113" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>486</v>
+        <v>992</v>
       </c>
       <c r="C36" s="113" t="s">
         <v>296</v>
       </c>
       <c r="D36" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E36" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="G36" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H36" s="114" t="s">
-        <v>1228</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="113" t="s">
-        <v>1202</v>
+        <v>1218</v>
       </c>
       <c r="B37" s="114" t="s">
-        <v>93</v>
+        <v>486</v>
       </c>
       <c r="C37" s="113" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="D37" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E37" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G37" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H37" s="114" t="s">
-        <v>1229</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="113" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="B38" s="114" t="s">
-        <v>1162</v>
+        <v>93</v>
       </c>
       <c r="C38" s="113" t="s">
         <v>327</v>
@@ -16769,25 +16925,25 @@
       </c>
       <c r="E38" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G38" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H38" s="114" t="s">
-        <v>1230</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="113" t="s">
-        <v>1204</v>
+        <v>1223</v>
       </c>
       <c r="B39" s="114" t="s">
-        <v>431</v>
+        <v>1176</v>
       </c>
       <c r="C39" s="113" t="s">
         <v>327</v>
@@ -16796,26 +16952,26 @@
         <v>0.2</v>
       </c>
       <c r="E39" s="113">
-        <f t="shared" ref="E39:E61" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
-        <v>3</v>
+        <f t="shared" ref="E39:E64" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
+        <v>4</v>
       </c>
       <c r="F39" s="113">
         <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="G39" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H39" s="114" t="s">
-        <v>1231</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="113" t="s">
-        <v>1203</v>
+        <v>1218</v>
       </c>
       <c r="B40" s="114" t="s">
-        <v>573</v>
+        <v>431</v>
       </c>
       <c r="C40" s="113" t="s">
         <v>327</v>
@@ -16835,15 +16991,15 @@
         <v>673</v>
       </c>
       <c r="H40" s="114" t="s">
-        <v>1232</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="113" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="B41" s="114" t="s">
-        <v>498</v>
+        <v>573</v>
       </c>
       <c r="C41" s="113" t="s">
         <v>327</v>
@@ -16863,43 +17019,43 @@
         <v>673</v>
       </c>
       <c r="H41" s="114" t="s">
-        <v>1233</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="113" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
       <c r="B42" s="114" t="s">
-        <v>93</v>
+        <v>498</v>
       </c>
       <c r="C42" s="113" t="s">
-        <v>389</v>
+        <v>327</v>
       </c>
       <c r="D42" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E42" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>2.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G42" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H42" s="114" t="s">
-        <v>695</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="113" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="B43" s="114" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C43" s="113" t="s">
         <v>389</v>
@@ -16909,25 +17065,25 @@
       </c>
       <c r="E43" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F43" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G43" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H43" s="114" t="s">
-        <v>1234</v>
+        <v>695</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="113" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B44" s="114" t="s">
-        <v>1118</v>
+        <v>95</v>
       </c>
       <c r="C44" s="113" t="s">
         <v>389</v>
@@ -16937,84 +17093,84 @@
       </c>
       <c r="E44" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G44" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H44" s="114" t="s">
-        <v>1235</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="113" t="s">
-        <v>1202</v>
+        <v>1217</v>
       </c>
       <c r="B45" s="114" t="s">
-        <v>388</v>
+        <v>1124</v>
       </c>
       <c r="C45" s="113" t="s">
         <v>389</v>
       </c>
       <c r="D45" s="113">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E45" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="G45" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H45" s="114" t="s">
-        <v>696</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="113" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="B46" s="114" t="s">
-        <v>573</v>
+        <v>388</v>
       </c>
       <c r="C46" s="113" t="s">
         <v>389</v>
       </c>
       <c r="D46" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E46" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="G46" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H46" s="114" t="s">
-        <v>1236</v>
+        <v>696</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="113" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B47" s="114" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C47" s="113" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D47" s="113">
         <v>0.5</v>
@@ -17031,15 +17187,15 @@
         <v>673</v>
       </c>
       <c r="H47" s="114" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="113" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B48" s="114" t="s">
-        <v>95</v>
+        <v>570</v>
       </c>
       <c r="C48" s="113" t="s">
         <v>398</v>
@@ -17049,25 +17205,25 @@
       </c>
       <c r="E48" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G48" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H48" s="114" t="s">
-        <v>1238</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="113" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B49" s="114" t="s">
-        <v>1118</v>
+        <v>95</v>
       </c>
       <c r="C49" s="113" t="s">
         <v>398</v>
@@ -17077,35 +17233,35 @@
       </c>
       <c r="E49" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G49" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H49" s="114" t="s">
-        <v>1239</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="113" t="s">
-        <v>1202</v>
+        <v>1217</v>
       </c>
       <c r="B50" s="114" t="s">
-        <v>93</v>
+        <v>1124</v>
       </c>
       <c r="C50" s="113" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D50" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E50" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F50" s="113">
         <f t="shared" ca="1" si="3"/>
@@ -17115,18 +17271,18 @@
         <v>673</v>
       </c>
       <c r="H50" s="114" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="51">
       <c r="A51" s="113" t="s">
-        <v>1202</v>
+        <v>1217</v>
       </c>
       <c r="B51" s="114" t="s">
-        <v>388</v>
+        <v>1130</v>
       </c>
       <c r="C51" s="113" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D51" s="113">
         <v>0.2</v>
@@ -17143,287 +17299,371 @@
         <v>673</v>
       </c>
       <c r="H51" s="114" t="s">
-        <v>1240</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="113" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="B52" s="114" t="s">
-        <v>495</v>
+        <v>93</v>
       </c>
       <c r="C52" s="113" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D52" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E52" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F52" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G52" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H52" s="114" t="s">
-        <v>676</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="113" t="s">
-        <v>1241</v>
+        <v>1216</v>
       </c>
       <c r="B53" s="114" t="s">
-        <v>605</v>
+        <v>388</v>
       </c>
       <c r="C53" s="113" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D53" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E53" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G53" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H53" s="114" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="113" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="B54" s="114" t="s">
-        <v>1178</v>
+        <v>1130</v>
       </c>
       <c r="C54" s="113" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D54" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E54" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G54" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H54" s="114" t="s">
-        <v>1242</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="113" t="s">
-        <v>1199</v>
+        <v>1218</v>
       </c>
       <c r="B55" s="114" t="s">
-        <v>97</v>
+        <v>495</v>
       </c>
       <c r="C55" s="113" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D55" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E55" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F55" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G55" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H55" s="114" t="s">
-        <v>1243</v>
+        <v>676</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="113" t="s">
-        <v>1209</v>
+        <v>1258</v>
       </c>
       <c r="B56" s="114" t="s">
-        <v>441</v>
+        <v>605</v>
       </c>
       <c r="C56" s="113" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D56" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E56" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G56" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H56" s="114" t="s">
-        <v>1244</v>
+        <v>676</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="113" t="s">
-        <v>1199</v>
+        <v>1223</v>
       </c>
       <c r="B57" s="114" t="s">
-        <v>531</v>
+        <v>1192</v>
       </c>
       <c r="C57" s="113" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="D57" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E57" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G57" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H57" s="114" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="113" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="B58" s="114" t="s">
-        <v>600</v>
+        <v>97</v>
       </c>
       <c r="C58" s="113" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D58" s="113">
         <v>0.2</v>
       </c>
       <c r="E58" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G58" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H58" s="114" t="s">
-        <v>1245</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="113" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
       <c r="B59" s="114" t="s">
-        <v>93</v>
+        <v>441</v>
       </c>
       <c r="C59" s="113" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="D59" s="113">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E59" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F59" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G59" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H59" s="114" t="s">
-        <v>1246</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="113" t="s">
-        <v>1202</v>
+        <v>1213</v>
       </c>
       <c r="B60" s="114" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
       <c r="C60" s="113" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="D60" s="113">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E60" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G60" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H60" s="114" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="25.5">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="113" t="s">
-        <v>1241</v>
+        <v>1213</v>
       </c>
       <c r="B61" s="114" t="s">
-        <v>1090</v>
+        <v>600</v>
       </c>
       <c r="C61" s="113" t="s">
-        <v>939</v>
+        <v>351</v>
       </c>
       <c r="D61" s="113">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E61" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G61" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H61" s="114" t="s">
-        <v>1248</v>
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="113" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B62" s="114" t="s">
+        <v>93</v>
+      </c>
+      <c r="C62" s="113" t="s">
+        <v>313</v>
+      </c>
+      <c r="D62" s="113">
+        <v>0</v>
+      </c>
+      <c r="E62" s="113">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F62" s="113">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="113" t="s">
+        <v>673</v>
+      </c>
+      <c r="H62" s="114" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="113" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B63" s="114" t="s">
+        <v>502</v>
+      </c>
+      <c r="C63" s="113" t="s">
+        <v>322</v>
+      </c>
+      <c r="D63" s="113">
+        <v>0</v>
+      </c>
+      <c r="E63" s="113">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F63" s="113">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="113" t="s">
+        <v>673</v>
+      </c>
+      <c r="H63" s="114" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="25.5">
+      <c r="A64" s="113" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B64" s="114" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C64" s="113" t="s">
+        <v>939</v>
+      </c>
+      <c r="D64" s="113">
+        <v>0</v>
+      </c>
+      <c r="E64" s="113">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F64" s="113">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="113" t="s">
+        <v>673</v>
+      </c>
+      <c r="H64" s="114" t="s">
+        <v>1265</v>
       </c>
     </row>
   </sheetData>
@@ -17434,7 +17674,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -17448,12 +17688,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1249</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1250</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -17497,7 +17737,7 @@
         <v>충분</v>
       </c>
       <c r="F5" s="114" t="s">
-        <v>1251</v>
+        <v>1268</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -17528,7 +17768,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="114" t="s">
-        <v>1252</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -17552,10 +17792,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1253</v>
+        <v>1270</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1254</v>
+        <v>1271</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -17583,7 +17823,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1255</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -17607,7 +17847,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>1256</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -17631,7 +17871,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="114" t="s">
-        <v>1257</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -17655,7 +17895,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1258</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -17679,7 +17919,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>1259</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -17703,7 +17943,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>1260</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -17727,7 +17967,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>1261</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -17739,26 +17979,26 @@
         <v>12</v>
       </c>
       <c r="C15" s="113">
-        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A15),0.5)</f>
-        <v>0</v>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A15),0.5)</f>
+        <v>1.5</v>
       </c>
       <c r="D15" s="113">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>13.5</v>
       </c>
       <c r="E15" s="113" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F15" s="114" t="s">
-        <v>1262</v>
+        <v>1279</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1263</v>
+        <v>1280</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
-        <v>31</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
@@ -17771,18 +18011,18 @@
       </c>
       <c r="C16" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A16),0.5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>1264</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -17791,7 +18031,7 @@
       </c>
       <c r="B17" s="113">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A17)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A17)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A17)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A17)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A17)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A17)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A17),0.5)</f>
@@ -17799,14 +18039,14 @@
       </c>
       <c r="D17" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F17" s="114" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -17830,7 +18070,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" s="114" t="s">
-        <v>1266</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -17854,7 +18094,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>1267</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -17878,7 +18118,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="114" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -17902,7 +18142,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="114" t="s">
-        <v>1269</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -17926,7 +18166,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="114" t="s">
-        <v>1270</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -17950,7 +18190,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1271</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -17963,18 +18203,18 @@
       </c>
       <c r="C24" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A24),0.5)</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D24" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E24" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1272</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -17998,7 +18238,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="114" t="s">
-        <v>1273</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18007,11 +18247,11 @@
       </c>
       <c r="B26" s="115">
         <f>SUM(B5:B25)</f>
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D26" s="115">
         <f ca="1">SUM(D5:D25)</f>
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -18021,112 +18261,122 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1274</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1275</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1276</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1277</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1278</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1279</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1280</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1281</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1282</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>1283</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1284</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1285</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1286</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1287</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="123" t="s">
-        <v>1288</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="123" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="107" t="s">
-        <v>1290</v>
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="123" t="s">
+        <v>1307</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="123" t="s">
-        <v>1291</v>
+      <c r="A49" s="107" t="s">
+        <v>1308</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1292</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="123" t="s">
-        <v>1293</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="123" t="s">
-        <v>1294</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1295</v>
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="123" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="123" t="s">
+        <v>1314</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5161D2470C0771BF7ABEB4345A4C9F872E0144CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_27AB22B2FD6E09657726B5396B754EF0E5A5D09F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="1321">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -103,10 +103,10 @@
     <t>주당 환산 161세트</t>
   </si>
   <si>
-    <t>168세트</t>
-  </si>
-  <si>
-    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 둘(원 레그 컬 · 발 높은 레그 프레스)</t>
+    <t>176세트</t>
+  </si>
+  <si>
+    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 셋(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터)</t>
   </si>
   <si>
     <t>증량 방식</t>
@@ -244,7 +244,7 @@
     <t>· 2순위 — 목 2종목(6). 2026-10-02 신설이라 되돌려도 잃을 적응이 없다.</t>
   </si>
   <si>
-    <t>· 3순위 — 레그 익스텐션 3 · 카프 2종 중 하나 3 · 라잉 레그 레이즈 3. 고립이라 메인 리프트 진행에 영향이 없다. 레그 익스텐션은 수요일 레그 프레스가 사두에 간접을 얹어 줘 값이 가장 싸졌다.</t>
+    <t>· 3순위 — 레그 익스텐션 3 · 카프 2종 중 하나 3 · 라잉 레그 레이즈 3. 고립이라 메인 리프트 진행에 영향이 없다. 레그 익스텐션은 수요일 레그 프레스가 사두에 간접을 얹어 줘 값이 가장 싸졌고, 수요일 케이블 힙 외전 3은 같은 날 아우터 타이 4가 같은 근육을 맡으므로 그다음이다.</t>
   </si>
   <si>
     <t>· 마지막까지 지키는 것은 스쿼트 · 벤치 · 오버헤드 프레스 · 데드 톱세트와 가슴 · 등 · 어깨 볼륨이다.</t>
@@ -2869,10 +2869,10 @@
     <t>하체 후면(햄 · 둔) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 87분</t>
-  </si>
-  <si>
-    <t>데드 톱1 + 백오프2 · 레그 프레스는 발을 발판 위쪽에(둔근). 스미스 오버헤드 프레스가 어깨 블록 첫 종목 — 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다</t>
+    <t>약 101분</t>
+  </si>
+  <si>
+    <t>데드 톱1 + 백오프2 · 레그 프레스는 발을 발판 위쪽에(둔근) · 이너 · 아우터 슈퍼세트. 스미스 오버헤드 프레스가 어깨 블록 첫 종목 — 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 자리다</t>
   </si>
   <si>
     <t>목</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 413분 (6시간 53분)</t>
+    <t>약 427분 (7시간 7분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -2923,19 +2923,19 @@
     <t>[빈도를 올리고 볼륨은 조금만 올렸다 — 2026-10-02]</t>
   </si>
   <si>
-    <t>· 주 4회 140세트 → 주 6회 168세트. 세트는 20% 늘었고 가슴 · 등 · 하체 · 햄스트링 빈도가 주 1회 → 2회로 올랐다.</t>
+    <t>· 주 4회 140세트 → 주 6회 176세트. 세트는 26% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 빈도가 주 1회 → 2회로 올랐다.</t>
   </si>
   <si>
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
   </si>
   <si>
-    <t>· [2026-10-02 사용자 추가 둘] 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량을 10으로 유지했다. 164 → 168.</t>
-  </si>
-  <si>
-    <t>· 유지한 곳 — 흉근 24 · 승모 중부 10 · 삼각 측면 10 · 후면 10 · 사두 12 · 햄스트링 10 · 내전근 4. 이미 성장 구간 상단이라 세트는 그대로 두고 빈도만 올렸다.</t>
-  </si>
-  <si>
-    <t>· 줄인 곳 — 삼각 전면 7 → 6 · 중둔근 8 → 7 · 광배 15 → 14. 날을 가르며 세트가 3으로 떨어진 자리이고, 간접이 그만큼 올라 실질은 같거나 높다.</t>
+    <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). 164 → 168 → 176.</t>
+  </si>
+  <si>
+    <t>· 유지한 곳 — 흉근 24 · 승모 중부 10 · 삼각 측면 10 · 후면 10 · 사두 12 · 햄스트링 10. 이미 성장 구간 상단이라 세트는 그대로 두고 빈도만 올렸다.</t>
+  </si>
+  <si>
+    <t>· 줄인 곳 — 삼각 전면 7 → 6 · 광배 15 → 14. 날을 가르며 세트가 3으로 떨어진 자리이고, 간접이 그만큼 올라 실질은 같거나 높다. (중둔근은 8 → 7로 내려갔다가 수요일 아우터 4로 11이 됐다.)</t>
   </si>
   <si>
     <t>· 계수로 전 종목을 일괄 조정하지 않았다. 종목 단위로 근거를 달아 움직였다 — 근거는 복귀_세트검산 아래에 한 줄씩 있다.</t>
@@ -2977,16 +2977,19 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 토 37세트 92분 · 수 32세트 87분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
-  </si>
-  <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 25를 빼면 실질 12, 수요일은 19를 빼면 13, 월요일은 6을 빼면 16이다.</t>
+    <t>· 수 40세트 101분 · 토 37세트 92분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 25를 빼면 실질 12, 수요일은 27을 빼면 13, 월요일은 6을 빼면 16이다.</t>
   </si>
   <si>
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 주 413분 = 6시간 53분. 주 4회 370분에서 43분 늘었다. 토(92) · 수(87)가 가장 크지만 주 4회 시절 토(107) · 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 주 427분 = 7시간 7분. 주 4회 370분에서 57분 늘었다. 수(101) · 토(92)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+  </si>
+  <si>
+    <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
   </si>
   <si>
     <t>[몸 상태가 안 좋으면]</t>
@@ -3487,12 +3490,18 @@
     <t>머신 힙 쓰러스트 / 글루트 브릿지 / 케이블 풀스루</t>
   </si>
   <si>
-    <t>어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤로 보냈다. 토요일 아우터 타이와 합쳐 주 7세트.</t>
+    <t>선 자세 · 편측이라 고관절이 펴진 각도에서 외전한다 — 앉아서 하는 아우터 타이(고관절 굽힘)와 각도가 갈린다. 둘 중 이쪽이 좌우 차가 드러나므로 아우터 타이 앞에 둬 더 신선한 자리를 줬다.</t>
   </si>
   <si>
     <t>머신 힙 어브덕션 / 밴드 사이드 워크</t>
   </si>
   <si>
+    <t>[2026-10-02 사용자 요청 — 토요일과 같은 슈퍼세트를 이 날에도] 내전근 직접이 주 4세트뿐이라 실질 6.5로 하한(8) 아래였다. 이 4세트로 8 → 실질 10.5가 된다. 아우터와 슈퍼세트 — 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 요청] 중둔근 실질 7.0도 하한 아래였다 — 이 4세트로 11이 된다. 앞의 케이블 힙 외전과 같은 근육이므로 중량이 토요일보다 낮게 나오는 것이 정상이다. 어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤에 둔다.</t>
+  </si>
+  <si>
     <t>무릎이 펴져 비복근 비중이 커진다 — 토요일 시티드(가자미근)와 각도를 나눈다. 데드 뒤라 발목이 이미 데워져 있다.</t>
   </si>
   <si>
@@ -3532,7 +3541,10 @@
     <t>· 햄스트링 주 10세트 중 7이 이 날이고 3은 토요일 원 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다.</t>
   </si>
   <si>
-    <t>· 토요일(사두 12 + 햄 3) · 수요일(후면 14 + 중둔근 3 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
+    <t>· 토요일(사두 12 + 햄 3 + 내전근 4 + 중둔근 4) · 수요일(후면 14 + 중둔근 7 + 내전근 4 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 사용자 요청] 이너 · 아우터 타이 슈퍼세트를 이 날에도 넣었다 — 하체에서 유일하게 하한 아래로 남아 있던 내전근(6.5)과 중둔근(7.0)이 둘 다 성장 구간으로 들어간다(10.5 · 11.0). 토요일과 같은 쌍이라 새로 익힐 것이 없다.</t>
   </si>
   <si>
     <t>[레그 프레스를 발 높게 — 2026-10-02 사용자 지정]</t>
@@ -3565,10 +3577,10 @@
     <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
   </si>
   <si>
-    <t>· 32세트 · 약 87분. 여섯 날 중 둘째로 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
-  </si>
-  <si>
-    <t>· 고립 19세트를 빼면 실질 13세트다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
+    <t>· 40세트 · 약 101분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
+  </si>
+  <si>
+    <t>· 고립 27세트를 빼면 실질 13세트다 — 어깨 블록 뒤 14세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 14분밖에 안 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
   </si>
   <si>
     <t>· 레그 컬 +75초 · 레터럴 +60초. 마지막 세트에만 2단.</t>
@@ -3577,7 +3589,10 @@
     <t>· 데드 · 백오프 · 루마니안 · 레그 프레스에는 걸지 않는다 — 척추가 버티거나 중량이 큰 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고  /  수 하체에는 레그 프레스 넣어주고, 수요일에 하는 레그 프레스는 발을 발판의 가장 위쪽에 두어서 햄스트링 후면을 타겟하도록 할거야. 동시에 사두도 좀 타겟되겠지만.</t>
+    <t>· 이너 · 아우터 타이에도 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다(토요일과 같은 이유).</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고  /  수 하체에는 레그 프레스 넣어주고, 수요일에 하는 레그 프레스는 발을 발판의 가장 위쪽에 두어서 햄스트링 후면을 타겟하도록 할거야. 동시에 사두도 좀 타겟되겠지만.  /  그리고 수요일하체에 이너타이랑 아우터타이 슈퍼세트도 넣어줘.</t>
   </si>
   <si>
     <t>목요일 — 등(승모·능형) · 가슴 · 팔</t>
@@ -3907,7 +3922,7 @@
     <t>직접 7세트: 수요일 레그 프레스(발 높게) 4 · 힙 쓰러스트 3 (3 → 7). 간접 6.8 — 스쿼트 0.5×5 + 루마니안 0.5×3 + 데드 0.5×1 + 백오프 0.5×2 + 토요일 레그 프레스 0.33×4. [2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 두면 고관절 굽힘 범위가 커져 고관절 신전 비중이 오르고, 둔근이 그 동작의 주동근이다. 햄스트링은 무릎이 같이 펴져 길이가 거의 안 바뀌므로 약관여(0.2)로 뒀다</t>
   </si>
   <si>
-    <t>직접 7세트: 토요일 아우터 타이 4 · 수요일 케이블 힙 외전 3. 간접 출처 없음 — 스쿼트 · 레그 프레스는 양측 지지라 계수가 없다. 8 → 7은 날을 가르며 생긴 차이이고 빈도는 1 → 2회가 됐다</t>
+    <t>직접 11세트: 토요일 아우터 타이 4 · 수요일 아우터 타이 4 · 케이블 힙 외전 3 (7 → 11). 간접 출처 없음 — 스쿼트 · 레그 프레스는 양측 지지라 계수가 없다. [2026-10-02 사용자 요청] 수요일에 슈퍼세트를 얹어 하한(8) 아래였던 7.0이 11로 올라갔다. 앉아서 하는 아우터(고관절 굽힘)와 선 자세 편측 케이블(고관절 펴짐)로 각도를 나눴다</t>
   </si>
   <si>
     <t>직접 6세트: 토요일 시티드 3 · 수요일 스탠딩 3 (3 → 6). 간접 출처 없음. 현장 일이 하루치를 얹어주던 것이 끝나 올렸다. 무릎 각도로 가자미근 · 비복근을 나눴다</t>
@@ -3925,7 +3940,7 @@
     <t>직접 6세트: 화요일 중량 크런치 3 · 라잉 레그 레이즈 3 (3 → 6). 간접 출처 없음 — 스쿼트 · 데드의 브레이싱은 등척성이라 0. 현장 일이 코어를 버티게만 하던 것이 끝나 직접 굴곡을 늘렸다</t>
   </si>
   <si>
-    <t>직접 4세트: 토요일 이너 타이 4 (아우터와 슈퍼세트). 간접 2.6 — 스쿼트 0.2×5 + 레그 프레스 2종 각 0.2×4 (토 발 낮게 · 수 발 높게). 복귀판 초안에 통째로 비어 있던 자리이고 2026-09-13에 되살렸다</t>
+    <t>직접 8세트: 토요일 이너 타이 4 · 수요일 이너 타이 4 (둘 다 아우터와 슈퍼세트, 4 → 8). 간접 2.6 — 스쿼트 0.2×5 + 레그 프레스 2종 각 0.2×4 (토 발 낮게 · 수 발 높게). 복귀판 초안에 통째로 비어 있던 자리이고 2026-09-13에 되살렸다. [2026-10-02 사용자 요청] 실질 6.5로 하한 아래였던 것이 10.5가 됐다 — 하체에서 마지막까지 하한 아래였던 자리다</t>
   </si>
   <si>
     <t>직접 6세트: 화요일 넥 익스텐션 3 · 넥 플렉션 3. 2026-10-02 신설 — 사용자 요청으로 화요일 구성에 들어 있었다. 간접 출처 없음. 데드 · 슈러그의 목 지지는 등척성이라 계수를 주지 않는다. 첫 2주는 무게 없이 가동범위만</t>
@@ -3973,7 +3988,7 @@
     <t>· 기립근 6.5 · 승모 상부 4.5 · 승모 하부 5.0 · 종아리 6.0 · 복부 6.0 · 내전근 6.0 — '보완 필요'로 뜨지만 넷은 이번에 올린 자리이고 이 이상 올리면 세션이 상한을 넘는다. 다음 카드는 여기다.</t>
   </si>
   <si>
-    <t>· 중둔근 7.0 — 하한 근처다. 유지는 되나 성장 여지는 없다. 아우터 타이를 5세트로 되돌리면 8이 된다.</t>
+    <t>· 중둔근 11.0 · 내전근 10.5 — 2026-10-02에 수요일 이너/아우터 슈퍼세트가 들어와 둘 다 하한 아래(7.0 · 6.5)에서 성장 구간으로 올라왔다. 하체에서 '보완 필요'로 남은 곳은 이제 종아리 6.0뿐이다.</t>
   </si>
   <si>
     <t>· 둔근 14.0 · 햄스트링 14.0 — 2026-10-02에 둘 다 올라왔다(둔근 10 → 14 · 햄 13 → 14). 수요일이 고관절 신전 넷(데드 · 루마니안 · 발 높은 레그 프레스 · 힙 쓰러스트)을 다 가진 날이 됐기 때문이다. 둘 다 성장 구간 안이고 천장까지 여유가 있다.</t>
@@ -3994,10 +4009,13 @@
     <t>· 다시 걸고 싶으면 J2에 수를, K3에 '상태'를 되살리면 시트와 앱이 그대로 돌아온다.</t>
   </si>
   <si>
-    <t>· 상한 이력 — 2026-09-13 최초 136 · 09-14 145 · 09-14 제거(당시 147) · 10-02 주 6회 개편으로 164 → 같은 날 사용자 추가 둘(원 레그 컬 3 · 발 높은 레그 프레스 4, 시티드 레그 컬 −3)로 168.</t>
-  </si>
-  <si>
-    <t>· 168은 사용자가 고른 밴드(155~165)를 3 넘는다. 상한이 없으므로 금지는 아니고 기록이다 — 밴드로 되돌리려면 레그 익스텐션 3 → 2(수요일 레그 프레스가 사두 간접을 얹어 줬다) 또는 힙 쓰러스트 3 → 2(둔근 직접이 4 더 생겼다)가 가장 값이 싸다.</t>
+    <t>· 상한 이력 — 2026-09-13 최초 136 · 09-14 145 · 09-14 제거(당시 147) · 10-02 주 6회 개편으로 164 → 같은 날 사용자 추가 셋(원 레그 컬 3 · 발 높은 레그 프레스 4 · 수요일 이너/아우터 8, 시티드 레그 컬 −3)로 176.</t>
+  </si>
+  <si>
+    <t>· 176은 사용자가 고른 밴드(155~165)를 11 넘고 재택 주당 환산(168)도 넘었다. 상한이 없으므로 금지가 아니라 기록이다. 다만 추가분이 전부 하체 고립이라 수(40세트 101분) · 토(37세트 92분)가 나머지 넷의 1.5배가 됐다.</t>
+  </si>
+  <si>
+    <t>· 되돌릴 순서 — 수요일 케이블 힙 외전 3(같은 날 아우터 4가 같은 근육을 맡는다) → 레그 익스텐션 3 → 2 (수요일 레그 프레스가 사두 간접을 얹어 줬다) → 힙 쓰러스트 3 → 2(둔근 직접이 4 더 생겼다).</t>
   </si>
   <si>
     <t>· 세트를 계수로 일괄 조정하지 않는다. 늘릴 때도 줄일 때도 종목 단위로, 근거를 F열에 달아 움직인다.</t>
@@ -10942,7 +10960,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11102,8 +11120,8 @@
         <v>936</v>
       </c>
       <c r="E10" s="121">
-        <f>복귀_수_하체후면!$E$33</f>
-        <v>32</v>
+        <f>복귀_수_하체후면!$E$35</f>
+        <v>40</v>
       </c>
       <c r="F10" s="113" t="s">
         <v>937</v>
@@ -11168,7 +11186,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="115">
         <f>SUM(E6:E12)</f>
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F13" s="115" t="s">
         <v>946</v>
@@ -11325,13 +11343,13 @@
         <v>976</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="107" t="s">
+    <row r="49" spans="1:1">
+      <c r="A49" s="123" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="123" t="s">
+      <c r="A51" s="107" t="s">
         <v>978</v>
       </c>
     </row>
@@ -11348,6 +11366,11 @@
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
         <v>981</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="123" t="s">
+        <v>982</v>
       </c>
     </row>
   </sheetData>
@@ -11378,7 +11401,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -11537,10 +11560,10 @@
         <v>17.5</v>
       </c>
       <c r="J14" s="112" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="K14" s="112" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="L14" s="111" t="s">
         <v>356</v>
@@ -11578,10 +11601,10 @@
         <v>13</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -11617,10 +11640,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -11658,7 +11681,7 @@
         <v>8</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="K17" s="114" t="s">
         <v>597</v>
@@ -11697,10 +11720,10 @@
         <v>7.7</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -11713,7 +11736,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="114" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C19" s="113" t="s">
         <v>372</v>
@@ -11738,10 +11761,10 @@
         <v>7.7</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -11779,10 +11802,10 @@
         <v>3.3</v>
       </c>
       <c r="J20" s="114" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="K20" s="114" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="L20" s="113"/>
       <c r="M20" s="113" t="s">
@@ -11820,10 +11843,10 @@
         <v>10.7</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="K21" s="114" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="L21" s="113"/>
       <c r="M21" s="113" t="s">
@@ -11861,10 +11884,10 @@
         <v>9</v>
       </c>
       <c r="J22" s="114" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K22" s="114" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L22" s="113"/>
       <c r="M22" s="113"/>
@@ -11900,10 +11923,10 @@
         <v>5.8</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -11930,32 +11953,32 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="116" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -11965,42 +11988,42 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="116" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="116" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="107" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="116" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="116" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="C43" s="117" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
   </sheetData>
@@ -12031,27 +12054,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="118" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12133,13 +12156,13 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L11" s="113" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M11" s="113"/>
       <c r="N11" s="113"/>
@@ -12149,7 +12172,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="114" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C12" s="113" t="s">
         <v>281</v>
@@ -12174,10 +12197,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -12188,7 +12211,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C13" s="113" t="s">
         <v>281</v>
@@ -12213,10 +12236,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -12254,10 +12277,10 @@
         <v>9</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -12293,10 +12316,10 @@
         <v>5.8</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -12332,10 +12355,10 @@
         <v>6.8</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -12373,10 +12396,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -12405,52 +12428,52 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="116" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="116" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -12460,37 +12483,37 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="C41" s="117" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
   </sheetData>
@@ -12521,7 +12544,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12607,7 +12630,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="118" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12695,10 +12718,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="112" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K18" s="112" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L18" s="111" t="s">
         <v>356</v>
@@ -12736,10 +12759,10 @@
         <v>12.7</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -12775,10 +12798,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J20" s="114" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K20" s="114" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L20" s="113"/>
       <c r="M20" s="113"/>
@@ -12814,13 +12837,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="K21" s="114" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="L21" s="113" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="M21" s="113"/>
       <c r="N21" s="113"/>
@@ -12830,13 +12853,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="114" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C22" s="113" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="113" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E22" s="113">
         <v>3</v>
@@ -12855,10 +12878,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="114" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="K22" s="114" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="L22" s="113"/>
       <c r="M22" s="113"/>
@@ -12875,7 +12898,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="113" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E23" s="113">
         <v>3</v>
@@ -12894,10 +12917,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -12924,42 +12947,42 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -12969,32 +12992,32 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="116" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="116" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="117" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
   </sheetData>
@@ -13025,22 +13048,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13127,10 +13150,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L11" s="113"/>
       <c r="M11" s="113"/>
@@ -13168,10 +13191,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -13207,10 +13230,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -13221,7 +13244,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>309</v>
@@ -13246,10 +13269,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -13285,10 +13308,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -13299,7 +13322,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="114" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>939</v>
@@ -13324,10 +13347,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -13338,7 +13361,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="114" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>939</v>
@@ -13363,10 +13386,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -13402,10 +13425,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -13441,10 +13464,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -13471,42 +13494,42 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="116" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -13516,42 +13539,42 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="116" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="C42" s="117" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -14243,7 +14266,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -14263,7 +14286,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14344,7 +14367,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14494,14 +14517,14 @@
         <v>180</v>
       </c>
       <c r="I22" s="111">
-        <f t="shared" ref="I22:I32" si="0">IF(E22=0,0,ROUND((E22*(G22+H22)+N22)/60,1))</f>
+        <f t="shared" ref="I22:I34" si="0">IF(E22=0,0,ROUND((E22*(G22+H22)+N22)/60,1))</f>
         <v>3.5</v>
       </c>
       <c r="J22" s="112" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="K22" s="112" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="L22" s="111"/>
       <c r="M22" s="111"/>
@@ -14512,7 +14535,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="114" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C23" s="113" t="s">
         <v>327</v>
@@ -14538,10 +14561,10 @@
         <v>7</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -14558,7 +14581,7 @@
         <v>398</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E24" s="113">
         <v>3</v>
@@ -14577,10 +14600,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J24" s="114" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K24" s="114" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="L24" s="113"/>
       <c r="M24" s="113"/>
@@ -14591,7 +14614,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C25" s="113" t="s">
         <v>389</v>
@@ -14616,10 +14639,10 @@
         <v>13</v>
       </c>
       <c r="J25" s="114" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="K25" s="114" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="L25" s="113"/>
       <c r="M25" s="113"/>
@@ -14655,10 +14678,10 @@
         <v>11.9</v>
       </c>
       <c r="J26" s="114" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="K26" s="114" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="L26" s="113"/>
       <c r="M26" s="113"/>
@@ -14671,7 +14694,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="112" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C27" s="111" t="s">
         <v>443</v>
@@ -14697,10 +14720,10 @@
         <v>10.5</v>
       </c>
       <c r="J27" s="112" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="K27" s="112" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="L27" s="111" t="s">
         <v>521</v>
@@ -14738,10 +14761,10 @@
         <v>6</v>
       </c>
       <c r="J28" s="114" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="K28" s="114" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L28" s="113"/>
       <c r="M28" s="113"/>
@@ -14779,10 +14802,10 @@
         <v>5</v>
       </c>
       <c r="J29" s="114" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="K29" s="114" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="L29" s="113"/>
       <c r="M29" s="113"/>
@@ -14818,10 +14841,10 @@
         <v>8</v>
       </c>
       <c r="J30" s="114" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="K30" s="114" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="L30" s="113"/>
       <c r="M30" s="113"/>
@@ -14857,10 +14880,10 @@
         <v>6.8</v>
       </c>
       <c r="J31" s="114" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="K31" s="114" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="L31" s="113"/>
       <c r="M31" s="113"/>
@@ -14871,16 +14894,16 @@
         <v>11</v>
       </c>
       <c r="B32" s="114" t="s">
-        <v>321</v>
+        <v>401</v>
       </c>
       <c r="C32" s="113" t="s">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="D32" s="113">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E32" s="113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="113" t="s">
         <v>303</v>
@@ -14889,189 +14912,281 @@
         <v>40</v>
       </c>
       <c r="H32" s="113">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="I32" s="113">
         <f t="shared" si="0"/>
+        <v>3.3</v>
+      </c>
+      <c r="J32" s="114" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K32" s="114" t="s">
+        <v>997</v>
+      </c>
+      <c r="L32" s="113"/>
+      <c r="M32" s="113" t="s">
+        <v>405</v>
+      </c>
+      <c r="N32" s="113"/>
+    </row>
+    <row r="33" spans="1:14" ht="30" customHeight="1">
+      <c r="A33" s="113">
+        <v>12</v>
+      </c>
+      <c r="B33" s="114" t="s">
+        <v>406</v>
+      </c>
+      <c r="C33" s="113" t="s">
+        <v>407</v>
+      </c>
+      <c r="D33" s="113">
+        <v>40</v>
+      </c>
+      <c r="E33" s="113">
+        <v>4</v>
+      </c>
+      <c r="F33" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="G33" s="113">
+        <v>40</v>
+      </c>
+      <c r="H33" s="113">
+        <v>120</v>
+      </c>
+      <c r="I33" s="113">
+        <f t="shared" si="0"/>
+        <v>10.7</v>
+      </c>
+      <c r="J33" s="114" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K33" s="114" t="s">
+        <v>999</v>
+      </c>
+      <c r="L33" s="113"/>
+      <c r="M33" s="113" t="s">
+        <v>405</v>
+      </c>
+      <c r="N33" s="113"/>
+    </row>
+    <row r="34" spans="1:14" ht="30" customHeight="1">
+      <c r="A34" s="113">
+        <v>13</v>
+      </c>
+      <c r="B34" s="114" t="s">
+        <v>321</v>
+      </c>
+      <c r="C34" s="113" t="s">
+        <v>322</v>
+      </c>
+      <c r="D34" s="113">
+        <v>10</v>
+      </c>
+      <c r="E34" s="113">
+        <v>3</v>
+      </c>
+      <c r="F34" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="G34" s="113">
+        <v>40</v>
+      </c>
+      <c r="H34" s="113">
+        <v>75</v>
+      </c>
+      <c r="I34" s="113">
+        <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="J32" s="114" t="s">
-        <v>1145</v>
-      </c>
-      <c r="K32" s="114" t="s">
-        <v>1146</v>
-      </c>
-      <c r="L32" s="113"/>
-      <c r="M32" s="113"/>
-      <c r="N32" s="113"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="115"/>
-      <c r="B33" s="115"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115" t="s">
+      <c r="J34" s="114" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K34" s="114" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L34" s="113"/>
+      <c r="M34" s="113"/>
+      <c r="N34" s="113"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="115"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="115" t="s">
         <v>335</v>
       </c>
-      <c r="E33" s="115">
-        <f>SUM(E22:E32)</f>
-        <v>32</v>
-      </c>
-      <c r="F33" s="115"/>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115">
-        <f>ROUND(SUM(I22:I32),0)</f>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="107" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="116" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="116" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="E35" s="115">
+        <f>SUM(E22:E34)</f>
+        <v>40</v>
+      </c>
+      <c r="F35" s="115"/>
+      <c r="G35" s="115"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="115">
+        <f>ROUND(SUM(I22:I34),0)</f>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="107" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="116" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="116" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="116" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="116" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="107" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="116" t="s">
+    <row r="42" spans="1:14">
+      <c r="A42" s="116" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="116" t="s">
+    <row r="43" spans="1:14">
+      <c r="A43" s="116" t="s">
         <v>1156</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="45" spans="1:14">
+      <c r="A45" s="107" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="116" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="116" t="s">
-        <v>1158</v>
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="116" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="107" t="s">
-        <v>1159</v>
+      <c r="A49" s="116" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="116" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="116" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="116" t="s">
-        <v>1162</v>
+      <c r="A52" s="107" t="s">
+        <v>1163</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="116" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="116" t="s">
-        <v>1164</v>
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="116" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="107" t="s">
-        <v>1165</v>
+      <c r="A56" s="116" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="116" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="116" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="116" t="s">
-        <v>1168</v>
+      <c r="A59" s="107" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="116" t="s">
+        <v>1170</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="107" t="s">
-        <v>972</v>
+      <c r="A61" s="116" t="s">
+        <v>1171</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="116" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="116" t="s">
-        <v>1170</v>
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="107" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="107" t="s">
-        <v>1012</v>
+      <c r="A65" s="116" t="s">
+        <v>1173</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="116" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="116" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="116" t="s">
-        <v>1015</v>
+      <c r="A68" s="107" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="116" t="s">
+        <v>1175</v>
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="C70" s="117" t="s">
-        <v>1173</v>
+      <c r="A70" s="116" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="116" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="116" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="C74" s="117" t="s">
+        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -15102,27 +15217,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="118" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15179,7 +15294,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="114" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>296</v>
@@ -15204,13 +15319,13 @@
         <v>12.7</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="L11" s="113" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M11" s="113"/>
       <c r="N11" s="113"/>
@@ -15245,10 +15360,10 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -15284,10 +15399,10 @@
         <v>6.8</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -15325,10 +15440,10 @@
         <v>6.5</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -15364,10 +15479,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -15403,10 +15518,10 @@
         <v>10.7</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -15419,7 +15534,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="114" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>359</v>
@@ -15444,10 +15559,10 @@
         <v>5.5</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -15458,7 +15573,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="114" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>283</v>
@@ -15483,10 +15598,10 @@
         <v>5.8</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -15513,42 +15628,42 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="107" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="116" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -15558,42 +15673,42 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="116" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="107" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="116" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="C41" s="117" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
     </row>
   </sheetData>
@@ -15994,12 +16109,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16013,12 +16128,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="110" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B6" s="110" t="s">
         <v>652</v>
@@ -16044,7 +16159,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B7" s="114" t="s">
         <v>97</v>
@@ -16067,12 +16182,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="114" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B8" s="114" t="s">
         <v>531</v>
@@ -16095,12 +16210,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="114" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B9" s="114" t="s">
         <v>357</v>
@@ -16123,12 +16238,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="114" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B10" s="114" t="s">
         <v>522</v>
@@ -16151,15 +16266,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="114" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B11" s="114" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>359</v>
@@ -16179,12 +16294,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="114" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B12" s="114" t="s">
         <v>280</v>
@@ -16207,15 +16322,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="114" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C13" s="113" t="s">
         <v>283</v>
@@ -16235,15 +16350,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="114" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>283</v>
@@ -16263,12 +16378,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="114" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B15" s="114" t="s">
         <v>486</v>
@@ -16291,15 +16406,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="114" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B16" s="114" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>283</v>
@@ -16319,12 +16434,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="114" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B17" s="114" t="s">
         <v>479</v>
@@ -16347,12 +16462,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="114" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B18" s="114" t="s">
         <v>97</v>
@@ -16375,12 +16490,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="114" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B19" s="114" t="s">
         <v>531</v>
@@ -16403,12 +16518,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="114" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B20" s="114" t="s">
         <v>357</v>
@@ -16431,12 +16546,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="114" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B21" s="114" t="s">
         <v>600</v>
@@ -16459,12 +16574,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="114" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B22" s="114" t="s">
         <v>441</v>
@@ -16487,15 +16602,15 @@
         <v>673</v>
       </c>
       <c r="H22" s="114" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B23" s="114" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C23" s="113" t="s">
         <v>368</v>
@@ -16515,15 +16630,15 @@
         <v>673</v>
       </c>
       <c r="H23" s="114" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B24" s="114" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C24" s="113" t="s">
         <v>383</v>
@@ -16543,15 +16658,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="114" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5">
       <c r="A25" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="C25" s="113" t="s">
         <v>281</v>
@@ -16571,12 +16686,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="114" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B26" s="114" t="s">
         <v>479</v>
@@ -16599,12 +16714,12 @@
         <v>673</v>
       </c>
       <c r="H26" s="114" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B27" s="114" t="s">
         <v>95</v>
@@ -16627,15 +16742,15 @@
         <v>673</v>
       </c>
       <c r="H27" s="114" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B28" s="114" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C28" s="113" t="s">
         <v>421</v>
@@ -16655,15 +16770,15 @@
         <v>673</v>
       </c>
       <c r="H28" s="114" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="C29" s="113" t="s">
         <v>421</v>
@@ -16683,12 +16798,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="114" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B30" s="114" t="s">
         <v>95</v>
@@ -16711,12 +16826,12 @@
         <v>673</v>
       </c>
       <c r="H30" s="114" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B31" s="114" t="s">
         <v>280</v>
@@ -16739,15 +16854,15 @@
         <v>673</v>
       </c>
       <c r="H31" s="114" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B32" s="114" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C32" s="113" t="s">
         <v>432</v>
@@ -16767,15 +16882,15 @@
         <v>673</v>
       </c>
       <c r="H32" s="114" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B33" s="114" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C33" s="113" t="s">
         <v>432</v>
@@ -16795,12 +16910,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="114" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B34" s="114" t="s">
         <v>424</v>
@@ -16823,12 +16938,12 @@
         <v>673</v>
       </c>
       <c r="H34" s="114" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B35" s="114" t="s">
         <v>537</v>
@@ -16851,15 +16966,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="114" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C36" s="113" t="s">
         <v>296</v>
@@ -16879,12 +16994,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="114" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B37" s="114" t="s">
         <v>486</v>
@@ -16907,12 +17022,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="114" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B38" s="114" t="s">
         <v>93</v>
@@ -16935,15 +17050,15 @@
         <v>673</v>
       </c>
       <c r="H38" s="114" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B39" s="114" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="C39" s="113" t="s">
         <v>327</v>
@@ -16963,12 +17078,12 @@
         <v>673</v>
       </c>
       <c r="H39" s="114" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B40" s="114" t="s">
         <v>431</v>
@@ -16991,12 +17106,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="114" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B41" s="114" t="s">
         <v>573</v>
@@ -17019,12 +17134,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="114" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B42" s="114" t="s">
         <v>498</v>
@@ -17047,12 +17162,12 @@
         <v>673</v>
       </c>
       <c r="H42" s="114" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B43" s="114" t="s">
         <v>93</v>
@@ -17080,7 +17195,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B44" s="114" t="s">
         <v>95</v>
@@ -17103,15 +17218,15 @@
         <v>673</v>
       </c>
       <c r="H44" s="114" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B45" s="114" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C45" s="113" t="s">
         <v>389</v>
@@ -17131,12 +17246,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="114" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B46" s="114" t="s">
         <v>388</v>
@@ -17164,7 +17279,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B47" s="114" t="s">
         <v>573</v>
@@ -17187,12 +17302,12 @@
         <v>673</v>
       </c>
       <c r="H47" s="114" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B48" s="114" t="s">
         <v>570</v>
@@ -17215,12 +17330,12 @@
         <v>673</v>
       </c>
       <c r="H48" s="114" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B49" s="114" t="s">
         <v>95</v>
@@ -17243,15 +17358,15 @@
         <v>673</v>
       </c>
       <c r="H49" s="114" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B50" s="114" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C50" s="113" t="s">
         <v>398</v>
@@ -17271,15 +17386,15 @@
         <v>673</v>
       </c>
       <c r="H50" s="114" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="51">
       <c r="A51" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B51" s="114" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C51" s="113" t="s">
         <v>398</v>
@@ -17299,12 +17414,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="114" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B52" s="114" t="s">
         <v>93</v>
@@ -17327,12 +17442,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="114" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B53" s="114" t="s">
         <v>388</v>
@@ -17355,15 +17470,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="114" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="113" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B54" s="114" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C54" s="113" t="s">
         <v>402</v>
@@ -17383,12 +17498,12 @@
         <v>673</v>
       </c>
       <c r="H54" s="114" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="113" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B55" s="114" t="s">
         <v>495</v>
@@ -17416,7 +17531,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="113" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="B56" s="114" t="s">
         <v>605</v>
@@ -17444,10 +17559,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B57" s="114" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="C57" s="113" t="s">
         <v>309</v>
@@ -17467,12 +17582,12 @@
         <v>673</v>
       </c>
       <c r="H57" s="114" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B58" s="114" t="s">
         <v>97</v>
@@ -17495,12 +17610,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="114" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="113" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="B59" s="114" t="s">
         <v>441</v>
@@ -17523,12 +17638,12 @@
         <v>673</v>
       </c>
       <c r="H59" s="114" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B60" s="114" t="s">
         <v>531</v>
@@ -17551,12 +17666,12 @@
         <v>673</v>
       </c>
       <c r="H60" s="114" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="113" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B61" s="114" t="s">
         <v>600</v>
@@ -17579,12 +17694,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="114" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B62" s="114" t="s">
         <v>93</v>
@@ -17607,12 +17722,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="114" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="113" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B63" s="114" t="s">
         <v>502</v>
@@ -17635,15 +17750,15 @@
         <v>673</v>
       </c>
       <c r="H63" s="114" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="113" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="B64" s="114" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C64" s="113" t="s">
         <v>939</v>
@@ -17663,7 +17778,7 @@
         <v>673</v>
       </c>
       <c r="H64" s="114" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -17674,7 +17789,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -17688,12 +17803,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -17737,7 +17852,7 @@
         <v>충분</v>
       </c>
       <c r="F5" s="114" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -17768,7 +17883,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="114" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -17792,10 +17907,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -17823,7 +17938,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -17847,7 +17962,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -17871,7 +17986,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="114" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -17895,7 +18010,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -17919,7 +18034,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -17943,7 +18058,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -17967,7 +18082,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -17991,10 +18106,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="114" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18022,7 +18137,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18046,7 +18161,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="114" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18055,7 +18170,7 @@
       </c>
       <c r="B18" s="113">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A18)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A18)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A18)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A18)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A18)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A18)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C18" s="113">
         <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A18),0.5)</f>
@@ -18063,14 +18178,14 @@
       </c>
       <c r="D18" s="113">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" s="113" t="str">
         <f t="shared" si="1"/>
-        <v>보완 필요</v>
+        <v>충분</v>
       </c>
       <c r="F18" s="114" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18094,7 +18209,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18118,7 +18233,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="114" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18142,7 +18257,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="114" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18166,7 +18281,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="114" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18190,7 +18305,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18199,7 +18314,7 @@
       </c>
       <c r="B24" s="113">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A24)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A24)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A24)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A24)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A24)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A24)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C24" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A24),0.5)</f>
@@ -18207,14 +18322,14 @@
       </c>
       <c r="D24" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="E24" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>보완 필요</v>
+        <v>충분</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18238,7 +18353,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="114" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18247,11 +18362,11 @@
       </c>
       <c r="B26" s="115">
         <f>SUM(B5:B25)</f>
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D26" s="115">
         <f ca="1">SUM(D5:D25)</f>
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -18261,122 +18376,127 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="123" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="123" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="107" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="123" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="123" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1314</v>
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="123" t="s">
+        <v>1320</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_27AB22B2FD6E09657726B5396B754EF0E5A5D09F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_7A914A6F33AD0B4F7726B5396B3544A9C9E12F4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="1324">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -2809,10 +2809,10 @@
     <t>하체 전면(사두) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 92분</t>
-  </si>
-  <si>
-    <t>스쿼트 5×5가 앞, 어깨 블록이 4~6번. 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 이너 · 아우터 · 원 레그 컬 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다</t>
+    <t>약 95분</t>
+  </si>
+  <si>
+    <t>스쿼트 5×5가 앞, 어깨 블록이 4~6번. 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 레그 컬 · 이너 · 아우터 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다 — 햄스트링 중량은 이 날이 가장 잘 나온다(토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하다)</t>
   </si>
   <si>
     <t>일</t>
@@ -2869,10 +2869,10 @@
     <t>하체 후면(햄 · 둔) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 101분</t>
-  </si>
-  <si>
-    <t>데드 톱1 + 백오프2 · 레그 프레스는 발을 발판 위쪽에(둔근) · 이너 · 아우터 슈퍼세트. 스미스 오버헤드 프레스가 어깨 블록 첫 종목 — 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 자리다</t>
+    <t>약 98분</t>
+  </si>
+  <si>
+    <t>데드 톱1 + 백오프2 · 레그 프레스는 발을 발판 위쪽에(둔근) · 원 레그 컬로 좌우 균형 · 이너 · 아우터 슈퍼세트. 스미스 오버헤드 프레스가 어깨 블록 첫 종목 — 앞의 13세트가 전부 하체다</t>
   </si>
   <si>
     <t>목</t>
@@ -2932,6 +2932,9 @@
     <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). 164 → 168 → 176.</t>
   </si>
   <si>
+    <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
+  </si>
+  <si>
     <t>· 유지한 곳 — 흉근 24 · 승모 중부 10 · 삼각 측면 10 · 후면 10 · 사두 12 · 햄스트링 10. 이미 성장 구간 상단이라 세트는 그대로 두고 빈도만 올렸다.</t>
   </si>
   <si>
@@ -2977,16 +2980,16 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 수 40세트 101분 · 토 37세트 92분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
-  </si>
-  <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 25를 빼면 실질 12, 수요일은 27을 빼면 13, 월요일은 6을 빼면 16이다.</t>
+    <t>· 수 39세트 98분 · 토 38세트 95분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
   </si>
   <si>
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 주 427분 = 7시간 7분. 주 4회 370분에서 57분 늘었다. 수(101) · 토(92)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 주 427분 = 7시간 7분. 주 4회 370분에서 57분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3046,6 +3049,12 @@
     <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
   </si>
   <si>
+    <t>[2026-10-02 추가 — 사용자 지적, 같은 날 수요일 원 레그 컬과 자리 교환] 전면 하체만 12세트인 날에 햄스트링이 0이었다. 이 4세트로 햄스트링이 주 1회 → 2회가 된다(여기 4 + 수요일 6). 이 날이 중량을 밀기에 가장 좋은 자리다 — 토요일엔 햄스트링을 직접 쓰는 종목이 하나도 없어 누적 24세트를 지나도 햄스트링 자체는 국소로 신선하다. 중량은 전신 피로가 아니라 국소 피로가 정한다. 그래서 후반 고립 블록의 첫 자리를 줬다.</t>
+  </si>
+  <si>
+    <t>시티드 레그 컬 (고관절이 굽어 늘어난 구간) / 라잉 레그 컬 / 노르딕 햄 컬 (맨몸)</t>
+  </si>
+  <si>
     <t>아우터와 슈퍼세트. 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
   </si>
   <si>
@@ -3058,12 +3067,6 @@
     <t>힙 어브덕션 머신 (겸용 머신이 없을 때) / 케이블 힙 외전</t>
   </si>
   <si>
-    <t>[2026-10-02 추가 — 사용자 지적] 전면 하체만 12세트인 날에 햄스트링이 0이었다. 이 3세트로 햄스트링이 주 1회 → 2회가 된다(수요일 7 + 여기 3) — 가슴 · 등처럼 빈도를 쪼갠 셈이다. 편측이라 좌우 차가 드러나고, 사두로만 때린 날의 무릎 균형도 맞춘다.</t>
-  </si>
-  <si>
-    <t>라잉 / 시티드 레그 컬 (양측) / 노르딕 햄 컬 (맨몸)</t>
-  </si>
-  <si>
     <t>앉아서 하는 쪽 — 무릎이 굽어 가자미근 비중이 커진다. 수요일 스탠딩과 각도를 나눈다.</t>
   </si>
   <si>
@@ -3079,19 +3082,22 @@
     <t>· 하체를 전면 · 후면으로 갈라 토요일이 사두 전담이 됐다. 스쿼트 · 레그 프레스 · 익스텐션 12세트로 사두 주간 세트가 한 날에 다 들어간다.</t>
   </si>
   <si>
-    <t>· 어깨 블록을 4~6번에 둔 이유 — 이너 · 아우터 타이와 원 레그 컬 · 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 14세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
+    <t>· 어깨 블록을 4~6번에 둔 이유 — 레그 컬 · 이너 · 아우터 타이 · 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 15세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
   </si>
   <si>
     <t>· 토요일에 어깨 세 방향(전 · 측 · 후)을 다 넣는 것이 사용자 지정이다. 전면은 머신 숄더, 측면은 덤벨 레터럴, 후면은 리버스 펙덱.</t>
   </si>
   <si>
-    <t>· [2026-10-02] 원 레그 컬 3을 더했다. 사두는 스쿼트 5×5 때문에 쪼갤 수 없어 주 1회지만 햄스트링은 쪼갤 수 있고, 전면 하체 날에 햄스트링이 0이면 무릎을 한쪽으로만 때리는 날이 된다.</t>
-  </si>
-  <si>
-    <t>· 37세트 · 약 92분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 이너 · 아우터 · 원 레그 컬 · 카프 25세트)은 예외로 본다 — 실질 12세트다.</t>
-  </si>
-  <si>
-    <t>· 여섯 날 중 가장 크다. 그래도 주 4회 시절 토요일(43세트 · 107분)보다는 작다.</t>
+    <t>· [2026-10-02] 햄스트링 4세트를 더했다. 사두는 스쿼트 5×5 때문에 쪼갤 수 없어 주 1회지만 햄스트링은 쪼갤 수 있고, 전면 하체 날에 햄스트링이 0이면 무릎을 한쪽으로만 때리는 날이 된다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 같은 날 교환] 처음엔 원 레그 컬 3을 뒀는데 사용자 제안으로 수요일 양측 레그 컬과 바꿨다. 토요일엔 햄스트링을 직접 쓰는 종목이 없어 국소로 신선하므로 중량 종목(양측)이 맞고, 편측은 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 둘 다 반대로 놓여 있었다.</t>
+  </si>
+  <si>
+    <t>· 38세트 · 약 95분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 레그 컬 · 이너 · 아우터 · 카프 26세트)은 예외로 본다 — 실질 12세트다.</t>
+  </si>
+  <si>
+    <t>· 여섯 날 중 둘째로 크다. 그래도 주 4회 시절 토요일(43세트 · 107분)보다는 작다.</t>
   </si>
   <si>
     <t>· 웜업은 별도다. 스쿼트가 있는 날이므로 10~15분을 더 잡는다.</t>
@@ -3100,7 +3106,7 @@
     <t>드롭 세트 (2026-10-02)</t>
   </si>
   <si>
-    <t>· 레그 익스텐션 +75초 · 레터럴 +60초 · 리버스 펙덱 +60초. 마지막 세트에만 2단.</t>
+    <t>· 레그 익스텐션 +75초 · 레터럴 +60초 · 리버스 펙덱 +60초 · 레그 컬 +75초. 마지막 세트에만 2단. 레그 컬 드롭은 2026-10-02 자리 교환 때 종목을 따라 수요일에서 옮겨 왔다.</t>
   </si>
   <si>
     <t>· 이너 · 아우터 타이에는 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다.</t>
@@ -3109,7 +3115,7 @@
     <t>· N열 '드롭(초)'는 마지막 세트에 더해지는 시간이다. I열 종목 분에 합산되고, 앱 타이머는 마지막 세트를 그만큼 늘린 뒤 '드롭세트'라고 읊는다. E열 세트 수와 복귀_세트검산은 건드리지 않는다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???</t>
+    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???  /  아 원 레그 컬이랑 토요일 레그컬 자리 바꾸는거 어떻게 생각해?</t>
   </si>
   <si>
     <t>일요일 — 등(광배) · 팔</t>
@@ -3460,16 +3466,16 @@
     <t>와이드 스탠스 레그 프레스 (발 높게) / 45도 레그 프레스 (발 높게) / 스미스 스쿼트 (발 앞쪽)</t>
   </si>
   <si>
-    <t>무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 라잉으로 하면 고관절이 펴져 짧아진 구간에서 훈련된다. 토요일 원 레그 컬과 같은 기능이지만 이쪽은 양측 · 고중량이다.</t>
-  </si>
-  <si>
-    <t>시티드 레그 컬 (고관절이 굽어 늘어난 구간) / 라잉 레그 컬 / 노르딕 햄 컬 (맨몸)</t>
+    <t>[2026-10-02 토요일 레그 컬과 자리 교환] 무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 편측 종목은 좌우 차를 드러내는 것이 목적이라 주의력이 필요하고, 그래서 여섯 날 중 누적 10세트짜리인 이 자리가 맞다. 토요일 9번(누적 34세트)은 반대였다. 중량은 토요일 양측 레그 컬이 밀고, 이쪽은 균형을 본다 — 좌우 반복 수가 2회 이상 벌어지면 약한 쪽 기준으로 맞춘다.</t>
+  </si>
+  <si>
+    <t>원 레그 시티드 컬 / 라잉 레그 컬 (양측 — 편측 자리가 없을 때) / 노르딕 햄 컬 (맨몸)</t>
   </si>
   <si>
     <t>스미스 오버헤드 프레스</t>
   </si>
   <si>
-    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 14세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
+    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 13세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
   </si>
   <si>
     <t>머신 숄더 프레스 (완전 머신을 원할 때 — 단 증량 추적은 이쪽으로 옮긴다) / 덤벨 숄더 프레스</t>
@@ -3520,13 +3526,13 @@
     <t>· 토요일(하체 전면) 뒤 — 중간이다. 전면 삼각 · 삼두는 온전하나 스쿼트 5×5의 전신 피로가 가장 크다.</t>
   </si>
   <si>
-    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 14세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
+    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 13세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
   </si>
   <si>
     <t>· 그래서 토요일 전면은 머신 숄더 프레스(볼륨용)이고, 증량을 추적하는 쪽은 이 날이다.</t>
   </si>
   <si>
-    <t>· 힙 쓰러스트 · 힙 외전 · 카프를 어깨 뒤로 보내 프레스 앞 누적을 14세트로 묶었다. 레그 프레스가 들어오며 17이 될 수 있었던 자리다.</t>
+    <t>· 힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프를 어깨 뒤로 보내 프레스 앞 누적을 13세트로 묶었다. 레그 프레스와 슈퍼세트가 들어오며 25가 될 수 있었던 자리다.</t>
   </si>
   <si>
     <t>[하체 후면을 한 날에 모은 이유]</t>
@@ -3535,10 +3541,10 @@
     <t>· 데드 · 루마니안 데드는 둘 다 고관절 힌지다. 주에 흩어 두면 기립근이 회복할 72시간을 못 받는다 — 같은 패턴은 한 날에 모은다.</t>
   </si>
   <si>
-    <t>· 고관절 신전 넷(데드 3 · 루마니안 3 · 레그 프레스 발 높게 4 · 힙 쓰러스트 3)과 무릎 굴곡(레그 컬 4)을 같이 둬 햄스트링 · 둔근의 두 기능을 다 쓴다.</t>
-  </si>
-  <si>
-    <t>· 햄스트링 주 10세트 중 7이 이 날이고 3은 토요일 원 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다.</t>
+    <t>· 고관절 신전 넷(데드 3 · 루마니안 3 · 레그 프레스 발 높게 4 · 힙 쓰러스트 3)과 무릎 굴곡(원 레그 컬 3)을 같이 둬 햄스트링 · 둔근의 두 기능을 다 쓴다.</t>
+  </si>
+  <si>
+    <t>· 햄스트링 주 10세트 중 6이 이 날이고 4는 토요일 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다. 중량은 토요일(양측 4세트)이 밀고 이 날은 힌지 + 편측 균형을 맡는다.</t>
   </si>
   <si>
     <t>· 토요일(사두 12 + 햄 3 + 내전근 4 + 중둔근 4) · 수요일(후면 14 + 중둔근 7 + 내전근 4 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
@@ -3577,13 +3583,16 @@
     <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
   </si>
   <si>
-    <t>· 40세트 · 약 101분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
-  </si>
-  <si>
-    <t>· 고립 27세트를 빼면 실질 13세트다 — 어깨 블록 뒤 14세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 14분밖에 안 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
-  </si>
-  <si>
-    <t>· 레그 컬 +75초 · 레터럴 +60초. 마지막 세트에만 2단.</t>
+    <t>· 39세트 · 약 98분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
+  </si>
+  <si>
+    <t>· 고립 26세트를 빼면 실질 13세트다 — 어깨 블록 뒤 17세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 35분이 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
+  </si>
+  <si>
+    <t>· 레터럴 +60초 하나뿐이다. 마지막 세트에만 2단 — 레그 컬 드롭은 2026-10-02에 양측 레그 컬과 함께 토요일로 갔다.</t>
+  </si>
+  <si>
+    <t>· 원 레그 컬에는 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 되고, 일요일 원암 케이블 로우와 같은 기준이다.</t>
   </si>
   <si>
     <t>· 데드 · 백오프 · 루마니안 · 레그 프레스에는 걸지 않는다 — 척추가 버티거나 중량이 큰 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
@@ -3916,7 +3925,7 @@
     <t>하체 합산(대퇴 · 햄 · 종아리)</t>
   </si>
   <si>
-    <t>직접 10세트: 수요일 루마니안 데드 3 · 레그 컬 4 + 토요일 원 레그 컬 3(편측). 간접 3.8 — 힙 쓰러스트 0.5×3 + 백오프 0.5×2 + 데드 0.5×1 + 레그 프레스(발 높게) 0.2×4. [2026-10-02 사용자 지적] 전면 하체 날에 햄스트링이 0이라 원 레그 컬 3을 토요일로 옮겨 빈도를 주 2회로 쪼갰다 — 총량 10은 그대로다(내가 넣었던 시티드 레그 컬 3을 뺐다)</t>
+    <t>직접 10세트: 토요일 레그 컬 4(양측 · 중량) + 수요일 루마니안 데드 3 · 원 레그 컬 3(편측 · 균형). 간접 3.8 — 힙 쓰러스트 0.5×3 + 백오프 0.5×2 + 데드 0.5×1 + 레그 프레스(발 높게) 0.2×4. [2026-10-02 사용자 지적] 전면 하체 날에 햄스트링이 0이라 4세트를 토요일로 옮겨 빈도를 주 2회로 쪼갰다 — 총량 10은 그대로다(내가 넣었던 시티드 레그 컬 3을 뺐다). 같은 날 사용자 제안으로 양측(중량)과 편측(균형)의 날을 맞바꿨다 — 중량은 전신 피로가 아니라 국소 피로가 정하고, 토요일은 햄스트링을 직접 쓰는 종목이 달리 없어 누적 24세트 뒤에도 국소로 신선하다</t>
   </si>
   <si>
     <t>직접 7세트: 수요일 레그 프레스(발 높게) 4 · 힙 쓰러스트 3 (3 → 7). 간접 6.8 — 스쿼트 0.5×5 + 루마니안 0.5×3 + 데드 0.5×1 + 백오프 0.5×2 + 토요일 레그 프레스 0.33×4. [2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 두면 고관절 굽힘 범위가 커져 고관절 신전 비중이 오르고, 둔근이 그 동작의 주동근이다. 햄스트링은 무릎이 같이 펴져 길이가 거의 안 바뀌므로 약관여(0.2)로 뒀다</t>
@@ -10960,7 +10969,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11025,7 +11034,7 @@
       </c>
       <c r="E6" s="121">
         <f>복귀_토_하체전면!$E$24</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="113" t="s">
         <v>917</v>
@@ -11121,7 +11130,7 @@
       </c>
       <c r="E10" s="121">
         <f>복귀_수_하체후면!$E$35</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="113" t="s">
         <v>937</v>
@@ -11263,13 +11272,13 @@
         <v>960</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="107" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="123" t="s">
         <v>961</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="123" t="s">
+      <c r="A32" s="107" t="s">
         <v>962</v>
       </c>
     </row>
@@ -11288,13 +11297,13 @@
         <v>965</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="107" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="123" t="s">
         <v>966</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="123" t="s">
+      <c r="A38" s="107" t="s">
         <v>967</v>
       </c>
     </row>
@@ -11318,13 +11327,13 @@
         <v>971</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="107" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="123" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="123" t="s">
+      <c r="A45" s="107" t="s">
         <v>973</v>
       </c>
     </row>
@@ -11348,13 +11357,13 @@
         <v>977</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="107" t="s">
+    <row r="50" spans="1:1">
+      <c r="A50" s="123" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="123" t="s">
+      <c r="A52" s="107" t="s">
         <v>979</v>
       </c>
     </row>
@@ -11371,6 +11380,11 @@
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
         <v>982</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="123" t="s">
+        <v>983</v>
       </c>
     </row>
   </sheetData>
@@ -11381,7 +11395,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -11401,7 +11415,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -11560,10 +11574,10 @@
         <v>17.5</v>
       </c>
       <c r="J14" s="112" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="K14" s="112" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="L14" s="111" t="s">
         <v>356</v>
@@ -11601,10 +11615,10 @@
         <v>13</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -11640,10 +11654,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -11681,7 +11695,7 @@
         <v>8</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K17" s="114" t="s">
         <v>597</v>
@@ -11720,10 +11734,10 @@
         <v>7.7</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -11736,7 +11750,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="114" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C19" s="113" t="s">
         <v>372</v>
@@ -11761,10 +11775,10 @@
         <v>7.7</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -11777,10 +11791,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="114" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C20" s="113" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D20" s="113">
         <v>40</v>
@@ -11789,39 +11803,39 @@
         <v>4</v>
       </c>
       <c r="F20" s="113" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="G20" s="113">
         <v>40</v>
       </c>
       <c r="H20" s="113">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I20" s="113">
         <f t="shared" si="0"/>
-        <v>3.3</v>
+        <v>11.9</v>
       </c>
       <c r="J20" s="114" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="K20" s="114" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="L20" s="113"/>
-      <c r="M20" s="113" t="s">
-        <v>405</v>
-      </c>
-      <c r="N20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="113">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" ht="30" customHeight="1">
       <c r="A21" s="113">
         <v>8</v>
       </c>
       <c r="B21" s="114" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C21" s="113" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D21" s="113">
         <v>40</v>
@@ -11836,17 +11850,17 @@
         <v>40</v>
       </c>
       <c r="H21" s="113">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="I21" s="113">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>3.3</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="K21" s="114" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="L21" s="113"/>
       <c r="M21" s="113" t="s">
@@ -11859,38 +11873,40 @@
         <v>9</v>
       </c>
       <c r="B22" s="114" t="s">
-        <v>576</v>
+        <v>406</v>
       </c>
       <c r="C22" s="113" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="D22" s="113">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E22" s="113">
-        <v>3</v>
-      </c>
-      <c r="F22" s="113">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="F22" s="113" t="s">
+        <v>303</v>
       </c>
       <c r="G22" s="113">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H22" s="113">
         <v>120</v>
       </c>
       <c r="I22" s="113">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10.7</v>
       </c>
       <c r="J22" s="114" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K22" s="114" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="L22" s="113"/>
-      <c r="M22" s="113"/>
+      <c r="M22" s="113" t="s">
+        <v>405</v>
+      </c>
       <c r="N22" s="113"/>
     </row>
     <row r="23" spans="1:14" ht="30" customHeight="1">
@@ -11923,10 +11939,10 @@
         <v>5.8</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -11941,89 +11957,94 @@
       </c>
       <c r="E24" s="115">
         <f>SUM(E14:E23)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" s="115"/>
       <c r="G24" s="115"/>
       <c r="H24" s="115"/>
       <c r="I24" s="115">
         <f>ROUND(SUM(I14:I23),0)</f>
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="116" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="107" t="s">
-        <v>972</v>
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="116" t="s">
+        <v>1011</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="116" t="s">
-        <v>1010</v>
+      <c r="A34" s="107" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="116" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="116" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="107" t="s">
         <v>1013</v>
       </c>
     </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="116" t="s">
+        <v>1014</v>
+      </c>
+    </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="116" t="s">
-        <v>1014</v>
+      <c r="A39" s="107" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="116" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="116" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="C43" s="117" t="s">
         <v>1017</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="116" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="C44" s="117" t="s">
+        <v>1019</v>
       </c>
     </row>
   </sheetData>
@@ -12054,27 +12075,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="118" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12156,13 +12177,13 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="L11" s="113" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="M11" s="113"/>
       <c r="N11" s="113"/>
@@ -12172,7 +12193,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="114" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C12" s="113" t="s">
         <v>281</v>
@@ -12197,10 +12218,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -12211,7 +12232,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C13" s="113" t="s">
         <v>281</v>
@@ -12236,10 +12257,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -12277,10 +12298,10 @@
         <v>9</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -12316,10 +12337,10 @@
         <v>5.8</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -12355,10 +12376,10 @@
         <v>6.8</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -12396,10 +12417,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -12428,92 +12449,92 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="116" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="116" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="C41" s="117" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
   </sheetData>
@@ -12544,7 +12565,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12630,7 +12651,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="118" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12718,10 +12739,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="112" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="K18" s="112" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="L18" s="111" t="s">
         <v>356</v>
@@ -12759,10 +12780,10 @@
         <v>12.7</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -12798,10 +12819,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J20" s="114" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="K20" s="114" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="L20" s="113"/>
       <c r="M20" s="113"/>
@@ -12837,13 +12858,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="K21" s="114" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="L21" s="113" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="M21" s="113"/>
       <c r="N21" s="113"/>
@@ -12853,13 +12874,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="114" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C22" s="113" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="113" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="E22" s="113">
         <v>3</v>
@@ -12878,10 +12899,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="114" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="K22" s="114" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="L22" s="113"/>
       <c r="M22" s="113"/>
@@ -12898,7 +12919,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="113" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="E23" s="113">
         <v>3</v>
@@ -12917,10 +12938,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -12947,77 +12968,77 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="116" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="116" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="117" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
   </sheetData>
@@ -13048,22 +13069,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13150,10 +13171,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="L11" s="113"/>
       <c r="M11" s="113"/>
@@ -13191,10 +13212,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -13230,10 +13251,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -13244,7 +13265,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>309</v>
@@ -13269,10 +13290,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -13308,10 +13329,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -13322,7 +13343,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="114" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>939</v>
@@ -13347,10 +13368,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -13361,7 +13382,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="114" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>939</v>
@@ -13386,10 +13407,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -13425,10 +13446,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -13464,10 +13485,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="K19" s="114" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="L19" s="113"/>
       <c r="M19" s="113"/>
@@ -13494,87 +13515,87 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="116" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="116" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="116" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="C42" s="117" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
   </sheetData>
@@ -14266,7 +14287,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -14286,7 +14307,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14367,7 +14388,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14521,10 +14542,10 @@
         <v>3.5</v>
       </c>
       <c r="J22" s="112" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="K22" s="112" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="L22" s="111"/>
       <c r="M22" s="111"/>
@@ -14535,7 +14556,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="114" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C23" s="113" t="s">
         <v>327</v>
@@ -14561,10 +14582,10 @@
         <v>7</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="K23" s="114" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
@@ -14581,7 +14602,7 @@
         <v>398</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E24" s="113">
         <v>3</v>
@@ -14600,10 +14621,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J24" s="114" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="K24" s="114" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="L24" s="113"/>
       <c r="M24" s="113"/>
@@ -14614,7 +14635,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C25" s="113" t="s">
         <v>389</v>
@@ -14639,10 +14660,10 @@
         <v>13</v>
       </c>
       <c r="J25" s="114" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="K25" s="114" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="L25" s="113"/>
       <c r="M25" s="113"/>
@@ -14653,48 +14674,46 @@
         <v>5</v>
       </c>
       <c r="B26" s="114" t="s">
-        <v>397</v>
+        <v>576</v>
       </c>
       <c r="C26" s="113" t="s">
         <v>398</v>
       </c>
       <c r="D26" s="113">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E26" s="113">
-        <v>4</v>
-      </c>
-      <c r="F26" s="113" t="s">
-        <v>364</v>
+        <v>3</v>
+      </c>
+      <c r="F26" s="113">
+        <v>10</v>
       </c>
       <c r="G26" s="113">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H26" s="113">
         <v>120</v>
       </c>
       <c r="I26" s="113">
         <f t="shared" si="0"/>
-        <v>11.9</v>
+        <v>9</v>
       </c>
       <c r="J26" s="114" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="K26" s="114" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="L26" s="113"/>
       <c r="M26" s="113"/>
-      <c r="N26" s="113">
-        <v>75</v>
-      </c>
+      <c r="N26" s="113"/>
     </row>
     <row r="27" spans="1:14" ht="30" customHeight="1">
       <c r="A27" s="111">
         <v>6</v>
       </c>
       <c r="B27" s="112" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C27" s="111" t="s">
         <v>443</v>
@@ -14720,10 +14739,10 @@
         <v>10.5</v>
       </c>
       <c r="J27" s="112" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="K27" s="112" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="L27" s="111" t="s">
         <v>521</v>
@@ -14761,10 +14780,10 @@
         <v>6</v>
       </c>
       <c r="J28" s="114" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="K28" s="114" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="L28" s="113"/>
       <c r="M28" s="113"/>
@@ -14802,10 +14821,10 @@
         <v>5</v>
       </c>
       <c r="J29" s="114" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="K29" s="114" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="L29" s="113"/>
       <c r="M29" s="113"/>
@@ -14841,10 +14860,10 @@
         <v>8</v>
       </c>
       <c r="J30" s="114" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="K30" s="114" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="L30" s="113"/>
       <c r="M30" s="113"/>
@@ -14880,10 +14899,10 @@
         <v>6.8</v>
       </c>
       <c r="J31" s="114" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="K31" s="114" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="L31" s="113"/>
       <c r="M31" s="113"/>
@@ -14919,10 +14938,10 @@
         <v>3.3</v>
       </c>
       <c r="J32" s="114" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K32" s="114" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="L32" s="113"/>
       <c r="M32" s="113" t="s">
@@ -14960,10 +14979,10 @@
         <v>10.7</v>
       </c>
       <c r="J33" s="114" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="K33" s="114" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="L33" s="113"/>
       <c r="M33" s="113" t="s">
@@ -15001,10 +15020,10 @@
         <v>5.8</v>
       </c>
       <c r="J34" s="114" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="K34" s="114" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="L34" s="113"/>
       <c r="M34" s="113"/>
@@ -15019,174 +15038,179 @@
       </c>
       <c r="E35" s="115">
         <f>SUM(E22:E34)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F35" s="115"/>
       <c r="G35" s="115"/>
       <c r="H35" s="115"/>
       <c r="I35" s="115">
         <f>ROUND(SUM(I22:I34),0)</f>
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="107" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="116" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="116" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="116" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="116" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="116" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="116" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="107" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="116" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="116" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="116" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="116" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="116" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="116" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="116" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="116" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="116" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="116" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="107" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="116" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="116" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="116" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="107" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="116" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="116" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="107" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="116" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="116" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="116" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="116" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="C74" s="117" t="s">
-        <v>1178</v>
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="116" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="C75" s="117" t="s">
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
@@ -15217,27 +15241,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="118" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="118" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="118" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15294,7 +15318,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="114" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>296</v>
@@ -15319,13 +15343,13 @@
         <v>12.7</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="K11" s="114" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="L11" s="113" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="M11" s="113"/>
       <c r="N11" s="113"/>
@@ -15360,10 +15384,10 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="K12" s="114" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="L12" s="113"/>
       <c r="M12" s="113"/>
@@ -15399,10 +15423,10 @@
         <v>6.8</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="K13" s="114" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="L13" s="113"/>
       <c r="M13" s="113"/>
@@ -15440,10 +15464,10 @@
         <v>6.5</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="K14" s="114" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="L14" s="113"/>
       <c r="M14" s="113"/>
@@ -15479,10 +15503,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="K15" s="114" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="L15" s="113"/>
       <c r="M15" s="113"/>
@@ -15518,10 +15542,10 @@
         <v>10.7</v>
       </c>
       <c r="J16" s="114" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="K16" s="114" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="L16" s="113"/>
       <c r="M16" s="113"/>
@@ -15534,7 +15558,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="114" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>359</v>
@@ -15559,10 +15583,10 @@
         <v>5.5</v>
       </c>
       <c r="J17" s="114" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="K17" s="114" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="L17" s="113"/>
       <c r="M17" s="113"/>
@@ -15573,7 +15597,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="114" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>283</v>
@@ -15598,10 +15622,10 @@
         <v>5.8</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="K18" s="114" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="L18" s="113"/>
       <c r="M18" s="113"/>
@@ -15628,87 +15652,87 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="107" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="116" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="116" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="116" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="116" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="116" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="116" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="107" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="116" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="107" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="116" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="116" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="116" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="C41" s="117" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
   </sheetData>
@@ -16109,12 +16133,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16128,12 +16152,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="110" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="B6" s="110" t="s">
         <v>652</v>
@@ -16159,7 +16183,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B7" s="114" t="s">
         <v>97</v>
@@ -16182,12 +16206,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="114" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B8" s="114" t="s">
         <v>531</v>
@@ -16210,12 +16234,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="114" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B9" s="114" t="s">
         <v>357</v>
@@ -16238,12 +16262,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="114" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B10" s="114" t="s">
         <v>522</v>
@@ -16266,15 +16290,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="114" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B11" s="114" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>359</v>
@@ -16294,12 +16318,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="114" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B12" s="114" t="s">
         <v>280</v>
@@ -16322,15 +16346,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="114" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B13" s="114" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C13" s="113" t="s">
         <v>283</v>
@@ -16350,15 +16374,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="114" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B14" s="114" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>283</v>
@@ -16378,12 +16402,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="114" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B15" s="114" t="s">
         <v>486</v>
@@ -16406,15 +16430,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="114" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B16" s="114" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>283</v>
@@ -16434,12 +16458,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="114" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B17" s="114" t="s">
         <v>479</v>
@@ -16462,12 +16486,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="114" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B18" s="114" t="s">
         <v>97</v>
@@ -16490,12 +16514,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="114" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B19" s="114" t="s">
         <v>531</v>
@@ -16518,12 +16542,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="114" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B20" s="114" t="s">
         <v>357</v>
@@ -16546,12 +16570,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="114" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B21" s="114" t="s">
         <v>600</v>
@@ -16574,12 +16598,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="114" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B22" s="114" t="s">
         <v>441</v>
@@ -16602,15 +16626,15 @@
         <v>673</v>
       </c>
       <c r="H22" s="114" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B23" s="114" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C23" s="113" t="s">
         <v>368</v>
@@ -16630,15 +16654,15 @@
         <v>673</v>
       </c>
       <c r="H23" s="114" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B24" s="114" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C24" s="113" t="s">
         <v>383</v>
@@ -16658,15 +16682,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="114" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5">
       <c r="A25" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="C25" s="113" t="s">
         <v>281</v>
@@ -16686,12 +16710,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="114" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B26" s="114" t="s">
         <v>479</v>
@@ -16714,12 +16738,12 @@
         <v>673</v>
       </c>
       <c r="H26" s="114" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B27" s="114" t="s">
         <v>95</v>
@@ -16742,15 +16766,15 @@
         <v>673</v>
       </c>
       <c r="H27" s="114" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B28" s="114" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C28" s="113" t="s">
         <v>421</v>
@@ -16770,15 +16794,15 @@
         <v>673</v>
       </c>
       <c r="H28" s="114" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="C29" s="113" t="s">
         <v>421</v>
@@ -16798,12 +16822,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="114" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B30" s="114" t="s">
         <v>95</v>
@@ -16826,12 +16850,12 @@
         <v>673</v>
       </c>
       <c r="H30" s="114" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B31" s="114" t="s">
         <v>280</v>
@@ -16854,15 +16878,15 @@
         <v>673</v>
       </c>
       <c r="H31" s="114" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B32" s="114" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C32" s="113" t="s">
         <v>432</v>
@@ -16882,15 +16906,15 @@
         <v>673</v>
       </c>
       <c r="H32" s="114" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B33" s="114" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C33" s="113" t="s">
         <v>432</v>
@@ -16910,12 +16934,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="114" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B34" s="114" t="s">
         <v>424</v>
@@ -16938,12 +16962,12 @@
         <v>673</v>
       </c>
       <c r="H34" s="114" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B35" s="114" t="s">
         <v>537</v>
@@ -16966,15 +16990,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="114" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C36" s="113" t="s">
         <v>296</v>
@@ -16994,12 +17018,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="114" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B37" s="114" t="s">
         <v>486</v>
@@ -17022,12 +17046,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="114" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B38" s="114" t="s">
         <v>93</v>
@@ -17050,15 +17074,15 @@
         <v>673</v>
       </c>
       <c r="H38" s="114" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B39" s="114" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="C39" s="113" t="s">
         <v>327</v>
@@ -17078,12 +17102,12 @@
         <v>673</v>
       </c>
       <c r="H39" s="114" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B40" s="114" t="s">
         <v>431</v>
@@ -17106,12 +17130,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="114" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B41" s="114" t="s">
         <v>573</v>
@@ -17134,12 +17158,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="114" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B42" s="114" t="s">
         <v>498</v>
@@ -17162,12 +17186,12 @@
         <v>673</v>
       </c>
       <c r="H42" s="114" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B43" s="114" t="s">
         <v>93</v>
@@ -17195,7 +17219,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B44" s="114" t="s">
         <v>95</v>
@@ -17218,15 +17242,15 @@
         <v>673</v>
       </c>
       <c r="H44" s="114" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B45" s="114" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C45" s="113" t="s">
         <v>389</v>
@@ -17246,12 +17270,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="114" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B46" s="114" t="s">
         <v>388</v>
@@ -17279,7 +17303,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B47" s="114" t="s">
         <v>573</v>
@@ -17302,12 +17326,12 @@
         <v>673</v>
       </c>
       <c r="H47" s="114" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B48" s="114" t="s">
         <v>570</v>
@@ -17330,12 +17354,12 @@
         <v>673</v>
       </c>
       <c r="H48" s="114" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B49" s="114" t="s">
         <v>95</v>
@@ -17358,15 +17382,15 @@
         <v>673</v>
       </c>
       <c r="H49" s="114" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B50" s="114" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C50" s="113" t="s">
         <v>398</v>
@@ -17386,15 +17410,15 @@
         <v>673</v>
       </c>
       <c r="H50" s="114" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="51">
       <c r="A51" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B51" s="114" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C51" s="113" t="s">
         <v>398</v>
@@ -17414,12 +17438,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="114" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B52" s="114" t="s">
         <v>93</v>
@@ -17442,12 +17466,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="114" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B53" s="114" t="s">
         <v>388</v>
@@ -17470,15 +17494,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="114" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="113" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B54" s="114" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C54" s="113" t="s">
         <v>402</v>
@@ -17498,12 +17522,12 @@
         <v>673</v>
       </c>
       <c r="H54" s="114" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="113" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B55" s="114" t="s">
         <v>495</v>
@@ -17531,7 +17555,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="113" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B56" s="114" t="s">
         <v>605</v>
@@ -17559,10 +17583,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B57" s="114" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="C57" s="113" t="s">
         <v>309</v>
@@ -17582,12 +17606,12 @@
         <v>673</v>
       </c>
       <c r="H57" s="114" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B58" s="114" t="s">
         <v>97</v>
@@ -17610,12 +17634,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="114" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="113" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B59" s="114" t="s">
         <v>441</v>
@@ -17638,12 +17662,12 @@
         <v>673</v>
       </c>
       <c r="H59" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B60" s="114" t="s">
         <v>531</v>
@@ -17666,12 +17690,12 @@
         <v>673</v>
       </c>
       <c r="H60" s="114" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="113" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B61" s="114" t="s">
         <v>600</v>
@@ -17694,12 +17718,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="114" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B62" s="114" t="s">
         <v>93</v>
@@ -17722,12 +17746,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="114" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="113" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B63" s="114" t="s">
         <v>502</v>
@@ -17750,15 +17774,15 @@
         <v>673</v>
       </c>
       <c r="H63" s="114" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="113" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B64" s="114" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C64" s="113" t="s">
         <v>939</v>
@@ -17778,7 +17802,7 @@
         <v>673</v>
       </c>
       <c r="H64" s="114" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
     </row>
   </sheetData>
@@ -17803,12 +17827,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -17852,7 +17876,7 @@
         <v>충분</v>
       </c>
       <c r="F5" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -17883,7 +17907,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="114" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -17907,10 +17931,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -17938,7 +17962,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -17962,7 +17986,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -17986,7 +18010,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="114" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18010,7 +18034,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18034,7 +18058,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18058,7 +18082,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18082,7 +18106,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18106,10 +18130,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="114" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18137,7 +18161,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18161,7 +18185,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="114" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18185,7 +18209,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="114" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18209,7 +18233,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18233,7 +18257,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="114" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18257,7 +18281,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="114" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18281,7 +18305,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="114" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18305,7 +18329,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18329,7 +18353,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18353,7 +18377,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="114" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18376,127 +18400,127 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="123" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="123" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="107" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="123" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="123" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_7A914A6F33AD0B4F7726B5396B3544A9C9E12F4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B6E4A24D2AAD0B4F57A6D21DAB2044A989E03B05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="1324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1333">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -3760,6 +3760,12 @@
     <t>엎침 그립 + 팔꿈치 벌린 수평 로우 — 굽히는 일은 주로 상완근 · 상완요골근. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
   </si>
   <si>
+    <t>복귀_화_팔</t>
+  </si>
+  <si>
+    <t>엎침 그립 팔꿈치 굴곡 — 이두가 불리한 자리에서 보조한다. 재택 4일차와 같은 등급 (2026-10-02 종목을 넣을 때 빠뜨렸던 줄)</t>
+  </si>
+  <si>
     <t>수평 내전 시 전면삼각 능동 관여</t>
   </si>
   <si>
@@ -3778,6 +3784,9 @@
     <t>머리 위 프레스 중 측면삼각 능동 외전</t>
   </si>
   <si>
+    <t>머리 위 프레스 중 측면삼각 외전 — 궤도가 고정돼 자유중량 프레스보다 부분적이다. 재택 맵에 있는 줄인데 복귀 맵에 계속 빠져 있었다 (2026-10-02 보충)</t>
+  </si>
+  <si>
     <t>발을 발판 위쪽에 둬도 무릎 신전은 남는다 — 부분 협력. 사두 직접은 토요일에 12세트가 있고 이 줄 덕에 사두 노출이 주 2회가 된다 (2026-10-02)</t>
   </si>
   <si>
@@ -3805,6 +3814,9 @@
     <t>견갑 하강 개시 관여 — 언더그립 랫풀다운과 같은 등급</t>
   </si>
   <si>
+    <t>로우 당김 구간의 견갑 하강 관여. 재택 맵에 있는 줄인데 복귀 맵에 계속 빠져 있었다 (2026-10-02 보충)</t>
+  </si>
+  <si>
     <t>수평 외전 + 견갑 후인 — 강한 협력</t>
   </si>
   <si>
@@ -3856,9 +3868,6 @@
     <t>벌어진 스탠스 구간 약관여 — 토요일 레그 프레스와 같은 등급 (2026-10-02)</t>
   </si>
   <si>
-    <t>복귀_화_팔</t>
-  </si>
-  <si>
     <t>컬 중 상완요골근 동적 굴곡 — 부분 협력 (2026-10-02)</t>
   </si>
   <si>
@@ -3901,7 +3910,7 @@
     <t>직접 3세트: 목요일 트랩바 슈러그 3 (2026-10-02 신설). 간접 1.6 — 오버헤드 프레스 · 스미스 로우 · 데드 각 0.2. 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
   </si>
   <si>
-    <t>직접 3세트: 일요일 오버헤드 슈러그 3. 간접 2.2 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
+    <t>직접 3세트: 일요일 오버헤드 슈러그 3. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
   </si>
   <si>
     <t>직접 10세트: 목요일 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3. 간접 5.3 — 케이블 리버스 플라이 0.5×3 + 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 벤트오버 레터럴 0.33×3</t>
@@ -3913,7 +3922,7 @@
     <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 6.7 — 벤치 0.5×5 + 인클라인 머신 0.5×4 + 딥스 0.2×3 + 인클라인 플라이 0.2×4 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
   </si>
   <si>
-    <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 1.5 — 오버헤드 프레스 0.5×3. 간접이 거의 없는 부위라 직접 세트로만 채워진다. 셋으로 나눠 주 3회 빈도가 됐다</t>
+    <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.5 — 오버헤드 프레스 0.5×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
   </si>
   <si>
     <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 출처 없음 — 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블로 저항곡선을 갈랐다</t>
@@ -3937,7 +3946,7 @@
     <t>직접 6세트: 토요일 시티드 3 · 수요일 스탠딩 3 (3 → 6). 간접 출처 없음. 현장 일이 하루치를 얹어주던 것이 끝나 올렸다. 무릎 각도로 가자미근 · 비복근을 나눴다</t>
   </si>
   <si>
-    <t>직접 9세트: 일요일 프리쳐 컬 3 · 화요일 인클라인 덤벨 컬 3 · 목요일 케이블 드래그 컬 3 (6 → 9). 간접 6.7 — 당기기 6종목을 그립별로 (뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2). 짧아진 · 늘어난 · 중간 구간 셋으로 나눴다</t>
+    <t>직접 9세트: 일요일 프리쳐 컬 3 · 화요일 인클라인 덤벨 컬 3 · 목요일 케이블 드래그 컬 3 (6 → 9). 간접 7.3 — 당기기 6종목을 그립별로 (뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2) + 리버스컬 0.2×3. 짧아진 · 늘어난 · 중간 구간 셋으로 나눴다</t>
   </si>
   <si>
     <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 9.0 — 프레스 5종목 0.5씩 (벤치 5 · 인클라인 머신 4 · 딥스 3 · 머신 숄더 3 · 오버헤드 3). 실질 18로 성장 구간 상단이다</t>
@@ -3965,6 +3974,24 @@
   </si>
   <si>
     <t>· 판정 열은 정보이지 지시가 아니다. '보완 필요'가 그 자체로 증액 근거가 되지는 못한다.</t>
+  </si>
+  <si>
+    <t>[간접계수맵 — 2026-10-02 재택 맵과 대조해 세 줄을 보충했다]</t>
+  </si>
+  <si>
+    <t>· 머신 숄더 프레스 → 삼각근(측면) 0.33 · 해머 스트랭스 로우 → 승모(하부) 0.2 · 리버스컬 → 이두 0.2. 셋 다 재택 맵에는 있는데 복귀 맵에 없던 줄이다(리버스컬은 2026-10-02에 종목을 넣으며 빠뜨렸다).</t>
+  </si>
+  <si>
+    <t>· 영향 — 삼각 측면 11.5 → 12.5 · 승모 하부 5.0 → 6.0 · 이두 15.5 → 16.5. 직접 세트는 하나도 안 바뀌었다.</t>
+  </si>
+  <si>
+    <t>· 아직 남은 것 — 재택 맵과 복귀 맵의 계수가 아홉 군데 다르다. 프레스 → 삼두 · 삼각 전면(재택 0.33 / 복귀 0.5) · 데드 → 햄스트링(0.33 / 0.5) · 힙 쓰러스트 → 햄스트링(0.2 / 0.5) · 루마니안 → 기립근(0.5 / 0.2) · 스쿼트 · 레그 프레스 → 내전근(0.33 / 0.2) · 스쿼트 → 기립근(0 / 0.2) · 벤치 → 흉근 상부(0 / 0.2) · 인클라인 머신 → 흉근 중하부(0 / 0.2) · 케이블 리버스 플라이 → 승모 중부(0.33 / 0.5) · 트랩바 슈러그 → 기립근(0 / 0.2).</t>
+  </si>
+  <si>
+    <t>· 두 맵이 다른 시점에 쓰여 같은 규칙서를 안 쓴다. 한쪽으로 맞추면 판정 축이 또 한 번 바뀌므로 사용자 결정 전까지는 손대지 않는다 — 계수를 일괄로 움직이는 것은 거부된 방식이다.</t>
+  </si>
+  <si>
+    <t>· 방향만 적어 두면: 복귀가 재택보다 높은 곳은 프레스 계열과 힙 쓰러스트 · 스쿼트 기립근, 낮은 곳은 내전근과 루마니안 기립근이다. 한쪽이 전체적으로 높거나 낮은 것이 아니라 항목마다 갈린다.</t>
   </si>
   <si>
     <t>[현장 일 보정 열을 걷어냈다 — 2026-10-02]</t>
@@ -16119,7 +16146,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -16489,32 +16516,32 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="113" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="B18" s="114" t="s">
-        <v>97</v>
+        <v>453</v>
       </c>
       <c r="C18" s="113" t="s">
-        <v>443</v>
+        <v>283</v>
       </c>
       <c r="D18" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E18" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G18" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H18" s="114" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -16522,7 +16549,7 @@
         <v>1221</v>
       </c>
       <c r="B19" s="114" t="s">
-        <v>531</v>
+        <v>97</v>
       </c>
       <c r="C19" s="113" t="s">
         <v>443</v>
@@ -16532,17 +16559,17 @@
       </c>
       <c r="E19" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G19" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H19" s="114" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -16550,27 +16577,27 @@
         <v>1221</v>
       </c>
       <c r="B20" s="114" t="s">
-        <v>357</v>
+        <v>531</v>
       </c>
       <c r="C20" s="113" t="s">
         <v>443</v>
       </c>
       <c r="D20" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E20" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>2</v>
       </c>
       <c r="G20" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H20" s="114" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -16578,7 +16605,7 @@
         <v>1221</v>
       </c>
       <c r="B21" s="114" t="s">
-        <v>600</v>
+        <v>357</v>
       </c>
       <c r="C21" s="113" t="s">
         <v>443</v>
@@ -16588,25 +16615,25 @@
       </c>
       <c r="E21" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G21" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H21" s="114" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="113" t="s">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="B22" s="114" t="s">
-        <v>441</v>
+        <v>600</v>
       </c>
       <c r="C22" s="113" t="s">
         <v>443</v>
@@ -16626,161 +16653,161 @@
         <v>673</v>
       </c>
       <c r="H22" s="114" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="113" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B23" s="114" t="s">
-        <v>1138</v>
+        <v>441</v>
       </c>
       <c r="C23" s="113" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="D23" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E23" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G23" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H23" s="114" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="25.5">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="113" t="s">
         <v>1225</v>
       </c>
       <c r="B24" s="114" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="C24" s="113" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="D24" s="113">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="G24" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H24" s="114" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="25.5">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="113" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1184</v>
+        <v>522</v>
       </c>
       <c r="C25" s="113" t="s">
-        <v>281</v>
+        <v>368</v>
       </c>
       <c r="D25" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E25" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0.99</v>
       </c>
       <c r="G25" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H25" s="114" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="113" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B26" s="114" t="s">
-        <v>479</v>
+        <v>1133</v>
       </c>
       <c r="C26" s="113" t="s">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="D26" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E26" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="G26" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H26" s="114" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="113" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B27" s="114" t="s">
-        <v>95</v>
+        <v>1184</v>
       </c>
       <c r="C27" s="113" t="s">
         <v>281</v>
       </c>
       <c r="D27" s="113">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E27" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H27" s="114" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="113" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B28" s="114" t="s">
-        <v>1138</v>
+        <v>479</v>
       </c>
       <c r="C28" s="113" t="s">
-        <v>421</v>
+        <v>281</v>
       </c>
       <c r="D28" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E28" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16788,41 +16815,41 @@
       </c>
       <c r="F28" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>1.5</v>
       </c>
       <c r="G28" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H28" s="114" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="113" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>1184</v>
+        <v>95</v>
       </c>
       <c r="C29" s="113" t="s">
-        <v>421</v>
+        <v>281</v>
       </c>
       <c r="D29" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G29" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H29" s="114" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -16830,7 +16857,7 @@
         <v>1225</v>
       </c>
       <c r="B30" s="114" t="s">
-        <v>95</v>
+        <v>1138</v>
       </c>
       <c r="C30" s="113" t="s">
         <v>421</v>
@@ -16840,28 +16867,28 @@
       </c>
       <c r="E30" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G30" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H30" s="114" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="113" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="B31" s="114" t="s">
-        <v>280</v>
+        <v>1184</v>
       </c>
       <c r="C31" s="113" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D31" s="113">
         <v>0.2</v>
@@ -16878,35 +16905,35 @@
         <v>673</v>
       </c>
       <c r="H31" s="114" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="113" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B32" s="114" t="s">
-        <v>1031</v>
+        <v>95</v>
       </c>
       <c r="C32" s="113" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D32" s="113">
         <v>0.2</v>
       </c>
       <c r="E32" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.2</v>
       </c>
       <c r="G32" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H32" s="114" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -16914,7 +16941,7 @@
         <v>1226</v>
       </c>
       <c r="B33" s="114" t="s">
-        <v>1028</v>
+        <v>280</v>
       </c>
       <c r="C33" s="113" t="s">
         <v>432</v>
@@ -16934,21 +16961,21 @@
         <v>673</v>
       </c>
       <c r="H33" s="114" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="113" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="B34" s="114" t="s">
-        <v>424</v>
+        <v>1031</v>
       </c>
       <c r="C34" s="113" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="D34" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E34" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16956,77 +16983,77 @@
       </c>
       <c r="F34" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G34" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H34" s="114" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B35" s="114" t="s">
-        <v>537</v>
+        <v>1028</v>
       </c>
       <c r="C35" s="113" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="D35" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E35" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G35" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H35" s="114" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="25.5">
       <c r="A36" s="113" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>994</v>
+        <v>479</v>
       </c>
       <c r="C36" s="113" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="D36" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E36" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G36" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H36" s="114" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="113" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="B37" s="114" t="s">
-        <v>486</v>
+        <v>424</v>
       </c>
       <c r="C37" s="113" t="s">
         <v>296</v>
@@ -17046,63 +17073,63 @@
         <v>673</v>
       </c>
       <c r="H37" s="114" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B38" s="114" t="s">
-        <v>93</v>
+        <v>537</v>
       </c>
       <c r="C38" s="113" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="D38" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E38" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F38" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G38" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H38" s="114" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="113" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="B39" s="114" t="s">
-        <v>1184</v>
+        <v>994</v>
       </c>
       <c r="C39" s="113" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="D39" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E39" s="113">
-        <f t="shared" ref="E39:E64" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
+        <f t="shared" ref="E39:E67" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
         <v>4</v>
       </c>
       <c r="F39" s="113">
         <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="G39" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H39" s="114" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -17110,13 +17137,13 @@
         <v>1226</v>
       </c>
       <c r="B40" s="114" t="s">
-        <v>431</v>
+        <v>486</v>
       </c>
       <c r="C40" s="113" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="D40" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E40" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17124,21 +17151,21 @@
       </c>
       <c r="F40" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>1.5</v>
       </c>
       <c r="G40" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H40" s="114" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="113" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B41" s="114" t="s">
-        <v>573</v>
+        <v>93</v>
       </c>
       <c r="C41" s="113" t="s">
         <v>327</v>
@@ -17148,17 +17175,17 @@
       </c>
       <c r="E41" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>1</v>
       </c>
       <c r="G41" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H41" s="114" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -17166,7 +17193,7 @@
         <v>1231</v>
       </c>
       <c r="B42" s="114" t="s">
-        <v>498</v>
+        <v>1184</v>
       </c>
       <c r="C42" s="113" t="s">
         <v>327</v>
@@ -17176,45 +17203,45 @@
       </c>
       <c r="E42" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="G42" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H42" s="114" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="113" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B43" s="114" t="s">
-        <v>93</v>
+        <v>431</v>
       </c>
       <c r="C43" s="113" t="s">
-        <v>389</v>
+        <v>327</v>
       </c>
       <c r="D43" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E43" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>2.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G43" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H43" s="114" t="s">
-        <v>695</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -17222,55 +17249,55 @@
         <v>1225</v>
       </c>
       <c r="B44" s="114" t="s">
-        <v>95</v>
+        <v>573</v>
       </c>
       <c r="C44" s="113" t="s">
-        <v>389</v>
+        <v>327</v>
       </c>
       <c r="D44" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E44" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G44" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H44" s="114" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="113" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B45" s="114" t="s">
-        <v>1127</v>
+        <v>498</v>
       </c>
       <c r="C45" s="113" t="s">
-        <v>389</v>
+        <v>327</v>
       </c>
       <c r="D45" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E45" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G45" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H45" s="114" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -17278,27 +17305,27 @@
         <v>1224</v>
       </c>
       <c r="B46" s="114" t="s">
-        <v>388</v>
+        <v>93</v>
       </c>
       <c r="C46" s="113" t="s">
         <v>389</v>
       </c>
       <c r="D46" s="113">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E46" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F46" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="G46" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H46" s="114" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -17306,7 +17333,7 @@
         <v>1225</v>
       </c>
       <c r="B47" s="114" t="s">
-        <v>573</v>
+        <v>95</v>
       </c>
       <c r="C47" s="113" t="s">
         <v>389</v>
@@ -17316,17 +17343,17 @@
       </c>
       <c r="E47" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G47" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H47" s="114" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -17334,55 +17361,55 @@
         <v>1225</v>
       </c>
       <c r="B48" s="114" t="s">
-        <v>570</v>
+        <v>1127</v>
       </c>
       <c r="C48" s="113" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D48" s="113">
         <v>0.5</v>
       </c>
       <c r="E48" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G48" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H48" s="114" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="113" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B49" s="114" t="s">
-        <v>95</v>
+        <v>388</v>
       </c>
       <c r="C49" s="113" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D49" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E49" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <v>1.32</v>
       </c>
       <c r="G49" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H49" s="114" t="s">
-        <v>1261</v>
+        <v>696</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -17390,114 +17417,114 @@
         <v>1225</v>
       </c>
       <c r="B50" s="114" t="s">
-        <v>1127</v>
+        <v>573</v>
       </c>
       <c r="C50" s="113" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D50" s="113">
         <v>0.5</v>
       </c>
       <c r="E50" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G50" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H50" s="114" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="51">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="113" t="s">
         <v>1225</v>
       </c>
       <c r="B51" s="114" t="s">
-        <v>1133</v>
+        <v>570</v>
       </c>
       <c r="C51" s="113" t="s">
         <v>398</v>
       </c>
       <c r="D51" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E51" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G51" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H51" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B52" s="114" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C52" s="113" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D52" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E52" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F52" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G52" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H52" s="114" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B53" s="114" t="s">
-        <v>388</v>
+        <v>1127</v>
       </c>
       <c r="C53" s="113" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D53" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E53" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F53" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G53" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H53" s="114" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="25.5">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="51">
       <c r="A54" s="113" t="s">
         <v>1225</v>
       </c>
@@ -17505,7 +17532,7 @@
         <v>1133</v>
       </c>
       <c r="C54" s="113" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D54" s="113">
         <v>0.2</v>
@@ -17522,169 +17549,169 @@
         <v>673</v>
       </c>
       <c r="H54" s="114" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="113" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B55" s="114" t="s">
-        <v>495</v>
+        <v>93</v>
       </c>
       <c r="C55" s="113" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D55" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E55" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G55" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H55" s="114" t="s">
-        <v>676</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="113" t="s">
-        <v>1266</v>
+        <v>1224</v>
       </c>
       <c r="B56" s="114" t="s">
-        <v>605</v>
+        <v>388</v>
       </c>
       <c r="C56" s="113" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D56" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E56" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G56" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H56" s="114" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="113" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B57" s="114" t="s">
-        <v>1200</v>
+        <v>1133</v>
       </c>
       <c r="C57" s="113" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D57" s="113">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E57" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G57" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H57" s="114" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="113" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="B58" s="114" t="s">
-        <v>97</v>
+        <v>495</v>
       </c>
       <c r="C58" s="113" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D58" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E58" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G58" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H58" s="114" t="s">
-        <v>1268</v>
+        <v>676</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="113" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="B59" s="114" t="s">
-        <v>441</v>
+        <v>605</v>
       </c>
       <c r="C59" s="113" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D59" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E59" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G59" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H59" s="114" t="s">
-        <v>1269</v>
+        <v>676</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="113" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="B60" s="114" t="s">
-        <v>531</v>
+        <v>1200</v>
       </c>
       <c r="C60" s="113" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="D60" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E60" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G60" s="113" t="s">
         <v>673</v>
@@ -17698,111 +17725,195 @@
         <v>1221</v>
       </c>
       <c r="B61" s="114" t="s">
-        <v>600</v>
+        <v>97</v>
       </c>
       <c r="C61" s="113" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D61" s="113">
         <v>0.2</v>
       </c>
       <c r="E61" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G61" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H61" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="113" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="B62" s="114" t="s">
-        <v>93</v>
+        <v>441</v>
       </c>
       <c r="C62" s="113" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="D62" s="113">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E62" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G62" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H62" s="114" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="113" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B63" s="114" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
       <c r="C63" s="113" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="D63" s="113">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E63" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G63" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H63" s="114" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="25.5">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="113" t="s">
-        <v>1266</v>
+        <v>1221</v>
       </c>
       <c r="B64" s="114" t="s">
-        <v>1099</v>
+        <v>600</v>
       </c>
       <c r="C64" s="113" t="s">
-        <v>939</v>
+        <v>351</v>
       </c>
       <c r="D64" s="113">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E64" s="113">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G64" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H64" s="114" t="s">
         <v>1273</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="113" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B65" s="114" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" s="113" t="s">
+        <v>313</v>
+      </c>
+      <c r="D65" s="113">
+        <v>0</v>
+      </c>
+      <c r="E65" s="113">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F65" s="113">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="113" t="s">
+        <v>673</v>
+      </c>
+      <c r="H65" s="114" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="113" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B66" s="114" t="s">
+        <v>502</v>
+      </c>
+      <c r="C66" s="113" t="s">
+        <v>322</v>
+      </c>
+      <c r="D66" s="113">
+        <v>0</v>
+      </c>
+      <c r="E66" s="113">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F66" s="113">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G66" s="113" t="s">
+        <v>673</v>
+      </c>
+      <c r="H66" s="114" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="25.5">
+      <c r="A67" s="113" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B67" s="114" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C67" s="113" t="s">
+        <v>939</v>
+      </c>
+      <c r="D67" s="113">
+        <v>0</v>
+      </c>
+      <c r="E67" s="113">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F67" s="113">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G67" s="113" t="s">
+        <v>673</v>
+      </c>
+      <c r="H67" s="114" t="s">
+        <v>1276</v>
       </c>
     </row>
   </sheetData>
@@ -17813,7 +17924,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -17827,12 +17938,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -17876,7 +17987,7 @@
         <v>충분</v>
       </c>
       <c r="F5" s="114" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -17907,7 +18018,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="114" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -17931,14 +18042,14 @@
         <v>충분</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1">
@@ -17962,7 +18073,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -17975,18 +18086,18 @@
       </c>
       <c r="C9" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A9),0.5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18010,7 +18121,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="114" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18034,7 +18145,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18058,7 +18169,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18071,18 +18182,18 @@
       </c>
       <c r="C13" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A13),0.5)</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E13" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18106,7 +18217,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18130,10 +18241,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="114" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18161,7 +18272,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18185,7 +18296,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="114" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18209,7 +18320,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="114" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18233,7 +18344,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18246,18 +18357,18 @@
       </c>
       <c r="C20" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A20),0.5)</f>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D20" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="E20" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F20" s="114" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18281,7 +18392,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="114" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18305,7 +18416,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="114" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18329,7 +18440,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18353,7 +18464,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18377,7 +18488,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="114" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18390,7 +18501,7 @@
       </c>
       <c r="D26" s="115">
         <f ca="1">SUM(D5:D25)</f>
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -18400,127 +18511,157 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="107" t="s">
-        <v>1308</v>
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="123" t="s">
+        <v>1311</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="123" t="s">
-        <v>1309</v>
+      <c r="A41" s="107" t="s">
+        <v>1312</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="123" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="123" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="123" t="s">
-        <v>1315</v>
+      <c r="A47" s="107" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="123" t="s">
+        <v>1318</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="107" t="s">
-        <v>1316</v>
+      <c r="A49" s="123" t="s">
+        <v>1319</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="123" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="123" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="123" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="123" t="s">
-        <v>1323</v>
+      <c r="A56" s="107" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="123" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="123" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="123" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="123" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="123" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="123" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="123" t="s">
+        <v>1332</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B6E4A24D2AAD0B4F57A6D21DAB2044A989E03B05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_76F186AC3FC3234DF38ACB75283919D16C568EA2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="1342">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -3724,6 +3724,9 @@
     <t>복귀_월_가슴</t>
   </si>
   <si>
+    <t>프레스 중 팔꿈치 신전 — 5×5 저반복 본세트라 가슴이 먼저 실패하고 삼두 유효반복이 적다. 보조 프레스는 0.5 유지. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
     <t>프레스 중 팔꿈치 신전 — 강한 협력</t>
   </si>
   <si>
@@ -3736,6 +3739,9 @@
     <t>복귀_수_하체후면</t>
   </si>
   <si>
+    <t>오버헤드 프레스 삼두 신전 — 5×5 저반복 본세트 하향. 머신 숄더 프레스(0.5)와 구분. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
     <t>복귀_일_등광배</t>
   </si>
   <si>
@@ -3766,7 +3772,7 @@
     <t>엎침 그립 팔꿈치 굴곡 — 이두가 불리한 자리에서 보조한다. 재택 4일차와 같은 등급 (2026-10-02 종목을 넣을 때 빠뜨렸던 줄)</t>
   </si>
   <si>
-    <t>수평 내전 시 전면삼각 능동 관여</t>
+    <t>수평 프레스의 전면삼각 비대 근거는 인클라인(0.5)만큼 확실하지 않다. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>경사각이 클수록 전면삼각 기여 증가</t>
@@ -3781,7 +3787,7 @@
     <t>플라이 시작 구간 전면삼각 약관여 — 인클라인 덤벨 플라이와 같은 등급</t>
   </si>
   <si>
-    <t>머리 위 프레스 중 측면삼각 능동 외전</t>
+    <t>오버헤드 프레스 측면삼각 관여 — 5×5 본세트라 측면삼각이 자기 실패 근처에 못 간다. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>머리 위 프레스 중 측면삼각 외전 — 궤도가 고정돼 자유중량 프레스보다 부분적이다. 재택 맵에 있는 줄인데 복귀 맵에 계속 빠져 있었다 (2026-10-02 보충)</t>
@@ -3802,7 +3808,7 @@
     <t>로우 상단 견갑 거상 — 약한 관여</t>
   </si>
   <si>
-    <t>고장력 등척성 지지</t>
+    <t>고장력 등척성 견갑대 유지 — 버티기만 하는 자극은 세지 않는다. 재택 2026-09-04 0.2→0 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>견갑 하강은 동작 개시 관여라 약계수</t>
@@ -3817,7 +3823,7 @@
     <t>로우 당김 구간의 견갑 하강 관여. 재택 맵에 있는 줄인데 복귀 맵에 계속 빠져 있었다 (2026-10-02 보충)</t>
   </si>
   <si>
-    <t>수평 외전 + 견갑 후인 — 강한 협력</t>
+    <t>견갑 후인 능동 수축 — 경부하 리어델트 종목이라 리버스 펙덱(0.33)과 같은 등급. 중량 로우(0.5)와 구분. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>견갑 후인 부분 협력</t>
@@ -3826,7 +3832,7 @@
     <t>로우 중 견갑 후인</t>
   </si>
   <si>
-    <t>고장력 등척성 — 실패지점까지 가지 않음</t>
+    <t>고장력 등척성 — 척추 중립 받치기(길이변화 작음). 데드→광배(0)와 같은 근거로 0으로 통일. 재택 2026-09-04 0.2→0 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>상체 각도 유지 등척성</t>
@@ -3835,10 +3841,10 @@
     <t>선 자세 유지 등척성</t>
   </si>
   <si>
-    <t>중립 척추 유지 등척성. 0.2 무리 중에서는 가장 무거운 쪽이다</t>
-  </si>
-  <si>
-    <t>선 자세 유지 등척성 — 오버헤드 슈러그와 같은 등급 (2026-10-02)</t>
+    <t>루마니안은 기립근이 동적으로 신전 · 수축한다 — 등척성이 아니다. 그래서 '등척성은 0' 무리(스쿼트 · 트랩바 슈러그 · 데드 승모)와 달리 0.5다. 재택 맵이 그 줄에 명시해 둔 구분이고 복귀는 0.2로 낮게 잡고 있었다 (2026-10-02 재택 09-04 규칙서 정렬 · 0.2→0.5)</t>
+  </si>
+  <si>
+    <t>고장력 등척성 — 중량 받치기. 버티기만 하는 자극은 세지 않는다. 재택 2026-09-04 0.2→0 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>고관절 신전 능동</t>
@@ -3850,31 +3856,37 @@
     <t>힌지 중 고관절 신전 능동 — 데드와 같은 등급</t>
   </si>
   <si>
-    <t>고관절 신전 시 햄스트링 능동 협력</t>
-  </si>
-  <si>
-    <t>힌지 중 햄스트링 신장성 부하</t>
-  </si>
-  <si>
-    <t>톱세트와 같은 동작 (2026-10-02 백오프 복귀)</t>
+    <t>무릎 90도 고정이라 햄스트링이 짧아진 채 작동(능동부전) — 루마니안의 신장 부하와 같은 등급일 수 없다. 재택 2026-09-04 0.5→0.2 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
+    <t>힌지 — 햄스트링 준주동. 단 컨벤셔널은 바닥에서 무릎 신전이 먼저라 ROM이 루마니안보다 작다. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
+    <t>톱세트와 같은 동작이므로 같은 계수. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>발을 높이면 고관절 신전 비중이 오르지만 무릎도 같이 펴진다 — 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 햄스트링 길이가 거의 안 바뀌고, 능동 단축이 작으면 자극도 작다. 그래서 주동근은 둔근이고 햄스트링은 약관여다 (2026-10-02 사용자 지정 종목)</t>
   </si>
   <si>
-    <t>벌어진 스탠스 구간 약관여</t>
-  </si>
-  <si>
-    <t>벌어진 스탠스 구간 약관여 — 토요일 레그 프레스와 같은 등급 (2026-10-02)</t>
+    <t>대내전근은 고관절 신전근 — 깊은 스쿼트에서 동적 작동. 둔근(0.5)과 동급은 과하고 레그 프레스 · 불가리안(0.33)과 같은 등급. 재택 2026-09-04 0.5→0.33이 기준 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
+    <t>벌어진 스탠스 구간의 동적 관여 — 재택이 09-04에 못박은 기준 등급 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
+    <t>토요일 레그 프레스와 같은 등급. 발을 높이면 고관절 굽힘이 커져 대내전근 관여가 줄지는 않는다 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>컬 중 상완요골근 동적 굴곡 — 부분 협력 (2026-10-02)</t>
   </si>
   <si>
-    <t>플랫 벤치가 쇄골지에도 일부 기여</t>
-  </si>
-  <si>
-    <t>수평 내전이라 쇄골지에도 일부 기여 — 플랫 벤치와 같은 등급</t>
+    <t>흉근 상/하는 I열에서 합산 판정한다 — 서로에게 간접을 얹으면 합산이 이중 계상된다. 재택 2026-09-04 0.2→0 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
+    <t>흉근 상/하 합산 판정이라 교차 계상 제거 — 플랫 벤치와 같은 등급. 재택 2026-09-04 0.2→0 (2026-10-02 재택 09-04 규칙서 정렬)</t>
+  </si>
+  <si>
+    <t>흉근 상/하 합산 판정이라 교차 계상 제거. 재택 2026-09-04 0.2→0 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
     <t>흉늑지 약관여</t>
@@ -3895,10 +3907,10 @@
     <t>세트는 근육군 단위로 센다. 복귀판은 주 6회 · 주 단위이므로 이 표의 숫자가 곧 주간 세트다 — 재택판처럼 주당 환산을 할 필요가 없다.</t>
   </si>
   <si>
-    <t>직접 8세트: 월요일 인클라인 벤치프레스 머신 4 · 인클라인 덤벨 플라이 4. 간접 1.8 — 벤치 0.2×5 + 펙덱 플라이 0.2×4. 상부지를 복합 하나 · 고립 하나로 나눠 각 4세트다</t>
-  </si>
-  <si>
-    <t>직접 16세트: 월요일 벤치 5 · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 4. 간접 1.6 — 인클라인 머신 0.2×4 + 인클라인 플라이 0.2×4. 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
+    <t>직접 8세트: 월요일 인클라인 벤치프레스 머신 4 · 인클라인 덤벨 플라이 4. 간접 0 — 흉근 상/하는 I열에서 합산 판정하므로 서로에게 간접을 얹지 않는다(2026-10-02 교차 계상 제거). 상부지를 복합 하나 · 고립 하나로 나눠 각 4세트다. 단독 판정이 '하한'으로 뜨지만 흉근은 I열 합산(25.0)으로 판정한다</t>
+  </si>
+  <si>
+    <t>직접 16세트: 월요일 벤치 5 · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 4. 간접 0.8 — 인클라인 덤벨 플라이 0.2×4 (인클라인 머신의 교차 간접은 2026-10-02에 0으로). 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
   </si>
   <si>
     <t>직접 14세트: 일요일 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 3 · 원암 케이블 로우 3. 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3. 15 → 14는 날을 가르며 생긴 1세트 차이다</t>
@@ -3907,22 +3919,22 @@
     <t>등 합산</t>
   </si>
   <si>
-    <t>직접 3세트: 목요일 트랩바 슈러그 3 (2026-10-02 신설). 간접 1.6 — 오버헤드 프레스 · 스미스 로우 · 데드 각 0.2. 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
+    <t>직접 3세트: 목요일 트랩바 슈러그 3 (2026-10-02 신설). 간접 1.4 — 오버헤드 프레스 · 스미스 바벨 로우 각 0.2 (데드의 등척성 견갑대 유지는 2026-10-02에 0으로). 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
   </si>
   <si>
     <t>직접 3세트: 일요일 오버헤드 슈러그 3. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
   </si>
   <si>
-    <t>직접 10세트: 목요일 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3. 간접 5.3 — 케이블 리버스 플라이 0.5×3 + 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 벤트오버 레터럴 0.33×3</t>
-  </si>
-  <si>
-    <t>직접 3세트: 수요일 데드 톱 1 + 백오프 2 (2026-10-02 백오프 복귀). 간접 3.6 — 스쿼트 · 스미스 로우 · 오버헤드 슈러그 · 루마니안 데드 · 트랩바 슈러그 각 0.2. 현장 일이 허리에 하루치를 얹던 것이 끝나 1 → 3이 됐다</t>
-  </si>
-  <si>
-    <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 6.7 — 벤치 0.5×5 + 인클라인 머신 0.5×4 + 딥스 0.2×3 + 인클라인 플라이 0.2×4 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
-  </si>
-  <si>
-    <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.5 — 오버헤드 프레스 0.5×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
+    <t>직접 10세트: 목요일 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3. 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
+  </si>
+  <si>
+    <t>직접 3세트: 수요일 데드 톱 1 + 백오프 2 (2026-10-02 백오프 복귀). 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
+  </si>
+  <si>
+    <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 5.9 — 벤치 0.33×5 + 인클라인 머신 0.5×4 + 딥스 0.2×3 + 인클라인 플라이 0.2×4 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
+  </si>
+  <si>
+    <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.0 — 오버헤드 프레스 0.33×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
   </si>
   <si>
     <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 출처 없음 — 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블로 저항곡선을 갈랐다</t>
@@ -3934,10 +3946,10 @@
     <t>하체 합산(대퇴 · 햄 · 종아리)</t>
   </si>
   <si>
-    <t>직접 10세트: 토요일 레그 컬 4(양측 · 중량) + 수요일 루마니안 데드 3 · 원 레그 컬 3(편측 · 균형). 간접 3.8 — 힙 쓰러스트 0.5×3 + 백오프 0.5×2 + 데드 0.5×1 + 레그 프레스(발 높게) 0.2×4. [2026-10-02 사용자 지적] 전면 하체 날에 햄스트링이 0이라 4세트를 토요일로 옮겨 빈도를 주 2회로 쪼갰다 — 총량 10은 그대로다(내가 넣었던 시티드 레그 컬 3을 뺐다). 같은 날 사용자 제안으로 양측(중량)과 편측(균형)의 날을 맞바꿨다 — 중량은 전신 피로가 아니라 국소 피로가 정하고, 토요일은 햄스트링을 직접 쓰는 종목이 달리 없어 누적 24세트 뒤에도 국소로 신선하다</t>
-  </si>
-  <si>
-    <t>직접 7세트: 수요일 레그 프레스(발 높게) 4 · 힙 쓰러스트 3 (3 → 7). 간접 6.8 — 스쿼트 0.5×5 + 루마니안 0.5×3 + 데드 0.5×1 + 백오프 0.5×2 + 토요일 레그 프레스 0.33×4. [2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 두면 고관절 굽힘 범위가 커져 고관절 신전 비중이 오르고, 둔근이 그 동작의 주동근이다. 햄스트링은 무릎이 같이 펴져 길이가 거의 안 바뀌므로 약관여(0.2)로 뒀다</t>
+    <t>직접 10세트: 토요일 레그 컬 4(양측 · 중량) + 수요일 루마니안 데드 3 · 원 레그 컬 3(편측 · 균형). 간접 2.4 — 백오프 0.33×2 + 데드 0.33×1 + 힙 쓰러스트 0.2×3 + 레그 프레스(발 높게) 0.2×4 (힌지 ROM과 힙 쓰러스트 능동부전을 2026-10-02에 반영). [2026-10-02 사용자 지적] 전면 하체 날에 햄스트링이 0이라 4세트를 토요일로 옮겨 빈도를 주 2회로 쪼갰다 — 총량 10은 그대로다(내가 넣었던 시티드 레그 컬 3을 뺐다). 같은 날 사용자 제안으로 양측(중량)과 편측(균형)의 날을 맞바꿨다 — 중량은 전신 피로가 아니라 국소 피로가 정하고, 토요일은 햄스트링을 직접 쓰는 종목이 달리 없어 누적 24세트 뒤에도 국소로 신선하다</t>
+  </si>
+  <si>
+    <t>직접 7세트: 수요일 레그 프레스(발 높게) 4 · 힙 쓰러스트 3 (3 → 7). 간접 6.8 — (둔근 계수는 09-04 하향 대상이 아니었다) 스쿼트 0.5×5 + 루마니안 0.5×3 + 데드 0.5×1 + 백오프 0.5×2 + 토요일 레그 프레스 0.33×4. [2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 두면 고관절 굽힘 범위가 커져 고관절 신전 비중이 오르고, 둔근이 그 동작의 주동근이다. 햄스트링은 무릎이 같이 펴져 길이가 거의 안 바뀌므로 약관여(0.2)로 뒀다</t>
   </si>
   <si>
     <t>직접 11세트: 토요일 아우터 타이 4 · 수요일 아우터 타이 4 · 케이블 힙 외전 3 (7 → 11). 간접 출처 없음 — 스쿼트 · 레그 프레스는 양측 지지라 계수가 없다. [2026-10-02 사용자 요청] 수요일에 슈퍼세트를 얹어 하한(8) 아래였던 7.0이 11로 올라갔다. 앉아서 하는 아우터(고관절 굽힘)와 선 자세 편측 케이블(고관절 펴짐)로 각도를 나눴다</t>
@@ -3949,7 +3961,7 @@
     <t>직접 9세트: 일요일 프리쳐 컬 3 · 화요일 인클라인 덤벨 컬 3 · 목요일 케이블 드래그 컬 3 (6 → 9). 간접 7.3 — 당기기 6종목을 그립별로 (뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2) + 리버스컬 0.2×3. 짧아진 · 늘어난 · 중간 구간 셋으로 나눴다</t>
   </si>
   <si>
-    <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 9.0 — 프레스 5종목 0.5씩 (벤치 5 · 인클라인 머신 4 · 딥스 3 · 머신 숄더 3 · 오버헤드 3). 실질 18로 성장 구간 상단이다</t>
+    <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 7.6 — 인클라인 머신 · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향, 2026-10-02). 실질 16.5로 성장 구간 상단이다</t>
   </si>
   <si>
     <t>직접 9세트: 화요일 리버스컬 3 · 시티드 리스트 컬 굴근 3 · 신근 3 (6 → 9). 간접 3.0 — 컬 3종 0.33씩. 그립을 쓰는 당기기가 없는 유일한 날에 모아 뒀다. 현장 일이 그립에 하루치를 얹던 것이 끝나 올렸다</t>
@@ -3958,7 +3970,7 @@
     <t>직접 6세트: 화요일 중량 크런치 3 · 라잉 레그 레이즈 3 (3 → 6). 간접 출처 없음 — 스쿼트 · 데드의 브레이싱은 등척성이라 0. 현장 일이 코어를 버티게만 하던 것이 끝나 직접 굴곡을 늘렸다</t>
   </si>
   <si>
-    <t>직접 8세트: 토요일 이너 타이 4 · 수요일 이너 타이 4 (둘 다 아우터와 슈퍼세트, 4 → 8). 간접 2.6 — 스쿼트 0.2×5 + 레그 프레스 2종 각 0.2×4 (토 발 낮게 · 수 발 높게). 복귀판 초안에 통째로 비어 있던 자리이고 2026-09-13에 되살렸다. [2026-10-02 사용자 요청] 실질 6.5로 하한 아래였던 것이 10.5가 됐다 — 하체에서 마지막까지 하한 아래였던 자리다</t>
+    <t>직접 8세트: 토요일 이너 타이 4 · 수요일 이너 타이 4 (둘 다 아우터와 슈퍼세트, 4 → 8). 간접 4.3 — 스쿼트 0.33×5 + 레그 프레스 2종 각 0.33×4 (토 발 낮게 · 수 발 높게). 09-04가 0.33을 기준 등급으로 못박아 2026-10-02에 0.2에서 올렸다 — 유일하게 올라간 자리다. 복귀판 초안에 통째로 비어 있던 자리이고 2026-09-13에 되살렸다. [2026-10-02 사용자 요청] 실질 6.5로 하한 아래였던 것이 10.5가 됐다 — 하체에서 마지막까지 하한 아래였던 자리다</t>
   </si>
   <si>
     <t>직접 6세트: 화요일 넥 익스텐션 3 · 넥 플렉션 3. 2026-10-02 신설 — 사용자 요청으로 화요일 구성에 들어 있었다. 간접 출처 없음. 데드 · 슈러그의 목 지지는 등척성이라 계수를 주지 않는다. 첫 2주는 무게 없이 가동범위만</t>
@@ -3985,13 +3997,28 @@
     <t>· 영향 — 삼각 측면 11.5 → 12.5 · 승모 하부 5.0 → 6.0 · 이두 15.5 → 16.5. 직접 세트는 하나도 안 바뀌었다.</t>
   </si>
   <si>
-    <t>· 아직 남은 것 — 재택 맵과 복귀 맵의 계수가 아홉 군데 다르다. 프레스 → 삼두 · 삼각 전면(재택 0.33 / 복귀 0.5) · 데드 → 햄스트링(0.33 / 0.5) · 힙 쓰러스트 → 햄스트링(0.2 / 0.5) · 루마니안 → 기립근(0.5 / 0.2) · 스쿼트 · 레그 프레스 → 내전근(0.33 / 0.2) · 스쿼트 → 기립근(0 / 0.2) · 벤치 → 흉근 상부(0 / 0.2) · 인클라인 머신 → 흉근 중하부(0 / 0.2) · 케이블 리버스 플라이 → 승모 중부(0.33 / 0.5) · 트랩바 슈러그 → 기립근(0 / 0.2).</t>
-  </si>
-  <si>
-    <t>· 두 맵이 다른 시점에 쓰여 같은 규칙서를 안 쓴다. 한쪽으로 맞추면 판정 축이 또 한 번 바뀌므로 사용자 결정 전까지는 손대지 않는다 — 계수를 일괄로 움직이는 것은 거부된 방식이다.</t>
-  </si>
-  <si>
-    <t>· 방향만 적어 두면: 복귀가 재택보다 높은 곳은 프레스 계열과 힙 쓰러스트 · 스쿼트 기립근, 낮은 곳은 내전근과 루마니안 기립근이다. 한쪽이 전체적으로 높거나 낮은 것이 아니라 항목마다 갈린다.</t>
+    <t>· 같은 날 18줄을 2026-09-04 규칙서로 정렬했다(사용자 결정). 복귀 맵은 09-13에 새로 쓰이며 하향 전 값을 쓰고 있었고, 재택 맵에는 줄마다 하향 이력이 근거와 함께 적혀 있었다 — 취향 차가 아니라 갱신 누락이었다.</t>
+  </si>
+  <si>
+    <t>· 내린 곳 — 벤치 · 오버헤드 프레스 → 삼두 · 삼각근 0.5→0.33(저반복 본세트라 협력근이 자기 실패에 못 간다) · 데드 · 백오프 → 햄스트링 0.5→0.33(컨벤셔널 ROM) · 힙 쓰러스트 → 햄스트링 0.5→0.2(무릎 90도 능동부전) · 케이블 리버스 플라이 → 승모 중부 0.5→0.33(경부하 리어델트).</t>
+  </si>
+  <si>
+    <t>· 0으로 내린 곳 — 스쿼트 · 트랩바 슈러그 → 기립근 · 데드 → 승모 상부. 전부 고장력 등척성이고 '버티기만 하는 자극은 세지 않는다'가 09-04 규칙이다. 벤치 → 흉근 상부 · 인클라인 머신 → 흉근 중하부도 0 — 흉근 상/하는 합산으로 판정하므로 교차 간접은 이중 계상이었다.</t>
+  </si>
+  <si>
+    <t>· 올린 곳 — 스쿼트 · 레그 프레스 2종 → 내전근 0.2→0.33(09-04가 0.33을 기준 등급으로 못박았다)과 루마니안 → 기립근 0.2→0.5. 루마니안은 기립근이 동적으로 신전 · 수축하므로 등척성 무리와 구분된다 — 재택 맵이 그 줄에 명시해 둔 구분이다.</t>
+  </si>
+  <si>
+    <t>· 결과 — 실질 총계 240 → 234.5. 흉근 합산 27.5 → 25.0(이중 계상 제거) · 삼두 18.0 → 16.5 · 햄스트링 14.0 → 12.5 · 기립근 6.5 → 6.0 · 내전근 10.5 → 12.5. 직접 세트 176과 훈련 내용은 한 칸도 안 바뀌었다 — 자가 바뀐 것이다.</t>
+  </si>
+  <si>
+    <t>· 이제 재택 수치와 복귀 수치를 직접 비교할 수 있다. 그 전에는 같은 종목에 다른 계수가 매겨져 있어 주당 환산을 나란히 놓는 것 자체가 틀렸다.</t>
+  </si>
+  <si>
+    <t>· 정렬 뒤 재택 맵과 다른 줄은 0개다 — 같은 종목에 같은 계수가 매겨져 두 판의 수치를 직접 비교할 수 있다.</t>
+  </si>
+  <si>
+    <t>· 아직 09-04 규칙서에 대응 줄이 없어 그대로 둔 곳 셋 — 스미스 바벨 로우 → 기립근 0.2 · 오버헤드 슈러그 → 기립근 0.2 · 레그 프레스(발 높게) → 햄스트링 0.2. 같은 '등척성은 0' 논리를 밀면 앞의 둘은 0이 된다. 재택 맵에 대응 줄이 없어 판정 근거가 없으므로 손대지 않았다 — 다음 카드는 여기다.</t>
   </si>
   <si>
     <t>[현장 일 보정 열을 걷어냈다 — 2026-10-02]</t>
@@ -16208,7 +16235,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="113" t="s">
         <v>1221</v>
       </c>
@@ -16219,7 +16246,7 @@
         <v>359</v>
       </c>
       <c r="D7" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E7" s="113">
         <f t="shared" ref="E7:E38" ca="1" si="0">IFERROR(INDEX(INDIRECT("'"&amp;$A7&amp;"'!$E$1:$E$45"),MATCH($B7,INDIRECT("'"&amp;$A7&amp;"'!$B$1:$B$45"),0)),"?")</f>
@@ -16227,7 +16254,7 @@
       </c>
       <c r="F7" s="113">
         <f t="shared" ref="F7:F38" ca="1" si="1">IF(ISNUMBER(E7),$D7*E7,0)</f>
-        <v>2.5</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G7" s="113" t="s">
         <v>673</v>
@@ -16261,7 +16288,7 @@
         <v>673</v>
       </c>
       <c r="H8" s="114" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -16289,12 +16316,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="114" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B10" s="114" t="s">
         <v>522</v>
@@ -16317,12 +16344,12 @@
         <v>673</v>
       </c>
       <c r="H10" s="114" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B11" s="114" t="s">
         <v>1138</v>
@@ -16331,7 +16358,7 @@
         <v>359</v>
       </c>
       <c r="D11" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E11" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16339,18 +16366,18 @@
       </c>
       <c r="F11" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G11" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H11" s="114" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B12" s="114" t="s">
         <v>280</v>
@@ -16373,12 +16400,12 @@
         <v>673</v>
       </c>
       <c r="H12" s="114" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B13" s="114" t="s">
         <v>1031</v>
@@ -16401,12 +16428,12 @@
         <v>673</v>
       </c>
       <c r="H13" s="114" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B14" s="114" t="s">
         <v>1028</v>
@@ -16429,12 +16456,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="114" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B15" s="114" t="s">
         <v>486</v>
@@ -16457,12 +16484,12 @@
         <v>673</v>
       </c>
       <c r="H15" s="114" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B16" s="114" t="s">
         <v>1184</v>
@@ -16485,12 +16512,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="114" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B17" s="114" t="s">
         <v>479</v>
@@ -16513,12 +16540,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="114" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="113" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B18" s="114" t="s">
         <v>453</v>
@@ -16541,10 +16568,10 @@
         <v>673</v>
       </c>
       <c r="H18" s="114" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="113" t="s">
         <v>1221</v>
       </c>
@@ -16555,7 +16582,7 @@
         <v>443</v>
       </c>
       <c r="D19" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E19" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16563,13 +16590,13 @@
       </c>
       <c r="F19" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G19" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H19" s="114" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -16597,7 +16624,7 @@
         <v>673</v>
       </c>
       <c r="H20" s="114" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -16625,7 +16652,7 @@
         <v>673</v>
       </c>
       <c r="H21" s="114" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -16653,12 +16680,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="114" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B23" s="114" t="s">
         <v>441</v>
@@ -16681,12 +16708,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="114" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="38.25">
       <c r="A24" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B24" s="114" t="s">
         <v>1138</v>
@@ -16695,7 +16722,7 @@
         <v>368</v>
       </c>
       <c r="D24" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E24" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16703,18 +16730,18 @@
       </c>
       <c r="F24" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G24" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H24" s="114" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B25" s="114" t="s">
         <v>522</v>
@@ -16737,12 +16764,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="114" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B26" s="114" t="s">
         <v>1133</v>
@@ -16765,12 +16792,12 @@
         <v>673</v>
       </c>
       <c r="H26" s="114" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B27" s="114" t="s">
         <v>1184</v>
@@ -16793,12 +16820,12 @@
         <v>673</v>
       </c>
       <c r="H27" s="114" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B28" s="114" t="s">
         <v>479</v>
@@ -16821,12 +16848,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="114" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B29" s="114" t="s">
         <v>95</v>
@@ -16849,12 +16876,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="114" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B30" s="114" t="s">
         <v>1138</v>
@@ -16877,12 +16904,12 @@
         <v>673</v>
       </c>
       <c r="H30" s="114" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B31" s="114" t="s">
         <v>1184</v>
@@ -16905,12 +16932,12 @@
         <v>673</v>
       </c>
       <c r="H31" s="114" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="25.5">
       <c r="A32" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B32" s="114" t="s">
         <v>95</v>
@@ -16919,7 +16946,7 @@
         <v>421</v>
       </c>
       <c r="D32" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -16927,18 +16954,18 @@
       </c>
       <c r="F32" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G32" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H32" s="114" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B33" s="114" t="s">
         <v>280</v>
@@ -16961,12 +16988,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="114" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B34" s="114" t="s">
         <v>1031</v>
@@ -16989,12 +17016,12 @@
         <v>673</v>
       </c>
       <c r="H34" s="114" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B35" s="114" t="s">
         <v>1028</v>
@@ -17017,12 +17044,12 @@
         <v>673</v>
       </c>
       <c r="H35" s="114" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="25.5">
       <c r="A36" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B36" s="114" t="s">
         <v>479</v>
@@ -17045,10 +17072,10 @@
         <v>673</v>
       </c>
       <c r="H36" s="114" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="38.25">
       <c r="A37" s="113" t="s">
         <v>1221</v>
       </c>
@@ -17059,7 +17086,7 @@
         <v>296</v>
       </c>
       <c r="D37" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E37" s="113">
         <f t="shared" ca="1" si="0"/>
@@ -17067,18 +17094,18 @@
       </c>
       <c r="F37" s="113">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G37" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H37" s="114" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B38" s="114" t="s">
         <v>537</v>
@@ -17101,12 +17128,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="114" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B39" s="114" t="s">
         <v>994</v>
@@ -17129,12 +17156,12 @@
         <v>673</v>
       </c>
       <c r="H39" s="114" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B40" s="114" t="s">
         <v>486</v>
@@ -17157,12 +17184,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="114" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="38.25">
       <c r="A41" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B41" s="114" t="s">
         <v>93</v>
@@ -17171,7 +17198,7 @@
         <v>327</v>
       </c>
       <c r="D41" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17179,18 +17206,18 @@
       </c>
       <c r="F41" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H41" s="114" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B42" s="114" t="s">
         <v>1184</v>
@@ -17213,12 +17240,12 @@
         <v>673</v>
       </c>
       <c r="H42" s="114" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B43" s="114" t="s">
         <v>431</v>
@@ -17241,12 +17268,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="114" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="51">
       <c r="A44" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B44" s="114" t="s">
         <v>573</v>
@@ -17255,7 +17282,7 @@
         <v>327</v>
       </c>
       <c r="D44" s="113">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E44" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17263,18 +17290,18 @@
       </c>
       <c r="F44" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>1.5</v>
       </c>
       <c r="G44" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H44" s="114" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="25.5">
       <c r="A45" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B45" s="114" t="s">
         <v>498</v>
@@ -17283,7 +17310,7 @@
         <v>327</v>
       </c>
       <c r="D45" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17291,18 +17318,18 @@
       </c>
       <c r="F45" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G45" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H45" s="114" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B46" s="114" t="s">
         <v>93</v>
@@ -17330,7 +17357,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B47" s="114" t="s">
         <v>95</v>
@@ -17353,12 +17380,12 @@
         <v>673</v>
       </c>
       <c r="H47" s="114" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B48" s="114" t="s">
         <v>1127</v>
@@ -17381,12 +17408,12 @@
         <v>673</v>
       </c>
       <c r="H48" s="114" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B49" s="114" t="s">
         <v>388</v>
@@ -17414,7 +17441,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B50" s="114" t="s">
         <v>573</v>
@@ -17437,12 +17464,12 @@
         <v>673</v>
       </c>
       <c r="H50" s="114" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="38.25">
       <c r="A51" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B51" s="114" t="s">
         <v>570</v>
@@ -17451,7 +17478,7 @@
         <v>398</v>
       </c>
       <c r="D51" s="113">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E51" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17459,18 +17486,18 @@
       </c>
       <c r="F51" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H51" s="114" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B52" s="114" t="s">
         <v>95</v>
@@ -17479,7 +17506,7 @@
         <v>398</v>
       </c>
       <c r="D52" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E52" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17487,18 +17514,18 @@
       </c>
       <c r="F52" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="G52" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H52" s="114" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="25.5">
       <c r="A53" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B53" s="114" t="s">
         <v>1127</v>
@@ -17507,7 +17534,7 @@
         <v>398</v>
       </c>
       <c r="D53" s="113">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E53" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17515,18 +17542,18 @@
       </c>
       <c r="F53" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="G53" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H53" s="114" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="51">
       <c r="A54" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B54" s="114" t="s">
         <v>1133</v>
@@ -17549,12 +17576,12 @@
         <v>673</v>
       </c>
       <c r="H54" s="114" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="38.25">
       <c r="A55" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B55" s="114" t="s">
         <v>93</v>
@@ -17563,7 +17590,7 @@
         <v>402</v>
       </c>
       <c r="D55" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E55" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17571,18 +17598,18 @@
       </c>
       <c r="F55" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G55" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H55" s="114" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="25.5">
       <c r="A56" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B56" s="114" t="s">
         <v>388</v>
@@ -17591,7 +17618,7 @@
         <v>402</v>
       </c>
       <c r="D56" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E56" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17599,18 +17626,18 @@
       </c>
       <c r="F56" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="G56" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H56" s="114" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="113" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B57" s="114" t="s">
         <v>1133</v>
@@ -17619,7 +17646,7 @@
         <v>402</v>
       </c>
       <c r="D57" s="113">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E57" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17627,18 +17654,18 @@
       </c>
       <c r="F57" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="G57" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H57" s="114" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="113" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B58" s="114" t="s">
         <v>495</v>
@@ -17666,7 +17693,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="113" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B59" s="114" t="s">
         <v>605</v>
@@ -17694,7 +17721,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B60" s="114" t="s">
         <v>1200</v>
@@ -17717,10 +17744,10 @@
         <v>673</v>
       </c>
       <c r="H60" s="114" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="38.25">
       <c r="A61" s="113" t="s">
         <v>1221</v>
       </c>
@@ -17731,7 +17758,7 @@
         <v>363</v>
       </c>
       <c r="D61" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E61" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17739,18 +17766,18 @@
       </c>
       <c r="F61" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H61" s="114" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="25.5">
       <c r="A62" s="113" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B62" s="114" t="s">
         <v>441</v>
@@ -17759,7 +17786,7 @@
         <v>363</v>
       </c>
       <c r="D62" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E62" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17767,16 +17794,16 @@
       </c>
       <c r="F62" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G62" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H62" s="114" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="113" t="s">
         <v>1221</v>
       </c>
@@ -17787,7 +17814,7 @@
         <v>351</v>
       </c>
       <c r="D63" s="113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E63" s="113">
         <f t="shared" ca="1" si="2"/>
@@ -17795,13 +17822,13 @@
       </c>
       <c r="F63" s="113">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G63" s="113" t="s">
         <v>673</v>
       </c>
       <c r="H63" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -17829,12 +17856,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="114" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B65" s="114" t="s">
         <v>93</v>
@@ -17857,12 +17884,12 @@
         <v>673</v>
       </c>
       <c r="H65" s="114" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="113" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B66" s="114" t="s">
         <v>502</v>
@@ -17885,12 +17912,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="114" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="25.5">
       <c r="A67" s="113" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B67" s="114" t="s">
         <v>1099</v>
@@ -17913,7 +17940,7 @@
         <v>673</v>
       </c>
       <c r="H67" s="114" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
   </sheetData>
@@ -17924,7 +17951,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -17938,12 +17965,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -17976,25 +18003,25 @@
       </c>
       <c r="C5" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A5),0.5)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="113">
         <f t="shared" ref="D5:D25" ca="1" si="0">B5+C5</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="113" t="str">
         <f t="shared" ref="E5:E25" ca="1" si="1">IF(D5&gt;20,"과다 점검",IF(D5&gt;=10,"충분",IF(D5&gt;=8,"하한",IF(D5&gt;=1,"보완 필요","미배치"))))</f>
-        <v>충분</v>
+        <v>하한</v>
       </c>
       <c r="F5" s="114" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
       </c>
       <c r="I5" s="125">
         <f ca="1">SUM(D5:D6)</f>
-        <v>27.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1">
@@ -18007,18 +18034,18 @@
       </c>
       <c r="C6" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A6),0.5)</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D6" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="E6" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F6" s="114" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18042,14 +18069,14 @@
         <v>충분</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
-        <v>43.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1">
@@ -18073,7 +18100,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18097,7 +18124,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18110,18 +18137,18 @@
       </c>
       <c r="C10" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A10),0.5)</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D10" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="E10" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F10" s="114" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18134,18 +18161,18 @@
       </c>
       <c r="C11" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A11),0.5)</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18158,18 +18185,18 @@
       </c>
       <c r="C12" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A12),0.5)</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="E12" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18182,18 +18209,18 @@
       </c>
       <c r="C13" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A13),0.5)</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="E13" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18217,7 +18244,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18241,14 +18268,14 @@
         <v>충분</v>
       </c>
       <c r="F15" s="114" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
-        <v>33.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
@@ -18261,18 +18288,18 @@
       </c>
       <c r="C16" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A16),0.5)</f>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="E16" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18296,7 +18323,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="114" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18320,7 +18347,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="114" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18344,7 +18371,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18368,7 +18395,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="114" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18381,18 +18408,18 @@
       </c>
       <c r="C21" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A21),0.5)</f>
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D21" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="E21" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F21" s="114" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18416,7 +18443,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="114" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18440,7 +18467,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18453,18 +18480,18 @@
       </c>
       <c r="C24" s="113">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A24),0.5)</f>
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24" s="113">
         <f t="shared" ca="1" si="0"/>
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="E24" s="113" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18488,7 +18515,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="114" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18501,7 +18528,7 @@
       </c>
       <c r="D26" s="115">
         <f ca="1">SUM(D5:D25)</f>
-        <v>240</v>
+        <v>234.5</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -18511,157 +18538,182 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1311</v>
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="123" t="s">
+        <v>1316</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="107" t="s">
-        <v>1312</v>
+      <c r="A41" s="123" t="s">
+        <v>1317</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="123" t="s">
-        <v>1316</v>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="107" t="s">
+        <v>1321</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="107" t="s">
-        <v>1317</v>
+      <c r="A47" s="123" t="s">
+        <v>1322</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="123" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="123" t="s">
-        <v>1322</v>
+      <c r="A52" s="107" t="s">
+        <v>1326</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1324</v>
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="123" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="107" t="s">
-        <v>1325</v>
+      <c r="A56" s="123" t="s">
+        <v>1330</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="123" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="123" t="s">
-        <v>1330</v>
+      <c r="A61" s="107" t="s">
+        <v>1334</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1332</v>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="123" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="123" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="123" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="123" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="123" t="s">
+        <v>1341</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_76F186AC3FC3234DF38ACB75283919D16C568EA2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_4FE98431F553776E9BA9B565A2E40611C52B1BB6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="1342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1351">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -103,10 +103,10 @@
     <t>주당 환산 161세트</t>
   </si>
   <si>
-    <t>176세트</t>
-  </si>
-  <si>
-    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 셋(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터)</t>
+    <t>179세트</t>
+  </si>
+  <si>
+    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 넷(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 토요일 페이스풀)</t>
   </si>
   <si>
     <t>증량 방식</t>
@@ -2809,10 +2809,10 @@
     <t>하체 전면(사두) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 95분</t>
-  </si>
-  <si>
-    <t>스쿼트 5×5가 앞, 어깨 블록이 4~6번. 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 레그 컬 · 이너 · 아우터 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다 — 햄스트링 중량은 이 날이 가장 잘 나온다(토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하다)</t>
+    <t>약 100분</t>
+  </si>
+  <si>
+    <t>스쿼트 5×5가 앞, 어깨 블록이 4~7번(프레스 · 레터럴 · 리버스 펙덱 · 페이스풀). 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 레그 컬 · 이너 · 아우터 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다 — 햄스트링 중량은 이 날이 가장 잘 나온다</t>
   </si>
   <si>
     <t>일</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 427분 (7시간 7분)</t>
+    <t>약 433분 (7시간 13분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -2923,13 +2923,13 @@
     <t>[빈도를 올리고 볼륨은 조금만 올렸다 — 2026-10-02]</t>
   </si>
   <si>
-    <t>· 주 4회 140세트 → 주 6회 176세트. 세트는 26% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 빈도가 주 1회 → 2회로 올랐다.</t>
+    <t>· 주 4회 140세트 → 주 6회 179세트. 세트는 28% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회로 올랐다. 주 1회로 남은 것은 광배(일 14)와 사두(토 12)뿐이다.</t>
   </si>
   <si>
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
   </si>
   <si>
-    <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). 164 → 168 → 176.</t>
+    <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). ④ 토요일 페이스풀 3 — 승모 중부 · 능형근이 주 1회로 남아 있던 것을 주 2회로 쪼갰고, 어깨 보조가 전부 외전인 날에 견갑 후인 · 외회전을 더했다. 164 → 168 → 176 → 179.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -2980,16 +2980,16 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 수 39세트 98분 · 토 38세트 95분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
-  </si>
-  <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
+    <t>· 토 41세트 100분 · 수 39세트 98분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 29를 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
   </si>
   <si>
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 주 427분 = 7시간 7분. 주 4회 370분에서 57분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 주 433분 = 7시간 13분. 주 4회 370분에서 63분 늘었다. 토(100) · 수(98)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3013,6 +3013,18 @@
     <t>토요일 — 하체 전면 · 어깨 (전/측/후)</t>
   </si>
   <si>
+    <t>웜업 — 회전근개 (세트 카운트 제외 · 어깨 블록 직전에)</t>
+  </si>
+  <si>
+    <t>· 스쿼트 램프와 따로다. 하체 3종목을 끝내고 어깨 블록(4번)에 들어가기 직전에 넣는다 — 그래야 식지 않는다.</t>
+  </si>
+  <si>
+    <t>· 케이블 외회전 2세트 × 12~15회. 팔꿈치 90도로 접어 옆구리에 붙이고 바깥으로만 회전. 매우 가볍게 — 2.5~5kg. 무거우면 광배와 후면 삼각근이 대신 일하며 목적을 잃는다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 보충] 어깨 보조가 11세트 이어지는 날인데 이 블록이 빠져 있었다. 일 · 월 · 목에는 있었다.</t>
+  </si>
+  <si>
     <t>매주 미는 세 리프트 중 하나. 금요일 휴식 다음날이라 주 전체에서 가장 신선한 자리다. 실패지점 3~4회 남기고 멈춘다.</t>
   </si>
   <si>
@@ -3043,12 +3055,18 @@
     <t>리버스 펙덱</t>
   </si>
   <si>
-    <t>후면 삼각. 월요일 케이블 리버스 플라이와 저항곡선이 갈린다 — 머신은 중간 구간, 케이블은 수축 끝단.</t>
+    <t>후면 삼각. 월요일 케이블 리버스 플라이와 저항곡선이 갈린다 — 머신은 중간 구간, 케이블은 수축 끝단. 팔을 편 채 수평 외전만 하므로 견갑 후인 · 외회전은 다음 종목(페이스풀)이 맡는다.</t>
   </si>
   <si>
     <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
   </si>
   <si>
+    <t>[2026-10-02 사용자 제안] 승모 중부 · 능형근이 주 1회(목요일 10세트)로 남아 있었다 — 다른 큰 부위는 전부 주 2회로 쪼갰는데 여기만 안 쪼개져 있었다. 이 3세트로 주 2회가 된다. 어깨 보조 11세트가 전부 외전 · 수평 외전인 날에 견갑 후인 + 외회전을 동시에 하는 유일한 종목이기도 하다. 로프를 얼굴 높이로 당기고 팔꿈치를 어깨선 위로 — 끝에서 외회전을 만든다. 재택 1일차와 같은 등급 · 같은 계수.</t>
+  </si>
+  <si>
+    <t>리어 델트 로우 (로프) / 케이블 리버스 플라이 (팔 편 채) / 리버스 펙덱</t>
+  </si>
+  <si>
     <t>[2026-10-02 추가 — 사용자 지적, 같은 날 수요일 원 레그 컬과 자리 교환] 전면 하체만 12세트인 날에 햄스트링이 0이었다. 이 4세트로 햄스트링이 주 1회 → 2회가 된다(여기 4 + 수요일 6). 이 날이 중량을 밀기에 가장 좋은 자리다 — 토요일엔 햄스트링을 직접 쓰는 종목이 하나도 없어 누적 24세트를 지나도 햄스트링 자체는 국소로 신선하다. 중량은 전신 피로가 아니라 국소 피로가 정한다. 그래서 후반 고립 블록의 첫 자리를 줬다.</t>
   </si>
   <si>
@@ -3082,10 +3100,10 @@
     <t>· 하체를 전면 · 후면으로 갈라 토요일이 사두 전담이 됐다. 스쿼트 · 레그 프레스 · 익스텐션 12세트로 사두 주간 세트가 한 날에 다 들어간다.</t>
   </si>
   <si>
-    <t>· 어깨 블록을 4~6번에 둔 이유 — 레그 컬 · 이너 · 아우터 타이 · 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 15세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
-  </si>
-  <si>
-    <t>· 토요일에 어깨 세 방향(전 · 측 · 후)을 다 넣는 것이 사용자 지정이다. 전면은 머신 숄더, 측면은 덤벨 레터럴, 후면은 리버스 펙덱.</t>
+    <t>· 어깨 블록을 4~7번에 둔 이유 — 레그 컬 · 이너 · 아우터 타이 · 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 15세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
+  </si>
+  <si>
+    <t>· 토요일에 어깨 세 방향(전 · 측 · 후)을 다 넣는 것이 사용자 지정이다. 전면은 머신 숄더, 측면은 덤벨 레터럴, 후면은 리버스 펙덱, 그리고 2026-10-02부터 견갑 후인 · 외회전을 페이스풀이 맡는다.</t>
   </si>
   <si>
     <t>· [2026-10-02] 햄스트링 4세트를 더했다. 사두는 스쿼트 5×5 때문에 쪼갤 수 없어 주 1회지만 햄스트링은 쪼갤 수 있고, 전면 하체 날에 햄스트링이 0이면 무릎을 한쪽으로만 때리는 날이 된다.</t>
@@ -3094,10 +3112,10 @@
     <t>· [2026-10-02 같은 날 교환] 처음엔 원 레그 컬 3을 뒀는데 사용자 제안으로 수요일 양측 레그 컬과 바꿨다. 토요일엔 햄스트링을 직접 쓰는 종목이 없어 국소로 신선하므로 중량 종목(양측)이 맞고, 편측은 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 둘 다 반대로 놓여 있었다.</t>
   </si>
   <si>
-    <t>· 38세트 · 약 95분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 레그 컬 · 이너 · 아우터 · 카프 26세트)은 예외로 본다 — 실질 12세트다.</t>
-  </si>
-  <si>
-    <t>· 여섯 날 중 둘째로 크다. 그래도 주 4회 시절 토요일(43세트 · 107분)보다는 작다.</t>
+    <t>· 41세트 · 약 100분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 페이스풀 · 레그 컬 · 이너 · 아우터 · 카프 29세트)은 예외로 본다 — 실질 12세트다.</t>
+  </si>
+  <si>
+    <t>· 여섯 날 중 가장 크다. 그래도 주 4회 시절 토요일(43세트 · 107분) · 일요일(44세트 · 121분)보다는 작다.</t>
   </si>
   <si>
     <t>· 웜업은 별도다. 스쿼트가 있는 날이므로 10~15분을 더 잡는다.</t>
@@ -3115,7 +3133,7 @@
     <t>· N열 '드롭(초)'는 마지막 세트에 더해지는 시간이다. I열 종목 분에 합산되고, 앱 타이머는 마지막 세트를 그만큼 늘린 뒤 '드롭세트'라고 읊는다. E열 세트 수와 복귀_세트검산은 건드리지 않는다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???  /  아 원 레그 컬이랑 토요일 레그컬 자리 바꾸는거 어떻게 생각해?</t>
+    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???  /  아 원 레그 컬이랑 토요일 레그컬 자리 바꾸는거 어떻게 생각해?  /  토요일 페이스풀 넣는게 안 낫겠나?</t>
   </si>
   <si>
     <t>일요일 — 등(광배) · 팔</t>
@@ -3127,9 +3145,6 @@
     <t>· 이 날은 증량을 추적하는 메인 리프트가 없다. 첫 종목(친업) 전에 랫풀다운 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
   </si>
   <si>
-    <t>· 케이블 외회전 2세트 × 12~15회. 팔꿈치 90도로 접어 옆구리에 붙이고 바깥으로만 회전. 매우 가볍게 — 2.5~5kg. 무거우면 광배와 후면 삼각근이 대신 일하며 목적을 잃는다.</t>
-  </si>
-  <si>
     <t>· 둘 다 근비대 항목이 아니라 관절 준비 항목이므로 세트 합계에 넣지 않는다.</t>
   </si>
   <si>
@@ -3433,6 +3448,15 @@
     <t>메인: 스미스 오버헤드 프레스</t>
   </si>
   <si>
+    <t>웜업 — 회전근개 (세트 카운트 제외 · 오버헤드 프레스 직전에)</t>
+  </si>
+  <si>
+    <t>· 데드 램프 · 프레스 램프와 따로다. 하체 5종목을 끝내고 오버헤드 프레스(6번)에 들어가기 직전에 넣는다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 보충] 메인이 둘이라 램프 블록 두 개에 가려 이 블록이 빠져 있었다. 어깨 보조가 9세트 이어지고 그 앞에 증량을 추적하는 프레스가 있는 날이다.</t>
+  </si>
+  <si>
     <t>톱세트. 현장 근무가 끝나 허리와 경쟁하는 것이 없어졌으므로 2026-10-02부터 백오프 2세트를 되살려 성장으로 돌린다.</t>
   </si>
   <si>
@@ -3787,6 +3811,9 @@
     <t>플라이 시작 구간 전면삼각 약관여 — 인클라인 덤벨 플라이와 같은 등급</t>
   </si>
   <si>
+    <t>페이스풀 중 후면삼각 능동 수축 — 재택 1일차와 같은 등급. 주동근(승모 중부 · 능형근)은 요일 시트에서 직접으로 센다 (2026-10-02)</t>
+  </si>
+  <si>
     <t>오버헤드 프레스 측면삼각 관여 — 5×5 본세트라 측면삼각이 자기 실패 근처에 못 간다. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
@@ -3925,7 +3952,7 @@
     <t>직접 3세트: 일요일 오버헤드 슈러그 3. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
   </si>
   <si>
-    <t>직접 10세트: 목요일 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3. 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
+    <t>직접 13세트: 목요일 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 토요일 페이스풀 3. [2026-10-02 사용자 제안] 주 1회(목요일)로 남아 있던 유일한 큰 부위라 토요일에 3세트를 더해 주 2회로 쪼갰다. 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
   </si>
   <si>
     <t>직접 3세트: 수요일 데드 톱 1 + 백오프 2 (2026-10-02 백오프 복귀). 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
@@ -3937,7 +3964,7 @@
     <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.0 — 오버헤드 프레스 0.33×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
   </si>
   <si>
-    <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 출처 없음 — 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블로 저항곡선을 갈랐다</t>
+    <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 1.5 — 토요일 페이스풀 0.5×3(2026-10-02). 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블 · 로프로 저항곡선과 외회전 요소를 갈랐다</t>
   </si>
   <si>
     <t>직접 12세트: 토요일 스쿼트 5 · 레그 프레스 4 · 레그 익스텐션 3. 간접 1.3 — 수요일 레그 프레스(발 높게) 0.33×4. 직접은 주 1회다(스쿼트 5×5가 한 날을 다 쓴다) — 다만 수요일 간접 덕에 자극 노출은 주 2회가 됐다 (2026-10-02)</t>
@@ -4439,14 +4466,14 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4850,19 +4877,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4872,16 +4902,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4890,7 +4917,7 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11051,207 +11078,207 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="110" t="s">
+      <c r="A5" s="111" t="s">
         <v>909</v>
       </c>
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="111" t="s">
         <v>910</v>
       </c>
-      <c r="C5" s="110" t="s">
+      <c r="C5" s="111" t="s">
         <v>911</v>
       </c>
-      <c r="D5" s="110" t="s">
+      <c r="D5" s="111" t="s">
         <v>912</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="110" t="s">
+      <c r="F5" s="111" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="110" t="s">
+      <c r="G5" s="111" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="114" t="s">
         <v>914</v>
       </c>
       <c r="B6" s="120" t="s">
         <v>915</v>
       </c>
-      <c r="C6" s="113" t="s">
+      <c r="C6" s="114" t="s">
         <v>911</v>
       </c>
-      <c r="D6" s="114" t="s">
+      <c r="D6" s="115" t="s">
         <v>916</v>
       </c>
       <c r="E6" s="121">
-        <f>복귀_토_하체전면!$E$24</f>
-        <v>38</v>
-      </c>
-      <c r="F6" s="113" t="s">
+        <f>복귀_토_하체전면!$E$31</f>
+        <v>41</v>
+      </c>
+      <c r="F6" s="114" t="s">
         <v>917</v>
       </c>
-      <c r="G6" s="114" t="s">
+      <c r="G6" s="115" t="s">
         <v>918</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="114" t="s">
         <v>919</v>
       </c>
       <c r="B7" s="120" t="s">
         <v>920</v>
       </c>
-      <c r="C7" s="113" t="s">
+      <c r="C7" s="114" t="s">
         <v>911</v>
       </c>
-      <c r="D7" s="114" t="s">
+      <c r="D7" s="115" t="s">
         <v>921</v>
       </c>
       <c r="E7" s="121">
         <f>복귀_일_등광배!$E$18</f>
         <v>23</v>
       </c>
-      <c r="F7" s="113" t="s">
+      <c r="F7" s="114" t="s">
         <v>922</v>
       </c>
-      <c r="G7" s="114" t="s">
+      <c r="G7" s="115" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1">
-      <c r="A8" s="113" t="s">
+      <c r="A8" s="114" t="s">
         <v>924</v>
       </c>
       <c r="B8" s="120" t="s">
         <v>925</v>
       </c>
-      <c r="C8" s="113" t="s">
+      <c r="C8" s="114" t="s">
         <v>911</v>
       </c>
-      <c r="D8" s="114" t="s">
+      <c r="D8" s="115" t="s">
         <v>926</v>
       </c>
       <c r="E8" s="121">
         <f>복귀_월_가슴!$E$24</f>
         <v>22</v>
       </c>
-      <c r="F8" s="113" t="s">
+      <c r="F8" s="114" t="s">
         <v>927</v>
       </c>
-      <c r="G8" s="114" t="s">
+      <c r="G8" s="115" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="114" t="s">
         <v>929</v>
       </c>
       <c r="B9" s="120" t="s">
         <v>930</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="114" t="s">
         <v>911</v>
       </c>
-      <c r="D9" s="114" t="s">
+      <c r="D9" s="115" t="s">
         <v>931</v>
       </c>
       <c r="E9" s="121">
         <f>복귀_화_팔!$E$20</f>
         <v>27</v>
       </c>
-      <c r="F9" s="113" t="s">
+      <c r="F9" s="114" t="s">
         <v>932</v>
       </c>
-      <c r="G9" s="114" t="s">
+      <c r="G9" s="115" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1">
-      <c r="A10" s="113" t="s">
+      <c r="A10" s="114" t="s">
         <v>934</v>
       </c>
       <c r="B10" s="120" t="s">
         <v>935</v>
       </c>
-      <c r="C10" s="113" t="s">
+      <c r="C10" s="114" t="s">
         <v>911</v>
       </c>
-      <c r="D10" s="114" t="s">
+      <c r="D10" s="115" t="s">
         <v>936</v>
       </c>
       <c r="E10" s="121">
-        <f>복귀_수_하체후면!$E$35</f>
+        <f>복귀_수_하체후면!$E$41</f>
         <v>39</v>
       </c>
-      <c r="F10" s="113" t="s">
+      <c r="F10" s="114" t="s">
         <v>937</v>
       </c>
-      <c r="G10" s="114" t="s">
+      <c r="G10" s="115" t="s">
         <v>938</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1">
-      <c r="A11" s="113" t="s">
+      <c r="A11" s="114" t="s">
         <v>939</v>
       </c>
       <c r="B11" s="120" t="s">
         <v>940</v>
       </c>
-      <c r="C11" s="113" t="s">
+      <c r="C11" s="114" t="s">
         <v>911</v>
       </c>
-      <c r="D11" s="114" t="s">
+      <c r="D11" s="115" t="s">
         <v>941</v>
       </c>
       <c r="E11" s="121">
         <f>복귀_목_등승모!$E$19</f>
         <v>27</v>
       </c>
-      <c r="F11" s="113" t="s">
+      <c r="F11" s="114" t="s">
         <v>942</v>
       </c>
-      <c r="G11" s="114" t="s">
+      <c r="G11" s="115" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="114" t="s">
         <v>944</v>
       </c>
       <c r="B12" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="113" t="s">
+      <c r="C12" s="114" t="s">
         <v>911</v>
       </c>
-      <c r="D12" s="114" t="s">
+      <c r="D12" s="115" t="s">
         <v>174</v>
       </c>
       <c r="E12" s="121">
         <v>0</v>
       </c>
-      <c r="F12" s="113" t="s">
+      <c r="F12" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="114" t="s">
+      <c r="G12" s="115" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="116" t="s">
         <v>185</v>
       </c>
       <c r="B13" s="122"/>
       <c r="C13" s="122"/>
       <c r="D13" s="122"/>
-      <c r="E13" s="115">
+      <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>176</v>
-      </c>
-      <c r="F13" s="115" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="116" t="s">
         <v>946</v>
       </c>
       <c r="G13" s="119"/>
@@ -11449,7 +11476,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -11467,17 +11494,17 @@
     <col min="14" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:3">
       <c r="A4" s="107" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:3">
       <c r="A5" s="108" t="s">
         <v>269</v>
       </c>
@@ -11488,7 +11515,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:3">
       <c r="A6" s="109">
         <f>MAX(20,(MROUND(시작중량_설정!$E$7*0.4,1)+(MOD(MROUND(시작중량_설정!$E$7*0.4,1),5)=4)))</f>
         <v>25</v>
@@ -11500,7 +11527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:3">
       <c r="A7" s="109">
         <f>IF(MAX(20,(MROUND(시작중량_설정!$E$7*0.6,1)+(MOD(MROUND(시작중량_설정!$E$7*0.6,1),5)=4)))&lt;=MAX(20,(MROUND(시작중량_설정!$E$7*0.4,1)+(MOD(MROUND(시작중량_설정!$E$7*0.4,1),5)=4))),"생략",MAX(20,(MROUND(시작중량_설정!$E$7*0.6,1)+(MOD(MROUND(시작중량_설정!$E$7*0.6,1),5)=4))))</f>
         <v>37</v>
@@ -11512,7 +11539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:3">
       <c r="A8" s="109">
         <f>IF(MAX(20,(MROUND(시작중량_설정!$E$7*0.75,1)+(MOD(MROUND(시작중량_설정!$E$7*0.75,1),5)=4)))&lt;=MAX(20,(MROUND(시작중량_설정!$E$7*0.6,1)+(MOD(MROUND(시작중량_설정!$E$7*0.6,1),5)=4))),"생략",MAX(20,(MROUND(시작중량_설정!$E$7*0.75,1)+(MOD(MROUND(시작중량_설정!$E$7*0.75,1),5)=4))))</f>
         <v>47</v>
@@ -11524,7 +11551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:3">
       <c r="A9" s="109">
         <f>IF(MAX(20,(MROUND(시작중량_설정!$E$7*0.9,1)+(MOD(MROUND(시작중량_설정!$E$7*0.9,1),5)=4)))&lt;=MAX(20,(MROUND(시작중량_설정!$E$7*0.75,1)+(MOD(MROUND(시작중량_설정!$E$7*0.75,1),5)=4))),"생략",MAX(20,(MROUND(시작중량_설정!$E$7*0.9,1)+(MOD(MROUND(시작중량_설정!$E$7*0.9,1),5)=4))))</f>
         <v>56</v>
@@ -11536,7 +11563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:3">
       <c r="A10" s="109">
         <f>시작중량_설정!$E$7</f>
         <v>62</v>
@@ -11548,557 +11575,621 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="110" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="110" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="110" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="110" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="107" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1">
-      <c r="A13" s="110" t="s">
+    <row r="19" spans="1:14" ht="15" customHeight="1">
+      <c r="A19" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="B13" s="110" t="s">
+      <c r="B19" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="110" t="s">
+      <c r="C19" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="D13" s="110" t="s">
+      <c r="D19" s="111" t="s">
         <v>269</v>
       </c>
-      <c r="E13" s="110" t="s">
+      <c r="E19" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="F13" s="110" t="s">
+      <c r="F19" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="G13" s="110" t="s">
+      <c r="G19" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="H13" s="110" t="s">
+      <c r="H19" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="I13" s="110" t="s">
+      <c r="I19" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="J13" s="110" t="s">
+      <c r="J19" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="K13" s="110" t="s">
+      <c r="K19" s="111" t="s">
         <v>276</v>
       </c>
-      <c r="L13" s="110" t="s">
+      <c r="L19" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="M13" s="110" t="s">
+      <c r="M19" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="N13" s="110" t="s">
+      <c r="N19" s="111" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="30" customHeight="1">
-      <c r="A14" s="111">
+    <row r="20" spans="1:14" ht="30" customHeight="1">
+      <c r="A20" s="112">
         <v>1</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B20" s="113" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="111" t="s">
+      <c r="C20" s="112" t="s">
         <v>383</v>
       </c>
-      <c r="D14" s="111">
+      <c r="D20" s="112">
         <f>시작중량_설정!$E$7</f>
         <v>62</v>
       </c>
-      <c r="E14" s="111">
+      <c r="E20" s="112">
         <v>5</v>
       </c>
-      <c r="F14" s="111">
+      <c r="F20" s="112">
         <v>5</v>
       </c>
-      <c r="G14" s="111">
+      <c r="G20" s="112">
         <v>30</v>
       </c>
-      <c r="H14" s="111">
+      <c r="H20" s="112">
         <v>180</v>
       </c>
-      <c r="I14" s="111">
-        <f t="shared" ref="I14:I23" si="0">IF(E14=0,0,ROUND((E14*(G14+H14)+N14)/60,1))</f>
+      <c r="I20" s="112">
+        <f t="shared" ref="I20:I30" si="0">IF(E20=0,0,ROUND((E20*(G20+H20)+N20)/60,1))</f>
         <v>17.5</v>
       </c>
-      <c r="J14" s="112" t="s">
-        <v>985</v>
-      </c>
-      <c r="K14" s="112" t="s">
-        <v>986</v>
-      </c>
-      <c r="L14" s="111" t="s">
+      <c r="J20" s="113" t="s">
+        <v>989</v>
+      </c>
+      <c r="K20" s="113" t="s">
+        <v>990</v>
+      </c>
+      <c r="L20" s="112" t="s">
         <v>356</v>
       </c>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-    </row>
-    <row r="15" spans="1:14" ht="30" customHeight="1">
-      <c r="A15" s="113">
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+    </row>
+    <row r="21" spans="1:14" ht="30" customHeight="1">
+      <c r="A21" s="114">
         <v>2</v>
       </c>
-      <c r="B15" s="114" t="s">
+      <c r="B21" s="115" t="s">
         <v>388</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C21" s="114" t="s">
         <v>383</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D21" s="114">
         <v>125</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E21" s="114">
         <v>4</v>
       </c>
-      <c r="F15" s="113" t="s">
+      <c r="F21" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G21" s="114">
         <v>45</v>
       </c>
-      <c r="H15" s="113">
+      <c r="H21" s="114">
         <v>150</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I21" s="114">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="J15" s="114" t="s">
-        <v>987</v>
-      </c>
-      <c r="K15" s="114" t="s">
-        <v>988</v>
-      </c>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
-    </row>
-    <row r="16" spans="1:14" ht="30" customHeight="1">
-      <c r="A16" s="113">
+      <c r="J21" s="115" t="s">
+        <v>991</v>
+      </c>
+      <c r="K21" s="115" t="s">
+        <v>992</v>
+      </c>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="114"/>
+    </row>
+    <row r="22" spans="1:14" ht="30" customHeight="1">
+      <c r="A22" s="114">
         <v>3</v>
       </c>
-      <c r="B16" s="114" t="s">
+      <c r="B22" s="115" t="s">
         <v>581</v>
       </c>
-      <c r="C16" s="113" t="s">
+      <c r="C22" s="114" t="s">
         <v>383</v>
       </c>
-      <c r="D16" s="113">
+      <c r="D22" s="114">
         <v>40</v>
       </c>
-      <c r="E16" s="113">
+      <c r="E22" s="114">
         <v>3</v>
       </c>
-      <c r="F16" s="113" t="s">
+      <c r="F22" s="114" t="s">
         <v>364</v>
       </c>
-      <c r="G16" s="113">
+      <c r="G22" s="114">
         <v>40</v>
       </c>
-      <c r="H16" s="113">
+      <c r="H22" s="114">
         <v>120</v>
       </c>
-      <c r="I16" s="113">
+      <c r="I22" s="114">
         <f t="shared" si="0"/>
         <v>9.3000000000000007</v>
       </c>
-      <c r="J16" s="114" t="s">
-        <v>989</v>
-      </c>
-      <c r="K16" s="114" t="s">
-        <v>990</v>
-      </c>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113">
+      <c r="J22" s="115" t="s">
+        <v>993</v>
+      </c>
+      <c r="K22" s="115" t="s">
+        <v>994</v>
+      </c>
+      <c r="L22" s="114"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="114">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="30" customHeight="1">
-      <c r="A17" s="113">
+    <row r="23" spans="1:14" ht="30" customHeight="1">
+      <c r="A23" s="114">
         <v>4</v>
       </c>
-      <c r="B17" s="114" t="s">
+      <c r="B23" s="115" t="s">
         <v>522</v>
       </c>
-      <c r="C17" s="113" t="s">
+      <c r="C23" s="114" t="s">
         <v>443</v>
       </c>
-      <c r="D17" s="113">
+      <c r="D23" s="114">
         <v>30</v>
       </c>
-      <c r="E17" s="113">
+      <c r="E23" s="114">
         <v>3</v>
       </c>
-      <c r="F17" s="113" t="s">
+      <c r="F23" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G17" s="113">
+      <c r="G23" s="114">
         <v>40</v>
       </c>
-      <c r="H17" s="113">
+      <c r="H23" s="114">
         <v>120</v>
       </c>
-      <c r="I17" s="113">
+      <c r="I23" s="114">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J17" s="114" t="s">
-        <v>991</v>
-      </c>
-      <c r="K17" s="114" t="s">
+      <c r="J23" s="115" t="s">
+        <v>995</v>
+      </c>
+      <c r="K23" s="115" t="s">
         <v>597</v>
       </c>
-      <c r="L17" s="113"/>
-      <c r="M17" s="113"/>
-      <c r="N17" s="113"/>
-    </row>
-    <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="113">
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="114"/>
+    </row>
+    <row r="24" spans="1:14" ht="30" customHeight="1">
+      <c r="A24" s="114">
         <v>5</v>
       </c>
-      <c r="B18" s="114" t="s">
+      <c r="B24" s="115" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="113" t="s">
+      <c r="C24" s="114" t="s">
         <v>368</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D24" s="114">
         <v>8</v>
       </c>
-      <c r="E18" s="113">
+      <c r="E24" s="114">
         <v>4</v>
       </c>
-      <c r="F18" s="113" t="s">
+      <c r="F24" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G18" s="113">
+      <c r="G24" s="114">
         <v>40</v>
       </c>
-      <c r="H18" s="113">
+      <c r="H24" s="114">
         <v>60</v>
       </c>
-      <c r="I18" s="113">
+      <c r="I24" s="114">
         <f t="shared" si="0"/>
         <v>7.7</v>
       </c>
-      <c r="J18" s="114" t="s">
-        <v>992</v>
-      </c>
-      <c r="K18" s="114" t="s">
-        <v>993</v>
-      </c>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="N18" s="113">
+      <c r="J24" s="115" t="s">
+        <v>996</v>
+      </c>
+      <c r="K24" s="115" t="s">
+        <v>997</v>
+      </c>
+      <c r="L24" s="114"/>
+      <c r="M24" s="114"/>
+      <c r="N24" s="114">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="30" customHeight="1">
-      <c r="A19" s="113">
+    <row r="25" spans="1:14" ht="30" customHeight="1">
+      <c r="A25" s="114">
         <v>6</v>
       </c>
-      <c r="B19" s="114" t="s">
-        <v>994</v>
-      </c>
-      <c r="C19" s="113" t="s">
+      <c r="B25" s="115" t="s">
+        <v>998</v>
+      </c>
+      <c r="C25" s="114" t="s">
         <v>372</v>
       </c>
-      <c r="D19" s="113">
+      <c r="D25" s="114">
         <v>30</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E25" s="114">
         <v>4</v>
       </c>
-      <c r="F19" s="113" t="s">
+      <c r="F25" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G19" s="113">
+      <c r="G25" s="114">
         <v>40</v>
       </c>
-      <c r="H19" s="113">
+      <c r="H25" s="114">
         <v>60</v>
       </c>
-      <c r="I19" s="113">
+      <c r="I25" s="114">
         <f t="shared" si="0"/>
         <v>7.7</v>
       </c>
-      <c r="J19" s="114" t="s">
-        <v>995</v>
-      </c>
-      <c r="K19" s="114" t="s">
-        <v>996</v>
-      </c>
-      <c r="L19" s="113"/>
-      <c r="M19" s="113"/>
-      <c r="N19" s="113">
+      <c r="J25" s="115" t="s">
+        <v>999</v>
+      </c>
+      <c r="K25" s="115" t="s">
+        <v>1000</v>
+      </c>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="30" customHeight="1">
-      <c r="A20" s="113">
+    <row r="26" spans="1:14" ht="30" customHeight="1">
+      <c r="A26" s="114">
         <v>7</v>
       </c>
-      <c r="B20" s="114" t="s">
+      <c r="B26" s="115" t="s">
+        <v>302</v>
+      </c>
+      <c r="C26" s="114" t="s">
+        <v>296</v>
+      </c>
+      <c r="D26" s="114">
+        <v>12.5</v>
+      </c>
+      <c r="E26" s="114">
+        <v>3</v>
+      </c>
+      <c r="F26" s="114" t="s">
+        <v>303</v>
+      </c>
+      <c r="G26" s="114">
+        <v>45</v>
+      </c>
+      <c r="H26" s="114">
+        <v>60</v>
+      </c>
+      <c r="I26" s="114">
+        <f t="shared" si="0"/>
+        <v>5.3</v>
+      </c>
+      <c r="J26" s="115" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K26" s="115" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L26" s="114"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="114"/>
+    </row>
+    <row r="27" spans="1:14" ht="30" customHeight="1">
+      <c r="A27" s="114">
+        <v>8</v>
+      </c>
+      <c r="B27" s="115" t="s">
         <v>397</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C27" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D20" s="113">
+      <c r="D27" s="114">
         <v>40</v>
       </c>
-      <c r="E20" s="113">
+      <c r="E27" s="114">
         <v>4</v>
       </c>
-      <c r="F20" s="113" t="s">
+      <c r="F27" s="114" t="s">
         <v>364</v>
       </c>
-      <c r="G20" s="113">
+      <c r="G27" s="114">
         <v>40</v>
       </c>
-      <c r="H20" s="113">
+      <c r="H27" s="114">
         <v>120</v>
       </c>
-      <c r="I20" s="113">
+      <c r="I27" s="114">
         <f t="shared" si="0"/>
         <v>11.9</v>
       </c>
-      <c r="J20" s="114" t="s">
-        <v>997</v>
-      </c>
-      <c r="K20" s="114" t="s">
-        <v>998</v>
-      </c>
-      <c r="L20" s="113"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="113">
+      <c r="J27" s="115" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K27" s="115" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="114">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="30" customHeight="1">
-      <c r="A21" s="113">
-        <v>8</v>
-      </c>
-      <c r="B21" s="114" t="s">
+    <row r="28" spans="1:14" ht="30" customHeight="1">
+      <c r="A28" s="114">
+        <v>9</v>
+      </c>
+      <c r="B28" s="115" t="s">
         <v>401</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C28" s="114" t="s">
         <v>402</v>
       </c>
-      <c r="D21" s="113">
+      <c r="D28" s="114">
         <v>40</v>
       </c>
-      <c r="E21" s="113">
+      <c r="E28" s="114">
         <v>4</v>
       </c>
-      <c r="F21" s="113" t="s">
+      <c r="F28" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G21" s="113">
+      <c r="G28" s="114">
         <v>40</v>
       </c>
-      <c r="H21" s="113">
+      <c r="H28" s="114">
         <v>10</v>
       </c>
-      <c r="I21" s="113">
+      <c r="I28" s="114">
         <f t="shared" si="0"/>
         <v>3.3</v>
       </c>
-      <c r="J21" s="114" t="s">
-        <v>999</v>
-      </c>
-      <c r="K21" s="114" t="s">
-        <v>1000</v>
-      </c>
-      <c r="L21" s="113"/>
-      <c r="M21" s="113" t="s">
+      <c r="J28" s="115" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K28" s="115" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L28" s="114"/>
+      <c r="M28" s="114" t="s">
         <v>405</v>
       </c>
-      <c r="N21" s="113"/>
-    </row>
-    <row r="22" spans="1:14" ht="30" customHeight="1">
-      <c r="A22" s="113">
-        <v>9</v>
-      </c>
-      <c r="B22" s="114" t="s">
+      <c r="N28" s="114"/>
+    </row>
+    <row r="29" spans="1:14" ht="30" customHeight="1">
+      <c r="A29" s="114">
+        <v>10</v>
+      </c>
+      <c r="B29" s="115" t="s">
         <v>406</v>
       </c>
-      <c r="C22" s="113" t="s">
+      <c r="C29" s="114" t="s">
         <v>407</v>
       </c>
-      <c r="D22" s="113">
+      <c r="D29" s="114">
         <v>40</v>
       </c>
-      <c r="E22" s="113">
+      <c r="E29" s="114">
         <v>4</v>
       </c>
-      <c r="F22" s="113" t="s">
+      <c r="F29" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G22" s="113">
+      <c r="G29" s="114">
         <v>40</v>
       </c>
-      <c r="H22" s="113">
+      <c r="H29" s="114">
         <v>120</v>
       </c>
-      <c r="I22" s="113">
+      <c r="I29" s="114">
         <f t="shared" si="0"/>
         <v>10.7</v>
       </c>
-      <c r="J22" s="114" t="s">
-        <v>1001</v>
-      </c>
-      <c r="K22" s="114" t="s">
-        <v>1002</v>
-      </c>
-      <c r="L22" s="113"/>
-      <c r="M22" s="113" t="s">
+      <c r="J29" s="115" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K29" s="115" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L29" s="114"/>
+      <c r="M29" s="114" t="s">
         <v>405</v>
       </c>
-      <c r="N22" s="113"/>
-    </row>
-    <row r="23" spans="1:14" ht="30" customHeight="1">
-      <c r="A23" s="113">
-        <v>10</v>
-      </c>
-      <c r="B23" s="114" t="s">
+      <c r="N29" s="114"/>
+    </row>
+    <row r="30" spans="1:14" ht="30" customHeight="1">
+      <c r="A30" s="114">
+        <v>11</v>
+      </c>
+      <c r="B30" s="115" t="s">
         <v>502</v>
       </c>
-      <c r="C23" s="113" t="s">
+      <c r="C30" s="114" t="s">
         <v>322</v>
       </c>
-      <c r="D23" s="113">
+      <c r="D30" s="114">
         <v>8</v>
       </c>
-      <c r="E23" s="113">
+      <c r="E30" s="114">
         <v>3</v>
       </c>
-      <c r="F23" s="113" t="s">
+      <c r="F30" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G23" s="113">
+      <c r="G30" s="114">
         <v>40</v>
       </c>
-      <c r="H23" s="113">
+      <c r="H30" s="114">
         <v>75</v>
       </c>
-      <c r="I23" s="113">
+      <c r="I30" s="114">
         <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="J23" s="114" t="s">
-        <v>1003</v>
-      </c>
-      <c r="K23" s="114" t="s">
-        <v>1004</v>
-      </c>
-      <c r="L23" s="113"/>
-      <c r="M23" s="113"/>
-      <c r="N23" s="113"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="115"/>
-      <c r="B24" s="115"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="115" t="s">
+      <c r="J30" s="115" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K30" s="115" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L30" s="114"/>
+      <c r="M30" s="114"/>
+      <c r="N30" s="114"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="116"/>
+      <c r="B31" s="116"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E24" s="115">
-        <f>SUM(E14:E23)</f>
-        <v>38</v>
-      </c>
-      <c r="F24" s="115"/>
-      <c r="G24" s="115"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="115">
-        <f>ROUND(SUM(I14:I23),0)</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="107" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="116" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="116" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="116" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="116" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="116" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="116" t="s">
+      <c r="E31" s="116">
+        <f>SUM(E20:E30)</f>
+        <v>41</v>
+      </c>
+      <c r="F31" s="116"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="116">
+        <f>ROUND(SUM(I20:I30),0)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="107" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="107" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="117" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="117" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="117" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="117" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="117" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="117" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="107" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="116" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="116" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="116" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="107" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="116" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="116" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="116" t="s">
+    <row r="42" spans="1:1">
+      <c r="A42" s="117" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="C44" s="117" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="117" t="s">
         <v>1019</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="117" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="107" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="117" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="117" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="117" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="C51" s="118" t="s">
+        <v>1025</v>
       </c>
     </row>
   </sheetData>
@@ -12129,27 +12220,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="118" t="s">
-        <v>1022</v>
+      <c r="A5" s="110" t="s">
+        <v>1028</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="118" t="s">
-        <v>1023</v>
+      <c r="A6" s="110" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="118" t="s">
-        <v>1024</v>
+      <c r="A7" s="110" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12158,397 +12249,397 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
-      <c r="A10" s="110" t="s">
+      <c r="A10" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="110" t="s">
+      <c r="C10" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="110" t="s">
+      <c r="D10" s="111" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="110" t="s">
+      <c r="E10" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="110" t="s">
+      <c r="F10" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="G10" s="110" t="s">
+      <c r="G10" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="H10" s="110" t="s">
+      <c r="H10" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="I10" s="110" t="s">
+      <c r="I10" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="J10" s="110" t="s">
+      <c r="J10" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="K10" s="110" t="s">
+      <c r="K10" s="111" t="s">
         <v>276</v>
       </c>
-      <c r="L10" s="110" t="s">
+      <c r="L10" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="M10" s="110" t="s">
+      <c r="M10" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="N10" s="110" t="s">
+      <c r="N10" s="111" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1">
-      <c r="A11" s="113">
+      <c r="A11" s="114">
         <v>1</v>
       </c>
-      <c r="B11" s="114" t="s">
+      <c r="B11" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="C11" s="113" t="s">
+      <c r="C11" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D11" s="113">
+      <c r="D11" s="114">
         <v>55</v>
       </c>
-      <c r="E11" s="113">
+      <c r="E11" s="114">
         <v>4</v>
       </c>
-      <c r="F11" s="113" t="s">
+      <c r="F11" s="114" t="s">
         <v>282</v>
       </c>
-      <c r="G11" s="113">
+      <c r="G11" s="114">
         <v>35</v>
       </c>
-      <c r="H11" s="113">
+      <c r="H11" s="114">
         <v>150</v>
       </c>
-      <c r="I11" s="113">
+      <c r="I11" s="114">
         <f t="shared" ref="I11:I17" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.3</v>
       </c>
-      <c r="J11" s="114" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K11" s="114" t="s">
-        <v>1026</v>
-      </c>
-      <c r="L11" s="113" t="s">
-        <v>1027</v>
-      </c>
-      <c r="M11" s="113"/>
-      <c r="N11" s="113"/>
+      <c r="J11" s="115" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K11" s="115" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L11" s="114" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M11" s="114"/>
+      <c r="N11" s="114"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1">
-      <c r="A12" s="113">
+      <c r="A12" s="114">
         <v>2</v>
       </c>
-      <c r="B12" s="114" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C12" s="113" t="s">
+      <c r="B12" s="115" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C12" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D12" s="113" t="s">
+      <c r="D12" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="113">
+      <c r="E12" s="114">
         <v>4</v>
       </c>
-      <c r="F12" s="113" t="s">
+      <c r="F12" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G12" s="113">
+      <c r="G12" s="114">
         <v>40</v>
       </c>
-      <c r="H12" s="113">
+      <c r="H12" s="114">
         <v>120</v>
       </c>
-      <c r="I12" s="113">
+      <c r="I12" s="114">
         <f t="shared" si="0"/>
         <v>10.7</v>
       </c>
-      <c r="J12" s="114" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K12" s="114" t="s">
-        <v>1030</v>
-      </c>
-      <c r="L12" s="113"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="113"/>
+      <c r="J12" s="115" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K12" s="115" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L12" s="114"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="114"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1">
-      <c r="A13" s="113">
+      <c r="A13" s="114">
         <v>3</v>
       </c>
-      <c r="B13" s="114" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C13" s="113" t="s">
+      <c r="B13" s="115" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C13" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D13" s="113" t="s">
+      <c r="D13" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="113">
+      <c r="E13" s="114">
         <v>3</v>
       </c>
-      <c r="F13" s="113" t="s">
+      <c r="F13" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G13" s="113">
+      <c r="G13" s="114">
         <v>40</v>
       </c>
-      <c r="H13" s="113">
+      <c r="H13" s="114">
         <v>120</v>
       </c>
-      <c r="I13" s="113">
+      <c r="I13" s="114">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J13" s="114" t="s">
-        <v>1032</v>
-      </c>
-      <c r="K13" s="114" t="s">
-        <v>1033</v>
-      </c>
-      <c r="L13" s="113"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="113">
+      <c r="J13" s="115" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K13" s="115" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114">
         <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1">
-      <c r="A14" s="113">
+      <c r="A14" s="114">
         <v>4</v>
       </c>
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="115" t="s">
         <v>486</v>
       </c>
-      <c r="C14" s="113" t="s">
+      <c r="C14" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D14" s="113">
+      <c r="D14" s="114">
         <v>25</v>
       </c>
-      <c r="E14" s="113">
+      <c r="E14" s="114">
         <v>3</v>
       </c>
-      <c r="F14" s="113" t="s">
+      <c r="F14" s="114" t="s">
         <v>292</v>
       </c>
-      <c r="G14" s="113">
+      <c r="G14" s="114">
         <v>60</v>
       </c>
-      <c r="H14" s="113">
+      <c r="H14" s="114">
         <v>120</v>
       </c>
-      <c r="I14" s="113">
+      <c r="I14" s="114">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J14" s="114" t="s">
-        <v>1034</v>
-      </c>
-      <c r="K14" s="114" t="s">
-        <v>1035</v>
-      </c>
-      <c r="L14" s="113"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
+      <c r="J14" s="115" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K14" s="115" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="114"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
-      <c r="A15" s="113">
+      <c r="A15" s="114">
         <v>5</v>
       </c>
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="115" t="s">
         <v>431</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="114" t="s">
         <v>432</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="114">
         <v>15</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E15" s="114">
         <v>3</v>
       </c>
-      <c r="F15" s="113" t="s">
+      <c r="F15" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G15" s="114">
         <v>40</v>
       </c>
-      <c r="H15" s="113">
+      <c r="H15" s="114">
         <v>75</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I15" s="114">
         <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="J15" s="114" t="s">
-        <v>1036</v>
-      </c>
-      <c r="K15" s="114" t="s">
-        <v>1037</v>
-      </c>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
+      <c r="J15" s="115" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K15" s="115" t="s">
+        <v>1042</v>
+      </c>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1">
-      <c r="A16" s="113">
+      <c r="A16" s="114">
         <v>6</v>
       </c>
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="115" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="113" t="s">
+      <c r="C16" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D16" s="113">
+      <c r="D16" s="114">
         <v>20</v>
       </c>
-      <c r="E16" s="113">
+      <c r="E16" s="114">
         <v>3</v>
       </c>
-      <c r="F16" s="113" t="s">
+      <c r="F16" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G16" s="113">
+      <c r="G16" s="114">
         <v>40</v>
       </c>
-      <c r="H16" s="113">
+      <c r="H16" s="114">
         <v>75</v>
       </c>
-      <c r="I16" s="113">
+      <c r="I16" s="114">
         <f t="shared" si="0"/>
         <v>6.8</v>
       </c>
-      <c r="J16" s="114" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K16" s="114" t="s">
-        <v>1039</v>
-      </c>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113">
+      <c r="J16" s="115" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K16" s="115" t="s">
+        <v>1044</v>
+      </c>
+      <c r="L16" s="114"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="114">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1">
-      <c r="A17" s="113">
+      <c r="A17" s="114">
         <v>7</v>
       </c>
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="115" t="s">
         <v>495</v>
       </c>
-      <c r="C17" s="113" t="s">
+      <c r="C17" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D17" s="113">
+      <c r="D17" s="114">
         <v>30</v>
       </c>
-      <c r="E17" s="113">
+      <c r="E17" s="114">
         <v>3</v>
       </c>
-      <c r="F17" s="113" t="s">
+      <c r="F17" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G17" s="113">
+      <c r="G17" s="114">
         <v>40</v>
       </c>
-      <c r="H17" s="113">
+      <c r="H17" s="114">
         <v>75</v>
       </c>
-      <c r="I17" s="113">
+      <c r="I17" s="114">
         <f t="shared" si="0"/>
         <v>6.8</v>
       </c>
-      <c r="J17" s="114" t="s">
-        <v>1040</v>
-      </c>
-      <c r="K17" s="114" t="s">
-        <v>1041</v>
-      </c>
-      <c r="L17" s="113"/>
-      <c r="M17" s="113"/>
-      <c r="N17" s="113">
+      <c r="J17" s="115" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K17" s="115" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="114">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115" t="s">
+      <c r="A18" s="116"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E18" s="115">
+      <c r="E18" s="116">
         <f>SUM(E11:E17)</f>
         <v>23</v>
       </c>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115">
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116">
         <f>ROUND(SUM(I11:I17),0)</f>
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="116" t="s">
-        <v>1043</v>
+      <c r="A21" s="117" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="116" t="s">
-        <v>1044</v>
+      <c r="A22" s="117" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="116" t="s">
-        <v>1045</v>
+      <c r="A23" s="117" t="s">
+        <v>1050</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="116" t="s">
-        <v>1046</v>
+      <c r="A24" s="117" t="s">
+        <v>1051</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="116" t="s">
-        <v>1006</v>
+      <c r="A27" s="117" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="116" t="s">
-        <v>1048</v>
+      <c r="A28" s="117" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="116" t="s">
-        <v>1049</v>
+      <c r="A29" s="117" t="s">
+        <v>1054</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="116" t="s">
-        <v>1050</v>
+      <c r="A30" s="117" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -12557,38 +12648,38 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="116" t="s">
-        <v>1051</v>
+      <c r="A33" s="117" t="s">
+        <v>1056</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="116" t="s">
-        <v>1052</v>
+      <c r="A34" s="117" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="116" t="s">
-        <v>1053</v>
+      <c r="A37" s="117" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="116" t="s">
-        <v>1054</v>
+      <c r="A38" s="117" t="s">
+        <v>1059</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="116" t="s">
-        <v>1018</v>
+      <c r="A39" s="117" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="C41" s="117" t="s">
-        <v>1055</v>
+      <c r="C41" s="118" t="s">
+        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -12619,7 +12710,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12704,12 +12795,12 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="118" t="s">
-        <v>1023</v>
+      <c r="A13" s="110" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="110" t="s">
         <v>349</v>
       </c>
     </row>
@@ -12719,345 +12810,345 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1">
-      <c r="A17" s="110" t="s">
+      <c r="A17" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="110" t="s">
+      <c r="C17" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="D17" s="110" t="s">
+      <c r="D17" s="111" t="s">
         <v>269</v>
       </c>
-      <c r="E17" s="110" t="s">
+      <c r="E17" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="F17" s="110" t="s">
+      <c r="F17" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="G17" s="110" t="s">
+      <c r="G17" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="H17" s="110" t="s">
+      <c r="H17" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="I17" s="110" t="s">
+      <c r="I17" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="J17" s="110" t="s">
+      <c r="J17" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="K17" s="110" t="s">
+      <c r="K17" s="111" t="s">
         <v>276</v>
       </c>
-      <c r="L17" s="110" t="s">
+      <c r="L17" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="M17" s="110" t="s">
+      <c r="M17" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="N17" s="110" t="s">
+      <c r="N17" s="111" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="111">
+      <c r="A18" s="112">
         <v>1</v>
       </c>
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="111" t="s">
+      <c r="C18" s="112" t="s">
         <v>351</v>
       </c>
-      <c r="D18" s="111">
+      <c r="D18" s="112">
         <f>시작중량_설정!$E$9</f>
         <v>35</v>
       </c>
-      <c r="E18" s="111">
+      <c r="E18" s="112">
         <v>5</v>
       </c>
-      <c r="F18" s="111">
+      <c r="F18" s="112">
         <v>5</v>
       </c>
-      <c r="G18" s="111">
+      <c r="G18" s="112">
         <v>30</v>
       </c>
-      <c r="H18" s="111">
+      <c r="H18" s="112">
         <v>180</v>
       </c>
-      <c r="I18" s="111">
+      <c r="I18" s="112">
         <f t="shared" ref="I18:I23" si="0">IF(E18=0,0,ROUND((E18*(G18+H18)+N18)/60,1))</f>
         <v>17.5</v>
       </c>
-      <c r="J18" s="112" t="s">
-        <v>1057</v>
-      </c>
-      <c r="K18" s="112" t="s">
-        <v>1058</v>
-      </c>
-      <c r="L18" s="111" t="s">
+      <c r="J18" s="113" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K18" s="113" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L18" s="112" t="s">
         <v>356</v>
       </c>
-      <c r="M18" s="111"/>
-      <c r="N18" s="111"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
     </row>
     <row r="19" spans="1:14" ht="30" customHeight="1">
-      <c r="A19" s="113">
+      <c r="A19" s="114">
         <v>2</v>
       </c>
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="115" t="s">
         <v>531</v>
       </c>
-      <c r="C19" s="113" t="s">
+      <c r="C19" s="114" t="s">
         <v>363</v>
       </c>
-      <c r="D19" s="113">
+      <c r="D19" s="114">
         <v>35</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E19" s="114">
         <v>4</v>
       </c>
-      <c r="F19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="G19" s="113">
+      <c r="G19" s="114">
         <v>40</v>
       </c>
-      <c r="H19" s="113">
+      <c r="H19" s="114">
         <v>150</v>
       </c>
-      <c r="I19" s="113">
+      <c r="I19" s="114">
         <f t="shared" si="0"/>
         <v>12.7</v>
       </c>
-      <c r="J19" s="114" t="s">
-        <v>1059</v>
-      </c>
-      <c r="K19" s="114" t="s">
-        <v>1060</v>
-      </c>
-      <c r="L19" s="113"/>
-      <c r="M19" s="113"/>
-      <c r="N19" s="113"/>
+      <c r="J19" s="115" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K19" s="115" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
     </row>
     <row r="20" spans="1:14" ht="30" customHeight="1">
-      <c r="A20" s="113">
+      <c r="A20" s="114">
         <v>3</v>
       </c>
-      <c r="B20" s="114" t="s">
+      <c r="B20" s="115" t="s">
         <v>600</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="114" t="s">
         <v>363</v>
       </c>
-      <c r="D20" s="113" t="s">
+      <c r="D20" s="114" t="s">
         <v>358</v>
       </c>
-      <c r="E20" s="113">
+      <c r="E20" s="114">
         <v>4</v>
       </c>
-      <c r="F20" s="113" t="s">
+      <c r="F20" s="114" t="s">
         <v>364</v>
       </c>
-      <c r="G20" s="113">
+      <c r="G20" s="114">
         <v>40</v>
       </c>
-      <c r="H20" s="113">
+      <c r="H20" s="114">
         <v>105</v>
       </c>
-      <c r="I20" s="113">
+      <c r="I20" s="114">
         <f t="shared" si="0"/>
         <v>9.6999999999999993</v>
       </c>
-      <c r="J20" s="114" t="s">
-        <v>1061</v>
-      </c>
-      <c r="K20" s="114" t="s">
-        <v>1062</v>
-      </c>
-      <c r="L20" s="113"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="113"/>
+      <c r="J20" s="115" t="s">
+        <v>1066</v>
+      </c>
+      <c r="K20" s="115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="114"/>
     </row>
     <row r="21" spans="1:14" ht="30" customHeight="1">
-      <c r="A21" s="113">
+      <c r="A21" s="114">
         <v>4</v>
       </c>
-      <c r="B21" s="114" t="s">
+      <c r="B21" s="115" t="s">
         <v>357</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C21" s="114" t="s">
         <v>351</v>
       </c>
-      <c r="D21" s="113" t="s">
+      <c r="D21" s="114" t="s">
         <v>297</v>
       </c>
-      <c r="E21" s="113">
+      <c r="E21" s="114">
         <v>3</v>
       </c>
-      <c r="F21" s="113" t="s">
+      <c r="F21" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G21" s="113">
+      <c r="G21" s="114">
         <v>40</v>
       </c>
-      <c r="H21" s="113">
+      <c r="H21" s="114">
         <v>120</v>
       </c>
-      <c r="I21" s="113">
+      <c r="I21" s="114">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J21" s="114" t="s">
-        <v>1063</v>
-      </c>
-      <c r="K21" s="114" t="s">
-        <v>1064</v>
-      </c>
-      <c r="L21" s="113" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M21" s="113"/>
-      <c r="N21" s="113"/>
+      <c r="J21" s="115" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K21" s="115" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L21" s="114" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M21" s="114"/>
+      <c r="N21" s="114"/>
     </row>
     <row r="22" spans="1:14" ht="30" customHeight="1">
-      <c r="A22" s="113">
+      <c r="A22" s="114">
         <v>5</v>
       </c>
-      <c r="B22" s="114" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C22" s="113" t="s">
+      <c r="B22" s="115" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C22" s="114" t="s">
         <v>368</v>
       </c>
-      <c r="D22" s="113" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E22" s="113">
+      <c r="D22" s="114" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E22" s="114">
         <v>3</v>
       </c>
-      <c r="F22" s="113" t="s">
+      <c r="F22" s="114" t="s">
         <v>318</v>
       </c>
-      <c r="G22" s="113">
+      <c r="G22" s="114">
         <v>60</v>
       </c>
-      <c r="H22" s="113">
+      <c r="H22" s="114">
         <v>60</v>
       </c>
-      <c r="I22" s="113">
+      <c r="I22" s="114">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="J22" s="114" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K22" s="114" t="s">
-        <v>1069</v>
-      </c>
-      <c r="L22" s="113"/>
-      <c r="M22" s="113"/>
-      <c r="N22" s="113"/>
+      <c r="J22" s="115" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K22" s="115" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L22" s="114"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="114"/>
     </row>
     <row r="23" spans="1:14" ht="30" customHeight="1">
-      <c r="A23" s="113">
+      <c r="A23" s="114">
         <v>6</v>
       </c>
-      <c r="B23" s="114" t="s">
+      <c r="B23" s="115" t="s">
         <v>424</v>
       </c>
-      <c r="C23" s="113" t="s">
+      <c r="C23" s="114" t="s">
         <v>372</v>
       </c>
-      <c r="D23" s="113" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E23" s="113">
+      <c r="D23" s="114" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E23" s="114">
         <v>3</v>
       </c>
-      <c r="F23" s="113" t="s">
+      <c r="F23" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G23" s="113">
+      <c r="G23" s="114">
         <v>40</v>
       </c>
-      <c r="H23" s="113">
+      <c r="H23" s="114">
         <v>60</v>
       </c>
-      <c r="I23" s="113">
+      <c r="I23" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J23" s="114" t="s">
-        <v>1070</v>
-      </c>
-      <c r="K23" s="114" t="s">
-        <v>1071</v>
-      </c>
-      <c r="L23" s="113"/>
-      <c r="M23" s="113"/>
-      <c r="N23" s="113"/>
+      <c r="J23" s="115" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K23" s="115" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="114"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="115"/>
-      <c r="B24" s="115"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="115" t="s">
+      <c r="A24" s="116"/>
+      <c r="B24" s="116"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E24" s="115">
+      <c r="E24" s="116">
         <f>SUM(E18:E23)</f>
         <v>22</v>
       </c>
-      <c r="F24" s="115"/>
-      <c r="G24" s="115"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="115">
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116">
         <f>ROUND(SUM(I18:I23),0)</f>
         <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="116" t="s">
-        <v>1006</v>
+      <c r="A27" s="117" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="116" t="s">
-        <v>1073</v>
+      <c r="A28" s="117" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="116" t="s">
-        <v>1074</v>
+      <c r="A29" s="117" t="s">
+        <v>1079</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="116" t="s">
-        <v>1075</v>
+      <c r="A30" s="117" t="s">
+        <v>1080</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="116" t="s">
-        <v>1077</v>
+      <c r="A33" s="117" t="s">
+        <v>1082</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="116" t="s">
-        <v>1078</v>
+      <c r="A34" s="117" t="s">
+        <v>1083</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -13066,33 +13157,33 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="116" t="s">
-        <v>1079</v>
+      <c r="A37" s="117" t="s">
+        <v>1084</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="116" t="s">
-        <v>1080</v>
+      <c r="A38" s="117" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="116" t="s">
-        <v>1082</v>
+      <c r="A41" s="117" t="s">
+        <v>1087</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="116" t="s">
-        <v>1083</v>
+      <c r="A42" s="117" t="s">
+        <v>1088</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="C44" s="117" t="s">
-        <v>1084</v>
+      <c r="C44" s="118" t="s">
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
@@ -13123,26 +13214,26 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="118" t="s">
-        <v>1086</v>
+      <c r="A5" s="110" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="118" t="s">
-        <v>1087</v>
+      <c r="A6" s="110" t="s">
+        <v>1092</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="110" t="s">
         <v>349</v>
       </c>
     </row>
@@ -13152,459 +13243,459 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
-      <c r="A10" s="110" t="s">
+      <c r="A10" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="110" t="s">
+      <c r="C10" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="110" t="s">
+      <c r="D10" s="111" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="110" t="s">
+      <c r="E10" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="110" t="s">
+      <c r="F10" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="G10" s="110" t="s">
+      <c r="G10" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="H10" s="110" t="s">
+      <c r="H10" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="I10" s="110" t="s">
+      <c r="I10" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="J10" s="110" t="s">
+      <c r="J10" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="K10" s="110" t="s">
+      <c r="K10" s="111" t="s">
         <v>276</v>
       </c>
-      <c r="L10" s="110" t="s">
+      <c r="L10" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="M10" s="110" t="s">
+      <c r="M10" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="N10" s="110" t="s">
+      <c r="N10" s="111" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1">
-      <c r="A11" s="113">
+      <c r="A11" s="114">
         <v>1</v>
       </c>
-      <c r="B11" s="114" t="s">
+      <c r="B11" s="115" t="s">
         <v>602</v>
       </c>
-      <c r="C11" s="113" t="s">
+      <c r="C11" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D11" s="113">
+      <c r="D11" s="114">
         <v>15</v>
       </c>
-      <c r="E11" s="113">
+      <c r="E11" s="114">
         <v>3</v>
       </c>
-      <c r="F11" s="113" t="s">
+      <c r="F11" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G11" s="113">
+      <c r="G11" s="114">
         <v>40</v>
       </c>
-      <c r="H11" s="113">
+      <c r="H11" s="114">
         <v>75</v>
       </c>
-      <c r="I11" s="113">
+      <c r="I11" s="114">
         <f t="shared" ref="I11:I19" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>6.8</v>
       </c>
-      <c r="J11" s="114" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K11" s="114" t="s">
-        <v>1089</v>
-      </c>
-      <c r="L11" s="113"/>
-      <c r="M11" s="113"/>
-      <c r="N11" s="113">
+      <c r="J11" s="115" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K11" s="115" t="s">
+        <v>1094</v>
+      </c>
+      <c r="L11" s="114"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="114">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1">
-      <c r="A12" s="113">
+      <c r="A12" s="114">
         <v>2</v>
       </c>
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="115" t="s">
         <v>605</v>
       </c>
-      <c r="C12" s="113" t="s">
+      <c r="C12" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D12" s="113">
+      <c r="D12" s="114">
         <v>6</v>
       </c>
-      <c r="E12" s="113">
+      <c r="E12" s="114">
         <v>3</v>
       </c>
-      <c r="F12" s="113" t="s">
+      <c r="F12" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G12" s="113">
+      <c r="G12" s="114">
         <v>40</v>
       </c>
-      <c r="H12" s="113">
+      <c r="H12" s="114">
         <v>75</v>
       </c>
-      <c r="I12" s="113">
+      <c r="I12" s="114">
         <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="J12" s="114" t="s">
-        <v>1090</v>
-      </c>
-      <c r="K12" s="114" t="s">
-        <v>1091</v>
-      </c>
-      <c r="L12" s="113"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="113"/>
+      <c r="J12" s="115" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K12" s="115" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L12" s="114"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="114"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1">
-      <c r="A13" s="113">
+      <c r="A13" s="114">
         <v>3</v>
       </c>
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="115" t="s">
         <v>453</v>
       </c>
-      <c r="C13" s="113" t="s">
+      <c r="C13" s="114" t="s">
         <v>309</v>
       </c>
-      <c r="D13" s="113">
+      <c r="D13" s="114">
         <v>15</v>
       </c>
-      <c r="E13" s="113">
+      <c r="E13" s="114">
         <v>3</v>
       </c>
-      <c r="F13" s="113" t="s">
+      <c r="F13" s="114" t="s">
         <v>317</v>
       </c>
-      <c r="G13" s="113">
+      <c r="G13" s="114">
         <v>40</v>
       </c>
-      <c r="H13" s="113">
+      <c r="H13" s="114">
         <v>70</v>
       </c>
-      <c r="I13" s="113">
+      <c r="I13" s="114">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J13" s="114" t="s">
-        <v>1092</v>
-      </c>
-      <c r="K13" s="114" t="s">
-        <v>1093</v>
-      </c>
-      <c r="L13" s="113"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="113"/>
+      <c r="J13" s="115" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K13" s="115" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1">
-      <c r="A14" s="113">
+      <c r="A14" s="114">
         <v>4</v>
       </c>
-      <c r="B14" s="114" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C14" s="113" t="s">
+      <c r="B14" s="115" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C14" s="114" t="s">
         <v>309</v>
       </c>
-      <c r="D14" s="113">
+      <c r="D14" s="114">
         <v>10</v>
       </c>
-      <c r="E14" s="113">
+      <c r="E14" s="114">
         <v>3</v>
       </c>
-      <c r="F14" s="113">
+      <c r="F14" s="114">
         <v>15</v>
       </c>
-      <c r="G14" s="113">
+      <c r="G14" s="114">
         <v>40</v>
       </c>
-      <c r="H14" s="113">
+      <c r="H14" s="114">
         <v>60</v>
       </c>
-      <c r="I14" s="113">
+      <c r="I14" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J14" s="114" t="s">
-        <v>1095</v>
-      </c>
-      <c r="K14" s="114" t="s">
-        <v>1096</v>
-      </c>
-      <c r="L14" s="113"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
+      <c r="J14" s="115" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K14" s="115" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="114"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
-      <c r="A15" s="113">
+      <c r="A15" s="114">
         <v>5</v>
       </c>
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="115" t="s">
         <v>608</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="114" t="s">
         <v>309</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="114">
         <v>10</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E15" s="114">
         <v>3</v>
       </c>
-      <c r="F15" s="113">
+      <c r="F15" s="114">
         <v>15</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G15" s="114">
         <v>40</v>
       </c>
-      <c r="H15" s="113">
+      <c r="H15" s="114">
         <v>60</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I15" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J15" s="114" t="s">
-        <v>1097</v>
-      </c>
-      <c r="K15" s="114" t="s">
-        <v>1098</v>
-      </c>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
+      <c r="J15" s="115" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K15" s="115" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1">
-      <c r="A16" s="113">
+      <c r="A16" s="114">
         <v>6</v>
       </c>
-      <c r="B16" s="114" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C16" s="113" t="s">
+      <c r="B16" s="115" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C16" s="114" t="s">
         <v>939</v>
       </c>
-      <c r="D16" s="113">
+      <c r="D16" s="114">
         <v>2.5</v>
       </c>
-      <c r="E16" s="113">
+      <c r="E16" s="114">
         <v>3</v>
       </c>
-      <c r="F16" s="113" t="s">
+      <c r="F16" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G16" s="113">
+      <c r="G16" s="114">
         <v>40</v>
       </c>
-      <c r="H16" s="113">
+      <c r="H16" s="114">
         <v>60</v>
       </c>
-      <c r="I16" s="113">
+      <c r="I16" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J16" s="114" t="s">
-        <v>1100</v>
-      </c>
-      <c r="K16" s="114" t="s">
-        <v>1101</v>
-      </c>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
+      <c r="J16" s="115" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K16" s="115" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L16" s="114"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="114"/>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1">
-      <c r="A17" s="113">
+      <c r="A17" s="114">
         <v>7</v>
       </c>
-      <c r="B17" s="114" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C17" s="113" t="s">
+      <c r="B17" s="115" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C17" s="114" t="s">
         <v>939</v>
       </c>
-      <c r="D17" s="113">
+      <c r="D17" s="114">
         <v>2.5</v>
       </c>
-      <c r="E17" s="113">
+      <c r="E17" s="114">
         <v>3</v>
       </c>
-      <c r="F17" s="113" t="s">
+      <c r="F17" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G17" s="113">
+      <c r="G17" s="114">
         <v>40</v>
       </c>
-      <c r="H17" s="113">
+      <c r="H17" s="114">
         <v>60</v>
       </c>
-      <c r="I17" s="113">
+      <c r="I17" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J17" s="114" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K17" s="114" t="s">
-        <v>1104</v>
-      </c>
-      <c r="L17" s="113"/>
-      <c r="M17" s="113"/>
-      <c r="N17" s="113"/>
+      <c r="J17" s="115" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K17" s="115" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="114"/>
     </row>
     <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="113">
+      <c r="A18" s="114">
         <v>8</v>
       </c>
-      <c r="B18" s="114" t="s">
+      <c r="B18" s="115" t="s">
         <v>547</v>
       </c>
-      <c r="C18" s="113" t="s">
+      <c r="C18" s="114" t="s">
         <v>313</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="114">
         <v>2.5</v>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="114">
         <v>3</v>
       </c>
-      <c r="F18" s="113">
+      <c r="F18" s="114">
         <v>12</v>
       </c>
-      <c r="G18" s="113">
+      <c r="G18" s="114">
         <v>40</v>
       </c>
-      <c r="H18" s="113">
+      <c r="H18" s="114">
         <v>60</v>
       </c>
-      <c r="I18" s="113">
+      <c r="I18" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J18" s="114" t="s">
-        <v>1105</v>
-      </c>
-      <c r="K18" s="114" t="s">
-        <v>1106</v>
-      </c>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="N18" s="113"/>
+      <c r="J18" s="115" t="s">
+        <v>1110</v>
+      </c>
+      <c r="K18" s="115" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114"/>
     </row>
     <row r="19" spans="1:14" ht="30" customHeight="1">
-      <c r="A19" s="113">
+      <c r="A19" s="114">
         <v>9</v>
       </c>
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="115" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="113" t="s">
+      <c r="C19" s="114" t="s">
         <v>313</v>
       </c>
-      <c r="D19" s="113" t="s">
+      <c r="D19" s="114" t="s">
         <v>297</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E19" s="114">
         <v>3</v>
       </c>
-      <c r="F19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G19" s="113">
+      <c r="G19" s="114">
         <v>40</v>
       </c>
-      <c r="H19" s="113">
+      <c r="H19" s="114">
         <v>60</v>
       </c>
-      <c r="I19" s="113">
+      <c r="I19" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J19" s="114" t="s">
-        <v>1107</v>
-      </c>
-      <c r="K19" s="114" t="s">
-        <v>1108</v>
-      </c>
-      <c r="L19" s="113"/>
-      <c r="M19" s="113"/>
-      <c r="N19" s="113"/>
+      <c r="J19" s="115" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K19" s="115" t="s">
+        <v>1113</v>
+      </c>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="115"/>
-      <c r="B20" s="115"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115" t="s">
+      <c r="A20" s="116"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E20" s="115">
+      <c r="E20" s="116">
         <f>SUM(E11:E19)</f>
         <v>27</v>
       </c>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115">
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116">
         <f>ROUND(SUM(I11:I19),0)</f>
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="116" t="s">
-        <v>1110</v>
+      <c r="A23" s="117" t="s">
+        <v>1115</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="116" t="s">
-        <v>1111</v>
+      <c r="A24" s="117" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="116" t="s">
-        <v>1112</v>
+      <c r="A25" s="117" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="116" t="s">
-        <v>1114</v>
+      <c r="A28" s="117" t="s">
+        <v>1119</v>
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="116" t="s">
-        <v>1115</v>
+      <c r="A29" s="117" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="116" t="s">
-        <v>1116</v>
+      <c r="A30" s="117" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -13613,43 +13704,43 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="116" t="s">
-        <v>1117</v>
+      <c r="A33" s="117" t="s">
+        <v>1122</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="116" t="s">
-        <v>1118</v>
+      <c r="A34" s="117" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="116" t="s">
-        <v>1119</v>
+      <c r="A37" s="117" t="s">
+        <v>1124</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="116" t="s">
-        <v>1120</v>
+      <c r="A38" s="117" t="s">
+        <v>1125</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="116" t="s">
-        <v>1121</v>
+      <c r="A39" s="117" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="116" t="s">
-        <v>1018</v>
+      <c r="A40" s="117" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="C42" s="117" t="s">
-        <v>1122</v>
+      <c r="C42" s="118" t="s">
+        <v>1127</v>
       </c>
     </row>
   </sheetData>
@@ -14341,7 +14432,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -14361,7 +14452,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14442,7 +14533,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14518,753 +14609,778 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="110" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="110" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="110" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="110" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="107" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1">
-      <c r="A21" s="110" t="s">
+    <row r="27" spans="1:14" ht="15" customHeight="1">
+      <c r="A27" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="B21" s="110" t="s">
+      <c r="B27" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="110" t="s">
+      <c r="C27" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="D21" s="110" t="s">
+      <c r="D27" s="111" t="s">
         <v>269</v>
       </c>
-      <c r="E21" s="110" t="s">
+      <c r="E27" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="110" t="s">
+      <c r="F27" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="G21" s="110" t="s">
+      <c r="G27" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="H21" s="110" t="s">
+      <c r="H27" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="I21" s="110" t="s">
+      <c r="I27" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="J21" s="110" t="s">
+      <c r="J27" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="K21" s="110" t="s">
+      <c r="K27" s="111" t="s">
         <v>276</v>
       </c>
-      <c r="L21" s="110" t="s">
+      <c r="L27" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="M21" s="110" t="s">
+      <c r="M27" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="N21" s="110" t="s">
+      <c r="N27" s="111" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="30" customHeight="1">
-      <c r="A22" s="111">
+    <row r="28" spans="1:14" ht="30" customHeight="1">
+      <c r="A28" s="112">
         <v>1</v>
       </c>
-      <c r="B22" s="112" t="s">
+      <c r="B28" s="113" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="111" t="s">
+      <c r="C28" s="112" t="s">
         <v>327</v>
       </c>
-      <c r="D22" s="111">
+      <c r="D28" s="112">
         <f>시작중량_설정!$E$8</f>
         <v>67</v>
       </c>
-      <c r="E22" s="111">
+      <c r="E28" s="112">
         <v>1</v>
       </c>
-      <c r="F22" s="111">
+      <c r="F28" s="112">
         <v>5</v>
       </c>
-      <c r="G22" s="111">
+      <c r="G28" s="112">
         <v>30</v>
       </c>
-      <c r="H22" s="111">
+      <c r="H28" s="112">
         <v>180</v>
       </c>
-      <c r="I22" s="111">
-        <f t="shared" ref="I22:I34" si="0">IF(E22=0,0,ROUND((E22*(G22+H22)+N22)/60,1))</f>
+      <c r="I28" s="112">
+        <f t="shared" ref="I28:I40" si="0">IF(E28=0,0,ROUND((E28*(G28+H28)+N28)/60,1))</f>
         <v>3.5</v>
       </c>
-      <c r="J22" s="112" t="s">
-        <v>1125</v>
-      </c>
-      <c r="K22" s="112" t="s">
-        <v>1126</v>
-      </c>
-      <c r="L22" s="111"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="111"/>
-    </row>
-    <row r="23" spans="1:14" ht="30" customHeight="1">
-      <c r="A23" s="113">
+      <c r="J28" s="113" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K28" s="113" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+    </row>
+    <row r="29" spans="1:14" ht="30" customHeight="1">
+      <c r="A29" s="114">
         <v>2</v>
       </c>
-      <c r="B23" s="114" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C23" s="113" t="s">
+      <c r="B29" s="115" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C29" s="114" t="s">
         <v>327</v>
       </c>
-      <c r="D23" s="113">
+      <c r="D29" s="114">
         <f>시작중량_설정!$E$8-5</f>
         <v>62</v>
       </c>
-      <c r="E23" s="113">
+      <c r="E29" s="114">
         <v>2</v>
       </c>
-      <c r="F23" s="113">
+      <c r="F29" s="114">
         <v>5</v>
       </c>
-      <c r="G23" s="113">
+      <c r="G29" s="114">
         <v>30</v>
       </c>
-      <c r="H23" s="113">
+      <c r="H29" s="114">
         <v>180</v>
       </c>
-      <c r="I23" s="113">
+      <c r="I29" s="114">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="J23" s="114" t="s">
-        <v>1128</v>
-      </c>
-      <c r="K23" s="114" t="s">
-        <v>1129</v>
-      </c>
-      <c r="L23" s="113"/>
-      <c r="M23" s="113"/>
-      <c r="N23" s="113"/>
-    </row>
-    <row r="24" spans="1:14" ht="30" customHeight="1">
-      <c r="A24" s="113">
+      <c r="J29" s="115" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K29" s="115" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L29" s="114"/>
+      <c r="M29" s="114"/>
+      <c r="N29" s="114"/>
+    </row>
+    <row r="30" spans="1:14" ht="30" customHeight="1">
+      <c r="A30" s="114">
         <v>3</v>
       </c>
-      <c r="B24" s="114" t="s">
+      <c r="B30" s="115" t="s">
         <v>573</v>
       </c>
-      <c r="C24" s="113" t="s">
+      <c r="C30" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D24" s="113" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E24" s="113">
+      <c r="D30" s="114" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E30" s="114">
         <v>3</v>
       </c>
-      <c r="F24" s="113" t="s">
+      <c r="F30" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G24" s="113">
+      <c r="G30" s="114">
         <v>45</v>
       </c>
-      <c r="H24" s="113">
+      <c r="H30" s="114">
         <v>150</v>
       </c>
-      <c r="I24" s="113">
+      <c r="I30" s="114">
         <f t="shared" si="0"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="J24" s="114" t="s">
-        <v>1131</v>
-      </c>
-      <c r="K24" s="114" t="s">
-        <v>1132</v>
-      </c>
-      <c r="L24" s="113"/>
-      <c r="M24" s="113"/>
-      <c r="N24" s="113"/>
-    </row>
-    <row r="25" spans="1:14" ht="30" customHeight="1">
-      <c r="A25" s="113">
+      <c r="J30" s="115" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K30" s="115" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L30" s="114"/>
+      <c r="M30" s="114"/>
+      <c r="N30" s="114"/>
+    </row>
+    <row r="31" spans="1:14" ht="30" customHeight="1">
+      <c r="A31" s="114">
         <v>4</v>
       </c>
-      <c r="B25" s="114" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C25" s="113" t="s">
+      <c r="B31" s="115" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C31" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="D25" s="113">
+      <c r="D31" s="114">
         <v>110</v>
       </c>
-      <c r="E25" s="113">
+      <c r="E31" s="114">
         <v>4</v>
       </c>
-      <c r="F25" s="113" t="s">
+      <c r="F31" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G25" s="113">
+      <c r="G31" s="114">
         <v>45</v>
       </c>
-      <c r="H25" s="113">
+      <c r="H31" s="114">
         <v>150</v>
       </c>
-      <c r="I25" s="113">
+      <c r="I31" s="114">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="J25" s="114" t="s">
-        <v>1134</v>
-      </c>
-      <c r="K25" s="114" t="s">
-        <v>1135</v>
-      </c>
-      <c r="L25" s="113"/>
-      <c r="M25" s="113"/>
-      <c r="N25" s="113"/>
-    </row>
-    <row r="26" spans="1:14" ht="30" customHeight="1">
-      <c r="A26" s="113">
+      <c r="J31" s="115" t="s">
+        <v>1142</v>
+      </c>
+      <c r="K31" s="115" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L31" s="114"/>
+      <c r="M31" s="114"/>
+      <c r="N31" s="114"/>
+    </row>
+    <row r="32" spans="1:14" ht="30" customHeight="1">
+      <c r="A32" s="114">
         <v>5</v>
       </c>
-      <c r="B26" s="114" t="s">
+      <c r="B32" s="115" t="s">
         <v>576</v>
       </c>
-      <c r="C26" s="113" t="s">
+      <c r="C32" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D26" s="113">
+      <c r="D32" s="114">
         <v>25</v>
       </c>
-      <c r="E26" s="113">
+      <c r="E32" s="114">
         <v>3</v>
       </c>
-      <c r="F26" s="113">
+      <c r="F32" s="114">
         <v>10</v>
       </c>
-      <c r="G26" s="113">
+      <c r="G32" s="114">
         <v>60</v>
       </c>
-      <c r="H26" s="113">
+      <c r="H32" s="114">
         <v>120</v>
       </c>
-      <c r="I26" s="113">
+      <c r="I32" s="114">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J26" s="114" t="s">
-        <v>1136</v>
-      </c>
-      <c r="K26" s="114" t="s">
-        <v>1137</v>
-      </c>
-      <c r="L26" s="113"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="113"/>
-    </row>
-    <row r="27" spans="1:14" ht="30" customHeight="1">
-      <c r="A27" s="111">
+      <c r="J32" s="115" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K32" s="115" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L32" s="114"/>
+      <c r="M32" s="114"/>
+      <c r="N32" s="114"/>
+    </row>
+    <row r="33" spans="1:14" ht="30" customHeight="1">
+      <c r="A33" s="112">
         <v>6</v>
       </c>
-      <c r="B27" s="112" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C27" s="111" t="s">
+      <c r="B33" s="113" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C33" s="112" t="s">
         <v>443</v>
       </c>
-      <c r="D27" s="111">
+      <c r="D33" s="112">
         <f>시작중량_설정!$E$10</f>
         <v>26</v>
       </c>
-      <c r="E27" s="111">
+      <c r="E33" s="112">
         <v>3</v>
       </c>
-      <c r="F27" s="111">
+      <c r="F33" s="112">
         <v>5</v>
       </c>
-      <c r="G27" s="111">
+      <c r="G33" s="112">
         <v>30</v>
       </c>
-      <c r="H27" s="111">
+      <c r="H33" s="112">
         <v>180</v>
       </c>
-      <c r="I27" s="111">
+      <c r="I33" s="112">
         <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
-      <c r="J27" s="112" t="s">
-        <v>1139</v>
-      </c>
-      <c r="K27" s="112" t="s">
-        <v>1140</v>
-      </c>
-      <c r="L27" s="111" t="s">
+      <c r="J33" s="113" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K33" s="113" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L33" s="112" t="s">
         <v>521</v>
       </c>
-      <c r="M27" s="111"/>
-      <c r="N27" s="111"/>
-    </row>
-    <row r="28" spans="1:14" ht="30" customHeight="1">
-      <c r="A28" s="113">
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+    </row>
+    <row r="34" spans="1:14" ht="30" customHeight="1">
+      <c r="A34" s="114">
         <v>7</v>
       </c>
-      <c r="B28" s="114" t="s">
+      <c r="B34" s="115" t="s">
         <v>367</v>
       </c>
-      <c r="C28" s="113" t="s">
+      <c r="C34" s="114" t="s">
         <v>368</v>
       </c>
-      <c r="D28" s="113">
+      <c r="D34" s="114">
         <v>8</v>
       </c>
-      <c r="E28" s="113">
+      <c r="E34" s="114">
         <v>3</v>
       </c>
-      <c r="F28" s="113" t="s">
+      <c r="F34" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G28" s="113">
+      <c r="G34" s="114">
         <v>40</v>
       </c>
-      <c r="H28" s="113">
+      <c r="H34" s="114">
         <v>60</v>
       </c>
-      <c r="I28" s="113">
+      <c r="I34" s="114">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="J28" s="114" t="s">
-        <v>1141</v>
-      </c>
-      <c r="K28" s="114" t="s">
-        <v>993</v>
-      </c>
-      <c r="L28" s="113"/>
-      <c r="M28" s="113"/>
-      <c r="N28" s="113">
+      <c r="J34" s="115" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K34" s="115" t="s">
+        <v>997</v>
+      </c>
+      <c r="L34" s="114"/>
+      <c r="M34" s="114"/>
+      <c r="N34" s="114">
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="30" customHeight="1">
-      <c r="A29" s="113">
+    <row r="35" spans="1:14" ht="30" customHeight="1">
+      <c r="A35" s="114">
         <v>8</v>
       </c>
-      <c r="B29" s="114" t="s">
+      <c r="B35" s="115" t="s">
         <v>537</v>
       </c>
-      <c r="C29" s="113" t="s">
+      <c r="C35" s="114" t="s">
         <v>372</v>
       </c>
-      <c r="D29" s="113" t="s">
+      <c r="D35" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="E29" s="113">
+      <c r="E35" s="114">
         <v>3</v>
       </c>
-      <c r="F29" s="113" t="s">
+      <c r="F35" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G29" s="113">
+      <c r="G35" s="114">
         <v>40</v>
       </c>
-      <c r="H29" s="113">
+      <c r="H35" s="114">
         <v>60</v>
       </c>
-      <c r="I29" s="113">
+      <c r="I35" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J29" s="114" t="s">
-        <v>1142</v>
-      </c>
-      <c r="K29" s="114" t="s">
-        <v>1143</v>
-      </c>
-      <c r="L29" s="113"/>
-      <c r="M29" s="113"/>
-      <c r="N29" s="113"/>
-    </row>
-    <row r="30" spans="1:14" ht="30" customHeight="1">
-      <c r="A30" s="113">
+      <c r="J35" s="115" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K35" s="115" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L35" s="114"/>
+      <c r="M35" s="114"/>
+      <c r="N35" s="114"/>
+    </row>
+    <row r="36" spans="1:14" ht="30" customHeight="1">
+      <c r="A36" s="114">
         <v>9</v>
       </c>
-      <c r="B30" s="114" t="s">
+      <c r="B36" s="115" t="s">
         <v>570</v>
       </c>
-      <c r="C30" s="113" t="s">
+      <c r="C36" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="D30" s="113">
+      <c r="D36" s="114">
         <v>25</v>
       </c>
-      <c r="E30" s="113">
+      <c r="E36" s="114">
         <v>3</v>
       </c>
-      <c r="F30" s="113" t="s">
+      <c r="F36" s="114" t="s">
         <v>364</v>
       </c>
-      <c r="G30" s="113">
+      <c r="G36" s="114">
         <v>40</v>
       </c>
-      <c r="H30" s="113">
+      <c r="H36" s="114">
         <v>120</v>
       </c>
-      <c r="I30" s="113">
+      <c r="I36" s="114">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J30" s="114" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K30" s="114" t="s">
-        <v>1145</v>
-      </c>
-      <c r="L30" s="113"/>
-      <c r="M30" s="113"/>
-      <c r="N30" s="113"/>
-    </row>
-    <row r="31" spans="1:14" ht="30" customHeight="1">
-      <c r="A31" s="113">
+      <c r="J36" s="115" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K36" s="115" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L36" s="114"/>
+      <c r="M36" s="114"/>
+      <c r="N36" s="114"/>
+    </row>
+    <row r="37" spans="1:14" ht="30" customHeight="1">
+      <c r="A37" s="114">
         <v>10</v>
       </c>
-      <c r="B31" s="114" t="s">
+      <c r="B37" s="115" t="s">
         <v>506</v>
       </c>
-      <c r="C31" s="113" t="s">
+      <c r="C37" s="114" t="s">
         <v>407</v>
       </c>
-      <c r="D31" s="113">
+      <c r="D37" s="114">
         <v>15</v>
       </c>
-      <c r="E31" s="113">
+      <c r="E37" s="114">
         <v>3</v>
       </c>
-      <c r="F31" s="113" t="s">
+      <c r="F37" s="114" t="s">
         <v>318</v>
       </c>
-      <c r="G31" s="113">
+      <c r="G37" s="114">
         <v>60</v>
       </c>
-      <c r="H31" s="113">
+      <c r="H37" s="114">
         <v>75</v>
       </c>
-      <c r="I31" s="113">
+      <c r="I37" s="114">
         <f t="shared" si="0"/>
         <v>6.8</v>
       </c>
-      <c r="J31" s="114" t="s">
-        <v>1146</v>
-      </c>
-      <c r="K31" s="114" t="s">
-        <v>1147</v>
-      </c>
-      <c r="L31" s="113"/>
-      <c r="M31" s="113"/>
-      <c r="N31" s="113"/>
-    </row>
-    <row r="32" spans="1:14" ht="30" customHeight="1">
-      <c r="A32" s="113">
+      <c r="J37" s="115" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K37" s="115" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L37" s="114"/>
+      <c r="M37" s="114"/>
+      <c r="N37" s="114"/>
+    </row>
+    <row r="38" spans="1:14" ht="30" customHeight="1">
+      <c r="A38" s="114">
         <v>11</v>
       </c>
-      <c r="B32" s="114" t="s">
+      <c r="B38" s="115" t="s">
         <v>401</v>
       </c>
-      <c r="C32" s="113" t="s">
+      <c r="C38" s="114" t="s">
         <v>402</v>
       </c>
-      <c r="D32" s="113">
+      <c r="D38" s="114">
         <v>40</v>
       </c>
-      <c r="E32" s="113">
+      <c r="E38" s="114">
         <v>4</v>
       </c>
-      <c r="F32" s="113" t="s">
+      <c r="F38" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G32" s="113">
+      <c r="G38" s="114">
         <v>40</v>
       </c>
-      <c r="H32" s="113">
+      <c r="H38" s="114">
         <v>10</v>
       </c>
-      <c r="I32" s="113">
+      <c r="I38" s="114">
         <f t="shared" si="0"/>
         <v>3.3</v>
       </c>
-      <c r="J32" s="114" t="s">
-        <v>1148</v>
-      </c>
-      <c r="K32" s="114" t="s">
-        <v>1000</v>
-      </c>
-      <c r="L32" s="113"/>
-      <c r="M32" s="113" t="s">
+      <c r="J38" s="115" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K38" s="115" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L38" s="114"/>
+      <c r="M38" s="114" t="s">
         <v>405</v>
       </c>
-      <c r="N32" s="113"/>
-    </row>
-    <row r="33" spans="1:14" ht="30" customHeight="1">
-      <c r="A33" s="113">
+      <c r="N38" s="114"/>
+    </row>
+    <row r="39" spans="1:14" ht="30" customHeight="1">
+      <c r="A39" s="114">
         <v>12</v>
       </c>
-      <c r="B33" s="114" t="s">
+      <c r="B39" s="115" t="s">
         <v>406</v>
       </c>
-      <c r="C33" s="113" t="s">
+      <c r="C39" s="114" t="s">
         <v>407</v>
       </c>
-      <c r="D33" s="113">
+      <c r="D39" s="114">
         <v>40</v>
       </c>
-      <c r="E33" s="113">
+      <c r="E39" s="114">
         <v>4</v>
       </c>
-      <c r="F33" s="113" t="s">
+      <c r="F39" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G33" s="113">
+      <c r="G39" s="114">
         <v>40</v>
       </c>
-      <c r="H33" s="113">
+      <c r="H39" s="114">
         <v>120</v>
       </c>
-      <c r="I33" s="113">
+      <c r="I39" s="114">
         <f t="shared" si="0"/>
         <v>10.7</v>
       </c>
-      <c r="J33" s="114" t="s">
-        <v>1149</v>
-      </c>
-      <c r="K33" s="114" t="s">
-        <v>1002</v>
-      </c>
-      <c r="L33" s="113"/>
-      <c r="M33" s="113" t="s">
+      <c r="J39" s="115" t="s">
+        <v>1157</v>
+      </c>
+      <c r="K39" s="115" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L39" s="114"/>
+      <c r="M39" s="114" t="s">
         <v>405</v>
       </c>
-      <c r="N33" s="113"/>
-    </row>
-    <row r="34" spans="1:14" ht="30" customHeight="1">
-      <c r="A34" s="113">
+      <c r="N39" s="114"/>
+    </row>
+    <row r="40" spans="1:14" ht="30" customHeight="1">
+      <c r="A40" s="114">
         <v>13</v>
       </c>
-      <c r="B34" s="114" t="s">
+      <c r="B40" s="115" t="s">
         <v>321</v>
       </c>
-      <c r="C34" s="113" t="s">
+      <c r="C40" s="114" t="s">
         <v>322</v>
       </c>
-      <c r="D34" s="113">
+      <c r="D40" s="114">
         <v>10</v>
       </c>
-      <c r="E34" s="113">
+      <c r="E40" s="114">
         <v>3</v>
       </c>
-      <c r="F34" s="113" t="s">
+      <c r="F40" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G34" s="113">
+      <c r="G40" s="114">
         <v>40</v>
       </c>
-      <c r="H34" s="113">
+      <c r="H40" s="114">
         <v>75</v>
       </c>
-      <c r="I34" s="113">
+      <c r="I40" s="114">
         <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="J34" s="114" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K34" s="114" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L34" s="113"/>
-      <c r="M34" s="113"/>
-      <c r="N34" s="113"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="115"/>
-      <c r="B35" s="115"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115" t="s">
+      <c r="J40" s="115" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K40" s="115" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L40" s="114"/>
+      <c r="M40" s="114"/>
+      <c r="N40" s="114"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="116"/>
+      <c r="B41" s="116"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E35" s="115">
-        <f>SUM(E22:E34)</f>
+      <c r="E41" s="116">
+        <f>SUM(E28:E40)</f>
         <v>39</v>
       </c>
-      <c r="F35" s="115"/>
-      <c r="G35" s="115"/>
-      <c r="H35" s="115"/>
-      <c r="I35" s="115">
-        <f>ROUND(SUM(I22:I34),0)</f>
+      <c r="F41" s="116"/>
+      <c r="G41" s="116"/>
+      <c r="H41" s="116"/>
+      <c r="I41" s="116">
+        <f>ROUND(SUM(I28:I40),0)</f>
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="107" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="116" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="116" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="116" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="116" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="116" t="s">
-        <v>1157</v>
-      </c>
-    </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="116" t="s">
-        <v>1158</v>
+      <c r="A43" s="107" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="117" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="107" t="s">
-        <v>1159</v>
+      <c r="A45" s="117" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="116" t="s">
-        <v>1160</v>
+      <c r="A46" s="117" t="s">
+        <v>1163</v>
       </c>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="116" t="s">
-        <v>1161</v>
+      <c r="A47" s="117" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="116" t="s">
-        <v>1162</v>
+      <c r="A48" s="117" t="s">
+        <v>1165</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="116" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="116" t="s">
-        <v>1164</v>
+      <c r="A49" s="117" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="107" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="107" t="s">
-        <v>1165</v>
+      <c r="A52" s="117" t="s">
+        <v>1168</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="116" t="s">
-        <v>1166</v>
+      <c r="A53" s="117" t="s">
+        <v>1169</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="116" t="s">
-        <v>1167</v>
+      <c r="A54" s="117" t="s">
+        <v>1170</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="116" t="s">
-        <v>1168</v>
+      <c r="A55" s="117" t="s">
+        <v>1171</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="116" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="116" t="s">
-        <v>1170</v>
+      <c r="A56" s="117" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="107" t="s">
+        <v>1173</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="107" t="s">
-        <v>1171</v>
+      <c r="A59" s="117" t="s">
+        <v>1174</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="116" t="s">
-        <v>1172</v>
+      <c r="A60" s="117" t="s">
+        <v>1175</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="116" t="s">
-        <v>1173</v>
+      <c r="A61" s="117" t="s">
+        <v>1176</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="116" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="107" t="s">
+      <c r="A62" s="117" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="117" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="107" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="117" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="117" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="117" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="107" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="116" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="116" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="107" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="116" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="116" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="116" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="116" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="116" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="C75" s="117" t="s">
-        <v>1181</v>
+    <row r="71" spans="1:1">
+      <c r="A71" s="117" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="117" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="107" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="117" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="117" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="117" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="117" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="117" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
+      <c r="C81" s="118" t="s">
+        <v>1189</v>
       </c>
     </row>
   </sheetData>
@@ -15295,27 +15411,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="118" t="s">
-        <v>1183</v>
+      <c r="A5" s="110" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="118" t="s">
-        <v>1023</v>
+      <c r="A6" s="110" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="118" t="s">
-        <v>1024</v>
+      <c r="A7" s="110" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15324,424 +15440,424 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
-      <c r="A10" s="110" t="s">
+      <c r="A10" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="110" t="s">
+      <c r="C10" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="110" t="s">
+      <c r="D10" s="111" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="110" t="s">
+      <c r="E10" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="110" t="s">
+      <c r="F10" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="G10" s="110" t="s">
+      <c r="G10" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="H10" s="110" t="s">
+      <c r="H10" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="I10" s="110" t="s">
+      <c r="I10" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="J10" s="110" t="s">
+      <c r="J10" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="K10" s="110" t="s">
+      <c r="K10" s="111" t="s">
         <v>276</v>
       </c>
-      <c r="L10" s="110" t="s">
+      <c r="L10" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="M10" s="110" t="s">
+      <c r="M10" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="N10" s="110" t="s">
+      <c r="N10" s="111" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1">
-      <c r="A11" s="113">
+      <c r="A11" s="114">
         <v>1</v>
       </c>
-      <c r="B11" s="114" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C11" s="113" t="s">
+      <c r="B11" s="115" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C11" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="D11" s="113">
+      <c r="D11" s="114">
         <v>35</v>
       </c>
-      <c r="E11" s="113">
+      <c r="E11" s="114">
         <v>4</v>
       </c>
-      <c r="F11" s="113" t="s">
+      <c r="F11" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="G11" s="113">
+      <c r="G11" s="114">
         <v>40</v>
       </c>
-      <c r="H11" s="113">
+      <c r="H11" s="114">
         <v>150</v>
       </c>
-      <c r="I11" s="113">
+      <c r="I11" s="114">
         <f t="shared" ref="I11:I18" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.7</v>
       </c>
-      <c r="J11" s="114" t="s">
-        <v>1185</v>
-      </c>
-      <c r="K11" s="114" t="s">
-        <v>1186</v>
-      </c>
-      <c r="L11" s="113" t="s">
-        <v>1027</v>
-      </c>
-      <c r="M11" s="113"/>
-      <c r="N11" s="113"/>
+      <c r="J11" s="115" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K11" s="115" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L11" s="114" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M11" s="114"/>
+      <c r="N11" s="114"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1">
-      <c r="A12" s="113">
+      <c r="A12" s="114">
         <v>2</v>
       </c>
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="115" t="s">
         <v>479</v>
       </c>
-      <c r="C12" s="113" t="s">
+      <c r="C12" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="D12" s="113">
+      <c r="D12" s="114">
         <v>45</v>
       </c>
-      <c r="E12" s="113">
+      <c r="E12" s="114">
         <v>3</v>
       </c>
-      <c r="F12" s="113" t="s">
+      <c r="F12" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="G12" s="113">
+      <c r="G12" s="114">
         <v>40</v>
       </c>
-      <c r="H12" s="113">
+      <c r="H12" s="114">
         <v>150</v>
       </c>
-      <c r="I12" s="113">
+      <c r="I12" s="114">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="J12" s="114" t="s">
-        <v>1187</v>
-      </c>
-      <c r="K12" s="114" t="s">
-        <v>1188</v>
-      </c>
-      <c r="L12" s="113"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="113"/>
+      <c r="J12" s="115" t="s">
+        <v>1195</v>
+      </c>
+      <c r="K12" s="115" t="s">
+        <v>1196</v>
+      </c>
+      <c r="L12" s="114"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="114"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1">
-      <c r="A13" s="113">
+      <c r="A13" s="114">
         <v>3</v>
       </c>
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="115" t="s">
         <v>489</v>
       </c>
-      <c r="C13" s="113" t="s">
+      <c r="C13" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="D13" s="113">
+      <c r="D13" s="114">
         <v>32</v>
       </c>
-      <c r="E13" s="113">
+      <c r="E13" s="114">
         <v>3</v>
       </c>
-      <c r="F13" s="113" t="s">
+      <c r="F13" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G13" s="113">
+      <c r="G13" s="114">
         <v>40</v>
       </c>
-      <c r="H13" s="113">
+      <c r="H13" s="114">
         <v>75</v>
       </c>
-      <c r="I13" s="113">
+      <c r="I13" s="114">
         <f t="shared" si="0"/>
         <v>6.8</v>
       </c>
-      <c r="J13" s="114" t="s">
-        <v>1189</v>
-      </c>
-      <c r="K13" s="114" t="s">
-        <v>1190</v>
-      </c>
-      <c r="L13" s="113"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="113">
+      <c r="J13" s="115" t="s">
+        <v>1197</v>
+      </c>
+      <c r="K13" s="115" t="s">
+        <v>1198</v>
+      </c>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114">
         <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1">
-      <c r="A14" s="113">
+      <c r="A14" s="114">
         <v>4</v>
       </c>
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="115" t="s">
         <v>498</v>
       </c>
-      <c r="C14" s="113" t="s">
+      <c r="C14" s="114" t="s">
         <v>421</v>
       </c>
-      <c r="D14" s="113">
+      <c r="D14" s="114">
         <v>15</v>
       </c>
-      <c r="E14" s="113">
+      <c r="E14" s="114">
         <v>3</v>
       </c>
-      <c r="F14" s="113" t="s">
+      <c r="F14" s="114" t="s">
         <v>364</v>
       </c>
-      <c r="G14" s="113">
+      <c r="G14" s="114">
         <v>40</v>
       </c>
-      <c r="H14" s="113">
+      <c r="H14" s="114">
         <v>90</v>
       </c>
-      <c r="I14" s="113">
+      <c r="I14" s="114">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="J14" s="114" t="s">
-        <v>1191</v>
-      </c>
-      <c r="K14" s="114" t="s">
-        <v>1192</v>
-      </c>
-      <c r="L14" s="113"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
+      <c r="J14" s="115" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K14" s="115" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="114"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
-      <c r="A15" s="113">
+      <c r="A15" s="114">
         <v>5</v>
       </c>
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="115" t="s">
         <v>441</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="114" t="s">
         <v>351</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="114">
         <v>30</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E15" s="114">
         <v>4</v>
       </c>
-      <c r="F15" s="113" t="s">
+      <c r="F15" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G15" s="114">
         <v>40</v>
       </c>
-      <c r="H15" s="113">
+      <c r="H15" s="114">
         <v>105</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I15" s="114">
         <f t="shared" si="0"/>
         <v>9.6999999999999993</v>
       </c>
-      <c r="J15" s="114" t="s">
-        <v>1193</v>
-      </c>
-      <c r="K15" s="114" t="s">
-        <v>1194</v>
-      </c>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
+      <c r="J15" s="115" t="s">
+        <v>1201</v>
+      </c>
+      <c r="K15" s="115" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1">
-      <c r="A16" s="113">
+      <c r="A16" s="114">
         <v>6</v>
       </c>
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="115" t="s">
         <v>534</v>
       </c>
-      <c r="C16" s="113" t="s">
+      <c r="C16" s="114" t="s">
         <v>351</v>
       </c>
-      <c r="D16" s="113">
+      <c r="D16" s="114">
         <v>10</v>
       </c>
-      <c r="E16" s="113">
+      <c r="E16" s="114">
         <v>4</v>
       </c>
-      <c r="F16" s="113" t="s">
+      <c r="F16" s="114" t="s">
         <v>303</v>
       </c>
-      <c r="G16" s="113">
+      <c r="G16" s="114">
         <v>40</v>
       </c>
-      <c r="H16" s="113">
+      <c r="H16" s="114">
         <v>105</v>
       </c>
-      <c r="I16" s="113">
+      <c r="I16" s="114">
         <f t="shared" si="0"/>
         <v>10.7</v>
       </c>
-      <c r="J16" s="114" t="s">
-        <v>1195</v>
-      </c>
-      <c r="K16" s="114" t="s">
-        <v>1196</v>
-      </c>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113">
+      <c r="J16" s="115" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K16" s="115" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L16" s="114"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="114">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1">
-      <c r="A17" s="113">
+      <c r="A17" s="114">
         <v>7</v>
       </c>
-      <c r="B17" s="114" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C17" s="113" t="s">
+      <c r="B17" s="115" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C17" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D17" s="113">
+      <c r="D17" s="114">
         <v>22</v>
       </c>
-      <c r="E17" s="113">
+      <c r="E17" s="114">
         <v>3</v>
       </c>
-      <c r="F17" s="113" t="s">
+      <c r="F17" s="114" t="s">
         <v>317</v>
       </c>
-      <c r="G17" s="113">
+      <c r="G17" s="114">
         <v>40</v>
       </c>
-      <c r="H17" s="113">
+      <c r="H17" s="114">
         <v>70</v>
       </c>
-      <c r="I17" s="113">
+      <c r="I17" s="114">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J17" s="114" t="s">
-        <v>1198</v>
-      </c>
-      <c r="K17" s="114" t="s">
-        <v>1199</v>
-      </c>
-      <c r="L17" s="113"/>
-      <c r="M17" s="113"/>
-      <c r="N17" s="113"/>
+      <c r="J17" s="115" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K17" s="115" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="114"/>
     </row>
     <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="113">
+      <c r="A18" s="114">
         <v>8</v>
       </c>
-      <c r="B18" s="114" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C18" s="113" t="s">
+      <c r="B18" s="115" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C18" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="114">
         <v>15</v>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="114">
         <v>3</v>
       </c>
-      <c r="F18" s="113" t="s">
+      <c r="F18" s="114" t="s">
         <v>288</v>
       </c>
-      <c r="G18" s="113">
+      <c r="G18" s="114">
         <v>40</v>
       </c>
-      <c r="H18" s="113">
+      <c r="H18" s="114">
         <v>75</v>
       </c>
-      <c r="I18" s="113">
+      <c r="I18" s="114">
         <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="J18" s="114" t="s">
-        <v>1201</v>
-      </c>
-      <c r="K18" s="114" t="s">
-        <v>1202</v>
-      </c>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="N18" s="113"/>
+      <c r="J18" s="115" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K18" s="115" t="s">
+        <v>1210</v>
+      </c>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="115"/>
-      <c r="B19" s="115"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115" t="s">
+      <c r="A19" s="116"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E19" s="115">
+      <c r="E19" s="116">
         <f>SUM(E11:E18)</f>
         <v>27</v>
       </c>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115">
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116">
         <f>ROUND(SUM(I11:I18),0)</f>
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="107" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="116" t="s">
-        <v>1204</v>
+      <c r="A22" s="117" t="s">
+        <v>1212</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="116" t="s">
-        <v>1205</v>
+      <c r="A23" s="117" t="s">
+        <v>1213</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="116" t="s">
-        <v>1206</v>
+      <c r="A24" s="117" t="s">
+        <v>1214</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="116" t="s">
-        <v>1208</v>
+      <c r="A27" s="117" t="s">
+        <v>1216</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="116" t="s">
-        <v>1209</v>
+      <c r="A28" s="117" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="116" t="s">
-        <v>1210</v>
+      <c r="A29" s="117" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -15750,43 +15866,43 @@
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="116" t="s">
-        <v>1211</v>
+      <c r="A32" s="117" t="s">
+        <v>1219</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="116" t="s">
-        <v>1212</v>
+      <c r="A33" s="117" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="107" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="116" t="s">
-        <v>1213</v>
+      <c r="A36" s="117" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="116" t="s">
-        <v>1214</v>
+      <c r="A37" s="117" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="116" t="s">
-        <v>1215</v>
+      <c r="A38" s="117" t="s">
+        <v>1223</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="116" t="s">
-        <v>1018</v>
+      <c r="A39" s="117" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="C41" s="117" t="s">
-        <v>1216</v>
+      <c r="C41" s="118" t="s">
+        <v>1224</v>
       </c>
     </row>
   </sheetData>
@@ -15817,156 +15933,156 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="111" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="114" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="114" t="s">
+      <c r="D5" s="115" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="114" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="120" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="114" t="s">
+      <c r="C6" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="114" t="s">
+      <c r="D6" s="115" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="114" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="114" t="s">
+      <c r="C7" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="114" t="s">
+      <c r="D7" s="115" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
-      <c r="A8" s="113" t="s">
+      <c r="A8" s="114" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="114" t="s">
+      <c r="C8" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="114" t="s">
+      <c r="D8" s="115" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="114" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="114" t="s">
+      <c r="C9" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="114" t="s">
+      <c r="D9" s="115" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
-      <c r="A10" s="113" t="s">
+      <c r="A10" s="114" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="114" t="s">
+      <c r="D10" s="115" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
-      <c r="A11" s="113" t="s">
+      <c r="A11" s="114" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="114" t="s">
+      <c r="C11" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="114" t="s">
+      <c r="D11" s="115" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="114" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="114" t="s">
+      <c r="C12" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="114" t="s">
+      <c r="D12" s="115" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="114" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="114" t="s">
+      <c r="C13" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="114" t="s">
+      <c r="D13" s="115" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
-      <c r="A14" s="113" t="s">
+      <c r="A14" s="114" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="114" t="s">
+      <c r="C14" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="114" t="s">
+      <c r="D14" s="115" t="s">
         <v>43</v>
       </c>
     </row>
@@ -16173,7 +16289,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -16187,12 +16303,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16206,1741 +16322,1769 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="110" t="s">
-        <v>1220</v>
-      </c>
-      <c r="B6" s="110" t="s">
+      <c r="A6" s="111" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B6" s="111" t="s">
         <v>652</v>
       </c>
-      <c r="C6" s="110" t="s">
+      <c r="C6" s="111" t="s">
         <v>653</v>
       </c>
-      <c r="D6" s="110" t="s">
+      <c r="D6" s="111" t="s">
         <v>654</v>
       </c>
-      <c r="E6" s="110" t="s">
+      <c r="E6" s="111" t="s">
         <v>655</v>
       </c>
-      <c r="F6" s="110" t="s">
+      <c r="F6" s="111" t="s">
         <v>656</v>
       </c>
-      <c r="G6" s="110" t="s">
+      <c r="G6" s="111" t="s">
         <v>657</v>
       </c>
-      <c r="H6" s="110" t="s">
+      <c r="H6" s="111" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="38.25">
-      <c r="A7" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B7" s="114" t="s">
+      <c r="A7" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B7" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="113" t="s">
+      <c r="C7" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D7" s="113">
+      <c r="D7" s="114">
         <v>0.33</v>
       </c>
-      <c r="E7" s="113">
-        <f t="shared" ref="E7:E38" ca="1" si="0">IFERROR(INDEX(INDIRECT("'"&amp;$A7&amp;"'!$E$1:$E$45"),MATCH($B7,INDIRECT("'"&amp;$A7&amp;"'!$B$1:$B$45"),0)),"?")</f>
+      <c r="E7" s="114">
+        <f t="shared" ref="E7:E38" ca="1" si="0">IFERROR(INDEX(INDIRECT("'"&amp;$A7&amp;"'!$E$1:$E$60"),MATCH($B7,INDIRECT("'"&amp;$A7&amp;"'!$B$1:$B$60"),0)),"?")</f>
         <v>5</v>
       </c>
-      <c r="F7" s="113">
+      <c r="F7" s="114">
         <f t="shared" ref="F7:F38" ca="1" si="1">IF(ISNUMBER(E7),$D7*E7,0)</f>
         <v>1.6500000000000001</v>
       </c>
-      <c r="G7" s="113" t="s">
+      <c r="G7" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H7" s="114" t="s">
-        <v>1222</v>
+      <c r="H7" s="115" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B8" s="114" t="s">
+      <c r="A8" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B8" s="115" t="s">
         <v>531</v>
       </c>
-      <c r="C8" s="113" t="s">
+      <c r="C8" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D8" s="113">
+      <c r="D8" s="114">
         <v>0.5</v>
       </c>
-      <c r="E8" s="113">
+      <c r="E8" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F8" s="113">
+      <c r="F8" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="G8" s="113" t="s">
+      <c r="G8" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H8" s="114" t="s">
-        <v>1223</v>
+      <c r="H8" s="115" t="s">
+        <v>1231</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B9" s="114" t="s">
+      <c r="A9" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B9" s="115" t="s">
         <v>357</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D9" s="113">
+      <c r="D9" s="114">
         <v>0.5</v>
       </c>
-      <c r="E9" s="113">
+      <c r="E9" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F9" s="113">
+      <c r="F9" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G9" s="113" t="s">
+      <c r="G9" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H9" s="114" t="s">
-        <v>1224</v>
+      <c r="H9" s="115" t="s">
+        <v>1232</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B10" s="114" t="s">
+      <c r="A10" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B10" s="115" t="s">
         <v>522</v>
       </c>
-      <c r="C10" s="113" t="s">
+      <c r="C10" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D10" s="113">
+      <c r="D10" s="114">
         <v>0.5</v>
       </c>
-      <c r="E10" s="113">
+      <c r="E10" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F10" s="113">
+      <c r="F10" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G10" s="113" t="s">
+      <c r="G10" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H10" s="114" t="s">
-        <v>1223</v>
+      <c r="H10" s="115" t="s">
+        <v>1231</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
-      <c r="A11" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B11" s="114" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C11" s="113" t="s">
+      <c r="A11" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B11" s="115" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C11" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="D11" s="113">
+      <c r="D11" s="114">
         <v>0.33</v>
       </c>
-      <c r="E11" s="113">
+      <c r="E11" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F11" s="113">
+      <c r="F11" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.99</v>
       </c>
-      <c r="G11" s="113" t="s">
+      <c r="G11" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H11" s="114" t="s">
-        <v>1227</v>
+      <c r="H11" s="115" t="s">
+        <v>1235</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
-      <c r="A12" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B12" s="114" t="s">
+      <c r="A12" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B12" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="C12" s="113" t="s">
+      <c r="C12" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D12" s="113">
+      <c r="D12" s="114">
         <v>0.5</v>
       </c>
-      <c r="E12" s="113">
+      <c r="E12" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F12" s="113">
+      <c r="F12" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="G12" s="113" t="s">
+      <c r="G12" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H12" s="114" t="s">
-        <v>1229</v>
+      <c r="H12" s="115" t="s">
+        <v>1237</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
-      <c r="A13" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B13" s="114" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C13" s="113" t="s">
+      <c r="A13" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B13" s="115" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C13" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="113">
+      <c r="D13" s="114">
         <v>0.5</v>
       </c>
-      <c r="E13" s="113">
+      <c r="E13" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="113">
+      <c r="F13" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G13" s="113" t="s">
+      <c r="G13" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H13" s="114" t="s">
-        <v>1230</v>
+      <c r="H13" s="115" t="s">
+        <v>1238</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
-      <c r="A14" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B14" s="114" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C14" s="113" t="s">
+      <c r="A14" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B14" s="115" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C14" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D14" s="113">
+      <c r="D14" s="114">
         <v>0.2</v>
       </c>
-      <c r="E14" s="113">
+      <c r="E14" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F14" s="113">
+      <c r="F14" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G14" s="113" t="s">
+      <c r="G14" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H14" s="114" t="s">
-        <v>1231</v>
+      <c r="H14" s="115" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
-      <c r="A15" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B15" s="114" t="s">
+      <c r="A15" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B15" s="115" t="s">
         <v>486</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="114">
         <v>0.33</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E15" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="113">
+      <c r="F15" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.99</v>
       </c>
-      <c r="G15" s="113" t="s">
+      <c r="G15" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H15" s="114" t="s">
-        <v>1232</v>
+      <c r="H15" s="115" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
-      <c r="A16" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B16" s="114" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C16" s="113" t="s">
+      <c r="A16" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B16" s="115" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C16" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D16" s="113">
+      <c r="D16" s="114">
         <v>0.2</v>
       </c>
-      <c r="E16" s="113">
+      <c r="E16" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="113">
+      <c r="F16" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G16" s="113" t="s">
+      <c r="G16" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H16" s="114" t="s">
-        <v>1234</v>
+      <c r="H16" s="115" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
-      <c r="A17" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B17" s="114" t="s">
+      <c r="A17" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B17" s="115" t="s">
         <v>479</v>
       </c>
-      <c r="C17" s="113" t="s">
+      <c r="C17" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D17" s="113">
+      <c r="D17" s="114">
         <v>0.2</v>
       </c>
-      <c r="E17" s="113">
+      <c r="E17" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F17" s="113">
+      <c r="F17" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G17" s="113" t="s">
+      <c r="G17" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H17" s="114" t="s">
-        <v>1235</v>
+      <c r="H17" s="115" t="s">
+        <v>1243</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
-      <c r="A18" s="113" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B18" s="114" t="s">
+      <c r="A18" s="114" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B18" s="115" t="s">
         <v>453</v>
       </c>
-      <c r="C18" s="113" t="s">
+      <c r="C18" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="114">
         <v>0.2</v>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F18" s="113">
+      <c r="F18" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G18" s="113" t="s">
+      <c r="G18" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H18" s="114" t="s">
-        <v>1237</v>
+      <c r="H18" s="115" t="s">
+        <v>1245</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
-      <c r="A19" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B19" s="114" t="s">
+      <c r="A19" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B19" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="113" t="s">
+      <c r="C19" s="114" t="s">
         <v>443</v>
       </c>
-      <c r="D19" s="113">
+      <c r="D19" s="114">
         <v>0.33</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E19" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="F19" s="113">
+      <c r="F19" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>1.6500000000000001</v>
       </c>
-      <c r="G19" s="113" t="s">
+      <c r="G19" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H19" s="114" t="s">
-        <v>1238</v>
+      <c r="H19" s="115" t="s">
+        <v>1246</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B20" s="114" t="s">
+      <c r="A20" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B20" s="115" t="s">
         <v>531</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="114" t="s">
         <v>443</v>
       </c>
-      <c r="D20" s="113">
+      <c r="D20" s="114">
         <v>0.5</v>
       </c>
-      <c r="E20" s="113">
+      <c r="E20" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F20" s="113">
+      <c r="F20" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="G20" s="113" t="s">
+      <c r="G20" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H20" s="114" t="s">
-        <v>1239</v>
+      <c r="H20" s="115" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B21" s="114" t="s">
+      <c r="A21" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B21" s="115" t="s">
         <v>357</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C21" s="114" t="s">
         <v>443</v>
       </c>
-      <c r="D21" s="113">
+      <c r="D21" s="114">
         <v>0.2</v>
       </c>
-      <c r="E21" s="113">
+      <c r="E21" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F21" s="113">
+      <c r="F21" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G21" s="113" t="s">
+      <c r="G21" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H21" s="114" t="s">
-        <v>1240</v>
+      <c r="H21" s="115" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B22" s="114" t="s">
+      <c r="A22" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B22" s="115" t="s">
         <v>600</v>
       </c>
-      <c r="C22" s="113" t="s">
+      <c r="C22" s="114" t="s">
         <v>443</v>
       </c>
-      <c r="D22" s="113">
+      <c r="D22" s="114">
         <v>0.2</v>
       </c>
-      <c r="E22" s="113">
+      <c r="E22" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F22" s="113">
+      <c r="F22" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G22" s="113" t="s">
+      <c r="G22" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H22" s="114" t="s">
+      <c r="H22" s="115" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="114" t="s">
         <v>1241</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B23" s="114" t="s">
+      <c r="B23" s="115" t="s">
         <v>441</v>
       </c>
-      <c r="C23" s="113" t="s">
+      <c r="C23" s="114" t="s">
         <v>443</v>
       </c>
-      <c r="D23" s="113">
+      <c r="D23" s="114">
         <v>0.2</v>
       </c>
-      <c r="E23" s="113">
+      <c r="E23" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F23" s="113">
+      <c r="F23" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G23" s="113" t="s">
+      <c r="G23" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H23" s="114" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="38.25">
-      <c r="A24" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B24" s="114" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C24" s="113" t="s">
-        <v>368</v>
-      </c>
-      <c r="D24" s="113">
-        <v>0.33</v>
-      </c>
-      <c r="E24" s="113">
+      <c r="H23" s="115" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="25.5">
+      <c r="A24" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B24" s="115" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="114" t="s">
+        <v>372</v>
+      </c>
+      <c r="D24" s="114">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F24" s="113">
+      <c r="F24" s="114">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="114" t="s">
+        <v>673</v>
+      </c>
+      <c r="H24" s="115" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="38.25">
+      <c r="A25" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B25" s="115" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C25" s="114" t="s">
+        <v>368</v>
+      </c>
+      <c r="D25" s="114">
+        <v>0.33</v>
+      </c>
+      <c r="E25" s="114">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F25" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.99</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="G25" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H24" s="114" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="38.25">
-      <c r="A25" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B25" s="114" t="s">
+      <c r="H25" s="115" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="38.25">
+      <c r="A26" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B26" s="115" t="s">
         <v>522</v>
       </c>
-      <c r="C25" s="113" t="s">
+      <c r="C26" s="114" t="s">
         <v>368</v>
       </c>
-      <c r="D25" s="113">
+      <c r="D26" s="114">
         <v>0.33</v>
       </c>
-      <c r="E25" s="113">
+      <c r="E26" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F25" s="113">
+      <c r="F26" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.99</v>
       </c>
-      <c r="G25" s="113" t="s">
+      <c r="G26" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H25" s="114" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="25.5">
-      <c r="A26" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B26" s="114" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C26" s="113" t="s">
+      <c r="H26" s="115" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="25.5">
+      <c r="A27" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B27" s="115" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C27" s="114" t="s">
         <v>383</v>
       </c>
-      <c r="D26" s="113">
+      <c r="D27" s="114">
         <v>0.33</v>
       </c>
-      <c r="E26" s="113">
+      <c r="E27" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F26" s="113">
+      <c r="F27" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>1.32</v>
       </c>
-      <c r="G26" s="113" t="s">
+      <c r="G27" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H26" s="114" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="25.5">
-      <c r="A27" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B27" s="114" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C27" s="113" t="s">
+      <c r="H27" s="115" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="25.5">
+      <c r="A28" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B28" s="115" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C28" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D27" s="113">
+      <c r="D28" s="114">
         <v>0.5</v>
       </c>
-      <c r="E27" s="113">
+      <c r="E28" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F27" s="113">
+      <c r="F28" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="G27" s="113" t="s">
+      <c r="G28" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H27" s="114" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="25.5">
-      <c r="A28" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B28" s="114" t="s">
+      <c r="H28" s="115" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="25.5">
+      <c r="A29" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B29" s="115" t="s">
         <v>479</v>
       </c>
-      <c r="C28" s="113" t="s">
+      <c r="C29" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D28" s="113">
+      <c r="D29" s="114">
         <v>0.5</v>
       </c>
-      <c r="E28" s="113">
+      <c r="E29" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F28" s="113">
+      <c r="F29" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G28" s="113" t="s">
+      <c r="G29" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H28" s="114" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B29" s="114" t="s">
+      <c r="H29" s="115" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B30" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="113" t="s">
+      <c r="C30" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D29" s="113">
+      <c r="D30" s="114">
         <v>0</v>
       </c>
-      <c r="E29" s="113">
+      <c r="E30" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="F29" s="113">
+      <c r="F30" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="G29" s="113" t="s">
+      <c r="G30" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H29" s="114" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B30" s="114" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C30" s="113" t="s">
+      <c r="H30" s="115" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B31" s="115" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C31" s="114" t="s">
         <v>421</v>
       </c>
-      <c r="D30" s="113">
+      <c r="D31" s="114">
         <v>0.2</v>
       </c>
-      <c r="E30" s="113">
+      <c r="E31" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F30" s="113">
+      <c r="F31" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G30" s="113" t="s">
+      <c r="G31" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H30" s="114" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B31" s="114" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C31" s="113" t="s">
+      <c r="H31" s="115" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B32" s="115" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C32" s="114" t="s">
         <v>421</v>
       </c>
-      <c r="D31" s="113">
+      <c r="D32" s="114">
         <v>0.2</v>
       </c>
-      <c r="E31" s="113">
+      <c r="E32" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F31" s="113">
+      <c r="F32" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G31" s="113" t="s">
+      <c r="G32" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H31" s="114" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="25.5">
-      <c r="A32" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B32" s="114" t="s">
+      <c r="H32" s="115" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="25.5">
+      <c r="A33" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B33" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="113" t="s">
+      <c r="C33" s="114" t="s">
         <v>421</v>
       </c>
-      <c r="D32" s="113">
+      <c r="D33" s="114">
         <v>0</v>
       </c>
-      <c r="E32" s="113">
+      <c r="E33" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="F32" s="113">
+      <c r="F33" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="G32" s="113" t="s">
+      <c r="G33" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H32" s="114" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B33" s="114" t="s">
+      <c r="H33" s="115" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B34" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="C33" s="113" t="s">
+      <c r="C34" s="114" t="s">
         <v>432</v>
       </c>
-      <c r="D33" s="113">
+      <c r="D34" s="114">
         <v>0.2</v>
       </c>
-      <c r="E33" s="113">
+      <c r="E34" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F33" s="113">
+      <c r="F34" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G33" s="113" t="s">
+      <c r="G34" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H33" s="114" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B34" s="114" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C34" s="113" t="s">
+      <c r="H34" s="115" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B35" s="115" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C35" s="114" t="s">
         <v>432</v>
       </c>
-      <c r="D34" s="113">
+      <c r="D35" s="114">
         <v>0.2</v>
       </c>
-      <c r="E34" s="113">
+      <c r="E35" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F34" s="113">
+      <c r="F35" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G34" s="113" t="s">
+      <c r="G35" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H34" s="114" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B35" s="114" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C35" s="113" t="s">
+      <c r="H35" s="115" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B36" s="115" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C36" s="114" t="s">
         <v>432</v>
       </c>
-      <c r="D35" s="113">
+      <c r="D36" s="114">
         <v>0.2</v>
       </c>
-      <c r="E35" s="113">
+      <c r="E36" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F35" s="113">
+      <c r="F36" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G35" s="113" t="s">
+      <c r="G36" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H35" s="114" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="25.5">
-      <c r="A36" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B36" s="114" t="s">
+      <c r="H36" s="115" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="25.5">
+      <c r="A37" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B37" s="115" t="s">
         <v>479</v>
       </c>
-      <c r="C36" s="113" t="s">
+      <c r="C37" s="114" t="s">
         <v>432</v>
       </c>
-      <c r="D36" s="113">
+      <c r="D37" s="114">
         <v>0.2</v>
       </c>
-      <c r="E36" s="113">
+      <c r="E37" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F36" s="113">
+      <c r="F37" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G36" s="113" t="s">
+      <c r="G37" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H36" s="114" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="38.25">
-      <c r="A37" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B37" s="114" t="s">
+      <c r="H37" s="115" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="38.25">
+      <c r="A38" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B38" s="115" t="s">
         <v>424</v>
       </c>
-      <c r="C37" s="113" t="s">
+      <c r="C38" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="D37" s="113">
+      <c r="D38" s="114">
         <v>0.33</v>
       </c>
-      <c r="E37" s="113">
+      <c r="E38" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="F37" s="113">
+      <c r="F38" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.99</v>
       </c>
-      <c r="G37" s="113" t="s">
+      <c r="G38" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H37" s="114" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B38" s="114" t="s">
+      <c r="H38" s="115" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B39" s="115" t="s">
         <v>537</v>
       </c>
-      <c r="C38" s="113" t="s">
+      <c r="C39" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="D38" s="113">
+      <c r="D39" s="114">
         <v>0.33</v>
       </c>
-      <c r="E38" s="113">
-        <f t="shared" ca="1" si="0"/>
+      <c r="E39" s="114">
+        <f t="shared" ref="E39:E68" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$60"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$60"),0)),"?")</f>
         <v>3</v>
       </c>
-      <c r="F38" s="113">
-        <f t="shared" ca="1" si="1"/>
+      <c r="F39" s="114">
+        <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
         <v>0.99</v>
       </c>
-      <c r="G38" s="113" t="s">
+      <c r="G39" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H38" s="114" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B39" s="114" t="s">
-        <v>994</v>
-      </c>
-      <c r="C39" s="113" t="s">
+      <c r="H39" s="115" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B40" s="115" t="s">
+        <v>998</v>
+      </c>
+      <c r="C40" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="D39" s="113">
+      <c r="D40" s="114">
         <v>0.33</v>
       </c>
-      <c r="E39" s="113">
-        <f t="shared" ref="E39:E67" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
+      <c r="E40" s="114">
+        <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F39" s="113">
-        <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
+      <c r="F40" s="114">
+        <f t="shared" ca="1" si="3"/>
         <v>1.32</v>
       </c>
-      <c r="G39" s="113" t="s">
+      <c r="G40" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H39" s="114" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B40" s="114" t="s">
+      <c r="H40" s="115" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B41" s="115" t="s">
         <v>486</v>
       </c>
-      <c r="C40" s="113" t="s">
+      <c r="C41" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="D40" s="113">
+      <c r="D41" s="114">
         <v>0.5</v>
       </c>
-      <c r="E40" s="113">
+      <c r="E41" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F40" s="113">
+      <c r="F41" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1.5</v>
       </c>
-      <c r="G40" s="113" t="s">
+      <c r="G41" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H40" s="114" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="38.25">
-      <c r="A41" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B41" s="114" t="s">
+      <c r="H41" s="115" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="38.25">
+      <c r="A42" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B42" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="113" t="s">
+      <c r="C42" s="114" t="s">
         <v>327</v>
       </c>
-      <c r="D41" s="113">
+      <c r="D42" s="114">
         <v>0</v>
       </c>
-      <c r="E41" s="113">
+      <c r="E42" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="F41" s="113">
+      <c r="F42" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G41" s="113" t="s">
+      <c r="G42" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H41" s="114" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B42" s="114" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C42" s="113" t="s">
+      <c r="H42" s="115" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B43" s="115" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C43" s="114" t="s">
         <v>327</v>
       </c>
-      <c r="D42" s="113">
+      <c r="D43" s="114">
         <v>0.2</v>
       </c>
-      <c r="E42" s="113">
+      <c r="E43" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F42" s="113">
+      <c r="F43" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="G42" s="113" t="s">
+      <c r="G43" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H42" s="114" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B43" s="114" t="s">
+      <c r="H43" s="115" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B44" s="115" t="s">
         <v>431</v>
       </c>
-      <c r="C43" s="113" t="s">
+      <c r="C44" s="114" t="s">
         <v>327</v>
       </c>
-      <c r="D43" s="113">
+      <c r="D44" s="114">
         <v>0.2</v>
       </c>
-      <c r="E43" s="113">
+      <c r="E44" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F43" s="113">
+      <c r="F44" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G43" s="113" t="s">
+      <c r="G44" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H43" s="114" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="51">
-      <c r="A44" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B44" s="114" t="s">
+      <c r="H44" s="115" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="51">
+      <c r="A45" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B45" s="115" t="s">
         <v>573</v>
       </c>
-      <c r="C44" s="113" t="s">
+      <c r="C45" s="114" t="s">
         <v>327</v>
       </c>
-      <c r="D44" s="113">
+      <c r="D45" s="114">
         <v>0.5</v>
       </c>
-      <c r="E44" s="113">
+      <c r="E45" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F44" s="113">
+      <c r="F45" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1.5</v>
       </c>
-      <c r="G44" s="113" t="s">
+      <c r="G45" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H44" s="114" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="25.5">
-      <c r="A45" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B45" s="114" t="s">
+      <c r="H45" s="115" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="25.5">
+      <c r="A46" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B46" s="115" t="s">
         <v>498</v>
       </c>
-      <c r="C45" s="113" t="s">
+      <c r="C46" s="114" t="s">
         <v>327</v>
       </c>
-      <c r="D45" s="113">
+      <c r="D46" s="114">
         <v>0</v>
       </c>
-      <c r="E45" s="113">
+      <c r="E46" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F45" s="113">
+      <c r="F46" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G45" s="113" t="s">
+      <c r="G46" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H45" s="114" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B46" s="114" t="s">
+      <c r="H46" s="115" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B47" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="113" t="s">
+      <c r="C47" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="D46" s="113">
+      <c r="D47" s="114">
         <v>0.5</v>
       </c>
-      <c r="E46" s="113">
+      <c r="E47" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="F46" s="113">
+      <c r="F47" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>2.5</v>
       </c>
-      <c r="G46" s="113" t="s">
+      <c r="G47" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H46" s="114" t="s">
+      <c r="H47" s="115" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B47" s="114" t="s">
+    <row r="48" spans="1:8">
+      <c r="A48" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B48" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="C47" s="113" t="s">
+      <c r="C48" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="D47" s="113">
+      <c r="D48" s="114">
         <v>0.5</v>
       </c>
-      <c r="E47" s="113">
+      <c r="E48" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="F47" s="113">
+      <c r="F48" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="G47" s="113" t="s">
+      <c r="G48" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H47" s="114" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B48" s="114" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C48" s="113" t="s">
+      <c r="H48" s="115" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B49" s="115" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C49" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="D48" s="113">
+      <c r="D49" s="114">
         <v>0.5</v>
       </c>
-      <c r="E48" s="113">
+      <c r="E49" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>2</v>
       </c>
-      <c r="F48" s="113">
+      <c r="F49" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
-      <c r="G48" s="113" t="s">
+      <c r="G49" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H48" s="114" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B49" s="114" t="s">
+      <c r="H49" s="115" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B50" s="115" t="s">
         <v>388</v>
       </c>
-      <c r="C49" s="113" t="s">
+      <c r="C50" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="D49" s="113">
+      <c r="D50" s="114">
         <v>0.33</v>
       </c>
-      <c r="E49" s="113">
+      <c r="E50" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F49" s="113">
+      <c r="F50" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1.32</v>
       </c>
-      <c r="G49" s="113" t="s">
+      <c r="G50" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H49" s="114" t="s">
+      <c r="H50" s="115" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B50" s="114" t="s">
+    <row r="51" spans="1:8">
+      <c r="A51" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B51" s="115" t="s">
         <v>573</v>
       </c>
-      <c r="C50" s="113" t="s">
+      <c r="C51" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="D50" s="113">
+      <c r="D51" s="114">
         <v>0.5</v>
       </c>
-      <c r="E50" s="113">
+      <c r="E51" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F50" s="113">
+      <c r="F51" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1.5</v>
       </c>
-      <c r="G50" s="113" t="s">
+      <c r="G51" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H50" s="114" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="38.25">
-      <c r="A51" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B51" s="114" t="s">
+      <c r="H51" s="115" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="38.25">
+      <c r="A52" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B52" s="115" t="s">
         <v>570</v>
       </c>
-      <c r="C51" s="113" t="s">
+      <c r="C52" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D51" s="113">
+      <c r="D52" s="114">
         <v>0.2</v>
       </c>
-      <c r="E51" s="113">
+      <c r="E52" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F51" s="113">
+      <c r="F52" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G51" s="113" t="s">
+      <c r="G52" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H51" s="114" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="38.25">
-      <c r="A52" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B52" s="114" t="s">
+      <c r="H52" s="115" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="38.25">
+      <c r="A53" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B53" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="113" t="s">
+      <c r="C53" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D52" s="113">
+      <c r="D53" s="114">
         <v>0.33</v>
       </c>
-      <c r="E52" s="113">
+      <c r="E53" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="F52" s="113">
+      <c r="F53" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.33</v>
       </c>
-      <c r="G52" s="113" t="s">
+      <c r="G53" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H52" s="114" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="25.5">
-      <c r="A53" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B53" s="114" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C53" s="113" t="s">
+      <c r="H53" s="115" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="25.5">
+      <c r="A54" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B54" s="115" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C54" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D53" s="113">
+      <c r="D54" s="114">
         <v>0.33</v>
       </c>
-      <c r="E53" s="113">
+      <c r="E54" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>2</v>
       </c>
-      <c r="F53" s="113">
+      <c r="F54" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.66</v>
       </c>
-      <c r="G53" s="113" t="s">
+      <c r="G54" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H53" s="114" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="51">
-      <c r="A54" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B54" s="114" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C54" s="113" t="s">
+      <c r="H54" s="115" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="51">
+      <c r="A55" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B55" s="115" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C55" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="D54" s="113">
+      <c r="D55" s="114">
         <v>0.2</v>
       </c>
-      <c r="E54" s="113">
+      <c r="E55" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F54" s="113">
+      <c r="F55" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="G54" s="113" t="s">
+      <c r="G55" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H54" s="114" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="38.25">
-      <c r="A55" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B55" s="114" t="s">
+      <c r="H55" s="115" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="38.25">
+      <c r="A56" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B56" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="C55" s="113" t="s">
+      <c r="C56" s="114" t="s">
         <v>402</v>
       </c>
-      <c r="D55" s="113">
+      <c r="D56" s="114">
         <v>0.33</v>
       </c>
-      <c r="E55" s="113">
+      <c r="E56" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="F55" s="113">
+      <c r="F56" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1.6500000000000001</v>
       </c>
-      <c r="G55" s="113" t="s">
+      <c r="G56" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H55" s="114" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="25.5">
-      <c r="A56" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B56" s="114" t="s">
+      <c r="H56" s="115" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="25.5">
+      <c r="A57" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B57" s="115" t="s">
         <v>388</v>
       </c>
-      <c r="C56" s="113" t="s">
+      <c r="C57" s="114" t="s">
         <v>402</v>
       </c>
-      <c r="D56" s="113">
+      <c r="D57" s="114">
         <v>0.33</v>
       </c>
-      <c r="E56" s="113">
+      <c r="E57" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F56" s="113">
+      <c r="F57" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1.32</v>
       </c>
-      <c r="G56" s="113" t="s">
+      <c r="G57" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H56" s="114" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="25.5">
-      <c r="A57" s="113" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B57" s="114" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C57" s="113" t="s">
+      <c r="H57" s="115" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="25.5">
+      <c r="A58" s="114" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B58" s="115" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C58" s="114" t="s">
         <v>402</v>
       </c>
-      <c r="D57" s="113">
+      <c r="D58" s="114">
         <v>0.33</v>
       </c>
-      <c r="E57" s="113">
+      <c r="E58" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F57" s="113">
+      <c r="F58" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1.32</v>
       </c>
-      <c r="G57" s="113" t="s">
+      <c r="G58" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H57" s="114" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="113" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B58" s="114" t="s">
+      <c r="H58" s="115" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="114" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B59" s="115" t="s">
         <v>495</v>
       </c>
-      <c r="C58" s="113" t="s">
+      <c r="C59" s="114" t="s">
         <v>309</v>
       </c>
-      <c r="D58" s="113">
+      <c r="D59" s="114">
         <v>0.33</v>
       </c>
-      <c r="E58" s="113">
+      <c r="E59" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F58" s="113">
+      <c r="F59" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.99</v>
       </c>
-      <c r="G58" s="113" t="s">
+      <c r="G59" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H58" s="114" t="s">
+      <c r="H59" s="115" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="113" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B59" s="114" t="s">
+    <row r="60" spans="1:8">
+      <c r="A60" s="114" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B60" s="115" t="s">
         <v>605</v>
       </c>
-      <c r="C59" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>309</v>
       </c>
-      <c r="D59" s="113">
+      <c r="D60" s="114">
         <v>0.33</v>
       </c>
-      <c r="E59" s="113">
+      <c r="E60" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F59" s="113">
+      <c r="F60" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.99</v>
       </c>
-      <c r="G59" s="113" t="s">
+      <c r="G60" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H59" s="114" t="s">
+      <c r="H60" s="115" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B60" s="114" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C60" s="113" t="s">
+    <row r="61" spans="1:8">
+      <c r="A61" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B61" s="115" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C61" s="114" t="s">
         <v>309</v>
       </c>
-      <c r="D60" s="113">
+      <c r="D61" s="114">
         <v>0.33</v>
       </c>
-      <c r="E60" s="113">
+      <c r="E61" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F60" s="113">
+      <c r="F61" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.99</v>
       </c>
-      <c r="G60" s="113" t="s">
+      <c r="G61" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H60" s="114" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="38.25">
-      <c r="A61" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B61" s="114" t="s">
+      <c r="H61" s="115" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="38.25">
+      <c r="A62" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B62" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="113" t="s">
+      <c r="C62" s="114" t="s">
         <v>363</v>
       </c>
-      <c r="D61" s="113">
+      <c r="D62" s="114">
         <v>0</v>
       </c>
-      <c r="E61" s="113">
+      <c r="E62" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="F61" s="113">
+      <c r="F62" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G61" s="113" t="s">
+      <c r="G62" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H61" s="114" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="25.5">
-      <c r="A62" s="113" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B62" s="114" t="s">
+      <c r="H62" s="115" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="25.5">
+      <c r="A63" s="114" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B63" s="115" t="s">
         <v>441</v>
       </c>
-      <c r="C62" s="113" t="s">
+      <c r="C63" s="114" t="s">
         <v>363</v>
       </c>
-      <c r="D62" s="113">
+      <c r="D63" s="114">
         <v>0</v>
       </c>
-      <c r="E62" s="113">
+      <c r="E63" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F62" s="113">
+      <c r="F63" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G62" s="113" t="s">
+      <c r="G63" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H62" s="114" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="25.5">
-      <c r="A63" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B63" s="114" t="s">
+      <c r="H63" s="115" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="25.5">
+      <c r="A64" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B64" s="115" t="s">
         <v>531</v>
       </c>
-      <c r="C63" s="113" t="s">
+      <c r="C64" s="114" t="s">
         <v>351</v>
       </c>
-      <c r="D63" s="113">
+      <c r="D64" s="114">
         <v>0</v>
       </c>
-      <c r="E63" s="113">
+      <c r="E64" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F63" s="113">
+      <c r="F64" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G63" s="113" t="s">
+      <c r="G64" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H63" s="114" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="113" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B64" s="114" t="s">
+      <c r="H64" s="115" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="114" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B65" s="115" t="s">
         <v>600</v>
       </c>
-      <c r="C64" s="113" t="s">
+      <c r="C65" s="114" t="s">
         <v>351</v>
       </c>
-      <c r="D64" s="113">
+      <c r="D65" s="114">
         <v>0.2</v>
       </c>
-      <c r="E64" s="113">
+      <c r="E65" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F64" s="113">
+      <c r="F65" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="G64" s="113" t="s">
+      <c r="G65" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H64" s="114" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B65" s="114" t="s">
+      <c r="H65" s="115" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B66" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="113" t="s">
+      <c r="C66" s="114" t="s">
         <v>313</v>
       </c>
-      <c r="D65" s="113">
+      <c r="D66" s="114">
         <v>0</v>
       </c>
-      <c r="E65" s="113">
+      <c r="E66" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="F65" s="113">
+      <c r="F66" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G65" s="113" t="s">
+      <c r="G66" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H65" s="114" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="113" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B66" s="114" t="s">
+      <c r="H66" s="115" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="114" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B67" s="115" t="s">
         <v>502</v>
       </c>
-      <c r="C66" s="113" t="s">
+      <c r="C67" s="114" t="s">
         <v>322</v>
       </c>
-      <c r="D66" s="113">
+      <c r="D67" s="114">
         <v>0</v>
       </c>
-      <c r="E66" s="113">
+      <c r="E67" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F66" s="113">
+      <c r="F67" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G66" s="113" t="s">
+      <c r="G67" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H66" s="114" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="25.5">
-      <c r="A67" s="113" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B67" s="114" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C67" s="113" t="s">
+      <c r="H67" s="115" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="25.5">
+      <c r="A68" s="114" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B68" s="115" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C68" s="114" t="s">
         <v>939</v>
       </c>
-      <c r="D67" s="113">
+      <c r="D68" s="114">
         <v>0</v>
       </c>
-      <c r="E67" s="113">
+      <c r="E68" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="F67" s="113">
+      <c r="F68" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G67" s="113" t="s">
+      <c r="G68" s="114" t="s">
         <v>673</v>
       </c>
-      <c r="H67" s="114" t="s">
-        <v>1280</v>
+      <c r="H68" s="115" t="s">
+        <v>1289</v>
       </c>
     </row>
   </sheetData>
@@ -17965,56 +18109,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1281</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1282</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="111" t="s">
         <v>746</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>747</v>
       </c>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="111" t="s">
         <v>748</v>
       </c>
-      <c r="E4" s="110" t="s">
+      <c r="E4" s="111" t="s">
         <v>749</v>
       </c>
-      <c r="F4" s="110" t="s">
+      <c r="F4" s="111" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="114" t="s">
         <v>363</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A5)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A5)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A5)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A5)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A5)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A5)</f>
         <v>8</v>
       </c>
-      <c r="C5" s="113">
+      <c r="C5" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A5),0.5)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="113">
+      <c r="D5" s="114">
         <f t="shared" ref="D5:D25" ca="1" si="0">B5+C5</f>
         <v>8</v>
       </c>
-      <c r="E5" s="113" t="str">
+      <c r="E5" s="114" t="str">
         <f t="shared" ref="E5:E25" ca="1" si="1">IF(D5&gt;20,"과다 점검",IF(D5&gt;=10,"충분",IF(D5&gt;=8,"하한",IF(D5&gt;=1,"보완 필요","미배치"))))</f>
         <v>하한</v>
       </c>
-      <c r="F5" s="114" t="s">
-        <v>1283</v>
+      <c r="F5" s="115" t="s">
+        <v>1292</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -18025,253 +18169,253 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="114" t="s">
         <v>351</v>
       </c>
-      <c r="B6" s="113">
+      <c r="B6" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A6)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A6)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A6)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A6)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A6)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A6)</f>
         <v>16</v>
       </c>
-      <c r="C6" s="113">
+      <c r="C6" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A6),0.5)</f>
         <v>1</v>
       </c>
-      <c r="D6" s="113">
+      <c r="D6" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="E6" s="113" t="str">
+      <c r="E6" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F6" s="114" t="s">
-        <v>1284</v>
+      <c r="F6" s="115" t="s">
+        <v>1293</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="B7" s="113">
+      <c r="B7" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A7)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A7)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A7)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A7)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A7)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A7)</f>
         <v>14</v>
       </c>
-      <c r="C7" s="113">
+      <c r="C7" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A7),0.5)</f>
         <v>3.5</v>
       </c>
-      <c r="D7" s="113">
+      <c r="D7" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>17.5</v>
       </c>
-      <c r="E7" s="113" t="str">
+      <c r="E7" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F7" s="114" t="s">
-        <v>1285</v>
+      <c r="F7" s="115" t="s">
+        <v>1294</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1286</v>
+        <v>1295</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1">
-      <c r="A8" s="113" t="s">
+      <c r="A8" s="114" t="s">
         <v>421</v>
       </c>
-      <c r="B8" s="113">
+      <c r="B8" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A8)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A8)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A8)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A8)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A8)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A8)</f>
         <v>3</v>
       </c>
-      <c r="C8" s="113">
+      <c r="C8" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A8),0.5)</f>
         <v>1.5</v>
       </c>
-      <c r="D8" s="113">
+      <c r="D8" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="E8" s="113" t="str">
+      <c r="E8" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
-      <c r="F8" s="114" t="s">
-        <v>1287</v>
+      <c r="F8" s="115" t="s">
+        <v>1296</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="114" t="s">
         <v>432</v>
       </c>
-      <c r="B9" s="113">
+      <c r="B9" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A9)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A9)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A9)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A9)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A9)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A9)</f>
         <v>3</v>
       </c>
-      <c r="C9" s="113">
+      <c r="C9" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A9),0.5)</f>
         <v>3</v>
       </c>
-      <c r="D9" s="113">
+      <c r="D9" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="E9" s="113" t="str">
+      <c r="E9" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
-      <c r="F9" s="114" t="s">
-        <v>1288</v>
+      <c r="F9" s="115" t="s">
+        <v>1297</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
-      <c r="A10" s="113" t="s">
+      <c r="A10" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="113">
+      <c r="B10" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A10)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A10)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A10)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A10)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A10)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A10)</f>
-        <v>10</v>
-      </c>
-      <c r="C10" s="113">
+        <v>13</v>
+      </c>
+      <c r="C10" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A10),0.5)</f>
         <v>5</v>
       </c>
-      <c r="D10" s="113">
+      <c r="D10" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E10" s="113" t="str">
+        <v>18</v>
+      </c>
+      <c r="E10" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F10" s="114" t="s">
-        <v>1289</v>
+      <c r="F10" s="115" t="s">
+        <v>1298</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
-      <c r="A11" s="113" t="s">
+      <c r="A11" s="114" t="s">
         <v>327</v>
       </c>
-      <c r="B11" s="113">
+      <c r="B11" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A11)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A11)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A11)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A11)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A11)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A11)</f>
         <v>3</v>
       </c>
-      <c r="C11" s="113">
+      <c r="C11" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A11),0.5)</f>
         <v>3</v>
       </c>
-      <c r="D11" s="113">
+      <c r="D11" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="E11" s="113" t="str">
+      <c r="E11" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
-      <c r="F11" s="114" t="s">
-        <v>1290</v>
+      <c r="F11" s="115" t="s">
+        <v>1299</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="114" t="s">
         <v>443</v>
       </c>
-      <c r="B12" s="113">
+      <c r="B12" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A12)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A12)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A12)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A12)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A12)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A12)</f>
         <v>6</v>
       </c>
-      <c r="C12" s="113">
+      <c r="C12" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A12),0.5)</f>
         <v>6</v>
       </c>
-      <c r="D12" s="113">
+      <c r="D12" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="E12" s="113" t="str">
+      <c r="E12" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F12" s="114" t="s">
-        <v>1291</v>
+      <c r="F12" s="115" t="s">
+        <v>1300</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="114" t="s">
         <v>368</v>
       </c>
-      <c r="B13" s="113">
+      <c r="B13" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A13)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A13)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A13)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A13)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A13)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A13)</f>
         <v>10</v>
       </c>
-      <c r="C13" s="113">
+      <c r="C13" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A13),0.5)</f>
         <v>2</v>
       </c>
-      <c r="D13" s="113">
+      <c r="D13" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="E13" s="113" t="str">
+      <c r="E13" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F13" s="114" t="s">
-        <v>1292</v>
+      <c r="F13" s="115" t="s">
+        <v>1301</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
-      <c r="A14" s="113" t="s">
+      <c r="A14" s="114" t="s">
         <v>372</v>
       </c>
-      <c r="B14" s="113">
+      <c r="B14" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A14)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A14)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A14)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A14)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A14)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A14)</f>
         <v>10</v>
       </c>
-      <c r="C14" s="113">
-        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A14),0.5)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="113">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E14" s="113" t="str">
-        <f t="shared" si="1"/>
+      <c r="C14" s="114">
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A14),0.5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="D14" s="114">
+        <f t="shared" ca="1" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="E14" s="114" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F14" s="114" t="s">
-        <v>1293</v>
+      <c r="F14" s="115" t="s">
+        <v>1302</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="114" t="s">
         <v>383</v>
       </c>
-      <c r="B15" s="113">
+      <c r="B15" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A15)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A15)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A15)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A15)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A15)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A15)</f>
         <v>12</v>
       </c>
-      <c r="C15" s="113">
+      <c r="C15" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A15),0.5)</f>
         <v>1.5</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="E15" s="113" t="str">
+      <c r="E15" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F15" s="114" t="s">
-        <v>1294</v>
+      <c r="F15" s="115" t="s">
+        <v>1303</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1295</v>
+        <v>1304</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18279,256 +18423,256 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
-      <c r="A16" s="113" t="s">
+      <c r="A16" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="B16" s="113">
+      <c r="B16" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A16)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A16)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A16)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A16)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A16)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A16)</f>
         <v>10</v>
       </c>
-      <c r="C16" s="113">
+      <c r="C16" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A16),0.5)</f>
         <v>2.5</v>
       </c>
-      <c r="D16" s="113">
+      <c r="D16" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="E16" s="113" t="str">
+      <c r="E16" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F16" s="114" t="s">
-        <v>1296</v>
+      <c r="F16" s="115" t="s">
+        <v>1305</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="114" t="s">
         <v>389</v>
       </c>
-      <c r="B17" s="113">
+      <c r="B17" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A17)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A17)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A17)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A17)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A17)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A17)</f>
         <v>7</v>
       </c>
-      <c r="C17" s="113">
+      <c r="C17" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A17),0.5)</f>
         <v>7</v>
       </c>
-      <c r="D17" s="113">
+      <c r="D17" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="E17" s="113" t="str">
+      <c r="E17" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F17" s="114" t="s">
-        <v>1297</v>
+      <c r="F17" s="115" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="113" t="s">
+      <c r="A18" s="114" t="s">
         <v>407</v>
       </c>
-      <c r="B18" s="113">
+      <c r="B18" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A18)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A18)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A18)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A18)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A18)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A18)</f>
         <v>11</v>
       </c>
-      <c r="C18" s="113">
+      <c r="C18" s="114">
         <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A18),0.5)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="114">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E18" s="113" t="str">
+      <c r="E18" s="114" t="str">
         <f t="shared" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F18" s="114" t="s">
-        <v>1298</v>
+      <c r="F18" s="115" t="s">
+        <v>1307</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="114" t="s">
         <v>322</v>
       </c>
-      <c r="B19" s="113">
+      <c r="B19" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A19)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A19)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A19)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A19)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A19)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A19)</f>
         <v>6</v>
       </c>
-      <c r="C19" s="113">
+      <c r="C19" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A19),0.5)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="113">
+      <c r="D19" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="E19" s="113" t="str">
+      <c r="E19" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
-      <c r="F19" s="114" t="s">
-        <v>1299</v>
+      <c r="F19" s="115" t="s">
+        <v>1308</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="114" t="s">
         <v>283</v>
       </c>
-      <c r="B20" s="113">
+      <c r="B20" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A20)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A20)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A20)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A20)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A20)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A20)</f>
         <v>9</v>
       </c>
-      <c r="C20" s="113">
+      <c r="C20" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A20),0.5)</f>
         <v>7.5</v>
       </c>
-      <c r="D20" s="113">
+      <c r="D20" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>16.5</v>
       </c>
-      <c r="E20" s="113" t="str">
+      <c r="E20" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F20" s="114" t="s">
-        <v>1300</v>
+      <c r="F20" s="115" t="s">
+        <v>1309</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="B21" s="113">
+      <c r="B21" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A21)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A21)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A21)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A21)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A21)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A21)</f>
         <v>9</v>
       </c>
-      <c r="C21" s="113">
+      <c r="C21" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A21),0.5)</f>
         <v>7.5</v>
       </c>
-      <c r="D21" s="113">
+      <c r="D21" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>16.5</v>
       </c>
-      <c r="E21" s="113" t="str">
+      <c r="E21" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F21" s="114" t="s">
-        <v>1301</v>
+      <c r="F21" s="115" t="s">
+        <v>1310</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="114" t="s">
         <v>309</v>
       </c>
-      <c r="B22" s="113">
+      <c r="B22" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A22)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A22)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A22)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A22)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A22)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A22)</f>
         <v>9</v>
       </c>
-      <c r="C22" s="113">
+      <c r="C22" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A22),0.5)</f>
         <v>3</v>
       </c>
-      <c r="D22" s="113">
+      <c r="D22" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="E22" s="113" t="str">
+      <c r="E22" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F22" s="114" t="s">
-        <v>1302</v>
+      <c r="F22" s="115" t="s">
+        <v>1311</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="114" t="s">
         <v>313</v>
       </c>
-      <c r="B23" s="113">
+      <c r="B23" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A23)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A23)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A23)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A23)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A23)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A23)</f>
         <v>6</v>
       </c>
-      <c r="C23" s="113">
+      <c r="C23" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A23),0.5)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="113">
+      <c r="D23" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="E23" s="113" t="str">
+      <c r="E23" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
-      <c r="F23" s="114" t="s">
-        <v>1303</v>
+      <c r="F23" s="115" t="s">
+        <v>1312</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
-      <c r="A24" s="113" t="s">
+      <c r="A24" s="114" t="s">
         <v>402</v>
       </c>
-      <c r="B24" s="113">
+      <c r="B24" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A24)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A24)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A24)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A24)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A24)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A24)</f>
         <v>8</v>
       </c>
-      <c r="C24" s="113">
+      <c r="C24" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A24),0.5)</f>
         <v>4.5</v>
       </c>
-      <c r="D24" s="113">
+      <c r="D24" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="E24" s="113" t="str">
+      <c r="E24" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
-      <c r="F24" s="114" t="s">
-        <v>1304</v>
+      <c r="F24" s="115" t="s">
+        <v>1313</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
-      <c r="A25" s="113" t="s">
+      <c r="A25" s="114" t="s">
         <v>939</v>
       </c>
-      <c r="B25" s="113">
+      <c r="B25" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A25)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A25)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A25)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A25)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A25)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A25)</f>
         <v>6</v>
       </c>
-      <c r="C25" s="113">
+      <c r="C25" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A25),0.5)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="113">
+      <c r="D25" s="114">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="E25" s="113" t="str">
+      <c r="E25" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
-      <c r="F25" s="114" t="s">
-        <v>1305</v>
+      <c r="F25" s="115" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="107" t="s">
         <v>773</v>
       </c>
-      <c r="B26" s="115">
+      <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>176</v>
-      </c>
-      <c r="D26" s="115">
+        <v>179</v>
+      </c>
+      <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>234.5</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -18538,182 +18682,182 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1306</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1307</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1308</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1311</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1312</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1316</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1320</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1321</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1322</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1323</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1324</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1325</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1326</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1327</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1328</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1329</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1330</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1331</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1332</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="107" t="s">
-        <v>1334</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>1335</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1336</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1337</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1338</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1339</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1340</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1341</v>
+        <v>1350</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4FE98431F553776E9BA9B565A2E40611C52B1BB6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2B26BDFD7D6256D6848844A04A6B0007F7B0B17E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,11 +29,11 @@
     <sheet name="9월이후조정" sheetId="14" r:id="rId14"/>
     <sheet name="복귀_주간계획" sheetId="15" r:id="rId15"/>
     <sheet name="복귀_토_하체전면" sheetId="16" r:id="rId16"/>
-    <sheet name="복귀_일_등광배" sheetId="17" r:id="rId17"/>
+    <sheet name="복귀_일_당기기A" sheetId="17" r:id="rId17"/>
     <sheet name="복귀_월_가슴" sheetId="18" r:id="rId18"/>
     <sheet name="복귀_화_팔" sheetId="19" r:id="rId19"/>
     <sheet name="복귀_수_하체후면" sheetId="20" r:id="rId20"/>
-    <sheet name="복귀_목_등승모" sheetId="21" r:id="rId21"/>
+    <sheet name="복귀_목_당기기B" sheetId="21" r:id="rId21"/>
     <sheet name="복귀_증량원칙" sheetId="22" r:id="rId22"/>
     <sheet name="복귀_간접계수맵" sheetId="23" r:id="rId23"/>
     <sheet name="복귀_세트검산" sheetId="24" r:id="rId24"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="1359">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -2809,25 +2809,25 @@
     <t>하체 전면(사두) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 100분</t>
-  </si>
-  <si>
-    <t>스쿼트 5×5가 앞, 어깨 블록이 4~7번(프레스 · 레터럴 · 리버스 펙덱 · 페이스풀). 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 레그 컬 · 이너 · 아우터 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다 — 햄스트링 중량은 이 날이 가장 잘 나온다</t>
+    <t>약 95분</t>
+  </si>
+  <si>
+    <t>스쿼트 5×5가 앞, 어깨 블록이 4~6번(프레스 · 레터럴 · 리버스 펙덱). 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 레그 컬 · 이너 · 아우터 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다 — 햄스트링 중량은 이 날이 가장 잘 나온다</t>
   </si>
   <si>
     <t>일</t>
   </si>
   <si>
-    <t>등 A</t>
-  </si>
-  <si>
-    <t>등(광배) · 팔 삼두/이두</t>
-  </si>
-  <si>
-    <t>약 60분</t>
-  </si>
-  <si>
-    <t>메인 리프트 없음. 당기기 14세트 뒤 팔 6 — 프레스가 하나도 없어 삼두 간접이 0인 유일한 날</t>
+    <t>당기기 A</t>
+  </si>
+  <si>
+    <t>등 수직 당기기 · 팔 삼두/이두</t>
+  </si>
+  <si>
+    <t>약 69분</t>
+  </si>
+  <si>
+    <t>메인 리프트 없음. 당기기 18세트 뒤 팔 6 — 프레스가 하나도 없어 삼두 간접이 0인 유일한 날. 척추로 버티는 유일한 로우(스미스 바벨 로우)와 페이스풀이 이 날에 있다</t>
   </si>
   <si>
     <t>월</t>
@@ -2842,7 +2842,7 @@
     <t>약 59분</t>
   </si>
   <si>
-    <t>벤치 5×5가 앞. 전면 삼각은 밀기 간접으로 6.5세트치가 차므로 어깨 블록에 프레스를 얹지 않는다</t>
+    <t>벤치 5×5가 앞. 전면 삼각은 밀기 간접으로 6세트치가 차므로 어깨 블록에 프레스를 얹지 않는다</t>
   </si>
   <si>
     <t>화</t>
@@ -2878,16 +2878,16 @@
     <t>목</t>
   </si>
   <si>
-    <t>등 B + 가슴 B</t>
-  </si>
-  <si>
-    <t>등(승모 · 능형) · 가슴(중하부) · 팔</t>
-  </si>
-  <si>
-    <t>약 67분</t>
-  </si>
-  <si>
-    <t>세 블록. 데드 다음날이라 로우를 전부 궤도 고정 · 체스트 서포티드로 골랐다</t>
+    <t>당기기 B + 가슴 B</t>
+  </si>
+  <si>
+    <t>등 수평 당기기 · 가슴(중하부) · 팔</t>
+  </si>
+  <si>
+    <t>약 64분</t>
+  </si>
+  <si>
+    <t>세 블록. 데드 다음날이라 로우를 전부 체스트 서포티드 · 궤도 고정 · 편측 케이블로 골랐다 — 척추로 버티는 로우는 일요일에 있다</t>
   </si>
   <si>
     <t>금</t>
@@ -2908,13 +2908,22 @@
     <t>· 어깨는 토 · 월 · 수, 팔은 일 · 화 · 목. 이틀 간격으로 정확히 엇갈려 어느 쪽도 이틀 연속이 되지 않는다.</t>
   </si>
   <si>
-    <t>· 큰 부위 셋을 둘로 쪼갰다 — 하체는 전면(토) / 후면(수), 등은 광배(일) / 승모 · 능형(목), 가슴은 상부(월) / 중하부(목).</t>
-  </si>
-  <si>
-    <t>· 쪼갠 축은 근육군이지 움직임 평면이 아니다. 2026-09-04에 '주동근은 그립 폭이 아니라 팔꿈치 경로가 정한다'로 바꾼 그 원칙을 그대로 쓴다. 그래서 수평 당기기인 원암 케이블 로우가 광배 날(일)에 있고, 발 높은 레그 프레스가 햄스트링이 아니라 둔근으로 계상된다.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02 보강] 햄스트링도 주 2회로 쪼갰다 — 수요일 7(루마니안 3 · 레그 컬 4) + 토요일 3(원 레그 컬). 사두만 주 1회로 남는데 스쿼트 5×5가 한 날을 다 쓰기 때문이다. 대신 수요일 레그 프레스가 사두에 간접 1.5세트치를 얹어 노출은 주 2회가 됐다.</t>
+    <t>· 큰 부위 셋을 둘로 쪼갰다 — 하체는 전면(토) / 후면(수), 등은 수직(일) / 수평(목), 가슴은 상부(월) / 중하부(목).</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 정정] 등을 가른 축은 움직임 평면이다 — 재택 1일차 '당기기 A (수직)' · 6일차 '당기기 B (수평)'과 같다(사용자 지정). 초안에서는 근육군으로 갈랐고(일=광배 전담 · 목=승모중부 전담) 그 근거로 2026-09-04 '주동근은 팔꿈치 경로가 정한다'를 들었는데, 그 원칙은 세트검산의 근육군 분류 규칙이고 날을 어떻게 가르라는 말이 아니었다 — 두 축을 뒤섞은 것이다.</t>
+  </si>
+  <si>
+    <t>· 평면 분할이 실제로 더 맞다. 근육군으로 가르면 '광배 주 1회'로 적히지만 목요일 로우 셋이 전부 광배를 쓴다(간접계수맵에 광배 0.5가 달려 있다) — 어느 쪽도 쉬지 못하면서 장부상으로만 주 1회가 된다. 평면으로 가르면 어깨 신전 ↔ 수평 외전 + 견갑 후인이라는 실제로 다른 관절 동작이 갈린다.</t>
+  </si>
+  <si>
+    <t>· 그래서 두 날 모두 광배와 승모 중부가 섞여 있다 — 광배 일 11 / 목 3 · 승모 중부 일 7 / 목 6. 재택도 같은 모양이다(광배 9/4 · 승모 중부 7/8). 근육군은 여전히 팔꿈치 경로로 매긴다 — 날 분할과 근육군 분류는 다른 축이고 둘을 섞지 않는다. 발 높은 레그 프레스가 햄스트링이 아니라 둔근으로 계상되는 것이 후자의 예다.</t>
+  </si>
+  <si>
+    <t>· 재택이 바벨 로우를 수직 날에 두는 것까지 따랐다 — 승모 중부를 두 날에 고르게 나누기 때문이고, 복귀에서는 이득이 하나 더 붙는다: 척추로 버티는 유일한 로우가 데드 다음날(목)에서 빠진다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 보강] 햄스트링도 주 2회로 쪼갰다 — 토요일 4(레그 컬) + 수요일 6(루마니안 3 · 원 레그 컬 3). 사두만 주 1회로 남는데 스쿼트 5×5가 한 날을 다 쓰기 때문이다. 대신 수요일 레그 프레스가 사두에 간접 1.5세트치를 얹어 노출은 주 2회가 됐다.</t>
   </si>
   <si>
     <t>· 금요일만 쉰다. 쉬는 날을 스쿼트 앞에 두는 것이 여섯 날 중 가장 값이 큰 자리다.</t>
@@ -2929,7 +2938,10 @@
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
   </si>
   <si>
-    <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). ④ 토요일 페이스풀 3 — 승모 중부 · 능형근이 주 1회로 남아 있던 것을 주 2회로 쪼갰고, 어깨 보조가 전부 외전인 날에 견갑 후인 · 외회전을 더했다. 164 → 168 → 176 → 179.</t>
+    <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). ④ 페이스풀 3 — 승모 중부 · 능형근에 견갑 후인 · 외회전을 더했다. 토요일에 넣었다가 같은 날 일요일(당기기 수직)로 옮겼다 — 재택도 당기기 날에 둔다. 164 → 168 → 176 → 179.</t>
+  </si>
+  <si>
+    <t>· ⑤ 같은 날 등 분할 축을 근육군 → 움직임 평면(수직 / 수평)으로 정정했다. 세트 총량 179와 부위별 숫자는 하나도 안 바뀌고 날 배치만 바뀌었다 — 원암 케이블 로우 일 → 목 · 스미스 바벨 로우 목 → 일.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -2980,16 +2992,16 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 토 41세트 100분 · 수 39세트 98분 · 목 27세트 67분 · 화 27세트 48분 · 일 23세트 60분 · 월 22세트 59분.</t>
-  </si>
-  <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 29를 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
+    <t>· 수 39세트 98분 · 토 38세트 95분 · 일 27세트 69분 · 화 27세트 48분 · 목 26세트 64분 · 월 22세트 59분.</t>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
   </si>
   <si>
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 주 433분 = 7시간 13분. 주 4회 370분에서 63분 늘었다. 토(100) · 수(98)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 주 433분 = 7시간 13분. 주 4회 370분에서 63분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3016,7 +3028,7 @@
     <t>웜업 — 회전근개 (세트 카운트 제외 · 어깨 블록 직전에)</t>
   </si>
   <si>
-    <t>· 스쿼트 램프와 따로다. 하체 3종목을 끝내고 어깨 블록(4번)에 들어가기 직전에 넣는다 — 그래야 식지 않는다.</t>
+    <t>· 스쿼트 램프와 따로다. 하체 3종목을 끝내고 어깨 블록(4~6번)에 들어가기 직전에 넣는다 — 그래야 식지 않는다.</t>
   </si>
   <si>
     <t>· 케이블 외회전 2세트 × 12~15회. 팔꿈치 90도로 접어 옆구리에 붙이고 바깥으로만 회전. 매우 가볍게 — 2.5~5kg. 무거우면 광배와 후면 삼각근이 대신 일하며 목적을 잃는다.</t>
@@ -3055,613 +3067,619 @@
     <t>리버스 펙덱</t>
   </si>
   <si>
-    <t>후면 삼각. 월요일 케이블 리버스 플라이와 저항곡선이 갈린다 — 머신은 중간 구간, 케이블은 수축 끝단. 팔을 편 채 수평 외전만 하므로 견갑 후인 · 외회전은 다음 종목(페이스풀)이 맡는다.</t>
+    <t>후면 삼각. 월요일 케이블 리버스 플라이와 저항곡선이 갈린다 — 머신은 중간 구간, 케이블은 수축 끝단. 팔을 편 채 수평 외전만 한다 — 견갑 후인 · 외회전은 일요일 페이스풀이 맡는다.</t>
   </si>
   <si>
     <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
   </si>
   <si>
-    <t>[2026-10-02 사용자 제안] 승모 중부 · 능형근이 주 1회(목요일 10세트)로 남아 있었다 — 다른 큰 부위는 전부 주 2회로 쪼갰는데 여기만 안 쪼개져 있었다. 이 3세트로 주 2회가 된다. 어깨 보조 11세트가 전부 외전 · 수평 외전인 날에 견갑 후인 + 외회전을 동시에 하는 유일한 종목이기도 하다. 로프를 얼굴 높이로 당기고 팔꿈치를 어깨선 위로 — 끝에서 외회전을 만든다. 재택 1일차와 같은 등급 · 같은 계수.</t>
+    <t>[2026-10-02 추가 — 사용자 지적, 같은 날 수요일 원 레그 컬과 자리 교환] 전면 하체만 12세트인 날에 햄스트링이 0이었다. 이 4세트로 햄스트링이 주 1회 → 2회가 된다(여기 4 + 수요일 6). 이 날이 중량을 밀기에 가장 좋은 자리다 — 토요일엔 햄스트링을 직접 쓰는 종목이 하나도 없어 누적 24세트를 지나도 햄스트링 자체는 국소로 신선하다. 중량은 전신 피로가 아니라 국소 피로가 정한다. 그래서 후반 고립 블록의 첫 자리를 줬다.</t>
+  </si>
+  <si>
+    <t>시티드 레그 컬 (고관절이 굽어 늘어난 구간) / 라잉 레그 컬 / 노르딕 햄 컬 (맨몸)</t>
+  </si>
+  <si>
+    <t>아우터와 슈퍼세트. 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
+  </si>
+  <si>
+    <t>와이드 스탠스 레그 프레스 / 케이블 어덕션</t>
+  </si>
+  <si>
+    <t>관상면 외전. 어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤로 보냈다.</t>
+  </si>
+  <si>
+    <t>힙 어브덕션 머신 (겸용 머신이 없을 때) / 케이블 힙 외전</t>
+  </si>
+  <si>
+    <t>앉아서 하는 쪽 — 무릎이 굽어 가자미근 비중이 커진다. 수요일 스탠딩과 각도를 나눈다.</t>
+  </si>
+  <si>
+    <t>스탠딩 카프 레이즈 머신 / 레그 프레스 카프 레이즈</t>
+  </si>
+  <si>
+    <t>[배치 이유]</t>
+  </si>
+  <si>
+    <t>· 어깨 · 팔을 세션 후반부에 두는 것이 이 개편의 전제다 (2026-10-02 사용자 지정). 큰 부위를 신선할 때 먼저 치고, 어깨 · 팔은 그 뒤에 붙인다.</t>
+  </si>
+  <si>
+    <t>· 하체를 전면 · 후면으로 갈라 토요일이 사두 전담이 됐다. 스쿼트 · 레그 프레스 · 익스텐션 12세트로 사두 주간 세트가 한 날에 다 들어간다.</t>
+  </si>
+  <si>
+    <t>· 어깨 블록을 4~6번에 둔 이유 — 레그 컬 · 이너 · 아우터 타이 · 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 15세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
+  </si>
+  <si>
+    <t>· 토요일에 어깨 세 방향(전 · 측 · 후)을 다 넣는 것이 사용자 지정이다. 전면은 머신 숄더, 측면은 덤벨 레터럴, 후면은 리버스 펙덱. 페이스풀은 2026-10-02에 여기 넣었다가 같은 날 일요일(당기기 수직)로 옮겼다 — 재택도 페이스풀을 당기기 날에 둔다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02] 햄스트링 4세트를 더했다. 사두는 스쿼트 5×5 때문에 쪼갤 수 없어 주 1회지만 햄스트링은 쪼갤 수 있고, 전면 하체 날에 햄스트링이 0이면 무릎을 한쪽으로만 때리는 날이 된다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 같은 날 교환] 처음엔 원 레그 컬 3을 뒀는데 사용자 제안으로 수요일 양측 레그 컬과 바꿨다. 토요일엔 햄스트링을 직접 쓰는 종목이 없어 국소로 신선하므로 중량 종목(양측)이 맞고, 편측은 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 둘 다 반대로 놓여 있었다.</t>
+  </si>
+  <si>
+    <t>· 38세트 · 약 95분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 레그 컬 · 이너 · 아우터 · 카프 26세트)은 예외로 본다 — 실질 12세트다.</t>
+  </si>
+  <si>
+    <t>· 여섯 날 중 둘째로 크다. 그래도 주 4회 시절 토요일(43세트 · 107분)보다는 작다.</t>
+  </si>
+  <si>
+    <t>· 웜업은 별도다. 스쿼트가 있는 날이므로 10~15분을 더 잡는다.</t>
+  </si>
+  <si>
+    <t>드롭 세트 (2026-10-02)</t>
+  </si>
+  <si>
+    <t>· 레그 익스텐션 +75초 · 레터럴 +60초 · 리버스 펙덱 +60초 · 레그 컬 +75초. 마지막 세트에만 2단. 레그 컬 드롭은 2026-10-02 자리 교환 때 종목을 따라 수요일에서 옮겨 왔다.</t>
+  </si>
+  <si>
+    <t>· 이너 · 아우터 타이에는 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다.</t>
+  </si>
+  <si>
+    <t>· N열 '드롭(초)'는 마지막 세트에 더해지는 시간이다. I열 종목 분에 합산되고, 앱 타이머는 마지막 세트를 그만큼 늘린 뒤 '드롭세트'라고 읊는다. E열 세트 수와 복귀_세트검산은 건드리지 않는다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???  /  아 원 레그 컬이랑 토요일 레그컬 자리 바꾸는거 어떻게 생각해?  /  토요일 페이스풀 넣는게 안 낫겠나?</t>
+  </si>
+  <si>
+    <t>일요일 — 당기기 A (수직) · 팔</t>
+  </si>
+  <si>
+    <t>웜업 (세트 카운트 제외)</t>
+  </si>
+  <si>
+    <t>· 이 날은 증량을 추적하는 메인 리프트가 없다. 첫 종목(친업) 전에 랫풀다운 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
+  </si>
+  <si>
+    <t>· 둘 다 근비대 항목이 아니라 관절 준비 항목이므로 세트 합계에 넣지 않는다.</t>
+  </si>
+  <si>
+    <t>수직 당기기 중 가장 무거운 쪽이라 맨 앞에 둔다. 그립이 지치면 주저 말고 어시스트 머신으로 간다 — 이 날 뒤쪽에 당기기가 10세트 더 있다.</t>
+  </si>
+  <si>
+    <t>어시스트 풀업 머신 (1순위 — 그립 부담 ↓) / 랫풀다운 / 뉴트럴 그립 친업</t>
+  </si>
+  <si>
+    <t>135/145/155/165</t>
+  </si>
+  <si>
+    <t>와이드 오버그립 랫풀다운</t>
+  </si>
+  <si>
+    <t>넓은 엎침 그립 — 팔꿈치가 몸에서 벌어진 경로로 들어온다. 이두 관여가 가장 적은 수직 당기기다.</t>
+  </si>
+  <si>
+    <t>오버그립 랫풀다운 (어깨너비 — 어깨가 불편할 때) / 풀업</t>
+  </si>
+  <si>
+    <t>랫풀다운(언더그립 좁게 안쪽으로)</t>
+  </si>
+  <si>
+    <t>짧고 깊은 쪽 — 뒤침 그립으로 좁게 잡아 어깨 신전 구간을 끝까지 쓴다. 이두 계수 0.5가 붙는 자리다.</t>
+  </si>
+  <si>
+    <t>뉴트럴 그립 랫풀다운 / 어시스트 풀업 머신</t>
+  </si>
+  <si>
+    <t>스미스 바벨 로우(오버그립)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 목요일에서 이동] 재택도 바벨 로우를 수직 날(1일차)에 둔다 — 승모 중부를 두 날에 7/6으로 고르게 나누기 때문이다. 복귀에서는 보너스가 하나 더 붙는다: 척추 부하가 있는 유일한 로우가 데드 다음날(목)에서 빠진다. 궤도가 고정돼 상체 각도를 기립근으로 버티지 않아도 된다.</t>
+  </si>
+  <si>
+    <t>티바 로우 / 해머 스트랭스 로우 (허리가 무거운 주) / 체스트 서포티드 로우</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 제안 · 토요일에서 이동] 재택도 페이스풀을 당기기 날(1일차)에 둔다. 로프를 얼굴 높이로 당기고 팔꿈치를 어깨선 위로 — 끝에서 외회전을 만든다. 당기기 15세트가 전부 어깨 신전 · 수평 외전인데 외회전을 같이 하는 종목은 이것뿐이다. 후면삼각에 0.5 간접이 붙는다.</t>
   </si>
   <si>
     <t>리어 델트 로우 (로프) / 케이블 리버스 플라이 (팔 편 채) / 리버스 펙덱</t>
   </si>
   <si>
-    <t>[2026-10-02 추가 — 사용자 지적, 같은 날 수요일 원 레그 컬과 자리 교환] 전면 하체만 12세트인 날에 햄스트링이 0이었다. 이 4세트로 햄스트링이 주 1회 → 2회가 된다(여기 4 + 수요일 6). 이 날이 중량을 밀기에 가장 좋은 자리다 — 토요일엔 햄스트링을 직접 쓰는 종목이 하나도 없어 누적 24세트를 지나도 햄스트링 자체는 국소로 신선하다. 중량은 전신 피로가 아니라 국소 피로가 정한다. 그래서 후반 고립 블록의 첫 자리를 줬다.</t>
-  </si>
-  <si>
-    <t>시티드 레그 컬 (고관절이 굽어 늘어난 구간) / 라잉 레그 컬 / 노르딕 햄 컬 (맨몸)</t>
-  </si>
-  <si>
-    <t>아우터와 슈퍼세트. 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
-  </si>
-  <si>
-    <t>와이드 스탠스 레그 프레스 / 케이블 어덕션</t>
-  </si>
-  <si>
-    <t>관상면 외전. 어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤로 보냈다.</t>
-  </si>
-  <si>
-    <t>힙 어브덕션 머신 (겸용 머신이 없을 때) / 케이블 힙 외전</t>
-  </si>
-  <si>
-    <t>앉아서 하는 쪽 — 무릎이 굽어 가자미근 비중이 커진다. 수요일 스탠딩과 각도를 나눈다.</t>
-  </si>
-  <si>
-    <t>스탠딩 카프 레이즈 머신 / 레그 프레스 카프 레이즈</t>
-  </si>
-  <si>
-    <t>[배치 이유]</t>
-  </si>
-  <si>
-    <t>· 어깨 · 팔을 세션 후반부에 두는 것이 이 개편의 전제다 (2026-10-02 사용자 지정). 큰 부위를 신선할 때 먼저 치고, 어깨 · 팔은 그 뒤에 붙인다.</t>
-  </si>
-  <si>
-    <t>· 하체를 전면 · 후면으로 갈라 토요일이 사두 전담이 됐다. 스쿼트 · 레그 프레스 · 익스텐션 12세트로 사두 주간 세트가 한 날에 다 들어간다.</t>
-  </si>
-  <si>
-    <t>· 어깨 블록을 4~7번에 둔 이유 — 레그 컬 · 이너 · 아우터 타이 · 카프는 어깨와 경쟁하지 않는 고립이라 뒤로 보냈다. 어깨가 세션 맨 끝에 오면 하체 고립 15세트를 더 지나야 하고, 그 자리에서는 레터럴 중량이 먼저 떨어진다.</t>
-  </si>
-  <si>
-    <t>· 토요일에 어깨 세 방향(전 · 측 · 후)을 다 넣는 것이 사용자 지정이다. 전면은 머신 숄더, 측면은 덤벨 레터럴, 후면은 리버스 펙덱, 그리고 2026-10-02부터 견갑 후인 · 외회전을 페이스풀이 맡는다.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02] 햄스트링 4세트를 더했다. 사두는 스쿼트 5×5 때문에 쪼갤 수 없어 주 1회지만 햄스트링은 쪼갤 수 있고, 전면 하체 날에 햄스트링이 0이면 무릎을 한쪽으로만 때리는 날이 된다.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02 같은 날 교환] 처음엔 원 레그 컬 3을 뒀는데 사용자 제안으로 수요일 양측 레그 컬과 바꿨다. 토요일엔 햄스트링을 직접 쓰는 종목이 없어 국소로 신선하므로 중량 종목(양측)이 맞고, 편측은 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 둘 다 반대로 놓여 있었다.</t>
-  </si>
-  <si>
-    <t>· 41세트 · 약 100분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 페이스풀 · 레그 컬 · 이너 · 아우터 · 카프 29세트)은 예외로 본다 — 실질 12세트다.</t>
-  </si>
-  <si>
-    <t>· 여섯 날 중 가장 크다. 그래도 주 4회 시절 토요일(43세트 · 107분) · 일요일(44세트 · 121분)보다는 작다.</t>
-  </si>
-  <si>
-    <t>· 웜업은 별도다. 스쿼트가 있는 날이므로 10~15분을 더 잡는다.</t>
-  </si>
-  <si>
-    <t>드롭 세트 (2026-10-02)</t>
-  </si>
-  <si>
-    <t>· 레그 익스텐션 +75초 · 레터럴 +60초 · 리버스 펙덱 +60초 · 레그 컬 +75초. 마지막 세트에만 2단. 레그 컬 드롭은 2026-10-02 자리 교환 때 종목을 따라 수요일에서 옮겨 왔다.</t>
-  </si>
-  <si>
-    <t>· 이너 · 아우터 타이에는 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다.</t>
-  </si>
-  <si>
-    <t>· N열 '드롭(초)'는 마지막 세트에 더해지는 시간이다. I열 종목 분에 합산되고, 앱 타이머는 마지막 세트를 그만큼 늘린 뒤 '드롭세트'라고 읊는다. E열 세트 수와 복귀_세트검산은 건드리지 않는다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???  /  아 원 레그 컬이랑 토요일 레그컬 자리 바꾸는거 어떻게 생각해?  /  토요일 페이스풀 넣는게 안 낫겠나?</t>
-  </si>
-  <si>
-    <t>일요일 — 등(광배) · 팔</t>
-  </si>
-  <si>
-    <t>웜업 (세트 카운트 제외)</t>
-  </si>
-  <si>
-    <t>· 이 날은 증량을 추적하는 메인 리프트가 없다. 첫 종목(친업) 전에 랫풀다운 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
-  </si>
-  <si>
-    <t>· 둘 다 근비대 항목이 아니라 관절 준비 항목이므로 세트 합계에 넣지 않는다.</t>
-  </si>
-  <si>
-    <t>수직 당기기 중 가장 무거운 쪽이라 맨 앞에 둔다. 그립이 지치면 주저 말고 어시스트 머신으로 간다 — 이 날 뒤쪽에 당기기가 10세트 더 있다.</t>
-  </si>
-  <si>
-    <t>어시스트 풀업 머신 (1순위 — 그립 부담 ↓) / 랫풀다운 / 뉴트럴 그립 친업</t>
-  </si>
-  <si>
-    <t>135/145/155/165</t>
-  </si>
-  <si>
-    <t>와이드 오버그립 랫풀다운</t>
-  </si>
-  <si>
-    <t>넓은 엎침 그립 — 팔꿈치가 몸에서 벌어진 경로로 들어온다. 이두 관여가 가장 적은 수직 당기기다.</t>
-  </si>
-  <si>
-    <t>오버그립 랫풀다운 (어깨너비 — 어깨가 불편할 때) / 풀업</t>
-  </si>
-  <si>
-    <t>랫풀다운(언더그립 좁게 안쪽으로)</t>
-  </si>
-  <si>
-    <t>짧고 깊은 쪽 — 뒤침 그립으로 좁게 잡아 어깨 신전 구간을 끝까지 쓴다. 이두 계수 0.5가 붙는 자리다.</t>
-  </si>
-  <si>
-    <t>뉴트럴 그립 랫풀다운 / 어시스트 풀업 머신</t>
-  </si>
-  <si>
-    <t>팔꿈치를 몸에 붙여 당기는 경로라 주동근이 광배다 — 그립 폭이 아니라 팔꿈치 경로가 정한다(2026-09-04 원칙). 좌우 독립이라 약한 쪽이 드러난다.</t>
+    <t>팔이 머리 위에 고정된 채 견갑을 내린다 — 승모 하부가 직접 걸리는 유일한 자리이고, 팔이 머리 위라는 점에서 수직 날에 맞는다.</t>
+  </si>
+  <si>
+    <t>프론 Y 레이즈 / 케이블 Y 레이즈</t>
+  </si>
+  <si>
+    <t>짧아진 구간. 당기기 뒤라 삼두가 전혀 쓰이지 않은 상태로 들어온다 — 팔을 세션 후반부에 두는 값이 이 날 가장 싸다.</t>
+  </si>
+  <si>
+    <t>케이블 오버헤드 익스텐션 (로프 · 장두 신전 구간) / V바 푸쉬다운</t>
+  </si>
+  <si>
+    <t>당기기 18세트 뒤라 이두가 이미 간접으로 7세트치를 받았다. 중량이 평소보다 낮게 나오는 것이 정상이다.</t>
+  </si>
+  <si>
+    <t>케이블 컬 (전 구간 장력) / 머신 컬 / EZ바 프리쳐 컬</t>
+  </si>
+  <si>
+    <t>[등을 가른 축 — 움직임 평면이다 (2026-10-02 정정)]</t>
+  </si>
+  <si>
+    <t>· 일요일은 수직, 목요일은 수평이다. 재택 1일차 '당기기 A (수직)' · 6일차 '당기기 B (수평)'과 같은 축이다 (사용자 지정).</t>
+  </si>
+  <si>
+    <t>· 2026-10-02 초안에서는 근육군으로 갈랐다(일=광배 전담 · 목=승모중부 전담). 그 근거로 2026-09-04 '주동근은 그립 폭이 아니라 팔꿈치 경로가 정한다'를 들었는데, 그 원칙은 세트검산의 근육군 분류를 정하는 규칙이고 날을 어떻게 가르라는 말이 아니었다 — 두 축을 뒤섞은 것이다.</t>
+  </si>
+  <si>
+    <t>· 그래서 두 날 모두 광배와 승모 중부가 섞여 있다 — 광배 일 11 / 목 3 · 승모 중부 일 7 / 목 6. 재택도 같은 모양이다(광배 9/4 · 승모 중부 7/8).</t>
+  </si>
+  <si>
+    <t>[팔이 이 날에 있는 이유]</t>
+  </si>
+  <si>
+    <t>· 삼두는 이 날 간접 자극이 0이다 — 당기기만 하는 날이라 프레스가 하나도 없다. 그래서 삼두 3세트가 가장 온전하게 나오는 자리다.</t>
+  </si>
+  <si>
+    <t>· 이두는 반대다. 당기기 18세트가 간접으로 7세트치를 얹으므로 프리쳐 컬은 '이미 데워진 근육을 마무리하는' 자리다.</t>
+  </si>
+  <si>
+    <t>· 삼두 · 이두는 일 · 화 · 목 3세트씩 주 9세트다. 실질은 둘 다 16.5 — 성장 구간 상단이라 더 올리지 않는다.</t>
+  </si>
+  <si>
+    <t>· 27세트 · 약 69분. 메인 리프트가 없어 중간 크기다.</t>
+  </si>
+  <si>
+    <t>· 그립이 이 날의 제약이다. 친업 → 와이드 → 언더그립 → 스미스 바벨 로우 순으로 그립 부담이 줄어드는 순서로 놓았다.</t>
+  </si>
+  <si>
+    <t>· 스미스 바벨 로우는 토요일 스쿼트 다음날에 온다. 궤도가 고정돼 있어 괜찮지만 허리가 무거운 주에는 해머 스트랭스 로우로 바꾼다 — 그러면 목요일과 종목이 겹치므로 그 주만 쓴다.</t>
+  </si>
+  <si>
+    <t>· 언더그립 랫풀다운 +60초 · 케이블 푸쉬다운 +60초 · 프리쳐 컬 +60초. 마지막 세트에만 2단.</t>
+  </si>
+  <si>
+    <t>· 친업 · 와이드 랫풀다운에는 걸지 않는다 — 그립이 먼저 나가 등이 실패지점에 못 간다.</t>
+  </si>
+  <si>
+    <t>· 스미스 바벨 로우 · 페이스풀에도 걸지 않는다. 바벨 로우는 척추가 버티는 종목이고, 페이스풀은 가벼운 외회전 종목이라 실패 뒤 반복에서 팔꿈치가 먼저 내려온다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 일요일 등 · 팔 삼두/이두/전완을 세트 후반부에 · 등도 나누고  /  일요일로 옮기는데, 그 전에 나 등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야</t>
+  </si>
+  <si>
+    <t>월요일 — 가슴 · 어깨 (측/후)</t>
+  </si>
+  <si>
+    <t>매주 미는 세 리프트 중 하나. 이 날은 하체 · 힌지가 없어 코어와 기립근이 가장 신선하다.</t>
+  </si>
+  <si>
+    <t>스미스 벤치 / 체스트 프레스 머신</t>
+  </si>
+  <si>
+    <t>상부지 복합. 복합이라 플라이보다 앞에 둔다.</t>
+  </si>
+  <si>
+    <t>인클라인 스미스 프레스 / 인클라인 덤벨 프레스</t>
+  </si>
+  <si>
+    <t>상부지를 프레스와 플라이 둘로 나눠 각 4세트. 각도는 30~45도.</t>
+  </si>
+  <si>
+    <t>펙덱 플라이 머신 (인클라인 각도) / 인클라인 케이블 플라이</t>
+  </si>
+  <si>
+    <t>하방 벡터 — 벤치(수평)와 각도를 나눈다. 몸을 앞으로 기울이면 가슴, 세우면 삼두로 간다.</t>
+  </si>
+  <si>
+    <t>어시스트 딥스 머신 / 헤머스트랭스 체스트 프레스 / 디클라인 벤치</t>
+  </si>
+  <si>
+    <t>105/120/135</t>
+  </si>
+  <si>
+    <t>원암 케이블 레터럴 레이즈</t>
+  </si>
+  <si>
+    <t>5~7</t>
+  </si>
+  <si>
+    <t>케이블이라 전 구간 장력이 걸린다 — 덤벨 레터럴이 약한 하단 구간을 맡는다.</t>
+  </si>
+  <si>
+    <t>리닝 케이블 레터럴 / 머신 레터럴</t>
+  </si>
+  <si>
+    <t>케이블이라 수축 끝단이 살아 있다 — 토요일 리버스 펙덱(중간 구간)과 갈린다. 밀기 날 뒤에 후면 삼각을 두면 벤치가 만든 전/후 불균형을 같은 세션에서 되돌린다.</t>
+  </si>
+  <si>
+    <t>리버스 펙덱 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
+  </si>
+  <si>
+    <t>[어깨 전면이 이 날에 없는 이유]</t>
+  </si>
+  <si>
+    <t>· 벤치 5 + 인클라인 머신 4 + 딥스 3 + 인클라인 플라이 4가 전면 삼각에 간접으로 6.5세트치를 얹는다. 그 위에 프레스를 더 얹으면 전면만 혼자 과다가 된다.</t>
+  </si>
+  <si>
+    <t>· 그래서 월요일 어깨 블록은 측면 · 후면 둘뿐이다. 전면 직접은 토요일 머신 숄더 3 · 수요일 스미스 오버헤드 3으로 주 6세트다.</t>
+  </si>
+  <si>
+    <t>· 전면 삼각 실질 12.5세트 — 직접 6 + 간접 6.5. 성장 구간 안이다.</t>
+  </si>
+  <si>
+    <t>[가슴을 둘로 가른 축]</t>
+  </si>
+  <si>
+    <t>· 월요일은 상부(인클라인 프레스 4 + 인클라인 플라이 4), 목요일은 중하부(펙덱 4 + 디클라인 플라이 4)다. 벤치와 딥스는 수평 · 하방이라 월요일에 함께 둔다.</t>
+  </si>
+  <si>
+    <t>· 흉근 합산 실질 27.5세트로 천장(20)을 크게 넘는다. 2026-09-14 사용자 지정 — 가슴은 되돌리는 자리가 아니다. 판단 기준은 세트 수가 아니라 벤치 진행이다. 벤치가 2주 연속 안 오르면 그때 이 숫자를 본다.</t>
+  </si>
+  <si>
+    <t>· 22세트 · 약 59분. 여섯 날 중 가장 작다 — 월요일은 가슴 하나만 맡고 어깨가 6세트뿐이다.</t>
+  </si>
+  <si>
+    <t>· 벤치가 있는 날이므로 웜업 10~15분을 따로 잡는다.</t>
+  </si>
+  <si>
+    <t>[드롭 세트를 이 날에 걸지 않은 이유]</t>
+  </si>
+  <si>
+    <t>· 인클라인 덤벨 플라이는 덤벨을 바꿔 드는 동작이라 2단 드롭에서 자세가 먼저 무너진다.</t>
+  </si>
+  <si>
+    <t>· 흉근 드롭은 목요일 디클라인 케이블 플라이 한 곳에 몰아 뒀다 — 핀만 옮기면 되는 자리다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 월요일 가슴 · 월요일 다시 어깨를 세트 후반부에</t>
+  </si>
+  <si>
+    <t>화요일 — 팔 · 목 · 복근</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없고 전부 고립이다. 첫 종목 작업중량의 50%로 12회 한 세트면 램프가 끝난다.</t>
+  </si>
+  <si>
+    <t>· 팔꿈치와 손목이 이 날의 관절이다. 가벼운 케이블 푸쉬다운 15회로 팔꿈치를 먼저 데운다.</t>
+  </si>
+  <si>
+    <t>늘어난 구간 — 팔이 머리 위로 가 장두가 신장된다. 일요일 푸쉬다운(짧아진 구간)과 각도를 나눈다. 팔꿈치가 시큰하면 EZ바로 바꾼다.</t>
+  </si>
+  <si>
+    <t>EZ바 라잉 익스텐션 (손목 · 팔꿈치 부담 ↓) / 케이블 오버헤드 익스텐션</t>
+  </si>
+  <si>
+    <t>늘어난 구간 — 등받이에 기대 어깨가 뒤로 가면 이두 장두가 신장된다. 프리쳐 컬(짧아진 구간)과 각도를 나눈다.</t>
+  </si>
+  <si>
+    <t>케이블 드래그 컬 / 스파이더 컬</t>
+  </si>
+  <si>
+    <t>엎침 그립 컬 — 상완요골근과 신근이 주동이다. 재택 4일차 종목이라 새로 익힐 것이 없다.</t>
+  </si>
+  <si>
+    <t>EZ바 리버스컬 / 케이블 리버스컬 / 해머 컬 (중립 그립)</t>
+  </si>
+  <si>
+    <t>시티드 리스트 컬(손등 아래)</t>
+  </si>
+  <si>
+    <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다.</t>
+  </si>
+  <si>
+    <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
+  </si>
+  <si>
+    <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다.</t>
+  </si>
+  <si>
+    <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
+  </si>
+  <si>
+    <t>넥 익스텐션 (플레이트)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 신설] 벤치에 엎드려 뒤통수에 플레이트를 올리고 목만 든다. 첫 2주는 무게 없이 가동범위만 — 경추는 되돌릴 수 없는 자리다. 통증이 아니라 '당기는 느낌'까지만.</t>
+  </si>
+  <si>
+    <t>넥 하네스 / 넥 익스텐션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
+  </si>
+  <si>
+    <t>넥 플렉션 (플레이트)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 신설] 벤치에 누워 이마에 수건을 깔고 플레이트를 올린다. 턱을 당겨 목만 굽힌다. 굴곡 쪽이 더 약하므로 익스텐션보다 가볍게 간다.</t>
+  </si>
+  <si>
+    <t>넥 하네스 / 넥 플렉션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
+  </si>
+  <si>
+    <t>직접 굴곡. 스쿼트 · 데드의 브레이싱은 등척성이라 복부 간접이 0이다 — 여기서만 채워진다.</t>
+  </si>
+  <si>
+    <t>케이블 크런치 (머신) / 앱스 머신</t>
+  </si>
+  <si>
+    <t>하복부 쪽 — 크런치(상복부)와 갈린다. 재택 1일차 종목이다.</t>
+  </si>
+  <si>
+    <t>캡틴 체어 니 레이즈 / 행잉 레그 레이즈 / 리버스 크런치</t>
+  </si>
+  <si>
+    <t>[이 날은 건드리지 않았다]</t>
+  </si>
+  <si>
+    <t>· 사용자 지정 — '화요일은 팔하니 놔두고'. 삼두 · 이두 · 전완 · 목 · 복근 구성을 그대로 두고 세트만 맞췄다.</t>
+  </si>
+  <si>
+    <t>· 다른 다섯 날은 큰 부위 뒤에 어깨나 팔이 붙지만, 이 날은 팔이 메인이다. 팔이 가장 신선한 유일한 자리다.</t>
+  </si>
+  <si>
+    <t>· 그래서 늘어난 구간(라잉 익스텐션 · 인클라인 컬)을 이 날에 뒀다. 신장된 자리에서의 부하가 가장 비싸고, 지친 팔로는 그 자세가 안 잡힌다.</t>
+  </si>
+  <si>
+    <t>[전완 · 목 · 복근이 이 날에 몰린 이유]</t>
+  </si>
+  <si>
+    <t>· 전완 주 9세트가 전부 이 날이다. 그립을 쓰는 당기기가 하나도 없는 유일한 날이라 리스트 컬이 온전히 나온다.</t>
+  </si>
+  <si>
+    <t>· 전완 6 → 9 · 복부 3 → 6으로 올렸다. 현장 근무가 끝나 그립과 코어에 하루치를 얹어주던 보정이 사라졌기 때문이다 (복귀_세트검산 참조).</t>
+  </si>
+  <si>
+    <t>· 목은 2026-10-02 신설이다. 직접 0에서 주 6세트. 데드 · 슈러그의 등척성 지지는 계수 0이라 여기서만 채워진다.</t>
+  </si>
+  <si>
+    <t>· 27세트 · 약 48분. 여섯 날 중 가장 짧다 — 전부 고립이고 휴식이 60~75초라 그렇다.</t>
+  </si>
+  <si>
+    <t>· 27세트지만 세션 상한 26의 적용 대상이 아니다. 메인 리프트가 없고 전부 고립 소근육이다.</t>
+  </si>
+  <si>
+    <t>· 라잉 트라이셉스 익스텐션 +60초 한 곳만. 마지막 세트에만 2단.</t>
+  </si>
+  <si>
+    <t>· 인클라인 덤벨 컬에는 걸지 않는다 — 2026-09-07에 제외로 정한 자리다.</t>
+  </si>
+  <si>
+    <t>· 넥 종목에는 절대 걸지 않는다. 실패지점 근처에서 목을 쓰는 것이 이 종목의 유일한 금기다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 화요일 삼두/이두/전완/목/복근 — 화요일은 팔하니 놔두고</t>
+  </si>
+  <si>
+    <t>수요일 — 하체 후면 · 어깨 (전/측/후)</t>
+  </si>
+  <si>
+    <t>메인: 스미스 오버헤드 프레스</t>
+  </si>
+  <si>
+    <t>웜업 — 회전근개 (세트 카운트 제외 · 오버헤드 프레스 직전에)</t>
+  </si>
+  <si>
+    <t>· 데드 램프 · 프레스 램프와 따로다. 하체 5종목을 끝내고 오버헤드 프레스(6번)에 들어가기 직전에 넣는다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 보충] 메인이 둘이라 램프 블록 두 개에 가려 이 블록이 빠져 있었다. 어깨 보조가 9세트 이어지고 그 앞에 증량을 추적하는 프레스가 있는 날이다.</t>
+  </si>
+  <si>
+    <t>톱세트. 현장 근무가 끝나 허리와 경쟁하는 것이 없어졌으므로 2026-10-02부터 백오프 2세트를 되살려 성장으로 돌린다.</t>
+  </si>
+  <si>
+    <t>트랩바 데드 (요추 전단력 ↓) / 루마니안 데드 (허리가 무거운 주)</t>
+  </si>
+  <si>
+    <t>데드리프트 백오프</t>
+  </si>
+  <si>
+    <t>톱세트 −5kg = 2주 전 중량. 폼이 살아 있는 중량에서 볼륨을 쌓는 자리다. 다음 아침 허리가 뻐근하면 이 2세트를 먼저 뺀다 — 톱세트가 아니다.</t>
+  </si>
+  <si>
+    <t>트랩바 데드 백오프 / 랙 풀 (가동범위 ↓)</t>
+  </si>
+  <si>
+    <t>40~45</t>
+  </si>
+  <si>
+    <t>고관절 신전으로 햄스트링을 늘어난 구간에서 훈련한다. 무릎은 살짝만 굽히고 중립 척추를 지킨다.</t>
+  </si>
+  <si>
+    <t>덤벨 루마니안 데드 (허리 부담 ↓ · 좌우 균형) / 케이블 풀스루</t>
+  </si>
+  <si>
+    <t>레그 프레스 (발 높게)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 둔다 — 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라간다. 근육군은 둔근으로 잡았다: 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀌고, 능동 단축이 작으면 자극도 작다. 그래서 사두 0.33 · 햄스트링 0.2를 간접으로 계상했다. 중량은 토요일(125)보다 낮게 잡았다 — 발 위치가 바뀌면 같은 중량이 안 나온다. 더블 프로그레션으로 맞춘다.</t>
+  </si>
+  <si>
+    <t>와이드 스탠스 레그 프레스 (발 높게) / 45도 레그 프레스 (발 높게) / 스미스 스쿼트 (발 앞쪽)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 토요일 레그 컬과 자리 교환] 무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 편측 종목은 좌우 차를 드러내는 것이 목적이라 주의력이 필요하고, 그래서 여섯 날 중 누적 10세트짜리인 이 자리가 맞다. 토요일 9번(누적 34세트)은 반대였다. 중량은 토요일 양측 레그 컬이 밀고, 이쪽은 균형을 본다 — 좌우 반복 수가 2회 이상 벌어지면 약한 쪽 기준으로 맞춘다.</t>
+  </si>
+  <si>
+    <t>원 레그 시티드 컬 / 라잉 레그 컬 (양측 — 편측 자리가 없을 때) / 노르딕 햄 컬 (맨몸)</t>
+  </si>
+  <si>
+    <t>스미스 오버헤드 프레스</t>
+  </si>
+  <si>
+    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 13세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
+  </si>
+  <si>
+    <t>머신 숄더 프레스 (완전 머신을 원할 때 — 단 증량 추적은 이쪽으로 옮긴다) / 덤벨 숄더 프레스</t>
+  </si>
+  <si>
+    <t>프레스 직후라 측면 삼각이 이미 1.5세트치 간접을 받았다. 중량을 토요일보다 낮춰 잡는 것이 정상이다.</t>
+  </si>
+  <si>
+    <t>머신이라 상체 각도가 고정된다 — 데드 뒤에 기립근으로 버티지 않아도 되는 후면 삼각 종목이 이것뿐이다.</t>
+  </si>
+  <si>
+    <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 리버스 펙덱</t>
+  </si>
+  <si>
+    <t>둔근 직접. 짧아진 구간에서 최대 장력이 걸려 데드 · 루마니안(늘어난 구간)과 갈린다. 어깨와 경쟁하지 않는 고관절 종목이라 어깨 블록 뒤로 보냈다 — 그만큼 오버헤드 프레스 앞 누적이 줄었다.</t>
+  </si>
+  <si>
+    <t>머신 힙 쓰러스트 / 글루트 브릿지 / 케이블 풀스루</t>
+  </si>
+  <si>
+    <t>선 자세 · 편측이라 고관절이 펴진 각도에서 외전한다 — 앉아서 하는 아우터 타이(고관절 굽힘)와 각도가 갈린다. 둘 중 이쪽이 좌우 차가 드러나므로 아우터 타이 앞에 둬 더 신선한 자리를 줬다.</t>
+  </si>
+  <si>
+    <t>머신 힙 어브덕션 / 밴드 사이드 워크</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 요청 — 토요일과 같은 슈퍼세트를 이 날에도] 내전근 직접이 주 4세트뿐이라 실질 6.5로 하한(8) 아래였다. 이 4세트로 8 → 실질 10.5가 된다. 아우터와 슈퍼세트 — 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 요청] 중둔근 실질 7.0도 하한 아래였다 — 이 4세트로 11이 된다. 앞의 케이블 힙 외전과 같은 근육이므로 중량이 토요일보다 낮게 나오는 것이 정상이다. 어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤에 둔다.</t>
+  </si>
+  <si>
+    <t>무릎이 펴져 비복근 비중이 커진다 — 토요일 시티드(가자미근)와 각도를 나눈다. 데드 뒤라 발목이 이미 데워져 있다.</t>
+  </si>
+  <si>
+    <t>레그 프레스 카프 레이즈 / 시티드 카프 레이즈 / 스미스 카프 레이즈</t>
+  </si>
+  <si>
+    <t>[오버헤드 프레스를 수요일에 둔 이유]</t>
+  </si>
+  <si>
+    <t>· 어깨를 전부 세션 후반부로 내리면(2026-10-02 사용자 지정) 매주 미는 세 리프트 중 오버헤드 프레스만 큰 부위 뒤로 밀린다. 어느 날 뒤에 두는 것이 가장 싼지가 문제였다.</t>
+  </si>
+  <si>
+    <t>· 월요일(가슴) 뒤 — 가장 비싸다. 벤치 5 + 인클라인 4 + 딥스 3이 전면 삼각과 삼두에 간접 6.5세트치를 얹은 상태로 메인을 치게 된다.</t>
+  </si>
+  <si>
+    <t>· 토요일(하체 전면) 뒤 — 중간이다. 전면 삼각 · 삼두는 온전하나 스쿼트 5×5의 전신 피로가 가장 크다.</t>
+  </si>
+  <si>
+    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 13세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
+  </si>
+  <si>
+    <t>· 그래서 토요일 전면은 머신 숄더 프레스(볼륨용)이고, 증량을 추적하는 쪽은 이 날이다.</t>
+  </si>
+  <si>
+    <t>· 힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프를 어깨 뒤로 보내 프레스 앞 누적을 13세트로 묶었다. 레그 프레스와 슈퍼세트가 들어오며 25가 될 수 있었던 자리다.</t>
+  </si>
+  <si>
+    <t>[하체 후면을 한 날에 모은 이유]</t>
+  </si>
+  <si>
+    <t>· 데드 · 루마니안 데드는 둘 다 고관절 힌지다. 주에 흩어 두면 기립근이 회복할 72시간을 못 받는다 — 같은 패턴은 한 날에 모은다.</t>
+  </si>
+  <si>
+    <t>· 고관절 신전 넷(데드 3 · 루마니안 3 · 레그 프레스 발 높게 4 · 힙 쓰러스트 3)과 무릎 굴곡(원 레그 컬 3)을 같이 둬 햄스트링 · 둔근의 두 기능을 다 쓴다.</t>
+  </si>
+  <si>
+    <t>· 햄스트링 주 10세트 중 6이 이 날이고 4는 토요일 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다. 중량은 토요일(양측 4세트)이 밀고 이 날은 힌지 + 편측 균형을 맡는다.</t>
+  </si>
+  <si>
+    <t>· 토요일(사두 12 + 햄 3 + 내전근 4 + 중둔근 4) · 수요일(후면 14 + 중둔근 7 + 내전근 4 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 사용자 요청] 이너 · 아우터 타이 슈퍼세트를 이 날에도 넣었다 — 하체에서 유일하게 하한 아래로 남아 있던 내전근(6.5)과 중둔근(7.0)이 둘 다 성장 구간으로 들어간다(10.5 · 11.0). 토요일과 같은 쌍이라 새로 익힐 것이 없다.</t>
+  </si>
+  <si>
+    <t>[레그 프레스를 발 높게 — 2026-10-02 사용자 지정]</t>
+  </si>
+  <si>
+    <t>· 발을 발판 가장 위쪽에 둔다. 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라가고, 무릎 신전 범위는 줄어든다.</t>
+  </si>
+  <si>
+    <t>· 다만 햄스트링 종목은 아니다 — 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀐다. 능동 단축이 작으면 자극도 작다.</t>
+  </si>
+  <si>
+    <t>· 그래서 주동근은 둔근으로 잡고 사두 0.33 · 햄스트링 0.2 · 내전근 0.2를 간접으로 계상했다. 후면을 노린다는 의도는 둔근 직접 4세트로 실현된다.</t>
+  </si>
+  <si>
+    <t>· 햄스트링 쪽을 직접 때리는 것은 루마니안 데드(늘어난 구간) · 레그 컬(짧아진 구간) · 토요일 원 레그 컬(편측)이다.</t>
+  </si>
+  <si>
+    <t>· 토요일 레그 프레스(발 낮게 · 사두)와 같은 종목 다른 자리다. 사두에도 간접 1.5세트치가 붙어 사두가 주 1회에서 '주 1회 + 간접 1회'가 됐다.</t>
+  </si>
+  <si>
+    <t>[데드리프트 운용 규칙]</t>
+  </si>
+  <si>
+    <t>· 유일한 지표는 다음날 아침 허리 상태다. 뻐근하면 그 주가 과했던 것 — 다음 주에 백오프를 먼저 뺀다.</t>
+  </si>
+  <si>
+    <t>· 톱세트 1×5는 지키고, 줄일 때는 항상 백오프 2세트부터다. 강도를 놓으면 근력이 먼저 빠진다.</t>
+  </si>
+  <si>
+    <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
+  </si>
+  <si>
+    <t>· 39세트 · 약 98분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
+  </si>
+  <si>
+    <t>· 고립 26세트를 빼면 실질 13세트다 — 어깨 블록 뒤 17세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 35분이 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
+  </si>
+  <si>
+    <t>· 레터럴 +60초 하나뿐이다. 마지막 세트에만 2단 — 레그 컬 드롭은 2026-10-02에 양측 레그 컬과 함께 토요일로 갔다.</t>
+  </si>
+  <si>
+    <t>· 원 레그 컬에는 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 되고, 일요일 원암 케이블 로우와 같은 기준이다.</t>
+  </si>
+  <si>
+    <t>· 데드 · 백오프 · 루마니안 · 레그 프레스에는 걸지 않는다 — 척추가 버티거나 중량이 큰 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
+  </si>
+  <si>
+    <t>· 이너 · 아우터 타이에도 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다(토요일과 같은 이유).</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고  /  수 하체에는 레그 프레스 넣어주고, 수요일에 하는 레그 프레스는 발을 발판의 가장 위쪽에 두어서 햄스트링 후면을 타겟하도록 할거야. 동시에 사두도 좀 타겟되겠지만.  /  그리고 수요일하체에 이너타이랑 아우터타이 슈퍼세트도 넣어줘.</t>
+  </si>
+  <si>
+    <t>목요일 — 당기기 B (수평) · 가슴 · 팔</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없다. 첫 종목(해머 스트랭스 로우) 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
+  </si>
+  <si>
+    <t>체스트 서포티드라 척추 부하가 0이다. 수요일 데드 다음날의 첫 종목으로 이보다 안전한 수평 로우가 없다. 넓은 엎침 그립 + 팔꿈치 벌림 — 주동근은 견갑 후인이다(2026-09-04 재분류).</t>
+  </si>
+  <si>
+    <t>시티드 케이블 로우 (넓은 그립) / 머신 로우 / 티바 로우</t>
+  </si>
+  <si>
+    <t>135/150/165</t>
+  </si>
+  <si>
+    <t>[2026-10-02 일요일에서 이동] 수평 당기기이므로 평면 기준으로는 이 날이 맞다. 팔꿈치를 몸에 붙여 당기는 경로라 주동근은 광배다 — 평면으로 날을 가르고 근육군은 팔꿈치 경로로 매긴다. 좌우 독립이라 약한 쪽이 드러난다.</t>
   </si>
   <si>
     <t>원암 해머 스트랭스 로우 / 원암 덤벨 로우 (벤치 지지) / 머신 로우</t>
   </si>
   <si>
-    <t>팔이 머리 위에 고정된 채 견갑을 내린다 — 승모 하부가 직접 걸리는 유일한 자리다.</t>
-  </si>
-  <si>
-    <t>프론 Y 레이즈 / 케이블 Y 레이즈</t>
-  </si>
-  <si>
-    <t>짧아진 구간. 당기기 뒤라 삼두가 전혀 쓰이지 않은 상태로 들어온다 — 팔을 세션 후반부에 두는 값이 이 날 가장 싸다.</t>
-  </si>
-  <si>
-    <t>케이블 오버헤드 익스텐션 (로프 · 장두 신전 구간) / V바 푸쉬다운</t>
-  </si>
-  <si>
-    <t>당기기 17세트 뒤라 이두가 이미 간접으로 6.5세트치를 받았다. 중량이 평소보다 낮게 나오는 것이 정상이다.</t>
-  </si>
-  <si>
-    <t>케이블 컬 (전 구간 장력) / 머신 컬 / EZ바 프리쳐 컬</t>
-  </si>
-  <si>
-    <t>[등을 둘로 가른 축 — 근육군이지 움직임 평면이 아니다]</t>
-  </si>
-  <si>
-    <t>· 일요일은 광배, 목요일은 승모 중부 · 능형근이다. 수직 / 수평으로 가르지 않았다.</t>
-  </si>
-  <si>
-    <t>· 2026-09-04에 넓은 그립 로우 둘을 광배 → 승모 중부 직접으로 재분류한 그 원칙을 그대로 쓴다 — 주동근은 그립 폭이 아니라 팔꿈치 경로가 정한다.</t>
-  </si>
-  <si>
-    <t>· 그래서 원암 케이블 로우(수평 당기기)가 광배 날에 있고, 스미스 바벨 로우는 목요일에 있다. 평면이 아니라 어느 근육이 주동이냐로 갈랐다.</t>
-  </si>
-  <si>
-    <t>· 광배 주 14세트가 한 날에 다 들어간다. 주 2회로 쪼개는 쪽은 가슴과 하체뿐이다 — 등은 주동근이 둘이라 날을 가르는 것으로 이미 빈도가 2회다.</t>
-  </si>
-  <si>
-    <t>[팔이 이 날에 있는 이유]</t>
-  </si>
-  <si>
-    <t>· 삼두는 이 날 간접 자극이 0이다 — 당기기만 하는 날이라 프레스가 하나도 없다. 그래서 삼두 3세트가 가장 온전하게 나오는 자리다.</t>
-  </si>
-  <si>
-    <t>· 이두는 반대다. 당기기 17세트가 간접으로 6.5세트치를 얹으므로 프리쳐 컬은 '이미 데워진 근육을 마무리하는' 자리다.</t>
-  </si>
-  <si>
-    <t>· 삼두 · 이두는 일 · 화 · 목 3세트씩 주 9세트다. 실질은 삼두 18 · 이두 15.5 — 둘 다 성장 구간 상단이라 더 올리지 않는다.</t>
-  </si>
-  <si>
-    <t>· 23세트 · 약 60분. 메인 리프트가 없어 여섯 날 중 둘째로 짧다.</t>
-  </si>
-  <si>
-    <t>· 그립이 이 날의 제약이다. 친업 → 와이드 → 언더그립 → 원암 순으로 그립 부담이 줄어드는 순서로 놓았다.</t>
-  </si>
-  <si>
-    <t>· 언더그립 랫풀다운 +60초 · 케이블 푸쉬다운 +60초 · 프리쳐 컬 +60초. 마지막 세트에만 2단.</t>
-  </si>
-  <si>
-    <t>· 친업 · 와이드 랫풀다운에는 걸지 않는다 — 그립이 먼저 나가 등이 실패지점에 못 간다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 일요일 등 · 팔 삼두/이두/전완을 세트 후반부에 · 등도 나누고</t>
-  </si>
-  <si>
-    <t>월요일 — 가슴 · 어깨 (측/후)</t>
-  </si>
-  <si>
-    <t>매주 미는 세 리프트 중 하나. 이 날은 하체 · 힌지가 없어 코어와 기립근이 가장 신선하다.</t>
-  </si>
-  <si>
-    <t>스미스 벤치 / 체스트 프레스 머신</t>
-  </si>
-  <si>
-    <t>상부지 복합. 복합이라 플라이보다 앞에 둔다.</t>
-  </si>
-  <si>
-    <t>인클라인 스미스 프레스 / 인클라인 덤벨 프레스</t>
-  </si>
-  <si>
-    <t>상부지를 프레스와 플라이 둘로 나눠 각 4세트. 각도는 30~45도.</t>
-  </si>
-  <si>
-    <t>펙덱 플라이 머신 (인클라인 각도) / 인클라인 케이블 플라이</t>
-  </si>
-  <si>
-    <t>하방 벡터 — 벤치(수평)와 각도를 나눈다. 몸을 앞으로 기울이면 가슴, 세우면 삼두로 간다.</t>
-  </si>
-  <si>
-    <t>어시스트 딥스 머신 / 헤머스트랭스 체스트 프레스 / 디클라인 벤치</t>
-  </si>
-  <si>
-    <t>105/120/135</t>
-  </si>
-  <si>
-    <t>원암 케이블 레터럴 레이즈</t>
-  </si>
-  <si>
-    <t>5~7</t>
-  </si>
-  <si>
-    <t>케이블이라 전 구간 장력이 걸린다 — 덤벨 레터럴이 약한 하단 구간을 맡는다.</t>
-  </si>
-  <si>
-    <t>리닝 케이블 레터럴 / 머신 레터럴</t>
-  </si>
-  <si>
-    <t>케이블이라 수축 끝단이 살아 있다 — 토요일 리버스 펙덱(중간 구간)과 갈린다. 밀기 날 뒤에 후면 삼각을 두면 벤치가 만든 전/후 불균형을 같은 세션에서 되돌린다.</t>
-  </si>
-  <si>
-    <t>리버스 펙덱 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
-  </si>
-  <si>
-    <t>[어깨 전면이 이 날에 없는 이유]</t>
-  </si>
-  <si>
-    <t>· 벤치 5 + 인클라인 머신 4 + 딥스 3 + 인클라인 플라이 4가 전면 삼각에 간접으로 6.5세트치를 얹는다. 그 위에 프레스를 더 얹으면 전면만 혼자 과다가 된다.</t>
-  </si>
-  <si>
-    <t>· 그래서 월요일 어깨 블록은 측면 · 후면 둘뿐이다. 전면 직접은 토요일 머신 숄더 3 · 수요일 스미스 오버헤드 3으로 주 6세트다.</t>
-  </si>
-  <si>
-    <t>· 전면 삼각 실질 12.5세트 — 직접 6 + 간접 6.5. 성장 구간 안이다.</t>
-  </si>
-  <si>
-    <t>[가슴을 둘로 가른 축]</t>
-  </si>
-  <si>
-    <t>· 월요일은 상부(인클라인 프레스 4 + 인클라인 플라이 4), 목요일은 중하부(펙덱 4 + 디클라인 플라이 4)다. 벤치와 딥스는 수평 · 하방이라 월요일에 함께 둔다.</t>
-  </si>
-  <si>
-    <t>· 흉근 합산 실질 27.5세트로 천장(20)을 크게 넘는다. 2026-09-14 사용자 지정 — 가슴은 되돌리는 자리가 아니다. 판단 기준은 세트 수가 아니라 벤치 진행이다. 벤치가 2주 연속 안 오르면 그때 이 숫자를 본다.</t>
-  </si>
-  <si>
-    <t>· 22세트 · 약 59분. 여섯 날 중 가장 작다 — 월요일은 가슴 하나만 맡고 어깨가 6세트뿐이다.</t>
-  </si>
-  <si>
-    <t>· 벤치가 있는 날이므로 웜업 10~15분을 따로 잡는다.</t>
-  </si>
-  <si>
-    <t>[드롭 세트를 이 날에 걸지 않은 이유]</t>
-  </si>
-  <si>
-    <t>· 인클라인 덤벨 플라이는 덤벨을 바꿔 드는 동작이라 2단 드롭에서 자세가 먼저 무너진다.</t>
-  </si>
-  <si>
-    <t>· 흉근 드롭은 목요일 디클라인 케이블 플라이 한 곳에 몰아 뒀다 — 핀만 옮기면 되는 자리다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 월요일 가슴 · 월요일 다시 어깨를 세트 후반부에</t>
-  </si>
-  <si>
-    <t>화요일 — 팔 · 목 · 복근</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없고 전부 고립이다. 첫 종목 작업중량의 50%로 12회 한 세트면 램프가 끝난다.</t>
-  </si>
-  <si>
-    <t>· 팔꿈치와 손목이 이 날의 관절이다. 가벼운 케이블 푸쉬다운 15회로 팔꿈치를 먼저 데운다.</t>
-  </si>
-  <si>
-    <t>늘어난 구간 — 팔이 머리 위로 가 장두가 신장된다. 일요일 푸쉬다운(짧아진 구간)과 각도를 나눈다. 팔꿈치가 시큰하면 EZ바로 바꾼다.</t>
-  </si>
-  <si>
-    <t>EZ바 라잉 익스텐션 (손목 · 팔꿈치 부담 ↓) / 케이블 오버헤드 익스텐션</t>
-  </si>
-  <si>
-    <t>늘어난 구간 — 등받이에 기대 어깨가 뒤로 가면 이두 장두가 신장된다. 프리쳐 컬(짧아진 구간)과 각도를 나눈다.</t>
-  </si>
-  <si>
-    <t>케이블 드래그 컬 / 스파이더 컬</t>
-  </si>
-  <si>
-    <t>엎침 그립 컬 — 상완요골근과 신근이 주동이다. 재택 4일차 종목이라 새로 익힐 것이 없다.</t>
-  </si>
-  <si>
-    <t>EZ바 리버스컬 / 케이블 리버스컬 / 해머 컬 (중립 그립)</t>
-  </si>
-  <si>
-    <t>시티드 리스트 컬(손등 아래)</t>
-  </si>
-  <si>
-    <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다.</t>
-  </si>
-  <si>
-    <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
-  </si>
-  <si>
-    <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다.</t>
-  </si>
-  <si>
-    <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
-  </si>
-  <si>
-    <t>넥 익스텐션 (플레이트)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 신설] 벤치에 엎드려 뒤통수에 플레이트를 올리고 목만 든다. 첫 2주는 무게 없이 가동범위만 — 경추는 되돌릴 수 없는 자리다. 통증이 아니라 '당기는 느낌'까지만.</t>
-  </si>
-  <si>
-    <t>넥 하네스 / 넥 익스텐션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
-  </si>
-  <si>
-    <t>넥 플렉션 (플레이트)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 신설] 벤치에 누워 이마에 수건을 깔고 플레이트를 올린다. 턱을 당겨 목만 굽힌다. 굴곡 쪽이 더 약하므로 익스텐션보다 가볍게 간다.</t>
-  </si>
-  <si>
-    <t>넥 하네스 / 넥 플렉션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
-  </si>
-  <si>
-    <t>직접 굴곡. 스쿼트 · 데드의 브레이싱은 등척성이라 복부 간접이 0이다 — 여기서만 채워진다.</t>
-  </si>
-  <si>
-    <t>케이블 크런치 (머신) / 앱스 머신</t>
-  </si>
-  <si>
-    <t>하복부 쪽 — 크런치(상복부)와 갈린다. 재택 1일차 종목이다.</t>
-  </si>
-  <si>
-    <t>캡틴 체어 니 레이즈 / 행잉 레그 레이즈 / 리버스 크런치</t>
-  </si>
-  <si>
-    <t>[이 날은 건드리지 않았다]</t>
-  </si>
-  <si>
-    <t>· 사용자 지정 — '화요일은 팔하니 놔두고'. 삼두 · 이두 · 전완 · 목 · 복근 구성을 그대로 두고 세트만 맞췄다.</t>
-  </si>
-  <si>
-    <t>· 다른 다섯 날은 큰 부위 뒤에 어깨나 팔이 붙지만, 이 날은 팔이 메인이다. 팔이 가장 신선한 유일한 자리다.</t>
-  </si>
-  <si>
-    <t>· 그래서 늘어난 구간(라잉 익스텐션 · 인클라인 컬)을 이 날에 뒀다. 신장된 자리에서의 부하가 가장 비싸고, 지친 팔로는 그 자세가 안 잡힌다.</t>
-  </si>
-  <si>
-    <t>[전완 · 목 · 복근이 이 날에 몰린 이유]</t>
-  </si>
-  <si>
-    <t>· 전완 주 9세트가 전부 이 날이다. 그립을 쓰는 당기기가 하나도 없는 유일한 날이라 리스트 컬이 온전히 나온다.</t>
-  </si>
-  <si>
-    <t>· 전완 6 → 9 · 복부 3 → 6으로 올렸다. 현장 근무가 끝나 그립과 코어에 하루치를 얹어주던 보정이 사라졌기 때문이다 (복귀_세트검산 참조).</t>
-  </si>
-  <si>
-    <t>· 목은 2026-10-02 신설이다. 직접 0에서 주 6세트. 데드 · 슈러그의 등척성 지지는 계수 0이라 여기서만 채워진다.</t>
-  </si>
-  <si>
-    <t>· 27세트 · 약 48분. 여섯 날 중 가장 짧다 — 전부 고립이고 휴식이 60~75초라 그렇다.</t>
-  </si>
-  <si>
-    <t>· 27세트지만 세션 상한 26의 적용 대상이 아니다. 메인 리프트가 없고 전부 고립 소근육이다.</t>
-  </si>
-  <si>
-    <t>· 라잉 트라이셉스 익스텐션 +60초 한 곳만. 마지막 세트에만 2단.</t>
-  </si>
-  <si>
-    <t>· 인클라인 덤벨 컬에는 걸지 않는다 — 2026-09-07에 제외로 정한 자리다.</t>
-  </si>
-  <si>
-    <t>· 넥 종목에는 절대 걸지 않는다. 실패지점 근처에서 목을 쓰는 것이 이 종목의 유일한 금기다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 화요일 삼두/이두/전완/목/복근 — 화요일은 팔하니 놔두고</t>
-  </si>
-  <si>
-    <t>수요일 — 하체 후면 · 어깨 (전/측/후)</t>
-  </si>
-  <si>
-    <t>메인: 스미스 오버헤드 프레스</t>
-  </si>
-  <si>
-    <t>웜업 — 회전근개 (세트 카운트 제외 · 오버헤드 프레스 직전에)</t>
-  </si>
-  <si>
-    <t>· 데드 램프 · 프레스 램프와 따로다. 하체 5종목을 끝내고 오버헤드 프레스(6번)에 들어가기 직전에 넣는다.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02 보충] 메인이 둘이라 램프 블록 두 개에 가려 이 블록이 빠져 있었다. 어깨 보조가 9세트 이어지고 그 앞에 증량을 추적하는 프레스가 있는 날이다.</t>
-  </si>
-  <si>
-    <t>톱세트. 현장 근무가 끝나 허리와 경쟁하는 것이 없어졌으므로 2026-10-02부터 백오프 2세트를 되살려 성장으로 돌린다.</t>
-  </si>
-  <si>
-    <t>트랩바 데드 (요추 전단력 ↓) / 루마니안 데드 (허리가 무거운 주)</t>
-  </si>
-  <si>
-    <t>데드리프트 백오프</t>
-  </si>
-  <si>
-    <t>톱세트 −5kg = 2주 전 중량. 폼이 살아 있는 중량에서 볼륨을 쌓는 자리다. 다음 아침 허리가 뻐근하면 이 2세트를 먼저 뺀다 — 톱세트가 아니다.</t>
-  </si>
-  <si>
-    <t>트랩바 데드 백오프 / 랙 풀 (가동범위 ↓)</t>
-  </si>
-  <si>
-    <t>40~45</t>
-  </si>
-  <si>
-    <t>고관절 신전으로 햄스트링을 늘어난 구간에서 훈련한다. 무릎은 살짝만 굽히고 중립 척추를 지킨다.</t>
-  </si>
-  <si>
-    <t>덤벨 루마니안 데드 (허리 부담 ↓ · 좌우 균형) / 케이블 풀스루</t>
-  </si>
-  <si>
-    <t>레그 프레스 (발 높게)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 둔다 — 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라간다. 근육군은 둔근으로 잡았다: 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀌고, 능동 단축이 작으면 자극도 작다. 그래서 사두 0.33 · 햄스트링 0.2를 간접으로 계상했다. 중량은 토요일(125)보다 낮게 잡았다 — 발 위치가 바뀌면 같은 중량이 안 나온다. 더블 프로그레션으로 맞춘다.</t>
-  </si>
-  <si>
-    <t>와이드 스탠스 레그 프레스 (발 높게) / 45도 레그 프레스 (발 높게) / 스미스 스쿼트 (발 앞쪽)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 토요일 레그 컬과 자리 교환] 무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 편측 종목은 좌우 차를 드러내는 것이 목적이라 주의력이 필요하고, 그래서 여섯 날 중 누적 10세트짜리인 이 자리가 맞다. 토요일 9번(누적 34세트)은 반대였다. 중량은 토요일 양측 레그 컬이 밀고, 이쪽은 균형을 본다 — 좌우 반복 수가 2회 이상 벌어지면 약한 쪽 기준으로 맞춘다.</t>
-  </si>
-  <si>
-    <t>원 레그 시티드 컬 / 라잉 레그 컬 (양측 — 편측 자리가 없을 때) / 노르딕 햄 컬 (맨몸)</t>
-  </si>
-  <si>
-    <t>스미스 오버헤드 프레스</t>
-  </si>
-  <si>
-    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 13세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
-  </si>
-  <si>
-    <t>머신 숄더 프레스 (완전 머신을 원할 때 — 단 증량 추적은 이쪽으로 옮긴다) / 덤벨 숄더 프레스</t>
-  </si>
-  <si>
-    <t>프레스 직후라 측면 삼각이 이미 1.5세트치 간접을 받았다. 중량을 토요일보다 낮춰 잡는 것이 정상이다.</t>
-  </si>
-  <si>
-    <t>머신이라 상체 각도가 고정된다 — 데드 뒤에 기립근으로 버티지 않아도 되는 후면 삼각 종목이 이것뿐이다.</t>
-  </si>
-  <si>
-    <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 리버스 펙덱</t>
-  </si>
-  <si>
-    <t>둔근 직접. 짧아진 구간에서 최대 장력이 걸려 데드 · 루마니안(늘어난 구간)과 갈린다. 어깨와 경쟁하지 않는 고관절 종목이라 어깨 블록 뒤로 보냈다 — 그만큼 오버헤드 프레스 앞 누적이 줄었다.</t>
-  </si>
-  <si>
-    <t>머신 힙 쓰러스트 / 글루트 브릿지 / 케이블 풀스루</t>
-  </si>
-  <si>
-    <t>선 자세 · 편측이라 고관절이 펴진 각도에서 외전한다 — 앉아서 하는 아우터 타이(고관절 굽힘)와 각도가 갈린다. 둘 중 이쪽이 좌우 차가 드러나므로 아우터 타이 앞에 둬 더 신선한 자리를 줬다.</t>
-  </si>
-  <si>
-    <t>머신 힙 어브덕션 / 밴드 사이드 워크</t>
-  </si>
-  <si>
-    <t>[2026-10-02 사용자 요청 — 토요일과 같은 슈퍼세트를 이 날에도] 내전근 직접이 주 4세트뿐이라 실질 6.5로 하한(8) 아래였다. 이 4세트로 8 → 실질 10.5가 된다. 아우터와 슈퍼세트 — 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
-  </si>
-  <si>
-    <t>[2026-10-02 사용자 요청] 중둔근 실질 7.0도 하한 아래였다 — 이 4세트로 11이 된다. 앞의 케이블 힙 외전과 같은 근육이므로 중량이 토요일보다 낮게 나오는 것이 정상이다. 어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤에 둔다.</t>
-  </si>
-  <si>
-    <t>무릎이 펴져 비복근 비중이 커진다 — 토요일 시티드(가자미근)와 각도를 나눈다. 데드 뒤라 발목이 이미 데워져 있다.</t>
-  </si>
-  <si>
-    <t>레그 프레스 카프 레이즈 / 시티드 카프 레이즈 / 스미스 카프 레이즈</t>
-  </si>
-  <si>
-    <t>[오버헤드 프레스를 수요일에 둔 이유]</t>
-  </si>
-  <si>
-    <t>· 어깨를 전부 세션 후반부로 내리면(2026-10-02 사용자 지정) 매주 미는 세 리프트 중 오버헤드 프레스만 큰 부위 뒤로 밀린다. 어느 날 뒤에 두는 것이 가장 싼지가 문제였다.</t>
-  </si>
-  <si>
-    <t>· 월요일(가슴) 뒤 — 가장 비싸다. 벤치 5 + 인클라인 4 + 딥스 3이 전면 삼각과 삼두에 간접 6.5세트치를 얹은 상태로 메인을 치게 된다.</t>
-  </si>
-  <si>
-    <t>· 토요일(하체 전면) 뒤 — 중간이다. 전면 삼각 · 삼두는 온전하나 스쿼트 5×5의 전신 피로가 가장 크다.</t>
-  </si>
-  <si>
-    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 13세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
-  </si>
-  <si>
-    <t>· 그래서 토요일 전면은 머신 숄더 프레스(볼륨용)이고, 증량을 추적하는 쪽은 이 날이다.</t>
-  </si>
-  <si>
-    <t>· 힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프를 어깨 뒤로 보내 프레스 앞 누적을 13세트로 묶었다. 레그 프레스와 슈퍼세트가 들어오며 25가 될 수 있었던 자리다.</t>
-  </si>
-  <si>
-    <t>[하체 후면을 한 날에 모은 이유]</t>
-  </si>
-  <si>
-    <t>· 데드 · 루마니안 데드는 둘 다 고관절 힌지다. 주에 흩어 두면 기립근이 회복할 72시간을 못 받는다 — 같은 패턴은 한 날에 모은다.</t>
-  </si>
-  <si>
-    <t>· 고관절 신전 넷(데드 3 · 루마니안 3 · 레그 프레스 발 높게 4 · 힙 쓰러스트 3)과 무릎 굴곡(원 레그 컬 3)을 같이 둬 햄스트링 · 둔근의 두 기능을 다 쓴다.</t>
-  </si>
-  <si>
-    <t>· 햄스트링 주 10세트 중 6이 이 날이고 4는 토요일 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다. 중량은 토요일(양측 4세트)이 밀고 이 날은 힌지 + 편측 균형을 맡는다.</t>
-  </si>
-  <si>
-    <t>· 토요일(사두 12 + 햄 3 + 내전근 4 + 중둔근 4) · 수요일(후면 14 + 중둔근 7 + 내전근 4 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02 사용자 요청] 이너 · 아우터 타이 슈퍼세트를 이 날에도 넣었다 — 하체에서 유일하게 하한 아래로 남아 있던 내전근(6.5)과 중둔근(7.0)이 둘 다 성장 구간으로 들어간다(10.5 · 11.0). 토요일과 같은 쌍이라 새로 익힐 것이 없다.</t>
-  </si>
-  <si>
-    <t>[레그 프레스를 발 높게 — 2026-10-02 사용자 지정]</t>
-  </si>
-  <si>
-    <t>· 발을 발판 가장 위쪽에 둔다. 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라가고, 무릎 신전 범위는 줄어든다.</t>
-  </si>
-  <si>
-    <t>· 다만 햄스트링 종목은 아니다 — 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀐다. 능동 단축이 작으면 자극도 작다.</t>
-  </si>
-  <si>
-    <t>· 그래서 주동근은 둔근으로 잡고 사두 0.33 · 햄스트링 0.2 · 내전근 0.2를 간접으로 계상했다. 후면을 노린다는 의도는 둔근 직접 4세트로 실현된다.</t>
-  </si>
-  <si>
-    <t>· 햄스트링 쪽을 직접 때리는 것은 루마니안 데드(늘어난 구간) · 레그 컬(짧아진 구간) · 토요일 원 레그 컬(편측)이다.</t>
-  </si>
-  <si>
-    <t>· 토요일 레그 프레스(발 낮게 · 사두)와 같은 종목 다른 자리다. 사두에도 간접 1.5세트치가 붙어 사두가 주 1회에서 '주 1회 + 간접 1회'가 됐다.</t>
-  </si>
-  <si>
-    <t>[데드리프트 운용 규칙]</t>
-  </si>
-  <si>
-    <t>· 유일한 지표는 다음날 아침 허리 상태다. 뻐근하면 그 주가 과했던 것 — 다음 주에 백오프를 먼저 뺀다.</t>
-  </si>
-  <si>
-    <t>· 톱세트 1×5는 지키고, 줄일 때는 항상 백오프 2세트부터다. 강도를 놓으면 근력이 먼저 빠진다.</t>
-  </si>
-  <si>
-    <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
-  </si>
-  <si>
-    <t>· 39세트 · 약 98분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
-  </si>
-  <si>
-    <t>· 고립 26세트를 빼면 실질 13세트다 — 어깨 블록 뒤 17세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 35분이 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
-  </si>
-  <si>
-    <t>· 레터럴 +60초 하나뿐이다. 마지막 세트에만 2단 — 레그 컬 드롭은 2026-10-02에 양측 레그 컬과 함께 토요일로 갔다.</t>
-  </si>
-  <si>
-    <t>· 원 레그 컬에는 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 되고, 일요일 원암 케이블 로우와 같은 기준이다.</t>
-  </si>
-  <si>
-    <t>· 데드 · 백오프 · 루마니안 · 레그 프레스에는 걸지 않는다 — 척추가 버티거나 중량이 큰 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
-  </si>
-  <si>
-    <t>· 이너 · 아우터 타이에도 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다(토요일과 같은 이유).</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고  /  수 하체에는 레그 프레스 넣어주고, 수요일에 하는 레그 프레스는 발을 발판의 가장 위쪽에 두어서 햄스트링 후면을 타겟하도록 할거야. 동시에 사두도 좀 타겟되겠지만.  /  그리고 수요일하체에 이너타이랑 아우터타이 슈퍼세트도 넣어줘.</t>
-  </si>
-  <si>
-    <t>목요일 — 등(승모·능형) · 가슴 · 팔</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없다. 첫 종목(스미스 바벨 로우) 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
-  </si>
-  <si>
-    <t>스미스 바벨 로우(오버그립)</t>
-  </si>
-  <si>
-    <t>넓은 엎침 그립 — 팔꿈치가 몸에서 벌어져 견갑 후인이 주동이 된다(2026-09-04 재분류). 궤도가 고정돼 수요일 데드 다음날에도 허리 비용이 낮다.</t>
-  </si>
-  <si>
-    <t>티바 로우 / 해머 스트랭스 로우 (허리가 무거운 주) / 체스트 서포티드 로우</t>
-  </si>
-  <si>
-    <t>체스트 서포티드라 척추 부하가 0이다. 데드 다음날 수평 당기기 볼륨을 안전하게 더하는 자리다.</t>
-  </si>
-  <si>
-    <t>시티드 케이블 로우 (넓은 그립) / 머신 로우</t>
-  </si>
-  <si>
     <t>팔을 편 채 견갑만 후인한다 — 로우의 간접만으로는 능형근이 실패지점에 안 간다.</t>
   </si>
   <si>
     <t>페이스풀 (로프) / 리버스 펙덱 (팔 편 채로)</t>
   </si>
   <si>
-    <t>[2026-10-02 신설] 복귀판에 승모 상부 직접이 0이었다. 현장 근무가 하루치를 얹어주던 것이 끝났으므로 재택 6일차 종목을 그대로 가져왔다. 트랩바라 손이 몸 옆에 와 견갑 거상이 수직으로 나온다.</t>
+    <t>[2026-10-02 신설] 복귀판에 승모 상부 직접이 0이었다. 현장 근무가 하루치를 얹어주던 것이 끝났으므로 재택 6일차 종목을 그대로 가져왔다 — 재택도 수평 날(6일차)에 둔다. 트랩바라 손이 몸 옆에 와 견갑 거상이 수직으로 나온다.</t>
   </si>
   <si>
     <t>덤벨 슈러그 / 바벨 슈러그 (몸 앞 — 궤도가 약간 앞으로 간다) / 머신 슈러그</t>
   </si>
   <si>
-    <t>수평 내전으로 중간 구간을 맡는다. 등 13세트 뒤라 가슴이 온전하다 — 당기기와 밀기는 경쟁하지 않는다.</t>
+    <t>수평 내전으로 중간 구간을 맡는다. 등 12세트 뒤라 가슴이 온전하다 — 당기기와 밀기는 경쟁하지 않는다.</t>
   </si>
   <si>
     <t>케이블 크로스오버 (중간 높이) / 덤벨 플라이 / 머신 체스트 프레스</t>
@@ -3691,31 +3709,34 @@
     <t>케이블 컬 (전 구간 장력) / 머신 컬 / 바벨 컬</t>
   </si>
   <si>
+    <t>[이 날이 수평 당기기인 이유 — 2026-10-02 정정]</t>
+  </si>
+  <si>
+    <t>· 재택 6일차 '당기기 B (수평)'과 같은 축이다. 네 종목 전부 수평 당김 또는 견갑 동작이다.</t>
+  </si>
+  <si>
+    <t>· 초안에서는 '승모 중부 · 능형근 전담일'로 잡았는데 그러면 광배가 장부상으로만 주 1회가 된다 — 여기 로우 셋이 전부 광배를 쓴다. 평면으로 가르고 근육군은 팔꿈치 경로로 따로 매기는 것이 재택 방식이다.</t>
+  </si>
+  <si>
+    <t>· 그래서 원암 케이블 로우(광배 · 수평)가 이 날로 왔고 스미스 바벨 로우(승모 중부 · 수평이지만)는 일요일로 갔다. 재택도 바벨 로우를 수직 날에 둔다 — 승모 중부를 두 날에 고르게 나누기 때문이다.</t>
+  </si>
+  <si>
+    <t>· 그 교환의 복귀 전용 이득 — 척추 부하가 있는 유일한 로우가 **데드 다음날에서 빠졌다**. 이제 이 날 로우 넷 중 셋이 체스트 서포티드이거나 궤도 고정이고, 나머지 하나는 편측 케이블이다.</t>
+  </si>
+  <si>
     <t>[이 날이 세 블록인 이유]</t>
   </si>
   <si>
     <t>· 사용자 지정 — '목요일 가슴/등'. 거기에 팔 후반부가 붙어 등 → 가슴 → 팔 세 블록이 됐다.</t>
   </si>
   <si>
-    <t>· 등(승모 중부 · 능형 10 + 승모 상부 3) → 가슴(중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
-  </si>
-  <si>
-    <t>· 팔이 맨 뒤인 이유 — 앞의 13세트(로우 · 슈러그)가 이두에 1.4세트치, 가슴 8세트가 삼두에 0세트치 간접을 얹는다. 플라이는 삼두를 쓰지 않으므로 V바 푸쉬다운이 온전히 나온다.</t>
-  </si>
-  <si>
-    <t>[수요일 데드 다음날인데 로우가 괜찮은 이유]</t>
-  </si>
-  <si>
-    <t>· 네 종목 중 셋이 궤도 고정이거나 체스트 서포티드다 — 스미스 바벨 로우 · 해머 로우 · 스캡 슈러그.</t>
-  </si>
-  <si>
-    <t>· 바벨 로우를 스미스로 바꾸면 상체 각도를 기립근으로 버티지 않아도 된다. 같은 자극에 허리 비용만 빠진다.</t>
-  </si>
-  <si>
-    <t>· 트랩바 슈러그만 선 자세 등척성이 걸린다. 허리가 무거운 주에는 머신 슈러그로 바꾼다.</t>
-  </si>
-  <si>
-    <t>· 27세트 · 약 67분. 세 블록이지만 각 블록이 작아 중간 크기다.</t>
+    <t>· 등(수평 12) → 가슴(중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
+  </si>
+  <si>
+    <t>· 팔이 맨 뒤인 이유 — 앞의 12세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
+  </si>
+  <si>
+    <t>· 26세트 · 약 64분. 세 블록이지만 각 블록이 작아 중간 크기다.</t>
   </si>
   <si>
     <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다.</t>
@@ -3727,10 +3748,13 @@
     <t>· 펙덱 플라이에는 걸지 않는다 — 디클라인 플라이 드롭과 같은 근육 · 같은 세션이라 겹친다(2026-09-14 판단 유지).</t>
   </si>
   <si>
-    <t>· 스미스 바벨 로우 · 트랩바 슈러그에는 걸지 않는다. 척추가 버티는 종목이다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고</t>
+    <t>· 트랩바 슈러그에는 걸지 않는다. 선 자세로 중량을 받치는 종목이다.</t>
+  </si>
+  <si>
+    <t>· 원암 케이블 로우에도 걸지 않는다 — 좌우 따로라 +120초가 된다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야</t>
   </si>
   <si>
     <t>복귀판 간접 세트 계수 맵 — 복귀_세트검산 간접 열(C)의 계산 원천</t>
@@ -3766,7 +3790,7 @@
     <t>오버헤드 프레스 삼두 신전 — 5×5 저반복 본세트 하향. 머신 숄더 프레스(0.5)와 구분. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
-    <t>복귀_일_등광배</t>
+    <t>복귀_일_당기기A</t>
   </si>
   <si>
     <t>뒤침 그립 — 이두가 유리한 자리에서 능동 굴곡. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
@@ -3778,12 +3802,12 @@
     <t>엎침 그립 수직 당기기. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
   </si>
   <si>
+    <t>복귀_목_당기기B</t>
+  </si>
+  <si>
     <t>좁은 뉴트럴 그립 — 엎침과 뒤침 사이. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
   </si>
   <si>
-    <t>복귀_목_등승모</t>
-  </si>
-  <si>
     <t>엎침 그립 수평 로우. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
   </si>
   <si>
@@ -3940,19 +3964,19 @@
     <t>직접 16세트: 월요일 벤치 5 · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 4. 간접 0.8 — 인클라인 덤벨 플라이 0.2×4 (인클라인 머신의 교차 간접은 2026-10-02에 0으로). 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
   </si>
   <si>
-    <t>직접 14세트: 일요일 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 3 · 원암 케이블 로우 3. 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3. 15 → 14는 날을 가르며 생긴 1세트 차이다</t>
+    <t>직접 14세트: 일요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 3 + 목요일(수평) 원암 케이블 로우 3. 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3. [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 목요일 로우가 전부 광배를 쓰고 있었다</t>
   </si>
   <si>
     <t>등 합산</t>
   </si>
   <si>
-    <t>직접 3세트: 목요일 트랩바 슈러그 3 (2026-10-02 신설). 간접 1.4 — 오버헤드 프레스 · 스미스 바벨 로우 각 0.2 (데드의 등척성 견갑대 유지는 2026-10-02에 0으로). 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
-  </si>
-  <si>
-    <t>직접 3세트: 일요일 오버헤드 슈러그 3. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
-  </si>
-  <si>
-    <t>직접 13세트: 목요일 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 토요일 페이스풀 3. [2026-10-02 사용자 제안] 주 1회(목요일)로 남아 있던 유일한 큰 부위라 토요일에 3세트를 더해 주 2회로 쪼갰다. 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
+    <t>직접 3세트: 목요일(수평) 트랩바 슈러그 3 — 재택도 수평 날(6일차)에 둔다 (2026-10-02 신설). 간접 1.4 — 오버헤드 프레스 · 스미스 바벨 로우 각 0.2 (데드의 등척성 견갑대 유지는 2026-10-02에 0으로). 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
+  </si>
+  <si>
+    <t>직접 3세트: 일요일(수직) 오버헤드 슈러그 3 — 팔이 머리 위라 수직 날에 맞는다. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
+  </si>
+  <si>
+    <t>직접 13세트: 일요일(수직) 스미스 바벨 로우 4 · 페이스풀 3 + 목요일(수평) 해머 스트랭스 로우 3 · 스캡 슈러그 3. 7/6으로 두 날에 고르게 나뉜다 — 재택(7/8)과 같은 모양이고 바벨 로우를 수직 날에 두는 것도 재택을 따랐다. 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
   </si>
   <si>
     <t>직접 3세트: 수요일 데드 톱 1 + 백오프 2 (2026-10-02 백오프 복귀). 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
@@ -3964,7 +3988,7 @@
     <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.0 — 오버헤드 프레스 0.33×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
   </si>
   <si>
-    <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 1.5 — 토요일 페이스풀 0.5×3(2026-10-02). 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블 · 로프로 저항곡선과 외회전 요소를 갈랐다</t>
+    <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 1.5 — 일요일 페이스풀 0.5×3(2026-10-02). 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블 · 로프로 저항곡선과 외회전 요소를 갈랐다</t>
   </si>
   <si>
     <t>직접 12세트: 토요일 스쿼트 5 · 레그 프레스 4 · 레그 익스텐션 3. 간접 1.3 — 수요일 레그 프레스(발 높게) 0.33×4. 직접은 주 1회다(스쿼트 5×5가 한 날을 다 쓴다) — 다만 수요일 간접 덕에 자극 노출은 주 2회가 됐다 (2026-10-02)</t>
@@ -11050,7 +11074,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11114,8 +11138,8 @@
         <v>916</v>
       </c>
       <c r="E6" s="121">
-        <f>복귀_토_하체전면!$E$31</f>
-        <v>41</v>
+        <f>복귀_토_하체전면!$E$30</f>
+        <v>38</v>
       </c>
       <c r="F6" s="114" t="s">
         <v>917</v>
@@ -11138,8 +11162,8 @@
         <v>921</v>
       </c>
       <c r="E7" s="121">
-        <f>복귀_일_등광배!$E$18</f>
-        <v>23</v>
+        <f>복귀_일_당기기A!$E$19</f>
+        <v>27</v>
       </c>
       <c r="F7" s="114" t="s">
         <v>922</v>
@@ -11234,8 +11258,8 @@
         <v>941</v>
       </c>
       <c r="E11" s="121">
-        <f>복귀_목_등승모!$E$19</f>
-        <v>27</v>
+        <f>복귀_목_당기기B!$E$19</f>
+        <v>26</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>942</v>
@@ -11318,23 +11342,23 @@
         <v>953</v>
       </c>
     </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="123" t="s">
+        <v>954</v>
+      </c>
+    </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="107" t="s">
-        <v>954</v>
+      <c r="A23" s="123" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="123" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="123" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="107" t="s">
         <v>957</v>
       </c>
     </row>
@@ -11358,53 +11382,53 @@
         <v>961</v>
       </c>
     </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="123" t="s">
+        <v>962</v>
+      </c>
+    </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="107" t="s">
-        <v>962</v>
+      <c r="A32" s="123" t="s">
+        <v>963</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="123" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="123" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="123" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="123" t="s">
+      <c r="A36" s="107" t="s">
         <v>966</v>
       </c>
     </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="123" t="s">
+        <v>967</v>
+      </c>
+    </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="107" t="s">
-        <v>967</v>
+      <c r="A38" s="123" t="s">
+        <v>968</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="123" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="123" t="s">
+      <c r="A42" s="107" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11413,28 +11437,28 @@
         <v>972</v>
       </c>
     </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="123" t="s">
+        <v>973</v>
+      </c>
+    </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="107" t="s">
-        <v>973</v>
+      <c r="A45" s="123" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="123" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="123" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="123" t="s">
+      <c r="A49" s="107" t="s">
         <v>977</v>
       </c>
     </row>
@@ -11443,29 +11467,49 @@
         <v>978</v>
       </c>
     </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="123" t="s">
+        <v>979</v>
+      </c>
+    </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="107" t="s">
-        <v>979</v>
+      <c r="A52" s="123" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="123" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="123" t="s">
+      <c r="A56" s="107" t="s">
         <v>983</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="123" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="123" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="123" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="123" t="s">
+        <v>987</v>
       </c>
     </row>
   </sheetData>
@@ -11476,7 +11520,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -11496,7 +11540,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11577,22 +11621,22 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="110" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="110" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11676,14 +11720,14 @@
         <v>180</v>
       </c>
       <c r="I20" s="112">
-        <f t="shared" ref="I20:I30" si="0">IF(E20=0,0,ROUND((E20*(G20+H20)+N20)/60,1))</f>
+        <f t="shared" ref="I20:I29" si="0">IF(E20=0,0,ROUND((E20*(G20+H20)+N20)/60,1))</f>
         <v>17.5</v>
       </c>
       <c r="J20" s="113" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="K20" s="113" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="L20" s="112" t="s">
         <v>356</v>
@@ -11721,10 +11765,10 @@
         <v>13</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -11760,10 +11804,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -11801,7 +11845,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="K23" s="115" t="s">
         <v>597</v>
@@ -11840,10 +11884,10 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -11856,7 +11900,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>372</v>
@@ -11881,10 +11925,10 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -11897,49 +11941,51 @@
         <v>7</v>
       </c>
       <c r="B26" s="115" t="s">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="C26" s="114" t="s">
-        <v>296</v>
+        <v>398</v>
       </c>
       <c r="D26" s="114">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="E26" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="114" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="G26" s="114">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H26" s="114">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I26" s="114">
         <f t="shared" si="0"/>
-        <v>5.3</v>
+        <v>11.9</v>
       </c>
       <c r="J26" s="115" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="K26" s="115" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="L26" s="114"/>
       <c r="M26" s="114"/>
-      <c r="N26" s="114"/>
+      <c r="N26" s="114">
+        <v>75</v>
+      </c>
     </row>
     <row r="27" spans="1:14" ht="30" customHeight="1">
       <c r="A27" s="114">
         <v>8</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C27" s="114" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D27" s="114">
         <v>40</v>
@@ -11948,39 +11994,39 @@
         <v>4</v>
       </c>
       <c r="F27" s="114" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="G27" s="114">
         <v>40</v>
       </c>
       <c r="H27" s="114">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="I27" s="114">
         <f t="shared" si="0"/>
-        <v>11.9</v>
+        <v>3.3</v>
       </c>
       <c r="J27" s="115" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="K27" s="115" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="L27" s="114"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114">
-        <v>75</v>
-      </c>
+      <c r="M27" s="114" t="s">
+        <v>405</v>
+      </c>
+      <c r="N27" s="114"/>
     </row>
     <row r="28" spans="1:14" ht="30" customHeight="1">
       <c r="A28" s="114">
         <v>9</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C28" s="114" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D28" s="114">
         <v>40</v>
@@ -11995,17 +12041,17 @@
         <v>40</v>
       </c>
       <c r="H28" s="114">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I28" s="114">
         <f t="shared" si="0"/>
-        <v>3.3</v>
+        <v>10.7</v>
       </c>
       <c r="J28" s="115" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="K28" s="115" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
@@ -12018,16 +12064,16 @@
         <v>10</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>406</v>
+        <v>502</v>
       </c>
       <c r="C29" s="114" t="s">
-        <v>407</v>
+        <v>322</v>
       </c>
       <c r="D29" s="114">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E29" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="114" t="s">
         <v>303</v>
@@ -12036,160 +12082,119 @@
         <v>40</v>
       </c>
       <c r="H29" s="114">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="I29" s="114">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>5.8</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="L29" s="114"/>
-      <c r="M29" s="114" t="s">
-        <v>405</v>
-      </c>
+      <c r="M29" s="114"/>
       <c r="N29" s="114"/>
     </row>
-    <row r="30" spans="1:14" ht="30" customHeight="1">
-      <c r="A30" s="114">
-        <v>11</v>
-      </c>
-      <c r="B30" s="115" t="s">
-        <v>502</v>
-      </c>
-      <c r="C30" s="114" t="s">
-        <v>322</v>
-      </c>
-      <c r="D30" s="114">
-        <v>8</v>
-      </c>
-      <c r="E30" s="114">
-        <v>3</v>
-      </c>
-      <c r="F30" s="114" t="s">
-        <v>303</v>
-      </c>
-      <c r="G30" s="114">
-        <v>40</v>
-      </c>
-      <c r="H30" s="114">
-        <v>75</v>
-      </c>
-      <c r="I30" s="114">
-        <f t="shared" si="0"/>
-        <v>5.8</v>
-      </c>
-      <c r="J30" s="115" t="s">
-        <v>1009</v>
-      </c>
-      <c r="K30" s="115" t="s">
-        <v>1010</v>
-      </c>
-      <c r="L30" s="114"/>
-      <c r="M30" s="114"/>
-      <c r="N30" s="114"/>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="116"/>
-      <c r="B31" s="116"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116" t="s">
+    <row r="30" spans="1:14">
+      <c r="A30" s="116"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E31" s="116">
-        <f>SUM(E20:E30)</f>
-        <v>41</v>
-      </c>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="116">
-        <f>ROUND(SUM(I20:I30),0)</f>
-        <v>100</v>
+      <c r="E30" s="116">
+        <f>SUM(E20:E29)</f>
+        <v>38</v>
+      </c>
+      <c r="F30" s="116"/>
+      <c r="G30" s="116"/>
+      <c r="H30" s="116"/>
+      <c r="I30" s="116">
+        <f>ROUND(SUM(I20:I29),0)</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="107" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="107" t="s">
-        <v>1011</v>
+      <c r="A33" s="117" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="117" t="s">
-        <v>1017</v>
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="107" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="107" t="s">
-        <v>973</v>
+      <c r="A41" s="117" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="117" t="s">
-        <v>1020</v>
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="107" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="107" t="s">
-        <v>1021</v>
+      <c r="A46" s="117" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="117" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="C51" s="118" t="s">
-        <v>1025</v>
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" s="118" t="s">
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
@@ -12200,7 +12205,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12220,27 +12225,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12318,17 +12323,17 @@
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I17" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <f t="shared" ref="I11:I18" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -12338,7 +12343,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
@@ -12363,10 +12368,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -12377,7 +12382,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
@@ -12402,10 +12407,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -12418,37 +12423,39 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>486</v>
+        <v>1041</v>
       </c>
       <c r="C14" s="114" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D14" s="114">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E14" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G14" s="114">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H14" s="114">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I14" s="114">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12.7</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1040</v>
-      </c>
-      <c r="L14" s="114"/>
+        <v>1043</v>
+      </c>
+      <c r="L14" s="114" t="s">
+        <v>1034</v>
+      </c>
       <c r="M14" s="114"/>
       <c r="N14" s="114"/>
     </row>
@@ -12457,13 +12464,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="115" t="s">
-        <v>431</v>
+        <v>302</v>
       </c>
       <c r="C15" s="114" t="s">
-        <v>432</v>
+        <v>296</v>
       </c>
       <c r="D15" s="114">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="E15" s="114">
         <v>3</v>
@@ -12472,20 +12479,20 @@
         <v>303</v>
       </c>
       <c r="G15" s="114">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H15" s="114">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I15" s="114">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -12496,19 +12503,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>359</v>
+        <v>432</v>
       </c>
       <c r="D16" s="114">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E16" s="114">
         <v>3</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="G16" s="114">
         <v>40</v>
@@ -12518,32 +12525,30 @@
       </c>
       <c r="I16" s="114">
         <f t="shared" si="0"/>
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
-      <c r="N16" s="114">
-        <v>60</v>
-      </c>
+      <c r="N16" s="114"/>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1">
       <c r="A17" s="114">
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>495</v>
+        <v>375</v>
       </c>
       <c r="C17" s="114" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="D17" s="114">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E17" s="114">
         <v>3</v>
@@ -12562,10 +12567,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12573,113 +12578,164 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="116"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116" t="s">
+    <row r="18" spans="1:14" ht="30" customHeight="1">
+      <c r="A18" s="114">
+        <v>8</v>
+      </c>
+      <c r="B18" s="115" t="s">
+        <v>495</v>
+      </c>
+      <c r="C18" s="114" t="s">
+        <v>283</v>
+      </c>
+      <c r="D18" s="114">
+        <v>30</v>
+      </c>
+      <c r="E18" s="114">
+        <v>3</v>
+      </c>
+      <c r="F18" s="114" t="s">
+        <v>288</v>
+      </c>
+      <c r="G18" s="114">
+        <v>40</v>
+      </c>
+      <c r="H18" s="114">
+        <v>75</v>
+      </c>
+      <c r="I18" s="114">
+        <f t="shared" si="0"/>
+        <v>6.8</v>
+      </c>
+      <c r="J18" s="115" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K18" s="115" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="116"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E18" s="116">
-        <f>SUM(E11:E17)</f>
-        <v>23</v>
-      </c>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="116">
-        <f>ROUND(SUM(I11:I17),0)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="107" t="s">
-        <v>1047</v>
+      <c r="E19" s="116">
+        <f>SUM(E11:E18)</f>
+        <v>27</v>
+      </c>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116">
+        <f>ROUND(SUM(I11:I18),0)</f>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="117" t="s">
-        <v>1048</v>
+      <c r="A21" s="107" t="s">
+        <v>1052</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="117" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="107" t="s">
-        <v>1052</v>
+        <v>952</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="117" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="117" t="s">
-        <v>1012</v>
+      <c r="A27" s="107" t="s">
+        <v>1056</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1053</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="107" t="s">
-        <v>973</v>
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="117" t="s">
+        <v>1059</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="117" t="s">
-        <v>1056</v>
+      <c r="A33" s="107" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1057</v>
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="117" t="s">
+        <v>1061</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="107" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="117" t="s">
-        <v>1058</v>
+      <c r="A36" s="117" t="s">
+        <v>1062</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="117" t="s">
-        <v>1059</v>
+      <c r="A38" s="107" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1024</v>
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="117" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="C41" s="118" t="s">
-        <v>1060</v>
+      <c r="A41" s="117" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="117" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="C44" s="118" t="s">
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -12710,7 +12766,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12796,7 +12852,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12884,10 +12940,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="113" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="K18" s="113" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="L18" s="112" t="s">
         <v>356</v>
@@ -12925,10 +12981,10 @@
         <v>12.7</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -12964,10 +13020,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13003,13 +13059,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="L21" s="114" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13019,13 +13075,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="E22" s="114">
         <v>3</v>
@@ -13044,10 +13100,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13064,7 +13120,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
@@ -13083,10 +13139,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13113,77 +13169,77 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="118" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
     </row>
   </sheetData>
@@ -13214,22 +13270,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13316,10 +13372,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13357,10 +13413,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13396,10 +13452,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -13410,7 +13466,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>309</v>
@@ -13435,10 +13491,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -13474,10 +13530,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -13488,7 +13544,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>939</v>
@@ -13513,10 +13569,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -13527,7 +13583,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>939</v>
@@ -13552,10 +13608,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -13591,10 +13647,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -13630,10 +13686,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13660,87 +13716,87 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="C42" s="118" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -14452,7 +14508,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14533,7 +14589,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14609,22 +14665,22 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="110" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -14712,10 +14768,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -14726,7 +14782,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -14752,10 +14808,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -14772,7 +14828,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -14791,10 +14847,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -14805,7 +14861,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -14830,10 +14886,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -14869,10 +14925,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -14883,7 +14939,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -14909,10 +14965,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -14950,10 +15006,10 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="K34" s="115" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="L34" s="114"/>
       <c r="M34" s="114"/>
@@ -14991,10 +15047,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15030,10 +15086,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15069,10 +15125,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15108,10 +15164,10 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="K38" s="115" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
@@ -15149,10 +15205,10 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
@@ -15190,10 +15246,10 @@
         <v>5.8</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15220,167 +15276,167 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="107" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="107" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="117" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
     </row>
   </sheetData>
@@ -15391,7 +15447,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -15411,27 +15467,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15488,16 +15544,16 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1192</v>
+        <v>479</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>296</v>
       </c>
       <c r="D11" s="114">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E11" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>298</v>
@@ -15510,16 +15566,16 @@
       </c>
       <c r="I11" s="114">
         <f t="shared" ref="I11:I18" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
-        <v>12.7</v>
+        <v>9.5</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1032</v>
+        <v>1200</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -15529,35 +15585,35 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C12" s="114" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D12" s="114">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E12" s="114">
         <v>3</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G12" s="114">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H12" s="114">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I12" s="114">
         <f t="shared" si="0"/>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15593,10 +15649,10 @@
         <v>6.8</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15634,10 +15690,10 @@
         <v>6.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15673,10 +15729,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -15712,10 +15768,10 @@
         <v>10.7</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -15728,7 +15784,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>359</v>
@@ -15753,10 +15809,10 @@
         <v>5.5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -15767,7 +15823,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>283</v>
@@ -15792,10 +15848,10 @@
         <v>5.8</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -15810,99 +15866,109 @@
       </c>
       <c r="E19" s="116">
         <f>SUM(E11:E18)</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="116"/>
       <c r="G19" s="116"/>
       <c r="H19" s="116"/>
       <c r="I19" s="116">
         <f>ROUND(SUM(I11:I18),0)</f>
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="107" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="117" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="107" t="s">
-        <v>1215</v>
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="117" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="117" t="s">
-        <v>1216</v>
+      <c r="A27" s="107" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="107" t="s">
-        <v>973</v>
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="117" t="s">
+        <v>1225</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="117" t="s">
-        <v>1219</v>
+      <c r="A32" s="107" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="107" t="s">
-        <v>1021</v>
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="117" t="s">
+        <v>1227</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="117" t="s">
-        <v>1221</v>
+      <c r="A36" s="107" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1024</v>
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="117" t="s">
+        <v>1231</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="C41" s="118" t="s">
-        <v>1224</v>
+      <c r="A41" s="117" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="C43" s="118" t="s">
+        <v>1232</v>
       </c>
     </row>
   </sheetData>
@@ -16303,12 +16369,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16322,12 +16388,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16353,7 +16419,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16376,12 +16442,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16404,12 +16470,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16432,12 +16498,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16460,15 +16526,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16488,12 +16554,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -16516,15 +16582,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -16544,15 +16610,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -16572,12 +16638,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -16600,15 +16666,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1240</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1192</v>
+        <v>1041</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>283</v>
@@ -16628,12 +16694,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -16656,12 +16722,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -16684,12 +16750,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -16712,12 +16778,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -16740,12 +16806,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -16768,12 +16834,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -16796,12 +16862,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -16824,12 +16890,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1233</v>
+        <v>1244</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>302</v>
@@ -16852,15 +16918,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>368</v>
@@ -16880,12 +16946,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.25">
       <c r="A26" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>522</v>
@@ -16908,15 +16974,15 @@
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>383</v>
@@ -16936,15 +17002,15 @@
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="114" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>1192</v>
+        <v>1041</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>281</v>
@@ -16964,12 +17030,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>479</v>
@@ -16992,12 +17058,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>95</v>
@@ -17020,15 +17086,15 @@
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>421</v>
@@ -17048,15 +17114,15 @@
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>1192</v>
+        <v>1041</v>
       </c>
       <c r="C32" s="114" t="s">
         <v>421</v>
@@ -17076,12 +17142,12 @@
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25.5">
       <c r="A33" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>95</v>
@@ -17104,12 +17170,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>280</v>
@@ -17132,15 +17198,15 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>432</v>
@@ -17160,15 +17226,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17188,12 +17254,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5">
       <c r="A37" s="114" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>479</v>
@@ -17216,12 +17282,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="38.25">
       <c r="A38" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>424</v>
@@ -17244,12 +17310,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>537</v>
@@ -17272,15 +17338,15 @@
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C40" s="114" t="s">
         <v>296</v>
@@ -17300,12 +17366,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>486</v>
@@ -17328,12 +17394,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
       <c r="A42" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>93</v>
@@ -17356,15 +17422,15 @@
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>1192</v>
+        <v>1041</v>
       </c>
       <c r="C43" s="114" t="s">
         <v>327</v>
@@ -17384,12 +17450,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>431</v>
@@ -17412,12 +17478,12 @@
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="51">
       <c r="A45" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>573</v>
@@ -17440,12 +17506,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B46" s="115" t="s">
         <v>498</v>
@@ -17468,12 +17534,12 @@
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>93</v>
@@ -17501,7 +17567,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>95</v>
@@ -17524,15 +17590,15 @@
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -17552,12 +17618,12 @@
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>388</v>
@@ -17585,7 +17651,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>573</v>
@@ -17608,12 +17674,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>570</v>
@@ -17636,12 +17702,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25">
       <c r="A53" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>95</v>
@@ -17664,15 +17730,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
@@ -17692,15 +17758,15 @@
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51">
       <c r="A55" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
@@ -17720,12 +17786,12 @@
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>93</v>
@@ -17748,12 +17814,12 @@
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>388</v>
@@ -17776,15 +17842,15 @@
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25.5">
       <c r="A58" s="114" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -17804,12 +17870,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="114" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B59" s="115" t="s">
         <v>495</v>
@@ -17837,7 +17903,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>605</v>
@@ -17865,10 +17931,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -17888,12 +17954,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="38.25">
       <c r="A62" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>97</v>
@@ -17916,12 +17982,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B63" s="115" t="s">
         <v>441</v>
@@ -17944,12 +18010,12 @@
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>531</v>
@@ -17972,12 +18038,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>600</v>
@@ -18000,12 +18066,12 @@
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>93</v>
@@ -18028,12 +18094,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>502</v>
@@ -18056,15 +18122,15 @@
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="C68" s="114" t="s">
         <v>939</v>
@@ -18084,7 +18150,7 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
   </sheetData>
@@ -18109,12 +18175,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18142,7 +18208,7 @@
         <v>363</v>
       </c>
       <c r="B5" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A5)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A5)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A5)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A5)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A5)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A5)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A5)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A5)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A5)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A5)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A5)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A5)</f>
         <v>8</v>
       </c>
       <c r="C5" s="114">
@@ -18158,7 +18224,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -18173,7 +18239,7 @@
         <v>351</v>
       </c>
       <c r="B6" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A6)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A6)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A6)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A6)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A6)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A6)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A6)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A6)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A6)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A6)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A6)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A6)</f>
         <v>16</v>
       </c>
       <c r="C6" s="114">
@@ -18189,7 +18255,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18197,7 +18263,7 @@
         <v>281</v>
       </c>
       <c r="B7" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A7)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A7)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A7)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A7)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A7)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A7)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A7)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A7)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A7)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A7)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A7)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A7)</f>
         <v>14</v>
       </c>
       <c r="C7" s="114">
@@ -18213,10 +18279,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -18228,7 +18294,7 @@
         <v>421</v>
       </c>
       <c r="B8" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A8)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A8)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A8)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A8)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A8)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A8)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A8)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A8)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A8)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A8)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A8)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A8)</f>
         <v>3</v>
       </c>
       <c r="C8" s="114">
@@ -18244,7 +18310,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18252,7 +18318,7 @@
         <v>432</v>
       </c>
       <c r="B9" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A9)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A9)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A9)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A9)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A9)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A9)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A9)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A9)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A9)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A9)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A9)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A9)</f>
         <v>3</v>
       </c>
       <c r="C9" s="114">
@@ -18268,7 +18334,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18276,7 +18342,7 @@
         <v>296</v>
       </c>
       <c r="B10" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A10)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A10)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A10)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A10)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A10)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A10)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A10)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A10)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A10)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A10)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A10)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A10)</f>
         <v>13</v>
       </c>
       <c r="C10" s="114">
@@ -18292,7 +18358,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18300,7 +18366,7 @@
         <v>327</v>
       </c>
       <c r="B11" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A11)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A11)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A11)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A11)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A11)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A11)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A11)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A11)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A11)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A11)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A11)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A11)</f>
         <v>3</v>
       </c>
       <c r="C11" s="114">
@@ -18316,7 +18382,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18324,7 +18390,7 @@
         <v>443</v>
       </c>
       <c r="B12" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A12)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A12)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A12)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A12)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A12)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A12)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A12)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A12)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A12)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A12)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A12)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A12)</f>
         <v>6</v>
       </c>
       <c r="C12" s="114">
@@ -18340,7 +18406,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18348,7 +18414,7 @@
         <v>368</v>
       </c>
       <c r="B13" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A13)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A13)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A13)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A13)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A13)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A13)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A13)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A13)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A13)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A13)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A13)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A13)</f>
         <v>10</v>
       </c>
       <c r="C13" s="114">
@@ -18364,7 +18430,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18372,7 +18438,7 @@
         <v>372</v>
       </c>
       <c r="B14" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A14)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A14)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A14)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A14)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A14)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A14)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A14)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A14)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A14)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A14)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A14)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A14)</f>
         <v>10</v>
       </c>
       <c r="C14" s="114">
@@ -18388,7 +18454,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18396,7 +18462,7 @@
         <v>383</v>
       </c>
       <c r="B15" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A15)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A15)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A15)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A15)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A15)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A15)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A15)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A15)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A15)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A15)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A15)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A15)</f>
         <v>12</v>
       </c>
       <c r="C15" s="114">
@@ -18412,10 +18478,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18427,7 +18493,7 @@
         <v>398</v>
       </c>
       <c r="B16" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A16)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A16)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A16)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A16)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A16)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A16)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A16)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A16)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A16)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A16)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A16)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A16)</f>
         <v>10</v>
       </c>
       <c r="C16" s="114">
@@ -18443,7 +18509,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18451,7 +18517,7 @@
         <v>389</v>
       </c>
       <c r="B17" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A17)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A17)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A17)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A17)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A17)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A17)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A17)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A17)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A17)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A17)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A17)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A17)</f>
         <v>7</v>
       </c>
       <c r="C17" s="114">
@@ -18467,7 +18533,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18475,7 +18541,7 @@
         <v>407</v>
       </c>
       <c r="B18" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A18)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A18)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A18)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A18)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A18)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A18)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A18)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A18)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A18)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A18)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A18)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A18)</f>
         <v>11</v>
       </c>
       <c r="C18" s="114">
@@ -18491,7 +18557,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18499,7 +18565,7 @@
         <v>322</v>
       </c>
       <c r="B19" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A19)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A19)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A19)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A19)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A19)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A19)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A19)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A19)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A19)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A19)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A19)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A19)</f>
         <v>6</v>
       </c>
       <c r="C19" s="114">
@@ -18515,7 +18581,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18523,7 +18589,7 @@
         <v>283</v>
       </c>
       <c r="B20" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A20)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A20)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A20)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A20)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A20)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A20)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A20)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A20)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A20)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A20)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A20)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A20)</f>
         <v>9</v>
       </c>
       <c r="C20" s="114">
@@ -18539,7 +18605,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18547,7 +18613,7 @@
         <v>359</v>
       </c>
       <c r="B21" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A21)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A21)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A21)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A21)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A21)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A21)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A21)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A21)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A21)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A21)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A21)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A21)</f>
         <v>9</v>
       </c>
       <c r="C21" s="114">
@@ -18563,7 +18629,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18571,7 +18637,7 @@
         <v>309</v>
       </c>
       <c r="B22" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A22)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A22)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A22)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A22)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A22)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A22)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A22)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A22)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A22)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A22)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A22)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A22)</f>
         <v>9</v>
       </c>
       <c r="C22" s="114">
@@ -18587,7 +18653,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18595,7 +18661,7 @@
         <v>313</v>
       </c>
       <c r="B23" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A23)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A23)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A23)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A23)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A23)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A23)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A23)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A23)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A23)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A23)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A23)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A23)</f>
         <v>6</v>
       </c>
       <c r="C23" s="114">
@@ -18611,7 +18677,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18619,7 +18685,7 @@
         <v>402</v>
       </c>
       <c r="B24" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A24)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A24)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A24)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A24)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A24)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A24)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A24)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A24)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A24)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A24)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A24)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A24)</f>
         <v>8</v>
       </c>
       <c r="C24" s="114">
@@ -18635,7 +18701,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18643,7 +18709,7 @@
         <v>939</v>
       </c>
       <c r="B25" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A25)+SUMIFS(복귀_일_등광배!$E:$E,복귀_일_등광배!$C:$C,$A25)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A25)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A25)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A25)+SUMIFS(복귀_목_등승모!$E:$E,복귀_목_등승모!$C:$C,$A25)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A25)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A25)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A25)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A25)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A25)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A25)</f>
         <v>6</v>
       </c>
       <c r="C25" s="114">
@@ -18659,7 +18725,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18682,182 +18748,182 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="107" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2B26BDFD7D6256D6848844A04A6B0007F7B0B17E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E1692C7AA29BE27C0FC0ED6CBDF80B9074476154" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -29,11 +29,11 @@
     <sheet name="9월이후조정" sheetId="14" r:id="rId14"/>
     <sheet name="복귀_주간계획" sheetId="15" r:id="rId15"/>
     <sheet name="복귀_토_하체전면" sheetId="16" r:id="rId16"/>
-    <sheet name="복귀_일_당기기A" sheetId="17" r:id="rId17"/>
+    <sheet name="복귀_일_수평당기기" sheetId="17" r:id="rId17"/>
     <sheet name="복귀_월_가슴" sheetId="18" r:id="rId18"/>
     <sheet name="복귀_화_팔" sheetId="19" r:id="rId19"/>
     <sheet name="복귀_수_하체후면" sheetId="20" r:id="rId20"/>
-    <sheet name="복귀_목_당기기B" sheetId="21" r:id="rId21"/>
+    <sheet name="복귀_목_수직당기기" sheetId="21" r:id="rId21"/>
     <sheet name="복귀_증량원칙" sheetId="22" r:id="rId22"/>
     <sheet name="복귀_간접계수맵" sheetId="23" r:id="rId23"/>
     <sheet name="복귀_세트검산" sheetId="24" r:id="rId24"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="1359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="1367">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -2818,16 +2818,16 @@
     <t>일</t>
   </si>
   <si>
-    <t>당기기 A</t>
-  </si>
-  <si>
-    <t>등 수직 당기기 · 팔 삼두/이두</t>
-  </si>
-  <si>
-    <t>약 69분</t>
-  </si>
-  <si>
-    <t>메인 리프트 없음. 당기기 18세트 뒤 팔 6 — 프레스가 하나도 없어 삼두 간접이 0인 유일한 날. 척추로 버티는 유일한 로우(스미스 바벨 로우)와 페이스풀이 이 날에 있다</t>
+    <t>당기기 수평</t>
+  </si>
+  <si>
+    <t>등 수평 당기기 · 팔 삼두/이두</t>
+  </si>
+  <si>
+    <t>약 58분</t>
+  </si>
+  <si>
+    <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 블록이 둘(등 16 · 팔 6)뿐이고 가슴이 없다</t>
   </si>
   <si>
     <t>월</t>
@@ -2878,16 +2878,16 @@
     <t>목</t>
   </si>
   <si>
-    <t>당기기 B + 가슴 B</t>
-  </si>
-  <si>
-    <t>등 수평 당기기 · 가슴(중하부) · 팔</t>
-  </si>
-  <si>
-    <t>약 64분</t>
-  </si>
-  <si>
-    <t>세 블록. 데드 다음날이라 로우를 전부 체스트 서포티드 · 궤도 고정 · 편측 케이블로 골랐다 — 척추로 버티는 로우는 일요일에 있다</t>
+    <t>당기기 수직 + 가슴 B</t>
+  </si>
+  <si>
+    <t>등 수직 당기기 · 가슴(중하부) · 팔</t>
+  </si>
+  <si>
+    <t>약 75분</t>
+  </si>
+  <si>
+    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로</t>
   </si>
   <si>
     <t>금</t>
@@ -2908,7 +2908,7 @@
     <t>· 어깨는 토 · 월 · 수, 팔은 일 · 화 · 목. 이틀 간격으로 정확히 엇갈려 어느 쪽도 이틀 연속이 되지 않는다.</t>
   </si>
   <si>
-    <t>· 큰 부위 셋을 둘로 쪼갰다 — 하체는 전면(토) / 후면(수), 등은 수직(일) / 수평(목), 가슴은 상부(월) / 중하부(목).</t>
+    <t>· 큰 부위 셋을 둘로 쪼갰다 — 하체는 전면(토) / 후면(수), 등은 수평(일) / 수직(목), 가슴은 상부(월) / 중하부(목).</t>
   </si>
   <si>
     <t>· [2026-10-02 정정] 등을 가른 축은 움직임 평면이다 — 재택 1일차 '당기기 A (수직)' · 6일차 '당기기 B (수평)'과 같다(사용자 지정). 초안에서는 근육군으로 갈랐고(일=광배 전담 · 목=승모중부 전담) 그 근거로 2026-09-04 '주동근은 팔꿈치 경로가 정한다'를 들었는데, 그 원칙은 세트검산의 근육군 분류 규칙이고 날을 어떻게 가르라는 말이 아니었다 — 두 축을 뒤섞은 것이다.</t>
@@ -2917,10 +2917,19 @@
     <t>· 평면 분할이 실제로 더 맞다. 근육군으로 가르면 '광배 주 1회'로 적히지만 목요일 로우 셋이 전부 광배를 쓴다(간접계수맵에 광배 0.5가 달려 있다) — 어느 쪽도 쉬지 못하면서 장부상으로만 주 1회가 된다. 평면으로 가르면 어깨 신전 ↔ 수평 외전 + 견갑 후인이라는 실제로 다른 관절 동작이 갈린다.</t>
   </si>
   <si>
-    <t>· 그래서 두 날 모두 광배와 승모 중부가 섞여 있다 — 광배 일 11 / 목 3 · 승모 중부 일 7 / 목 6. 재택도 같은 모양이다(광배 9/4 · 승모 중부 7/8). 근육군은 여전히 팔꿈치 경로로 매긴다 — 날 분할과 근육군 분류는 다른 축이고 둘을 섞지 않는다. 발 높은 레그 프레스가 햄스트링이 아니라 둔근으로 계상되는 것이 후자의 예다.</t>
-  </si>
-  <si>
-    <t>· 재택이 바벨 로우를 수직 날에 두는 것까지 따랐다 — 승모 중부를 두 날에 고르게 나누기 때문이고, 복귀에서는 이득이 하나 더 붙는다: 척추로 버티는 유일한 로우가 데드 다음날(목)에서 빠진다.</t>
+    <t>· 그래서 두 날 모두 광배와 승모 중부가 섞여 있다 — 광배 일 3 / 목 11 · 승모 중부 일 10 / 목 3. 근육군은 여전히 팔꿈치 경로로 매긴다 — 날 분할과 근육군 분류는 다른 축이고 둘을 섞지 않는다. 발 높은 레그 프레스가 햄스트링이 아니라 둔근으로 계상되는 것이 후자의 예다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 같은 날 재배치] 어느 평면을 어느 날에 둘지는 사용자가 정했다 — '수평이 강도가 더 쎈 것 같아서 집중적으로 공략하고 싶다'. 일요일 = 수평 · 목요일 = 수직이다(재택은 순서가 반대다).</t>
+  </si>
+  <si>
+    <t>· 근거가 전날에 있다. 일요일은 토요일(하체 전면) 다음날이고 스쿼트는 등 · 그립 · 기립근을 쓰지 않아 등이 온전하다. 목요일은 수요일(데드 + 루마니안) 다음날이라 그 셋이 전부 지쳐 있다 — 거기서 무거운 로우를 치면 등이 아니라 그립과 허리가 먼저 막힌다.</t>
+  </si>
+  <si>
+    <t>· 결과로 무거운 로우 7세트(바벨 4 · 해머 3)가 데드 다음날에서 완전히 빠졌고, 목요일에 남은 당기기는 척추 부하가 거의 0이다. 주간 척추 부하 순서 — 토 스쿼트(높음) → 일 바벨 로우(중간) → 월 · 화 0 → 수 데드 + 루마니안(최고) → 목 수직 당기기(거의 0) → 금 휴식.</t>
+  </si>
+  <si>
+    <t>· 페이스풀만 수직 날에 남겼다 — 재택도 수직 날에 두고, 이것이 없으면 승모 중부가 일요일 주 1회가 된다.</t>
   </si>
   <si>
     <t>· [2026-10-02 보강] 햄스트링도 주 2회로 쪼갰다 — 토요일 4(레그 컬) + 수요일 6(루마니안 3 · 원 레그 컬 3). 사두만 주 1회로 남는데 스쿼트 5×5가 한 날을 다 쓰기 때문이다. 대신 수요일 레그 프레스가 사두에 간접 1.5세트치를 얹어 노출은 주 2회가 됐다.</t>
@@ -2941,7 +2950,7 @@
     <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). ④ 페이스풀 3 — 승모 중부 · 능형근에 견갑 후인 · 외회전을 더했다. 토요일에 넣었다가 같은 날 일요일(당기기 수직)로 옮겼다 — 재택도 당기기 날에 둔다. 164 → 168 → 176 → 179.</t>
   </si>
   <si>
-    <t>· ⑤ 같은 날 등 분할 축을 근육군 → 움직임 평면(수직 / 수평)으로 정정했다. 세트 총량 179와 부위별 숫자는 하나도 안 바뀌고 날 배치만 바뀌었다 — 원암 케이블 로우 일 → 목 · 스미스 바벨 로우 목 → 일.</t>
+    <t>· ⑤ 같은 날 등 분할 축을 근육군 → 움직임 평면으로 정정하고, 이어서 사용자 지정으로 평면을 요일에 배정했다 — 일요일 수평 · 목요일 수직. 세트 총량 179와 부위별 숫자는 하나도 안 바뀌고 날 배치만 바뀌었다.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -2992,7 +3001,7 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 수 39세트 98분 · 토 38세트 95분 · 일 27세트 69분 · 화 27세트 48분 · 목 26세트 64분 · 월 22세트 59분.</t>
+    <t>· 수 39세트 98분 · 토 38세트 95분 · 목 31세트 75분 · 화 27세트 48분 · 월 22세트 59분 · 일 22세트 58분.</t>
   </si>
   <si>
     <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
@@ -3001,6 +3010,9 @@
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
+    <t>· 등 블록 둘이 22(일) / 31(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등'). 일요일이 가장 작은 것은 의도다 — 무거운 로우 넷을 신선할 때 치는 날이라 뒤에 붙는 것을 줄였다.</t>
+  </si>
+  <si>
     <t>· 주 433분 = 7시간 13분. 주 4회 370분에서 63분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
@@ -3142,27 +3154,522 @@
     <t>[요청 원문 2026-10-02] 토요일부터 출발 · 토 하체 · 어깨 전면/후면/측면을 세트 후반부에 · 하체는 전면 후면 나누고  /  그래도 하체하는 날에 원레그컬 하나 정도는 있어야하는거 아냐???  /  아 원 레그 컬이랑 토요일 레그컬 자리 바꾸는거 어떻게 생각해?  /  토요일 페이스풀 넣는게 안 낫겠나?</t>
   </si>
   <si>
-    <t>일요일 — 당기기 A (수직) · 팔</t>
+    <t>일요일 — 당기기 (수평) · 팔</t>
   </si>
   <si>
     <t>웜업 (세트 카운트 제외)</t>
   </si>
   <si>
-    <t>· 이 날은 증량을 추적하는 메인 리프트가 없다. 첫 종목(친업) 전에 랫풀다운 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
+    <t>· 이 날은 증량을 추적하는 메인 리프트가 없다. 첫 종목(스미스 바벨 로우) 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
   </si>
   <si>
     <t>· 둘 다 근비대 항목이 아니라 관절 준비 항목이므로 세트 합계에 넣지 않는다.</t>
   </si>
   <si>
-    <t>수직 당기기 중 가장 무거운 쪽이라 맨 앞에 둔다. 그립이 지치면 주저 말고 어시스트 머신으로 간다 — 이 날 뒤쪽에 당기기가 10세트 더 있다.</t>
-  </si>
-  <si>
-    <t>어시스트 풀업 머신 (1순위 — 그립 부담 ↓) / 랫풀다운 / 뉴트럴 그립 친업</t>
+    <t>스미스 바벨 로우(오버그립)</t>
+  </si>
+  <si>
+    <t>수평 당기기 중 가장 무거운 쪽이라 맨 앞에 둔다. 넓은 엎침 그립 + 팔꿈치 벌림 — 주동근은 견갑 후인이다(2026-09-04 재분류). 궤도가 고정돼 상체 각도를 기립근으로 버티지 않아도 된다.</t>
+  </si>
+  <si>
+    <t>티바 로우 / 해머 스트랭스 로우 (허리가 무거운 주) / 체스트 서포티드 로우</t>
   </si>
   <si>
     <t>135/145/155/165</t>
   </si>
   <si>
+    <t>체스트 서포티드라 척추 부하가 0이다. 바벨 로우로 쓴 기립근을 더 쓰지 않고 수평 볼륨을 쌓는 자리다.</t>
+  </si>
+  <si>
+    <t>시티드 케이블 로우 (넓은 그립) / 머신 로우 / 티바 로우</t>
+  </si>
+  <si>
+    <t>135/150/165</t>
+  </si>
+  <si>
+    <t>팔꿈치를 몸에 붙여 당기는 경로라 주동근이 광배다 — 평면으로 날을 가르고 근육군은 팔꿈치 경로로 매긴다(2026-09-04 원칙). 좌우 독립이라 약한 쪽이 드러난다. 이 날 유일한 광배 직접이고 나머지 11세트는 목요일(수직)에 있다.</t>
+  </si>
+  <si>
+    <t>원암 해머 스트랭스 로우 / 원암 덤벨 로우 (벤치 지지) / 머신 로우</t>
+  </si>
+  <si>
+    <t>팔을 편 채 견갑만 후인한다 — 로우의 간접만으로는 능형근이 실패지점에 안 간다.</t>
+  </si>
+  <si>
+    <t>페이스풀 (로프) / 리버스 펙덱 (팔 편 채로)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 신설] 복귀판에 승모 상부 직접이 0이었다. 현장 근무가 하루치를 얹어주던 것이 끝났으므로 재택 6일차 종목을 그대로 가져왔다 — 재택도 수평 날에 둔다. 트랩바라 손이 몸 옆에 와 견갑 거상이 수직으로 나온다.</t>
+  </si>
+  <si>
+    <t>덤벨 슈러그 / 바벨 슈러그 (몸 앞 — 궤도가 약간 앞으로 간다) / 머신 슈러그</t>
+  </si>
+  <si>
+    <t>짧아진 구간. 당기기 뒤라 삼두가 전혀 쓰이지 않은 상태로 들어온다 — 팔을 세션 후반부에 두는 값이 이 날 가장 싸다.</t>
+  </si>
+  <si>
+    <t>케이블 오버헤드 익스텐션 (로프 · 장두 신전 구간) / V바 푸쉬다운</t>
+  </si>
+  <si>
+    <t>당기기 16세트 뒤라 이두가 이미 간접을 받았다. 중량이 평소보다 낮게 나오는 것이 정상이다.</t>
+  </si>
+  <si>
+    <t>케이블 컬 (전 구간 장력) / 머신 컬 / EZ바 프리쳐 컬</t>
+  </si>
+  <si>
+    <t>[무거운 수평 당기기를 이 날에 둔 이유 — 2026-10-02 사용자 지정]</t>
+  </si>
+  <si>
+    <t>· 사용자 판단 — '수평이 강도가 더 쎈 것 같아서 집중적으로 공략하고 싶다'. 맞는 감각이고 근거가 있다.</t>
+  </si>
+  <si>
+    <t>· 수평 로우가 실제로 무겁다(바벨 35 · 해머 45 vs 랫풀다운 · 친업). 그리고 **전날이 무엇이냐**가 더 크게 갈린다 — 일요일은 토요일(하체 전면) 다음날이고 스쿼트는 등 · 그립 · 기립근을 쓰지 않는다. 등이 온전한 상태로 들어온다.</t>
+  </si>
+  <si>
+    <t>· 반대로 목요일은 수요일(데드 + 루마니안) 다음날이라 그립 · 광배 · 기립근이 전부 지쳐 있다. 거기서 무거운 로우를 치면 등이 아니라 그립과 허리가 먼저 막힌다.</t>
+  </si>
+  <si>
+    <t>· 그래서 무거운 로우 7세트(바벨 4 · 해머 3)가 데드 다음날에서 완전히 빠졌다. 목요일에 남은 당기기는 수직(친업 · 랫풀다운)이고 척추 부하가 거의 0이다.</t>
+  </si>
+  <si>
+    <t>· 같은 이유로 이 날은 블록이 둘(수평 등 16 · 팔 6)뿐이다 — 가슴은 목요일에 남겼다(사용자 지정 '목요일 가슴/등'). 수평 당기기에만 집중하는 날이 됐다.</t>
+  </si>
+  <si>
+    <t>[등을 가른 축 — 움직임 평면이다]</t>
+  </si>
+  <si>
+    <t>· 일요일은 수평, 목요일은 수직이다. 재택 1일차 '당기기 A (수직)' · 6일차 '당기기 B (수평)'과 같은 축이고 순서만 반대다(2026-10-02 사용자 지정).</t>
+  </si>
+  <si>
+    <t>· 날 분할은 평면으로, 근육군은 팔꿈치 경로로 매긴다 — 다른 축이고 섞지 않는다. 그래서 수평 날에 광배(원암 케이블 로우)가 있고 수직 날에 승모 중부(페이스풀)가 있다.</t>
+  </si>
+  <si>
+    <t>· 광배 일 3 / 목 11 · 승모 중부 일 10 / 목 3 — 둘 다 주 2회다. 근육군으로 날을 가르면 '주 1회'로 적히지만 실제로는 로우가 광배를 쓰고 랫풀다운이 능형근을 쓴다.</t>
+  </si>
+  <si>
+    <t>· 22세트 · 약 58분. 여섯 날 중 가장 작다 — 블록이 둘뿐이고 가슴이 없다.</t>
+  </si>
+  <si>
+    <t>· 작은 것이 목적이다. 무거운 로우 넷을 신선한 상태로 치는 날이므로 뒤에 붙는 것을 줄였다.</t>
+  </si>
+  <si>
+    <t>· 그립이 이 날의 제약이다. 바벨 → 해머(서포티드) → 원암 → 스캡 슈러그 순으로 그립 부담이 줄어드는 순서다.</t>
+  </si>
+  <si>
+    <t>· 스캡 슈러그 +60초 · 케이블 푸쉬다운 +60초 · 프리쳐 컬 +60초. 마지막 세트에만 2단.</t>
+  </si>
+  <si>
+    <t>· 바벨 로우 · 해머 로우에는 걸지 않는다 — 중량이 큰 로우에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
+  </si>
+  <si>
+    <t>· 원암 케이블 로우에도 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 된다.</t>
+  </si>
+  <si>
+    <t>· 트랩바 슈러그에도 걸지 않는다. 선 자세로 중량을 받치는 종목이다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 일요일 등 · 팔 삼두/이두/전완을 세트 후반부에 · 등도 나누고  /  일요일로 옮기는데, 그 전에 나 등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  근데 나 일요일을 수평으로 바꿔줘. 뭔가 수평이 강도가 더 쎈거 같아서. 집중적으로 공략하고 싶다고나 할까?</t>
+  </si>
+  <si>
+    <t>월요일 — 가슴 · 어깨 (측/후)</t>
+  </si>
+  <si>
+    <t>매주 미는 세 리프트 중 하나. 이 날은 하체 · 힌지가 없어 코어와 기립근이 가장 신선하다.</t>
+  </si>
+  <si>
+    <t>스미스 벤치 / 체스트 프레스 머신</t>
+  </si>
+  <si>
+    <t>상부지 복합. 복합이라 플라이보다 앞에 둔다.</t>
+  </si>
+  <si>
+    <t>인클라인 스미스 프레스 / 인클라인 덤벨 프레스</t>
+  </si>
+  <si>
+    <t>상부지를 프레스와 플라이 둘로 나눠 각 4세트. 각도는 30~45도.</t>
+  </si>
+  <si>
+    <t>펙덱 플라이 머신 (인클라인 각도) / 인클라인 케이블 플라이</t>
+  </si>
+  <si>
+    <t>하방 벡터 — 벤치(수평)와 각도를 나눈다. 몸을 앞으로 기울이면 가슴, 세우면 삼두로 간다.</t>
+  </si>
+  <si>
+    <t>어시스트 딥스 머신 / 헤머스트랭스 체스트 프레스 / 디클라인 벤치</t>
+  </si>
+  <si>
+    <t>105/120/135</t>
+  </si>
+  <si>
+    <t>원암 케이블 레터럴 레이즈</t>
+  </si>
+  <si>
+    <t>5~7</t>
+  </si>
+  <si>
+    <t>케이블이라 전 구간 장력이 걸린다 — 덤벨 레터럴이 약한 하단 구간을 맡는다.</t>
+  </si>
+  <si>
+    <t>리닝 케이블 레터럴 / 머신 레터럴</t>
+  </si>
+  <si>
+    <t>케이블이라 수축 끝단이 살아 있다 — 토요일 리버스 펙덱(중간 구간)과 갈린다. 밀기 날 뒤에 후면 삼각을 두면 벤치가 만든 전/후 불균형을 같은 세션에서 되돌린다.</t>
+  </si>
+  <si>
+    <t>리버스 펙덱 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
+  </si>
+  <si>
+    <t>[어깨 전면이 이 날에 없는 이유]</t>
+  </si>
+  <si>
+    <t>· 벤치 5 + 인클라인 머신 4 + 딥스 3 + 인클라인 플라이 4가 전면 삼각에 간접으로 6.5세트치를 얹는다. 그 위에 프레스를 더 얹으면 전면만 혼자 과다가 된다.</t>
+  </si>
+  <si>
+    <t>· 그래서 월요일 어깨 블록은 측면 · 후면 둘뿐이다. 전면 직접은 토요일 머신 숄더 3 · 수요일 스미스 오버헤드 3으로 주 6세트다.</t>
+  </si>
+  <si>
+    <t>· 전면 삼각 실질 12.5세트 — 직접 6 + 간접 6.5. 성장 구간 안이다.</t>
+  </si>
+  <si>
+    <t>[가슴을 둘로 가른 축]</t>
+  </si>
+  <si>
+    <t>· 월요일은 상부(인클라인 프레스 4 + 인클라인 플라이 4), 목요일은 중하부(펙덱 4 + 디클라인 플라이 4)다. 벤치와 딥스는 수평 · 하방이라 월요일에 함께 둔다.</t>
+  </si>
+  <si>
+    <t>· 흉근 합산 실질 27.5세트로 천장(20)을 크게 넘는다. 2026-09-14 사용자 지정 — 가슴은 되돌리는 자리가 아니다. 판단 기준은 세트 수가 아니라 벤치 진행이다. 벤치가 2주 연속 안 오르면 그때 이 숫자를 본다.</t>
+  </si>
+  <si>
+    <t>· 22세트 · 약 59분. 여섯 날 중 가장 작다 — 월요일은 가슴 하나만 맡고 어깨가 6세트뿐이다.</t>
+  </si>
+  <si>
+    <t>· 벤치가 있는 날이므로 웜업 10~15분을 따로 잡는다.</t>
+  </si>
+  <si>
+    <t>[드롭 세트를 이 날에 걸지 않은 이유]</t>
+  </si>
+  <si>
+    <t>· 인클라인 덤벨 플라이는 덤벨을 바꿔 드는 동작이라 2단 드롭에서 자세가 먼저 무너진다.</t>
+  </si>
+  <si>
+    <t>· 흉근 드롭은 목요일 디클라인 케이블 플라이 한 곳에 몰아 뒀다 — 핀만 옮기면 되는 자리다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 월요일 가슴 · 월요일 다시 어깨를 세트 후반부에</t>
+  </si>
+  <si>
+    <t>화요일 — 팔 · 목 · 복근</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없고 전부 고립이다. 첫 종목 작업중량의 50%로 12회 한 세트면 램프가 끝난다.</t>
+  </si>
+  <si>
+    <t>· 팔꿈치와 손목이 이 날의 관절이다. 가벼운 케이블 푸쉬다운 15회로 팔꿈치를 먼저 데운다.</t>
+  </si>
+  <si>
+    <t>늘어난 구간 — 팔이 머리 위로 가 장두가 신장된다. 일요일 푸쉬다운(짧아진 구간)과 각도를 나눈다. 팔꿈치가 시큰하면 EZ바로 바꾼다.</t>
+  </si>
+  <si>
+    <t>EZ바 라잉 익스텐션 (손목 · 팔꿈치 부담 ↓) / 케이블 오버헤드 익스텐션</t>
+  </si>
+  <si>
+    <t>늘어난 구간 — 등받이에 기대 어깨가 뒤로 가면 이두 장두가 신장된다. 프리쳐 컬(짧아진 구간)과 각도를 나눈다.</t>
+  </si>
+  <si>
+    <t>케이블 드래그 컬 / 스파이더 컬</t>
+  </si>
+  <si>
+    <t>엎침 그립 컬 — 상완요골근과 신근이 주동이다. 재택 4일차 종목이라 새로 익힐 것이 없다.</t>
+  </si>
+  <si>
+    <t>EZ바 리버스컬 / 케이블 리버스컬 / 해머 컬 (중립 그립)</t>
+  </si>
+  <si>
+    <t>시티드 리스트 컬(손등 아래)</t>
+  </si>
+  <si>
+    <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다.</t>
+  </si>
+  <si>
+    <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
+  </si>
+  <si>
+    <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다.</t>
+  </si>
+  <si>
+    <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
+  </si>
+  <si>
+    <t>넥 익스텐션 (플레이트)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 신설] 벤치에 엎드려 뒤통수에 플레이트를 올리고 목만 든다. 첫 2주는 무게 없이 가동범위만 — 경추는 되돌릴 수 없는 자리다. 통증이 아니라 '당기는 느낌'까지만.</t>
+  </si>
+  <si>
+    <t>넥 하네스 / 넥 익스텐션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
+  </si>
+  <si>
+    <t>넥 플렉션 (플레이트)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 신설] 벤치에 누워 이마에 수건을 깔고 플레이트를 올린다. 턱을 당겨 목만 굽힌다. 굴곡 쪽이 더 약하므로 익스텐션보다 가볍게 간다.</t>
+  </si>
+  <si>
+    <t>넥 하네스 / 넥 플렉션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
+  </si>
+  <si>
+    <t>직접 굴곡. 스쿼트 · 데드의 브레이싱은 등척성이라 복부 간접이 0이다 — 여기서만 채워진다.</t>
+  </si>
+  <si>
+    <t>케이블 크런치 (머신) / 앱스 머신</t>
+  </si>
+  <si>
+    <t>하복부 쪽 — 크런치(상복부)와 갈린다. 재택 1일차 종목이다.</t>
+  </si>
+  <si>
+    <t>캡틴 체어 니 레이즈 / 행잉 레그 레이즈 / 리버스 크런치</t>
+  </si>
+  <si>
+    <t>[이 날은 건드리지 않았다]</t>
+  </si>
+  <si>
+    <t>· 사용자 지정 — '화요일은 팔하니 놔두고'. 삼두 · 이두 · 전완 · 목 · 복근 구성을 그대로 두고 세트만 맞췄다.</t>
+  </si>
+  <si>
+    <t>· 다른 다섯 날은 큰 부위 뒤에 어깨나 팔이 붙지만, 이 날은 팔이 메인이다. 팔이 가장 신선한 유일한 자리다.</t>
+  </si>
+  <si>
+    <t>· 그래서 늘어난 구간(라잉 익스텐션 · 인클라인 컬)을 이 날에 뒀다. 신장된 자리에서의 부하가 가장 비싸고, 지친 팔로는 그 자세가 안 잡힌다.</t>
+  </si>
+  <si>
+    <t>[전완 · 목 · 복근이 이 날에 몰린 이유]</t>
+  </si>
+  <si>
+    <t>· 전완 주 9세트가 전부 이 날이다. 그립을 쓰는 당기기가 하나도 없는 유일한 날이라 리스트 컬이 온전히 나온다.</t>
+  </si>
+  <si>
+    <t>· 전완 6 → 9 · 복부 3 → 6으로 올렸다. 현장 근무가 끝나 그립과 코어에 하루치를 얹어주던 보정이 사라졌기 때문이다 (복귀_세트검산 참조).</t>
+  </si>
+  <si>
+    <t>· 목은 2026-10-02 신설이다. 직접 0에서 주 6세트. 데드 · 슈러그의 등척성 지지는 계수 0이라 여기서만 채워진다.</t>
+  </si>
+  <si>
+    <t>· 27세트 · 약 48분. 여섯 날 중 가장 짧다 — 전부 고립이고 휴식이 60~75초라 그렇다.</t>
+  </si>
+  <si>
+    <t>· 27세트지만 세션 상한 26의 적용 대상이 아니다. 메인 리프트가 없고 전부 고립 소근육이다.</t>
+  </si>
+  <si>
+    <t>· 라잉 트라이셉스 익스텐션 +60초 한 곳만. 마지막 세트에만 2단.</t>
+  </si>
+  <si>
+    <t>· 인클라인 덤벨 컬에는 걸지 않는다 — 2026-09-07에 제외로 정한 자리다.</t>
+  </si>
+  <si>
+    <t>· 넥 종목에는 절대 걸지 않는다. 실패지점 근처에서 목을 쓰는 것이 이 종목의 유일한 금기다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 화요일 삼두/이두/전완/목/복근 — 화요일은 팔하니 놔두고</t>
+  </si>
+  <si>
+    <t>수요일 — 하체 후면 · 어깨 (전/측/후)</t>
+  </si>
+  <si>
+    <t>메인: 스미스 오버헤드 프레스</t>
+  </si>
+  <si>
+    <t>웜업 — 회전근개 (세트 카운트 제외 · 오버헤드 프레스 직전에)</t>
+  </si>
+  <si>
+    <t>· 데드 램프 · 프레스 램프와 따로다. 하체 5종목을 끝내고 오버헤드 프레스(6번)에 들어가기 직전에 넣는다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 보충] 메인이 둘이라 램프 블록 두 개에 가려 이 블록이 빠져 있었다. 어깨 보조가 9세트 이어지고 그 앞에 증량을 추적하는 프레스가 있는 날이다.</t>
+  </si>
+  <si>
+    <t>톱세트. 현장 근무가 끝나 허리와 경쟁하는 것이 없어졌으므로 2026-10-02부터 백오프 2세트를 되살려 성장으로 돌린다.</t>
+  </si>
+  <si>
+    <t>트랩바 데드 (요추 전단력 ↓) / 루마니안 데드 (허리가 무거운 주)</t>
+  </si>
+  <si>
+    <t>데드리프트 백오프</t>
+  </si>
+  <si>
+    <t>톱세트 −5kg = 2주 전 중량. 폼이 살아 있는 중량에서 볼륨을 쌓는 자리다. 다음 아침 허리가 뻐근하면 이 2세트를 먼저 뺀다 — 톱세트가 아니다.</t>
+  </si>
+  <si>
+    <t>트랩바 데드 백오프 / 랙 풀 (가동범위 ↓)</t>
+  </si>
+  <si>
+    <t>40~45</t>
+  </si>
+  <si>
+    <t>고관절 신전으로 햄스트링을 늘어난 구간에서 훈련한다. 무릎은 살짝만 굽히고 중립 척추를 지킨다.</t>
+  </si>
+  <si>
+    <t>덤벨 루마니안 데드 (허리 부담 ↓ · 좌우 균형) / 케이블 풀스루</t>
+  </si>
+  <si>
+    <t>레그 프레스 (발 높게)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 둔다 — 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라간다. 근육군은 둔근으로 잡았다: 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀌고, 능동 단축이 작으면 자극도 작다. 그래서 사두 0.33 · 햄스트링 0.2를 간접으로 계상했다. 중량은 토요일(125)보다 낮게 잡았다 — 발 위치가 바뀌면 같은 중량이 안 나온다. 더블 프로그레션으로 맞춘다.</t>
+  </si>
+  <si>
+    <t>와이드 스탠스 레그 프레스 (발 높게) / 45도 레그 프레스 (발 높게) / 스미스 스쿼트 (발 앞쪽)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 토요일 레그 컬과 자리 교환] 무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 편측 종목은 좌우 차를 드러내는 것이 목적이라 주의력이 필요하고, 그래서 여섯 날 중 누적 10세트짜리인 이 자리가 맞다. 토요일 9번(누적 34세트)은 반대였다. 중량은 토요일 양측 레그 컬이 밀고, 이쪽은 균형을 본다 — 좌우 반복 수가 2회 이상 벌어지면 약한 쪽 기준으로 맞춘다.</t>
+  </si>
+  <si>
+    <t>원 레그 시티드 컬 / 라잉 레그 컬 (양측 — 편측 자리가 없을 때) / 노르딕 햄 컬 (맨몸)</t>
+  </si>
+  <si>
+    <t>스미스 오버헤드 프레스</t>
+  </si>
+  <si>
+    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 13세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
+  </si>
+  <si>
+    <t>머신 숄더 프레스 (완전 머신을 원할 때 — 단 증량 추적은 이쪽으로 옮긴다) / 덤벨 숄더 프레스</t>
+  </si>
+  <si>
+    <t>프레스 직후라 측면 삼각이 이미 1.5세트치 간접을 받았다. 중량을 토요일보다 낮춰 잡는 것이 정상이다.</t>
+  </si>
+  <si>
+    <t>머신이라 상체 각도가 고정된다 — 데드 뒤에 기립근으로 버티지 않아도 되는 후면 삼각 종목이 이것뿐이다.</t>
+  </si>
+  <si>
+    <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 리버스 펙덱</t>
+  </si>
+  <si>
+    <t>둔근 직접. 짧아진 구간에서 최대 장력이 걸려 데드 · 루마니안(늘어난 구간)과 갈린다. 어깨와 경쟁하지 않는 고관절 종목이라 어깨 블록 뒤로 보냈다 — 그만큼 오버헤드 프레스 앞 누적이 줄었다.</t>
+  </si>
+  <si>
+    <t>머신 힙 쓰러스트 / 글루트 브릿지 / 케이블 풀스루</t>
+  </si>
+  <si>
+    <t>선 자세 · 편측이라 고관절이 펴진 각도에서 외전한다 — 앉아서 하는 아우터 타이(고관절 굽힘)와 각도가 갈린다. 둘 중 이쪽이 좌우 차가 드러나므로 아우터 타이 앞에 둬 더 신선한 자리를 줬다.</t>
+  </si>
+  <si>
+    <t>머신 힙 어브덕션 / 밴드 사이드 워크</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 요청 — 토요일과 같은 슈퍼세트를 이 날에도] 내전근 직접이 주 4세트뿐이라 실질 6.5로 하한(8) 아래였다. 이 4세트로 8 → 실질 10.5가 된다. 아우터와 슈퍼세트 — 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 요청] 중둔근 실질 7.0도 하한 아래였다 — 이 4세트로 11이 된다. 앞의 케이블 힙 외전과 같은 근육이므로 중량이 토요일보다 낮게 나오는 것이 정상이다. 어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤에 둔다.</t>
+  </si>
+  <si>
+    <t>무릎이 펴져 비복근 비중이 커진다 — 토요일 시티드(가자미근)와 각도를 나눈다. 데드 뒤라 발목이 이미 데워져 있다.</t>
+  </si>
+  <si>
+    <t>레그 프레스 카프 레이즈 / 시티드 카프 레이즈 / 스미스 카프 레이즈</t>
+  </si>
+  <si>
+    <t>[오버헤드 프레스를 수요일에 둔 이유]</t>
+  </si>
+  <si>
+    <t>· 어깨를 전부 세션 후반부로 내리면(2026-10-02 사용자 지정) 매주 미는 세 리프트 중 오버헤드 프레스만 큰 부위 뒤로 밀린다. 어느 날 뒤에 두는 것이 가장 싼지가 문제였다.</t>
+  </si>
+  <si>
+    <t>· 월요일(가슴) 뒤 — 가장 비싸다. 벤치 5 + 인클라인 4 + 딥스 3이 전면 삼각과 삼두에 간접 6.5세트치를 얹은 상태로 메인을 치게 된다.</t>
+  </si>
+  <si>
+    <t>· 토요일(하체 전면) 뒤 — 중간이다. 전면 삼각 · 삼두는 온전하나 스쿼트 5×5의 전신 피로가 가장 크다.</t>
+  </si>
+  <si>
+    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 13세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
+  </si>
+  <si>
+    <t>· 그래서 토요일 전면은 머신 숄더 프레스(볼륨용)이고, 증량을 추적하는 쪽은 이 날이다.</t>
+  </si>
+  <si>
+    <t>· 힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프를 어깨 뒤로 보내 프레스 앞 누적을 13세트로 묶었다. 레그 프레스와 슈퍼세트가 들어오며 25가 될 수 있었던 자리다.</t>
+  </si>
+  <si>
+    <t>[하체 후면을 한 날에 모은 이유]</t>
+  </si>
+  <si>
+    <t>· 데드 · 루마니안 데드는 둘 다 고관절 힌지다. 주에 흩어 두면 기립근이 회복할 72시간을 못 받는다 — 같은 패턴은 한 날에 모은다.</t>
+  </si>
+  <si>
+    <t>· 고관절 신전 넷(데드 3 · 루마니안 3 · 레그 프레스 발 높게 4 · 힙 쓰러스트 3)과 무릎 굴곡(원 레그 컬 3)을 같이 둬 햄스트링 · 둔근의 두 기능을 다 쓴다.</t>
+  </si>
+  <si>
+    <t>· 햄스트링 주 10세트 중 6이 이 날이고 4는 토요일 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다. 중량은 토요일(양측 4세트)이 밀고 이 날은 힌지 + 편측 균형을 맡는다.</t>
+  </si>
+  <si>
+    <t>· 토요일(사두 12 + 햄 3 + 내전근 4 + 중둔근 4) · 수요일(후면 14 + 중둔근 7 + 내전근 4 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02 사용자 요청] 이너 · 아우터 타이 슈퍼세트를 이 날에도 넣었다 — 하체에서 유일하게 하한 아래로 남아 있던 내전근(6.5)과 중둔근(7.0)이 둘 다 성장 구간으로 들어간다(10.5 · 11.0). 토요일과 같은 쌍이라 새로 익힐 것이 없다.</t>
+  </si>
+  <si>
+    <t>[레그 프레스를 발 높게 — 2026-10-02 사용자 지정]</t>
+  </si>
+  <si>
+    <t>· 발을 발판 가장 위쪽에 둔다. 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라가고, 무릎 신전 범위는 줄어든다.</t>
+  </si>
+  <si>
+    <t>· 다만 햄스트링 종목은 아니다 — 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀐다. 능동 단축이 작으면 자극도 작다.</t>
+  </si>
+  <si>
+    <t>· 그래서 주동근은 둔근으로 잡고 사두 0.33 · 햄스트링 0.2 · 내전근 0.2를 간접으로 계상했다. 후면을 노린다는 의도는 둔근 직접 4세트로 실현된다.</t>
+  </si>
+  <si>
+    <t>· 햄스트링 쪽을 직접 때리는 것은 루마니안 데드(늘어난 구간) · 레그 컬(짧아진 구간) · 토요일 원 레그 컬(편측)이다.</t>
+  </si>
+  <si>
+    <t>· 토요일 레그 프레스(발 낮게 · 사두)와 같은 종목 다른 자리다. 사두에도 간접 1.5세트치가 붙어 사두가 주 1회에서 '주 1회 + 간접 1회'가 됐다.</t>
+  </si>
+  <si>
+    <t>[데드리프트 운용 규칙]</t>
+  </si>
+  <si>
+    <t>· 유일한 지표는 다음날 아침 허리 상태다. 뻐근하면 그 주가 과했던 것 — 다음 주에 백오프를 먼저 뺀다.</t>
+  </si>
+  <si>
+    <t>· 톱세트 1×5는 지키고, 줄일 때는 항상 백오프 2세트부터다. 강도를 놓으면 근력이 먼저 빠진다.</t>
+  </si>
+  <si>
+    <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
+  </si>
+  <si>
+    <t>· 39세트 · 약 98분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
+  </si>
+  <si>
+    <t>· 고립 26세트를 빼면 실질 13세트다 — 어깨 블록 뒤 17세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 35분이 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
+  </si>
+  <si>
+    <t>· 레터럴 +60초 하나뿐이다. 마지막 세트에만 2단 — 레그 컬 드롭은 2026-10-02에 양측 레그 컬과 함께 토요일로 갔다.</t>
+  </si>
+  <si>
+    <t>· 원 레그 컬에는 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 되고, 일요일 원암 케이블 로우와 같은 기준이다.</t>
+  </si>
+  <si>
+    <t>· 데드 · 백오프 · 루마니안 · 레그 프레스에는 걸지 않는다 — 척추가 버티거나 중량이 큰 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
+  </si>
+  <si>
+    <t>· 이너 · 아우터 타이에도 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다(토요일과 같은 이유).</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고  /  수 하체에는 레그 프레스 넣어주고, 수요일에 하는 레그 프레스는 발을 발판의 가장 위쪽에 두어서 햄스트링 후면을 타겟하도록 할거야. 동시에 사두도 좀 타겟되겠지만.  /  그리고 수요일하체에 이너타이랑 아우터타이 슈퍼세트도 넣어줘.</t>
+  </si>
+  <si>
+    <t>목요일 — 당기기 (수직) · 가슴 · 팔</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없다. 첫 종목(친업) 전에 랫풀다운 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
+  </si>
+  <si>
+    <t>수직 당기기 중 가장 무거운 쪽이라 맨 앞에 둔다. 수요일 데드 다음날이므로 그립이 지쳐 있으면 주저 말고 어시스트 머신으로 간다 — 이 날 등은 그립이 아니라 광배가 실패해야 한다.</t>
+  </si>
+  <si>
+    <t>어시스트 풀업 머신 (1순위 — 데드 다음날이면 기본값으로 생각한다) / 랫풀다운 / 뉴트럴 그립 친업</t>
+  </si>
+  <si>
     <t>와이드 오버그립 랫풀다운</t>
   </si>
   <si>
@@ -3181,505 +3688,19 @@
     <t>뉴트럴 그립 랫풀다운 / 어시스트 풀업 머신</t>
   </si>
   <si>
-    <t>스미스 바벨 로우(오버그립)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 목요일에서 이동] 재택도 바벨 로우를 수직 날(1일차)에 둔다 — 승모 중부를 두 날에 7/6으로 고르게 나누기 때문이다. 복귀에서는 보너스가 하나 더 붙는다: 척추 부하가 있는 유일한 로우가 데드 다음날(목)에서 빠진다. 궤도가 고정돼 상체 각도를 기립근으로 버티지 않아도 된다.</t>
-  </si>
-  <si>
-    <t>티바 로우 / 해머 스트랭스 로우 (허리가 무거운 주) / 체스트 서포티드 로우</t>
-  </si>
-  <si>
-    <t>[2026-10-02 사용자 제안 · 토요일에서 이동] 재택도 페이스풀을 당기기 날(1일차)에 둔다. 로프를 얼굴 높이로 당기고 팔꿈치를 어깨선 위로 — 끝에서 외회전을 만든다. 당기기 15세트가 전부 어깨 신전 · 수평 외전인데 외회전을 같이 하는 종목은 이것뿐이다. 후면삼각에 0.5 간접이 붙는다.</t>
+    <t>팔이 머리 위에 고정된 채 견갑을 내린다 — 승모 하부가 직접 걸리는 유일한 자리이고, 팔이 머리 위라는 점에서 수직 날에 맞는다.</t>
+  </si>
+  <si>
+    <t>프론 Y 레이즈 / 케이블 Y 레이즈</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 제안] 재택도 페이스풀을 수직 날(1일차)에 둔다. 승모 중부를 두 날에 10/3으로 나누는 자리이기도 하다 — 이것이 없으면 승모 중부가 일요일 주 1회가 된다. 로프를 얼굴 높이로 당기고 팔꿈치를 어깨선 위로 — 끝에서 외회전을 만든다. 후면삼각에 0.5 간접.</t>
   </si>
   <si>
     <t>리어 델트 로우 (로프) / 케이블 리버스 플라이 (팔 편 채) / 리버스 펙덱</t>
   </si>
   <si>
-    <t>팔이 머리 위에 고정된 채 견갑을 내린다 — 승모 하부가 직접 걸리는 유일한 자리이고, 팔이 머리 위라는 점에서 수직 날에 맞는다.</t>
-  </si>
-  <si>
-    <t>프론 Y 레이즈 / 케이블 Y 레이즈</t>
-  </si>
-  <si>
-    <t>짧아진 구간. 당기기 뒤라 삼두가 전혀 쓰이지 않은 상태로 들어온다 — 팔을 세션 후반부에 두는 값이 이 날 가장 싸다.</t>
-  </si>
-  <si>
-    <t>케이블 오버헤드 익스텐션 (로프 · 장두 신전 구간) / V바 푸쉬다운</t>
-  </si>
-  <si>
-    <t>당기기 18세트 뒤라 이두가 이미 간접으로 7세트치를 받았다. 중량이 평소보다 낮게 나오는 것이 정상이다.</t>
-  </si>
-  <si>
-    <t>케이블 컬 (전 구간 장력) / 머신 컬 / EZ바 프리쳐 컬</t>
-  </si>
-  <si>
-    <t>[등을 가른 축 — 움직임 평면이다 (2026-10-02 정정)]</t>
-  </si>
-  <si>
-    <t>· 일요일은 수직, 목요일은 수평이다. 재택 1일차 '당기기 A (수직)' · 6일차 '당기기 B (수평)'과 같은 축이다 (사용자 지정).</t>
-  </si>
-  <si>
-    <t>· 2026-10-02 초안에서는 근육군으로 갈랐다(일=광배 전담 · 목=승모중부 전담). 그 근거로 2026-09-04 '주동근은 그립 폭이 아니라 팔꿈치 경로가 정한다'를 들었는데, 그 원칙은 세트검산의 근육군 분류를 정하는 규칙이고 날을 어떻게 가르라는 말이 아니었다 — 두 축을 뒤섞은 것이다.</t>
-  </si>
-  <si>
-    <t>· 그래서 두 날 모두 광배와 승모 중부가 섞여 있다 — 광배 일 11 / 목 3 · 승모 중부 일 7 / 목 6. 재택도 같은 모양이다(광배 9/4 · 승모 중부 7/8).</t>
-  </si>
-  <si>
-    <t>[팔이 이 날에 있는 이유]</t>
-  </si>
-  <si>
-    <t>· 삼두는 이 날 간접 자극이 0이다 — 당기기만 하는 날이라 프레스가 하나도 없다. 그래서 삼두 3세트가 가장 온전하게 나오는 자리다.</t>
-  </si>
-  <si>
-    <t>· 이두는 반대다. 당기기 18세트가 간접으로 7세트치를 얹으므로 프리쳐 컬은 '이미 데워진 근육을 마무리하는' 자리다.</t>
-  </si>
-  <si>
-    <t>· 삼두 · 이두는 일 · 화 · 목 3세트씩 주 9세트다. 실질은 둘 다 16.5 — 성장 구간 상단이라 더 올리지 않는다.</t>
-  </si>
-  <si>
-    <t>· 27세트 · 약 69분. 메인 리프트가 없어 중간 크기다.</t>
-  </si>
-  <si>
-    <t>· 그립이 이 날의 제약이다. 친업 → 와이드 → 언더그립 → 스미스 바벨 로우 순으로 그립 부담이 줄어드는 순서로 놓았다.</t>
-  </si>
-  <si>
-    <t>· 스미스 바벨 로우는 토요일 스쿼트 다음날에 온다. 궤도가 고정돼 있어 괜찮지만 허리가 무거운 주에는 해머 스트랭스 로우로 바꾼다 — 그러면 목요일과 종목이 겹치므로 그 주만 쓴다.</t>
-  </si>
-  <si>
-    <t>· 언더그립 랫풀다운 +60초 · 케이블 푸쉬다운 +60초 · 프리쳐 컬 +60초. 마지막 세트에만 2단.</t>
-  </si>
-  <si>
-    <t>· 친업 · 와이드 랫풀다운에는 걸지 않는다 — 그립이 먼저 나가 등이 실패지점에 못 간다.</t>
-  </si>
-  <si>
-    <t>· 스미스 바벨 로우 · 페이스풀에도 걸지 않는다. 바벨 로우는 척추가 버티는 종목이고, 페이스풀은 가벼운 외회전 종목이라 실패 뒤 반복에서 팔꿈치가 먼저 내려온다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 일요일 등 · 팔 삼두/이두/전완을 세트 후반부에 · 등도 나누고  /  일요일로 옮기는데, 그 전에 나 등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야</t>
-  </si>
-  <si>
-    <t>월요일 — 가슴 · 어깨 (측/후)</t>
-  </si>
-  <si>
-    <t>매주 미는 세 리프트 중 하나. 이 날은 하체 · 힌지가 없어 코어와 기립근이 가장 신선하다.</t>
-  </si>
-  <si>
-    <t>스미스 벤치 / 체스트 프레스 머신</t>
-  </si>
-  <si>
-    <t>상부지 복합. 복합이라 플라이보다 앞에 둔다.</t>
-  </si>
-  <si>
-    <t>인클라인 스미스 프레스 / 인클라인 덤벨 프레스</t>
-  </si>
-  <si>
-    <t>상부지를 프레스와 플라이 둘로 나눠 각 4세트. 각도는 30~45도.</t>
-  </si>
-  <si>
-    <t>펙덱 플라이 머신 (인클라인 각도) / 인클라인 케이블 플라이</t>
-  </si>
-  <si>
-    <t>하방 벡터 — 벤치(수평)와 각도를 나눈다. 몸을 앞으로 기울이면 가슴, 세우면 삼두로 간다.</t>
-  </si>
-  <si>
-    <t>어시스트 딥스 머신 / 헤머스트랭스 체스트 프레스 / 디클라인 벤치</t>
-  </si>
-  <si>
-    <t>105/120/135</t>
-  </si>
-  <si>
-    <t>원암 케이블 레터럴 레이즈</t>
-  </si>
-  <si>
-    <t>5~7</t>
-  </si>
-  <si>
-    <t>케이블이라 전 구간 장력이 걸린다 — 덤벨 레터럴이 약한 하단 구간을 맡는다.</t>
-  </si>
-  <si>
-    <t>리닝 케이블 레터럴 / 머신 레터럴</t>
-  </si>
-  <si>
-    <t>케이블이라 수축 끝단이 살아 있다 — 토요일 리버스 펙덱(중간 구간)과 갈린다. 밀기 날 뒤에 후면 삼각을 두면 벤치가 만든 전/후 불균형을 같은 세션에서 되돌린다.</t>
-  </si>
-  <si>
-    <t>리버스 펙덱 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
-  </si>
-  <si>
-    <t>[어깨 전면이 이 날에 없는 이유]</t>
-  </si>
-  <si>
-    <t>· 벤치 5 + 인클라인 머신 4 + 딥스 3 + 인클라인 플라이 4가 전면 삼각에 간접으로 6.5세트치를 얹는다. 그 위에 프레스를 더 얹으면 전면만 혼자 과다가 된다.</t>
-  </si>
-  <si>
-    <t>· 그래서 월요일 어깨 블록은 측면 · 후면 둘뿐이다. 전면 직접은 토요일 머신 숄더 3 · 수요일 스미스 오버헤드 3으로 주 6세트다.</t>
-  </si>
-  <si>
-    <t>· 전면 삼각 실질 12.5세트 — 직접 6 + 간접 6.5. 성장 구간 안이다.</t>
-  </si>
-  <si>
-    <t>[가슴을 둘로 가른 축]</t>
-  </si>
-  <si>
-    <t>· 월요일은 상부(인클라인 프레스 4 + 인클라인 플라이 4), 목요일은 중하부(펙덱 4 + 디클라인 플라이 4)다. 벤치와 딥스는 수평 · 하방이라 월요일에 함께 둔다.</t>
-  </si>
-  <si>
-    <t>· 흉근 합산 실질 27.5세트로 천장(20)을 크게 넘는다. 2026-09-14 사용자 지정 — 가슴은 되돌리는 자리가 아니다. 판단 기준은 세트 수가 아니라 벤치 진행이다. 벤치가 2주 연속 안 오르면 그때 이 숫자를 본다.</t>
-  </si>
-  <si>
-    <t>· 22세트 · 약 59분. 여섯 날 중 가장 작다 — 월요일은 가슴 하나만 맡고 어깨가 6세트뿐이다.</t>
-  </si>
-  <si>
-    <t>· 벤치가 있는 날이므로 웜업 10~15분을 따로 잡는다.</t>
-  </si>
-  <si>
-    <t>[드롭 세트를 이 날에 걸지 않은 이유]</t>
-  </si>
-  <si>
-    <t>· 인클라인 덤벨 플라이는 덤벨을 바꿔 드는 동작이라 2단 드롭에서 자세가 먼저 무너진다.</t>
-  </si>
-  <si>
-    <t>· 흉근 드롭은 목요일 디클라인 케이블 플라이 한 곳에 몰아 뒀다 — 핀만 옮기면 되는 자리다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 월요일 가슴 · 월요일 다시 어깨를 세트 후반부에</t>
-  </si>
-  <si>
-    <t>화요일 — 팔 · 목 · 복근</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없고 전부 고립이다. 첫 종목 작업중량의 50%로 12회 한 세트면 램프가 끝난다.</t>
-  </si>
-  <si>
-    <t>· 팔꿈치와 손목이 이 날의 관절이다. 가벼운 케이블 푸쉬다운 15회로 팔꿈치를 먼저 데운다.</t>
-  </si>
-  <si>
-    <t>늘어난 구간 — 팔이 머리 위로 가 장두가 신장된다. 일요일 푸쉬다운(짧아진 구간)과 각도를 나눈다. 팔꿈치가 시큰하면 EZ바로 바꾼다.</t>
-  </si>
-  <si>
-    <t>EZ바 라잉 익스텐션 (손목 · 팔꿈치 부담 ↓) / 케이블 오버헤드 익스텐션</t>
-  </si>
-  <si>
-    <t>늘어난 구간 — 등받이에 기대 어깨가 뒤로 가면 이두 장두가 신장된다. 프리쳐 컬(짧아진 구간)과 각도를 나눈다.</t>
-  </si>
-  <si>
-    <t>케이블 드래그 컬 / 스파이더 컬</t>
-  </si>
-  <si>
-    <t>엎침 그립 컬 — 상완요골근과 신근이 주동이다. 재택 4일차 종목이라 새로 익힐 것이 없다.</t>
-  </si>
-  <si>
-    <t>EZ바 리버스컬 / 케이블 리버스컬 / 해머 컬 (중립 그립)</t>
-  </si>
-  <si>
-    <t>시티드 리스트 컬(손등 아래)</t>
-  </si>
-  <si>
-    <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다.</t>
-  </si>
-  <si>
-    <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
-  </si>
-  <si>
-    <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다.</t>
-  </si>
-  <si>
-    <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
-  </si>
-  <si>
-    <t>넥 익스텐션 (플레이트)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 신설] 벤치에 엎드려 뒤통수에 플레이트를 올리고 목만 든다. 첫 2주는 무게 없이 가동범위만 — 경추는 되돌릴 수 없는 자리다. 통증이 아니라 '당기는 느낌'까지만.</t>
-  </si>
-  <si>
-    <t>넥 하네스 / 넥 익스텐션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
-  </si>
-  <si>
-    <t>넥 플렉션 (플레이트)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 신설] 벤치에 누워 이마에 수건을 깔고 플레이트를 올린다. 턱을 당겨 목만 굽힌다. 굴곡 쪽이 더 약하므로 익스텐션보다 가볍게 간다.</t>
-  </si>
-  <si>
-    <t>넥 하네스 / 넥 플렉션 머신 / 손바닥으로 저항 (아이소메트릭 10초 × 10회)</t>
-  </si>
-  <si>
-    <t>직접 굴곡. 스쿼트 · 데드의 브레이싱은 등척성이라 복부 간접이 0이다 — 여기서만 채워진다.</t>
-  </si>
-  <si>
-    <t>케이블 크런치 (머신) / 앱스 머신</t>
-  </si>
-  <si>
-    <t>하복부 쪽 — 크런치(상복부)와 갈린다. 재택 1일차 종목이다.</t>
-  </si>
-  <si>
-    <t>캡틴 체어 니 레이즈 / 행잉 레그 레이즈 / 리버스 크런치</t>
-  </si>
-  <si>
-    <t>[이 날은 건드리지 않았다]</t>
-  </si>
-  <si>
-    <t>· 사용자 지정 — '화요일은 팔하니 놔두고'. 삼두 · 이두 · 전완 · 목 · 복근 구성을 그대로 두고 세트만 맞췄다.</t>
-  </si>
-  <si>
-    <t>· 다른 다섯 날은 큰 부위 뒤에 어깨나 팔이 붙지만, 이 날은 팔이 메인이다. 팔이 가장 신선한 유일한 자리다.</t>
-  </si>
-  <si>
-    <t>· 그래서 늘어난 구간(라잉 익스텐션 · 인클라인 컬)을 이 날에 뒀다. 신장된 자리에서의 부하가 가장 비싸고, 지친 팔로는 그 자세가 안 잡힌다.</t>
-  </si>
-  <si>
-    <t>[전완 · 목 · 복근이 이 날에 몰린 이유]</t>
-  </si>
-  <si>
-    <t>· 전완 주 9세트가 전부 이 날이다. 그립을 쓰는 당기기가 하나도 없는 유일한 날이라 리스트 컬이 온전히 나온다.</t>
-  </si>
-  <si>
-    <t>· 전완 6 → 9 · 복부 3 → 6으로 올렸다. 현장 근무가 끝나 그립과 코어에 하루치를 얹어주던 보정이 사라졌기 때문이다 (복귀_세트검산 참조).</t>
-  </si>
-  <si>
-    <t>· 목은 2026-10-02 신설이다. 직접 0에서 주 6세트. 데드 · 슈러그의 등척성 지지는 계수 0이라 여기서만 채워진다.</t>
-  </si>
-  <si>
-    <t>· 27세트 · 약 48분. 여섯 날 중 가장 짧다 — 전부 고립이고 휴식이 60~75초라 그렇다.</t>
-  </si>
-  <si>
-    <t>· 27세트지만 세션 상한 26의 적용 대상이 아니다. 메인 리프트가 없고 전부 고립 소근육이다.</t>
-  </si>
-  <si>
-    <t>· 라잉 트라이셉스 익스텐션 +60초 한 곳만. 마지막 세트에만 2단.</t>
-  </si>
-  <si>
-    <t>· 인클라인 덤벨 컬에는 걸지 않는다 — 2026-09-07에 제외로 정한 자리다.</t>
-  </si>
-  <si>
-    <t>· 넥 종목에는 절대 걸지 않는다. 실패지점 근처에서 목을 쓰는 것이 이 종목의 유일한 금기다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 화요일 삼두/이두/전완/목/복근 — 화요일은 팔하니 놔두고</t>
-  </si>
-  <si>
-    <t>수요일 — 하체 후면 · 어깨 (전/측/후)</t>
-  </si>
-  <si>
-    <t>메인: 스미스 오버헤드 프레스</t>
-  </si>
-  <si>
-    <t>웜업 — 회전근개 (세트 카운트 제외 · 오버헤드 프레스 직전에)</t>
-  </si>
-  <si>
-    <t>· 데드 램프 · 프레스 램프와 따로다. 하체 5종목을 끝내고 오버헤드 프레스(6번)에 들어가기 직전에 넣는다.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02 보충] 메인이 둘이라 램프 블록 두 개에 가려 이 블록이 빠져 있었다. 어깨 보조가 9세트 이어지고 그 앞에 증량을 추적하는 프레스가 있는 날이다.</t>
-  </si>
-  <si>
-    <t>톱세트. 현장 근무가 끝나 허리와 경쟁하는 것이 없어졌으므로 2026-10-02부터 백오프 2세트를 되살려 성장으로 돌린다.</t>
-  </si>
-  <si>
-    <t>트랩바 데드 (요추 전단력 ↓) / 루마니안 데드 (허리가 무거운 주)</t>
-  </si>
-  <si>
-    <t>데드리프트 백오프</t>
-  </si>
-  <si>
-    <t>톱세트 −5kg = 2주 전 중량. 폼이 살아 있는 중량에서 볼륨을 쌓는 자리다. 다음 아침 허리가 뻐근하면 이 2세트를 먼저 뺀다 — 톱세트가 아니다.</t>
-  </si>
-  <si>
-    <t>트랩바 데드 백오프 / 랙 풀 (가동범위 ↓)</t>
-  </si>
-  <si>
-    <t>40~45</t>
-  </si>
-  <si>
-    <t>고관절 신전으로 햄스트링을 늘어난 구간에서 훈련한다. 무릎은 살짝만 굽히고 중립 척추를 지킨다.</t>
-  </si>
-  <si>
-    <t>덤벨 루마니안 데드 (허리 부담 ↓ · 좌우 균형) / 케이블 풀스루</t>
-  </si>
-  <si>
-    <t>레그 프레스 (발 높게)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 사용자 지정] 발을 발판 가장 위쪽에 둔다 — 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라간다. 근육군은 둔근으로 잡았다: 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀌고, 능동 단축이 작으면 자극도 작다. 그래서 사두 0.33 · 햄스트링 0.2를 간접으로 계상했다. 중량은 토요일(125)보다 낮게 잡았다 — 발 위치가 바뀌면 같은 중량이 안 나온다. 더블 프로그레션으로 맞춘다.</t>
-  </si>
-  <si>
-    <t>와이드 스탠스 레그 프레스 (발 높게) / 45도 레그 프레스 (발 높게) / 스미스 스쿼트 (발 앞쪽)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 토요일 레그 컬과 자리 교환] 무릎 굴곡 쪽 — 힌지(고관절 신전)와 기능이 갈린다. 편측 종목은 좌우 차를 드러내는 것이 목적이라 주의력이 필요하고, 그래서 여섯 날 중 누적 10세트짜리인 이 자리가 맞다. 토요일 9번(누적 34세트)은 반대였다. 중량은 토요일 양측 레그 컬이 밀고, 이쪽은 균형을 본다 — 좌우 반복 수가 2회 이상 벌어지면 약한 쪽 기준으로 맞춘다.</t>
-  </si>
-  <si>
-    <t>원 레그 시티드 컬 / 라잉 레그 컬 (양측 — 편측 자리가 없을 때) / 노르딕 햄 컬 (맨몸)</t>
-  </si>
-  <si>
-    <t>스미스 오버헤드 프레스</t>
-  </si>
-  <si>
-    <t>매주 미는 세 리프트 중 하나. 어깨 블록 첫 종목이고, 이 자리가 여섯 날 중 전면 삼각 · 삼두가 가장 온전한 어깨 자리다 — 앞에 있는 13세트가 전부 하체이기 때문이다. 아래 [오버헤드 프레스를 수요일에 둔 이유] 참조.</t>
-  </si>
-  <si>
-    <t>머신 숄더 프레스 (완전 머신을 원할 때 — 단 증량 추적은 이쪽으로 옮긴다) / 덤벨 숄더 프레스</t>
-  </si>
-  <si>
-    <t>프레스 직후라 측면 삼각이 이미 1.5세트치 간접을 받았다. 중량을 토요일보다 낮춰 잡는 것이 정상이다.</t>
-  </si>
-  <si>
-    <t>머신이라 상체 각도가 고정된다 — 데드 뒤에 기립근으로 버티지 않아도 되는 후면 삼각 종목이 이것뿐이다.</t>
-  </si>
-  <si>
-    <t>케이블 리버스 플라이 / 리어 델트 로우 (로프) / 리버스 펙덱</t>
-  </si>
-  <si>
-    <t>둔근 직접. 짧아진 구간에서 최대 장력이 걸려 데드 · 루마니안(늘어난 구간)과 갈린다. 어깨와 경쟁하지 않는 고관절 종목이라 어깨 블록 뒤로 보냈다 — 그만큼 오버헤드 프레스 앞 누적이 줄었다.</t>
-  </si>
-  <si>
-    <t>머신 힙 쓰러스트 / 글루트 브릿지 / 케이블 풀스루</t>
-  </si>
-  <si>
-    <t>선 자세 · 편측이라 고관절이 펴진 각도에서 외전한다 — 앉아서 하는 아우터 타이(고관절 굽힘)와 각도가 갈린다. 둘 중 이쪽이 좌우 차가 드러나므로 아우터 타이 앞에 둬 더 신선한 자리를 줬다.</t>
-  </si>
-  <si>
-    <t>머신 힙 어브덕션 / 밴드 사이드 워크</t>
-  </si>
-  <si>
-    <t>[2026-10-02 사용자 요청 — 토요일과 같은 슈퍼세트를 이 날에도] 내전근 직접이 주 4세트뿐이라 실질 6.5로 하한(8) 아래였다. 이 4세트로 8 → 실질 10.5가 된다. 아우터와 슈퍼세트 — 같은 머신에서 핀만 옮기므로 휴식 10초가 전환 시간이다.</t>
-  </si>
-  <si>
-    <t>[2026-10-02 사용자 요청] 중둔근 실질 7.0도 하한 아래였다 — 이 4세트로 11이 된다. 앞의 케이블 힙 외전과 같은 근육이므로 중량이 토요일보다 낮게 나오는 것이 정상이다. 어깨와 경쟁하지 않는 고립이라 어깨 블록 뒤에 둔다.</t>
-  </si>
-  <si>
-    <t>무릎이 펴져 비복근 비중이 커진다 — 토요일 시티드(가자미근)와 각도를 나눈다. 데드 뒤라 발목이 이미 데워져 있다.</t>
-  </si>
-  <si>
-    <t>레그 프레스 카프 레이즈 / 시티드 카프 레이즈 / 스미스 카프 레이즈</t>
-  </si>
-  <si>
-    <t>[오버헤드 프레스를 수요일에 둔 이유]</t>
-  </si>
-  <si>
-    <t>· 어깨를 전부 세션 후반부로 내리면(2026-10-02 사용자 지정) 매주 미는 세 리프트 중 오버헤드 프레스만 큰 부위 뒤로 밀린다. 어느 날 뒤에 두는 것이 가장 싼지가 문제였다.</t>
-  </si>
-  <si>
-    <t>· 월요일(가슴) 뒤 — 가장 비싸다. 벤치 5 + 인클라인 4 + 딥스 3이 전면 삼각과 삼두에 간접 6.5세트치를 얹은 상태로 메인을 치게 된다.</t>
-  </si>
-  <si>
-    <t>· 토요일(하체 전면) 뒤 — 중간이다. 전면 삼각 · 삼두는 온전하나 스쿼트 5×5의 전신 피로가 가장 크다.</t>
-  </si>
-  <si>
-    <t>· 수요일(하체 후면) 뒤 — 가장 싸다. 앞의 13세트가 전부 햄스트링 · 둔근이라 전면 삼각 · 삼두를 하나도 쓰지 않고, 스미스는 궤도가 고정돼 데드 뒤 기립근 피로의 비용이 작다. 월요일 벤치와 이틀 간격이라 전면 삼각이 회복될 시간도 있다.</t>
-  </si>
-  <si>
-    <t>· 그래서 토요일 전면은 머신 숄더 프레스(볼륨용)이고, 증량을 추적하는 쪽은 이 날이다.</t>
-  </si>
-  <si>
-    <t>· 힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프를 어깨 뒤로 보내 프레스 앞 누적을 13세트로 묶었다. 레그 프레스와 슈퍼세트가 들어오며 25가 될 수 있었던 자리다.</t>
-  </si>
-  <si>
-    <t>[하체 후면을 한 날에 모은 이유]</t>
-  </si>
-  <si>
-    <t>· 데드 · 루마니안 데드는 둘 다 고관절 힌지다. 주에 흩어 두면 기립근이 회복할 72시간을 못 받는다 — 같은 패턴은 한 날에 모은다.</t>
-  </si>
-  <si>
-    <t>· 고관절 신전 넷(데드 3 · 루마니안 3 · 레그 프레스 발 높게 4 · 힙 쓰러스트 3)과 무릎 굴곡(원 레그 컬 3)을 같이 둬 햄스트링 · 둔근의 두 기능을 다 쓴다.</t>
-  </si>
-  <si>
-    <t>· 햄스트링 주 10세트 중 6이 이 날이고 4는 토요일 레그 컬이다 — 2026-10-02에 햄스트링 빈도를 주 2회로 쪼갰다. 중량은 토요일(양측 4세트)이 밀고 이 날은 힌지 + 편측 균형을 맡는다.</t>
-  </si>
-  <si>
-    <t>· 토요일(사두 12 + 햄 3 + 내전근 4 + 중둔근 4) · 수요일(후면 14 + 중둔근 7 + 내전근 4 + 종아리 3)로 갈라 하체 빈도가 주 2회가 됐다.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02 사용자 요청] 이너 · 아우터 타이 슈퍼세트를 이 날에도 넣었다 — 하체에서 유일하게 하한 아래로 남아 있던 내전근(6.5)과 중둔근(7.0)이 둘 다 성장 구간으로 들어간다(10.5 · 11.0). 토요일과 같은 쌍이라 새로 익힐 것이 없다.</t>
-  </si>
-  <si>
-    <t>[레그 프레스를 발 높게 — 2026-10-02 사용자 지정]</t>
-  </si>
-  <si>
-    <t>· 발을 발판 가장 위쪽에 둔다. 고관절 굽힘 범위가 커져 고관절 신전 비중이 올라가고, 무릎 신전 범위는 줄어든다.</t>
-  </si>
-  <si>
-    <t>· 다만 햄스트링 종목은 아니다 — 발을 높여도 무릎이 같이 펴지므로 햄스트링은 고관절 신전(+)과 무릎 굴곡(−)이 상쇄돼 길이가 거의 안 바뀐다. 능동 단축이 작으면 자극도 작다.</t>
-  </si>
-  <si>
-    <t>· 그래서 주동근은 둔근으로 잡고 사두 0.33 · 햄스트링 0.2 · 내전근 0.2를 간접으로 계상했다. 후면을 노린다는 의도는 둔근 직접 4세트로 실현된다.</t>
-  </si>
-  <si>
-    <t>· 햄스트링 쪽을 직접 때리는 것은 루마니안 데드(늘어난 구간) · 레그 컬(짧아진 구간) · 토요일 원 레그 컬(편측)이다.</t>
-  </si>
-  <si>
-    <t>· 토요일 레그 프레스(발 낮게 · 사두)와 같은 종목 다른 자리다. 사두에도 간접 1.5세트치가 붙어 사두가 주 1회에서 '주 1회 + 간접 1회'가 됐다.</t>
-  </si>
-  <si>
-    <t>[데드리프트 운용 규칙]</t>
-  </si>
-  <si>
-    <t>· 유일한 지표는 다음날 아침 허리 상태다. 뻐근하면 그 주가 과했던 것 — 다음 주에 백오프를 먼저 뺀다.</t>
-  </si>
-  <si>
-    <t>· 톱세트 1×5는 지키고, 줄일 때는 항상 백오프 2세트부터다. 강도를 놓으면 근력이 먼저 빠진다.</t>
-  </si>
-  <si>
-    <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
-  </si>
-  <si>
-    <t>· 39세트 · 약 98분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
-  </si>
-  <si>
-    <t>· 고립 26세트를 빼면 실질 13세트다 — 어깨 블록 뒤 17세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 35분이 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
-  </si>
-  <si>
-    <t>· 레터럴 +60초 하나뿐이다. 마지막 세트에만 2단 — 레그 컬 드롭은 2026-10-02에 양측 레그 컬과 함께 토요일로 갔다.</t>
-  </si>
-  <si>
-    <t>· 원 레그 컬에는 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 되고, 일요일 원암 케이블 로우와 같은 기준이다.</t>
-  </si>
-  <si>
-    <t>· 데드 · 백오프 · 루마니안 · 레그 프레스에는 걸지 않는다 — 척추가 버티거나 중량이 큰 종목에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
-  </si>
-  <si>
-    <t>· 이너 · 아우터 타이에도 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다(토요일과 같은 이유).</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 수요일 하체/어깨 — 수요일 어깨를 세트 후반부에 · 하체는 전면 후면 나누고  /  수 하체에는 레그 프레스 넣어주고, 수요일에 하는 레그 프레스는 발을 발판의 가장 위쪽에 두어서 햄스트링 후면을 타겟하도록 할거야. 동시에 사두도 좀 타겟되겠지만.  /  그리고 수요일하체에 이너타이랑 아우터타이 슈퍼세트도 넣어줘.</t>
-  </si>
-  <si>
-    <t>목요일 — 당기기 B (수평) · 가슴 · 팔</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없다. 첫 종목(해머 스트랭스 로우) 작업중량의 50%로 10회 · 75%로 5회, 두 세트면 램프가 끝난다.</t>
-  </si>
-  <si>
-    <t>체스트 서포티드라 척추 부하가 0이다. 수요일 데드 다음날의 첫 종목으로 이보다 안전한 수평 로우가 없다. 넓은 엎침 그립 + 팔꿈치 벌림 — 주동근은 견갑 후인이다(2026-09-04 재분류).</t>
-  </si>
-  <si>
-    <t>시티드 케이블 로우 (넓은 그립) / 머신 로우 / 티바 로우</t>
-  </si>
-  <si>
-    <t>135/150/165</t>
-  </si>
-  <si>
-    <t>[2026-10-02 일요일에서 이동] 수평 당기기이므로 평면 기준으로는 이 날이 맞다. 팔꿈치를 몸에 붙여 당기는 경로라 주동근은 광배다 — 평면으로 날을 가르고 근육군은 팔꿈치 경로로 매긴다. 좌우 독립이라 약한 쪽이 드러난다.</t>
-  </si>
-  <si>
-    <t>원암 해머 스트랭스 로우 / 원암 덤벨 로우 (벤치 지지) / 머신 로우</t>
-  </si>
-  <si>
-    <t>팔을 편 채 견갑만 후인한다 — 로우의 간접만으로는 능형근이 실패지점에 안 간다.</t>
-  </si>
-  <si>
-    <t>페이스풀 (로프) / 리버스 펙덱 (팔 편 채로)</t>
-  </si>
-  <si>
-    <t>[2026-10-02 신설] 복귀판에 승모 상부 직접이 0이었다. 현장 근무가 하루치를 얹어주던 것이 끝났으므로 재택 6일차 종목을 그대로 가져왔다 — 재택도 수평 날(6일차)에 둔다. 트랩바라 손이 몸 옆에 와 견갑 거상이 수직으로 나온다.</t>
-  </si>
-  <si>
-    <t>덤벨 슈러그 / 바벨 슈러그 (몸 앞 — 궤도가 약간 앞으로 간다) / 머신 슈러그</t>
-  </si>
-  <si>
-    <t>수평 내전으로 중간 구간을 맡는다. 등 12세트 뒤라 가슴이 온전하다 — 당기기와 밀기는 경쟁하지 않는다.</t>
+    <t>수평 내전으로 중간 구간을 맡는다. 등 17세트 뒤라 가슴이 온전하다 — 당기기와 밀기는 경쟁하지 않는다.</t>
   </si>
   <si>
     <t>케이블 크로스오버 (중간 높이) / 덤벨 플라이 / 머신 체스트 프레스</t>
@@ -3709,19 +3730,19 @@
     <t>케이블 컬 (전 구간 장력) / 머신 컬 / 바벨 컬</t>
   </si>
   <si>
-    <t>[이 날이 수평 당기기인 이유 — 2026-10-02 정정]</t>
-  </si>
-  <si>
-    <t>· 재택 6일차 '당기기 B (수평)'과 같은 축이다. 네 종목 전부 수평 당김 또는 견갑 동작이다.</t>
-  </si>
-  <si>
-    <t>· 초안에서는 '승모 중부 · 능형근 전담일'로 잡았는데 그러면 광배가 장부상으로만 주 1회가 된다 — 여기 로우 셋이 전부 광배를 쓴다. 평면으로 가르고 근육군은 팔꿈치 경로로 따로 매기는 것이 재택 방식이다.</t>
-  </si>
-  <si>
-    <t>· 그래서 원암 케이블 로우(광배 · 수평)가 이 날로 왔고 스미스 바벨 로우(승모 중부 · 수평이지만)는 일요일로 갔다. 재택도 바벨 로우를 수직 날에 둔다 — 승모 중부를 두 날에 고르게 나누기 때문이다.</t>
-  </si>
-  <si>
-    <t>· 그 교환의 복귀 전용 이득 — 척추 부하가 있는 유일한 로우가 **데드 다음날에서 빠졌다**. 이제 이 날 로우 넷 중 셋이 체스트 서포티드이거나 궤도 고정이고, 나머지 하나는 편측 케이블이다.</t>
+    <t>[데드 다음날에 수직 당기기를 둔 이유 — 2026-10-02]</t>
+  </si>
+  <si>
+    <t>· 수요일 데드 · 루마니안이 그립 · 광배 · 기립근을 다 쓴다. 그 다음날 무거운 로우를 치면 등이 아니라 그립과 허리가 먼저 막힌다. 그래서 무거운 수평 로우 7세트(바벨 4 · 해머 3)를 일요일로 보냈다.</t>
+  </si>
+  <si>
+    <t>· 남은 수직 당기기는 척추 부하가 거의 0이다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 데드 다음날에 이보다 싼 등 자극이 없다.</t>
+  </si>
+  <si>
+    <t>· 그립만 남은 변수다. 친업이 그립을 쓰므로 데드 다음날에는 어시스트 머신을 기본값으로 생각한다 — 이 날 광배가 실패해야 하고 그립이 실패하면 세트를 잃는다.</t>
+  </si>
+  <si>
+    <t>· 주간 척추 부하 순서가 이렇게 된다 — 토 스쿼트(높음) → 일 바벨 로우(중간) → 월 · 화 0 → 수 데드 + 루마니안(최고) → 목 수직 당기기(거의 0) → 금 휴식.</t>
   </si>
   <si>
     <t>[이 날이 세 블록인 이유]</t>
@@ -3730,31 +3751,34 @@
     <t>· 사용자 지정 — '목요일 가슴/등'. 거기에 팔 후반부가 붙어 등 → 가슴 → 팔 세 블록이 됐다.</t>
   </si>
   <si>
-    <t>· 등(수평 12) → 가슴(중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
-  </si>
-  <si>
-    <t>· 팔이 맨 뒤인 이유 — 앞의 12세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
-  </si>
-  <si>
-    <t>· 26세트 · 약 64분. 세 블록이지만 각 블록이 작아 중간 크기다.</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다.</t>
-  </si>
-  <si>
-    <t>· 스캡 슈러그 +60초 · 디클라인 케이블 플라이 +60초. 마지막 세트에만 2단.</t>
+    <t>· 등(수직 17) → 가슴(중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
+  </si>
+  <si>
+    <t>· 팔이 맨 뒤인 이유 — 앞의 17세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
+  </si>
+  <si>
+    <t>· 31세트 · 약 75분. 여섯 날 중 세 번째다(수 39 · 토 38 다음).</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 13을 빼면 실질 18이다.</t>
+  </si>
+  <si>
+    <t>· 일요일(22세트 58분)과 합쳐 보면 등 블록 둘이 22/31로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
+  </si>
+  <si>
+    <t>· 언더그립 랫풀다운 +60초 · 디클라인 케이블 플라이 +60초. 마지막 세트에만 2단.</t>
+  </si>
+  <si>
+    <t>· 친업 · 와이드 랫풀다운에는 걸지 않는다 — 데드 다음날이라 그립이 먼저 나가고 등이 실패지점에 못 간다.</t>
   </si>
   <si>
     <t>· 펙덱 플라이에는 걸지 않는다 — 디클라인 플라이 드롭과 같은 근육 · 같은 세션이라 겹친다(2026-09-14 판단 유지).</t>
   </si>
   <si>
-    <t>· 트랩바 슈러그에는 걸지 않는다. 선 자세로 중량을 받치는 종목이다.</t>
-  </si>
-  <si>
-    <t>· 원암 케이블 로우에도 걸지 않는다 — 좌우 따로라 +120초가 된다.</t>
-  </si>
-  <si>
-    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야</t>
+    <t>· 페이스풀에도 걸지 않는다. 가벼운 외회전 종목이라 실패 뒤 반복에서 팔꿈치가 먼저 내려온다.</t>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  일요일을 수평으로 바꿔줘</t>
   </si>
   <si>
     <t>복귀판 간접 세트 계수 맵 — 복귀_세트검산 간접 열(C)의 계산 원천</t>
@@ -3790,7 +3814,7 @@
     <t>오버헤드 프레스 삼두 신전 — 5×5 저반복 본세트 하향. 머신 숄더 프레스(0.5)와 구분. 재택 2026-09-04 0.5→0.33 (2026-10-02 재택 09-04 규칙서 정렬)</t>
   </si>
   <si>
-    <t>복귀_일_당기기A</t>
+    <t>복귀_목_수직당기기</t>
   </si>
   <si>
     <t>뒤침 그립 — 이두가 유리한 자리에서 능동 굴곡. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
@@ -3802,7 +3826,7 @@
     <t>엎침 그립 수직 당기기. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
   </si>
   <si>
-    <t>복귀_목_당기기B</t>
+    <t>복귀_일_수평당기기</t>
   </si>
   <si>
     <t>좁은 뉴트럴 그립 — 엎침과 뒤침 사이. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙)</t>
@@ -3964,19 +3988,19 @@
     <t>직접 16세트: 월요일 벤치 5 · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 4. 간접 0.8 — 인클라인 덤벨 플라이 0.2×4 (인클라인 머신의 교차 간접은 2026-10-02에 0으로). 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
   </si>
   <si>
-    <t>직접 14세트: 일요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 3 + 목요일(수평) 원암 케이블 로우 3. 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3. [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 목요일 로우가 전부 광배를 쓰고 있었다</t>
+    <t>직접 14세트: 목요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 3 + 일요일(수평) 원암 케이블 로우 3. 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3(둘 다 일요일). [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 반대 날 로우가 전부 광배를 쓰고 있었다</t>
   </si>
   <si>
     <t>등 합산</t>
   </si>
   <si>
-    <t>직접 3세트: 목요일(수평) 트랩바 슈러그 3 — 재택도 수평 날(6일차)에 둔다 (2026-10-02 신설). 간접 1.4 — 오버헤드 프레스 · 스미스 바벨 로우 각 0.2 (데드의 등척성 견갑대 유지는 2026-10-02에 0으로). 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
-  </si>
-  <si>
-    <t>직접 3세트: 일요일(수직) 오버헤드 슈러그 3 — 팔이 머리 위라 수직 날에 맞는다. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
-  </si>
-  <si>
-    <t>직접 13세트: 일요일(수직) 스미스 바벨 로우 4 · 페이스풀 3 + 목요일(수평) 해머 스트랭스 로우 3 · 스캡 슈러그 3. 7/6으로 두 날에 고르게 나뉜다 — 재택(7/8)과 같은 모양이고 바벨 로우를 수직 날에 두는 것도 재택을 따랐다. 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
+    <t>직접 3세트: 일요일(수평) 트랩바 슈러그 3 — 재택도 수평 날에 둔다 (2026-10-02 신설). 간접 1.4 — 오버헤드 프레스 · 스미스 바벨 로우 각 0.2 (데드의 등척성 견갑대 유지는 2026-10-02에 0으로). 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
+  </si>
+  <si>
+    <t>직접 3세트: 목요일(수직) 오버헤드 슈러그 3 — 팔이 머리 위라 수직 날에 맞는다. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
+  </si>
+  <si>
+    <t>직접 13세트: 일요일(수평) 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 목요일(수직) 페이스풀 3. 10/3으로 나뉜다 — 페이스풀이 없으면 일요일 주 1회가 되므로 그 자리를 유지한다(재택도 페이스풀을 수직 날에 둔다). 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
   </si>
   <si>
     <t>직접 3세트: 수요일 데드 톱 1 + 백오프 2 (2026-10-02 백오프 복귀). 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
@@ -3988,7 +4012,7 @@
     <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.0 — 오버헤드 프레스 0.33×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
   </si>
   <si>
-    <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 1.5 — 일요일 페이스풀 0.5×3(2026-10-02). 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블 · 로프로 저항곡선과 외회전 요소를 갈랐다</t>
+    <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 케이블 리버스 플라이 3 · 수요일 벤트오버 레터럴 머신 3. 간접 1.5 — 목요일 페이스풀 0.5×3(2026-10-02). 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블 · 로프로 저항곡선과 외회전 요소를 갈랐다</t>
   </si>
   <si>
     <t>직접 12세트: 토요일 스쿼트 5 · 레그 프레스 4 · 레그 익스텐션 3. 간접 1.3 — 수요일 레그 프레스(발 높게) 0.33×4. 직접은 주 1회다(스쿼트 5×5가 한 날을 다 쓴다) — 다만 수요일 간접 덕에 자극 노출은 주 2회가 됐다 (2026-10-02)</t>
@@ -11074,7 +11098,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11162,8 +11186,8 @@
         <v>921</v>
       </c>
       <c r="E7" s="121">
-        <f>복귀_일_당기기A!$E$19</f>
-        <v>27</v>
+        <f>복귀_일_수평당기기!$E$18</f>
+        <v>22</v>
       </c>
       <c r="F7" s="114" t="s">
         <v>922</v>
@@ -11258,8 +11282,8 @@
         <v>941</v>
       </c>
       <c r="E11" s="121">
-        <f>복귀_목_당기기B!$E$19</f>
-        <v>26</v>
+        <f>복귀_목_수직당기기!$E$20</f>
+        <v>31</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>942</v>
@@ -11357,23 +11381,23 @@
         <v>956</v>
       </c>
     </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="123" t="s">
+        <v>957</v>
+      </c>
+    </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="107" t="s">
-        <v>957</v>
+      <c r="A26" s="123" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="123" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="123" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="123" t="s">
+      <c r="A29" s="107" t="s">
         <v>960</v>
       </c>
     </row>
@@ -11402,23 +11426,23 @@
         <v>965</v>
       </c>
     </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="123" t="s">
+        <v>966</v>
+      </c>
+    </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="107" t="s">
-        <v>966</v>
+      <c r="A36" s="123" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="123" t="s">
         <v>968</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="123" t="s">
+      <c r="A39" s="107" t="s">
         <v>969</v>
       </c>
     </row>
@@ -11427,23 +11451,23 @@
         <v>970</v>
       </c>
     </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="123" t="s">
+        <v>971</v>
+      </c>
+    </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="107" t="s">
-        <v>971</v>
+      <c r="A42" s="123" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="123" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="123" t="s">
+      <c r="A45" s="107" t="s">
         <v>974</v>
       </c>
     </row>
@@ -11457,23 +11481,23 @@
         <v>976</v>
       </c>
     </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="123" t="s">
+        <v>977</v>
+      </c>
+    </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="107" t="s">
-        <v>977</v>
+      <c r="A49" s="123" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="123" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="123" t="s">
+      <c r="A52" s="107" t="s">
         <v>980</v>
       </c>
     </row>
@@ -11487,29 +11511,49 @@
         <v>982</v>
       </c>
     </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="123" t="s">
+        <v>983</v>
+      </c>
+    </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="107" t="s">
-        <v>983</v>
+      <c r="A56" s="123" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="123" t="s">
         <v>986</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="123" t="s">
+      <c r="A60" s="107" t="s">
         <v>987</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="123" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="123" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="123" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="123" t="s">
+        <v>991</v>
       </c>
     </row>
   </sheetData>
@@ -11540,7 +11584,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11621,22 +11665,22 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="110" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="110" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11724,10 +11768,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="113" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="K20" s="113" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="L20" s="112" t="s">
         <v>356</v>
@@ -11765,10 +11809,10 @@
         <v>13</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -11804,10 +11848,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -11845,7 +11889,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K23" s="115" t="s">
         <v>597</v>
@@ -11884,10 +11928,10 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -11900,7 +11944,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>372</v>
@@ -11925,10 +11969,10 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -11966,10 +12010,10 @@
         <v>11.9</v>
       </c>
       <c r="J26" s="115" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="K26" s="115" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="L26" s="114"/>
       <c r="M26" s="114"/>
@@ -12007,10 +12051,10 @@
         <v>3.3</v>
       </c>
       <c r="J27" s="115" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="K27" s="115" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="L27" s="114"/>
       <c r="M27" s="114" t="s">
@@ -12048,10 +12092,10 @@
         <v>10.7</v>
       </c>
       <c r="J28" s="115" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="K28" s="115" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
@@ -12089,10 +12133,10 @@
         <v>5.8</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -12119,82 +12163,82 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="107" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
   </sheetData>
@@ -12225,27 +12269,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12302,38 +12346,38 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>280</v>
+        <v>1036</v>
       </c>
       <c r="C11" s="114" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D11" s="114">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E11" s="114">
         <v>4</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="G11" s="114">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H11" s="114">
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I18" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
-        <v>12.3</v>
+        <f t="shared" ref="I11:I17" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <v>12.7</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -12343,37 +12387,39 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1035</v>
+        <v>479</v>
       </c>
       <c r="C12" s="114" t="s">
-        <v>281</v>
-      </c>
-      <c r="D12" s="114" t="s">
-        <v>30</v>
+        <v>296</v>
+      </c>
+      <c r="D12" s="114">
+        <v>45</v>
       </c>
       <c r="E12" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="G12" s="114">
         <v>40</v>
       </c>
       <c r="H12" s="114">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I12" s="114">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1037</v>
-      </c>
-      <c r="L12" s="114"/>
+        <v>1041</v>
+      </c>
+      <c r="L12" s="114" t="s">
+        <v>1042</v>
+      </c>
       <c r="M12" s="114"/>
       <c r="N12" s="114"/>
     </row>
@@ -12382,22 +12428,22 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1038</v>
+        <v>486</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D13" s="114" t="s">
-        <v>30</v>
+      <c r="D13" s="114">
+        <v>25</v>
       </c>
       <c r="E13" s="114">
         <v>3</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G13" s="114">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H13" s="114">
         <v>120</v>
@@ -12407,92 +12453,90 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
-      <c r="N13" s="114">
-        <v>60</v>
-      </c>
+      <c r="N13" s="114"/>
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1">
       <c r="A14" s="114">
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1041</v>
+        <v>489</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>296</v>
       </c>
       <c r="D14" s="114">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E14" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G14" s="114">
         <v>40</v>
       </c>
       <c r="H14" s="114">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="I14" s="114">
         <f t="shared" si="0"/>
-        <v>12.7</v>
+        <v>6.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1043</v>
-      </c>
-      <c r="L14" s="114" t="s">
-        <v>1034</v>
-      </c>
+        <v>1046</v>
+      </c>
+      <c r="L14" s="114"/>
       <c r="M14" s="114"/>
-      <c r="N14" s="114"/>
+      <c r="N14" s="114">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
       <c r="A15" s="114">
         <v>5</v>
       </c>
       <c r="B15" s="115" t="s">
-        <v>302</v>
+        <v>498</v>
       </c>
       <c r="C15" s="114" t="s">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="D15" s="114">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="E15" s="114">
         <v>3</v>
       </c>
       <c r="F15" s="114" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="G15" s="114">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H15" s="114">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I15" s="114">
         <f t="shared" si="0"/>
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -12503,19 +12547,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
       <c r="D16" s="114">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" s="114">
         <v>3</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G16" s="114">
         <v>40</v>
@@ -12525,30 +12569,32 @@
       </c>
       <c r="I16" s="114">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
-      <c r="N16" s="114"/>
+      <c r="N16" s="114">
+        <v>60</v>
+      </c>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1">
       <c r="A17" s="114">
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>375</v>
+        <v>495</v>
       </c>
       <c r="C17" s="114" t="s">
-        <v>359</v>
+        <v>283</v>
       </c>
       <c r="D17" s="114">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E17" s="114">
         <v>3</v>
@@ -12567,10 +12613,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12578,164 +12624,128 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="114">
-        <v>8</v>
-      </c>
-      <c r="B18" s="115" t="s">
-        <v>495</v>
-      </c>
-      <c r="C18" s="114" t="s">
-        <v>283</v>
-      </c>
-      <c r="D18" s="114">
-        <v>30</v>
-      </c>
-      <c r="E18" s="114">
-        <v>3</v>
-      </c>
-      <c r="F18" s="114" t="s">
-        <v>288</v>
-      </c>
-      <c r="G18" s="114">
-        <v>40</v>
-      </c>
-      <c r="H18" s="114">
-        <v>75</v>
-      </c>
-      <c r="I18" s="114">
-        <f t="shared" si="0"/>
-        <v>6.8</v>
-      </c>
-      <c r="J18" s="115" t="s">
-        <v>1050</v>
-      </c>
-      <c r="K18" s="115" t="s">
-        <v>1051</v>
-      </c>
-      <c r="L18" s="114"/>
-      <c r="M18" s="114"/>
-      <c r="N18" s="114">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116" t="s">
+    <row r="18" spans="1:14">
+      <c r="A18" s="116"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E19" s="116">
-        <f>SUM(E11:E18)</f>
-        <v>27</v>
-      </c>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116">
-        <f>ROUND(SUM(I11:I18),0)</f>
-        <v>69</v>
+      <c r="E18" s="116">
+        <f>SUM(E11:E17)</f>
+        <v>22</v>
+      </c>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116">
+        <f>ROUND(SUM(I11:I17),0)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="107" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="107" t="s">
-        <v>1052</v>
+      <c r="A21" s="117" t="s">
+        <v>1054</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="117" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>952</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1014</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="117" t="s">
-        <v>1059</v>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="107" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="107" t="s">
-        <v>977</v>
+      <c r="A33" s="117" t="s">
+        <v>1063</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="117" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="117" t="s">
-        <v>1062</v>
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="107" t="s">
+        <v>1027</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="107" t="s">
-        <v>1023</v>
+      <c r="A38" s="117" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="118" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
     </row>
   </sheetData>
@@ -12766,7 +12776,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12852,7 +12862,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12940,10 +12950,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="113" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="K18" s="113" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="L18" s="112" t="s">
         <v>356</v>
@@ -12981,10 +12991,10 @@
         <v>12.7</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13020,10 +13030,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13059,13 +13069,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="L21" s="114" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13075,13 +13085,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="E22" s="114">
         <v>3</v>
@@ -13100,10 +13110,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13120,7 +13130,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
@@ -13139,10 +13149,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13169,77 +13179,77 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="118" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
@@ -13270,22 +13280,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13372,10 +13382,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13413,10 +13423,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13452,10 +13462,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -13466,7 +13476,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>309</v>
@@ -13491,10 +13501,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -13530,10 +13540,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -13544,7 +13554,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>939</v>
@@ -13569,10 +13579,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -13583,7 +13593,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>939</v>
@@ -13608,10 +13618,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -13647,10 +13657,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -13686,10 +13696,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13716,87 +13726,87 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="C42" s="118" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
   </sheetData>
@@ -14508,7 +14518,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14589,7 +14599,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14665,22 +14675,22 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="110" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -14768,10 +14778,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -14782,7 +14792,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -14808,10 +14818,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -14828,7 +14838,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -14847,10 +14857,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -14861,7 +14871,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -14886,10 +14896,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -14925,10 +14935,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -14939,7 +14949,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -14965,10 +14975,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -15006,10 +15016,10 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="K34" s="115" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="L34" s="114"/>
       <c r="M34" s="114"/>
@@ -15047,10 +15057,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15086,10 +15096,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15125,10 +15135,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15164,10 +15174,10 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K38" s="115" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
@@ -15205,10 +15215,10 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
@@ -15246,10 +15256,10 @@
         <v>5.8</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15276,167 +15286,167 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="107" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="107" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="117" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
     </row>
   </sheetData>
@@ -15447,7 +15457,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -15467,27 +15477,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15544,38 +15554,38 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>479</v>
+        <v>280</v>
       </c>
       <c r="C11" s="114" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D11" s="114">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E11" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="G11" s="114">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H11" s="114">
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I18" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
-        <v>9.5</v>
+        <f t="shared" ref="I11:I19" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1200</v>
+        <v>1039</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -15585,35 +15595,35 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>486</v>
+        <v>1204</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="D12" s="114">
-        <v>25</v>
+      <c r="D12" s="114" t="s">
+        <v>30</v>
       </c>
       <c r="E12" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="114" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G12" s="114">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H12" s="114">
         <v>120</v>
       </c>
       <c r="I12" s="114">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15624,35 +15634,35 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>489</v>
+        <v>1207</v>
       </c>
       <c r="C13" s="114" t="s">
-        <v>296</v>
-      </c>
-      <c r="D13" s="114">
-        <v>32</v>
+        <v>281</v>
+      </c>
+      <c r="D13" s="114" t="s">
+        <v>30</v>
       </c>
       <c r="E13" s="114">
         <v>3</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G13" s="114">
         <v>40</v>
       </c>
       <c r="H13" s="114">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="I13" s="114">
         <f t="shared" si="0"/>
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15665,10 +15675,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>498</v>
+        <v>431</v>
       </c>
       <c r="C14" s="114" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="D14" s="114">
         <v>15</v>
@@ -15677,23 +15687,23 @@
         <v>3</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="G14" s="114">
         <v>40</v>
       </c>
       <c r="H14" s="114">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I14" s="114">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15704,35 +15714,35 @@
         <v>5</v>
       </c>
       <c r="B15" s="115" t="s">
-        <v>441</v>
+        <v>302</v>
       </c>
       <c r="C15" s="114" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="D15" s="114">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="E15" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="114" t="s">
         <v>303</v>
       </c>
       <c r="G15" s="114">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H15" s="114">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="I15" s="114">
         <f t="shared" si="0"/>
-        <v>9.6999999999999993</v>
+        <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -15743,13 +15753,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>534</v>
+        <v>441</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>351</v>
       </c>
       <c r="D16" s="114">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E16" s="114">
         <v>4</v>
@@ -15765,210 +15775,254 @@
       </c>
       <c r="I16" s="114">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
-      <c r="N16" s="114">
-        <v>60</v>
-      </c>
+      <c r="N16" s="114"/>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1">
       <c r="A17" s="114">
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1211</v>
+        <v>534</v>
       </c>
       <c r="C17" s="114" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D17" s="114">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E17" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="114" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="G17" s="114">
         <v>40</v>
       </c>
       <c r="H17" s="114">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="I17" s="114">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>10.7</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
-      <c r="N17" s="114"/>
+      <c r="N17" s="114">
+        <v>60</v>
+      </c>
     </row>
     <row r="18" spans="1:14" ht="30" customHeight="1">
       <c r="A18" s="114">
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="D18" s="114">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E18" s="114">
         <v>3</v>
       </c>
       <c r="F18" s="114" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="G18" s="114">
         <v>40</v>
       </c>
       <c r="H18" s="114">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I18" s="114">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
       <c r="N18" s="114"/>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116" t="s">
+    <row r="19" spans="1:14" ht="30" customHeight="1">
+      <c r="A19" s="114">
+        <v>9</v>
+      </c>
+      <c r="B19" s="115" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C19" s="114" t="s">
+        <v>283</v>
+      </c>
+      <c r="D19" s="114">
+        <v>15</v>
+      </c>
+      <c r="E19" s="114">
+        <v>3</v>
+      </c>
+      <c r="F19" s="114" t="s">
+        <v>288</v>
+      </c>
+      <c r="G19" s="114">
+        <v>40</v>
+      </c>
+      <c r="H19" s="114">
+        <v>75</v>
+      </c>
+      <c r="I19" s="114">
+        <f t="shared" si="0"/>
+        <v>5.8</v>
+      </c>
+      <c r="J19" s="115" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K19" s="115" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="116"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E19" s="116">
-        <f>SUM(E11:E18)</f>
-        <v>26</v>
-      </c>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116">
-        <f>ROUND(SUM(I11:I18),0)</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="107" t="s">
-        <v>1217</v>
+      <c r="E20" s="116">
+        <f>SUM(E11:E19)</f>
+        <v>31</v>
+      </c>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116">
+        <f>ROUND(SUM(I11:I19),0)</f>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="117" t="s">
-        <v>1218</v>
+      <c r="A22" s="107" t="s">
+        <v>1224</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="107" t="s">
-        <v>1222</v>
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="117" t="s">
+        <v>1228</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="117" t="s">
-        <v>1223</v>
+      <c r="A28" s="107" t="s">
+        <v>1229</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="107" t="s">
-        <v>977</v>
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="117" t="s">
+        <v>1232</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="117" t="s">
-        <v>1226</v>
+      <c r="A33" s="107" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1227</v>
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="117" t="s">
+        <v>1234</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="107" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="117" t="s">
-        <v>1228</v>
+      <c r="A36" s="117" t="s">
+        <v>1235</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="117" t="s">
-        <v>1229</v>
+      <c r="A38" s="107" t="s">
+        <v>1027</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1026</v>
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="117" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="C43" s="118" t="s">
-        <v>1232</v>
+      <c r="A43" s="117" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="C45" s="118" t="s">
+        <v>1240</v>
       </c>
     </row>
   </sheetData>
@@ -16369,12 +16423,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16388,12 +16442,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16419,7 +16473,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16442,12 +16496,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16470,12 +16524,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16498,12 +16552,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16526,15 +16580,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16554,12 +16608,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -16582,15 +16636,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1038</v>
+        <v>1207</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -16610,15 +16664,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1035</v>
+        <v>1204</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -16638,12 +16692,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -16666,15 +16720,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>283</v>
@@ -16694,12 +16748,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -16722,12 +16776,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -16750,12 +16804,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -16778,12 +16832,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -16806,12 +16860,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -16834,12 +16888,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -16862,12 +16916,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -16890,12 +16944,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>302</v>
@@ -16918,15 +16972,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>368</v>
@@ -16946,12 +17000,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.25">
       <c r="A26" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>522</v>
@@ -16974,15 +17028,15 @@
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>383</v>
@@ -17002,15 +17056,15 @@
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="114" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>281</v>
@@ -17030,12 +17084,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>479</v>
@@ -17058,12 +17112,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>95</v>
@@ -17086,15 +17140,15 @@
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>421</v>
@@ -17114,15 +17168,15 @@
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C32" s="114" t="s">
         <v>421</v>
@@ -17142,12 +17196,12 @@
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25.5">
       <c r="A33" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>95</v>
@@ -17170,12 +17224,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>280</v>
@@ -17198,15 +17252,15 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1038</v>
+        <v>1207</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>432</v>
@@ -17226,15 +17280,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1035</v>
+        <v>1204</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17254,12 +17308,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5">
       <c r="A37" s="114" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>479</v>
@@ -17282,12 +17336,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="38.25">
       <c r="A38" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>424</v>
@@ -17310,12 +17364,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>537</v>
@@ -17338,15 +17392,15 @@
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="C40" s="114" t="s">
         <v>296</v>
@@ -17366,12 +17420,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>486</v>
@@ -17394,12 +17448,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
       <c r="A42" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>93</v>
@@ -17422,15 +17476,15 @@
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C43" s="114" t="s">
         <v>327</v>
@@ -17450,12 +17504,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="114" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>431</v>
@@ -17478,12 +17532,12 @@
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="51">
       <c r="A45" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>573</v>
@@ -17506,12 +17560,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B46" s="115" t="s">
         <v>498</v>
@@ -17534,12 +17588,12 @@
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>93</v>
@@ -17567,7 +17621,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>95</v>
@@ -17590,15 +17644,15 @@
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -17618,12 +17672,12 @@
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>388</v>
@@ -17651,7 +17705,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>573</v>
@@ -17674,12 +17728,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>570</v>
@@ -17702,12 +17756,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25">
       <c r="A53" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>95</v>
@@ -17730,15 +17784,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
@@ -17758,15 +17812,15 @@
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51">
       <c r="A55" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
@@ -17786,12 +17840,12 @@
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>93</v>
@@ -17814,12 +17868,12 @@
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>388</v>
@@ -17842,15 +17896,15 @@
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25.5">
       <c r="A58" s="114" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -17870,12 +17924,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="114" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="B59" s="115" t="s">
         <v>495</v>
@@ -17903,7 +17957,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="114" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>605</v>
@@ -17931,10 +17985,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -17954,12 +18008,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="38.25">
       <c r="A62" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>97</v>
@@ -17982,12 +18036,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="B63" s="115" t="s">
         <v>441</v>
@@ -18010,12 +18064,12 @@
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>531</v>
@@ -18038,12 +18092,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>600</v>
@@ -18066,12 +18120,12 @@
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>93</v>
@@ -18094,12 +18148,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>502</v>
@@ -18122,15 +18176,15 @@
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C68" s="114" t="s">
         <v>939</v>
@@ -18150,7 +18204,7 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>
@@ -18175,12 +18229,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18208,7 +18262,7 @@
         <v>363</v>
       </c>
       <c r="B5" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A5)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A5)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A5)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A5)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A5)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A5)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A5)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A5)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A5)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A5)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A5)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A5)</f>
         <v>8</v>
       </c>
       <c r="C5" s="114">
@@ -18224,7 +18278,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -18239,7 +18293,7 @@
         <v>351</v>
       </c>
       <c r="B6" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A6)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A6)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A6)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A6)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A6)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A6)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A6)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A6)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A6)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A6)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A6)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A6)</f>
         <v>16</v>
       </c>
       <c r="C6" s="114">
@@ -18255,7 +18309,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18263,7 +18317,7 @@
         <v>281</v>
       </c>
       <c r="B7" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A7)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A7)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A7)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A7)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A7)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A7)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A7)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A7)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A7)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A7)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A7)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A7)</f>
         <v>14</v>
       </c>
       <c r="C7" s="114">
@@ -18279,10 +18333,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -18294,7 +18348,7 @@
         <v>421</v>
       </c>
       <c r="B8" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A8)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A8)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A8)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A8)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A8)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A8)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A8)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A8)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A8)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A8)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A8)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A8)</f>
         <v>3</v>
       </c>
       <c r="C8" s="114">
@@ -18310,7 +18364,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18318,7 +18372,7 @@
         <v>432</v>
       </c>
       <c r="B9" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A9)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A9)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A9)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A9)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A9)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A9)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A9)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A9)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A9)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A9)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A9)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A9)</f>
         <v>3</v>
       </c>
       <c r="C9" s="114">
@@ -18334,7 +18388,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18342,7 +18396,7 @@
         <v>296</v>
       </c>
       <c r="B10" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A10)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A10)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A10)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A10)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A10)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A10)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A10)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A10)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A10)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A10)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A10)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A10)</f>
         <v>13</v>
       </c>
       <c r="C10" s="114">
@@ -18358,7 +18412,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18366,7 +18420,7 @@
         <v>327</v>
       </c>
       <c r="B11" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A11)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A11)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A11)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A11)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A11)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A11)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A11)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A11)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A11)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A11)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A11)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A11)</f>
         <v>3</v>
       </c>
       <c r="C11" s="114">
@@ -18382,7 +18436,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18390,7 +18444,7 @@
         <v>443</v>
       </c>
       <c r="B12" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A12)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A12)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A12)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A12)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A12)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A12)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A12)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A12)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A12)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A12)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A12)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A12)</f>
         <v>6</v>
       </c>
       <c r="C12" s="114">
@@ -18406,7 +18460,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18414,7 +18468,7 @@
         <v>368</v>
       </c>
       <c r="B13" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A13)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A13)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A13)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A13)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A13)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A13)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A13)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A13)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A13)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A13)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A13)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A13)</f>
         <v>10</v>
       </c>
       <c r="C13" s="114">
@@ -18430,7 +18484,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18438,7 +18492,7 @@
         <v>372</v>
       </c>
       <c r="B14" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A14)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A14)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A14)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A14)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A14)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A14)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A14)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A14)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A14)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A14)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A14)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A14)</f>
         <v>10</v>
       </c>
       <c r="C14" s="114">
@@ -18454,7 +18508,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18462,7 +18516,7 @@
         <v>383</v>
       </c>
       <c r="B15" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A15)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A15)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A15)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A15)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A15)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A15)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A15)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A15)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A15)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A15)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A15)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A15)</f>
         <v>12</v>
       </c>
       <c r="C15" s="114">
@@ -18478,10 +18532,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18493,7 +18547,7 @@
         <v>398</v>
       </c>
       <c r="B16" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A16)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A16)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A16)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A16)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A16)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A16)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A16)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A16)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A16)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A16)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A16)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A16)</f>
         <v>10</v>
       </c>
       <c r="C16" s="114">
@@ -18509,7 +18563,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18517,7 +18571,7 @@
         <v>389</v>
       </c>
       <c r="B17" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A17)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A17)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A17)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A17)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A17)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A17)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A17)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A17)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A17)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A17)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A17)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A17)</f>
         <v>7</v>
       </c>
       <c r="C17" s="114">
@@ -18533,7 +18587,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18541,7 +18595,7 @@
         <v>407</v>
       </c>
       <c r="B18" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A18)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A18)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A18)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A18)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A18)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A18)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A18)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A18)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A18)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A18)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A18)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A18)</f>
         <v>11</v>
       </c>
       <c r="C18" s="114">
@@ -18557,7 +18611,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18565,7 +18619,7 @@
         <v>322</v>
       </c>
       <c r="B19" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A19)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A19)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A19)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A19)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A19)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A19)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A19)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A19)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A19)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A19)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A19)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A19)</f>
         <v>6</v>
       </c>
       <c r="C19" s="114">
@@ -18581,7 +18635,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18589,7 +18643,7 @@
         <v>283</v>
       </c>
       <c r="B20" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A20)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A20)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A20)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A20)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A20)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A20)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A20)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A20)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A20)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A20)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A20)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A20)</f>
         <v>9</v>
       </c>
       <c r="C20" s="114">
@@ -18605,7 +18659,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18613,7 +18667,7 @@
         <v>359</v>
       </c>
       <c r="B21" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A21)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A21)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A21)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A21)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A21)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A21)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A21)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A21)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A21)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A21)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A21)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A21)</f>
         <v>9</v>
       </c>
       <c r="C21" s="114">
@@ -18629,7 +18683,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18637,7 +18691,7 @@
         <v>309</v>
       </c>
       <c r="B22" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A22)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A22)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A22)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A22)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A22)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A22)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A22)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A22)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A22)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A22)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A22)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A22)</f>
         <v>9</v>
       </c>
       <c r="C22" s="114">
@@ -18653,7 +18707,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18661,7 +18715,7 @@
         <v>313</v>
       </c>
       <c r="B23" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A23)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A23)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A23)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A23)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A23)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A23)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A23)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A23)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A23)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A23)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A23)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A23)</f>
         <v>6</v>
       </c>
       <c r="C23" s="114">
@@ -18677,7 +18731,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18685,7 +18739,7 @@
         <v>402</v>
       </c>
       <c r="B24" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A24)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A24)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A24)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A24)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A24)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A24)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A24)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A24)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A24)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A24)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A24)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A24)</f>
         <v>8</v>
       </c>
       <c r="C24" s="114">
@@ -18701,7 +18755,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18709,7 +18763,7 @@
         <v>939</v>
       </c>
       <c r="B25" s="114">
-        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A25)+SUMIFS(복귀_일_당기기A!$E:$E,복귀_일_당기기A!$C:$C,$A25)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A25)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A25)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A25)+SUMIFS(복귀_목_당기기B!$E:$E,복귀_목_당기기B!$C:$C,$A25)</f>
+        <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A25)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A25)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A25)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A25)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A25)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A25)</f>
         <v>6</v>
       </c>
       <c r="C25" s="114">
@@ -18725,7 +18779,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18748,182 +18802,182 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="107" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_E1692C7AA29BE27C0FC0ED6CBDF80B9074476154" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_751387AEAA69E7C8D54AE08EFC8143F26BF94676" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="1367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2630" uniqueCount="1374">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -2854,10 +2854,10 @@
     <t>팔 삼두/이두/전완 · 목 · 복근</t>
   </si>
   <si>
-    <t>약 48분</t>
-  </si>
-  <si>
-    <t>사용자 지정으로 구성을 그대로 둔 날. 팔이 메인인 유일한 자리라 늘어난 구간 종목을 여기 뒀다. 전완 9 · 목 6 · 복근 6이 전부 이 날이다</t>
+    <t>약 46분</t>
+  </si>
+  <si>
+    <t>사용자 지정으로 구성을 그대로 둔 날. 팔이 메인인 유일한 자리라 늘어난 구간 종목을 여기 뒀다. 전완 9 · 목 6 · 복근 6이 전부 이 날이고, 리스트 컬 손등 아래 ↔ 위는 슈퍼세트다</t>
   </si>
   <si>
     <t>수</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 433분 (7시간 13분)</t>
+    <t>약 431분 (7시간 11분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -3001,7 +3001,7 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 수 39세트 98분 · 토 38세트 95분 · 목 31세트 75분 · 화 27세트 48분 · 월 22세트 59분 · 일 22세트 58분.</t>
+    <t>· 수 39세트 98분 · 토 38세트 95분 · 목 31세트 75분 · 화 27세트 46분 · 월 22세트 59분 · 일 22세트 58분.</t>
   </si>
   <si>
     <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
@@ -3013,7 +3013,7 @@
     <t>· 등 블록 둘이 22(일) / 31(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등'). 일요일이 가장 작은 것은 의도다 — 무거운 로우 넷을 신선할 때 치는 날이라 뒤에 붙는 것을 줄였다.</t>
   </si>
   <si>
-    <t>· 주 433분 = 7시간 13분. 주 4회 370분에서 63분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 주 431분 = 7시간 11분. 주 4회 370분에서 61분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3388,13 +3388,13 @@
     <t>시티드 리스트 컬(손등 아래)</t>
   </si>
   <si>
-    <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다.</t>
+    <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다. [2026-10-02 사용자 제안] 손등 위와 슈퍼세트 — 굴근과 신근은 길항근이라 한쪽이 일하는 동안 다른 쪽이 쉰다. 같은 자리 같은 바에서 그립만 뒤집으므로 휴식 10초가 전환 시간이다.</t>
   </si>
   <si>
     <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
   </si>
   <si>
-    <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다.</t>
+    <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다. 당기기가 신근을 전혀 쓰지 않으므로 주간 신근 자극은 이 3세트와 리버스컬 3세트가 전부다 — 굴근(당기기 등척성이 온종일 쓴다)보다 직접 세트가 더 필요한 쪽이다. 라운드 간 휴식 60초.</t>
   </si>
   <si>
     <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
@@ -3445,7 +3445,10 @@
     <t>[전완 · 목 · 복근이 이 날에 몰린 이유]</t>
   </si>
   <si>
-    <t>· 전완 주 9세트가 전부 이 날이다. 그립을 쓰는 당기기가 하나도 없는 유일한 날이라 리스트 컬이 온전히 나온다.</t>
+    <t>· 전완 주 9세트가 전부 이 날이다. 그립을 쓰는 당기기가 하나도 없는 유일한 날이라 리스트 컬이 온전히 나온다 — 일요일(수평 로우 16세트)과 목요일(친업 · 랫풀다운 11세트)은 그립이 제약인 날이고, 거기에 리스트 컬을 두면 주간 전완 자극 중 가장 깎이는 자리가 된다.</t>
+  </si>
+  <si>
+    <t>· 전완을 주 2회로 쪼개고 싶으면 다음 자리는 월요일이다 — 가슴 · 어깨뿐이라 당기기가 0인 두 번째 날이고, 22세트 59분으로 작다. 다만 전완 실질이 12.0 → 18.0으로 천장(20) 근처까지 간다.</t>
   </si>
   <si>
     <t>· 전완 6 → 9 · 복부 3 → 6으로 올렸다. 현장 근무가 끝나 그립과 코어에 하루치를 얹어주던 보정이 사라졌기 때문이다 (복귀_세트검산 참조).</t>
@@ -3454,22 +3457,40 @@
     <t>· 목은 2026-10-02 신설이다. 직접 0에서 주 6세트. 데드 · 슈러그의 등척성 지지는 계수 0이라 여기서만 채워진다.</t>
   </si>
   <si>
-    <t>· 27세트 · 약 48분. 여섯 날 중 가장 짧다 — 전부 고립이고 휴식이 60~75초라 그렇다.</t>
+    <t>· 27세트 · 약 46분. 여섯 날 중 가장 짧다 — 전부 고립이고 휴식이 60~75초이며 리스트 컬 쌍이 슈퍼세트다.</t>
   </si>
   <si>
     <t>· 27세트지만 세션 상한 26의 적용 대상이 아니다. 메인 리프트가 없고 전부 고립 소근육이다.</t>
   </si>
   <si>
+    <t>슈퍼세트 (2026-10-02 사용자 제안)</t>
+  </si>
+  <si>
+    <t>· 시티드 리스트 컬 손등 아래 ↔ 손등 위를 슈퍼세트(A)로 묶었다. 굴근 ↔ 신근 길항근 쌍이고 같은 자리 같은 바에서 그립만 뒤집는다 — 토요일 · 수요일의 이너 ↔ 아우터 타이와 같은 구조다.</t>
+  </si>
+  <si>
+    <t>· 세트 수는 그대로 3 + 3이고 시간만 10분 → 7.5분으로 줄었다. 아래 휴식 10초(전환) · 위 휴식 60초(라운드 간).</t>
+  </si>
+  <si>
+    <t>· 넥 익스텐션 ↔ 플렉션은 묶지 않았다. 둘도 길항근이지만 엎드림 ↔ 누움으로 자세를 바꿔야 해 전환이 그립 뒤집기만큼 싸지 않고, 신설 부위라 세트마다 통제된 휴식을 주는 쪽이 낫다.</t>
+  </si>
+  <si>
+    <t>· 중량 크런치 ↔ 라잉 레그 레이즈도 묶지 않았다. 둘 다 복부 굴곡이라 길항이 아니라 같은 근육을 겹쳐 쓴다.</t>
+  </si>
+  <si>
     <t>· 라잉 트라이셉스 익스텐션 +60초 한 곳만. 마지막 세트에만 2단.</t>
   </si>
   <si>
     <t>· 인클라인 덤벨 컬에는 걸지 않는다 — 2026-09-07에 제외로 정한 자리다.</t>
   </si>
   <si>
+    <t>· 리스트 컬 쌍에도 걸지 않는다. 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다(이너 · 아우터와 같은 이유).</t>
+  </si>
+  <si>
     <t>· 넥 종목에는 절대 걸지 않는다. 실패지점 근처에서 목을 쓰는 것이 이 종목의 유일한 금기다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 화요일 삼두/이두/전완/목/복근 — 화요일은 팔하니 놔두고</t>
+    <t>[요청 원문 2026-10-02] 화요일 삼두/이두/전완/목/복근 — 화요일은 팔하니 놔두고  /  팔하는 날들 왜 전완은 없어? 손등 위아래 슈퍼세트로 묶어서 넣는건 어떻게 생각해?</t>
   </si>
   <si>
     <t>수요일 — 하체 후면 · 어깨 (전/측/후)</t>
@@ -4039,7 +4060,7 @@
     <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 7.6 — 인클라인 머신 · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향, 2026-10-02). 실질 16.5로 성장 구간 상단이다</t>
   </si>
   <si>
-    <t>직접 9세트: 화요일 리버스컬 3 · 시티드 리스트 컬 굴근 3 · 신근 3 (6 → 9). 간접 3.0 — 컬 3종 0.33씩. 그립을 쓰는 당기기가 없는 유일한 날에 모아 뒀다. 현장 일이 그립에 하루치를 얹던 것이 끝나 올렸다</t>
+    <t>직접 9세트: 화요일 리버스컬 3 + 시티드 리스트 컬 굴근 3 · 신근 3(2026-10-02 사용자 제안으로 길항근 슈퍼세트). 간접 3.0 — 컬 3종 0.33씩. 그립을 쓰는 당기기가 없는 유일한 날에 모아 뒀다 — 일요일(수평 로우 16) · 목요일(수직 당기기 11)은 그립이 제약인 날이라 리스트 컬이 가장 깎인다. 주 2회로 쪼개려면 다음 자리는 월요일(당기기 0인 두 번째 날)이고 실질이 18.0까지 간다. 순수 그립(로우 · 친업 · 데드 · 슈러그)은 09-04 규칙상 계수 0이다 — 등척성은 세지 않는다</t>
   </si>
   <si>
     <t>직접 6세트: 화요일 중량 크런치 3 · 라잉 레그 레이즈 3 (3 → 6). 간접 출처 없음 — 스쿼트 · 데드의 브레이싱은 등척성이라 0. 현장 일이 코어를 버티게만 하던 것이 끝나 직접 굴곡을 늘렸다</t>
@@ -13260,7 +13281,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -13494,11 +13515,11 @@
         <v>40</v>
       </c>
       <c r="H14" s="114">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I14" s="114">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
         <v>1110</v>
@@ -13507,7 +13528,9 @@
         <v>1111</v>
       </c>
       <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
+      <c r="M14" s="114" t="s">
+        <v>405</v>
+      </c>
       <c r="N14" s="114"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
@@ -13546,7 +13569,9 @@
         <v>1113</v>
       </c>
       <c r="L15" s="114"/>
-      <c r="M15" s="114"/>
+      <c r="M15" s="114" t="s">
+        <v>405</v>
+      </c>
       <c r="N15" s="114"/>
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1">
@@ -13721,7 +13746,7 @@
       <c r="H20" s="116"/>
       <c r="I20" s="116">
         <f>ROUND(SUM(I11:I19),0)</f>
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -13764,49 +13789,84 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="107" t="s">
+    <row r="31" spans="1:14">
+      <c r="A31" s="117" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="107" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="117" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
         <v>1133</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="107" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="117" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="107" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="117" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="117" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="117" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="117" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="107" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="117" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="117" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="117" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="117" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="117" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="117" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="117" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="117" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="117" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="C42" s="118" t="s">
-        <v>1137</v>
+    <row r="50" spans="3:3">
+      <c r="C50" s="118" t="s">
+        <v>1144</v>
       </c>
     </row>
   </sheetData>
@@ -14518,7 +14578,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14599,7 +14659,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14675,12 +14735,12 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -14690,7 +14750,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -14778,10 +14838,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -14792,7 +14852,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -14818,10 +14878,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -14838,7 +14898,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -14857,10 +14917,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -14871,7 +14931,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -14896,10 +14956,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -14935,10 +14995,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -14949,7 +15009,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -14975,10 +15035,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -15016,7 +15076,7 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="K34" s="115" t="s">
         <v>1005</v>
@@ -15057,10 +15117,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15096,10 +15156,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15135,10 +15195,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15174,7 +15234,7 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="K38" s="115" t="s">
         <v>1012</v>
@@ -15215,7 +15275,7 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="K39" s="115" t="s">
         <v>1014</v>
@@ -15256,10 +15316,10 @@
         <v>5.8</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15286,117 +15346,117 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -15406,12 +15466,12 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -15421,22 +15481,22 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="79" spans="1:1">
@@ -15446,7 +15506,7 @@
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
@@ -15477,7 +15537,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -15487,7 +15547,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -15579,10 +15639,10 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="L11" s="114" t="s">
         <v>1039</v>
@@ -15595,7 +15655,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
@@ -15620,10 +15680,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15634,7 +15694,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
@@ -15659,10 +15719,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15700,10 +15760,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15739,10 +15799,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -15778,10 +15838,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -15817,10 +15877,10 @@
         <v>10.7</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -15833,7 +15893,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>359</v>
@@ -15858,10 +15918,10 @@
         <v>5.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -15872,7 +15932,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>283</v>
@@ -15897,10 +15957,10 @@
         <v>5.8</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -15927,47 +15987,47 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="107" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15977,17 +16037,17 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="117" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15997,22 +16057,22 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -16022,7 +16082,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="C45" s="118" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
     </row>
   </sheetData>
@@ -16423,12 +16483,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16442,12 +16502,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16473,7 +16533,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16496,12 +16556,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16524,12 +16584,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16552,12 +16612,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16580,15 +16640,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16608,12 +16668,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -16636,15 +16696,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -16664,15 +16724,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -16692,12 +16752,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -16720,12 +16780,12 @@
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B16" s="115" t="s">
         <v>1036</v>
@@ -16748,12 +16808,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1258</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -16776,12 +16836,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -16804,12 +16864,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -16832,12 +16892,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -16860,12 +16920,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -16888,12 +16948,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -16916,12 +16976,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1265</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -16944,12 +17004,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1266</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>302</v>
@@ -16972,15 +17032,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1267</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>368</v>
@@ -17000,12 +17060,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1268</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.25">
       <c r="A26" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>522</v>
@@ -17028,15 +17088,15 @@
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1269</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>383</v>
@@ -17056,12 +17116,12 @@
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1270</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B28" s="115" t="s">
         <v>1036</v>
@@ -17084,12 +17144,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>479</v>
@@ -17112,12 +17172,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>95</v>
@@ -17140,15 +17200,15 @@
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1272</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>421</v>
@@ -17168,12 +17228,12 @@
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B32" s="115" t="s">
         <v>1036</v>
@@ -17196,12 +17256,12 @@
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1274</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25.5">
       <c r="A33" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>95</v>
@@ -17224,12 +17284,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1275</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>280</v>
@@ -17252,15 +17312,15 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1276</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>432</v>
@@ -17280,15 +17340,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1277</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17308,12 +17368,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1278</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5">
       <c r="A37" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>479</v>
@@ -17336,12 +17396,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="38.25">
       <c r="A38" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>424</v>
@@ -17364,12 +17424,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>537</v>
@@ -17392,12 +17452,12 @@
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B40" s="115" t="s">
         <v>1006</v>
@@ -17420,12 +17480,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>486</v>
@@ -17448,12 +17508,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
       <c r="A42" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>93</v>
@@ -17476,12 +17536,12 @@
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B43" s="115" t="s">
         <v>1036</v>
@@ -17504,12 +17564,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>431</v>
@@ -17532,12 +17592,12 @@
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="51">
       <c r="A45" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>573</v>
@@ -17560,12 +17620,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1286</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B46" s="115" t="s">
         <v>498</v>
@@ -17588,12 +17648,12 @@
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>93</v>
@@ -17621,7 +17681,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>95</v>
@@ -17644,15 +17704,15 @@
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1288</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -17672,12 +17732,12 @@
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1289</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>388</v>
@@ -17705,7 +17765,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>573</v>
@@ -17728,12 +17788,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>570</v>
@@ -17756,12 +17816,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1291</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25">
       <c r="A53" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>95</v>
@@ -17784,15 +17844,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
@@ -17812,15 +17872,15 @@
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51">
       <c r="A55" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
@@ -17840,12 +17900,12 @@
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>93</v>
@@ -17868,12 +17928,12 @@
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1295</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>388</v>
@@ -17896,15 +17956,15 @@
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25.5">
       <c r="A58" s="114" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -17924,12 +17984,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="114" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="B59" s="115" t="s">
         <v>495</v>
@@ -17957,7 +18017,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="114" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>605</v>
@@ -17985,10 +18045,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -18008,12 +18068,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="38.25">
       <c r="A62" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>97</v>
@@ -18036,12 +18096,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1299</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B63" s="115" t="s">
         <v>441</v>
@@ -18064,12 +18124,12 @@
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>531</v>
@@ -18092,12 +18152,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>600</v>
@@ -18120,12 +18180,12 @@
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>93</v>
@@ -18148,12 +18208,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1303</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>502</v>
@@ -18176,12 +18236,12 @@
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="B68" s="115" t="s">
         <v>1114</v>
@@ -18204,7 +18264,7 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
     </row>
   </sheetData>
@@ -18229,12 +18289,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18278,7 +18338,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -18309,7 +18369,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1309</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18333,10 +18393,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1311</v>
+        <v>1318</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -18364,7 +18424,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1312</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18388,7 +18448,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1313</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18412,7 +18472,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1314</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18436,7 +18496,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1315</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18460,7 +18520,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1316</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18484,7 +18544,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1317</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18508,7 +18568,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1318</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18532,10 +18592,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18563,7 +18623,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18587,7 +18647,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18611,7 +18671,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1323</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18635,7 +18695,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18659,7 +18719,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18683,7 +18743,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1326</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18707,7 +18767,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18731,7 +18791,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1328</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18755,7 +18815,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1329</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18779,7 +18839,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18802,182 +18862,182 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1332</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1335</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1337</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1341</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1345</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1346</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1354</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1356</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="107" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>1360</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1365</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1366</v>
+        <v>1373</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_751387AEAA69E7C8D54AE08EFC8143F26BF94676" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_CDCC47E3E49CF581AE129B2D5D931371C62E70D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2630" uniqueCount="1374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="1381">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -103,10 +103,10 @@
     <t>주당 환산 161세트</t>
   </si>
   <si>
-    <t>179세트</t>
-  </si>
-  <si>
-    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 넷(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 토요일 페이스풀)</t>
+    <t>191세트</t>
+  </si>
+  <si>
+    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 다섯(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 페이스풀 · 전완 슈퍼세트 주 3회)</t>
   </si>
   <si>
     <t>증량 방식</t>
@@ -2824,10 +2824,10 @@
     <t>등 수평 당기기 · 팔 삼두/이두</t>
   </si>
   <si>
-    <t>약 58분</t>
-  </si>
-  <si>
-    <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 블록이 둘(등 16 · 팔 6)뿐이고 가슴이 없다</t>
+    <t>약 66분</t>
+  </si>
+  <si>
+    <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 등 16 · 팔 6 · 전완 6(슈퍼세트)이고 가슴이 없다</t>
   </si>
   <si>
     <t>월</t>
@@ -2884,10 +2884,10 @@
     <t>등 수직 당기기 · 가슴(중하부) · 팔</t>
   </si>
   <si>
-    <t>약 75분</t>
-  </si>
-  <si>
-    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로</t>
+    <t>약 82분</t>
+  </si>
+  <si>
+    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 맨 뒤에 전완 슈퍼세트 6</t>
   </si>
   <si>
     <t>금</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 431분 (7시간 11분)</t>
+    <t>약 446분 (7시간 26분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -2941,7 +2941,7 @@
     <t>[빈도를 올리고 볼륨은 조금만 올렸다 — 2026-10-02]</t>
   </si>
   <si>
-    <t>· 주 4회 140세트 → 주 6회 179세트. 세트는 28% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회로 올랐다. 주 1회로 남은 것은 광배(일 14)와 사두(토 12)뿐이다.</t>
+    <t>· 주 4회 140세트 → 주 6회 191세트. 세트는 36% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회, 전완은 주 1회 → 3회로 올랐다. 주 1회로 남은 것은 사두(토 12)뿐이다.</t>
   </si>
   <si>
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
@@ -2950,7 +2950,10 @@
     <t>· [2026-10-02 사용자 추가 셋] ① 토요일 원 레그 컬 3 — 전면 하체 날에 햄스트링이 0이었다. ② 수요일 레그 프레스 발 높게 4 — 둔근 3 → 7. 내가 넣었던 시티드 레그 컬 3은 빼서 햄스트링 총량 10을 유지했다. ③ 수요일 이너 · 아우터 타이 슈퍼세트 4+4 — 하체에서 유일하게 하한 아래였던 내전근(6.5) · 중둔근(7.0)이 둘 다 성장 구간으로 들어갔다(10.5 · 11.0). ④ 페이스풀 3 — 승모 중부 · 능형근에 견갑 후인 · 외회전을 더했다. 토요일에 넣었다가 같은 날 일요일(당기기 수직)로 옮겼다 — 재택도 당기기 날에 둔다. 164 → 168 → 176 → 179.</t>
   </si>
   <si>
-    <t>· ⑤ 같은 날 등 분할 축을 근육군 → 움직임 평면으로 정정하고, 이어서 사용자 지정으로 평면을 요일에 배정했다 — 일요일 수평 · 목요일 수직. 세트 총량 179와 부위별 숫자는 하나도 안 바뀌고 날 배치만 바뀌었다.</t>
+    <t>· ⑤ 같은 날 등 분할 축을 근육군 → 움직임 평면으로 정정하고, 이어서 사용자 지정으로 평면을 요일에 배정했다 — 일요일 수평 · 목요일 수직. 세트 총량과 부위별 숫자는 안 바뀌고 날 배치만 바뀌었다.</t>
+  </si>
+  <si>
+    <t>· ⑥ 전완 리스트 컬을 길항근 슈퍼세트로 묶고(굴근 ↔ 신근) 팔 하는 날 셋 모두에 넣었다 — 사용자 지정 '그냥 다 넣어'. 일 6 · 화 6 · 목 6 + 리버스컬 3 = 전완 직접 21 · 실질 24.0. 179 → 191세트 · 446분.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -3001,19 +3004,19 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 수 39세트 98분 · 토 38세트 95분 · 목 31세트 75분 · 화 27세트 46분 · 월 22세트 59분 · 일 22세트 58분.</t>
-  </si>
-  <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다.</t>
+    <t>· 수 39세트 98분 · 목 37세트 82분 · 토 38세트 95분 · 일 28세트 66분 · 화 27세트 46분 · 월 22세트 59분.</t>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
   </si>
   <si>
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 등 블록 둘이 22(일) / 31(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등'). 일요일이 가장 작은 것은 의도다 — 무거운 로우 넷을 신선할 때 치는 날이라 뒤에 붙는 것을 줄였다.</t>
-  </si>
-  <si>
-    <t>· 주 431분 = 7시간 11분. 주 4회 370분에서 61분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 등 블록 둘이 28(일) / 37(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등').</t>
+  </si>
+  <si>
+    <t>· 주 446분 = 7시간 26분. 주 4회 370분에서 76분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3217,6 +3220,21 @@
     <t>케이블 컬 (전 구간 장력) / 머신 컬 / EZ바 프리쳐 컬</t>
   </si>
   <si>
+    <t>시티드 리스트 컬(손등 아래)</t>
+  </si>
+  <si>
+    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 굴근 쪽. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 16세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
+  </si>
+  <si>
+    <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
+  </si>
+  <si>
+    <t>신근 쪽. 당기기가 신근을 전혀 쓰지 않으므로 이쪽은 화요일과 같은 중량이 나와도 이상하지 않다 — 깎이는 것은 굴근뿐이다. 라운드 간 휴식 60초.</t>
+  </si>
+  <si>
+    <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
+  </si>
+  <si>
     <t>[무거운 수평 당기기를 이 날에 둔 이유 — 2026-10-02 사용자 지정]</t>
   </si>
   <si>
@@ -3232,7 +3250,7 @@
     <t>· 그래서 무거운 로우 7세트(바벨 4 · 해머 3)가 데드 다음날에서 완전히 빠졌다. 목요일에 남은 당기기는 수직(친업 · 랫풀다운)이고 척추 부하가 거의 0이다.</t>
   </si>
   <si>
-    <t>· 같은 이유로 이 날은 블록이 둘(수평 등 16 · 팔 6)뿐이다 — 가슴은 목요일에 남겼다(사용자 지정 '목요일 가슴/등'). 수평 당기기에만 집중하는 날이 됐다.</t>
+    <t>· 가슴은 목요일에 남겼다(사용자 지정 '목요일 가슴/등'). 이 날은 수평 등 16 · 팔 6 · 전완 6이다.</t>
   </si>
   <si>
     <t>[등을 가른 축 — 움직임 평면이다]</t>
@@ -3247,10 +3265,10 @@
     <t>· 광배 일 3 / 목 11 · 승모 중부 일 10 / 목 3 — 둘 다 주 2회다. 근육군으로 날을 가르면 '주 1회'로 적히지만 실제로는 로우가 광배를 쓰고 랫풀다운이 능형근을 쓴다.</t>
   </si>
   <si>
-    <t>· 22세트 · 약 58분. 여섯 날 중 가장 작다 — 블록이 둘뿐이고 가슴이 없다.</t>
-  </si>
-  <si>
-    <t>· 작은 것이 목적이다. 무거운 로우 넷을 신선한 상태로 치는 날이므로 뒤에 붙는 것을 줄였다.</t>
+    <t>· 28세트 · 약 66분. 2026-10-02에 전완 슈퍼세트 6세트가 들어와 22 → 28이 됐다.</t>
+  </si>
+  <si>
+    <t>· 앞쪽은 그대로다 — 무거운 로우 넷을 신선한 상태로 치는 구조는 손대지 않았고, 더한 것은 전부 맨 뒤 고립이다.</t>
   </si>
   <si>
     <t>· 그립이 이 날의 제약이다. 바벨 → 해머(서포티드) → 원암 → 스캡 슈러그 순으로 그립 부담이 줄어드는 순서다.</t>
@@ -3259,6 +3277,9 @@
     <t>· 스캡 슈러그 +60초 · 케이블 푸쉬다운 +60초 · 프리쳐 컬 +60초. 마지막 세트에만 2단.</t>
   </si>
   <si>
+    <t>· 리스트 컬 쌍에는 걸지 않는다 — 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다(이너 · 아우터와 같은 이유).</t>
+  </si>
+  <si>
     <t>· 바벨 로우 · 해머 로우에는 걸지 않는다 — 중량이 큰 로우에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
   </si>
   <si>
@@ -3268,7 +3289,7 @@
     <t>· 트랩바 슈러그에도 걸지 않는다. 선 자세로 중량을 받치는 종목이다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 일요일 등 · 팔 삼두/이두/전완을 세트 후반부에 · 등도 나누고  /  일요일로 옮기는데, 그 전에 나 등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  근데 나 일요일을 수평으로 바꿔줘. 뭔가 수평이 강도가 더 쎈거 같아서. 집중적으로 공략하고 싶다고나 할까?</t>
+    <t>[요청 원문 2026-10-02] 일요일 등 · 팔 삼두/이두/전완을 세트 후반부에 · 등도 나누고  /  일요일로 옮기는데, 그 전에 나 등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  근데 나 일요일을 수평으로 바꿔줘. 뭔가 수평이 강도가 더 쎈거 같아서. 집중적으로 공략하고 싶다고나 할까?  /  그냥 다 넣어. 팔하는 날에는 슈퍼세트로 묶어서 (전완)</t>
   </si>
   <si>
     <t>월요일 — 가슴 · 어깨 (측/후)</t>
@@ -3385,21 +3406,12 @@
     <t>EZ바 리버스컬 / 케이블 리버스컬 / 해머 컬 (중립 그립)</t>
   </si>
   <si>
-    <t>시티드 리스트 컬(손등 아래)</t>
-  </si>
-  <si>
     <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다. [2026-10-02 사용자 제안] 손등 위와 슈퍼세트 — 굴근과 신근은 길항근이라 한쪽이 일하는 동안 다른 쪽이 쉰다. 같은 자리 같은 바에서 그립만 뒤집으므로 휴식 10초가 전환 시간이다.</t>
   </si>
   <si>
-    <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
-  </si>
-  <si>
     <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다. 당기기가 신근을 전혀 쓰지 않으므로 주간 신근 자극은 이 3세트와 리버스컬 3세트가 전부다 — 굴근(당기기 등척성이 온종일 쓴다)보다 직접 세트가 더 필요한 쪽이다. 라운드 간 휴식 60초.</t>
   </si>
   <si>
-    <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
-  </si>
-  <si>
     <t>넥 익스텐션 (플레이트)</t>
   </si>
   <si>
@@ -3751,6 +3763,9 @@
     <t>케이블 컬 (전 구간 장력) / 머신 컬 / 바벨 컬</t>
   </si>
   <si>
+    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 굴근 쪽. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 11세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
+  </si>
+  <si>
     <t>[데드 다음날에 수직 당기기를 둔 이유 — 2026-10-02]</t>
   </si>
   <si>
@@ -3778,18 +3793,21 @@
     <t>· 팔이 맨 뒤인 이유 — 앞의 17세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
   </si>
   <si>
-    <t>· 31세트 · 약 75분. 여섯 날 중 세 번째다(수 39 · 토 38 다음).</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 13을 빼면 실질 18이다.</t>
-  </si>
-  <si>
-    <t>· 일요일(22세트 58분)과 합쳐 보면 등 블록 둘이 22/31로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
+    <t>· 37세트 · 약 82분. 2026-10-02에 전완 슈퍼세트 6세트가 들어와 31 → 37이 됐고, 여섯 날 중 둘째로 크다(수 39 다음).</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 19를 빼면 실질 18이다.</t>
+  </si>
+  <si>
+    <t>· 일요일(28세트 66분)과 합쳐 보면 등 블록 둘이 28/37로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
   </si>
   <si>
     <t>· 언더그립 랫풀다운 +60초 · 디클라인 케이블 플라이 +60초. 마지막 세트에만 2단.</t>
   </si>
   <si>
+    <t>· 리스트 컬 쌍에는 걸지 않는다 — 슈퍼세트라 한쪽만 길어지면 라운드가 어긋난다.</t>
+  </si>
+  <si>
     <t>· 친업 · 와이드 랫풀다운에는 걸지 않는다 — 데드 다음날이라 그립이 먼저 나가고 등이 실패지점에 못 간다.</t>
   </si>
   <si>
@@ -3799,7 +3817,7 @@
     <t>· 페이스풀에도 걸지 않는다. 가벼운 외회전 종목이라 실패 뒤 반복에서 팔꿈치가 먼저 내려온다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  일요일을 수평으로 바꿔줘</t>
+    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  일요일을 수평으로 바꿔줘  /  그냥 다 넣어. 팔하는 날에는 슈퍼세트로 묶어서 (전완)</t>
   </si>
   <si>
     <t>복귀판 간접 세트 계수 맵 — 복귀_세트검산 간접 열(C)의 계산 원천</t>
@@ -4060,7 +4078,7 @@
     <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 7.6 — 인클라인 머신 · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향, 2026-10-02). 실질 16.5로 성장 구간 상단이다</t>
   </si>
   <si>
-    <t>직접 9세트: 화요일 리버스컬 3 + 시티드 리스트 컬 굴근 3 · 신근 3(2026-10-02 사용자 제안으로 길항근 슈퍼세트). 간접 3.0 — 컬 3종 0.33씩. 그립을 쓰는 당기기가 없는 유일한 날에 모아 뒀다 — 일요일(수평 로우 16) · 목요일(수직 당기기 11)은 그립이 제약인 날이라 리스트 컬이 가장 깎인다. 주 2회로 쪼개려면 다음 자리는 월요일(당기기 0인 두 번째 날)이고 실질이 18.0까지 간다. 순수 그립(로우 · 친업 · 데드 · 슈러그)은 09-04 규칙상 계수 0이다 — 등척성은 세지 않는다</t>
+    <t>직접 21세트: 리스트 컬 굴근 · 신근 슈퍼세트를 팔 하는 날 셋에 각 3+3(일 · 화 · 목) + 화요일 리버스컬 3. 간접 3.0 — 컬 3종 0.33씩. [2026-10-02 사용자 지정 '그냥 다 넣어'] 9 → 21로 올렸고 빈도가 주 1회 → 3회가 됐다. 실질 24.0으로 천장(20)을 넘겨 '과다 점검'이 뜨는 첫 부위다. 굴근은 일 · 목에서 당기기(16 · 11세트) 뒤에 오므로 중량을 7.5로 낮춰 잡았다(화요일 10) — 신근은 당기기가 전혀 안 쓰므로 세 날 다 같은 중량이 나와도 이상하지 않다. 되돌리려면 일 · 목의 굴근(손등 아래)부터 뺀다 — 순수 그립이 온종일 등척성으로 쓰는 쪽이고, 09-04 규칙상 그 등척성은 계수 0이라 표에 안 보이지만 실제 부하는 있다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다</t>
   </si>
   <si>
     <t>직접 6세트: 화요일 중량 크런치 3 · 라잉 레그 레이즈 3 (3 → 6). 간접 출처 없음 — 스쿼트 · 데드의 브레이싱은 등척성이라 0. 현장 일이 코어를 버티게만 하던 것이 끝나 직접 굴곡을 늘렸다</t>
@@ -4147,7 +4165,10 @@
     <t>· 기립근 6.5 · 승모 상부 4.5 · 승모 하부 5.0 · 종아리 6.0 · 복부 6.0 · 내전근 6.0 — '보완 필요'로 뜨지만 넷은 이번에 올린 자리이고 이 이상 올리면 세션이 상한을 넘는다. 다음 카드는 여기다.</t>
   </si>
   <si>
-    <t>· 중둔근 11.0 · 내전근 10.5 — 2026-10-02에 수요일 이너/아우터 슈퍼세트가 들어와 둘 다 하한 아래(7.0 · 6.5)에서 성장 구간으로 올라왔다. 하체에서 '보완 필요'로 남은 곳은 이제 종아리 6.0뿐이다.</t>
+    <t>· 중둔근 11.0 · 내전근 12.5 — 2026-10-02에 수요일 이너/아우터 슈퍼세트가 들어와 둘 다 하한 아래(7.0 · 6.5)에서 성장 구간으로 올라왔다. 하체에서 '보완 필요'로 남은 곳은 이제 종아리 6.0뿐이다.</t>
+  </si>
+  <si>
+    <t>· 전완 24.0 — **'과다 점검'이 뜨는 유일한 부위이고 그게 뜬 첫 사례다**(2026-10-02 사용자 지정). 표가 금지하지는 않는다. 다만 손목 · 팔꿈치가 시큰해지면 가장 먼저 의심할 자리이고, 되돌리는 순서는 일 · 목의 굴근(손등 아래) → 리버스컬이다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다.</t>
   </si>
   <si>
     <t>· 둔근 14.0 · 햄스트링 14.0 — 2026-10-02에 둘 다 올라왔다(둔근 10 → 14 · 햄 13 → 14). 수요일이 고관절 신전 넷(데드 · 루마니안 · 발 높은 레그 프레스 · 힙 쓰러스트)을 다 가진 날이 됐기 때문이다. 둘 다 성장 구간 안이고 천장까지 여유가 있다.</t>
@@ -11119,7 +11140,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11207,8 +11228,8 @@
         <v>921</v>
       </c>
       <c r="E7" s="121">
-        <f>복귀_일_수평당기기!$E$18</f>
-        <v>22</v>
+        <f>복귀_일_수평당기기!$E$20</f>
+        <v>28</v>
       </c>
       <c r="F7" s="114" t="s">
         <v>922</v>
@@ -11303,8 +11324,8 @@
         <v>941</v>
       </c>
       <c r="E11" s="121">
-        <f>복귀_목_수직당기기!$E$20</f>
-        <v>31</v>
+        <f>복귀_목_수직당기기!$E$22</f>
+        <v>37</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>942</v>
@@ -11345,7 +11366,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F13" s="116" t="s">
         <v>946</v>
@@ -11462,13 +11483,13 @@
         <v>968</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="107" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="123" t="s">
         <v>969</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="123" t="s">
+      <c r="A40" s="107" t="s">
         <v>970</v>
       </c>
     </row>
@@ -11487,13 +11508,13 @@
         <v>973</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="107" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="123" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="123" t="s">
+      <c r="A46" s="107" t="s">
         <v>975</v>
       </c>
     </row>
@@ -11517,13 +11538,13 @@
         <v>979</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="107" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" s="123" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="123" t="s">
+      <c r="A53" s="107" t="s">
         <v>981</v>
       </c>
     </row>
@@ -11552,13 +11573,13 @@
         <v>986</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="107" t="s">
+    <row r="59" spans="1:1">
+      <c r="A59" s="123" t="s">
         <v>987</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="123" t="s">
+      <c r="A61" s="107" t="s">
         <v>988</v>
       </c>
     </row>
@@ -11575,6 +11596,11 @@
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
         <v>991</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="123" t="s">
+        <v>992</v>
       </c>
     </row>
   </sheetData>
@@ -11605,7 +11631,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11686,22 +11712,22 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="110" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11789,10 +11815,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="113" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="K20" s="113" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="L20" s="112" t="s">
         <v>356</v>
@@ -11830,10 +11856,10 @@
         <v>13</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -11869,10 +11895,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -11910,7 +11936,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K23" s="115" t="s">
         <v>597</v>
@@ -11949,10 +11975,10 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -11965,7 +11991,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>372</v>
@@ -11990,10 +12016,10 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -12031,10 +12057,10 @@
         <v>11.9</v>
       </c>
       <c r="J26" s="115" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="K26" s="115" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="L26" s="114"/>
       <c r="M26" s="114"/>
@@ -12072,10 +12098,10 @@
         <v>3.3</v>
       </c>
       <c r="J27" s="115" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="K27" s="115" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="L27" s="114"/>
       <c r="M27" s="114" t="s">
@@ -12113,10 +12139,10 @@
         <v>10.7</v>
       </c>
       <c r="J28" s="115" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="K28" s="115" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
@@ -12154,10 +12180,10 @@
         <v>5.8</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -12184,82 +12210,82 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="107" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
   </sheetData>
@@ -12270,7 +12296,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12290,27 +12316,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12367,7 +12393,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>296</v>
@@ -12388,17 +12414,17 @@
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I17" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <f t="shared" ref="I11:I19" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.7</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -12433,13 +12459,13 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="L12" s="114" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="M12" s="114"/>
       <c r="N12" s="114"/>
@@ -12474,10 +12500,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -12513,10 +12539,10 @@
         <v>6.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -12554,10 +12580,10 @@
         <v>6.5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -12593,10 +12619,10 @@
         <v>6.8</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -12634,10 +12660,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12645,128 +12671,215 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="116"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116" t="s">
+    <row r="18" spans="1:14" ht="30" customHeight="1">
+      <c r="A18" s="114">
+        <v>8</v>
+      </c>
+      <c r="B18" s="115" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C18" s="114" t="s">
+        <v>309</v>
+      </c>
+      <c r="D18" s="114">
+        <v>7.5</v>
+      </c>
+      <c r="E18" s="114">
+        <v>3</v>
+      </c>
+      <c r="F18" s="114">
+        <v>15</v>
+      </c>
+      <c r="G18" s="114">
+        <v>40</v>
+      </c>
+      <c r="H18" s="114">
+        <v>10</v>
+      </c>
+      <c r="I18" s="114">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+      <c r="J18" s="115" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K18" s="115" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114" t="s">
+        <v>405</v>
+      </c>
+      <c r="N18" s="114"/>
+    </row>
+    <row r="19" spans="1:14" ht="30" customHeight="1">
+      <c r="A19" s="114">
+        <v>9</v>
+      </c>
+      <c r="B19" s="115" t="s">
+        <v>608</v>
+      </c>
+      <c r="C19" s="114" t="s">
+        <v>309</v>
+      </c>
+      <c r="D19" s="114">
+        <v>7.5</v>
+      </c>
+      <c r="E19" s="114">
+        <v>3</v>
+      </c>
+      <c r="F19" s="114">
+        <v>15</v>
+      </c>
+      <c r="G19" s="114">
+        <v>40</v>
+      </c>
+      <c r="H19" s="114">
+        <v>60</v>
+      </c>
+      <c r="I19" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J19" s="115" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K19" s="115" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114" t="s">
+        <v>405</v>
+      </c>
+      <c r="N19" s="114"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="116"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E18" s="116">
-        <f>SUM(E11:E17)</f>
-        <v>22</v>
-      </c>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="116">
-        <f>ROUND(SUM(I11:I17),0)</f>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="107" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="117" t="s">
-        <v>1054</v>
+      <c r="E20" s="116">
+        <f>SUM(E11:E19)</f>
+        <v>28</v>
+      </c>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116">
+        <f>ROUND(SUM(I11:I19),0)</f>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="117" t="s">
-        <v>1055</v>
+      <c r="A22" s="107" t="s">
+        <v>1059</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1058</v>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="117" t="s">
+        <v>1063</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="107" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="117" t="s">
-        <v>1060</v>
+      <c r="A27" s="117" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="117" t="s">
-        <v>1061</v>
+      <c r="A29" s="107" t="s">
+        <v>1065</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1062</v>
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="117" t="s">
+        <v>1067</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="107" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="117" t="s">
-        <v>1063</v>
+      <c r="A32" s="117" t="s">
+        <v>1068</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="117" t="s">
-        <v>1064</v>
+      <c r="A34" s="107" t="s">
+        <v>981</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="117" t="s">
-        <v>1065</v>
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="117" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="107" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="117" t="s">
-        <v>1066</v>
+      <c r="A37" s="117" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="117" t="s">
-        <v>1067</v>
+      <c r="A39" s="107" t="s">
+        <v>1028</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1030</v>
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="117" t="s">
+        <v>1075</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="C44" s="118" t="s">
-        <v>1070</v>
+      <c r="A44" s="117" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="117" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="C47" s="118" t="s">
+        <v>1077</v>
       </c>
     </row>
   </sheetData>
@@ -12797,7 +12910,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12883,7 +12996,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12971,10 +13084,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="113" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="K18" s="113" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="L18" s="112" t="s">
         <v>356</v>
@@ -13012,10 +13125,10 @@
         <v>12.7</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13051,10 +13164,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13090,13 +13203,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="L21" s="114" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13106,13 +13219,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="E22" s="114">
         <v>3</v>
@@ -13131,10 +13244,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13151,7 +13264,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
@@ -13170,10 +13283,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13200,77 +13313,77 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="118" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
@@ -13301,22 +13414,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13403,10 +13516,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13444,10 +13557,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13483,10 +13596,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -13497,7 +13610,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1109</v>
+        <v>1054</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>309</v>
@@ -13522,10 +13635,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1111</v>
+        <v>1056</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114" t="s">
@@ -13563,10 +13676,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1113</v>
+        <v>1058</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114" t="s">
@@ -13579,7 +13692,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>939</v>
@@ -13604,10 +13717,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -13618,7 +13731,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>939</v>
@@ -13643,10 +13756,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -13682,10 +13795,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -13721,10 +13834,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13751,122 +13864,122 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="107" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="107" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="107" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
   </sheetData>
@@ -14578,7 +14691,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14659,7 +14772,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14735,22 +14848,22 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="110" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -14838,10 +14951,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -14852,7 +14965,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -14878,10 +14991,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -14898,7 +15011,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -14917,10 +15030,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -14931,7 +15044,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -14956,10 +15069,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -14995,10 +15108,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -15009,7 +15122,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -15035,10 +15148,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -15076,10 +15189,10 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="K34" s="115" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="L34" s="114"/>
       <c r="M34" s="114"/>
@@ -15117,10 +15230,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15156,10 +15269,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15195,10 +15308,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15234,10 +15347,10 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="K38" s="115" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
@@ -15275,10 +15388,10 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
@@ -15316,10 +15429,10 @@
         <v>5.8</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15346,167 +15459,167 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="107" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="107" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="117" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
     </row>
   </sheetData>
@@ -15517,7 +15630,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -15537,27 +15650,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15635,17 +15748,17 @@
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I19" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <f t="shared" ref="I11:I21" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -15655,7 +15768,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
@@ -15680,10 +15793,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15694,7 +15807,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
@@ -15719,10 +15832,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15760,10 +15873,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15799,10 +15912,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -15838,10 +15951,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -15877,10 +15990,10 @@
         <v>10.7</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -15893,7 +16006,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>359</v>
@@ -15918,10 +16031,10 @@
         <v>5.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -15932,7 +16045,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>283</v>
@@ -15957,132 +16070,219 @@
         <v>5.8</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
       <c r="N19" s="114"/>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="116"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116" t="s">
+    <row r="20" spans="1:14" ht="30" customHeight="1">
+      <c r="A20" s="114">
+        <v>10</v>
+      </c>
+      <c r="B20" s="115" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C20" s="114" t="s">
+        <v>309</v>
+      </c>
+      <c r="D20" s="114">
+        <v>7.5</v>
+      </c>
+      <c r="E20" s="114">
+        <v>3</v>
+      </c>
+      <c r="F20" s="114">
+        <v>15</v>
+      </c>
+      <c r="G20" s="114">
+        <v>40</v>
+      </c>
+      <c r="H20" s="114">
+        <v>10</v>
+      </c>
+      <c r="I20" s="114">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+      <c r="J20" s="115" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K20" s="115" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114" t="s">
+        <v>405</v>
+      </c>
+      <c r="N20" s="114"/>
+    </row>
+    <row r="21" spans="1:14" ht="30" customHeight="1">
+      <c r="A21" s="114">
+        <v>11</v>
+      </c>
+      <c r="B21" s="115" t="s">
+        <v>608</v>
+      </c>
+      <c r="C21" s="114" t="s">
+        <v>309</v>
+      </c>
+      <c r="D21" s="114">
+        <v>7.5</v>
+      </c>
+      <c r="E21" s="114">
+        <v>3</v>
+      </c>
+      <c r="F21" s="114">
+        <v>15</v>
+      </c>
+      <c r="G21" s="114">
+        <v>40</v>
+      </c>
+      <c r="H21" s="114">
+        <v>60</v>
+      </c>
+      <c r="I21" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="115" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K21" s="115" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114" t="s">
+        <v>405</v>
+      </c>
+      <c r="N21" s="114"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E20" s="116">
-        <f>SUM(E11:E19)</f>
-        <v>31</v>
-      </c>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116">
-        <f>ROUND(SUM(I11:I19),0)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="107" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="117" t="s">
-        <v>1232</v>
+      <c r="E22" s="116">
+        <f>SUM(E11:E21)</f>
+        <v>37</v>
+      </c>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116">
+        <f>ROUND(SUM(I11:I21),0)</f>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="117" t="s">
-        <v>1233</v>
+      <c r="A24" s="107" t="s">
+        <v>1236</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1235</v>
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="117" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="107" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="117" t="s">
-        <v>1237</v>
+      <c r="A28" s="117" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="117" t="s">
-        <v>1238</v>
+      <c r="A30" s="107" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1239</v>
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="117" t="s">
+        <v>1243</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="107" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="117" t="s">
-        <v>1240</v>
+      <c r="A33" s="117" t="s">
+        <v>1244</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="117" t="s">
-        <v>1241</v>
+      <c r="A35" s="107" t="s">
+        <v>981</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1242</v>
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="117" t="s">
+        <v>1246</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="107" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="117" t="s">
-        <v>1243</v>
+      <c r="A38" s="117" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="117" t="s">
-        <v>1244</v>
+      <c r="A40" s="107" t="s">
+        <v>1028</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1030</v>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="117" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="C45" s="118" t="s">
-        <v>1247</v>
+      <c r="A45" s="117" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="117" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="C48" s="118" t="s">
+        <v>1253</v>
       </c>
     </row>
   </sheetData>
@@ -16483,12 +16683,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16502,12 +16702,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16533,7 +16733,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16556,12 +16756,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16584,12 +16784,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16612,12 +16812,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16640,15 +16840,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16668,12 +16868,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -16696,15 +16896,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -16724,15 +16924,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -16752,12 +16952,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -16780,15 +16980,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>283</v>
@@ -16808,12 +17008,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -16836,12 +17036,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -16864,12 +17064,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -16892,12 +17092,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -16920,12 +17120,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -16948,12 +17148,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -16976,12 +17176,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -17004,12 +17204,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>302</v>
@@ -17032,15 +17232,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>368</v>
@@ -17060,12 +17260,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.25">
       <c r="A26" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>522</v>
@@ -17088,15 +17288,15 @@
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>383</v>
@@ -17116,15 +17316,15 @@
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>281</v>
@@ -17144,12 +17344,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>479</v>
@@ -17172,12 +17372,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>95</v>
@@ -17200,15 +17400,15 @@
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>421</v>
@@ -17228,15 +17428,15 @@
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C32" s="114" t="s">
         <v>421</v>
@@ -17256,12 +17456,12 @@
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25.5">
       <c r="A33" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>95</v>
@@ -17284,12 +17484,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>280</v>
@@ -17312,15 +17512,15 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>432</v>
@@ -17340,15 +17540,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17368,12 +17568,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5">
       <c r="A37" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>479</v>
@@ -17396,12 +17596,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="38.25">
       <c r="A38" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>424</v>
@@ -17424,12 +17624,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>537</v>
@@ -17452,15 +17652,15 @@
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C40" s="114" t="s">
         <v>296</v>
@@ -17480,12 +17680,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>486</v>
@@ -17508,12 +17708,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
       <c r="A42" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>93</v>
@@ -17536,15 +17736,15 @@
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C43" s="114" t="s">
         <v>327</v>
@@ -17564,12 +17764,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>431</v>
@@ -17592,12 +17792,12 @@
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="51">
       <c r="A45" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>573</v>
@@ -17620,12 +17820,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B46" s="115" t="s">
         <v>498</v>
@@ -17648,12 +17848,12 @@
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>93</v>
@@ -17681,7 +17881,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>95</v>
@@ -17704,15 +17904,15 @@
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -17732,12 +17932,12 @@
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>388</v>
@@ -17765,7 +17965,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>573</v>
@@ -17788,12 +17988,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>570</v>
@@ -17816,12 +18016,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25">
       <c r="A53" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>95</v>
@@ -17844,15 +18044,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
@@ -17872,15 +18072,15 @@
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51">
       <c r="A55" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
@@ -17900,12 +18100,12 @@
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>93</v>
@@ -17928,12 +18128,12 @@
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>388</v>
@@ -17956,15 +18156,15 @@
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25.5">
       <c r="A58" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -17984,12 +18184,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B59" s="115" t="s">
         <v>495</v>
@@ -18017,7 +18217,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="114" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>605</v>
@@ -18045,10 +18245,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -18068,12 +18268,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="38.25">
       <c r="A62" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>97</v>
@@ -18096,12 +18296,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B63" s="115" t="s">
         <v>441</v>
@@ -18124,12 +18324,12 @@
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>531</v>
@@ -18152,12 +18352,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>600</v>
@@ -18180,12 +18380,12 @@
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>93</v>
@@ -18208,12 +18408,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>502</v>
@@ -18236,15 +18436,15 @@
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C68" s="114" t="s">
         <v>939</v>
@@ -18264,7 +18464,7 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
     </row>
   </sheetData>
@@ -18275,7 +18475,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -18289,12 +18489,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18338,7 +18538,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -18369,7 +18569,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18393,10 +18593,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -18424,7 +18624,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18448,7 +18648,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18472,7 +18672,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18496,7 +18696,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18520,7 +18720,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18544,7 +18744,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18568,7 +18768,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18592,10 +18792,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18623,7 +18823,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18647,7 +18847,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18671,7 +18871,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18695,7 +18895,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18719,7 +18919,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18743,7 +18943,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18752,7 +18952,7 @@
       </c>
       <c r="B22" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A22)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A22)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A22)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A22)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A22)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A22)</f>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C22" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A22),0.5)</f>
@@ -18760,14 +18960,14 @@
       </c>
       <c r="D22" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E22" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>충분</v>
+        <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18791,7 +18991,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -18815,7 +19015,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -18839,7 +19039,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18848,11 +19048,11 @@
       </c>
       <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>239</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -18862,182 +19062,187 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="107" t="s">
-        <v>1366</v>
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="123" t="s">
+        <v>1372</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="123" t="s">
-        <v>1367</v>
+      <c r="A62" s="107" t="s">
+        <v>1373</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1373</v>
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="123" t="s">
+        <v>1380</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CDCC47E3E49CF581AE129B2D5D931371C62E70D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_0F1087E5D91BF74F36C6DA343B93137146A78851" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="1381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="1382">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -3223,13 +3223,13 @@
     <t>시티드 리스트 컬(손등 아래)</t>
   </si>
   <si>
-    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 굴근 쪽. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 16세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
+    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 16세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
   </si>
   <si>
     <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
   </si>
   <si>
-    <t>신근 쪽. 당기기가 신근을 전혀 쓰지 않으므로 이쪽은 화요일과 같은 중량이 나와도 이상하지 않다 — 깎이는 것은 굴근뿐이다. 라운드 간 휴식 60초.</t>
+    <t>손등을 위로 — 손목 신전, 전완 뒷면 신근군(요측 · 척측수근신근 + 지신근). 굴근과 앞뒤로 갈린 다른 근육 묶음이다. 당기기가 신근을 전혀 쓰지 않으므로 이쪽은 세 날 다 같은 중량이다 — 깎이는 것은 굴근뿐이다. 라운드 간 휴식 60초.</t>
   </si>
   <si>
     <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
@@ -3406,10 +3406,10 @@
     <t>EZ바 리버스컬 / 케이블 리버스컬 / 해머 컬 (중립 그립)</t>
   </si>
   <si>
-    <t>굴근 쪽. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다 — 전완을 화요일에 모은 이유다. [2026-10-02 사용자 제안] 손등 위와 슈퍼세트 — 굴근과 신근은 길항근이라 한쪽이 일하는 동안 다른 쪽이 쉰다. 같은 자리 같은 바에서 그립만 뒤집으므로 휴식 10초가 전환 시간이다.</t>
-  </si>
-  <si>
-    <t>신근 쪽. 굴근과 짝으로 가야 손목이 한쪽으로 당겨지지 않는다. 당기기가 신근을 전혀 쓰지 않으므로 주간 신근 자극은 이 3세트와 리버스컬 3세트가 전부다 — 굴근(당기기 등척성이 온종일 쓴다)보다 직접 세트가 더 필요한 쪽이다. 라운드 간 휴식 60초.</t>
+    <t>손바닥을 위로 — 손목 굴곡. 전완 앞면(손바닥쪽) 굴근군이다: 요측 · 척측수근굴근 + 장요굴근, 쥐는 동안 심지 · 천지굴근이 보조한다. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다 (2026-10-02).</t>
+  </si>
+  <si>
+    <t>손등을 위로 — 손목 신전. 전완 뒷면(손등쪽) 신근군이다: 요측수근신근 장 · 단, 척측수근신근, 지신근. 굴근과 완전히 다른 근육 묶음이고 앞뒤로 갈린다. 당기기가 신근을 전혀 쓰지 않으므로 주간 신근 자극은 리스트 컬 9세트와 리버스컬 3세트가 전부다. [2026-10-02 중량 정정] 신근은 굴근의 절반 남짓한 힘밖에 없어 같은 10kg을 쓰는 것이 말이 안 됐다 — 7.5로 내렸다(재택도 굴근 15 / 신근 10으로 갈라 둔다). 15회를 못 채우면 더 내린다. 일 · 목과 같은 중량인 이유는 당기기가 신근을 안 써서 날마다 흔들리지 않기 때문이다.</t>
   </si>
   <si>
     <t>넥 익스텐션 (플레이트)</t>
@@ -3460,7 +3460,10 @@
     <t>· 전완 주 9세트가 전부 이 날이다. 그립을 쓰는 당기기가 하나도 없는 유일한 날이라 리스트 컬이 온전히 나온다 — 일요일(수평 로우 16세트)과 목요일(친업 · 랫풀다운 11세트)은 그립이 제약인 날이고, 거기에 리스트 컬을 두면 주간 전완 자극 중 가장 깎이는 자리가 된다.</t>
   </si>
   <si>
-    <t>· 전완을 주 2회로 쪼개고 싶으면 다음 자리는 월요일이다 — 가슴 · 어깨뿐이라 당기기가 0인 두 번째 날이고, 22세트 59분으로 작다. 다만 전완 실질이 12.0 → 18.0으로 천장(20) 근처까지 간다.</t>
+    <t>· [2026-10-02] 사용자 지정으로 리스트 컬 슈퍼세트를 팔 하는 날 셋(일 · 화 · 목) 모두에 넣었다. 전완 직접 21 · 실질 24.0 — '과다 점검'이 뜨는 첫 부위다.</t>
+  </si>
+  <si>
+    <t>· 전완은 세 갈래이고 셋을 다 덮는다 — 손목 굴근군(앞면 · 손등 아래 리스트 컬 9) · 손목 신근군(뒷면 · 손등 위 리스트 컬 9) · 상완요골근(요측이고 팔꿈치를 넘는다 · 리버스컬 3). 앞뒤로 갈리는 것은 리스트 컬 두 개이고, 요측 / 척측(엄지쪽 / 새끼손가락쪽)으로 갈리는 종목은 없다 — 리스트 컬은 요측 · 척측 머리를 둘 다 쓴다.</t>
   </si>
   <si>
     <t>· 전완 6 → 9 · 복부 3 → 6으로 올렸다. 현장 근무가 끝나 그립과 코어에 하루치를 얹어주던 보정이 사라졌기 때문이다 (복귀_세트검산 참조).</t>
@@ -3763,7 +3766,7 @@
     <t>케이블 컬 (전 구간 장력) / 머신 컬 / 바벨 컬</t>
   </si>
   <si>
-    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 굴근 쪽. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 11세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
+    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 11세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
   </si>
   <si>
     <t>[데드 다음날에 수직 당기기를 둔 이유 — 2026-10-02]</t>
@@ -4078,7 +4081,7 @@
     <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 7.6 — 인클라인 머신 · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향, 2026-10-02). 실질 16.5로 성장 구간 상단이다</t>
   </si>
   <si>
-    <t>직접 21세트: 리스트 컬 굴근 · 신근 슈퍼세트를 팔 하는 날 셋에 각 3+3(일 · 화 · 목) + 화요일 리버스컬 3. 간접 3.0 — 컬 3종 0.33씩. [2026-10-02 사용자 지정 '그냥 다 넣어'] 9 → 21로 올렸고 빈도가 주 1회 → 3회가 됐다. 실질 24.0으로 천장(20)을 넘겨 '과다 점검'이 뜨는 첫 부위다. 굴근은 일 · 목에서 당기기(16 · 11세트) 뒤에 오므로 중량을 7.5로 낮춰 잡았다(화요일 10) — 신근은 당기기가 전혀 안 쓰므로 세 날 다 같은 중량이 나와도 이상하지 않다. 되돌리려면 일 · 목의 굴근(손등 아래)부터 뺀다 — 순수 그립이 온종일 등척성으로 쓰는 쪽이고, 09-04 규칙상 그 등척성은 계수 0이라 표에 안 보이지만 실제 부하는 있다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다</t>
+    <t>직접 21세트: 리스트 컬 굴근 · 신근 슈퍼세트를 팔 하는 날 셋에 각 3+3(일 · 화 · 목) + 화요일 리버스컬 3. 간접 3.0 — 컬 3종 0.33씩. [2026-10-02 사용자 지정 '그냥 다 넣어'] 9 → 21로 올렸고 빈도가 주 1회 → 3회가 됐다. 실질 24.0으로 천장(20)을 넘겨 '과다 점검'이 뜨는 첫 부위다. 굴근은 일 · 목에서 당기기(16 · 11세트) 뒤에 오므로 중량을 7.5로 낮춰 잡았다(화요일 10) — 신근은 세 날 다 같은 중량이다 — 당기기가 신근을 전혀 쓰지 않아 날마다 흔들리지 않는다. 전완은 세 갈래이고 셋을 다 덮는다 — 손목 굴근군(앞면 · 손등 아래 9) · 손목 신근군(뒷면 · 손등 위 9) · 상완요골근(요측 · 팔꿈치를 넘는다 · 리버스컬 3). 리스트 컬 두 개가 가르는 것은 앞/뒤이고, 요측 / 척측(엄지쪽 / 새끼손가락쪽)으로 가르는 종목은 없다. 신근 중량은 7.5로 통일했다 — 굴근의 절반 남짓한 힘이라 같은 10kg을 쓰는 것이 말이 안 됐다(재택도 굴근 15 / 신근 10으로 갈라 둔다). 되돌리려면 일 · 목의 굴근(손등 아래)부터 뺀다 — 순수 그립이 온종일 등척성으로 쓰는 쪽이고, 09-04 규칙상 그 등척성은 계수 0이라 표에 안 보이지만 실제 부하는 있다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다</t>
   </si>
   <si>
     <t>직접 6세트: 화요일 중량 크런치 3 · 라잉 레그 레이즈 3 (3 → 6). 간접 출처 없음 — 스쿼트 · 데드의 브레이싱은 등척성이라 0. 현장 일이 코어를 버티게만 하던 것이 끝나 직접 굴곡을 늘렸다</t>
@@ -13394,7 +13397,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -13657,7 +13660,7 @@
         <v>309</v>
       </c>
       <c r="D15" s="114">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="E15" s="114">
         <v>3</v>
@@ -13907,14 +13910,14 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="107" t="s">
+    <row r="32" spans="1:14">
+      <c r="A32" s="117" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="107" t="s">
         <v>981</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="117" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -13922,13 +13925,13 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="107" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="117" t="s">
         <v>1139</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="117" t="s">
+      <c r="A38" s="107" t="s">
         <v>1140</v>
       </c>
     </row>
@@ -13947,14 +13950,14 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="107" t="s">
+    <row r="42" spans="1:1">
+      <c r="A42" s="117" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="107" t="s">
         <v>1028</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="117" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -13974,12 +13977,17 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="117" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="118" t="s">
-        <v>1148</v>
+    <row r="51" spans="1:3">
+      <c r="C51" s="118" t="s">
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -14691,7 +14699,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14772,7 +14780,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14848,12 +14856,12 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -14863,7 +14871,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -14951,10 +14959,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -14965,7 +14973,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -14991,10 +14999,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -15011,7 +15019,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -15030,10 +15038,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -15044,7 +15052,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -15069,10 +15077,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -15108,10 +15116,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -15122,7 +15130,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -15148,10 +15156,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -15189,7 +15197,7 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K34" s="115" t="s">
         <v>1006</v>
@@ -15230,10 +15238,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15269,10 +15277,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15308,10 +15316,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15347,7 +15355,7 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="K38" s="115" t="s">
         <v>1013</v>
@@ -15388,7 +15396,7 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="K39" s="115" t="s">
         <v>1015</v>
@@ -15429,10 +15437,10 @@
         <v>5.8</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15459,117 +15467,117 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -15579,12 +15587,12 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -15594,22 +15602,22 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="79" spans="1:1">
@@ -15619,7 +15627,7 @@
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -15650,7 +15658,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -15660,7 +15668,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -15752,10 +15760,10 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="L11" s="114" t="s">
         <v>1040</v>
@@ -15768,7 +15776,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
@@ -15793,10 +15801,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15807,7 +15815,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
@@ -15832,10 +15840,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15873,10 +15881,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15912,10 +15920,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -15951,10 +15959,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -15990,10 +15998,10 @@
         <v>10.7</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -16006,7 +16014,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>359</v>
@@ -16031,10 +16039,10 @@
         <v>5.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -16045,7 +16053,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>283</v>
@@ -16070,10 +16078,10 @@
         <v>5.8</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -16109,7 +16117,7 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="K20" s="115" t="s">
         <v>1056</v>
@@ -16182,47 +16190,47 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="107" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="107" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -16232,17 +16240,17 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -16252,27 +16260,27 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="117" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="117" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -16282,7 +16290,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="C48" s="118" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
   </sheetData>
@@ -16683,12 +16691,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16702,12 +16710,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16733,7 +16741,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16756,12 +16764,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16784,12 +16792,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16812,12 +16820,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16840,15 +16848,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16868,12 +16876,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -16896,15 +16904,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -16924,15 +16932,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -16952,12 +16960,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -16980,12 +16988,12 @@
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B16" s="115" t="s">
         <v>1037</v>
@@ -17008,12 +17016,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -17036,12 +17044,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -17064,12 +17072,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -17092,12 +17100,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -17120,12 +17128,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -17148,12 +17156,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -17176,12 +17184,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -17204,12 +17212,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>302</v>
@@ -17232,15 +17240,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>368</v>
@@ -17260,12 +17268,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.25">
       <c r="A26" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>522</v>
@@ -17288,15 +17296,15 @@
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>383</v>
@@ -17316,12 +17324,12 @@
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B28" s="115" t="s">
         <v>1037</v>
@@ -17344,12 +17352,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>479</v>
@@ -17372,12 +17380,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>95</v>
@@ -17400,15 +17408,15 @@
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>421</v>
@@ -17428,12 +17436,12 @@
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B32" s="115" t="s">
         <v>1037</v>
@@ -17456,12 +17464,12 @@
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25.5">
       <c r="A33" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>95</v>
@@ -17484,12 +17492,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>280</v>
@@ -17512,15 +17520,15 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>432</v>
@@ -17540,15 +17548,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17568,12 +17576,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5">
       <c r="A37" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>479</v>
@@ -17596,12 +17604,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="38.25">
       <c r="A38" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>424</v>
@@ -17624,12 +17632,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>537</v>
@@ -17652,12 +17660,12 @@
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B40" s="115" t="s">
         <v>1007</v>
@@ -17680,12 +17688,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>486</v>
@@ -17708,12 +17716,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
       <c r="A42" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>93</v>
@@ -17736,12 +17744,12 @@
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B43" s="115" t="s">
         <v>1037</v>
@@ -17764,12 +17772,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>431</v>
@@ -17792,12 +17800,12 @@
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="51">
       <c r="A45" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>573</v>
@@ -17820,12 +17828,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B46" s="115" t="s">
         <v>498</v>
@@ -17848,12 +17856,12 @@
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>93</v>
@@ -17881,7 +17889,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>95</v>
@@ -17904,15 +17912,15 @@
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -17932,12 +17940,12 @@
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>388</v>
@@ -17965,7 +17973,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>573</v>
@@ -17988,12 +17996,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>570</v>
@@ -18016,12 +18024,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25">
       <c r="A53" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>95</v>
@@ -18044,15 +18052,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
@@ -18072,15 +18080,15 @@
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51">
       <c r="A55" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
@@ -18100,12 +18108,12 @@
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>93</v>
@@ -18128,12 +18136,12 @@
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>388</v>
@@ -18156,15 +18164,15 @@
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25.5">
       <c r="A58" s="114" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -18184,12 +18192,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B59" s="115" t="s">
         <v>495</v>
@@ -18217,7 +18225,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="114" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>605</v>
@@ -18245,10 +18253,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -18268,12 +18276,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="38.25">
       <c r="A62" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>97</v>
@@ -18296,12 +18304,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B63" s="115" t="s">
         <v>441</v>
@@ -18324,12 +18332,12 @@
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>531</v>
@@ -18352,12 +18360,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>600</v>
@@ -18380,12 +18388,12 @@
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>93</v>
@@ -18408,12 +18416,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>502</v>
@@ -18436,12 +18444,12 @@
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B68" s="115" t="s">
         <v>1118</v>
@@ -18464,7 +18472,7 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
   </sheetData>
@@ -18489,12 +18497,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18538,7 +18546,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -18569,7 +18577,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18593,10 +18601,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -18624,7 +18632,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18648,7 +18656,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18672,7 +18680,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18696,7 +18704,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18720,7 +18728,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18744,7 +18752,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18768,7 +18776,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18792,10 +18800,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18823,7 +18831,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18847,7 +18855,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18871,7 +18879,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18895,7 +18903,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18919,7 +18927,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18943,7 +18951,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18967,7 +18975,7 @@
         <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18991,7 +18999,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -19015,7 +19023,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -19039,7 +19047,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -19062,187 +19070,187 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="107" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0F1087E5D91BF74F36C6DA343B93137146A78851" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_62F4241DC3D12F35F0809F1FB7D3997C8A6204F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="1389">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -103,10 +103,10 @@
     <t>주당 환산 161세트</t>
   </si>
   <si>
-    <t>191세트</t>
-  </si>
-  <si>
-    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 다섯(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 페이스풀 · 전완 슈퍼세트 주 3회)</t>
+    <t>197세트</t>
+  </si>
+  <si>
+    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 여섯(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 페이스풀 · 전완 슈퍼세트 주 3회 · 백 익스텐션 주 2회)</t>
   </si>
   <si>
     <t>증량 방식</t>
@@ -2824,10 +2824,10 @@
     <t>등 수평 당기기 · 팔 삼두/이두</t>
   </si>
   <si>
-    <t>약 66분</t>
-  </si>
-  <si>
-    <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 등 16 · 팔 6 · 전완 6(슈퍼세트)이고 가슴이 없다</t>
+    <t>약 71분</t>
+  </si>
+  <si>
+    <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 등 16 · 팔 6 · 전완 6(슈퍼세트) · 백 익스텐션 3이고 가슴이 없다</t>
   </si>
   <si>
     <t>월</t>
@@ -2884,10 +2884,10 @@
     <t>등 수직 당기기 · 가슴(중하부) · 팔</t>
   </si>
   <si>
-    <t>약 82분</t>
-  </si>
-  <si>
-    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 맨 뒤에 전완 슈퍼세트 6</t>
+    <t>약 87분</t>
+  </si>
+  <si>
+    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 맨 뒤에 전완 슈퍼세트 6 + 백 익스텐션 3 (데드 다음날이므로 맨몸 유지가 규칙이다)</t>
   </si>
   <si>
     <t>금</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 446분 (7시간 26분)</t>
+    <t>약 456분 (7시간 36분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -2941,7 +2941,7 @@
     <t>[빈도를 올리고 볼륨은 조금만 올렸다 — 2026-10-02]</t>
   </si>
   <si>
-    <t>· 주 4회 140세트 → 주 6회 191세트. 세트는 36% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회, 전완은 주 1회 → 3회로 올랐다. 주 1회로 남은 것은 사두(토 12)뿐이다.</t>
+    <t>· 주 4회 140세트 → 주 6회 197세트. 세트는 41% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회, 전완은 주 1회 → 3회로 올랐다. 주 1회로 남은 것은 사두(토 12)뿐이다.</t>
   </si>
   <si>
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
@@ -2953,7 +2953,10 @@
     <t>· ⑤ 같은 날 등 분할 축을 근육군 → 움직임 평면으로 정정하고, 이어서 사용자 지정으로 평면을 요일에 배정했다 — 일요일 수평 · 목요일 수직. 세트 총량과 부위별 숫자는 안 바뀌고 날 배치만 바뀌었다.</t>
   </si>
   <si>
-    <t>· ⑥ 전완 리스트 컬을 길항근 슈퍼세트로 묶고(굴근 ↔ 신근) 팔 하는 날 셋 모두에 넣었다 — 사용자 지정 '그냥 다 넣어'. 일 6 · 화 6 · 목 6 + 리버스컬 3 = 전완 직접 21 · 실질 24.0. 179 → 191세트 · 446분.</t>
+    <t>· ⑥ 전완 리스트 컬을 길항근 슈퍼세트로 묶고(굴근 ↔ 신근) 팔 하는 날 셋 모두에 넣었다 — 사용자 지정 '그냥 다 넣어'. 일 6 · 화 6 · 목 6 + 리버스컬 3 = 전완 직접 21 · 실질 24.0.</t>
+  </si>
+  <si>
+    <t>· ⑦ 백 익스텐션(45도 · 맨몸) 3세트를 등 하는 날 둘에 넣었다 — 사용자 요청. 기립근 직접 3 → 9 · 실질 6.0 → 12.0으로 '보완 필요'가 '충분'이 됐다. 재택도 당기기 두 날에 3세트씩 맨몸으로 둔다. 191 → 197세트 · 456분.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -3004,7 +3007,7 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 수 39세트 98분 · 목 37세트 82분 · 토 38세트 95분 · 일 28세트 66분 · 화 27세트 46분 · 월 22세트 59분.</t>
+    <t>· 목 40세트 87분 · 수 39세트 98분 · 토 38세트 95분 · 일 31세트 71분 · 화 27세트 46분 · 월 22세트 59분.</t>
   </si>
   <si>
     <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
@@ -3013,10 +3016,10 @@
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 등 블록 둘이 28(일) / 37(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등').</t>
-  </si>
-  <si>
-    <t>· 주 446분 = 7시간 26분. 주 4회 370분에서 76분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 등 블록 둘이 31(일) / 40(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등').</t>
+  </si>
+  <si>
+    <t>· 주 456분 = 7시간 36분. 주 4회 370분에서 86분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3235,6 +3238,12 @@
     <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
   </si>
   <si>
+    <t>[2026-10-02 사용자 요청 — 등 하는 날마다 3세트] 복귀판 기립근 직접이 데드 3세트뿐이라 실질 6.0 '보완 필요'였다. 이 6세트(일 · 목)로 9 · 실질 12.0이 된다. 재택도 당기기 두 날에 3세트씩 맨몸으로 둔다. 고관절을 접어 상체를 내리고 중립 척추로 펴 올린다 — 과신전까지 가지 않는다. 이 날은 앞에 바벨 로우 4세트가 기립근을 등척성으로 썼으므로 맨 뒤가 맞다.</t>
+  </si>
+  <si>
+    <t>루마니안 데드 (중량을 걸고 싶을 때 — 단 수요일과 겹친다) / 케이블 풀스루 / 글루트 햄 레이즈</t>
+  </si>
+  <si>
     <t>[무거운 수평 당기기를 이 날에 둔 이유 — 2026-10-02 사용자 지정]</t>
   </si>
   <si>
@@ -3250,7 +3259,7 @@
     <t>· 그래서 무거운 로우 7세트(바벨 4 · 해머 3)가 데드 다음날에서 완전히 빠졌다. 목요일에 남은 당기기는 수직(친업 · 랫풀다운)이고 척추 부하가 거의 0이다.</t>
   </si>
   <si>
-    <t>· 가슴은 목요일에 남겼다(사용자 지정 '목요일 가슴/등'). 이 날은 수평 등 16 · 팔 6 · 전완 6이다.</t>
+    <t>· 가슴은 목요일에 남겼다(사용자 지정 '목요일 가슴/등'). 이 날은 수평 등 16 · 팔 6 · 전완 6 · 기립근 3이다.</t>
   </si>
   <si>
     <t>[등을 가른 축 — 움직임 평면이다]</t>
@@ -3265,7 +3274,7 @@
     <t>· 광배 일 3 / 목 11 · 승모 중부 일 10 / 목 3 — 둘 다 주 2회다. 근육군으로 날을 가르면 '주 1회'로 적히지만 실제로는 로우가 광배를 쓰고 랫풀다운이 능형근을 쓴다.</t>
   </si>
   <si>
-    <t>· 28세트 · 약 66분. 2026-10-02에 전완 슈퍼세트 6세트가 들어와 22 → 28이 됐다.</t>
+    <t>· 31세트 · 약 71분. 2026-10-02에 전완 슈퍼세트 6 + 백 익스텐션 3이 들어와 22 → 31이 됐다.</t>
   </si>
   <si>
     <t>· 앞쪽은 그대로다 — 무거운 로우 넷을 신선한 상태로 치는 구조는 손대지 않았고, 더한 것은 전부 맨 뒤 고립이다.</t>
@@ -3769,6 +3778,12 @@
     <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 11세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
   </si>
   <si>
+    <t>[2026-10-02 사용자 요청 — 등 하는 날마다 3세트] **맨몸 유지가 이 날의 규칙이다.** 수요일 데드 톱1 + 백오프2 + 루마니안 3 다음날이고, 이 날을 척추 부하 거의 0으로 비워 둔 것이 설계 의도다. 맨몸 12~15회는 데드와 비교할 부하가 아니라 오히려 혈류 · 가동 회복 쪽이지만, 원판을 안으면 그 자리가 '데드 다음날 기립근 중량 운동'으로 바뀐다. 중량을 걸고 싶으면 일요일 쪽에만 건다.</t>
+  </si>
+  <si>
+    <t>맨몸 유지 (중량 금지) / 버드독 · 데드버그 (허리가 무거운 주) / 건너뛴다</t>
+  </si>
+  <si>
     <t>[데드 다음날에 수직 당기기를 둔 이유 — 2026-10-02]</t>
   </si>
   <si>
@@ -3781,7 +3796,10 @@
     <t>· 그립만 남은 변수다. 친업이 그립을 쓰므로 데드 다음날에는 어시스트 머신을 기본값으로 생각한다 — 이 날 광배가 실패해야 하고 그립이 실패하면 세트를 잃는다.</t>
   </si>
   <si>
-    <t>· 주간 척추 부하 순서가 이렇게 된다 — 토 스쿼트(높음) → 일 바벨 로우(중간) → 월 · 화 0 → 수 데드 + 루마니안(최고) → 목 수직 당기기(거의 0) → 금 휴식.</t>
+    <t>· 주간 척추 부하 순서가 이렇게 된다 — 토 스쿼트(높음) → 일 바벨 로우 + 백 익스텐션 맨몸(중간) → 월 · 화 0 → 수 데드 + 루마니안(최고) → 목 수직 당기기 + 백 익스텐션 맨몸(낮음) → 금 휴식.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02] 백 익스텐션 3세트가 이 날에 들어왔다. 맨몸이면 이 순서가 깨지지 않지만 원판을 안으면 깨진다 — 중량 금지를 종목 메모와 대체 종목 칸에 같이 박아 뒀다.</t>
   </si>
   <si>
     <t>[이 날이 세 블록인 이유]</t>
@@ -3796,13 +3814,13 @@
     <t>· 팔이 맨 뒤인 이유 — 앞의 17세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
   </si>
   <si>
-    <t>· 37세트 · 약 82분. 2026-10-02에 전완 슈퍼세트 6세트가 들어와 31 → 37이 됐고, 여섯 날 중 둘째로 크다(수 39 다음).</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 19를 빼면 실질 18이다.</t>
-  </si>
-  <si>
-    <t>· 일요일(28세트 66분)과 합쳐 보면 등 블록 둘이 28/37로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
+    <t>· 40세트 · 약 87분. 2026-10-02에 전완 슈퍼세트 6 + 백 익스텐션 3이 들어와 31 → 40이 됐고, 여섯 날 중 가장 크다.</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 22를 빼면 실질 18이다.</t>
+  </si>
+  <si>
+    <t>· 일요일(31세트 71분)과 합쳐 보면 등 블록 둘이 31/40으로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
   </si>
   <si>
     <t>· 언더그립 랫풀다운 +60초 · 디클라인 케이블 플라이 +60초. 마지막 세트에만 2단.</t>
@@ -4045,7 +4063,7 @@
     <t>직접 13세트: 일요일(수평) 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 목요일(수직) 페이스풀 3. 10/3으로 나뉜다 — 페이스풀이 없으면 일요일 주 1회가 되므로 그 자리를 유지한다(재택도 페이스풀을 수직 날에 둔다). 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
   </si>
   <si>
-    <t>직접 3세트: 수요일 데드 톱 1 + 백오프 2 (2026-10-02 백오프 복귀). 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
+    <t>직접 9세트: 수요일 데드 톱 1 + 백오프 2 + 등 하는 날 둘에 백 익스텐션(45도 · 맨몸) 3씩 (2026-10-02 사용자 요청 — 재택도 당기기 두 날에 3세트씩 맨몸으로 둔다). 3 → 9으로 '보완 필요'가 '충분'이 됐다. 목요일 것은 **맨몸 유지가 규칙이다** — 수요일 데드 다음날이고 그 날을 척추 부하 거의 0으로 비워 둔 것이 설계 의도다. 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
   </si>
   <si>
     <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 5.9 — 벤치 0.33×5 + 인클라인 머신 0.5×4 + 딥스 0.2×3 + 인클라인 플라이 0.2×4 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
@@ -4169,6 +4187,9 @@
   </si>
   <si>
     <t>· 중둔근 11.0 · 내전근 12.5 — 2026-10-02에 수요일 이너/아우터 슈퍼세트가 들어와 둘 다 하한 아래(7.0 · 6.5)에서 성장 구간으로 올라왔다. 하체에서 '보완 필요'로 남은 곳은 이제 종아리 6.0뿐이다.</t>
+  </si>
+  <si>
+    <t>· 기립근 12.0 — 2026-10-02에 백 익스텐션 6세트가 들어와 6.0 '보완 필요'에서 올라왔다. 하체 · 등에서 '보완 필요'로 남은 곳은 종아리 6.0 · 승모 상부 4.5 · 승모 하부 6.0이다.</t>
   </si>
   <si>
     <t>· 전완 24.0 — **'과다 점검'이 뜨는 유일한 부위이고 그게 뜬 첫 사례다**(2026-10-02 사용자 지정). 표가 금지하지는 않는다. 다만 손목 · 팔꿈치가 시큰해지면 가장 먼저 의심할 자리이고, 되돌리는 순서는 일 · 목의 굴근(손등 아래) → 리버스컬이다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다.</t>
@@ -11143,7 +11164,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11231,8 +11252,8 @@
         <v>921</v>
       </c>
       <c r="E7" s="121">
-        <f>복귀_일_수평당기기!$E$20</f>
-        <v>28</v>
+        <f>복귀_일_수평당기기!$E$21</f>
+        <v>31</v>
       </c>
       <c r="F7" s="114" t="s">
         <v>922</v>
@@ -11327,8 +11348,8 @@
         <v>941</v>
       </c>
       <c r="E11" s="121">
-        <f>복귀_목_수직당기기!$E$22</f>
-        <v>37</v>
+        <f>복귀_목_수직당기기!$E$23</f>
+        <v>40</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>942</v>
@@ -11369,7 +11390,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F13" s="116" t="s">
         <v>946</v>
@@ -11491,13 +11512,13 @@
         <v>969</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="107" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="123" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="123" t="s">
+      <c r="A41" s="107" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11516,13 +11537,13 @@
         <v>974</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="107" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="123" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="123" t="s">
+      <c r="A47" s="107" t="s">
         <v>976</v>
       </c>
     </row>
@@ -11546,13 +11567,13 @@
         <v>980</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="107" t="s">
+    <row r="52" spans="1:1">
+      <c r="A52" s="123" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="123" t="s">
+      <c r="A54" s="107" t="s">
         <v>982</v>
       </c>
     </row>
@@ -11581,13 +11602,13 @@
         <v>987</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="107" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" s="123" t="s">
         <v>988</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="123" t="s">
+      <c r="A62" s="107" t="s">
         <v>989</v>
       </c>
     </row>
@@ -11604,6 +11625,11 @@
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
         <v>992</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="123" t="s">
+        <v>993</v>
       </c>
     </row>
   </sheetData>
@@ -11634,7 +11660,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11715,22 +11741,22 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11818,10 +11844,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="113" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="K20" s="113" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="L20" s="112" t="s">
         <v>356</v>
@@ -11859,10 +11885,10 @@
         <v>13</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -11898,10 +11924,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -11939,7 +11965,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K23" s="115" t="s">
         <v>597</v>
@@ -11978,10 +12004,10 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -11994,7 +12020,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>372</v>
@@ -12019,10 +12045,10 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -12060,10 +12086,10 @@
         <v>11.9</v>
       </c>
       <c r="J26" s="115" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K26" s="115" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="L26" s="114"/>
       <c r="M26" s="114"/>
@@ -12101,10 +12127,10 @@
         <v>3.3</v>
       </c>
       <c r="J27" s="115" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="K27" s="115" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="L27" s="114"/>
       <c r="M27" s="114" t="s">
@@ -12142,10 +12168,10 @@
         <v>10.7</v>
       </c>
       <c r="J28" s="115" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="K28" s="115" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
@@ -12183,10 +12209,10 @@
         <v>5.8</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -12213,82 +12239,82 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="107" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
   </sheetData>
@@ -12299,7 +12325,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12319,27 +12345,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12396,7 +12422,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>296</v>
@@ -12417,17 +12443,17 @@
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I19" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <f t="shared" ref="I11:I20" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.7</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -12462,13 +12488,13 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="L12" s="114" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="M12" s="114"/>
       <c r="N12" s="114"/>
@@ -12503,10 +12529,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -12542,10 +12568,10 @@
         <v>6.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -12583,10 +12609,10 @@
         <v>6.5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -12622,10 +12648,10 @@
         <v>6.8</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -12663,10 +12689,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12679,7 +12705,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>309</v>
@@ -12704,10 +12730,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114" t="s">
@@ -12745,10 +12771,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114" t="s">
@@ -12756,133 +12782,172 @@
       </c>
       <c r="N19" s="114"/>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="116"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116" t="s">
+    <row r="20" spans="1:14" ht="30" customHeight="1">
+      <c r="A20" s="114">
+        <v>10</v>
+      </c>
+      <c r="B20" s="115" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" s="114" t="s">
+        <v>327</v>
+      </c>
+      <c r="D20" s="114" t="s">
+        <v>297</v>
+      </c>
+      <c r="E20" s="114">
+        <v>3</v>
+      </c>
+      <c r="F20" s="114" t="s">
+        <v>303</v>
+      </c>
+      <c r="G20" s="114">
+        <v>40</v>
+      </c>
+      <c r="H20" s="114">
+        <v>60</v>
+      </c>
+      <c r="I20" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J20" s="115" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K20" s="115" t="s">
+        <v>1061</v>
+      </c>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="114"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="116"/>
+      <c r="B21" s="116"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E20" s="116">
-        <f>SUM(E11:E19)</f>
-        <v>28</v>
-      </c>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116">
-        <f>ROUND(SUM(I11:I19),0)</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="107" t="s">
-        <v>1059</v>
+      <c r="E21" s="116">
+        <f>SUM(E11:E20)</f>
+        <v>31</v>
+      </c>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116">
+        <f>ROUND(SUM(I11:I20),0)</f>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="117" t="s">
-        <v>1060</v>
+      <c r="A23" s="107" t="s">
+        <v>1062</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="107" t="s">
-        <v>1065</v>
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="117" t="s">
+        <v>1067</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="117" t="s">
-        <v>1066</v>
+      <c r="A30" s="107" t="s">
+        <v>1068</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="107" t="s">
-        <v>981</v>
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="117" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="117" t="s">
-        <v>1069</v>
+      <c r="A35" s="107" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="107" t="s">
-        <v>1028</v>
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="117" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="117" t="s">
-        <v>1072</v>
+      <c r="A40" s="107" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="117" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="117" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="C47" s="118" t="s">
-        <v>1077</v>
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="117" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="C48" s="118" t="s">
+        <v>1080</v>
       </c>
     </row>
   </sheetData>
@@ -12913,7 +12978,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -12999,7 +13064,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -13087,10 +13152,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="113" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="K18" s="113" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="L18" s="112" t="s">
         <v>356</v>
@@ -13128,10 +13193,10 @@
         <v>12.7</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13167,10 +13232,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13206,13 +13271,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="L21" s="114" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13222,13 +13287,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="E22" s="114">
         <v>3</v>
@@ -13247,10 +13312,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13267,7 +13332,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
@@ -13286,10 +13351,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13316,77 +13381,77 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="118" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
   </sheetData>
@@ -13417,22 +13482,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13519,10 +13584,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13560,10 +13625,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13599,10 +13664,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -13613,7 +13678,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>309</v>
@@ -13638,10 +13703,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114" t="s">
@@ -13679,10 +13744,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114" t="s">
@@ -13695,7 +13760,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>939</v>
@@ -13720,10 +13785,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -13734,7 +13799,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>939</v>
@@ -13759,10 +13824,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -13798,10 +13863,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -13837,10 +13902,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13867,127 +13932,127 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="107" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="107" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="117" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
   </sheetData>
@@ -14699,7 +14764,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14780,7 +14845,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14856,22 +14921,22 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -14959,10 +15024,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -14973,7 +15038,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -14999,10 +15064,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -15019,7 +15084,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -15038,10 +15103,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -15052,7 +15117,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -15077,10 +15142,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -15116,10 +15181,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -15130,7 +15195,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -15156,10 +15221,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -15197,10 +15262,10 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="K34" s="115" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="L34" s="114"/>
       <c r="M34" s="114"/>
@@ -15238,10 +15303,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15277,10 +15342,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15316,10 +15381,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15355,10 +15420,10 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="K38" s="115" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
@@ -15396,10 +15461,10 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
@@ -15437,10 +15502,10 @@
         <v>5.8</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15467,167 +15532,167 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="107" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="107" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="117" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
     </row>
   </sheetData>
@@ -15638,7 +15703,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -15658,27 +15723,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15756,17 +15821,17 @@
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I21" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <f t="shared" ref="I11:I22" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -15776,7 +15841,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
@@ -15801,10 +15866,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15815,7 +15880,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
@@ -15840,10 +15905,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15881,10 +15946,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15920,10 +15985,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -15959,10 +16024,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -15998,10 +16063,10 @@
         <v>10.7</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -16014,7 +16079,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>359</v>
@@ -16039,10 +16104,10 @@
         <v>5.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -16053,7 +16118,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>283</v>
@@ -16078,10 +16143,10 @@
         <v>5.8</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -16092,7 +16157,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>309</v>
@@ -16117,10 +16182,10 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114" t="s">
@@ -16158,10 +16223,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114" t="s">
@@ -16169,128 +16234,172 @@
       </c>
       <c r="N21" s="114"/>
     </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116" t="s">
+    <row r="22" spans="1:14" ht="30" customHeight="1">
+      <c r="A22" s="114">
+        <v>12</v>
+      </c>
+      <c r="B22" s="115" t="s">
+        <v>332</v>
+      </c>
+      <c r="C22" s="114" t="s">
+        <v>327</v>
+      </c>
+      <c r="D22" s="114" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="114">
+        <v>3</v>
+      </c>
+      <c r="F22" s="114" t="s">
+        <v>303</v>
+      </c>
+      <c r="G22" s="114">
+        <v>40</v>
+      </c>
+      <c r="H22" s="114">
+        <v>60</v>
+      </c>
+      <c r="I22" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J22" s="115" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K22" s="115" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L22" s="114"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="114"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="116"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E22" s="116">
-        <f>SUM(E11:E21)</f>
-        <v>37</v>
-      </c>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116">
-        <f>ROUND(SUM(I11:I21),0)</f>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="107" t="s">
-        <v>1237</v>
+      <c r="E23" s="116">
+        <f>SUM(E11:E22)</f>
+        <v>40</v>
+      </c>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116">
+        <f>ROUND(SUM(I11:I22),0)</f>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="117" t="s">
-        <v>1238</v>
+      <c r="A25" s="107" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1241</v>
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="117" t="s">
+        <v>1246</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="107" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="117" t="s">
-        <v>1243</v>
+      <c r="A30" s="117" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="117" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="A32" s="107" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="107" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="117" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="117" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="117" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="117" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="107" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="107" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="117" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="117" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="117" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="117" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="107" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="C48" s="118" t="s">
-        <v>1254</v>
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="117" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="117" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" s="118" t="s">
+        <v>1260</v>
       </c>
     </row>
   </sheetData>
@@ -16691,12 +16800,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16710,12 +16819,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16741,7 +16850,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16764,12 +16873,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16792,12 +16901,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16820,12 +16929,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16848,15 +16957,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16876,12 +16985,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -16904,15 +17013,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -16932,15 +17041,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -16960,12 +17069,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -16988,15 +17097,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>283</v>
@@ -17016,12 +17125,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -17044,12 +17153,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -17072,12 +17181,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -17100,12 +17209,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -17128,12 +17237,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -17156,12 +17265,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -17184,12 +17293,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -17212,12 +17321,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>302</v>
@@ -17240,15 +17349,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>368</v>
@@ -17268,12 +17377,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.25">
       <c r="A26" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>522</v>
@@ -17296,15 +17405,15 @@
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>383</v>
@@ -17324,15 +17433,15 @@
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>281</v>
@@ -17352,12 +17461,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>479</v>
@@ -17380,12 +17489,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>95</v>
@@ -17408,15 +17517,15 @@
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>421</v>
@@ -17436,15 +17545,15 @@
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C32" s="114" t="s">
         <v>421</v>
@@ -17464,12 +17573,12 @@
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25.5">
       <c r="A33" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>95</v>
@@ -17492,12 +17601,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>280</v>
@@ -17520,15 +17629,15 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>432</v>
@@ -17548,15 +17657,15 @@
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17576,12 +17685,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5">
       <c r="A37" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>479</v>
@@ -17604,12 +17713,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="38.25">
       <c r="A38" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>424</v>
@@ -17632,12 +17741,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>537</v>
@@ -17660,15 +17769,15 @@
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C40" s="114" t="s">
         <v>296</v>
@@ -17688,12 +17797,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>486</v>
@@ -17716,12 +17825,12 @@
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
       <c r="A42" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>93</v>
@@ -17744,15 +17853,15 @@
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C43" s="114" t="s">
         <v>327</v>
@@ -17772,12 +17881,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>431</v>
@@ -17800,12 +17909,12 @@
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="51">
       <c r="A45" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>573</v>
@@ -17828,12 +17937,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B46" s="115" t="s">
         <v>498</v>
@@ -17856,12 +17965,12 @@
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>93</v>
@@ -17889,7 +17998,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>95</v>
@@ -17912,15 +18021,15 @@
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -17940,12 +18049,12 @@
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>388</v>
@@ -17973,7 +18082,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>573</v>
@@ -17996,12 +18105,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>570</v>
@@ -18024,12 +18133,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25">
       <c r="A53" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>95</v>
@@ -18052,15 +18161,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
@@ -18080,15 +18189,15 @@
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51">
       <c r="A55" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
@@ -18108,12 +18217,12 @@
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>93</v>
@@ -18136,12 +18245,12 @@
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>388</v>
@@ -18164,15 +18273,15 @@
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25.5">
       <c r="A58" s="114" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -18192,12 +18301,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B59" s="115" t="s">
         <v>495</v>
@@ -18225,7 +18334,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="114" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>605</v>
@@ -18253,10 +18362,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -18276,12 +18385,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="38.25">
       <c r="A62" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>97</v>
@@ -18304,12 +18413,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B63" s="115" t="s">
         <v>441</v>
@@ -18332,12 +18441,12 @@
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>531</v>
@@ -18360,12 +18469,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>600</v>
@@ -18388,12 +18497,12 @@
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>93</v>
@@ -18416,12 +18525,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>502</v>
@@ -18444,15 +18553,15 @@
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="C68" s="114" t="s">
         <v>939</v>
@@ -18472,7 +18581,7 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -18483,7 +18592,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -18497,12 +18606,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18546,7 +18655,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
@@ -18577,7 +18686,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18601,10 +18710,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -18632,7 +18741,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18656,7 +18765,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18680,7 +18789,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18689,7 +18798,7 @@
       </c>
       <c r="B11" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A11)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A11)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A11)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A11)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A11)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A11)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C11" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A11),0.5)</f>
@@ -18697,14 +18806,14 @@
       </c>
       <c r="D11" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E11" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>보완 필요</v>
+        <v>충분</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18728,7 +18837,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18752,7 +18861,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18776,7 +18885,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18800,10 +18909,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18831,7 +18940,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18855,7 +18964,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18879,7 +18988,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18903,7 +19012,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -18927,7 +19036,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -18951,7 +19060,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -18975,7 +19084,7 @@
         <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -18999,7 +19108,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -19023,7 +19132,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -19047,7 +19156,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -19056,11 +19165,11 @@
       </c>
       <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -19070,187 +19179,192 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="107" t="s">
-        <v>1374</v>
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="123" t="s">
+        <v>1380</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="123" t="s">
-        <v>1375</v>
+      <c r="A63" s="107" t="s">
+        <v>1381</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>1381</v>
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="123" t="s">
+        <v>1388</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_62F4241DC3D12F35F0809F1FB7D3997C8A6204F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F0601BC17324615065040E13D1FE7B4CB44DAA76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2887,7 +2887,7 @@
     <t>약 87분</t>
   </si>
   <si>
-    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 맨 뒤에 전완 슈퍼세트 6 + 백 익스텐션 3 (데드 다음날이므로 맨몸 유지가 규칙이다)</t>
+    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 맨 뒤에 전완 슈퍼세트 6 + 백 익스텐션 3 (데드 다음날이라 일요일보다 중량이 낮게 나오는 것이 정상 — 금지는 아니다)</t>
   </si>
   <si>
     <t>금</t>
@@ -2956,7 +2956,7 @@
     <t>· ⑥ 전완 리스트 컬을 길항근 슈퍼세트로 묶고(굴근 ↔ 신근) 팔 하는 날 셋 모두에 넣었다 — 사용자 지정 '그냥 다 넣어'. 일 6 · 화 6 · 목 6 + 리버스컬 3 = 전완 직접 21 · 실질 24.0.</t>
   </si>
   <si>
-    <t>· ⑦ 백 익스텐션(45도 · 맨몸) 3세트를 등 하는 날 둘에 넣었다 — 사용자 요청. 기립근 직접 3 → 9 · 실질 6.0 → 12.0으로 '보완 필요'가 '충분'이 됐다. 재택도 당기기 두 날에 3세트씩 맨몸으로 둔다. 191 → 197세트 · 456분.</t>
+    <t>· ⑦ 백 익스텐션(45도) 3세트를 등 하는 날 둘에 넣었다 — 사용자 요청. 기립근 직접 3 → 9 · 실질 6.0 → 12.0으로 '보완 필요'가 '충분'이 됐다. 재택도 당기기 두 날에 3세트씩 둔다. 맨몸은 시작값이고 원판 5~10kg이 진행 경로다 — 두 날 다 중량 금지가 아니다. 척추 신전을 강조해서 해야 기립근이 주동근이 된다(힌지식이면 등척성이라 계수 0). 191 → 197세트 · 456분.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -3238,10 +3238,10 @@
     <t>바벨 리버스 리스트 컬 / 케이블 리스트 익스텐션</t>
   </si>
   <si>
-    <t>[2026-10-02 사용자 요청 — 등 하는 날마다 3세트] 복귀판 기립근 직접이 데드 3세트뿐이라 실질 6.0 '보완 필요'였다. 이 6세트(일 · 목)로 9 · 실질 12.0이 된다. 재택도 당기기 두 날에 3세트씩 맨몸으로 둔다. 고관절을 접어 상체를 내리고 중립 척추로 펴 올린다 — 과신전까지 가지 않는다. 이 날은 앞에 바벨 로우 4세트가 기립근을 등척성으로 썼으므로 맨 뒤가 맞다.</t>
-  </si>
-  <si>
-    <t>루마니안 데드 (중량을 걸고 싶을 때 — 단 수요일과 겹친다) / 케이블 풀스루 / 글루트 햄 레이즈</t>
+    <t>[2026-10-02 사용자 요청 — 등 하는 날마다 3세트] 복귀판 기립근 직접이 데드 3세트뿐이라 실질 6.0 '보완 필요'였다. 이 6세트(일 · 목)로 9 · 실질 12.0이 된다. 재택도 당기기 두 날에 3세트씩 둔다. **척추 신전을 강조해서 한다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근 · 햄스트링이 주동근이 되고 기립근은 버티기만 한다. 그러면 09-04 규칙상 등척성이라 계수 0이고, 검산표의 기립근 직접 9가 거짓이 된다. 재택 메모의 핵심 문장이 이것이다. 중량은 더블 프로그레션 — 맨몸 15회를 전 세트에서 채우면 원판 5~10kg을 안는다. '맨몸'은 시작값이지 상한이 아니다(재택 대체 종목 칸에도 '원판 5~10kg 안고 (맨몸이 쉬워지면)'으로 적혀 있다). 이 날이 중량을 올리기에 좋은 쪽이다 — 다음 데드(수)까지 사흘이 남는다. 앞에 바벨 로우 4세트가 기립근을 등척성으로 썼으므로 세션 맨 뒤가 맞다.</t>
+  </si>
+  <si>
+    <t>원판 5~10kg 안고 (맨몸 15회가 쉬워지면) / 굿모닝(스미스) / 덤벨 루마니안 데드 / 글루트 햄 레이즈</t>
   </si>
   <si>
     <t>[무거운 수평 당기기를 이 날에 둔 이유 — 2026-10-02 사용자 지정]</t>
@@ -3778,10 +3778,10 @@
     <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 11세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
   </si>
   <si>
-    <t>[2026-10-02 사용자 요청 — 등 하는 날마다 3세트] **맨몸 유지가 이 날의 규칙이다.** 수요일 데드 톱1 + 백오프2 + 루마니안 3 다음날이고, 이 날을 척추 부하 거의 0으로 비워 둔 것이 설계 의도다. 맨몸 12~15회는 데드와 비교할 부하가 아니라 오히려 혈류 · 가동 회복 쪽이지만, 원판을 안으면 그 자리가 '데드 다음날 기립근 중량 운동'으로 바뀐다. 중량을 걸고 싶으면 일요일 쪽에만 건다.</t>
-  </si>
-  <si>
-    <t>맨몸 유지 (중량 금지) / 버드독 · 데드버그 (허리가 무거운 주) / 건너뛴다</t>
+    <t>[2026-10-02 사용자 요청 — 등 하는 날마다 3세트] **척추 신전을 강조해서 한다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근 · 햄스트링이 주동근이 되고 기립근은 버티기만 한다. 그러면 09-04 규칙상 등척성이라 계수 0이고, 검산표의 기립근 직접 9가 거짓이 된다. 재택 메모의 핵심 문장이 이것이다. 중량은 더블 프로그레션 — 맨몸 15회를 전 세트에서 채우면 원판 5~10kg을 안는다. '맨몸'은 시작값이지 상한이 아니다(재택 대체 종목 칸에도 '원판 5~10kg 안고 (맨몸이 쉬워지면)'으로 적혀 있다). 원판을 안아도 된다 — 금지가 아니다. 다만 수요일 데드 톱1 + 백오프2 + 루마니안 3 다음날이라 일요일과 같은 중량이 안 나온다. 낮게 나오는 것이 정상이고 더블 프로그레션은 날마다 따로 본다. 되돌리는 트리거는 하나다 — 수요일 데드나 토요일 스쿼트가 2주 연속 안 오르면 이 날 중량을 가장 먼저 의심한다(다음 스쿼트까지 금요일 휴식 하나뿐이다).</t>
+  </si>
+  <si>
+    <t>원판 5~10kg 안고 (맨몸 15회가 쉬워지면) / 굿모닝(스미스) / 맨몸 유지 (허리가 무거운 주) / 건너뛴다</t>
   </si>
   <si>
     <t>[데드 다음날에 수직 당기기를 둔 이유 — 2026-10-02]</t>
@@ -3796,10 +3796,10 @@
     <t>· 그립만 남은 변수다. 친업이 그립을 쓰므로 데드 다음날에는 어시스트 머신을 기본값으로 생각한다 — 이 날 광배가 실패해야 하고 그립이 실패하면 세트를 잃는다.</t>
   </si>
   <si>
-    <t>· 주간 척추 부하 순서가 이렇게 된다 — 토 스쿼트(높음) → 일 바벨 로우 + 백 익스텐션 맨몸(중간) → 월 · 화 0 → 수 데드 + 루마니안(최고) → 목 수직 당기기 + 백 익스텐션 맨몸(낮음) → 금 휴식.</t>
-  </si>
-  <si>
-    <t>· [2026-10-02] 백 익스텐션 3세트가 이 날에 들어왔다. 맨몸이면 이 순서가 깨지지 않지만 원판을 안으면 깨진다 — 중량 금지를 종목 메모와 대체 종목 칸에 같이 박아 뒀다.</t>
+    <t>· 주간 척추 부하 순서가 이렇게 된다 — 토 스쿼트(높음) → 일 바벨 로우 + 백 익스텐션(중간) → 월 · 화 0 → 수 데드 + 루마니안(최고) → 목 수직 당기기 + 백 익스텐션(낮음) → 금 휴식.</t>
+  </si>
+  <si>
+    <t>· [2026-10-02] 백 익스텐션 3세트가 이 날에 들어왔다. 원판을 안아도 되고 금지가 아니다 — 다만 데드 다음날이라 일요일보다 중량이 낮게 나오는 것이 정상이다. 되돌리는 트리거는 수요일 데드나 토요일 스쿼트가 2주 연속 안 오르는 것이다.</t>
   </si>
   <si>
     <t>[이 날이 세 블록인 이유]</t>
@@ -4063,7 +4063,7 @@
     <t>직접 13세트: 일요일(수평) 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 목요일(수직) 페이스풀 3. 10/3으로 나뉜다 — 페이스풀이 없으면 일요일 주 1회가 되므로 그 자리를 유지한다(재택도 페이스풀을 수직 날에 둔다). 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
   </si>
   <si>
-    <t>직접 9세트: 수요일 데드 톱 1 + 백오프 2 + 등 하는 날 둘에 백 익스텐션(45도 · 맨몸) 3씩 (2026-10-02 사용자 요청 — 재택도 당기기 두 날에 3세트씩 맨몸으로 둔다). 3 → 9으로 '보완 필요'가 '충분'이 됐다. 목요일 것은 **맨몸 유지가 규칙이다** — 수요일 데드 다음날이고 그 날을 척추 부하 거의 0으로 비워 둔 것이 설계 의도다. 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
+    <t>직접 9세트: 수요일 데드 톱 1 + 백오프 2 + 등 하는 날 둘에 백 익스텐션(45도 · 맨몸) 3씩 (2026-10-02 사용자 요청 — 재택도 당기기 두 날에 3세트씩 둔다). 3 → 9으로 '보완 필요'가 '충분'이 됐다. **척추 신전을 강조해서 해야 이 9세트가 유효하다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근 · 햄스트링이 주동근이 되고 기립근은 버티기만 한다. 그러면 09-04 규칙상 등척성이라 계수 0이고 이 숫자가 거짓이 된다. 중량은 더블 프로그레션 — 맨몸 15회를 채우면 원판 5~10kg을 안는다('맨몸'은 시작값이지 상한이 아니다). 목요일 것도 원판 금지가 아니고, 데드 다음날이라 일요일보다 낮게 나오는 것이 정상이다 — 수요일 데드나 토요일 스쿼트가 2주 연속 안 오르면 그 날 중량을 먼저 의심한다. 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
   </si>
   <si>
     <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 5.9 — 벤치 0.33×5 + 인클라인 머신 0.5×4 + 딥스 0.2×3 + 인클라인 플라이 0.2×4 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F0601BC17324615065040E13D1FE7B4CB44DAA76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_976DDB3BF43AA339F7E760932C78BE6F3F568295" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="1389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2672" uniqueCount="1391">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -103,7 +103,7 @@
     <t>주당 환산 161세트</t>
   </si>
   <si>
-    <t>197세트</t>
+    <t>203세트</t>
   </si>
   <si>
     <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 여섯(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 페이스풀 · 전완 슈퍼세트 주 3회 · 백 익스텐션 주 2회)</t>
@@ -2809,7 +2809,7 @@
     <t>하체 전면(사두) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 95분</t>
+    <t>약 101분</t>
   </si>
   <si>
     <t>스쿼트 5×5가 앞, 어깨 블록이 4~6번(프레스 · 레터럴 · 리버스 펙덱). 금요일 휴식 다음날이라 주 전체에서 가장 신선하다. 레그 컬 · 이너 · 아우터 · 카프는 어깨와 경쟁하지 않아 뒤로 보냈다 — 햄스트링 중량은 이 날이 가장 잘 나온다</t>
@@ -2824,10 +2824,10 @@
     <t>등 수평 당기기 · 팔 삼두/이두</t>
   </si>
   <si>
-    <t>약 71분</t>
-  </si>
-  <si>
-    <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 등 16 · 팔 6 · 전완 6(슈퍼세트) · 백 익스텐션 3이고 가슴이 없다</t>
+    <t>약 74분</t>
+  </si>
+  <si>
+    <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 등 17 · 팔 6 · 전완 6(슈퍼세트) · 백 익스텐션 3이고 가슴이 없다</t>
   </si>
   <si>
     <t>월</t>
@@ -2839,10 +2839,10 @@
     <t>가슴(상부 중심) · 어깨 측/후</t>
   </si>
   <si>
-    <t>약 59분</t>
-  </si>
-  <si>
-    <t>벤치 5×5가 앞. 전면 삼각은 밀기 간접으로 6세트치가 차므로 어깨 블록에 프레스를 얹지 않는다</t>
+    <t>약 53분</t>
+  </si>
+  <si>
+    <t>벤치 5×5가 앞. 전면 삼각은 밀기 간접으로 5세트치가 차므로 어깨 블록에 프레스를 얹지 않는다</t>
   </si>
   <si>
     <t>화</t>
@@ -2869,7 +2869,7 @@
     <t>하체 후면(햄 · 둔) · 어깨 전/측/후</t>
   </si>
   <si>
-    <t>약 98분</t>
+    <t>약 104분</t>
   </si>
   <si>
     <t>데드 톱1 + 백오프2 · 레그 프레스는 발을 발판 위쪽에(둔근) · 원 레그 컬로 좌우 균형 · 이너 · 아우터 슈퍼세트. 스미스 오버헤드 프레스가 어깨 블록 첫 종목 — 앞의 13세트가 전부 하체다</t>
@@ -2884,7 +2884,7 @@
     <t>등 수직 당기기 · 가슴(중하부) · 팔</t>
   </si>
   <si>
-    <t>약 87분</t>
+    <t>약 90분</t>
   </si>
   <si>
     <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 맨 뒤에 전완 슈퍼세트 6 + 백 익스텐션 3 (데드 다음날이라 일요일보다 중량이 낮게 나오는 것이 정상 — 금지는 아니다)</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 456분 (7시간 36분)</t>
+    <t>약 468분 (7시간 48분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -2941,7 +2941,7 @@
     <t>[빈도를 올리고 볼륨은 조금만 올렸다 — 2026-10-02]</t>
   </si>
   <si>
-    <t>· 주 4회 140세트 → 주 6회 197세트. 세트는 41% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회, 전완은 주 1회 → 3회로 올랐다. 주 1회로 남은 것은 사두(토 12)뿐이다.</t>
+    <t>· 주 4회 140세트 → 주 6회 203세트. 세트는 45% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회, 전완은 주 1회 → 3회로 올랐다. 주 1회로 남은 것은 사두(토 12)뿐이다.</t>
   </si>
   <si>
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
@@ -2956,7 +2956,10 @@
     <t>· ⑥ 전완 리스트 컬을 길항근 슈퍼세트로 묶고(굴근 ↔ 신근) 팔 하는 날 셋 모두에 넣었다 — 사용자 지정 '그냥 다 넣어'. 일 6 · 화 6 · 목 6 + 리버스컬 3 = 전완 직접 21 · 실질 24.0.</t>
   </si>
   <si>
-    <t>· ⑦ 백 익스텐션(45도) 3세트를 등 하는 날 둘에 넣었다 — 사용자 요청. 기립근 직접 3 → 9 · 실질 6.0 → 12.0으로 '보완 필요'가 '충분'이 됐다. 재택도 당기기 두 날에 3세트씩 둔다. 맨몸은 시작값이고 원판 5~10kg이 진행 경로다 — 두 날 다 중량 금지가 아니다. 척추 신전을 강조해서 해야 기립근이 주동근이 된다(힌지식이면 등척성이라 계수 0). 191 → 197세트 · 456분.</t>
+    <t>· ⑦ 백 익스텐션(45도) 3세트를 등 하는 날 둘에 넣었다 — 사용자 요청. 기립근 직접 3 → 9 · 실질 6.0 → 12.0으로 '보완 필요'가 '충분'이 됐다. 재택도 당기기 두 날에 3세트씩 둔다. 맨몸은 시작값이고 원판 5~10kg이 진행 경로다 — 두 날 다 중량 금지가 아니다. 척추 신전을 강조해서 해야 기립근이 주동근이 된다(힌지식이면 등척성이라 계수 0). 191 → 197세트.</t>
+  </si>
+  <si>
+    <t>· ⑧ 같은 날 사용자가 엑셀에서 여섯 칸을 직접 조정했다 — 카프 토 · 수 각 3 → 6(종아리 6 → 12로 '보완 필요' 해결) · 원암 케이블 로우 3 → 4 · 언더그립 랫풀다운 3 → 4(광배 14 → 16 · 실질 19.5) · 인클라인 머신 · 인클라인 덤벨 플라이 각 4 → 3(흉근 상부 8 → 6 · 흉근 합산 25.0 → 22.5). 197 → 203세트 · 468분. 세트검산에 '등 중요부위' 보조 칸도 직접 만들었다 — 당기기 본 종목만 센다.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -3007,19 +3010,19 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 목 40세트 87분 · 수 39세트 98분 · 토 38세트 95분 · 일 31세트 71분 · 화 27세트 46분 · 월 22세트 59분.</t>
-  </si>
-  <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 26을 빼면 실질 12, 수요일은 26을 빼면 13, 월요일은 6을 빼면 16이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
+    <t>· 수 42세트 104분 · 토 41세트 101분 · 목 41세트 90분 · 일 32세트 74분 · 화 27세트 46분 · 월 20세트 53분.</t>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 29를 빼면 실질 12, 수요일은 26을 빼면 16, 월요일은 9를 빼면 11이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
   </si>
   <si>
     <t>· 일 · 화 · 목은 메인 리프트가 없어 상한의 적용 대상이 아니다. 셋 다 휴식이 짧아 세트 수에 비해 시간이 안 든다.</t>
   </si>
   <si>
-    <t>· 등 블록 둘이 31(일) / 40(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등').</t>
-  </si>
-  <si>
-    <t>· 주 456분 = 7시간 36분. 주 4회 370분에서 86분 늘었다. 수(98) · 토(95)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 등 블록 둘이 32(일) / 41(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등').</t>
+  </si>
+  <si>
+    <t>· 주 468분 = 7시간 48분. 주 4회 370분에서 98분 늘었다. 수(104) · 토(101)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3136,10 +3139,10 @@
     <t>· [2026-10-02 같은 날 교환] 처음엔 원 레그 컬 3을 뒀는데 사용자 제안으로 수요일 양측 레그 컬과 바꿨다. 토요일엔 햄스트링을 직접 쓰는 종목이 없어 국소로 신선하므로 중량 종목(양측)이 맞고, 편측은 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 둘 다 반대로 놓여 있었다.</t>
   </si>
   <si>
-    <t>· 38세트 · 약 95분. 세션 상한 26세트를 넘지만 고립 소근육(익스텐션 · 레터럴 · 리버스 펙덱 · 레그 컬 · 이너 · 아우터 · 카프 26세트)은 예외로 본다 — 실질 12세트다.</t>
-  </si>
-  <si>
-    <t>· 여섯 날 중 둘째로 크다. 그래도 주 4회 시절 토요일(43세트 · 107분)보다는 작다.</t>
+    <t>· 41세트 · 약 101분. 세션 상한 26세트를 넘지만 고립 소근육 29세트(익스텐션 3 · 레터럴 4 · 리버스 펙덱 4 · 레그 컬 4 · 이너 4 · 아우터 4 · 카프 6)는 예외로 본다 — 실질 12세트다. 카프가 3 → 6으로 올라 38 → 41이 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정).</t>
+  </si>
+  <si>
+    <t>· 세트로는 수요일(42)에 이어 둘째다. 그래도 주 4회 시절 토요일(43세트 · 107분)보다는 작다.</t>
   </si>
   <si>
     <t>· 웜업은 별도다. 스쿼트가 있는 날이므로 10~15분을 더 잡는다.</t>
@@ -3193,7 +3196,7 @@
     <t>135/150/165</t>
   </si>
   <si>
-    <t>팔꿈치를 몸에 붙여 당기는 경로라 주동근이 광배다 — 평면으로 날을 가르고 근육군은 팔꿈치 경로로 매긴다(2026-09-04 원칙). 좌우 독립이라 약한 쪽이 드러난다. 이 날 유일한 광배 직접이고 나머지 11세트는 목요일(수직)에 있다.</t>
+    <t>팔꿈치를 몸에 붙여 당기는 경로라 주동근이 광배다 — 평면으로 날을 가르고 근육군은 팔꿈치 경로로 매긴다(2026-09-04 원칙). 좌우 독립이라 약한 쪽이 드러난다. 이 날 유일한 광배 직접이고 나머지 12세트는 목요일(수직)에 있다.</t>
   </si>
   <si>
     <t>원암 해머 스트랭스 로우 / 원암 덤벨 로우 (벤치 지지) / 머신 로우</t>
@@ -3217,7 +3220,7 @@
     <t>케이블 오버헤드 익스텐션 (로프 · 장두 신전 구간) / V바 푸쉬다운</t>
   </si>
   <si>
-    <t>당기기 16세트 뒤라 이두가 이미 간접을 받았다. 중량이 평소보다 낮게 나오는 것이 정상이다.</t>
+    <t>당기기 17세트 뒤라 이두가 이미 간접을 받았다. 중량이 평소보다 낮게 나오는 것이 정상이다.</t>
   </si>
   <si>
     <t>케이블 컬 (전 구간 장력) / 머신 컬 / EZ바 프리쳐 컬</t>
@@ -3226,7 +3229,7 @@
     <t>시티드 리스트 컬(손등 아래)</t>
   </si>
   <si>
-    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 16세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
+    <t>[2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 17세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
   </si>
   <si>
     <t>바벨 리스트 컬 / 케이블 리스트 컬</t>
@@ -3259,7 +3262,7 @@
     <t>· 그래서 무거운 로우 7세트(바벨 4 · 해머 3)가 데드 다음날에서 완전히 빠졌다. 목요일에 남은 당기기는 수직(친업 · 랫풀다운)이고 척추 부하가 거의 0이다.</t>
   </si>
   <si>
-    <t>· 가슴은 목요일에 남겼다(사용자 지정 '목요일 가슴/등'). 이 날은 수평 등 16 · 팔 6 · 전완 6 · 기립근 3이다.</t>
+    <t>· 가슴은 목요일에 남겼다(사용자 지정 '목요일 가슴/등'). 이 날은 수평 등 17 · 팔 6 · 전완 6 · 기립근 3이다.</t>
   </si>
   <si>
     <t>[등을 가른 축 — 움직임 평면이다]</t>
@@ -3271,10 +3274,10 @@
     <t>· 날 분할은 평면으로, 근육군은 팔꿈치 경로로 매긴다 — 다른 축이고 섞지 않는다. 그래서 수평 날에 광배(원암 케이블 로우)가 있고 수직 날에 승모 중부(페이스풀)가 있다.</t>
   </si>
   <si>
-    <t>· 광배 일 3 / 목 11 · 승모 중부 일 10 / 목 3 — 둘 다 주 2회다. 근육군으로 날을 가르면 '주 1회'로 적히지만 실제로는 로우가 광배를 쓰고 랫풀다운이 능형근을 쓴다.</t>
-  </si>
-  <si>
-    <t>· 31세트 · 약 71분. 2026-10-02에 전완 슈퍼세트 6 + 백 익스텐션 3이 들어와 22 → 31이 됐다.</t>
+    <t>· 광배 일 4 / 목 12 · 승모 중부 일 10 / 목 3 — 둘 다 주 2회다. 근육군으로 날을 가르면 '주 1회'로 적히지만 실제로는 로우가 광배를 쓰고 랫풀다운이 능형근을 쓴다.</t>
+  </si>
+  <si>
+    <t>· 32세트 · 약 74분. 전완 슈퍼세트 6 + 백 익스텐션 3이 들어오고 원암 케이블 로우가 3 → 4로 올라 22 → 32가 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정). 복합 11 / 고립 21이다.</t>
   </si>
   <si>
     <t>· 앞쪽은 그대로다 — 무거운 로우 넷을 신선한 상태로 치는 구조는 손대지 않았고, 더한 것은 전부 맨 뒤 고립이다.</t>
@@ -3316,7 +3319,7 @@
     <t>인클라인 스미스 프레스 / 인클라인 덤벨 프레스</t>
   </si>
   <si>
-    <t>상부지를 프레스와 플라이 둘로 나눠 각 4세트. 각도는 30~45도.</t>
+    <t>상부지를 프레스와 플라이 둘로 나눠 각 3세트 (2026-10-02 사용자가 엑셀에서 직접 조정) — 흉근 합산을 25.0 → 22.5로 내리려고 둘에서 하나씩 뺐다. 각도는 30~45도.</t>
   </si>
   <si>
     <t>펙덱 플라이 머신 (인클라인 각도) / 인클라인 케이블 플라이</t>
@@ -3352,7 +3355,7 @@
     <t>[어깨 전면이 이 날에 없는 이유]</t>
   </si>
   <si>
-    <t>· 벤치 5 + 인클라인 머신 4 + 딥스 3 + 인클라인 플라이 4가 전면 삼각에 간접으로 6.5세트치를 얹는다. 그 위에 프레스를 더 얹으면 전면만 혼자 과다가 된다.</t>
+    <t>· 벤치 5 + 인클라인 머신 3 + 딥스 3 + 인클라인 플라이 3이 전면 삼각에 간접으로 5.0세트치를 얹는다. 그 위에 프레스를 더 얹으면 전면만 혼자 과다가 된다.</t>
   </si>
   <si>
     <t>· 그래서 월요일 어깨 블록은 측면 · 후면 둘뿐이다. 전면 직접은 토요일 머신 숄더 3 · 수요일 스미스 오버헤드 3으로 주 6세트다.</t>
@@ -3364,13 +3367,13 @@
     <t>[가슴을 둘로 가른 축]</t>
   </si>
   <si>
-    <t>· 월요일은 상부(인클라인 프레스 4 + 인클라인 플라이 4), 목요일은 중하부(펙덱 4 + 디클라인 플라이 4)다. 벤치와 딥스는 수평 · 하방이라 월요일에 함께 둔다.</t>
+    <t>· 월요일은 상부(인클라인 프레스 3 + 인클라인 플라이 3), 목요일은 중하부(펙덱 4 + 디클라인 플라이 4)다. 벤치와 딥스는 수평 · 하방이라 월요일에 함께 둔다. 상부 둘을 4 → 3으로 내려 흉근 합산이 22.5가 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정).</t>
   </si>
   <si>
     <t>· 흉근 합산 실질 27.5세트로 천장(20)을 크게 넘는다. 2026-09-14 사용자 지정 — 가슴은 되돌리는 자리가 아니다. 판단 기준은 세트 수가 아니라 벤치 진행이다. 벤치가 2주 연속 안 오르면 그때 이 숫자를 본다.</t>
   </si>
   <si>
-    <t>· 22세트 · 약 59분. 여섯 날 중 가장 작다 — 월요일은 가슴 하나만 맡고 어깨가 6세트뿐이다.</t>
+    <t>· 20세트 · 약 53분. 여섯 날 중 가장 작다 — 가슴 하나만 맡고 어깨가 6세트뿐이며, 상부 둘이 3세트씩으로 내려왔다 (2026-10-02 사용자가 엑셀에서 직접 조정).</t>
   </si>
   <si>
     <t>· 벤치가 있는 날이므로 웜업 10~15분을 따로 잡는다.</t>
@@ -3619,7 +3622,7 @@
     <t>· 어깨를 전부 세션 후반부로 내리면(2026-10-02 사용자 지정) 매주 미는 세 리프트 중 오버헤드 프레스만 큰 부위 뒤로 밀린다. 어느 날 뒤에 두는 것이 가장 싼지가 문제였다.</t>
   </si>
   <si>
-    <t>· 월요일(가슴) 뒤 — 가장 비싸다. 벤치 5 + 인클라인 4 + 딥스 3이 전면 삼각과 삼두에 간접 6.5세트치를 얹은 상태로 메인을 치게 된다.</t>
+    <t>· 월요일(가슴) 뒤 — 가장 비싸다. 벤치 5 + 인클라인 3 + 딥스 3이 전면 삼각과 삼두에 간접 5세트치를 얹은 상태로 메인을 치게 된다.</t>
   </si>
   <si>
     <t>· 토요일(하체 전면) 뒤 — 중간이다. 전면 삼각 · 삼두는 온전하나 스쿼트 5×5의 전신 피로가 가장 크다.</t>
@@ -3682,10 +3685,10 @@
     <t>· 디로드 주에는 데드를 건너뛴다. 중량은 손대지 않는다.</t>
   </si>
   <si>
-    <t>· 39세트 · 약 98분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이다.</t>
-  </si>
-  <si>
-    <t>· 고립 26세트를 빼면 실질 13세트다 — 어깨 블록 뒤 17세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 35분이 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
+    <t>· 42세트 · 약 104분. 여섯 날 중 가장 크다 — 메인이 둘(데드 · 오버헤드 프레스) 있는 유일한 날이고 카프가 3 → 6으로 올랐다 (2026-10-02 사용자가 엑셀에서 직접 조정).</t>
+  </si>
+  <si>
+    <t>· 고립 26세트를 빼면 실질 16세트다 — 어깨 블록 뒤 20세트(힙 쓰러스트 · 힙 외전 · 이너 · 아우터 · 카프)는 휴식이 짧아 41분이 든다. 메인 둘이 있으므로 웜업은 램프 두 블록을 따로 잡는다.</t>
   </si>
   <si>
     <t>· 레터럴 +60초 하나뿐이다. 마지막 세트에만 2단 — 레그 컬 드롭은 2026-10-02에 양측 레그 컬과 함께 토요일로 갔다.</t>
@@ -3745,7 +3748,7 @@
     <t>리어 델트 로우 (로프) / 케이블 리버스 플라이 (팔 편 채) / 리버스 펙덱</t>
   </si>
   <si>
-    <t>수평 내전으로 중간 구간을 맡는다. 등 17세트 뒤라 가슴이 온전하다 — 당기기와 밀기는 경쟁하지 않는다.</t>
+    <t>수평 내전으로 중간 구간을 맡는다. 등 18세트 뒤라 가슴이 온전하다 — 당기기와 밀기는 경쟁하지 않는다.</t>
   </si>
   <si>
     <t>케이블 크로스오버 (중간 높이) / 덤벨 플라이 / 머신 체스트 프레스</t>
@@ -3808,19 +3811,19 @@
     <t>· 사용자 지정 — '목요일 가슴/등'. 거기에 팔 후반부가 붙어 등 → 가슴 → 팔 세 블록이 됐다.</t>
   </si>
   <si>
-    <t>· 등(수직 17) → 가슴(중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
-  </si>
-  <si>
-    <t>· 팔이 맨 뒤인 이유 — 앞의 17세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
-  </si>
-  <si>
-    <t>· 40세트 · 약 87분. 2026-10-02에 전완 슈퍼세트 6 + 백 익스텐션 3이 들어와 31 → 40이 됐고, 여섯 날 중 가장 크다.</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 22를 빼면 실질 18이다.</t>
-  </si>
-  <si>
-    <t>· 일요일(31세트 71분)과 합쳐 보면 등 블록 둘이 31/40으로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
+    <t>· 등(수직 18) → 가슴(중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
+  </si>
+  <si>
+    <t>· 팔이 맨 뒤인 이유 — 앞의 18세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
+  </si>
+  <si>
+    <t>· 41세트 · 약 90분. 전완 슈퍼세트 6 + 백 익스텐션 3이 들어오고 언더그립 랫풀다운이 3 → 4로 올라 31 → 41이 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정).</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 29를 빼면 실질 12다.</t>
+  </si>
+  <si>
+    <t>· 일요일(32세트 74분)과 합쳐 보면 등 블록 둘이 32/41로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
   </si>
   <si>
     <t>· 언더그립 랫풀다운 +60초 · 디클라인 케이블 플라이 +60초. 마지막 세트에만 2단.</t>
@@ -4042,13 +4045,13 @@
     <t>세트는 근육군 단위로 센다. 복귀판은 주 6회 · 주 단위이므로 이 표의 숫자가 곧 주간 세트다 — 재택판처럼 주당 환산을 할 필요가 없다.</t>
   </si>
   <si>
-    <t>직접 8세트: 월요일 인클라인 벤치프레스 머신 4 · 인클라인 덤벨 플라이 4. 간접 0 — 흉근 상/하는 I열에서 합산 판정하므로 서로에게 간접을 얹지 않는다(2026-10-02 교차 계상 제거). 상부지를 복합 하나 · 고립 하나로 나눠 각 4세트다. 단독 판정이 '하한'으로 뜨지만 흉근은 I열 합산(25.0)으로 판정한다</t>
-  </si>
-  <si>
-    <t>직접 16세트: 월요일 벤치 5 · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 4. 간접 0.8 — 인클라인 덤벨 플라이 0.2×4 (인클라인 머신의 교차 간접은 2026-10-02에 0으로). 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
-  </si>
-  <si>
-    <t>직접 14세트: 목요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 3 + 일요일(수평) 원암 케이블 로우 3. 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3(둘 다 일요일). [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 반대 날 로우가 전부 광배를 쓰고 있었다</t>
+    <t>직접 6세트: 월요일 인클라인 벤치프레스 머신 3 · 인클라인 덤벨 플라이 3 (2026-10-02 사용자 조정) — 흉근 합산을 내리려고 둘에서 하나씩 뺐다. 간접 0 — 흉근 상/하는 I열에서 합산 판정하므로 서로에게 간접을 얹지 않는다(2026-10-02 교차 계상 제거). 상부지를 복합 하나 · 고립 하나로 나눠 각 4세트다. 단독 판정이 '하한'으로 뜨지만 흉근은 I열 합산(25.0)으로 판정한다</t>
+  </si>
+  <si>
+    <t>직접 16세트: 월요일 벤치 5 · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 4. 간접 0.6 — 인클라인 덤벨 플라이 0.2×3 (인클라인 머신의 교차 간접은 2026-10-02에 0으로). 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
+  </si>
+  <si>
+    <t>직접 16세트: 목요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 4 + 일요일(수평) 원암 케이블 로우 4 (2026-10-02 사용자 조정). 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3(둘 다 일요일). [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 반대 날 로우가 전부 광배를 쓰고 있었다</t>
   </si>
   <si>
     <t>등 합산</t>
@@ -4057,6 +4060,9 @@
     <t>직접 3세트: 일요일(수평) 트랩바 슈러그 3 — 재택도 수평 날에 둔다 (2026-10-02 신설). 간접 1.4 — 오버헤드 프레스 · 스미스 바벨 로우 각 0.2 (데드의 등척성 견갑대 유지는 2026-10-02에 0으로). 현장 일이 하루치를 얹어주던 것이 끝나 0 → 3으로 되살렸다. 재택 6일차와 같은 종목이다</t>
   </si>
   <si>
+    <t>등 중요부위</t>
+  </si>
+  <si>
     <t>직접 3세트: 목요일(수직) 오버헤드 슈러그 3 — 팔이 머리 위라 수직 날에 맞는다. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
   </si>
   <si>
@@ -4066,7 +4072,7 @@
     <t>직접 9세트: 수요일 데드 톱 1 + 백오프 2 + 등 하는 날 둘에 백 익스텐션(45도 · 맨몸) 3씩 (2026-10-02 사용자 요청 — 재택도 당기기 두 날에 3세트씩 둔다). 3 → 9으로 '보완 필요'가 '충분'이 됐다. **척추 신전을 강조해서 해야 이 9세트가 유효하다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근 · 햄스트링이 주동근이 되고 기립근은 버티기만 한다. 그러면 09-04 규칙상 등척성이라 계수 0이고 이 숫자가 거짓이 된다. 중량은 더블 프로그레션 — 맨몸 15회를 채우면 원판 5~10kg을 안는다('맨몸'은 시작값이지 상한이 아니다). 목요일 것도 원판 금지가 아니고, 데드 다음날이라 일요일보다 낮게 나오는 것이 정상이다 — 수요일 데드나 토요일 스쿼트가 2주 연속 안 오르면 그 날 중량을 먼저 의심한다. 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
   </si>
   <si>
-    <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 5.9 — 벤치 0.33×5 + 인클라인 머신 0.5×4 + 딥스 0.2×3 + 인클라인 플라이 0.2×4 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
+    <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 5.0 — 벤치 0.33×5 + 인클라인 머신 0.5×3 + 딥스 0.2×3 + 인클라인 플라이 0.2×3 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
   </si>
   <si>
     <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.0 — 오버헤드 프레스 0.33×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
@@ -4090,13 +4096,13 @@
     <t>직접 11세트: 토요일 아우터 타이 4 · 수요일 아우터 타이 4 · 케이블 힙 외전 3 (7 → 11). 간접 출처 없음 — 스쿼트 · 레그 프레스는 양측 지지라 계수가 없다. [2026-10-02 사용자 요청] 수요일에 슈퍼세트를 얹어 하한(8) 아래였던 7.0이 11로 올라갔다. 앉아서 하는 아우터(고관절 굽힘)와 선 자세 편측 케이블(고관절 펴짐)로 각도를 나눴다</t>
   </si>
   <si>
-    <t>직접 6세트: 토요일 시티드 3 · 수요일 스탠딩 3 (3 → 6). 간접 출처 없음. 현장 일이 하루치를 얹어주던 것이 끝나 올렸다. 무릎 각도로 가자미근 · 비복근을 나눴다</t>
+    <t>직접 12세트: 토요일 시티드 6 · 수요일 스탠딩 6. 간접 출처 없음. 현장 일이 하루치를 얹어주던 것이 끝나 3 → 6으로 한 번 올렸고, (2026-10-02 사용자 조정)으로 두 날 모두 6이 되어 실질 6.0 '보완 필요'가 12.0 '충분'이 됐다. 무릎 각도로 가자미근 · 비복근을 나눴다</t>
   </si>
   <si>
     <t>직접 9세트: 일요일 프리쳐 컬 3 · 화요일 인클라인 덤벨 컬 3 · 목요일 케이블 드래그 컬 3 (6 → 9). 간접 7.3 — 당기기 6종목을 그립별로 (뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2) + 리버스컬 0.2×3. 짧아진 · 늘어난 · 중간 구간 셋으로 나눴다</t>
   </si>
   <si>
-    <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 7.6 — 인클라인 머신 · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향, 2026-10-02). 실질 16.5로 성장 구간 상단이다</t>
+    <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 7.1 — 인클라인 머신(3) · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향). 실질 16.0으로 성장 구간 상단이다</t>
   </si>
   <si>
     <t>직접 21세트: 리스트 컬 굴근 · 신근 슈퍼세트를 팔 하는 날 셋에 각 3+3(일 · 화 · 목) + 화요일 리버스컬 3. 간접 3.0 — 컬 3종 0.33씩. [2026-10-02 사용자 지정 '그냥 다 넣어'] 9 → 21로 올렸고 빈도가 주 1회 → 3회가 됐다. 실질 24.0으로 천장(20)을 넘겨 '과다 점검'이 뜨는 첫 부위다. 굴근은 일 · 목에서 당기기(16 · 11세트) 뒤에 오므로 중량을 7.5로 낮춰 잡았다(화요일 10) — 신근은 세 날 다 같은 중량이다 — 당기기가 신근을 전혀 쓰지 않아 날마다 흔들리지 않는다. 전완은 세 갈래이고 셋을 다 덮는다 — 손목 굴근군(앞면 · 손등 아래 9) · 손목 신근군(뒷면 · 손등 위 9) · 상완요골근(요측 · 팔꿈치를 넘는다 · 리버스컬 3). 리스트 컬 두 개가 가르는 것은 앞/뒤이고, 요측 / 척측(엄지쪽 / 새끼손가락쪽)으로 가르는 종목은 없다. 신근 중량은 7.5로 통일했다 — 굴근의 절반 남짓한 힘이라 같은 10kg을 쓰는 것이 말이 안 됐다(재택도 굴근 15 / 신근 10으로 갈라 둔다). 되돌리려면 일 · 목의 굴근(손등 아래)부터 뺀다 — 순수 그립이 온종일 등척성으로 쓰는 쪽이고, 09-04 규칙상 그 등척성은 계수 0이라 표에 안 보이지만 실제 부하는 있다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다</t>
@@ -4186,10 +4192,10 @@
     <t>· 기립근 6.5 · 승모 상부 4.5 · 승모 하부 5.0 · 종아리 6.0 · 복부 6.0 · 내전근 6.0 — '보완 필요'로 뜨지만 넷은 이번에 올린 자리이고 이 이상 올리면 세션이 상한을 넘는다. 다음 카드는 여기다.</t>
   </si>
   <si>
-    <t>· 중둔근 11.0 · 내전근 12.5 — 2026-10-02에 수요일 이너/아우터 슈퍼세트가 들어와 둘 다 하한 아래(7.0 · 6.5)에서 성장 구간으로 올라왔다. 하체에서 '보완 필요'로 남은 곳은 이제 종아리 6.0뿐이다.</t>
-  </si>
-  <si>
-    <t>· 기립근 12.0 — 2026-10-02에 백 익스텐션 6세트가 들어와 6.0 '보완 필요'에서 올라왔다. 하체 · 등에서 '보완 필요'로 남은 곳은 종아리 6.0 · 승모 상부 4.5 · 승모 하부 6.0이다.</t>
+    <t>· 중둔근 11.0 · 내전근 12.5 — 2026-10-02에 수요일 이너/아우터 슈퍼세트가 들어와 둘 다 하한 아래(7.0 · 6.5)에서 성장 구간으로 올라왔다.</t>
+  </si>
+  <si>
+    <t>· 기립근 12.0 · 종아리 12.0 — 백 익스텐션 6세트와 카프 3 → 6씩(사용자 조정)으로 둘 다 6.0 '보완 필요'에서 올라왔다. 남은 '보완 필요'는 승모 상부 4.5 · 승모 하부 6.0 · 흉근 상부 6.0 · 복부 6.0 · 목 6.0 다섯이다 — 흉근 상부는 사용자가 합산(22.5)을 내리려고 일부러 6으로 내린 자리이므로 I열 합산으로 판정한다.</t>
   </si>
   <si>
     <t>· 전완 24.0 — **'과다 점검'이 뜨는 유일한 부위이고 그게 뜬 첫 사례다**(2026-10-02 사용자 지정). 표가 금지하지는 않는다. 다만 손목 · 팔꿈치가 시큰해지면 가장 먼저 의심할 자리이고, 되돌리는 순서는 일 · 목의 굴근(손등 아래) → 리버스컬이다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다.</t>
@@ -11164,7 +11170,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11229,7 +11235,7 @@
       </c>
       <c r="E6" s="121">
         <f>복귀_토_하체전면!$E$30</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" s="114" t="s">
         <v>917</v>
@@ -11253,7 +11259,7 @@
       </c>
       <c r="E7" s="121">
         <f>복귀_일_수평당기기!$E$21</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="114" t="s">
         <v>922</v>
@@ -11277,7 +11283,7 @@
       </c>
       <c r="E8" s="121">
         <f>복귀_월_가슴!$E$24</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F8" s="114" t="s">
         <v>927</v>
@@ -11325,7 +11331,7 @@
       </c>
       <c r="E10" s="121">
         <f>복귀_수_하체후면!$E$41</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F10" s="114" t="s">
         <v>937</v>
@@ -11349,7 +11355,7 @@
       </c>
       <c r="E11" s="121">
         <f>복귀_목_수직당기기!$E$23</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>942</v>
@@ -11390,7 +11396,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F13" s="116" t="s">
         <v>946</v>
@@ -11517,13 +11523,13 @@
         <v>970</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="107" t="s">
+    <row r="40" spans="1:1">
+      <c r="A40" s="123" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="123" t="s">
+      <c r="A42" s="107" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11542,13 +11548,13 @@
         <v>975</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="107" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="123" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="123" t="s">
+      <c r="A48" s="107" t="s">
         <v>977</v>
       </c>
     </row>
@@ -11572,13 +11578,13 @@
         <v>981</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="107" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" s="123" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="123" t="s">
+      <c r="A55" s="107" t="s">
         <v>983</v>
       </c>
     </row>
@@ -11607,13 +11613,13 @@
         <v>988</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="107" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" s="123" t="s">
         <v>989</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="123" t="s">
+      <c r="A63" s="107" t="s">
         <v>990</v>
       </c>
     </row>
@@ -11630,6 +11636,11 @@
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
         <v>993</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="123" t="s">
+        <v>994</v>
       </c>
     </row>
   </sheetData>
@@ -11660,7 +11671,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11741,22 +11752,22 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="110" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11844,10 +11855,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="113" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K20" s="113" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L20" s="112" t="s">
         <v>356</v>
@@ -11885,10 +11896,10 @@
         <v>13</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -11924,10 +11935,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -11965,7 +11976,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K23" s="115" t="s">
         <v>597</v>
@@ -12004,10 +12015,10 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -12020,7 +12031,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>372</v>
@@ -12045,10 +12056,10 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -12086,10 +12097,10 @@
         <v>11.9</v>
       </c>
       <c r="J26" s="115" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="K26" s="115" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="L26" s="114"/>
       <c r="M26" s="114"/>
@@ -12127,10 +12138,10 @@
         <v>3.3</v>
       </c>
       <c r="J27" s="115" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="K27" s="115" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L27" s="114"/>
       <c r="M27" s="114" t="s">
@@ -12168,10 +12179,10 @@
         <v>10.7</v>
       </c>
       <c r="J28" s="115" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="K28" s="115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
@@ -12193,7 +12204,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="114">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F29" s="114" t="s">
         <v>303</v>
@@ -12206,13 +12217,13 @@
       </c>
       <c r="I29" s="114">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -12227,94 +12238,94 @@
       </c>
       <c r="E30" s="116">
         <f>SUM(E20:E29)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F30" s="116"/>
       <c r="G30" s="116"/>
       <c r="H30" s="116"/>
       <c r="I30" s="116">
         <f>ROUND(SUM(I20:I29),0)</f>
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="107" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
   </sheetData>
@@ -12345,27 +12356,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12422,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>296</v>
@@ -12447,13 +12458,13 @@
         <v>12.7</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -12488,13 +12499,13 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="L12" s="114" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="M12" s="114"/>
       <c r="N12" s="114"/>
@@ -12513,7 +12524,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="114" t="s">
         <v>292</v>
@@ -12526,13 +12537,13 @@
       </c>
       <c r="I13" s="114">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -12568,10 +12579,10 @@
         <v>6.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -12609,10 +12620,10 @@
         <v>6.5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -12648,10 +12659,10 @@
         <v>6.8</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -12689,10 +12700,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12705,7 +12716,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>309</v>
@@ -12730,10 +12741,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114" t="s">
@@ -12771,10 +12782,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114" t="s">
@@ -12812,10 +12823,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -12830,124 +12841,124 @@
       </c>
       <c r="E21" s="116">
         <f>SUM(E11:E20)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" s="116"/>
       <c r="G21" s="116"/>
       <c r="H21" s="116"/>
       <c r="I21" s="116">
         <f>ROUND(SUM(I11:I20),0)</f>
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="107" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="107" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="107" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="117" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="117" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="117" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="C48" s="118" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
   </sheetData>
@@ -12978,7 +12989,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -13064,7 +13075,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -13152,10 +13163,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="113" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="K18" s="113" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="L18" s="112" t="s">
         <v>356</v>
@@ -13177,7 +13188,7 @@
         <v>35</v>
       </c>
       <c r="E19" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="114" t="s">
         <v>298</v>
@@ -13190,13 +13201,13 @@
       </c>
       <c r="I19" s="114">
         <f t="shared" si="0"/>
-        <v>12.7</v>
+        <v>9.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13216,7 +13227,7 @@
         <v>358</v>
       </c>
       <c r="E20" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="114" t="s">
         <v>364</v>
@@ -13229,13 +13240,13 @@
       </c>
       <c r="I20" s="114">
         <f t="shared" si="0"/>
-        <v>9.6999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13271,13 +13282,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="L21" s="114" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13287,13 +13298,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E22" s="114">
         <v>3</v>
@@ -13312,10 +13323,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13332,7 +13343,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
@@ -13351,10 +13362,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13369,89 +13380,89 @@
       </c>
       <c r="E24" s="116">
         <f>SUM(E18:E23)</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F24" s="116"/>
       <c r="G24" s="116"/>
       <c r="H24" s="116"/>
       <c r="I24" s="116">
         <f>ROUND(SUM(I18:I23),0)</f>
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="118" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
   </sheetData>
@@ -13482,22 +13493,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13584,10 +13595,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13625,10 +13636,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13664,10 +13675,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -13678,7 +13689,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>309</v>
@@ -13703,10 +13714,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114" t="s">
@@ -13744,10 +13755,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114" t="s">
@@ -13760,7 +13771,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>939</v>
@@ -13785,10 +13796,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -13799,7 +13810,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>939</v>
@@ -13824,10 +13835,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -13863,10 +13874,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -13902,10 +13913,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13932,127 +13943,127 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="107" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="107" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="117" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
   </sheetData>
@@ -14764,7 +14775,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14845,7 +14856,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14921,22 +14932,22 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -15024,10 +15035,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -15038,7 +15049,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -15064,10 +15075,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -15084,7 +15095,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -15103,10 +15114,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -15117,7 +15128,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -15142,10 +15153,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -15181,10 +15192,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -15195,7 +15206,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -15221,10 +15232,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -15262,10 +15273,10 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K34" s="115" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L34" s="114"/>
       <c r="M34" s="114"/>
@@ -15303,10 +15314,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15342,10 +15353,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15381,10 +15392,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15420,10 +15431,10 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="K38" s="115" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
@@ -15461,10 +15472,10 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
@@ -15486,7 +15497,7 @@
         <v>10</v>
       </c>
       <c r="E40" s="114">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F40" s="114" t="s">
         <v>303</v>
@@ -15499,13 +15510,13 @@
       </c>
       <c r="I40" s="114">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15520,179 +15531,179 @@
       </c>
       <c r="E41" s="116">
         <f>SUM(E28:E40)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F41" s="116"/>
       <c r="G41" s="116"/>
       <c r="H41" s="116"/>
       <c r="I41" s="116">
         <f>ROUND(SUM(I28:I40),0)</f>
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="107" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="107" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="117" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
   </sheetData>
@@ -15723,27 +15734,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15825,13 +15836,13 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -15841,7 +15852,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
@@ -15866,10 +15877,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15880,7 +15891,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
@@ -15889,7 +15900,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="114" t="s">
         <v>288</v>
@@ -15902,13 +15913,13 @@
       </c>
       <c r="I13" s="114">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11.7</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15946,10 +15957,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15985,10 +15996,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -16024,10 +16035,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -16063,10 +16074,10 @@
         <v>10.7</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -16079,7 +16090,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>359</v>
@@ -16104,10 +16115,10 @@
         <v>5.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -16118,7 +16129,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>283</v>
@@ -16143,10 +16154,10 @@
         <v>5.8</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -16157,7 +16168,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>309</v>
@@ -16182,10 +16193,10 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114" t="s">
@@ -16223,10 +16234,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114" t="s">
@@ -16264,10 +16275,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -16282,124 +16293,124 @@
       </c>
       <c r="E23" s="116">
         <f>SUM(E11:E22)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" s="116"/>
       <c r="G23" s="116"/>
       <c r="H23" s="116"/>
       <c r="I23" s="116">
         <f>ROUND(SUM(I11:I22),0)</f>
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="107" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="107" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="107" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
   </sheetData>
@@ -16800,12 +16811,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16819,12 +16830,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16850,7 +16861,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16873,12 +16884,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16891,22 +16902,22 @@
       </c>
       <c r="E8" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16929,12 +16940,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16957,15 +16968,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16985,12 +16996,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -17013,15 +17024,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -17031,25 +17042,25 @@
       </c>
       <c r="E13" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -17069,12 +17080,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -17087,25 +17098,25 @@
       </c>
       <c r="E15" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="G15" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>283</v>
@@ -17125,12 +17136,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -17153,12 +17164,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -17181,12 +17192,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -17209,12 +17220,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -17227,22 +17238,22 @@
       </c>
       <c r="E20" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -17265,12 +17276,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -17283,22 +17294,22 @@
       </c>
       <c r="E22" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G22" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -17321,12 +17332,12 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>302</v>
@@ -17349,15 +17360,15 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="38.25">
       <c r="A25" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>368</v>
@@ -17377,12 +17388,12 @@
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.25">
       <c r="A26" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>522</v>
@@ -17405,15 +17416,15 @@
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>383</v>
@@ -17433,15 +17444,15 @@
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5">
       <c r="A28" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>281</v>
@@ -17461,12 +17472,12 @@
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>479</v>
@@ -17489,12 +17500,12 @@
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>95</v>
@@ -17517,15 +17528,15 @@
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>421</v>
@@ -17545,15 +17556,15 @@
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C32" s="114" t="s">
         <v>421</v>
@@ -17573,12 +17584,12 @@
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25.5">
       <c r="A33" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>95</v>
@@ -17601,12 +17612,12 @@
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>280</v>
@@ -17629,15 +17640,15 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>432</v>
@@ -17647,25 +17658,25 @@
       </c>
       <c r="E35" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="G35" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17685,12 +17696,12 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5">
       <c r="A37" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>479</v>
@@ -17713,12 +17724,12 @@
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="38.25">
       <c r="A38" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>424</v>
@@ -17741,12 +17752,12 @@
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>537</v>
@@ -17769,15 +17780,15 @@
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C40" s="114" t="s">
         <v>296</v>
@@ -17797,12 +17808,12 @@
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>486</v>
@@ -17815,22 +17826,22 @@
       </c>
       <c r="E41" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G41" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
       <c r="A42" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>93</v>
@@ -17853,15 +17864,15 @@
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C43" s="114" t="s">
         <v>327</v>
@@ -17881,12 +17892,12 @@
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>431</v>
@@ -17909,12 +17920,12 @@
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="51">
       <c r="A45" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>573</v>
@@ -17937,12 +17948,12 @@
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B46" s="115" t="s">
         <v>498</v>
@@ -17965,12 +17976,12 @@
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>93</v>
@@ -17998,7 +18009,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>95</v>
@@ -18021,15 +18032,15 @@
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -18049,12 +18060,12 @@
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>388</v>
@@ -18082,7 +18093,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>573</v>
@@ -18105,12 +18116,12 @@
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="38.25">
       <c r="A52" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>570</v>
@@ -18133,12 +18144,12 @@
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25">
       <c r="A53" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>95</v>
@@ -18161,15 +18172,15 @@
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25.5">
       <c r="A54" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
@@ -18189,15 +18200,15 @@
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51">
       <c r="A55" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
@@ -18217,12 +18228,12 @@
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>93</v>
@@ -18245,12 +18256,12 @@
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>388</v>
@@ -18273,15 +18284,15 @@
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25.5">
       <c r="A58" s="114" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -18301,12 +18312,12 @@
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="114" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B59" s="115" t="s">
         <v>495</v>
@@ -18334,7 +18345,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="114" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>605</v>
@@ -18362,10 +18373,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -18385,12 +18396,12 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="38.25">
       <c r="A62" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>97</v>
@@ -18413,12 +18424,12 @@
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B63" s="115" t="s">
         <v>441</v>
@@ -18441,12 +18452,12 @@
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5">
       <c r="A64" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>531</v>
@@ -18459,7 +18470,7 @@
       </c>
       <c r="E64" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -18469,12 +18480,12 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>600</v>
@@ -18487,22 +18498,22 @@
       </c>
       <c r="E65" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G65" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>93</v>
@@ -18525,12 +18536,12 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>502</v>
@@ -18543,7 +18554,7 @@
       </c>
       <c r="E67" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F67" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -18553,15 +18564,15 @@
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C68" s="114" t="s">
         <v>939</v>
@@ -18581,7 +18592,7 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
   </sheetData>
@@ -18606,12 +18617,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18640,7 +18651,7 @@
       </c>
       <c r="B5" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A5)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A5)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A5)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A5)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A5)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A5)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A5),0.5)</f>
@@ -18648,21 +18659,21 @@
       </c>
       <c r="D5" s="114">
         <f t="shared" ref="D5:D25" ca="1" si="0">B5+C5</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="114" t="str">
         <f t="shared" ref="E5:E25" ca="1" si="1">IF(D5&gt;20,"과다 점검",IF(D5&gt;=10,"충분",IF(D5&gt;=8,"하한",IF(D5&gt;=1,"보완 필요","미배치"))))</f>
-        <v>하한</v>
+        <v>보완 필요</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
       </c>
       <c r="I5" s="125">
         <f ca="1">SUM(D5:D6)</f>
-        <v>25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1">
@@ -18675,18 +18686,18 @@
       </c>
       <c r="C6" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A6),0.5)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="E6" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18695,7 +18706,7 @@
       </c>
       <c r="B7" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A7)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A7)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A7)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A7)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A7)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A7)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A7),0.5)</f>
@@ -18703,21 +18714,21 @@
       </c>
       <c r="D7" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="E7" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
-        <v>46</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1">
@@ -18741,7 +18752,14 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1332</v>
+        <v>1333</v>
+      </c>
+      <c r="H8" s="124" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I8" s="125">
+        <f>SUM(복귀_일_수평당기기!E11:E14,복귀_목_수직당기기!E11:E13)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
@@ -18765,7 +18783,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18778,18 +18796,18 @@
       </c>
       <c r="C10" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A10),0.5)</f>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D10" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="E10" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18813,7 +18831,7 @@
         <v>충분</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18826,18 +18844,18 @@
       </c>
       <c r="C12" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A12),0.5)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18861,7 +18879,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18885,7 +18903,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18909,14 +18927,14 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
@@ -18940,7 +18958,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18964,7 +18982,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18988,7 +19006,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -18997,7 +19015,7 @@
       </c>
       <c r="B19" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A19)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A19)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A19)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A19)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A19)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A19)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C19" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A19),0.5)</f>
@@ -19005,14 +19023,14 @@
       </c>
       <c r="D19" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E19" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>보완 필요</v>
+        <v>충분</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -19025,18 +19043,18 @@
       </c>
       <c r="C20" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A20),0.5)</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D20" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="E20" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -19049,18 +19067,18 @@
       </c>
       <c r="C21" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A21),0.5)</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D21" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="E21" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -19084,7 +19102,7 @@
         <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -19108,7 +19126,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -19132,7 +19150,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -19156,7 +19174,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -19165,11 +19183,11 @@
       </c>
       <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -19179,192 +19197,192 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="107" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="123" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_976DDB3BF43AA339F7E760932C78BE6F3F568295" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_0C25657BE93238B977D730997BA8BB147CE377DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2672" uniqueCount="1391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="1396">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -103,7 +103,7 @@
     <t>주당 환산 161세트</t>
   </si>
   <si>
-    <t>203세트</t>
+    <t>206세트</t>
   </si>
   <si>
     <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 여섯(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 페이스풀 · 전완 슈퍼세트 주 3회 · 백 익스텐션 주 2회)</t>
@@ -2881,13 +2881,13 @@
     <t>당기기 수직 + 가슴 B</t>
   </si>
   <si>
-    <t>등 수직 당기기 · 가슴(중하부) · 팔</t>
-  </si>
-  <si>
-    <t>약 90분</t>
-  </si>
-  <si>
-    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 맨 뒤에 전완 슈퍼세트 6 + 백 익스텐션 3 (데드 다음날이라 일요일보다 중량이 낮게 나오는 것이 정상 — 금지는 아니다)</t>
+    <t>등 수직 당기기 · 가슴(상부 + 중하부) · 팔</t>
+  </si>
+  <si>
+    <t>약 100분</t>
+  </si>
+  <si>
+    <t>데드 다음날이라 척추 부하가 거의 0인 수직 당기기만 둔다 — 친업은 매달리고 랫풀다운은 앉아서 고정된다. 그립이 지쳐 있으면 친업을 어시스트 머신으로. 가슴 블록은 인클라인 벤치프레스(스미스) 3 + 플라이 8로 11이다. 맨 뒤에 전완 슈퍼세트 6 + 백 익스텐션 3 (데드 다음날이라 일요일보다 중량이 낮게 나오는 것이 정상 — 금지는 아니다)</t>
   </si>
   <si>
     <t>금</t>
@@ -2896,7 +2896,7 @@
     <t>유일한 휴식일. 토요일에 스쿼트가 있으므로 휴식을 그 앞에 둔다</t>
   </si>
   <si>
-    <t>약 468분 (7시간 48분)</t>
+    <t>약 478분 (7시간 58분)</t>
   </si>
   <si>
     <t>[배치 논리]</t>
@@ -2941,7 +2941,7 @@
     <t>[빈도를 올리고 볼륨은 조금만 올렸다 — 2026-10-02]</t>
   </si>
   <si>
-    <t>· 주 4회 140세트 → 주 6회 203세트. 세트는 45% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회, 전완은 주 1회 → 3회로 올랐다. 주 1회로 남은 것은 사두(토 12)뿐이다.</t>
+    <t>· 주 4회 140세트 → 주 6회 206세트. 세트는 47% 늘었고 가슴 · 등 · 하체 · 햄스트링 · 내전근 · 중둔근 · 승모 중부 빈도가 주 1회 → 2회, 전완은 주 1회 → 3회로 올랐다. 주 1회로 남은 것은 사두(토 12)뿐이다.</t>
   </si>
   <si>
     <t>· 늘린 곳은 전부 '현장 일 보정'이 사라진 자리다 — 승모 상부 0 → 3 · 기립근 1 → 3 · 종아리 3 → 6 · 전완 6 → 9 · 복부 3 → 6 · 목 0 → 6(신설). 삼두 · 이두도 6 → 9로 올렸다.</t>
@@ -2959,7 +2959,10 @@
     <t>· ⑦ 백 익스텐션(45도) 3세트를 등 하는 날 둘에 넣었다 — 사용자 요청. 기립근 직접 3 → 9 · 실질 6.0 → 12.0으로 '보완 필요'가 '충분'이 됐다. 재택도 당기기 두 날에 3세트씩 둔다. 맨몸은 시작값이고 원판 5~10kg이 진행 경로다 — 두 날 다 중량 금지가 아니다. 척추 신전을 강조해서 해야 기립근이 주동근이 된다(힌지식이면 등척성이라 계수 0). 191 → 197세트.</t>
   </si>
   <si>
-    <t>· ⑧ 같은 날 사용자가 엑셀에서 여섯 칸을 직접 조정했다 — 카프 토 · 수 각 3 → 6(종아리 6 → 12로 '보완 필요' 해결) · 원암 케이블 로우 3 → 4 · 언더그립 랫풀다운 3 → 4(광배 14 → 16 · 실질 19.5) · 인클라인 머신 · 인클라인 덤벨 플라이 각 4 → 3(흉근 상부 8 → 6 · 흉근 합산 25.0 → 22.5). 197 → 203세트 · 468분. 세트검산에 '등 중요부위' 보조 칸도 직접 만들었다 — 당기기 본 종목만 센다.</t>
+    <t>· ⑧ 같은 날 사용자가 엑셀에서 여섯 칸을 직접 조정했다 — 카프 토 · 수 각 3 → 6(종아리 6 → 12로 '보완 필요' 해결) · 원암 케이블 로우 3 → 4 · 언더그립 랫풀다운 3 → 4(광배 14 → 16 · 실질 19.5) · 인클라인 머신 · 인클라인 덤벨 플라이 각 4 → 3(흉근 상부 8 → 6 · 흉근 합산 25.0 → 22.5). 197 → 203세트. 세트검산에 '등 중요부위' 보조 칸도 직접 만들었다 — 당기기 본 종목만 센다.</t>
+  </si>
+  <si>
+    <t>· ⑨ 목요일에 인클라인 벤치프레스(스미스) 3세트 — 사용자 요청. 재택 4일차와 같은 종목 · 중량 · 세트이고 계수도 그대로 쓴다(삼두 0.5 · 전면삼각 0.5). 흉근 상부 6 → 9로 주 2회가 됐고 흉근 합산은 22.5 → 25.5로 되올라왔다. 203 → 206세트 · 478분.</t>
   </si>
   <si>
     <t>· [2026-10-02 사용자 제안 교환] 토요일 원 레그 컬 3 ↔ 수요일 레그 컬 4를 맞바꿨다. 중량은 국소 피로가 정하고 토요일엔 햄스트링 직접 종목이 달리 없어 국소로 신선하므로 양측 중량 종목이 그 날에 맞고, 편측은 좌우 차를 드러내는 것이 목적이라 주의력이 필요해 누적이 적은 수요일 5번이 맞다. 햄스트링 주 10세트와 총량 176은 그대로고 세션만 고르게 됐다(토 92/수 101 → 95/98).</t>
@@ -3010,7 +3013,7 @@
     <t>[세션 크기]</t>
   </si>
   <si>
-    <t>· 수 42세트 104분 · 토 41세트 101분 · 목 41세트 90분 · 일 32세트 74분 · 화 27세트 46분 · 월 20세트 53분.</t>
+    <t>· 목 44세트 100분 · 수 42세트 104분 · 토 41세트 101분 · 일 32세트 74분 · 화 27세트 46분 · 월 20세트 53분.</t>
   </si>
   <si>
     <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 29를 빼면 실질 12, 수요일은 26을 빼면 16, 월요일은 9를 빼면 11이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
@@ -3022,7 +3025,7 @@
     <t>· 등 블록 둘이 32(일) / 41(목)로 갈리는 것은 가슴 8세트가 목요일에 묶여 있어서다(사용자 지정 '목요일 가슴/등').</t>
   </si>
   <si>
-    <t>· 주 468분 = 7시간 48분. 주 4회 370분에서 98분 늘었다. 수(104) · 토(101)가 가장 크지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>· 주 478분 = 7시간 58분. 주 4회 370분에서 108분 늘었다. 수(104) · 토(101) · 목(100) 셋이 100분을 넘지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
   </si>
   <si>
     <t>· 수 · 토가 100분 안팎으로 커진 것은 하체 고립이 그 둘에 몰려 있기 때문이다. 세트 수는 많아도 휴식이 10~120초라 분으로는 덜 든다 — 수요일 어깨 뒤 14세트가 14분이다.</t>
@@ -3748,6 +3751,12 @@
     <t>리어 델트 로우 (로프) / 케이블 리버스 플라이 (팔 편 채) / 리버스 펙덱</t>
   </si>
   <si>
+    <t>[2026-10-02 사용자 요청] 가슴 블록 첫째 — 복합이라 플라이보다 앞에 둔다. 재택 4일차와 같은 종목 · 같은 중량 · 같은 세트이고 계수도 그대로 쓴다(삼두 0.5 · 전면삼각 0.5). 월요일 인클라인 벤치프레스 머신(35kg)과 기구가 갈린다 — 스미스는 궤도가 고정되되 바를 직접 쥐므로 안정화가 조금 더 든다. 상부지를 월 6(머신 3 + 플라이 3) + 목 3으로 주 2회로 쪼갰다.</t>
+  </si>
+  <si>
+    <t>인클라인 벤치프레스 머신 (월요일과 같은 기구가 되나 자리는 유효) / 인클라인 덤벨 프레스 / 헤머스트랭스 인클라인 프레스</t>
+  </si>
+  <si>
     <t>수평 내전으로 중간 구간을 맡는다. 등 18세트 뒤라 가슴이 온전하다 — 당기기와 밀기는 경쟁하지 않는다.</t>
   </si>
   <si>
@@ -3811,19 +3820,19 @@
     <t>· 사용자 지정 — '목요일 가슴/등'. 거기에 팔 후반부가 붙어 등 → 가슴 → 팔 세 블록이 됐다.</t>
   </si>
   <si>
-    <t>· 등(수직 18) → 가슴(중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
+    <t>· 등(수직 18) → 가슴(상부 3 + 중하부 8) → 팔(삼두 3 · 이두 3) 순서다. 당기기와 밀기는 주동근이 겹치지 않아 한 세션에 붙여도 서로 깎지 않는다.</t>
   </si>
   <si>
     <t>· 팔이 맨 뒤인 이유 — 앞의 18세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
   </si>
   <si>
-    <t>· 41세트 · 약 90분. 전완 슈퍼세트 6 + 백 익스텐션 3이 들어오고 언더그립 랫풀다운이 3 → 4로 올라 31 → 41이 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정).</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 29를 빼면 실질 12다.</t>
-  </si>
-  <si>
-    <t>· 일요일(32세트 74분)과 합쳐 보면 등 블록 둘이 32/41로 갈린다 — 가슴 8세트가 이 날에 묶여 있어서다.</t>
+    <t>· 44세트 · 약 100분. 전완 슈퍼세트 6 + 백 익스텐션 3 + 인클라인 벤치프레스(스미스) 3이 들어오고 언더그립 랫풀다운이 3 → 4로 올라 31 → 44가 됐다 (2026-10-02 사용자 요청 · 조정).</t>
+  </si>
+  <si>
+    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 29를 빼면 실질 15다.</t>
+  </si>
+  <si>
+    <t>· 일요일(32세트 74분)과 합쳐 보면 등 블록 둘이 32/44로 갈린다 — 가슴 11세트가 이 날에 묶여 있어서다. 수요일(42/104)과 함께 100분을 넘는 두 날이 됐다.</t>
   </si>
   <si>
     <t>· 언더그립 랫풀다운 +60초 · 디클라인 케이블 플라이 +60초. 마지막 세트에만 2단.</t>
@@ -3841,7 +3850,7 @@
     <t>· 페이스풀에도 걸지 않는다. 가벼운 외회전 종목이라 실패 뒤 반복에서 팔꿈치가 먼저 내려온다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  일요일을 수평으로 바꿔줘  /  그냥 다 넣어. 팔하는 날에는 슈퍼세트로 묶어서 (전완)</t>
+    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  일요일을 수평으로 바꿔줘  /  그냥 다 넣어. 팔하는 날에는 슈퍼세트로 묶어서 (전완)  /  목요일 날에 인클라인 벤치프레스 넣어줘. 3세트</t>
   </si>
   <si>
     <t>복귀판 간접 세트 계수 맵 — 복귀_세트검산 간접 열(C)의 계산 원천</t>
@@ -3922,6 +3931,12 @@
     <t>플라이 시작 구간 전면삼각 약관여 — 인클라인 덤벨 플라이와 같은 등급</t>
   </si>
   <si>
+    <t>인클라인은 전면삼각 관여 큼 — 인클라인 벤치프레스 머신(0.5)과 같은 등급. 재택 맵과 같은 계수 (2026-10-02)</t>
+  </si>
+  <si>
+    <t>프레스 중 팔꿈치 신전 — 보조 프레스라 0.5 유지(저반복 본세트 하향은 벤치 · 오버헤드에만 걸린다). 재택 맵과 같은 계수 (2026-10-02)</t>
+  </si>
+  <si>
     <t>페이스풀 중 후면삼각 능동 수축 — 재택 1일차와 같은 등급. 주동근(승모 중부 · 능형근)은 요일 시트에서 직접으로 센다 (2026-10-02)</t>
   </si>
   <si>
@@ -4045,7 +4060,7 @@
     <t>세트는 근육군 단위로 센다. 복귀판은 주 6회 · 주 단위이므로 이 표의 숫자가 곧 주간 세트다 — 재택판처럼 주당 환산을 할 필요가 없다.</t>
   </si>
   <si>
-    <t>직접 6세트: 월요일 인클라인 벤치프레스 머신 3 · 인클라인 덤벨 플라이 3 (2026-10-02 사용자 조정) — 흉근 합산을 내리려고 둘에서 하나씩 뺐다. 간접 0 — 흉근 상/하는 I열에서 합산 판정하므로 서로에게 간접을 얹지 않는다(2026-10-02 교차 계상 제거). 상부지를 복합 하나 · 고립 하나로 나눠 각 4세트다. 단독 판정이 '하한'으로 뜨지만 흉근은 I열 합산(25.0)으로 판정한다</t>
+    <t>직접 9세트: 월요일 인클라인 벤치프레스 머신 3 · 인클라인 덤벨 플라이 3 + 목요일 인클라인 벤치프레스(스미스) 3 (2026-10-02 사용자 요청). 월요일 둘을 4 → 3으로 내려 합산을 22.5까지 낮췄다가 목요일에 3을 더해 25.5가 됐다 — 주 1회 6에서 주 2회 9로 바뀐 셈이다. 간접 0 — 흉근 상/하는 I열에서 합산 판정하므로 서로에게 간접을 얹지 않는다(2026-10-02 교차 계상 제거). 상부지를 복합 하나 · 고립 하나로 나눠 각 4세트다. 단독 판정이 '하한'으로 뜨지만 흉근은 I열 합산(25.0)으로 판정한다</t>
   </si>
   <si>
     <t>직접 16세트: 월요일 벤치 5 · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 4. 간접 0.6 — 인클라인 덤벨 플라이 0.2×3 (인클라인 머신의 교차 간접은 2026-10-02에 0으로). 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
@@ -4072,7 +4087,7 @@
     <t>직접 9세트: 수요일 데드 톱 1 + 백오프 2 + 등 하는 날 둘에 백 익스텐션(45도 · 맨몸) 3씩 (2026-10-02 사용자 요청 — 재택도 당기기 두 날에 3세트씩 둔다). 3 → 9으로 '보완 필요'가 '충분'이 됐다. **척추 신전을 강조해서 해야 이 9세트가 유효하다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근 · 햄스트링이 주동근이 되고 기립근은 버티기만 한다. 그러면 09-04 규칙상 등척성이라 계수 0이고 이 숫자가 거짓이 된다. 중량은 더블 프로그레션 — 맨몸 15회를 채우면 원판 5~10kg을 안는다('맨몸'은 시작값이지 상한이 아니다). 목요일 것도 원판 금지가 아니고, 데드 다음날이라 일요일보다 낮게 나오는 것이 정상이다 — 수요일 데드나 토요일 스쿼트가 2주 연속 안 오르면 그 날 중량을 먼저 의심한다. 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
   </si>
   <si>
-    <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 5.0 — 벤치 0.33×5 + 인클라인 머신 0.5×3 + 딥스 0.2×3 + 인클라인 플라이 0.2×3 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
+    <t>직접 6세트: 토요일 머신 숄더 프레스 3 · 수요일 스미스 오버헤드 프레스 3. 간접 6.5 — 벤치 0.33×5 + 인클라인 스미스 0.5×3 + 인클라인 머신 0.5×3 + 딥스 0.2×3 + 인클라인 플라이 0.2×3 + 펙덱 0.2×4. 월요일에 프레스를 안 얹은 이유가 이 간접이다</t>
   </si>
   <si>
     <t>직접 10세트: 토요일 레터럴 4 · 월요일 원암 케이블 레터럴 3 · 수요일 레터럴 3. 간접 2.0 — 오버헤드 프레스 0.33×3 + 머신 숄더 프레스 0.33×3. 직접 세트가 대부분을 채우는 부위다. 셋으로 나눠 주 3회 빈도가 됐다</t>
@@ -4102,7 +4117,7 @@
     <t>직접 9세트: 일요일 프리쳐 컬 3 · 화요일 인클라인 덤벨 컬 3 · 목요일 케이블 드래그 컬 3 (6 → 9). 간접 7.3 — 당기기 6종목을 그립별로 (뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2) + 리버스컬 0.2×3. 짧아진 · 늘어난 · 중간 구간 셋으로 나눴다</t>
   </si>
   <si>
-    <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 7.1 — 인클라인 머신(3) · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향). 실질 16.0으로 성장 구간 상단이다</t>
+    <t>직접 9세트: 일요일 케이블 푸쉬다운 3 · 화요일 라잉 익스텐션 3 · 목요일 V바 푸쉬다운 3 (6 → 9). 간접 8.5 — 인클라인 머신(3) · 인클라인 스미스(3) · 딥스 · 머신 숄더 0.5씩 + 벤치 · 오버헤드 0.33씩(저반복 본세트 하향). 실질 17.5로 성장 구간 상단이고 천장까지 2.5다</t>
   </si>
   <si>
     <t>직접 21세트: 리스트 컬 굴근 · 신근 슈퍼세트를 팔 하는 날 셋에 각 3+3(일 · 화 · 목) + 화요일 리버스컬 3. 간접 3.0 — 컬 3종 0.33씩. [2026-10-02 사용자 지정 '그냥 다 넣어'] 9 → 21로 올렸고 빈도가 주 1회 → 3회가 됐다. 실질 24.0으로 천장(20)을 넘겨 '과다 점검'이 뜨는 첫 부위다. 굴근은 일 · 목에서 당기기(16 · 11세트) 뒤에 오므로 중량을 7.5로 낮춰 잡았다(화요일 10) — 신근은 세 날 다 같은 중량이다 — 당기기가 신근을 전혀 쓰지 않아 날마다 흔들리지 않는다. 전완은 세 갈래이고 셋을 다 덮는다 — 손목 굴근군(앞면 · 손등 아래 9) · 손목 신근군(뒷면 · 손등 위 9) · 상완요골근(요측 · 팔꿈치를 넘는다 · 리버스컬 3). 리스트 컬 두 개가 가르는 것은 앞/뒤이고, 요측 / 척측(엄지쪽 / 새끼손가락쪽)으로 가르는 종목은 없다. 신근 중량은 7.5로 통일했다 — 굴근의 절반 남짓한 힘이라 같은 10kg을 쓰는 것이 말이 안 됐다(재택도 굴근 15 / 신근 10으로 갈라 둔다). 되돌리려면 일 · 목의 굴근(손등 아래)부터 뺀다 — 순수 그립이 온종일 등척성으로 쓰는 쪽이고, 09-04 규칙상 그 등척성은 계수 0이라 표에 안 보이지만 실제 부하는 있다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다</t>
@@ -4180,7 +4195,7 @@
     <t>지금 표에서 눈여겨볼 곳</t>
   </si>
   <si>
-    <t>· 흉근 상 · 하는 한 근육이라 합산으로 판정한다. 합산 실질 27.5 — 천장(20)을 크게 넘는다. 2026-09-14 사용자 지정으로 가슴은 되돌리는 자리가 아니다. 판단 기준은 세트 수가 아니라 벤치 진행이다 — 월요일 벤치가 2주 연속 안 오르면 그때 이 숫자를 본다.</t>
+    <t>· 흉근 상 · 하는 한 근육이라 합산으로 판정한다. 합산 실질 25.5 — 천장(20)을 넘는다. 2026-09-14 사용자 지정으로 가슴은 되돌리는 자리가 아니다. 판단 기준은 세트 수가 아니라 벤치 진행이다 — 월요일 벤치가 2주 연속 안 오르면 그때 이 숫자를 본다.</t>
   </si>
   <si>
     <t>· 삼두 18.0 · 이두 15.5 — 둘 다 성장 구간 상단이다. 직접 9가 상한이고 더 올리면 간접 때문에 천장을 넘는다. 주 6회에서 프레스 · 당기기 빈도가 올라 간접이 먼저 늘었기 때문이다.</t>
@@ -11170,7 +11185,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11354,8 +11369,8 @@
         <v>941</v>
       </c>
       <c r="E11" s="121">
-        <f>복귀_목_수직당기기!$E$23</f>
-        <v>41</v>
+        <f>복귀_목_수직당기기!$E$24</f>
+        <v>44</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>942</v>
@@ -11396,7 +11411,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F13" s="116" t="s">
         <v>946</v>
@@ -11528,13 +11543,13 @@
         <v>971</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="107" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" s="123" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="123" t="s">
+      <c r="A43" s="107" t="s">
         <v>973</v>
       </c>
     </row>
@@ -11553,13 +11568,13 @@
         <v>976</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="107" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="123" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="123" t="s">
+      <c r="A49" s="107" t="s">
         <v>978</v>
       </c>
     </row>
@@ -11583,13 +11598,13 @@
         <v>982</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="107" t="s">
+    <row r="54" spans="1:1">
+      <c r="A54" s="123" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="123" t="s">
+      <c r="A56" s="107" t="s">
         <v>984</v>
       </c>
     </row>
@@ -11618,13 +11633,13 @@
         <v>989</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="107" t="s">
+    <row r="62" spans="1:1">
+      <c r="A62" s="123" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="123" t="s">
+      <c r="A64" s="107" t="s">
         <v>991</v>
       </c>
     </row>
@@ -11641,6 +11656,11 @@
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
         <v>994</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="123" t="s">
+        <v>995</v>
       </c>
     </row>
   </sheetData>
@@ -11671,7 +11691,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11752,22 +11772,22 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="110" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="110" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11855,10 +11875,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="113" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K20" s="113" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="L20" s="112" t="s">
         <v>356</v>
@@ -11896,10 +11916,10 @@
         <v>13</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -11935,10 +11955,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -11976,7 +11996,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K23" s="115" t="s">
         <v>597</v>
@@ -12015,10 +12035,10 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -12031,7 +12051,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>372</v>
@@ -12056,10 +12076,10 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -12097,10 +12117,10 @@
         <v>11.9</v>
       </c>
       <c r="J26" s="115" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="K26" s="115" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="L26" s="114"/>
       <c r="M26" s="114"/>
@@ -12138,10 +12158,10 @@
         <v>3.3</v>
       </c>
       <c r="J27" s="115" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="K27" s="115" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="L27" s="114"/>
       <c r="M27" s="114" t="s">
@@ -12179,10 +12199,10 @@
         <v>10.7</v>
       </c>
       <c r="J28" s="115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="K28" s="115" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
@@ -12220,10 +12240,10 @@
         <v>11.5</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -12250,82 +12270,82 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="107" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
   </sheetData>
@@ -12356,27 +12376,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12433,7 +12453,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>296</v>
@@ -12458,13 +12478,13 @@
         <v>12.7</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -12499,13 +12519,13 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L12" s="114" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="M12" s="114"/>
       <c r="N12" s="114"/>
@@ -12540,10 +12560,10 @@
         <v>12</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -12579,10 +12599,10 @@
         <v>6.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -12620,10 +12640,10 @@
         <v>6.5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -12659,10 +12679,10 @@
         <v>6.8</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -12700,10 +12720,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12716,7 +12736,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>309</v>
@@ -12741,10 +12761,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114" t="s">
@@ -12782,10 +12802,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114" t="s">
@@ -12823,10 +12843,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -12853,112 +12873,112 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="107" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="107" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="107" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="117" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="117" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="117" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="C48" s="118" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
   </sheetData>
@@ -12989,7 +13009,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -13075,7 +13095,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -13163,10 +13183,10 @@
         <v>17.5</v>
       </c>
       <c r="J18" s="113" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="K18" s="113" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="L18" s="112" t="s">
         <v>356</v>
@@ -13204,10 +13224,10 @@
         <v>9.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13243,10 +13263,10 @@
         <v>7.3</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13282,13 +13302,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="L21" s="114" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13298,13 +13318,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>368</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E22" s="114">
         <v>3</v>
@@ -13323,10 +13343,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13343,7 +13363,7 @@
         <v>372</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
@@ -13362,10 +13382,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13392,77 +13412,77 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="117" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="117" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="107" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="117" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="117" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="107" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="117" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="117" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" s="118" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
   </sheetData>
@@ -13493,22 +13513,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13595,10 +13615,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13636,10 +13656,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13675,10 +13695,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -13689,7 +13709,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>309</v>
@@ -13714,10 +13734,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114" t="s">
@@ -13755,10 +13775,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114" t="s">
@@ -13771,7 +13791,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>939</v>
@@ -13796,10 +13816,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -13810,7 +13830,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>939</v>
@@ -13835,10 +13855,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -13874,10 +13894,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -13913,10 +13933,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13943,127 +13963,127 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="107" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="107" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="117" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
   </sheetData>
@@ -14775,7 +14795,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14856,7 +14876,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -14932,22 +14952,22 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="110" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -15035,10 +15055,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -15049,7 +15069,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>327</v>
@@ -15075,10 +15095,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -15095,7 +15115,7 @@
         <v>398</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -15114,10 +15134,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -15128,7 +15148,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>389</v>
@@ -15153,10 +15173,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -15192,10 +15212,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -15206,7 +15226,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>443</v>
@@ -15232,10 +15252,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>521</v>
@@ -15273,10 +15293,10 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K34" s="115" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="L34" s="114"/>
       <c r="M34" s="114"/>
@@ -15314,10 +15334,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15353,10 +15373,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15392,10 +15412,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15431,10 +15451,10 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="K38" s="115" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
@@ -15472,10 +15492,10 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
@@ -15513,10 +15533,10 @@
         <v>11.5</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15543,167 +15563,167 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="107" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="107" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="117" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
   </sheetData>
@@ -15714,7 +15734,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -15734,27 +15754,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -15832,17 +15852,17 @@
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I22" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <f t="shared" ref="I11:I23" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -15852,7 +15872,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>281</v>
@@ -15877,10 +15897,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -15891,7 +15911,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>281</v>
@@ -15916,10 +15936,10 @@
         <v>11.7</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -15957,10 +15977,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -15996,10 +16016,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -16010,35 +16030,35 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D16" s="114">
         <v>30</v>
       </c>
       <c r="E16" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G16" s="114">
         <v>40</v>
       </c>
       <c r="H16" s="114">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="0"/>
-        <v>9.6999999999999993</v>
+        <v>9.5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -16049,13 +16069,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>534</v>
+        <v>441</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>351</v>
       </c>
       <c r="D17" s="114">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E17" s="114">
         <v>4</v>
@@ -16071,48 +16091,46 @@
       </c>
       <c r="I17" s="114">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
-      <c r="N17" s="114">
-        <v>60</v>
-      </c>
+      <c r="N17" s="114"/>
     </row>
     <row r="18" spans="1:14" ht="30" customHeight="1">
       <c r="A18" s="114">
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1234</v>
+        <v>534</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D18" s="114">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E18" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="114" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="G18" s="114">
         <v>40</v>
       </c>
       <c r="H18" s="114">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="I18" s="114">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>10.7</v>
       </c>
       <c r="J18" s="115" t="s">
         <v>1235</v>
@@ -16122,7 +16140,9 @@
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
-      <c r="N18" s="114"/>
+      <c r="N18" s="114">
+        <v>60</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="30" customHeight="1">
       <c r="A19" s="114">
@@ -16132,26 +16152,26 @@
         <v>1237</v>
       </c>
       <c r="C19" s="114" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="D19" s="114">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E19" s="114">
         <v>3</v>
       </c>
       <c r="F19" s="114" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="G19" s="114">
         <v>40</v>
       </c>
       <c r="H19" s="114">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I19" s="114">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J19" s="115" t="s">
         <v>1238</v>
@@ -16168,40 +16188,38 @@
         <v>10</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>1056</v>
+        <v>1240</v>
       </c>
       <c r="C20" s="114" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="D20" s="114">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="E20" s="114">
         <v>3</v>
       </c>
-      <c r="F20" s="114">
-        <v>15</v>
+      <c r="F20" s="114" t="s">
+        <v>288</v>
       </c>
       <c r="G20" s="114">
         <v>40</v>
       </c>
       <c r="H20" s="114">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="I20" s="114">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1058</v>
+        <v>1242</v>
       </c>
       <c r="L20" s="114"/>
-      <c r="M20" s="114" t="s">
-        <v>405</v>
-      </c>
+      <c r="M20" s="114"/>
       <c r="N20" s="114"/>
     </row>
     <row r="21" spans="1:14" ht="30" customHeight="1">
@@ -16209,7 +16227,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="115" t="s">
-        <v>608</v>
+        <v>1057</v>
       </c>
       <c r="C21" s="114" t="s">
         <v>309</v>
@@ -16227,17 +16245,17 @@
         <v>40</v>
       </c>
       <c r="H21" s="114">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I21" s="114">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" s="115" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K21" s="115" t="s">
         <v>1059</v>
-      </c>
-      <c r="K21" s="115" t="s">
-        <v>1060</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114" t="s">
@@ -16250,19 +16268,19 @@
         <v>12</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>332</v>
+        <v>608</v>
       </c>
       <c r="C22" s="114" t="s">
-        <v>327</v>
-      </c>
-      <c r="D22" s="114" t="s">
-        <v>297</v>
+        <v>309</v>
+      </c>
+      <c r="D22" s="114">
+        <v>7.5</v>
       </c>
       <c r="E22" s="114">
         <v>3</v>
       </c>
-      <c r="F22" s="114" t="s">
-        <v>303</v>
+      <c r="F22" s="114">
+        <v>15</v>
       </c>
       <c r="G22" s="114">
         <v>40</v>
@@ -16275,142 +16293,183 @@
         <v>5</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1241</v>
+        <v>1060</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1242</v>
+        <v>1061</v>
       </c>
       <c r="L22" s="114"/>
-      <c r="M22" s="114"/>
+      <c r="M22" s="114" t="s">
+        <v>405</v>
+      </c>
       <c r="N22" s="114"/>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="116"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="116" t="s">
+    <row r="23" spans="1:14" ht="30" customHeight="1">
+      <c r="A23" s="114">
+        <v>13</v>
+      </c>
+      <c r="B23" s="115" t="s">
+        <v>332</v>
+      </c>
+      <c r="C23" s="114" t="s">
+        <v>327</v>
+      </c>
+      <c r="D23" s="114" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="114">
+        <v>3</v>
+      </c>
+      <c r="F23" s="114" t="s">
+        <v>303</v>
+      </c>
+      <c r="G23" s="114">
+        <v>40</v>
+      </c>
+      <c r="H23" s="114">
+        <v>60</v>
+      </c>
+      <c r="I23" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J23" s="115" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K23" s="115" t="s">
+        <v>1245</v>
+      </c>
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="114"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="116"/>
+      <c r="B24" s="116"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116" t="s">
         <v>335</v>
       </c>
-      <c r="E23" s="116">
-        <f>SUM(E11:E22)</f>
-        <v>41</v>
-      </c>
-      <c r="F23" s="116"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="116"/>
-      <c r="I23" s="116">
-        <f>ROUND(SUM(I11:I22),0)</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="107" t="s">
-        <v>1243</v>
+      <c r="E24" s="116">
+        <f>SUM(E11:E23)</f>
+        <v>44</v>
+      </c>
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116">
+        <f>ROUND(SUM(I11:I23),0)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="117" t="s">
-        <v>1244</v>
+      <c r="A26" s="107" t="s">
+        <v>1246</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="107" t="s">
-        <v>1249</v>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="117" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="117" t="s">
-        <v>1250</v>
+      <c r="A33" s="107" t="s">
+        <v>1252</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="107" t="s">
-        <v>983</v>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="117" t="s">
+        <v>1255</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="117" t="s">
-        <v>1253</v>
+      <c r="A38" s="107" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="107" t="s">
-        <v>1030</v>
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="117" t="s">
+        <v>1258</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="117" t="s">
-        <v>1256</v>
+      <c r="A43" s="107" t="s">
+        <v>1031</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="118" t="s">
-        <v>1261</v>
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="117" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="C51" s="118" t="s">
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -16797,7 +16856,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -16811,12 +16870,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16824,18 +16883,18 @@
         <v>649</v>
       </c>
       <c r="F3" s="107">
-        <f ca="1">COUNTIF($E$7:$E$70,"?")</f>
+        <f ca="1">COUNTIF($E$7:$E$90,"?")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>652</v>
@@ -16861,7 +16920,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>97</v>
@@ -16884,12 +16943,12 @@
         <v>673</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>531</v>
@@ -16912,12 +16971,12 @@
         <v>673</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>357</v>
@@ -16940,12 +16999,12 @@
         <v>673</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>522</v>
@@ -16968,15 +17027,15 @@
         <v>673</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>359</v>
@@ -16996,12 +17055,12 @@
         <v>673</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>280</v>
@@ -17024,15 +17083,15 @@
         <v>673</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>283</v>
@@ -17052,15 +17111,15 @@
         <v>673</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>283</v>
@@ -17080,12 +17139,12 @@
         <v>673</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>486</v>
@@ -17108,15 +17167,15 @@
         <v>673</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>283</v>
@@ -17136,12 +17195,12 @@
         <v>673</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>479</v>
@@ -17164,12 +17223,12 @@
         <v>673</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>453</v>
@@ -17192,12 +17251,12 @@
         <v>673</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>97</v>
@@ -17220,12 +17279,12 @@
         <v>673</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>531</v>
@@ -17248,12 +17307,12 @@
         <v>673</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>357</v>
@@ -17276,12 +17335,12 @@
         <v>673</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>600</v>
@@ -17304,12 +17363,12 @@
         <v>673</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>441</v>
@@ -17332,18 +17391,18 @@
         <v>673</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B24" s="115" t="s">
-        <v>302</v>
+        <v>436</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
       <c r="D24" s="114">
         <v>0.5</v>
@@ -17360,21 +17419,21 @@
         <v>673</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="38.25">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="25.5">
       <c r="A25" s="114" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1172</v>
+        <v>436</v>
       </c>
       <c r="C25" s="114" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="D25" s="114">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="114">
         <f t="shared" ca="1" si="0"/>
@@ -17382,27 +17441,27 @@
       </c>
       <c r="F25" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="38.25">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="114" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="B26" s="115" t="s">
-        <v>522</v>
+        <v>302</v>
       </c>
       <c r="C26" s="114" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D26" s="114">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="114">
         <f t="shared" ca="1" si="0"/>
@@ -17410,139 +17469,139 @@
       </c>
       <c r="F26" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G26" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="25.5">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="38.25">
       <c r="A27" s="114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="C27" s="114" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="D27" s="114">
         <v>0.33</v>
       </c>
       <c r="E27" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="G27" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="25.5">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="38.25">
       <c r="A28" s="114" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>1039</v>
+        <v>522</v>
       </c>
       <c r="C28" s="114" t="s">
-        <v>281</v>
+        <v>368</v>
       </c>
       <c r="D28" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E28" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0.99</v>
       </c>
       <c r="G28" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>479</v>
+        <v>1168</v>
       </c>
       <c r="C29" s="114" t="s">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="D29" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E29" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="G29" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="25.5">
       <c r="A30" s="114" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="B30" s="115" t="s">
-        <v>95</v>
+        <v>1040</v>
       </c>
       <c r="C30" s="114" t="s">
         <v>281</v>
       </c>
       <c r="D30" s="114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="25.5">
       <c r="A31" s="114" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1172</v>
+        <v>479</v>
       </c>
       <c r="C31" s="114" t="s">
-        <v>421</v>
+        <v>281</v>
       </c>
       <c r="D31" s="114">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="114">
         <f t="shared" ca="1" si="0"/>
@@ -17550,80 +17609,80 @@
       </c>
       <c r="F31" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>1.5</v>
       </c>
       <c r="G31" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>1039</v>
+        <v>95</v>
       </c>
       <c r="C32" s="114" t="s">
-        <v>421</v>
+        <v>281</v>
       </c>
       <c r="D32" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G32" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="25.5">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B33" s="115" t="s">
-        <v>95</v>
+        <v>1173</v>
       </c>
       <c r="C33" s="114" t="s">
         <v>421</v>
       </c>
       <c r="D33" s="114">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E33" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G33" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="B34" s="115" t="s">
-        <v>280</v>
+        <v>1040</v>
       </c>
       <c r="C34" s="114" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D34" s="114">
         <v>0.2</v>
@@ -17640,43 +17699,43 @@
         <v>673</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="25.5">
       <c r="A35" s="114" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>1223</v>
+        <v>95</v>
       </c>
       <c r="C35" s="114" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D35" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G35" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>1220</v>
+        <v>280</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>432</v>
@@ -17696,15 +17755,15 @@
         <v>673</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="25.5">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="114" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>479</v>
+        <v>1224</v>
       </c>
       <c r="C37" s="114" t="s">
         <v>432</v>
@@ -17714,81 +17773,81 @@
       </c>
       <c r="E37" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="G37" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="38.25">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="114" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>424</v>
+        <v>1221</v>
       </c>
       <c r="C38" s="114" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="D38" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E38" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G38" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="25.5">
       <c r="A39" s="114" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>537</v>
+        <v>479</v>
       </c>
       <c r="C39" s="114" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="D39" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E39" s="114">
-        <f t="shared" ref="E39:E68" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$60"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$60"),0)),"?")</f>
+        <f t="shared" ref="E39:E70" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$60"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$60"),0)),"?")</f>
         <v>3</v>
       </c>
       <c r="F39" s="114">
         <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
-        <v>0.99</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G39" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="38.25">
       <c r="A40" s="114" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>1009</v>
+        <v>424</v>
       </c>
       <c r="C40" s="114" t="s">
         <v>296</v>
@@ -17798,87 +17857,87 @@
       </c>
       <c r="E40" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="G40" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B41" s="115" t="s">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="C41" s="114" t="s">
         <v>296</v>
       </c>
       <c r="D41" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E41" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>0.99</v>
       </c>
       <c r="G41" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="38.25">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="114" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B42" s="115" t="s">
-        <v>93</v>
+        <v>1010</v>
       </c>
       <c r="C42" s="114" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="D42" s="114">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E42" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="G42" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>1039</v>
+        <v>486</v>
       </c>
       <c r="C43" s="114" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="D43" s="114">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E43" s="114">
         <f t="shared" ca="1" si="2"/>
@@ -17886,83 +17945,83 @@
       </c>
       <c r="F43" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G43" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="38.25">
       <c r="A44" s="114" t="s">
         <v>1273</v>
       </c>
       <c r="B44" s="115" t="s">
-        <v>431</v>
+        <v>93</v>
       </c>
       <c r="C44" s="114" t="s">
         <v>327</v>
       </c>
       <c r="D44" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F44" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G44" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="51">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="114" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="B45" s="115" t="s">
-        <v>573</v>
+        <v>1040</v>
       </c>
       <c r="C45" s="114" t="s">
         <v>327</v>
       </c>
       <c r="D45" s="114">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E45" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G45" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="25.5">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="114" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B46" s="115" t="s">
-        <v>498</v>
+        <v>431</v>
       </c>
       <c r="C46" s="114" t="s">
         <v>327</v>
       </c>
       <c r="D46" s="114">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E46" s="114">
         <f t="shared" ca="1" si="2"/>
@@ -17970,77 +18029,77 @@
       </c>
       <c r="F46" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G46" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="51">
       <c r="A47" s="114" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B47" s="115" t="s">
-        <v>93</v>
+        <v>573</v>
       </c>
       <c r="C47" s="114" t="s">
-        <v>389</v>
+        <v>327</v>
       </c>
       <c r="D47" s="114">
         <v>0.5</v>
       </c>
       <c r="E47" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F47" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G47" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H47" s="115" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="25.5">
       <c r="A48" s="114" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="B48" s="115" t="s">
-        <v>95</v>
+        <v>498</v>
       </c>
       <c r="C48" s="114" t="s">
-        <v>389</v>
+        <v>327</v>
       </c>
       <c r="D48" s="114">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E48" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G48" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>1161</v>
+        <v>93</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>389</v>
@@ -18050,53 +18109,53 @@
       </c>
       <c r="E49" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F49" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G49" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1310</v>
+        <v>695</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B50" s="115" t="s">
-        <v>388</v>
+        <v>95</v>
       </c>
       <c r="C50" s="114" t="s">
         <v>389</v>
       </c>
       <c r="D50" s="114">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E50" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>0.5</v>
       </c>
       <c r="G50" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H50" s="115" t="s">
-        <v>696</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B51" s="115" t="s">
-        <v>573</v>
+        <v>1162</v>
       </c>
       <c r="C51" s="114" t="s">
         <v>389</v>
@@ -18106,171 +18165,171 @@
       </c>
       <c r="E51" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G51" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="38.25">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="114" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B52" s="115" t="s">
-        <v>570</v>
+        <v>388</v>
       </c>
       <c r="C52" s="114" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D52" s="114">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E52" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>1.32</v>
       </c>
       <c r="G52" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="38.25">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B53" s="115" t="s">
-        <v>95</v>
+        <v>573</v>
       </c>
       <c r="C53" s="114" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D53" s="114">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E53" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.33</v>
+        <v>1.5</v>
       </c>
       <c r="G53" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="25.5">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="38.25">
       <c r="A54" s="114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1161</v>
+        <v>570</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>398</v>
       </c>
       <c r="D54" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E54" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.66</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G54" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="51">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="38.25">
       <c r="A55" s="114" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>1167</v>
+        <v>95</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>398</v>
       </c>
       <c r="D55" s="114">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E55" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="G55" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="38.25">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="25.5">
       <c r="A56" s="114" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B56" s="115" t="s">
-        <v>93</v>
+        <v>1162</v>
       </c>
       <c r="C56" s="114" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D56" s="114">
         <v>0.33</v>
       </c>
       <c r="E56" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F56" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="G56" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="25.5">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="51">
       <c r="A57" s="114" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B57" s="115" t="s">
-        <v>388</v>
+        <v>1168</v>
       </c>
       <c r="C57" s="114" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D57" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E57" s="114">
         <f t="shared" ca="1" si="2"/>
@@ -18278,21 +18337,21 @@
       </c>
       <c r="F57" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>0.8</v>
       </c>
       <c r="G57" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="25.5">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="38.25">
       <c r="A58" s="114" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1167</v>
+        <v>93</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>402</v>
@@ -18302,81 +18361,81 @@
       </c>
       <c r="E58" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G58" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="25.5">
       <c r="A59" s="114" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B59" s="115" t="s">
-        <v>495</v>
+        <v>388</v>
       </c>
       <c r="C59" s="114" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D59" s="114">
         <v>0.33</v>
       </c>
       <c r="E59" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="G59" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H59" s="115" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="25.5">
       <c r="A60" s="114" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="B60" s="115" t="s">
-        <v>605</v>
+        <v>1168</v>
       </c>
       <c r="C60" s="114" t="s">
-        <v>309</v>
+        <v>402</v>
       </c>
       <c r="D60" s="114">
         <v>0.33</v>
       </c>
       <c r="E60" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="G60" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H60" s="115" t="s">
-        <v>676</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="114" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1237</v>
+        <v>495</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>309</v>
@@ -18396,81 +18455,81 @@
         <v>673</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="38.25">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="114" t="s">
-        <v>1266</v>
+        <v>1284</v>
       </c>
       <c r="B62" s="115" t="s">
-        <v>97</v>
+        <v>605</v>
       </c>
       <c r="C62" s="114" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D62" s="114">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E62" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F62" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G62" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="25.5">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="114" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B63" s="115" t="s">
-        <v>441</v>
+        <v>1240</v>
       </c>
       <c r="C63" s="114" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D63" s="114">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E63" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G63" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="25.5">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="38.25">
       <c r="A64" s="114" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B64" s="115" t="s">
-        <v>531</v>
+        <v>97</v>
       </c>
       <c r="C64" s="114" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D64" s="114">
         <v>0</v>
       </c>
       <c r="E64" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -18480,53 +18539,53 @@
         <v>673</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="25.5">
       <c r="A65" s="114" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="B65" s="115" t="s">
-        <v>600</v>
+        <v>441</v>
       </c>
       <c r="C65" s="114" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D65" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E65" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G65" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="25.5">
       <c r="A66" s="114" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B66" s="115" t="s">
-        <v>93</v>
+        <v>531</v>
       </c>
       <c r="C66" s="114" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="D66" s="114">
         <v>0</v>
       </c>
       <c r="E66" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F66" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -18536,53 +18595,53 @@
         <v>673</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="114" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B67" s="115" t="s">
-        <v>502</v>
+        <v>600</v>
       </c>
       <c r="C67" s="114" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="D67" s="114">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E67" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F67" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G67" s="114" t="s">
         <v>673</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="25.5">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="114" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>1122</v>
+        <v>93</v>
       </c>
       <c r="C68" s="114" t="s">
-        <v>939</v>
+        <v>313</v>
       </c>
       <c r="D68" s="114">
         <v>0</v>
       </c>
       <c r="E68" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F68" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -18592,7 +18651,63 @@
         <v>673</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1326</v>
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="114" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B69" s="115" t="s">
+        <v>502</v>
+      </c>
+      <c r="C69" s="114" t="s">
+        <v>322</v>
+      </c>
+      <c r="D69" s="114">
+        <v>0</v>
+      </c>
+      <c r="E69" s="114">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F69" s="114">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G69" s="114" t="s">
+        <v>673</v>
+      </c>
+      <c r="H69" s="115" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="25.5">
+      <c r="A70" s="114" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B70" s="115" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C70" s="114" t="s">
+        <v>939</v>
+      </c>
+      <c r="D70" s="114">
+        <v>0</v>
+      </c>
+      <c r="E70" s="114">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F70" s="114">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="114" t="s">
+        <v>673</v>
+      </c>
+      <c r="H70" s="115" t="s">
+        <v>1331</v>
       </c>
     </row>
   </sheetData>
@@ -18617,12 +18732,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18651,29 +18766,29 @@
       </c>
       <c r="B5" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A5)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A5)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A5)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A5)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A5)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A5)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A5),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A5),0.5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="114">
         <f t="shared" ref="D5:D25" ca="1" si="0">B5+C5</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" s="114" t="str">
         <f t="shared" ref="E5:E25" ca="1" si="1">IF(D5&gt;20,"과다 점검",IF(D5&gt;=10,"충분",IF(D5&gt;=8,"하한",IF(D5&gt;=1,"보완 필요","미배치"))))</f>
-        <v>보완 필요</v>
+        <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>752</v>
       </c>
       <c r="I5" s="125">
         <f ca="1">SUM(D5:D6)</f>
-        <v>22.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1">
@@ -18685,7 +18800,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A6),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A6),0.5)</f>
         <v>0.5</v>
       </c>
       <c r="D6" s="114">
@@ -18697,7 +18812,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -18709,7 +18824,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A7),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A7),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D7" s="114">
@@ -18721,10 +18836,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -18740,7 +18855,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A8),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A8),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D8" s="114">
@@ -18752,10 +18867,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="H8" s="124" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="I8" s="125">
         <f>SUM(복귀_일_수평당기기!E11:E14,복귀_목_수직당기기!E11:E13)</f>
@@ -18771,7 +18886,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A9),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A9),0.5)</f>
         <v>3</v>
       </c>
       <c r="D9" s="114">
@@ -18783,7 +18898,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -18795,7 +18910,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A10),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A10),0.5)</f>
         <v>5.5</v>
       </c>
       <c r="D10" s="114">
@@ -18807,7 +18922,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -18819,7 +18934,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A11),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A11),0.5)</f>
         <v>3</v>
       </c>
       <c r="D11" s="114">
@@ -18831,7 +18946,7 @@
         <v>충분</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -18843,19 +18958,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A12),0.5)</f>
-        <v>5</v>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A12),0.5)</f>
+        <v>6.5</v>
       </c>
       <c r="D12" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="E12" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -18867,7 +18982,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A13),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A13),0.5)</f>
         <v>2</v>
       </c>
       <c r="D13" s="114">
@@ -18879,7 +18994,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -18891,7 +19006,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A14),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A14),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D14" s="114">
@@ -18903,7 +19018,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -18915,7 +19030,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A15),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A15),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D15" s="114">
@@ -18927,10 +19042,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -18946,7 +19061,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A16),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A16),0.5)</f>
         <v>2.5</v>
       </c>
       <c r="D16" s="114">
@@ -18958,7 +19073,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -18970,7 +19085,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A17),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A17),0.5)</f>
         <v>7</v>
       </c>
       <c r="D17" s="114">
@@ -18982,7 +19097,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -18994,7 +19109,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="114">
-        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A18),0.5)</f>
+        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A18),0.5)</f>
         <v>0</v>
       </c>
       <c r="D18" s="114">
@@ -19006,7 +19121,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -19018,7 +19133,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A19),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A19),0.5)</f>
         <v>0</v>
       </c>
       <c r="D19" s="114">
@@ -19030,7 +19145,7 @@
         <v>충분</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -19042,7 +19157,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A20),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A20),0.5)</f>
         <v>8</v>
       </c>
       <c r="D20" s="114">
@@ -19054,7 +19169,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -19066,19 +19181,19 @@
         <v>9</v>
       </c>
       <c r="C21" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A21),0.5)</f>
-        <v>7</v>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A21),0.5)</f>
+        <v>8.5</v>
       </c>
       <c r="D21" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="E21" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -19090,7 +19205,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A22),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A22),0.5)</f>
         <v>3</v>
       </c>
       <c r="D22" s="114">
@@ -19102,7 +19217,7 @@
         <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -19114,7 +19229,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A23),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A23),0.5)</f>
         <v>0</v>
       </c>
       <c r="D23" s="114">
@@ -19126,7 +19241,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -19138,7 +19253,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A24),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A24),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D24" s="114">
@@ -19150,7 +19265,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -19162,7 +19277,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$70,복귀_간접계수맵!$C$7:$C$70,$A25),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A25),0.5)</f>
         <v>0</v>
       </c>
       <c r="D25" s="114">
@@ -19174,7 +19289,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -19183,11 +19298,11 @@
       </c>
       <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -19197,192 +19312,192 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="107" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="123" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0C25657BE93238B977D730997BA8BB147CE377DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8E3F657BE93238B977D730997BA8BB14DC6B1CFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8E3F657BE93238B977D730997BA8BB14DC6B1CFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_8E3F657BE93238B977D730997BA8BB14DC6B1CFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA870588-3AAE-48BF-AC2C-A9BCFC049B84}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -8628,7 +8628,7 @@
         <v>4</v>
       </c>
       <c r="F71">
-        <f t="shared" ref="F71:F102" ca="1" si="4">IF(ISNUMBER(E71),$D71*E71,0)</f>
+        <f t="shared" ref="F71:F75" ca="1" si="4">IF(ISNUMBER(E71),$D71*E71,0)</f>
         <v>2</v>
       </c>
       <c r="G71" t="s">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E8" s="121">
         <f>복귀_월_가슴!$E$24</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="114" t="s">
         <v>927</v>
@@ -11411,7 +11411,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F13" s="116" t="s">
         <v>946</v>
@@ -13167,20 +13167,20 @@
         <v>35</v>
       </c>
       <c r="E18" s="112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="112">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="112">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H18" s="112">
         <v>180</v>
       </c>
       <c r="I18" s="112">
         <f t="shared" ref="I18:I23" si="0">IF(E18=0,0,ROUND((E18*(G18+H18)+N18)/60,1))</f>
-        <v>17.5</v>
+        <v>15.3</v>
       </c>
       <c r="J18" s="113" t="s">
         <v>1084</v>
@@ -13400,14 +13400,14 @@
       </c>
       <c r="E24" s="116">
         <f>SUM(E18:E23)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" s="116"/>
       <c r="G24" s="116"/>
       <c r="H24" s="116"/>
       <c r="I24" s="116">
         <f>ROUND(SUM(I18:I23),0)</f>
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -16117,7 +16117,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="114" t="s">
         <v>303</v>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="I18" s="114">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J18" s="115" t="s">
         <v>1235</v>
@@ -16318,7 +16318,7 @@
         <v>297</v>
       </c>
       <c r="E23" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="114" t="s">
         <v>303</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="I23" s="114">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="J23" s="115" t="s">
         <v>1244</v>
@@ -16359,7 +16359,7 @@
       <c r="H24" s="116"/>
       <c r="I24" s="116">
         <f>ROUND(SUM(I11:I23),0)</f>
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -16933,11 +16933,11 @@
       </c>
       <c r="E7" s="114">
         <f t="shared" ref="E7:E38" ca="1" si="0">IFERROR(INDEX(INDIRECT("'"&amp;$A7&amp;"'!$E$1:$E$60"),MATCH($B7,INDIRECT("'"&amp;$A7&amp;"'!$B$1:$B$60"),0)),"?")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="114">
         <f t="shared" ref="F7:F38" ca="1" si="1">IF(ISNUMBER(E7),$D7*E7,0)</f>
-        <v>1.6500000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="G7" s="114" t="s">
         <v>673</v>
@@ -17269,11 +17269,11 @@
       </c>
       <c r="E19" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.6500000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="G19" s="114" t="s">
         <v>673</v>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="E64" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F64" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="I5" s="125">
         <f ca="1">SUM(D5:D6)</f>
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="B6" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A6)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A6)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A6)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A6)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A6)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A6)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A6),0.5)</f>
@@ -18805,7 +18805,7 @@
       </c>
       <c r="D6" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="E6" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18931,7 +18931,7 @@
       </c>
       <c r="B11" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A11)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A11)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A11)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A11)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A11)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A11)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A11),0.5)</f>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="D11" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19298,11 +19298,11 @@
       </c>
       <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:6">

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14469D63-8BAF-4686-B148-81A2CFA64C57}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2134022A-0FAA-4591-8677-26E5337CC2BB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2706" uniqueCount="1415">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -3326,9 +3326,6 @@
   </si>
   <si>
     <t>리닝 케이블 레터럴 / 머신 레터럴</t>
-  </si>
-  <si>
-    <t>리버스 펙덱 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
   </si>
   <si>
     <t>[어깨 전면이 이 날에 없는 이유]</t>
@@ -4249,10 +4246,6 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 월요일 가슴 · 월요일 다시 어깨를 세트 후반부에  /  벤치만 4x8이야 (사용자 엑셀 조정 · 램프 · 시작중량_설정까지 맞췄다)  /  [2026-10-04] 측면 MAV 하단까지 · 나 월요일에하는 후면운동도 원암으로 진행하고 싶어. 뭔가 집중이 더 잘 되더라고</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>측면 삼각은 간접 자극이 2.0세트뿐이라 직접 세트로만 채워진다. 토 4 · 월 7(원암 4 · 머신 3) · 수 3으로 나눠 주 14세트 · 실질 16 (2026-10-04 MAV 하단).</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -4265,770 +4258,83 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>직접 10세트: 토요일 리버스 펙덱 4 · 월요일 원암 케이블 리버스 플라이 3(2026-10-04 사용자 지정 편측) · 수요일 벤트오버 레터럴 머신 3. 간접 1.5 — 목요일 페이스풀 0.5×3(2026-10-02). 로우 계열은 전부 승모 중부 · 능형근으로 계상했다. 머신 · 케이블 · 로프로 저항곡선과 외회전 요소를 갈랐다. [2026-10-04] 16에 못 미치지만 두었다 — RP 표가 후면 MV를 0으로 두는 것은 등 운동 간접 때문이고, 일요일 넓은 그립 로우 7세트를 후면 0.33으로만 쳐도 약 14다. 4~6주 뒤 뒤쪽 어깨가 눈에 띄게 늦을 때만 월요일 3 → 4</t>
+    <t>삼각근(후면)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 삼각근 측면 16.0 · 후면 11.5 — 셋으로 나눠 주 3회. 2026-10-04에 측면만 직접 10 → 14(월요일 +4)로 MAV 하단에 올렸다. 후면을 안 올린 이유는 F14에 있다.</t>
+    <t>5~7</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>209세트</t>
+    <t>리버스 펙덱 / 리어 델트 로우 (로프) / 페이스풀 (로프)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 여섯(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 페이스풀 · 전완 슈퍼세트 주 3회 · 백 익스텐션 주 2회) · 2026-10-04 월요일 측면 +4</t>
+    <t>리버스 펙덱</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>약 60분</t>
+    <t>[2026-10-04 사용자 요청] 후면 마무리 2세트. 토요일과 같은 머신 · 같은 동작이다 — 팔을 편 채 수평 외전만. 앞에 원암 리버스 플라이 3세트가 있어 토요일보다 덜 나오는 것이 정상이다. 어깨 블록은 측 → 후 → 측 → 후로 교대한다(사용자 지정) — 같은 머리를 연달아 치지 않아 종목 사이가 서로의 휴식이 된다.</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>약 484분 (8시간 4분)</t>
+    <t>케이블 리버스 플라이 / 리어 델트 로우 (로프)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>⑪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> [2026-10-04] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>월요일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>측면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> +4 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>원암</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>케이블</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>레터럴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>머신</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>레터럴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>신설</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>마지막</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>세트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>드롭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>측면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>직접</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>실질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 16(MAV </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>하단</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>날</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>케이블</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>리버스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>플라이를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>원암으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>바꿨다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>사용자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>지정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>편측이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>집중이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>잘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>된다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. 205 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 209</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>세트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>월요일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>세트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>분</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>· 목 44세트 99분 · 수 42세트 104분 · 토 41세트 101분 · 일 32세트 74분 · 화 27세트 46분 · 월 23세트 60분.</t>
+    <t>[요청 원문 2026-10-02] 월요일 가슴 · 월요일 다시 어깨를 세트 후반부에  /  벤치만 4x8이야 (사용자 엑셀 조정 · 램프 · 시작중량_설정까지 맞췄다)  /  [2026-10-04] 측면 MAV 하단까지 · 나 월요일에하는 후면운동도 원암으로 진행하고 싶어. 뭔가 집중이 더 잘 되더라고  /  뒤에 백덱플라이 2세트도 넣어줘 후면으로 · 패턴을 측면, 후면, 측면, 후면으로</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 29를 빼면 실질 12, 수요일은 26을 빼면 16, 월요일은 13을 빼면 10이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
+    <t>복귀_월_가슴</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 주 484분 = 8시간 4분. 주 4회 370분에서 105분 늘었다. 수(104) · 토(101)가 100분을 넘지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <t>견갑 후인 부분 협력 — 토요일 리버스 펙덱과 같은 종목 · 같은 계수 (2026-10-04 월요일 2세트 신설)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 23세트 · 약 60분. 여섯 날 중 가장 작다 — 가슴 하나만 맡고 어깨가 측면 7 · 후면 3이다. 2026-10-04에 측면 +4(원암 레터럴 3 → 4 · 머신 레터럴 3)를 이 날에 넣은 것도 가장 작은 날이어서다.</t>
+    <t>직접 12세트: 토요일 리버스 펙덱 4 · 월요일 원암 케이블 리버스 플라이 3 · 리버스 펙덱 2 · 수요일 벤트오버 레터럴 머신 3. 간접 1.5 — 목요일 페이스풀 0.5×3. 로우 계열은 전부 승모 중부 · 능형근으로 계상했다(일요일 넓은 그립 로우 7세트를 후면 0.33으로 치면 +2.3). [2026-10-04] 월요일 리버스 플라이를 원암으로(사용자 지정 — 집중이 더 잘 된다) · 같은 날 리버스 펙덱 2를 더했다(사용자 요청) — 10 → 12. 월요일 어깨 블록은 측 → 후 → 측 → 후로 교대한다</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 삼각근 측면 16.0 · 후면 13.5 — 셋으로 나눠 주 3회. 2026-10-04에 둘 다 월요일에서 올렸다 — 측면 직접 10 → 14(MAV 하단) · 후면 10 → 12. 월요일 어깨 블록은 측 → 후 → 측 → 후 교대.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>211세트</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>주 4회 140에서 올렸다. 유지선은 75. 현장 일 보정이 사라진 자리들 + 2026-10-02 사용자 추가 여섯(원 레그 컬 · 발 높은 레그 프레스 · 수요일 이너/아우터 · 페이스풀 · 전완 슈퍼세트 주 3회 · 백 익스텐션 주 2회) · 2026-10-04 월요일 측면 +4 · 후면 +2</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 63분</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 487분 (8시간 7분)</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· ⑪ [2026-10-04] 월요일 측면 +4 — 원암 케이블 레터럴 3 → 4 · 머신 레터럴 3 신설(마지막 세트 드롭). 측면 직접 10 → 14 · 실질 12 → 16(MAV 하단). 같은 날 케이블 리버스 플라이를 원암으로 바꿨다 — 사용자 지정, 편측이 집중이 더 잘 된다. 이어서 사용자 요청으로 리버스 펙덱 2(후면)를 더하고 월요일 어깨를 측 → 후 → 측 → 후로 교대 배열했다 — 후면 직접 10 → 12 · 실질 11.5 → 13.5. 205 → 211세트 · 월요일 25세트 63분.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 목 44세트 99분 · 수 42세트 104분 · 토 41세트 101분 · 일 32세트 74분 · 화 27세트 46분 · 월 25세트 63분.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 29를 빼면 실질 12, 수요일은 26을 빼면 16, 월요일은 15를 빼면 10이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 주 487분 = 8시간 7분. 주 4회 370분에서 105분 늘었다. 수(104) · 토(101)가 100분을 넘지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 25세트 · 약 63분. 여섯 날 중 가장 작다 — 가슴 하나만 맡고 어깨가 측면 7 · 후면 5이다. 2026-10-04에 어깨 6 → 12(측면 +4 · 후면 +2)를 이 날에 넣은 것도 가장 작은 날이어서다. 어깨 블록은 측 → 후 → 측 → 후로 교대한다(사용자 지정).</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
@@ -5040,7 +4346,7 @@
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="57">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5414,13 +4720,6 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5855,6 +5154,7 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5866,7 +5166,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -7564,16 +6863,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="128" t="s">
+      <c r="A2" s="129" t="s">
         <v>647</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
@@ -7585,16 +6884,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="127" t="s">
         <v>649</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
@@ -9684,7 +8983,7 @@
       <c r="F5" s="53" t="s">
         <v>750</v>
       </c>
-      <c r="G5" s="129" t="s">
+      <c r="G5" s="130" t="s">
         <v>751</v>
       </c>
       <c r="H5" s="56">
@@ -9727,7 +9026,7 @@
       <c r="F6" s="53" t="s">
         <v>752</v>
       </c>
-      <c r="G6" s="130"/>
+      <c r="G6" s="131"/>
       <c r="J6" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>12.6</v>
@@ -9760,7 +9059,7 @@
       <c r="F7" s="53" t="s">
         <v>753</v>
       </c>
-      <c r="G7" s="129" t="s">
+      <c r="G7" s="130" t="s">
         <v>754</v>
       </c>
       <c r="H7" s="56">
@@ -9799,7 +9098,7 @@
       <c r="F8" s="53" t="s">
         <v>755</v>
       </c>
-      <c r="G8" s="130"/>
+      <c r="G8" s="131"/>
       <c r="J8" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>3.9</v>
@@ -9832,7 +9131,7 @@
       <c r="F9" s="53" t="s">
         <v>756</v>
       </c>
-      <c r="G9" s="130"/>
+      <c r="G9" s="131"/>
       <c r="J9" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.5</v>
@@ -9865,7 +9164,7 @@
       <c r="F10" s="53" t="s">
         <v>757</v>
       </c>
-      <c r="G10" s="130"/>
+      <c r="G10" s="131"/>
       <c r="J10" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>14.4</v>
@@ -10103,7 +9402,7 @@
       <c r="F17" s="53" t="s">
         <v>764</v>
       </c>
-      <c r="G17" s="129" t="s">
+      <c r="G17" s="130" t="s">
         <v>388</v>
       </c>
       <c r="H17" s="56">
@@ -10142,7 +9441,7 @@
       <c r="F18" s="53" t="s">
         <v>765</v>
       </c>
-      <c r="G18" s="130"/>
+      <c r="G18" s="131"/>
       <c r="J18" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.1</v>
@@ -12101,11 +11400,11 @@
         <v>925</v>
       </c>
       <c r="E8" s="121">
-        <f>복귀_월_가슴!$E$25</f>
-        <v>23</v>
+        <f>복귀_월_가슴!$E$26</f>
+        <v>25</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="G8" s="115" t="s">
         <v>926</v>
@@ -12215,10 +11514,10 @@
       <c r="D13" s="122"/>
       <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F13" s="116" t="s">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="G13" s="119"/>
     </row>
@@ -12358,8 +11657,8 @@
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="131" t="s">
-        <v>1403</v>
+      <c r="A43" s="126" t="s">
+        <v>1410</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -12424,12 +11723,12 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -12444,7 +11743,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -12849,7 +12148,7 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="K24" s="115" t="s">
         <v>1003</v>
@@ -12890,7 +12189,7 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="K25" s="115" t="s">
         <v>1005</v>
@@ -13803,7 +13102,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -14157,7 +13456,7 @@
         <v>8</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="K22" s="115" t="s">
         <v>1089</v>
@@ -14171,173 +13470,212 @@
         <v>6</v>
       </c>
       <c r="B23" s="115" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="C23" s="114" t="s">
-        <v>1383</v>
+        <v>1395</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1384</v>
+        <v>1396</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="G23" s="114">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H23" s="114">
         <v>60</v>
       </c>
       <c r="I23" s="114">
-        <f t="shared" ref="I23" si="1">IF(E23=0,0,ROUND((E23*(G23+H23)+N23)/60,1))</f>
+        <f>IF(E23=0,0,ROUND((E23*(G23+H23)+N23)/60,1))</f>
         <v>6</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
-      <c r="N23" s="114">
-        <v>60</v>
-      </c>
+      <c r="N23" s="114"/>
     </row>
     <row r="24" spans="1:14" ht="30" customHeight="1">
       <c r="A24" s="114">
         <v>7</v>
       </c>
       <c r="B24" s="115" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>371</v>
+        <v>1382</v>
       </c>
       <c r="D24" s="114" t="s">
-        <v>1088</v>
+        <v>1383</v>
       </c>
       <c r="E24" s="114">
         <v>3</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="G24" s="114">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H24" s="114">
         <v>60</v>
       </c>
       <c r="I24" s="114">
-        <f t="shared" si="0"/>
+        <f>IF(E24=0,0,ROUND((E24*(G24+H24)+N24)/60,1))</f>
         <v>6</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1090</v>
+        <v>1386</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
-      <c r="N24" s="114"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="116"/>
-      <c r="B25" s="116"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116" t="s">
+      <c r="N24" s="114">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30" customHeight="1">
+      <c r="A25" s="114">
+        <v>8</v>
+      </c>
+      <c r="B25" s="115" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C25" s="114" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D25" s="114">
+        <v>30</v>
+      </c>
+      <c r="E25" s="114">
+        <v>2</v>
+      </c>
+      <c r="F25" s="114" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G25" s="114">
+        <v>40</v>
+      </c>
+      <c r="H25" s="114">
+        <v>60</v>
+      </c>
+      <c r="I25" s="114">
+        <f>IF(E25=0,0,ROUND((E25*(G25+H25)+N25)/60,1))</f>
+        <v>3.3</v>
+      </c>
+      <c r="J25" s="115" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K25" s="115" t="s">
+        <v>1400</v>
+      </c>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="116"/>
+      <c r="B26" s="116"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116" t="s">
         <v>334</v>
       </c>
-      <c r="E25" s="116">
-        <f>SUM(E18:E24)</f>
-        <v>23</v>
-      </c>
-      <c r="F25" s="116"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="116"/>
-      <c r="I25" s="116">
-        <f>ROUND(SUM(I18:I24),0)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="107" t="s">
-        <v>1091</v>
+      <c r="E26" s="116">
+        <f>SUM(E18:E25)</f>
+        <v>25</v>
+      </c>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116">
+        <f>ROUND(SUM(I18:I25),0)</f>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="117" t="s">
-        <v>1015</v>
+      <c r="A28" s="107" t="s">
+        <v>1090</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1092</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="117" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="107" t="s">
         <v>1094</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="107" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="117" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="117" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="107" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="117" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="107" t="s">
         <v>982</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="117" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="107" t="s">
-        <v>1391</v>
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="117" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="117" t="s">
-        <v>1392</v>
+      <c r="A42" s="107" t="s">
+        <v>1390</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="C45" s="118" t="s">
-        <v>1393</v>
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="117" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="C46" s="118" t="s">
+        <v>1401</v>
       </c>
     </row>
   </sheetData>
@@ -14368,7 +13706,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -14378,12 +13716,12 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -14470,10 +13808,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K11" s="115" t="s">
         <v>1103</v>
-      </c>
-      <c r="K11" s="115" t="s">
-        <v>1104</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -14511,10 +13849,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K12" s="115" t="s">
         <v>1105</v>
-      </c>
-      <c r="K12" s="115" t="s">
-        <v>1106</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -14550,10 +13888,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K13" s="115" t="s">
         <v>1107</v>
-      </c>
-      <c r="K13" s="115" t="s">
-        <v>1108</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -14589,7 +13927,7 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="K14" s="115" t="s">
         <v>1052</v>
@@ -14630,7 +13968,7 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="K15" s="115" t="s">
         <v>1054</v>
@@ -14646,7 +13984,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>937</v>
@@ -14671,10 +14009,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
+        <v>1111</v>
+      </c>
+      <c r="K16" s="115" t="s">
         <v>1112</v>
-      </c>
-      <c r="K16" s="115" t="s">
-        <v>1113</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -14685,7 +14023,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>937</v>
@@ -14710,10 +14048,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K17" s="115" t="s">
         <v>1115</v>
-      </c>
-      <c r="K17" s="115" t="s">
-        <v>1116</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -14749,10 +14087,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K18" s="115" t="s">
         <v>1117</v>
-      </c>
-      <c r="K18" s="115" t="s">
-        <v>1118</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -14788,10 +14126,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K19" s="115" t="s">
         <v>1119</v>
-      </c>
-      <c r="K19" s="115" t="s">
-        <v>1120</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -14818,52 +14156,52 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -14873,37 +14211,37 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="107" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -14913,22 +14251,22 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -14938,7 +14276,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
   </sheetData>
@@ -15650,7 +14988,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -15731,7 +15069,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -15807,12 +15145,12 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -15822,7 +15160,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -15910,10 +15248,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K28" s="113" t="s">
         <v>1148</v>
-      </c>
-      <c r="K28" s="113" t="s">
-        <v>1149</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -15924,7 +15262,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>326</v>
@@ -15950,10 +15288,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K29" s="115" t="s">
         <v>1151</v>
-      </c>
-      <c r="K29" s="115" t="s">
-        <v>1152</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -15970,7 +15308,7 @@
         <v>397</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -15989,10 +15327,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K30" s="115" t="s">
         <v>1154</v>
-      </c>
-      <c r="K30" s="115" t="s">
-        <v>1155</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -16003,7 +15341,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>388</v>
@@ -16028,10 +15366,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K31" s="115" t="s">
         <v>1157</v>
-      </c>
-      <c r="K31" s="115" t="s">
-        <v>1158</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -16067,10 +15405,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K32" s="115" t="s">
         <v>1159</v>
-      </c>
-      <c r="K32" s="115" t="s">
-        <v>1160</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -16081,7 +15419,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>442</v>
@@ -16107,10 +15445,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K33" s="113" t="s">
         <v>1162</v>
-      </c>
-      <c r="K33" s="113" t="s">
-        <v>1163</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>520</v>
@@ -16148,7 +15486,7 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K34" s="115" t="s">
         <v>1003</v>
@@ -16189,10 +15527,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
+        <v>1164</v>
+      </c>
+      <c r="K35" s="115" t="s">
         <v>1165</v>
-      </c>
-      <c r="K35" s="115" t="s">
-        <v>1166</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -16228,10 +15566,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K36" s="115" t="s">
         <v>1167</v>
-      </c>
-      <c r="K36" s="115" t="s">
-        <v>1168</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -16267,10 +15605,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K37" s="115" t="s">
         <v>1169</v>
-      </c>
-      <c r="K37" s="115" t="s">
-        <v>1170</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -16306,7 +15644,7 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="K38" s="115" t="s">
         <v>1009</v>
@@ -16347,7 +15685,7 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K39" s="115" t="s">
         <v>1011</v>
@@ -16388,10 +15726,10 @@
         <v>11.5</v>
       </c>
       <c r="J40" s="115" t="s">
+        <v>1172</v>
+      </c>
+      <c r="K40" s="115" t="s">
         <v>1173</v>
-      </c>
-      <c r="K40" s="115" t="s">
-        <v>1174</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -16418,117 +15756,117 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -16538,12 +15876,12 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -16553,22 +15891,22 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="79" spans="1:1">
@@ -16578,7 +15916,7 @@
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
   </sheetData>
@@ -16609,7 +15947,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -16619,7 +15957,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -16711,10 +16049,10 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K11" s="115" t="s">
         <v>1207</v>
-      </c>
-      <c r="K11" s="115" t="s">
-        <v>1208</v>
       </c>
       <c r="L11" s="114" t="s">
         <v>1036</v>
@@ -16727,7 +16065,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>280</v>
@@ -16752,10 +16090,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K12" s="115" t="s">
         <v>1210</v>
-      </c>
-      <c r="K12" s="115" t="s">
-        <v>1211</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -16766,7 +16104,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>280</v>
@@ -16791,10 +16129,10 @@
         <v>11.7</v>
       </c>
       <c r="J13" s="115" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K13" s="115" t="s">
         <v>1213</v>
-      </c>
-      <c r="K13" s="115" t="s">
-        <v>1214</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -16832,10 +16170,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K14" s="115" t="s">
         <v>1215</v>
-      </c>
-      <c r="K14" s="115" t="s">
-        <v>1216</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -16871,10 +16209,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K15" s="115" t="s">
         <v>1217</v>
-      </c>
-      <c r="K15" s="115" t="s">
-        <v>1218</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -16910,10 +16248,10 @@
         <v>9.5</v>
       </c>
       <c r="J16" s="115" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K16" s="115" t="s">
         <v>1219</v>
-      </c>
-      <c r="K16" s="115" t="s">
-        <v>1220</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -16949,10 +16287,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J17" s="115" t="s">
+        <v>1220</v>
+      </c>
+      <c r="K17" s="115" t="s">
         <v>1221</v>
-      </c>
-      <c r="K17" s="115" t="s">
-        <v>1222</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -16988,10 +16326,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J18" s="115" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K18" s="115" t="s">
         <v>1223</v>
-      </c>
-      <c r="K18" s="115" t="s">
-        <v>1224</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -17004,7 +16342,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>358</v>
@@ -17029,10 +16367,10 @@
         <v>5.5</v>
       </c>
       <c r="J19" s="115" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K19" s="115" t="s">
         <v>1226</v>
-      </c>
-      <c r="K19" s="115" t="s">
-        <v>1227</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -17043,7 +16381,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>282</v>
@@ -17068,10 +16406,10 @@
         <v>5.8</v>
       </c>
       <c r="J20" s="115" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K20" s="115" t="s">
         <v>1229</v>
-      </c>
-      <c r="K20" s="115" t="s">
-        <v>1230</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -17107,7 +16445,7 @@
         <v>2.5</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="K21" s="115" t="s">
         <v>1052</v>
@@ -17189,10 +16527,10 @@
         <v>6.7</v>
       </c>
       <c r="J23" s="115" t="s">
+        <v>1231</v>
+      </c>
+      <c r="K23" s="115" t="s">
         <v>1232</v>
-      </c>
-      <c r="K23" s="115" t="s">
-        <v>1233</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -17219,52 +16557,52 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="107" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -17274,17 +16612,17 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -17294,27 +16632,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -17324,7 +16662,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
   </sheetData>
@@ -17404,10 +16742,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>1399</v>
+        <v>1406</v>
       </c>
       <c r="D7" s="115" t="s">
-        <v>1400</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
@@ -17711,7 +17049,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -17725,12 +17063,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -17738,18 +17076,18 @@
         <v>648</v>
       </c>
       <c r="F3" s="107">
-        <f ca="1">COUNTIF($E$7:$E$90,"?")</f>
+        <f ca="1">COUNTIF($E$7:$E$91,"?")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>651</v>
@@ -17775,7 +17113,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>95</v>
@@ -17798,12 +17136,12 @@
         <v>672</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>530</v>
@@ -17826,12 +17164,12 @@
         <v>672</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>356</v>
@@ -17854,12 +17192,12 @@
         <v>672</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>521</v>
@@ -17882,15 +17220,15 @@
         <v>672</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>358</v>
@@ -17910,12 +17248,12 @@
         <v>672</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>279</v>
@@ -17938,15 +17276,15 @@
         <v>672</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>282</v>
@@ -17966,15 +17304,15 @@
         <v>672</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>282</v>
@@ -17994,12 +17332,12 @@
         <v>672</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>485</v>
@@ -18022,12 +17360,12 @@
         <v>672</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25.5">
       <c r="A16" s="114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B16" s="115" t="s">
         <v>1033</v>
@@ -18050,12 +17388,12 @@
         <v>672</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="38.25">
       <c r="A17" s="114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>478</v>
@@ -18078,12 +17416,12 @@
         <v>672</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5">
       <c r="A18" s="114" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>452</v>
@@ -18106,12 +17444,12 @@
         <v>672</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>95</v>
@@ -18134,12 +17472,12 @@
         <v>672</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>530</v>
@@ -18162,12 +17500,12 @@
         <v>672</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>356</v>
@@ -18190,12 +17528,12 @@
         <v>672</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>599</v>
@@ -18218,12 +17556,12 @@
         <v>672</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>440</v>
@@ -18246,12 +17584,12 @@
         <v>672</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5">
       <c r="A24" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>435</v>
@@ -18274,12 +17612,12 @@
         <v>672</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5">
       <c r="A25" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B25" s="115" t="s">
         <v>435</v>
@@ -18302,12 +17640,12 @@
         <v>672</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>301</v>
@@ -18330,15 +17668,15 @@
         <v>672</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="38.25">
       <c r="A27" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C27" s="114" t="s">
         <v>367</v>
@@ -18358,12 +17696,12 @@
         <v>672</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="38.25">
       <c r="A28" s="114" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B28" s="115" t="s">
         <v>521</v>
@@ -18386,15 +17724,15 @@
         <v>672</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5">
       <c r="A29" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>382</v>
@@ -18414,12 +17752,12 @@
         <v>672</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="25.5">
       <c r="A30" s="114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B30" s="115" t="s">
         <v>1033</v>
@@ -18442,12 +17780,12 @@
         <v>672</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25.5">
       <c r="A31" s="114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B31" s="115" t="s">
         <v>478</v>
@@ -18470,12 +17808,12 @@
         <v>672</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B32" s="115" t="s">
         <v>93</v>
@@ -18498,15 +17836,15 @@
         <v>672</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B33" s="115" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C33" s="114" t="s">
         <v>420</v>
@@ -18526,12 +17864,12 @@
         <v>672</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>1033</v>
@@ -18554,12 +17892,12 @@
         <v>672</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="25.5">
       <c r="A35" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B35" s="115" t="s">
         <v>93</v>
@@ -18582,12 +17920,12 @@
         <v>672</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B36" s="115" t="s">
         <v>279</v>
@@ -18610,15 +17948,15 @@
         <v>672</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C37" s="114" t="s">
         <v>431</v>
@@ -18638,15 +17976,15 @@
         <v>672</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="114" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C38" s="114" t="s">
         <v>431</v>
@@ -18666,12 +18004,12 @@
         <v>672</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="25.5">
       <c r="A39" s="114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B39" s="115" t="s">
         <v>478</v>
@@ -18683,26 +18021,26 @@
         <v>0.2</v>
       </c>
       <c r="E39" s="114">
-        <f t="shared" ref="E39:E70" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$60"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$60"),0)),"?")</f>
+        <f t="shared" ref="E39:E71" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$60"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$60"),0)),"?")</f>
         <v>3</v>
       </c>
       <c r="F39" s="114">
-        <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
+        <f t="shared" ref="F39:F71" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="G39" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="38.25">
       <c r="A40" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C40" s="114" t="s">
         <v>295</v>
@@ -18722,12 +18060,12 @@
         <v>672</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B41" s="115" t="s">
         <v>536</v>
@@ -18750,12 +18088,12 @@
         <v>672</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="114" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>1004</v>
@@ -18778,133 +18116,133 @@
         <v>672</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="25.5">
       <c r="A43" s="114" t="s">
-        <v>1268</v>
+        <v>1402</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>485</v>
+        <v>1004</v>
       </c>
       <c r="C43" s="114" t="s">
         <v>295</v>
       </c>
       <c r="D43" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E43" s="114">
         <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F43" s="114">
+        <f t="shared" ref="F43" ca="1" si="4">IF(ISNUMBER(E43),$D43*E43,0)</f>
+        <v>0.66</v>
+      </c>
+      <c r="G43" s="114" t="s">
+        <v>672</v>
+      </c>
+      <c r="H43" s="115" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="114" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B44" s="115" t="s">
+        <v>485</v>
+      </c>
+      <c r="C44" s="114" t="s">
+        <v>295</v>
+      </c>
+      <c r="D44" s="114">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="114">
+        <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F43" s="114">
+      <c r="F44" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>2</v>
       </c>
-      <c r="G43" s="114" t="s">
+      <c r="G44" s="114" t="s">
         <v>672</v>
       </c>
-      <c r="H43" s="115" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="38.25">
-      <c r="A44" s="114" t="s">
-        <v>1261</v>
-      </c>
-      <c r="B44" s="115" t="s">
+      <c r="H44" s="115" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="38.25">
+      <c r="A45" s="114" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B45" s="115" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="114" t="s">
+      <c r="C45" s="114" t="s">
         <v>326</v>
       </c>
-      <c r="D44" s="114">
+      <c r="D45" s="114">
         <v>0</v>
       </c>
-      <c r="E44" s="114">
+      <c r="E45" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="F44" s="114">
+      <c r="F45" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="G44" s="114" t="s">
+      <c r="G45" s="114" t="s">
         <v>672</v>
       </c>
-      <c r="H44" s="115" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="114" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B45" s="115" t="s">
+      <c r="H45" s="115" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="114" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B46" s="115" t="s">
         <v>1033</v>
       </c>
-      <c r="C45" s="114" t="s">
+      <c r="C46" s="114" t="s">
         <v>326</v>
       </c>
-      <c r="D45" s="114">
+      <c r="D46" s="114">
         <v>0.2</v>
       </c>
-      <c r="E45" s="114">
+      <c r="E46" s="114">
         <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="F45" s="114">
+      <c r="F46" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="G45" s="114" t="s">
-        <v>672</v>
-      </c>
-      <c r="H45" s="115" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="114" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B46" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="C46" s="114" t="s">
-        <v>326</v>
-      </c>
-      <c r="D46" s="114">
-        <v>0.2</v>
-      </c>
-      <c r="E46" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="F46" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
-      </c>
       <c r="G46" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="51">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B47" s="115" t="s">
-        <v>572</v>
+        <v>430</v>
       </c>
       <c r="C47" s="114" t="s">
         <v>326</v>
       </c>
       <c r="D47" s="114">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E47" s="114">
         <f t="shared" ca="1" si="2"/>
@@ -18912,27 +18250,27 @@
       </c>
       <c r="F47" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G47" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H47" s="115" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="25.5">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="51">
       <c r="A48" s="114" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
       <c r="B48" s="115" t="s">
-        <v>497</v>
+        <v>572</v>
       </c>
       <c r="C48" s="114" t="s">
         <v>326</v>
       </c>
       <c r="D48" s="114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E48" s="114">
         <f t="shared" ca="1" si="2"/>
@@ -18940,49 +18278,49 @@
       </c>
       <c r="F48" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G48" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="25.5">
       <c r="A49" s="114" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>91</v>
+        <v>497</v>
       </c>
       <c r="C49" s="114" t="s">
-        <v>388</v>
+        <v>326</v>
       </c>
       <c r="D49" s="114">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E49" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F49" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G49" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>694</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="114" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B50" s="115" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="114" t="s">
         <v>388</v>
@@ -18992,25 +18330,25 @@
       </c>
       <c r="E50" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F50" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G50" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H50" s="115" t="s">
-        <v>1302</v>
+        <v>694</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B51" s="115" t="s">
-        <v>1150</v>
+        <v>93</v>
       </c>
       <c r="C51" s="114" t="s">
         <v>388</v>
@@ -19020,17 +18358,17 @@
       </c>
       <c r="E51" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G51" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -19038,69 +18376,69 @@
         <v>1261</v>
       </c>
       <c r="B52" s="115" t="s">
-        <v>387</v>
+        <v>1149</v>
       </c>
       <c r="C52" s="114" t="s">
         <v>388</v>
       </c>
       <c r="D52" s="114">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E52" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F52" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="G52" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H52" s="115" t="s">
-        <v>695</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="114" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B53" s="115" t="s">
-        <v>572</v>
+        <v>387</v>
       </c>
       <c r="C53" s="114" t="s">
         <v>388</v>
       </c>
       <c r="D53" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E53" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="G53" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="38.25">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C54" s="114" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D54" s="114">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E54" s="114">
         <f t="shared" ca="1" si="2"/>
@@ -19108,49 +18446,49 @@
       </c>
       <c r="F54" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>1.5</v>
       </c>
       <c r="G54" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="38.25">
       <c r="A55" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>93</v>
+        <v>569</v>
       </c>
       <c r="C55" s="114" t="s">
         <v>397</v>
       </c>
       <c r="D55" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E55" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.33</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G55" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="25.5">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="38.25">
       <c r="A56" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B56" s="115" t="s">
-        <v>1150</v>
+        <v>93</v>
       </c>
       <c r="C56" s="114" t="s">
         <v>397</v>
@@ -19160,81 +18498,81 @@
       </c>
       <c r="E56" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="G56" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="51">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="114" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B57" s="115" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="C57" s="114" t="s">
         <v>397</v>
       </c>
       <c r="D57" s="114">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E57" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F57" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="G57" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="38.25">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="51">
       <c r="A58" s="114" t="s">
         <v>1261</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>91</v>
+        <v>1155</v>
       </c>
       <c r="C58" s="114" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D58" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E58" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F58" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G58" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="25.5">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="38.25">
       <c r="A59" s="114" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B59" s="115" t="s">
-        <v>387</v>
+        <v>91</v>
       </c>
       <c r="C59" s="114" t="s">
         <v>401</v>
@@ -19244,25 +18582,25 @@
       </c>
       <c r="E59" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G59" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H59" s="115" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="25.5">
       <c r="A60" s="114" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B60" s="115" t="s">
-        <v>1156</v>
+        <v>387</v>
       </c>
       <c r="C60" s="114" t="s">
         <v>401</v>
@@ -19282,43 +18620,43 @@
         <v>672</v>
       </c>
       <c r="H60" s="115" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="25.5">
       <c r="A61" s="114" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>494</v>
+        <v>1155</v>
       </c>
       <c r="C61" s="114" t="s">
-        <v>308</v>
+        <v>401</v>
       </c>
       <c r="D61" s="114">
         <v>0.33</v>
       </c>
       <c r="E61" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="G61" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>675</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="114" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="B62" s="115" t="s">
-        <v>604</v>
+        <v>494</v>
       </c>
       <c r="C62" s="114" t="s">
         <v>308</v>
@@ -19343,10 +18681,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="114" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="B63" s="115" t="s">
-        <v>1228</v>
+        <v>604</v>
       </c>
       <c r="C63" s="114" t="s">
         <v>308</v>
@@ -19366,43 +18704,43 @@
         <v>672</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="38.25">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B64" s="115" t="s">
-        <v>95</v>
+        <v>1227</v>
       </c>
       <c r="C64" s="114" t="s">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="D64" s="114">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E64" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G64" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="25.5">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="38.25">
       <c r="A65" s="114" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="B65" s="115" t="s">
-        <v>440</v>
+        <v>95</v>
       </c>
       <c r="C65" s="114" t="s">
         <v>362</v>
@@ -19422,25 +18760,25 @@
         <v>672</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="25.5">
       <c r="A66" s="114" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B66" s="115" t="s">
-        <v>530</v>
+        <v>440</v>
       </c>
       <c r="C66" s="114" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D66" s="114">
         <v>0</v>
       </c>
       <c r="E66" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -19450,21 +18788,21 @@
         <v>672</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="25.5">
       <c r="A67" s="114" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B67" s="115" t="s">
-        <v>599</v>
+        <v>530</v>
       </c>
       <c r="C67" s="114" t="s">
         <v>350</v>
       </c>
       <c r="D67" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E67" s="114">
         <f t="shared" ca="1" si="2"/>
@@ -19472,59 +18810,59 @@
       </c>
       <c r="F67" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G67" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="114" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>91</v>
+        <v>599</v>
       </c>
       <c r="C68" s="114" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="D68" s="114">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E68" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F68" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G68" s="114" t="s">
         <v>672</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="114" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B69" s="115" t="s">
-        <v>501</v>
+        <v>91</v>
       </c>
       <c r="C69" s="114" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D69" s="114">
         <v>0</v>
       </c>
       <c r="E69" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F69" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -19534,25 +18872,25 @@
         <v>672</v>
       </c>
       <c r="H69" s="115" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="25.5">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="114" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="B70" s="115" t="s">
-        <v>1111</v>
+        <v>501</v>
       </c>
       <c r="C70" s="114" t="s">
-        <v>937</v>
+        <v>321</v>
       </c>
       <c r="D70" s="114">
         <v>0</v>
       </c>
       <c r="E70" s="114">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F70" s="114">
         <f t="shared" ca="1" si="3"/>
@@ -19562,7 +18900,35 @@
         <v>672</v>
       </c>
       <c r="H70" s="115" t="s">
-        <v>1319</v>
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="25.5">
+      <c r="A71" s="114" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B71" s="115" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C71" s="114" t="s">
+        <v>937</v>
+      </c>
+      <c r="D71" s="114">
+        <v>0</v>
+      </c>
+      <c r="E71" s="114">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F71" s="114">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G71" s="114" t="s">
+        <v>672</v>
+      </c>
+      <c r="H71" s="115" t="s">
+        <v>1318</v>
       </c>
     </row>
   </sheetData>
@@ -19587,12 +18953,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -19624,7 +18990,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A5),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A5),0.5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="114">
@@ -19636,7 +19002,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>751</v>
@@ -19655,7 +19021,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A6),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A6),0.5)</f>
         <v>0.5</v>
       </c>
       <c r="D6" s="114">
@@ -19667,7 +19033,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -19679,7 +19045,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A7),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A7),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D7" s="114">
@@ -19691,14 +19057,14 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
+        <v>1323</v>
+      </c>
+      <c r="H7" s="124" t="s">
         <v>1324</v>
-      </c>
-      <c r="H7" s="124" t="s">
-        <v>1325</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
-        <v>48.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1">
@@ -19710,7 +19076,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A8),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A8),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D8" s="114">
@@ -19722,10 +19088,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H8" s="124" t="s">
         <v>1326</v>
-      </c>
-      <c r="H8" s="124" t="s">
-        <v>1327</v>
       </c>
       <c r="I8" s="125">
         <f>SUM(복귀_일_수평당기기!E11:E14,복귀_목_수직당기기!E11:E13)</f>
@@ -19741,7 +19107,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A9),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A9),0.5)</f>
         <v>3</v>
       </c>
       <c r="D9" s="114">
@@ -19753,7 +19119,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -19765,19 +19131,19 @@
         <v>13</v>
       </c>
       <c r="C10" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A10),0.5)</f>
-        <v>5.5</v>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A10),0.5)</f>
+        <v>6</v>
       </c>
       <c r="D10" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="E10" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -19789,7 +19155,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A11),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A11),0.5)</f>
         <v>3</v>
       </c>
       <c r="D11" s="114">
@@ -19801,7 +19167,7 @@
         <v>충분</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -19813,7 +19179,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A12),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A12),0.5)</f>
         <v>6.5</v>
       </c>
       <c r="D12" s="114">
@@ -19825,7 +19191,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -19837,7 +19203,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A13),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A13),0.5)</f>
         <v>2</v>
       </c>
       <c r="D13" s="114">
@@ -19849,7 +19215,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -19858,22 +19224,22 @@
       </c>
       <c r="B14" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A14)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A14)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A14)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A14)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A14)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A14)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C14" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A14),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A14),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D14" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="E14" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1397</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -19885,7 +19251,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A15),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A15),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D15" s="114">
@@ -19897,10 +19263,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H15" s="124" t="s">
         <v>1332</v>
-      </c>
-      <c r="H15" s="124" t="s">
-        <v>1333</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -19916,7 +19282,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A16),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A16),0.5)</f>
         <v>2.5</v>
       </c>
       <c r="D16" s="114">
@@ -19928,7 +19294,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -19940,7 +19306,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A17),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A17),0.5)</f>
         <v>7</v>
       </c>
       <c r="D17" s="114">
@@ -19952,7 +19318,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -19964,7 +19330,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="114">
-        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A18),0.5)</f>
+        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A18),0.5)</f>
         <v>0</v>
       </c>
       <c r="D18" s="114">
@@ -19976,7 +19342,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -19988,7 +19354,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A19),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A19),0.5)</f>
         <v>0</v>
       </c>
       <c r="D19" s="114">
@@ -20000,7 +19366,7 @@
         <v>충분</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -20012,7 +19378,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A20),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A20),0.5)</f>
         <v>8</v>
       </c>
       <c r="D20" s="114">
@@ -20024,7 +19390,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -20036,7 +19402,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A21),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A21),0.5)</f>
         <v>8.5</v>
       </c>
       <c r="D21" s="114">
@@ -20048,7 +19414,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -20060,7 +19426,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A22),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A22),0.5)</f>
         <v>3</v>
       </c>
       <c r="D22" s="114">
@@ -20072,7 +19438,7 @@
         <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -20084,7 +19450,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A23),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A23),0.5)</f>
         <v>0</v>
       </c>
       <c r="D23" s="114">
@@ -20096,7 +19462,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -20108,7 +19474,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A24),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A24),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D24" s="114">
@@ -20120,7 +19486,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -20132,7 +19498,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$90,복귀_간접계수맵!$C$7:$C$90,$A25),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A25),0.5)</f>
         <v>0</v>
       </c>
       <c r="D25" s="114">
@@ -20144,7 +19510,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -20153,11 +19519,11 @@
       </c>
       <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>271</v>
+        <v>273.5</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -20167,192 +19533,192 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1398</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="107" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="123" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4625D75-B2F3-4BC7-8F2B-F9B177F20834}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCE85DC3-B137-4929-AE54-87154EFAFB51}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="1417">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -4342,6 +4342,9 @@
   <si>
     <t>날짜 (토요일)</t>
     <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· [2026-10-04 사용자 지정] 오버헤드 프레스를 11주차 30kg으로 — 계획 28에서 두 칸 앞당겼다. 앱도 6주차 시작값에서 사다리를 걸어 중량을 내므로 11주차 칸 하나를 덮지 않고 D10을 26 → 27로 바꿔 11주차에 30이 나오게 했다(29는 못 끼우는 값이라 30). 격주 1kg은 그대로 — 12주차 31 · 14주차 32.</t>
   </si>
 </sst>
 </file>
@@ -5544,7 +5547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5668,14 +5671,14 @@
       </c>
       <c r="C10" s="8" t="str">
         <f>TEXT(D10/B10,"0%")</f>
-        <v>65%</v>
+        <v>68%</v>
       </c>
       <c r="D10" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="9">
         <f>INDEX(증량기록!$I$10:$I$39,MAX(1,MIN(30,$C$4-5)))</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>98</v>
@@ -5856,7 +5859,7 @@
       </c>
       <c r="E43" s="9">
         <f>증량기록!I10</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1">
@@ -5877,7 +5880,7 @@
       </c>
       <c r="E44" s="16">
         <f>증량기록!I11</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1">
@@ -5898,7 +5901,7 @@
       </c>
       <c r="E45" s="16">
         <f>증량기록!I12</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" customHeight="1">
@@ -5919,7 +5922,7 @@
       </c>
       <c r="E46" s="16">
         <f>증량기록!I13</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" customHeight="1">
@@ -5940,7 +5943,7 @@
       </c>
       <c r="E47" s="16">
         <f>증량기록!I14</f>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1">
@@ -5961,7 +5964,7 @@
       </c>
       <c r="E48" s="16">
         <f>증량기록!I15</f>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1">
@@ -5982,7 +5985,7 @@
       </c>
       <c r="E49" s="16">
         <f>증량기록!I16</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1">
@@ -6003,7 +6006,7 @@
       </c>
       <c r="E50" s="16">
         <f>증량기록!I17</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1">
@@ -6024,7 +6027,7 @@
       </c>
       <c r="E51" s="16">
         <f>증량기록!I18</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1">
@@ -6045,7 +6048,7 @@
       </c>
       <c r="E52" s="16">
         <f>증량기록!I19</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1">
@@ -6066,7 +6069,7 @@
       </c>
       <c r="E53" s="16">
         <f>증량기록!I20</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1">
@@ -6087,7 +6090,7 @@
       </c>
       <c r="E54" s="16">
         <f>증량기록!I21</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="51.75" customHeight="1">
@@ -6188,6 +6191,11 @@
     <row r="70" spans="1:1">
       <c r="A70" t="s">
         <v>1414</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>1416</v>
       </c>
     </row>
   </sheetData>
@@ -10126,7 +10134,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="16">
         <f>시작중량_설정!$D$10</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="65" t="s">
@@ -10159,7 +10167,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="16">
         <f t="shared" ref="I11:I39" si="3">IF(OR(J10="",J10="O"),IF(MOD(ROW()-10,$E$8)=0,I10+$C$8+(MOD(I10+$C$8,5)=4),I10),I10)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="65"/>
@@ -10190,7 +10198,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="16">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="65"/>
@@ -10221,7 +10229,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="16">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="65"/>
@@ -10252,7 +10260,7 @@
       <c r="H14" s="4"/>
       <c r="I14" s="16">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="65"/>
@@ -10283,7 +10291,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="16">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="65"/>
@@ -10314,7 +10322,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="16">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="65"/>
@@ -10345,7 +10353,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="16">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="65"/>
@@ -10376,7 +10384,7 @@
       <c r="H18" s="4"/>
       <c r="I18" s="16">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="65"/>
@@ -10407,7 +10415,7 @@
       <c r="H19" s="4"/>
       <c r="I19" s="16">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="65"/>
@@ -10438,7 +10446,7 @@
       <c r="H20" s="4"/>
       <c r="I20" s="16">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="65"/>
@@ -10469,7 +10477,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="16">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="65"/>
@@ -10500,7 +10508,7 @@
       <c r="H22" s="102"/>
       <c r="I22" s="103">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J22" s="102"/>
       <c r="K22" s="104"/>
@@ -10531,7 +10539,7 @@
       <c r="H23" s="102"/>
       <c r="I23" s="103">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J23" s="102"/>
       <c r="K23" s="104"/>
@@ -10562,7 +10570,7 @@
       <c r="H24" s="102"/>
       <c r="I24" s="103">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J24" s="102"/>
       <c r="K24" s="104"/>
@@ -10593,7 +10601,7 @@
       <c r="H25" s="102"/>
       <c r="I25" s="103">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J25" s="102"/>
       <c r="K25" s="104"/>
@@ -10624,7 +10632,7 @@
       <c r="H26" s="102"/>
       <c r="I26" s="103">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J26" s="102"/>
       <c r="K26" s="104"/>
@@ -10655,7 +10663,7 @@
       <c r="H27" s="102"/>
       <c r="I27" s="103">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J27" s="102"/>
       <c r="K27" s="104"/>
@@ -10686,7 +10694,7 @@
       <c r="H28" s="102"/>
       <c r="I28" s="103">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J28" s="102"/>
       <c r="K28" s="104"/>
@@ -10717,7 +10725,7 @@
       <c r="H29" s="102"/>
       <c r="I29" s="103">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J29" s="102"/>
       <c r="K29" s="104"/>
@@ -10748,7 +10756,7 @@
       <c r="H30" s="102"/>
       <c r="I30" s="103">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J30" s="102"/>
       <c r="K30" s="104"/>
@@ -10779,7 +10787,7 @@
       <c r="H31" s="102"/>
       <c r="I31" s="103">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J31" s="102"/>
       <c r="K31" s="104"/>
@@ -10810,7 +10818,7 @@
       <c r="H32" s="102"/>
       <c r="I32" s="103">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J32" s="102"/>
       <c r="K32" s="104"/>
@@ -10841,7 +10849,7 @@
       <c r="H33" s="102"/>
       <c r="I33" s="103">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J33" s="102"/>
       <c r="K33" s="104"/>
@@ -10872,7 +10880,7 @@
       <c r="H34" s="102"/>
       <c r="I34" s="103">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J34" s="102"/>
       <c r="K34" s="104"/>
@@ -10903,7 +10911,7 @@
       <c r="H35" s="102"/>
       <c r="I35" s="103">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J35" s="102"/>
       <c r="K35" s="104"/>
@@ -10934,7 +10942,7 @@
       <c r="H36" s="102"/>
       <c r="I36" s="103">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J36" s="102"/>
       <c r="K36" s="104"/>
@@ -10965,7 +10973,7 @@
       <c r="H37" s="102"/>
       <c r="I37" s="103">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J37" s="102"/>
       <c r="K37" s="104"/>
@@ -10996,7 +11004,7 @@
       <c r="H38" s="102"/>
       <c r="I38" s="103">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J38" s="102"/>
       <c r="K38" s="104"/>
@@ -11027,7 +11035,7 @@
       <c r="H39" s="102"/>
       <c r="I39" s="103">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J39" s="102"/>
       <c r="K39" s="104"/>
@@ -15121,7 +15129,7 @@
     <row r="16" spans="1:3">
       <c r="A16" s="109">
         <f>IF(MAX(20,(MROUND(시작중량_설정!$E$10*0.75,1)+(MOD(MROUND(시작중량_설정!$E$10*0.75,1),5)=4)))&lt;=MAX(20,(MROUND(시작중량_설정!$E$10*0.6,1)+(MOD(MROUND(시작중량_설정!$E$10*0.6,1),5)=4))),"생략",MAX(20,(MROUND(시작중량_설정!$E$10*0.75,1)+(MOD(MROUND(시작중량_설정!$E$10*0.75,1),5)=4))))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="109">
         <v>3</v>
@@ -15133,7 +15141,7 @@
     <row r="17" spans="1:14">
       <c r="A17" s="109">
         <f>IF(MAX(20,(MROUND(시작중량_설정!$E$10*0.9,1)+(MOD(MROUND(시작중량_설정!$E$10*0.9,1),5)=4)))&lt;=MAX(20,(MROUND(시작중량_설정!$E$10*0.75,1)+(MOD(MROUND(시작중량_설정!$E$10*0.75,1),5)=4))),"생략",MAX(20,(MROUND(시작중량_설정!$E$10*0.9,1)+(MOD(MROUND(시작중량_설정!$E$10*0.9,1),5)=4))))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17" s="109">
         <v>2</v>
@@ -15145,7 +15153,7 @@
     <row r="18" spans="1:14">
       <c r="A18" s="109">
         <f>시작중량_설정!$E$10</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" s="109">
         <v>5</v>
@@ -15437,7 +15445,7 @@
       </c>
       <c r="D33" s="112">
         <f>시작중량_설정!$E$10</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E33" s="112">
         <v>3</v>
@@ -22549,7 +22557,7 @@
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="20">
         <f>IF(MAX(20,(MROUND(시작중량_설정!$E$10*0.75,1)+(MOD(MROUND(시작중량_설정!$E$10*0.75,1),5)=4)))&lt;=MAX(20,(MROUND(시작중량_설정!$E$10*0.6,1)+(MOD(MROUND(시작중량_설정!$E$10*0.6,1),5)=4))),"생략",MAX(20,(MROUND(시작중량_설정!$E$10*0.75,1)+(MOD(MROUND(시작중량_설정!$E$10*0.75,1),5)=4))))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="20">
         <v>3</v>
@@ -22561,7 +22569,7 @@
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="20">
         <f>IF(MAX(20,(MROUND(시작중량_설정!$E$10*0.9,1)+(MOD(MROUND(시작중량_설정!$E$10*0.9,1),5)=4)))&lt;=MAX(20,(MROUND(시작중량_설정!$E$10*0.75,1)+(MOD(MROUND(시작중량_설정!$E$10*0.75,1),5)=4))),"생략",MAX(20,(MROUND(시작중량_설정!$E$10*0.9,1)+(MOD(MROUND(시작중량_설정!$E$10*0.9,1),5)=4))))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="20">
         <v>2</v>
@@ -22573,7 +22581,7 @@
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="37">
         <f>시작중량_설정!$E$10</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" s="27">
         <v>5</v>
@@ -22671,7 +22679,7 @@
       </c>
       <c r="D20" s="41">
         <f>시작중량_설정!$E$10</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E20" s="40">
         <v>3</v>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCE85DC3-B137-4929-AE54-87154EFAFB51}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60AB3D08-F24F-4970-8076-F8DFB8E99E40}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="1417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1425">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -2812,9 +2812,6 @@
     <t>등 수평 당기기 · 팔 삼두/이두</t>
   </si>
   <si>
-    <t>약 74분</t>
-  </si>
-  <si>
     <t>무거운 로우 넷을 신선할 때 치는 날. 토요일 하체 전면 다음날이라 등 · 그립 · 기립근이 온전하다 — 스쿼트는 그 셋을 쓰지 않는다. 등 17 · 팔 6 · 전완 6(슈퍼세트) · 백 익스텐션 3이고 가슴이 없다</t>
   </si>
   <si>
@@ -3169,9 +3166,6 @@
     <t>135/150/165</t>
   </si>
   <si>
-    <t>팔꿈치를 몸에 붙여 당기는 경로라 주동근이 광배다 — 평면으로 날을 가르고 근육군은 팔꿈치 경로로 매긴다(2026-09-04 원칙). 좌우 독립이라 약한 쪽이 드러난다. 이 날 유일한 광배 직접이고 나머지 12세트는 목요일(수직)에 있다.</t>
-  </si>
-  <si>
     <t>원암 해머 스트랭스 로우 / 원암 덤벨 로우 (벤치 지지) / 머신 로우</t>
   </si>
   <si>
@@ -3244,21 +3238,12 @@
     <t>· 일요일은 수평, 목요일은 수직이다. 재택 1일차 '당기기 A (수직)' · 6일차 '당기기 B (수평)'과 같은 축이고 순서만 반대다(2026-10-02 사용자 지정).</t>
   </si>
   <si>
-    <t>· 날 분할은 평면으로, 근육군은 팔꿈치 경로로 매긴다 — 다른 축이고 섞지 않는다. 그래서 수평 날에 광배(원암 케이블 로우)가 있고 수직 날에 승모 중부(페이스풀)가 있다.</t>
-  </si>
-  <si>
     <t>· 광배 일 4 / 목 12 · 승모 중부 일 10 / 목 3 — 둘 다 주 2회다. 근육군으로 날을 가르면 '주 1회'로 적히지만 실제로는 로우가 광배를 쓰고 랫풀다운이 능형근을 쓴다.</t>
   </si>
   <si>
-    <t>· 32세트 · 약 74분. 전완 슈퍼세트 6 + 백 익스텐션 3이 들어오고 원암 케이블 로우가 3 → 4로 올라 22 → 32가 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정). 복합 11 / 고립 21이다.</t>
-  </si>
-  <si>
     <t>· 앞쪽은 그대로다 — 무거운 로우 넷을 신선한 상태로 치는 구조는 손대지 않았고, 더한 것은 전부 맨 뒤 고립이다.</t>
   </si>
   <si>
-    <t>· 그립이 이 날의 제약이다. 바벨 → 해머(서포티드) → 원암 → 스캡 슈러그 순으로 그립 부담이 줄어드는 순서다.</t>
-  </si>
-  <si>
     <t>· 스캡 슈러그 +60초 · 케이블 푸쉬다운 +60초 · 프리쳐 컬 +60초. 마지막 세트에만 2단.</t>
   </si>
   <si>
@@ -3268,9 +3253,6 @@
     <t>· 바벨 로우 · 해머 로우에는 걸지 않는다 — 중량이 큰 로우에서 실패 뒤 반복은 폼이 먼저 무너진다.</t>
   </si>
   <si>
-    <t>· 원암 케이블 로우에도 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 된다.</t>
-  </si>
-  <si>
     <t>· 트랩바 슈러그에도 걸지 않는다. 선 자세로 중량을 받치는 종목이다.</t>
   </si>
   <si>
@@ -4018,9 +4000,6 @@
     <t>직접 14세트: 월요일 벤치 4(4×8) · 딥스 3 · 목요일 펙덱 플라이 4 · 디클라인 케이블 플라이 3 (2026-10-02 사용자 지정). 간접 0.6 — 인클라인 덤벨 플라이 0.2×3 (인클라인 머신의 교차 간접은 2026-10-02에 0으로). 수평 · 하방 · 내전 세 벡터가 다 들어 있다</t>
   </si>
   <si>
-    <t>직접 16세트: 목요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 4 + 일요일(수평) 원암 케이블 로우 4 (2026-10-02 사용자 조정). 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3(둘 다 일요일). [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 반대 날 로우가 전부 광배를 쓰고 있었다</t>
-  </si>
-  <si>
     <t>등 합산</t>
   </si>
   <si>
@@ -4031,9 +4010,6 @@
   </si>
   <si>
     <t>직접 3세트: 목요일(수직) 오버헤드 슈러그 3 — 팔이 머리 위라 수직 날에 맞는다. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
-  </si>
-  <si>
-    <t>직접 13세트: 일요일(수평) 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 목요일(수직) 페이스풀 3. 10/3으로 나뉜다 — 페이스풀이 없으면 일요일 주 1회가 되므로 그 자리를 유지한다(재택도 페이스풀을 수직 날에 둔다). 간접 5.0 — 원암 로우 0.5×3 + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
   </si>
   <si>
     <t>직접 10세트: 수요일 데드 톱 1 + 백오프 2 + 일요일 백 익스텐션 3 · 목요일 4(45도 · 맨몸) (재택도 당기기 두 날에 3세트씩 둔다 · 목요일만 4로 올린 것은 사용자 조정). 3 → 10으로 '보완 필요'가 '충분'이 됐다. **척추 신전을 강조해서 해야 이 9세트가 유효하다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근 · 햄스트링이 주동근이 되고 기립근은 버티기만 한다. 그러면 09-04 규칙상 등척성이라 계수 0이고 이 숫자가 거짓이 된다. 중량은 더블 프로그레션 — 맨몸 15회를 채우면 원판 5~10kg을 안는다('맨몸'은 시작값이지 상한이 아니다). 목요일 것도 원판 금지가 아니고, 데드 다음날이라 일요일보다 낮게 나오는 것이 정상이다 — 수요일 데드나 토요일 스쿼트가 2주 연속 안 오르면 그 날 중량을 먼저 의심한다. 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
@@ -4305,26 +4281,14 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>약 487분 (8시간 7분)</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>· ⑪ [2026-10-04] 월요일 측면 +4 — 원암 케이블 레터럴 3 → 4 · 머신 레터럴 3 신설(마지막 세트 드롭). 측면 직접 10 → 14 · 실질 12 → 16(MAV 하단). 같은 날 케이블 리버스 플라이를 원암으로 바꿨다 — 사용자 지정, 편측이 집중이 더 잘 된다. 이어서 사용자 요청으로 리버스 펙덱 2(후면)를 더하고 월요일 어깨를 측 → 후 → 측 → 후로 교대 배열했다 — 후면 직접 10 → 12 · 실질 11.5 → 13.5. 205 → 211세트 · 월요일 25세트 63분.</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 목 44세트 99분 · 수 42세트 104분 · 토 41세트 101분 · 일 32세트 74분 · 화 27세트 46분 · 월 25세트 63분.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>· 세션 상한 26세트는 메인 리프트가 있는 날(토 · 월 · 수)에만 적용하고 고립 소근육은 예외로 센다 — 토요일은 고립 29를 빼면 실질 12, 수요일은 26을 빼면 16, 월요일은 15를 빼면 10이다. 메인이 없는 일 · 화 · 목은 상한의 적용 대상이 아니다.</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 주 487분 = 8시간 7분. 주 4회 370분에서 105분 늘었다. 수(104) · 토(101)가 100분을 넘지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>· 25세트 · 약 63분. 여섯 날 중 가장 작다 — 가슴 하나만 맡고 어깨가 측면 7 · 후면 5이다. 2026-10-04에 어깨 6 → 12(측면 +4 · 후면 +2)를 이 날에 넣은 것도 가장 작은 날이어서다. 어깨 블록은 측 → 후 → 측 → 후로 교대한다(사용자 지정).</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -4345,6 +4309,82 @@
   </si>
   <si>
     <t>· [2026-10-04 사용자 지정] 오버헤드 프레스를 11주차 30kg으로 — 계획 28에서 두 칸 앞당겼다. 앱도 6주차 시작값에서 사다리를 걸어 중량을 내므로 11주차 칸 하나를 덮지 않고 D10을 26 → 27로 바꿔 11주차에 30이 나오게 했다(29는 못 끼우는 값이라 30). 격주 1kg은 그대로 — 12주차 31 · 14주차 32.</t>
+  </si>
+  <si>
+    <t>시티드 케이블 로우</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>광배</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>8~12</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-10-04 사용자 요청] 원암 케이블 로우 4세트를 양팔 2 + 원암 2로 나눴다 — 재택 6일차(양팔 3 + 원암 2)와 같은 구조다. 양팔로 무게를 싣고, 이어지는 원암으로 좌우 차를 본다. 좁은 뉴트럴 그립(V바) · 팔꿈치를 몸에 붙여 당기므로 주동근은 광배다(팔꿈치 경로 원칙). 중량 50은 원암 25의 두 배에서 잡은 출발값이라 첫 세션에 8~12회에 맞춰 조정한다. 같은 스테이션에서 원암(D핸들) → 스캡 슈러그(바)까지 자리 이동 없이 이어진다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>머신 로우 (뉴트럴 그립) / 체스트 서포티드 로우 (뉴트럴) / 원암 케이블 로우 4세트로 합치기</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-10-04 4 → 2] 앞 2세트를 3번 시티드 케이블 로우(양팔)로 나눴다 — 사용자 요청. 같은 스테이션에서 바를 D핸들로 바꿔 한 팔씩, 무게는 양팔의 절반에서 시작해 약한 쪽 기준으로 올린다. 반대 손은 기구를 잡아 몸통을 고정한다. 팔꿈치를 몸에 붙여 당기는 경로라 주동근이 광배다 — 평면으로 날을 가르고 근육군은 팔꿈치 경로로 매긴다(2026-09-04 원칙). 좌우 독립이라 약한 쪽이 드러난다. 이 날 광배 직접은 이것과 3번 시티드 케이블 로우(합 4)이고 나머지 12세트는 목요일(수직)에 있다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 날 분할은 평면으로, 근육군은 팔꿈치 경로로 매긴다 — 다른 축이고 섞지 않는다. 그래서 수평 날에 광배(시티드 · 원암 케이블 로우)가 있고 수직 날에 승모 중부(페이스풀)가 있다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 그립이 이 날의 제약이다. 바벨 → 해머(서포티드) → 시티드(양팔) → 원암 → 스캡 슈러그 순으로 그립 부담이 줄어드는 순서다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 시티드 · 원암 케이블 로우에도 걸지 않는다. 좌우 따로라 2단 드롭이 +120초가 된다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>좁은 뉴트럴 그립(V바) — 원암 케이블 로우와 같은 등급. 당기기 → 이두 계수는 그립으로 정한다: 뒤침 0.5 · 뉴트럴 0.33 · 엎침 0.2 (2026-09-04 원칙). 재택 6일차 시티드 케이블 로우와 같은 계수 (2026-10-04 원암 4 → 양팔 2 + 원암 2로 신설)</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>견갑 후인 능동 수축 — 원암 케이블 로우와 같은 등급, 재택 6일차와 같은 계수 (2026-10-04 신설)</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>직접 16세트: 목요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 4 + 일요일(수평) 시티드 케이블 로우 2 · 원암 케이블 로우 2 (2026-10-02 사용자 조정 4세트 · 2026-10-04 양팔 2 + 원암 2로 분할). 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3(둘 다 일요일). [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 반대 날 로우가 전부 광배를 쓰고 있었다</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>직접 13세트: 일요일(수평) 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 목요일(수직) 페이스풀 3. 10/3으로 나뉜다 — 페이스풀이 없으면 일요일 주 1회가 되므로 그 자리를 유지한다(재택도 페이스풀을 수직 날에 둔다). 간접 5.0 — 시티드 · 원암 케이블 로우 0.5×(2+2) + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· ⑫ [2026-10-04] 일요일 원암 케이블 로우 4 → 시티드 케이블 로우(양팔) 2 + 원암 2 — 사용자 요청, 재택 6일차와 같은 분할. 광배 직접 4 · 세트 합계 그대로이고, 계수도 같아(이두 0.33 · 승모 중부 0.5) 검산 숫자는 안 바뀐다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 32세트 · 약 73분. 전완 슈퍼세트 6 + 백 익스텐션 3이 들어오고 원암 케이블 로우가 3 → 4로 올라 22 → 32가 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정). 복합 11 / 고립 21이다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 목 44세트 99분 · 수 42세트 104분 · 토 41세트 101분 · 일 32세트 73분 · 화 27세트 46분 · 월 25세트 63분.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 주 486분 = 8시간 6분. 주 4회 370분에서 105분 늘었다. 수(104) · 토(101)가 100분을 넘지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 73분</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 486분 (8시간 6분)</t>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6111,7 +6151,7 @@
         <v>46228</v>
       </c>
       <c r="D59" t="s">
-        <v>1412</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -6122,7 +6162,7 @@
         <v>46298</v>
       </c>
       <c r="D60" t="s">
-        <v>1413</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -6190,12 +6230,12 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>1414</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>1416</v>
+        <v>1405</v>
       </c>
     </row>
   </sheetData>
@@ -10074,7 +10114,7 @@
         <v>124</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1415</v>
+        <v>1404</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>828</v>
@@ -11307,7 +11347,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11395,115 +11435,115 @@
         <v>917</v>
       </c>
       <c r="E7" s="121">
-        <f>복귀_일_수평당기기!$E$21</f>
+        <f>복귀_일_수평당기기!$E$22</f>
         <v>32</v>
       </c>
       <c r="F7" s="114" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G7" s="115" t="s">
         <v>918</v>
-      </c>
-      <c r="G7" s="115" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1">
       <c r="A8" s="114" t="s">
+        <v>919</v>
+      </c>
+      <c r="B8" s="120" t="s">
         <v>920</v>
-      </c>
-      <c r="B8" s="120" t="s">
-        <v>921</v>
       </c>
       <c r="C8" s="114" t="s">
         <v>907</v>
       </c>
       <c r="D8" s="115" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E8" s="121">
         <f>복귀_월_가슴!$E$26</f>
         <v>25</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="G8" s="115" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1">
       <c r="A9" s="114" t="s">
+        <v>923</v>
+      </c>
+      <c r="B9" s="120" t="s">
         <v>924</v>
-      </c>
-      <c r="B9" s="120" t="s">
-        <v>925</v>
       </c>
       <c r="C9" s="114" t="s">
         <v>907</v>
       </c>
       <c r="D9" s="115" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E9" s="121">
         <f>복귀_화_팔!$E$20</f>
         <v>27</v>
       </c>
       <c r="F9" s="114" t="s">
+        <v>926</v>
+      </c>
+      <c r="G9" s="115" t="s">
         <v>927</v>
-      </c>
-      <c r="G9" s="115" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1">
       <c r="A10" s="114" t="s">
+        <v>928</v>
+      </c>
+      <c r="B10" s="120" t="s">
         <v>929</v>
-      </c>
-      <c r="B10" s="120" t="s">
-        <v>930</v>
       </c>
       <c r="C10" s="114" t="s">
         <v>907</v>
       </c>
       <c r="D10" s="115" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E10" s="121">
         <f>복귀_수_하체후면!$E$41</f>
         <v>42</v>
       </c>
       <c r="F10" s="114" t="s">
+        <v>931</v>
+      </c>
+      <c r="G10" s="115" t="s">
         <v>932</v>
-      </c>
-      <c r="G10" s="115" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1">
       <c r="A11" s="114" t="s">
+        <v>933</v>
+      </c>
+      <c r="B11" s="120" t="s">
         <v>934</v>
-      </c>
-      <c r="B11" s="120" t="s">
-        <v>935</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>907</v>
       </c>
       <c r="D11" s="115" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E11" s="121">
         <f>복귀_목_수직당기기!$E$24</f>
         <v>44</v>
       </c>
       <c r="F11" s="114" t="s">
+        <v>936</v>
+      </c>
+      <c r="G11" s="115" t="s">
         <v>937</v>
-      </c>
-      <c r="G11" s="115" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1">
       <c r="A12" s="114" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B12" s="120" t="s">
         <v>171</v>
@@ -11521,7 +11561,7 @@
         <v>28</v>
       </c>
       <c r="G12" s="115" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -11536,263 +11576,268 @@
         <v>211</v>
       </c>
       <c r="F13" s="116" t="s">
-        <v>1406</v>
+        <v>1424</v>
       </c>
       <c r="G13" s="119"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="107" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="123" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="123" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="123" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="123" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="123" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="123" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="123" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="123" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="123" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="123" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="123" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="123" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="107" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="123" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="123" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="123" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="123" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="123" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="126" t="s">
-        <v>1407</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="107" t="s">
-        <v>968</v>
+      <c r="A44" s="126" t="s">
+        <v>1419</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="123" t="s">
-        <v>969</v>
+      <c r="A45" s="107" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="123" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="123" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="107" t="s">
         <v>972</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="107" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="123" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="123" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="123" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="107" t="s">
         <v>978</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="107" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="123" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1409</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>980</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>1410</v>
+        <v>980</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="123" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="107" t="s">
         <v>982</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="107" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="123" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>987</v>
+        <v>985</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="123" t="s">
+        <v>986</v>
       </c>
     </row>
   </sheetData>
@@ -11823,7 +11868,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11904,22 +11949,22 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="110" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="110" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -12007,10 +12052,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="113" t="s">
+        <v>992</v>
+      </c>
+      <c r="K20" s="113" t="s">
         <v>993</v>
-      </c>
-      <c r="K20" s="113" t="s">
-        <v>994</v>
       </c>
       <c r="L20" s="112" t="s">
         <v>353</v>
@@ -12048,10 +12093,10 @@
         <v>13</v>
       </c>
       <c r="J21" s="115" t="s">
+        <v>994</v>
+      </c>
+      <c r="K21" s="115" t="s">
         <v>995</v>
-      </c>
-      <c r="K21" s="115" t="s">
-        <v>996</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -12087,10 +12132,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J22" s="115" t="s">
+        <v>996</v>
+      </c>
+      <c r="K22" s="115" t="s">
         <v>997</v>
-      </c>
-      <c r="K22" s="115" t="s">
-        <v>998</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -12128,7 +12173,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="K23" s="115" t="s">
         <v>594</v>
@@ -12167,10 +12212,10 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -12183,7 +12228,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>369</v>
@@ -12208,10 +12253,10 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -12249,10 +12294,10 @@
         <v>11.9</v>
       </c>
       <c r="J26" s="115" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K26" s="115" t="s">
         <v>1003</v>
-      </c>
-      <c r="K26" s="115" t="s">
-        <v>1004</v>
       </c>
       <c r="L26" s="114"/>
       <c r="M26" s="114"/>
@@ -12290,10 +12335,10 @@
         <v>3.3</v>
       </c>
       <c r="J27" s="115" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K27" s="115" t="s">
         <v>1005</v>
-      </c>
-      <c r="K27" s="115" t="s">
-        <v>1006</v>
       </c>
       <c r="L27" s="114"/>
       <c r="M27" s="114" t="s">
@@ -12331,10 +12376,10 @@
         <v>10.7</v>
       </c>
       <c r="J28" s="115" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K28" s="115" t="s">
         <v>1007</v>
-      </c>
-      <c r="K28" s="115" t="s">
-        <v>1008</v>
       </c>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
@@ -12372,10 +12417,10 @@
         <v>11.5</v>
       </c>
       <c r="J29" s="115" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K29" s="115" t="s">
         <v>1009</v>
-      </c>
-      <c r="K29" s="115" t="s">
-        <v>1010</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -12402,82 +12447,82 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="107" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="107" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="107" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="118" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -12488,7 +12533,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12508,27 +12553,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12585,7 +12630,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>293</v>
@@ -12606,17 +12651,17 @@
         <v>150</v>
       </c>
       <c r="I11" s="114">
-        <f t="shared" ref="I11:I20" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
+        <f t="shared" ref="I11:I21" si="0">IF(E11=0,0,ROUND((E11*(G11+H11)+N11)/60,1))</f>
         <v>12.7</v>
       </c>
       <c r="J11" s="115" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K11" s="115" t="s">
         <v>1031</v>
       </c>
-      <c r="K11" s="115" t="s">
+      <c r="L11" s="114" t="s">
         <v>1032</v>
-      </c>
-      <c r="L11" s="114" t="s">
-        <v>1033</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -12651,13 +12696,13 @@
         <v>9.5</v>
       </c>
       <c r="J12" s="115" t="s">
+        <v>1033</v>
+      </c>
+      <c r="K12" s="115" t="s">
         <v>1034</v>
       </c>
-      <c r="K12" s="115" t="s">
+      <c r="L12" s="114" t="s">
         <v>1035</v>
-      </c>
-      <c r="L12" s="114" t="s">
-        <v>1036</v>
       </c>
       <c r="M12" s="114"/>
       <c r="N12" s="114"/>
@@ -12667,35 +12712,35 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>483</v>
+        <v>1406</v>
       </c>
       <c r="C13" s="114" t="s">
-        <v>278</v>
+        <v>1407</v>
       </c>
       <c r="D13" s="114">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E13" s="114">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>289</v>
+        <v>1408</v>
       </c>
       <c r="G13" s="114">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H13" s="114">
         <v>120</v>
       </c>
       <c r="I13" s="114">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f t="shared" ref="I13" si="1">IF(E13=0,0,ROUND((E13*(G13+H13)+N13)/60,1))</f>
+        <v>5.3</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1037</v>
+        <v>1409</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1038</v>
+        <v>1410</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -12706,134 +12751,132 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C14" s="114" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="D14" s="114">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E14" s="114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="114" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="G14" s="114">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H14" s="114">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="I14" s="114">
         <f t="shared" si="0"/>
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1039</v>
+        <v>1411</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
-      <c r="N14" s="114">
-        <v>60</v>
-      </c>
+      <c r="N14" s="114"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
       <c r="A15" s="114">
         <v>5</v>
       </c>
       <c r="B15" s="115" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C15" s="114" t="s">
-        <v>418</v>
+        <v>293</v>
       </c>
       <c r="D15" s="114">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E15" s="114">
         <v>3</v>
       </c>
       <c r="F15" s="114" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="G15" s="114">
         <v>40</v>
       </c>
       <c r="H15" s="114">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I15" s="114">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
+      <c r="N15" s="114">
+        <v>60</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1">
       <c r="A16" s="114">
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>372</v>
+        <v>495</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>356</v>
+        <v>418</v>
       </c>
       <c r="D16" s="114">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E16" s="114">
         <v>3</v>
       </c>
       <c r="F16" s="114" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
       <c r="G16" s="114">
         <v>40</v>
       </c>
       <c r="H16" s="114">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="0"/>
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
-      <c r="N16" s="114">
-        <v>60</v>
-      </c>
+      <c r="N16" s="114"/>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1">
       <c r="A17" s="114">
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>492</v>
+        <v>372</v>
       </c>
       <c r="C17" s="114" t="s">
-        <v>280</v>
+        <v>356</v>
       </c>
       <c r="D17" s="114">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E17" s="114">
         <v>3</v>
@@ -12852,10 +12895,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12868,48 +12911,48 @@
         <v>8</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>1047</v>
+        <v>492</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="D18" s="114">
-        <v>7.5</v>
+        <v>30</v>
       </c>
       <c r="E18" s="114">
         <v>3</v>
       </c>
-      <c r="F18" s="114">
-        <v>15</v>
+      <c r="F18" s="114" t="s">
+        <v>285</v>
       </c>
       <c r="G18" s="114">
         <v>40</v>
       </c>
       <c r="H18" s="114">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="I18" s="114">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="L18" s="114"/>
-      <c r="M18" s="114" t="s">
-        <v>402</v>
-      </c>
-      <c r="N18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114">
+        <v>60</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="30" customHeight="1">
       <c r="A19" s="114">
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>605</v>
+        <v>1045</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>306</v>
@@ -12927,17 +12970,17 @@
         <v>40</v>
       </c>
       <c r="H19" s="114">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I19" s="114">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114" t="s">
@@ -12950,19 +12993,19 @@
         <v>10</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>329</v>
+        <v>605</v>
       </c>
       <c r="C20" s="114" t="s">
-        <v>324</v>
-      </c>
-      <c r="D20" s="114" t="s">
-        <v>294</v>
+        <v>306</v>
+      </c>
+      <c r="D20" s="114">
+        <v>7.5</v>
       </c>
       <c r="E20" s="114">
         <v>3</v>
       </c>
-      <c r="F20" s="114" t="s">
-        <v>300</v>
+      <c r="F20" s="114">
+        <v>15</v>
       </c>
       <c r="G20" s="114">
         <v>40</v>
@@ -12975,142 +13018,183 @@
         <v>5</v>
       </c>
       <c r="J20" s="115" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K20" s="115" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114" t="s">
+        <v>402</v>
+      </c>
+      <c r="N20" s="114"/>
+    </row>
+    <row r="21" spans="1:14" ht="30" customHeight="1">
+      <c r="A21" s="114">
+        <v>11</v>
+      </c>
+      <c r="B21" s="115" t="s">
+        <v>329</v>
+      </c>
+      <c r="C21" s="114" t="s">
+        <v>324</v>
+      </c>
+      <c r="D21" s="114" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" s="114">
+        <v>3</v>
+      </c>
+      <c r="F21" s="114" t="s">
+        <v>300</v>
+      </c>
+      <c r="G21" s="114">
+        <v>40</v>
+      </c>
+      <c r="H21" s="114">
+        <v>60</v>
+      </c>
+      <c r="I21" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="115" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K21" s="115" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="114"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116" t="s">
+        <v>332</v>
+      </c>
+      <c r="E22" s="116">
+        <f>SUM(E11:E21)</f>
+        <v>32</v>
+      </c>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116">
+        <f>ROUND(SUM(I11:I21),0)</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="107" t="s">
         <v>1052</v>
-      </c>
-      <c r="K20" s="115" t="s">
-        <v>1053</v>
-      </c>
-      <c r="L20" s="114"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="114"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="116"/>
-      <c r="B21" s="116"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116" t="s">
-        <v>332</v>
-      </c>
-      <c r="E21" s="116">
-        <f>SUM(E11:E20)</f>
-        <v>32</v>
-      </c>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116">
-        <f>ROUND(SUM(I11:I20),0)</f>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="107" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="117" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="107" t="s">
-        <v>1060</v>
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="117" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="117" t="s">
-        <v>1061</v>
+      <c r="A31" s="107" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="117" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="117" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="107" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="117" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="117" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="117" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="107" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="117" t="s">
         <v>1062</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="117" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="117" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="107" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="117" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="117" t="s">
         <v>1064</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="117" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="117" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="117" t="s">
         <v>1065</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="117" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="117" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="118" t="s">
         <v>1066</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="107" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="117" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="117" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="117" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="117" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="117" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="117" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="C48" s="118" t="s">
-        <v>1072</v>
       </c>
     </row>
   </sheetData>
@@ -13141,7 +13225,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -13227,7 +13311,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="110" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -13315,13 +13399,13 @@
         <v>15.3</v>
       </c>
       <c r="J18" s="113" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="K18" s="113" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="L18" s="112" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="M18" s="112"/>
       <c r="N18" s="112"/>
@@ -13356,10 +13440,10 @@
         <v>9.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13395,10 +13479,10 @@
         <v>7.3</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13434,13 +13518,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="L21" s="114" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13450,13 +13534,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>365</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="E22" s="114">
         <v>4</v>
@@ -13475,10 +13559,10 @@
         <v>8</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13489,19 +13573,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="115" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C23" s="114" t="s">
         <v>1384</v>
       </c>
-      <c r="C23" s="114" t="s">
-        <v>1392</v>
-      </c>
       <c r="D23" s="114" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
       <c r="G23" s="114">
         <v>60</v>
@@ -13514,10 +13598,10 @@
         <v>6</v>
       </c>
       <c r="J23" s="115" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K23" s="115" t="s">
         <v>1386</v>
-      </c>
-      <c r="K23" s="115" t="s">
-        <v>1394</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13528,19 +13612,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="115" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
       <c r="D24" s="114" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="E24" s="114">
         <v>3</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
       <c r="G24" s="114">
         <v>40</v>
@@ -13553,10 +13637,10 @@
         <v>6</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -13569,10 +13653,10 @@
         <v>8</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
       <c r="C25" s="114" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
       <c r="D25" s="114">
         <v>30</v>
@@ -13581,7 +13665,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="114" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
       <c r="G25" s="114">
         <v>40</v>
@@ -13594,10 +13678,10 @@
         <v>3.3</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -13624,77 +13708,77 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="107" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="107" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="117" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="107" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1411</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="107" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="117" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="C46" s="118" t="s">
-        <v>1398</v>
+        <v>1390</v>
       </c>
     </row>
   </sheetData>
@@ -13725,22 +13809,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13827,10 +13911,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13868,10 +13952,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13907,10 +13991,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -13921,7 +14005,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>306</v>
@@ -13946,10 +14030,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114" t="s">
@@ -13987,10 +14071,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114" t="s">
@@ -14003,10 +14087,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D16" s="114">
         <v>2.5</v>
@@ -14028,10 +14112,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -14042,10 +14126,10 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="C17" s="114" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D17" s="114">
         <v>2.5</v>
@@ -14067,10 +14151,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -14106,10 +14190,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -14145,10 +14229,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -14175,127 +14259,127 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="107" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="107" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="117" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -15007,7 +15091,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -15088,7 +15172,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -15164,22 +15248,22 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="110" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -15267,10 +15351,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="K28" s="113" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -15281,7 +15365,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>324</v>
@@ -15307,10 +15391,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="K29" s="115" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -15327,7 +15411,7 @@
         <v>395</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -15346,10 +15430,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="K30" s="115" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -15360,7 +15444,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>386</v>
@@ -15385,10 +15469,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="K31" s="115" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -15424,10 +15508,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="K32" s="115" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -15438,7 +15522,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>440</v>
@@ -15464,10 +15548,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="K33" s="113" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>518</v>
@@ -15505,10 +15589,10 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="K34" s="115" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="L34" s="114"/>
       <c r="M34" s="114"/>
@@ -15546,10 +15630,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="K35" s="115" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15585,10 +15669,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="K36" s="115" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15624,10 +15708,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15663,10 +15747,10 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="K38" s="115" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
@@ -15704,10 +15788,10 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
@@ -15745,10 +15829,10 @@
         <v>11.5</v>
       </c>
       <c r="J40" s="115" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="K40" s="115" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15775,167 +15859,167 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="107" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="107" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="117" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
     </row>
   </sheetData>
@@ -15966,27 +16050,27 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="110" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -16068,13 +16152,13 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="K11" s="115" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="L11" s="114" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M11" s="114"/>
       <c r="N11" s="114"/>
@@ -16084,7 +16168,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>278</v>
@@ -16109,10 +16193,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="K12" s="115" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -16123,7 +16207,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>278</v>
@@ -16148,10 +16232,10 @@
         <v>11.7</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -16189,10 +16273,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -16228,10 +16312,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -16267,10 +16351,10 @@
         <v>9.5</v>
       </c>
       <c r="J16" s="115" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="K16" s="115" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -16306,10 +16390,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J17" s="115" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="K17" s="115" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -16345,10 +16429,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="K18" s="115" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -16361,7 +16445,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>356</v>
@@ -16386,10 +16470,10 @@
         <v>5.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="K19" s="115" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -16400,7 +16484,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>280</v>
@@ -16425,10 +16509,10 @@
         <v>5.8</v>
       </c>
       <c r="J20" s="115" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -16439,7 +16523,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="115" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C21" s="114" t="s">
         <v>306</v>
@@ -16464,10 +16548,10 @@
         <v>2.5</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114" t="s">
@@ -16505,10 +16589,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114" t="s">
@@ -16546,10 +16630,10 @@
         <v>6.7</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -16576,112 +16660,112 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="107" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="107" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="107" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="117" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
     </row>
   </sheetData>
@@ -16761,10 +16845,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="D7" s="115" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
@@ -17068,7 +17152,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -17082,12 +17166,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -17095,18 +17179,18 @@
         <v>646</v>
       </c>
       <c r="F3" s="107">
-        <f ca="1">COUNTIF($E$7:$E$91,"?")</f>
+        <f ca="1">COUNTIF($E$7:$E$93,"?")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>649</v>
@@ -17132,7 +17216,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>95</v>
@@ -17144,23 +17228,23 @@
         <v>0.33</v>
       </c>
       <c r="E7" s="114">
-        <f t="shared" ref="E7:E38" ca="1" si="0">IFERROR(INDEX(INDIRECT("'"&amp;$A7&amp;"'!$E$1:$E$60"),MATCH($B7,INDIRECT("'"&amp;$A7&amp;"'!$B$1:$B$60"),0)),"?")</f>
+        <f t="shared" ref="E7:E39" ca="1" si="0">IFERROR(INDEX(INDIRECT("'"&amp;$A7&amp;"'!$E$1:$E$60"),MATCH($B7,INDIRECT("'"&amp;$A7&amp;"'!$B$1:$B$60"),0)),"?")</f>
         <v>4</v>
       </c>
       <c r="F7" s="114">
-        <f t="shared" ref="F7:F38" ca="1" si="1">IF(ISNUMBER(E7),$D7*E7,0)</f>
+        <f t="shared" ref="F7:F39" ca="1" si="1">IF(ISNUMBER(E7),$D7*E7,0)</f>
         <v>1.32</v>
       </c>
       <c r="G7" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>528</v>
@@ -17183,12 +17267,12 @@
         <v>670</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>354</v>
@@ -17211,12 +17295,12 @@
         <v>670</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>519</v>
@@ -17239,15 +17323,15 @@
         <v>670</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>356</v>
@@ -17267,12 +17351,12 @@
         <v>670</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>277</v>
@@ -17295,15 +17379,15 @@
         <v>670</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>280</v>
@@ -17323,15 +17407,15 @@
         <v>670</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>280</v>
@@ -17351,12 +17435,12 @@
         <v>670</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>483</v>
@@ -17369,81 +17453,81 @@
       </c>
       <c r="E15" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>0.66</v>
       </c>
       <c r="G15" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="25.5">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="51">
       <c r="A16" s="114" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1030</v>
+        <v>1406</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>280</v>
       </c>
       <c r="D16" s="114">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E16" s="114">
         <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F16" s="114">
+        <f t="shared" ref="F16" ca="1" si="2">IF(ISNUMBER(E16),$D16*E16,0)</f>
+        <v>0.66</v>
+      </c>
+      <c r="G16" s="114" t="s">
+        <v>670</v>
+      </c>
+      <c r="H16" s="115" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="25.5">
+      <c r="A17" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B17" s="115" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C17" s="114" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" s="114">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="114">
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="114">
+      <c r="F17" s="114">
         <f t="shared" ca="1" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G16" s="114" t="s">
-        <v>670</v>
-      </c>
-      <c r="H16" s="115" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="38.25">
-      <c r="A17" s="114" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B17" s="115" t="s">
-        <v>476</v>
-      </c>
-      <c r="C17" s="114" t="s">
-        <v>280</v>
-      </c>
-      <c r="D17" s="114">
-        <v>0.2</v>
-      </c>
-      <c r="E17" s="114">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="F17" s="114">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
-      </c>
       <c r="G17" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="25.5">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="38.25">
       <c r="A18" s="114" t="s">
-        <v>1268</v>
+        <v>1258</v>
       </c>
       <c r="B18" s="115" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="C18" s="114" t="s">
         <v>280</v>
@@ -17463,77 +17547,77 @@
         <v>670</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>95</v>
+        <v>450</v>
       </c>
       <c r="C19" s="114" t="s">
-        <v>440</v>
+        <v>280</v>
       </c>
       <c r="D19" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E19" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G19" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="25.5">
       <c r="A20" s="114" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>528</v>
+        <v>95</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>440</v>
       </c>
       <c r="D20" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E20" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="G20" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B21" s="115" t="s">
-        <v>354</v>
+        <v>528</v>
       </c>
       <c r="C21" s="114" t="s">
         <v>440</v>
       </c>
       <c r="D21" s="114">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E21" s="114">
         <f t="shared" ca="1" si="0"/>
@@ -17541,21 +17625,21 @@
       </c>
       <c r="F21" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>1.5</v>
       </c>
       <c r="G21" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>597</v>
+        <v>354</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>440</v>
@@ -17575,15 +17659,15 @@
         <v>670</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1260</v>
+        <v>1247</v>
       </c>
       <c r="B23" s="115" t="s">
-        <v>438</v>
+        <v>597</v>
       </c>
       <c r="C23" s="114" t="s">
         <v>440</v>
@@ -17593,56 +17677,56 @@
       </c>
       <c r="E23" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G23" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="25.5">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B24" s="115" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C24" s="114" t="s">
         <v>440</v>
       </c>
       <c r="D24" s="114">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E24" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G24" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5">
       <c r="A25" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B25" s="115" t="s">
         <v>433</v>
       </c>
       <c r="C25" s="114" t="s">
-        <v>356</v>
+        <v>440</v>
       </c>
       <c r="D25" s="114">
         <v>0.5</v>
@@ -17659,18 +17743,18 @@
         <v>670</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B26" s="115" t="s">
-        <v>299</v>
+        <v>433</v>
       </c>
       <c r="C26" s="114" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D26" s="114">
         <v>0.5</v>
@@ -17687,21 +17771,21 @@
         <v>670</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="38.25">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>1157</v>
+        <v>299</v>
       </c>
       <c r="C27" s="114" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D27" s="114">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E27" s="114">
         <f t="shared" ca="1" si="0"/>
@@ -17709,21 +17793,21 @@
       </c>
       <c r="F27" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G27" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="38.25">
       <c r="A28" s="114" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>519</v>
+        <v>1151</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>365</v>
@@ -17743,49 +17827,49 @@
         <v>670</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="25.5">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="38.25">
       <c r="A29" s="114" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1152</v>
+        <v>519</v>
       </c>
       <c r="C29" s="114" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D29" s="114">
         <v>0.33</v>
       </c>
       <c r="E29" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="G29" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="25.5">
       <c r="A30" s="114" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="B30" s="115" t="s">
-        <v>1030</v>
+        <v>1146</v>
       </c>
       <c r="C30" s="114" t="s">
-        <v>278</v>
+        <v>380</v>
       </c>
       <c r="D30" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E30" s="114">
         <f t="shared" ca="1" si="0"/>
@@ -17793,21 +17877,21 @@
       </c>
       <c r="F30" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="G30" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25.5">
       <c r="A31" s="114" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>476</v>
+        <v>1029</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>278</v>
@@ -17817,81 +17901,81 @@
       </c>
       <c r="E31" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G31" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="25.5">
       <c r="A32" s="114" t="s">
         <v>1258</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>93</v>
+        <v>476</v>
       </c>
       <c r="C32" s="114" t="s">
         <v>278</v>
       </c>
       <c r="D32" s="114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E32" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G32" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="114" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B33" s="115" t="s">
-        <v>1157</v>
+        <v>93</v>
       </c>
       <c r="C33" s="114" t="s">
-        <v>418</v>
+        <v>278</v>
       </c>
       <c r="D33" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G33" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="B34" s="115" t="s">
-        <v>1030</v>
+        <v>1151</v>
       </c>
       <c r="C34" s="114" t="s">
         <v>418</v>
@@ -17901,81 +17985,81 @@
       </c>
       <c r="E34" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G34" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="25.5">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
         <v>1258</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>93</v>
+        <v>1029</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>418</v>
       </c>
       <c r="D35" s="114">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E35" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G35" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="25.5">
       <c r="A36" s="114" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>277</v>
+        <v>93</v>
       </c>
       <c r="C36" s="114" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="D36" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G36" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>1208</v>
+        <v>277</v>
       </c>
       <c r="C37" s="114" t="s">
         <v>429</v>
@@ -17995,15 +18079,15 @@
         <v>670</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="C38" s="114" t="s">
         <v>429</v>
@@ -18023,15 +18107,15 @@
         <v>670</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="25.5">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1264</v>
+        <v>1254</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>476</v>
+        <v>1199</v>
       </c>
       <c r="C39" s="114" t="s">
         <v>429</v>
@@ -18040,54 +18124,54 @@
         <v>0.2</v>
       </c>
       <c r="E39" s="114">
-        <f t="shared" ref="E39:E71" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$60"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$60"),0)),"?")</f>
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="F39" s="114">
-        <f t="shared" ref="F39:F71" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
-        <v>0.60000000000000009</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="G39" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="38.25">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="25.5">
       <c r="A40" s="114" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="B40" s="115" t="s">
-        <v>1384</v>
+        <v>476</v>
       </c>
       <c r="C40" s="114" t="s">
-        <v>293</v>
+        <v>429</v>
       </c>
       <c r="D40" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E40" s="114">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ref="E40:E73" ca="1" si="3">IFERROR(INDEX(INDIRECT("'"&amp;$A40&amp;"'!$E$1:$E$60"),MATCH($B40,INDIRECT("'"&amp;$A40&amp;"'!$B$1:$B$60"),0)),"?")</f>
         <v>3</v>
       </c>
       <c r="F40" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <f t="shared" ref="F40:F73" ca="1" si="4">IF(ISNUMBER(E40),$D40*E40,0)</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G40" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="38.25">
       <c r="A41" s="114" t="s">
-        <v>1258</v>
+        <v>1247</v>
       </c>
       <c r="B41" s="115" t="s">
-        <v>534</v>
+        <v>1376</v>
       </c>
       <c r="C41" s="114" t="s">
         <v>293</v>
@@ -18096,26 +18180,26 @@
         <v>0.33</v>
       </c>
       <c r="E41" s="114">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>3</v>
       </c>
       <c r="F41" s="114">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0.99</v>
       </c>
       <c r="G41" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1291</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="114" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="B42" s="115" t="s">
-        <v>1001</v>
+        <v>534</v>
       </c>
       <c r="C42" s="114" t="s">
         <v>293</v>
@@ -18124,26 +18208,26 @@
         <v>0.33</v>
       </c>
       <c r="E42" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F42" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.99</v>
       </c>
       <c r="G42" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="25.5">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1399</v>
+        <v>1251</v>
       </c>
       <c r="B43" s="115" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C43" s="114" t="s">
         <v>293</v>
@@ -18152,250 +18236,250 @@
         <v>0.33</v>
       </c>
       <c r="E43" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
       <c r="F43" s="114">
-        <f t="shared" ref="F43" ca="1" si="4">IF(ISNUMBER(E43),$D43*E43,0)</f>
-        <v>0.66</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.32</v>
       </c>
       <c r="G43" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="25.5">
       <c r="A44" s="114" t="s">
-        <v>1264</v>
+        <v>1391</v>
       </c>
       <c r="B44" s="115" t="s">
-        <v>483</v>
+        <v>1000</v>
       </c>
       <c r="C44" s="114" t="s">
         <v>293</v>
       </c>
       <c r="D44" s="114">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E44" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="F44" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>2</v>
       </c>
+      <c r="F44" s="114">
+        <f t="shared" ref="F44" ca="1" si="5">IF(ISNUMBER(E44),$D44*E44,0)</f>
+        <v>0.66</v>
+      </c>
       <c r="G44" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="38.25">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="114" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B45" s="115" t="s">
-        <v>91</v>
+        <v>483</v>
       </c>
       <c r="C45" s="114" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="D45" s="114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E45" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
       <c r="F45" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G45" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="B46" s="115" t="s">
-        <v>1030</v>
+        <v>1406</v>
       </c>
       <c r="C46" s="114" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="D46" s="114">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E46" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
       <c r="F46" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <f t="shared" ref="F46" ca="1" si="6">IF(ISNUMBER(E46),$D46*E46,0)</f>
+        <v>1</v>
       </c>
       <c r="G46" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="38.25">
       <c r="A47" s="114" t="s">
-        <v>1260</v>
+        <v>1251</v>
       </c>
       <c r="B47" s="115" t="s">
-        <v>428</v>
+        <v>91</v>
       </c>
       <c r="C47" s="114" t="s">
         <v>324</v>
       </c>
       <c r="D47" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E47" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
       <c r="F47" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G47" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H47" s="115" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="51">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
         <v>1258</v>
       </c>
       <c r="B48" s="115" t="s">
-        <v>570</v>
+        <v>1029</v>
       </c>
       <c r="C48" s="114" t="s">
         <v>324</v>
       </c>
       <c r="D48" s="114">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E48" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
       <c r="F48" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.8</v>
       </c>
       <c r="G48" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="25.5">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1264</v>
+        <v>1254</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>495</v>
+        <v>428</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>324</v>
       </c>
       <c r="D49" s="114">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E49" s="114">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>3</v>
       </c>
       <c r="F49" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="51">
       <c r="A50" s="114" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="B50" s="115" t="s">
-        <v>91</v>
+        <v>570</v>
       </c>
       <c r="C50" s="114" t="s">
-        <v>386</v>
+        <v>324</v>
       </c>
       <c r="D50" s="114">
         <v>0.5</v>
       </c>
       <c r="E50" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F50" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>2.5</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.5</v>
       </c>
       <c r="G50" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H50" s="115" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="25.5">
       <c r="A51" s="114" t="s">
         <v>1258</v>
       </c>
       <c r="B51" s="115" t="s">
-        <v>93</v>
+        <v>495</v>
       </c>
       <c r="C51" s="114" t="s">
-        <v>386</v>
+        <v>324</v>
       </c>
       <c r="D51" s="114">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E51" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F51" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.5</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G51" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="114" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="B52" s="115" t="s">
-        <v>1146</v>
+        <v>91</v>
       </c>
       <c r="C52" s="114" t="s">
         <v>386</v>
@@ -18404,54 +18488,54 @@
         <v>0.5</v>
       </c>
       <c r="E52" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
       <c r="F52" s="114">
+        <f t="shared" ca="1" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="G52" s="114" t="s">
+        <v>670</v>
+      </c>
+      <c r="H52" s="115" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="114" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B53" s="115" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="114" t="s">
+        <v>386</v>
+      </c>
+      <c r="D53" s="114">
+        <v>0.5</v>
+      </c>
+      <c r="E53" s="114">
         <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
-      <c r="G52" s="114" t="s">
-        <v>670</v>
-      </c>
-      <c r="H52" s="115" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="114" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B53" s="115" t="s">
-        <v>385</v>
-      </c>
-      <c r="C53" s="114" t="s">
-        <v>386</v>
-      </c>
-      <c r="D53" s="114">
-        <v>0.33</v>
-      </c>
-      <c r="E53" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
       <c r="F53" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.5</v>
       </c>
       <c r="G53" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>693</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="114" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>570</v>
+        <v>1140</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>386</v>
@@ -18460,194 +18544,194 @@
         <v>0.5</v>
       </c>
       <c r="E54" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
       <c r="F54" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G54" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="38.25">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="114" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="B55" s="115" t="s">
-        <v>567</v>
+        <v>385</v>
       </c>
       <c r="C55" s="114" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D55" s="114">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E55" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
       <c r="F55" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.32</v>
       </c>
       <c r="G55" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H55" s="115" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="38.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="114" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B56" s="115" t="s">
-        <v>93</v>
+        <v>570</v>
       </c>
       <c r="C56" s="114" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D56" s="114">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E56" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F56" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.33</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.5</v>
       </c>
       <c r="G56" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="25.5">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="38.25">
       <c r="A57" s="114" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B57" s="115" t="s">
-        <v>1146</v>
+        <v>567</v>
       </c>
       <c r="C57" s="114" t="s">
         <v>395</v>
       </c>
       <c r="D57" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E57" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F57" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.66</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G57" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="51">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="38.25">
       <c r="A58" s="114" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B58" s="115" t="s">
-        <v>1152</v>
+        <v>93</v>
       </c>
       <c r="C58" s="114" t="s">
         <v>395</v>
       </c>
       <c r="D58" s="114">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E58" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F58" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.33</v>
       </c>
       <c r="G58" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="38.25">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="25.5">
       <c r="A59" s="114" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="B59" s="115" t="s">
-        <v>91</v>
+        <v>1140</v>
       </c>
       <c r="C59" s="114" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D59" s="114">
         <v>0.33</v>
       </c>
       <c r="E59" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
       <c r="F59" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.66</v>
       </c>
       <c r="G59" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H59" s="115" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="25.5">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="51">
       <c r="A60" s="114" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="B60" s="115" t="s">
-        <v>385</v>
+        <v>1146</v>
       </c>
       <c r="C60" s="114" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D60" s="114">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E60" s="114">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>4</v>
       </c>
       <c r="F60" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.8</v>
       </c>
       <c r="G60" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H60" s="115" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="25.5">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="38.25">
       <c r="A61" s="114" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="B61" s="115" t="s">
-        <v>1152</v>
+        <v>91</v>
       </c>
       <c r="C61" s="114" t="s">
         <v>399</v>
@@ -18656,82 +18740,82 @@
         <v>0.33</v>
       </c>
       <c r="E61" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
       <c r="F61" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>1.32</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G61" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="25.5">
       <c r="A62" s="114" t="s">
-        <v>1264</v>
+        <v>1251</v>
       </c>
       <c r="B62" s="115" t="s">
-        <v>492</v>
+        <v>385</v>
       </c>
       <c r="C62" s="114" t="s">
-        <v>306</v>
+        <v>399</v>
       </c>
       <c r="D62" s="114">
         <v>0.33</v>
       </c>
       <c r="E62" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
       <c r="F62" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.32</v>
       </c>
       <c r="G62" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
       <c r="B63" s="115" t="s">
-        <v>602</v>
+        <v>1146</v>
       </c>
       <c r="C63" s="114" t="s">
-        <v>306</v>
+        <v>399</v>
       </c>
       <c r="D63" s="114">
         <v>0.33</v>
       </c>
       <c r="E63" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
       <c r="F63" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.32</v>
       </c>
       <c r="G63" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>673</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="114" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B64" s="115" t="s">
-        <v>1224</v>
+        <v>492</v>
       </c>
       <c r="C64" s="114" t="s">
         <v>306</v>
@@ -18740,214 +18824,270 @@
         <v>0.33</v>
       </c>
       <c r="E64" s="114">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>3</v>
       </c>
       <c r="F64" s="114">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0.99</v>
       </c>
       <c r="G64" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H64" s="115" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="38.25">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="B65" s="115" t="s">
-        <v>95</v>
+        <v>602</v>
       </c>
       <c r="C65" s="114" t="s">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="D65" s="114">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E65" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F65" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.99</v>
       </c>
       <c r="G65" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H65" s="115" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="25.5">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B66" s="115" t="s">
-        <v>438</v>
+        <v>1218</v>
       </c>
       <c r="C66" s="114" t="s">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="D66" s="114">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E66" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F66" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.99</v>
       </c>
       <c r="G66" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="25.5">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="38.25">
       <c r="A67" s="114" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B67" s="115" t="s">
-        <v>528</v>
+        <v>95</v>
       </c>
       <c r="C67" s="114" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="D67" s="114">
         <v>0</v>
       </c>
       <c r="E67" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
       <c r="F67" s="114">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G67" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B68" s="115" t="s">
-        <v>597</v>
+        <v>438</v>
       </c>
       <c r="C68" s="114" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="D68" s="114">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E68" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
       <c r="F68" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G68" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="25.5">
       <c r="A69" s="114" t="s">
-        <v>1257</v>
+        <v>1247</v>
       </c>
       <c r="B69" s="115" t="s">
-        <v>91</v>
+        <v>528</v>
       </c>
       <c r="C69" s="114" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="D69" s="114">
         <v>0</v>
       </c>
       <c r="E69" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F69" s="114">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G69" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H69" s="115" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="114" t="s">
-        <v>1257</v>
+        <v>1247</v>
       </c>
       <c r="B70" s="115" t="s">
-        <v>499</v>
+        <v>597</v>
       </c>
       <c r="C70" s="114" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="D70" s="114">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E70" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
       <c r="F70" s="114">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G70" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H70" s="115" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="25.5">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="114" t="s">
-        <v>1268</v>
+        <v>1251</v>
       </c>
       <c r="B71" s="115" t="s">
-        <v>1107</v>
+        <v>91</v>
       </c>
       <c r="C71" s="114" t="s">
-        <v>934</v>
+        <v>310</v>
       </c>
       <c r="D71" s="114">
         <v>0</v>
       </c>
       <c r="E71" s="114">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
       <c r="F71" s="114">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G71" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H71" s="115" t="s">
-        <v>1315</v>
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="114" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B72" s="115" t="s">
+        <v>499</v>
+      </c>
+      <c r="C72" s="114" t="s">
+        <v>319</v>
+      </c>
+      <c r="D72" s="114">
+        <v>0</v>
+      </c>
+      <c r="E72" s="114">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="F72" s="114">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="114" t="s">
+        <v>670</v>
+      </c>
+      <c r="H72" s="115" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="25.5">
+      <c r="A73" s="114" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B73" s="115" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C73" s="114" t="s">
+        <v>933</v>
+      </c>
+      <c r="D73" s="114">
+        <v>0</v>
+      </c>
+      <c r="E73" s="114">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F73" s="114">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="114" t="s">
+        <v>670</v>
+      </c>
+      <c r="H73" s="115" t="s">
+        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -18972,12 +19112,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -19009,7 +19149,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A5),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A5),0.5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="114">
@@ -19021,7 +19161,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>749</v>
@@ -19040,7 +19180,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A6),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A6),0.5)</f>
         <v>0.5</v>
       </c>
       <c r="D6" s="114">
@@ -19052,7 +19192,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -19064,7 +19204,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A7),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A7),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D7" s="114">
@@ -19076,10 +19216,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1320</v>
+        <v>1417</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -19095,7 +19235,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A8),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A8),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D8" s="114">
@@ -19107,13 +19247,13 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
       <c r="H8" s="124" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
       <c r="I8" s="125">
-        <f>SUM(복귀_일_수평당기기!E11:E14,복귀_목_수직당기기!E11:E13)</f>
+        <f>SUM(복귀_일_수평당기기!E11:E15,복귀_목_수직당기기!E11:E13)</f>
         <v>26</v>
       </c>
     </row>
@@ -19126,7 +19266,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A9),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A9),0.5)</f>
         <v>3</v>
       </c>
       <c r="D9" s="114">
@@ -19138,7 +19278,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1324</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -19150,7 +19290,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A10),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A10),0.5)</f>
         <v>6</v>
       </c>
       <c r="D10" s="114">
@@ -19162,7 +19302,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1325</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -19174,7 +19314,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A11),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A11),0.5)</f>
         <v>3</v>
       </c>
       <c r="D11" s="114">
@@ -19186,7 +19326,7 @@
         <v>충분</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -19198,7 +19338,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A12),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A12),0.5)</f>
         <v>6.5</v>
       </c>
       <c r="D12" s="114">
@@ -19210,7 +19350,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -19222,7 +19362,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A13),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A13),0.5)</f>
         <v>2</v>
       </c>
       <c r="D13" s="114">
@@ -19234,7 +19374,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -19246,7 +19386,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A14),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A14),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D14" s="114">
@@ -19258,7 +19398,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -19270,7 +19410,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A15),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A15),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D15" s="114">
@@ -19282,10 +19422,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -19301,7 +19441,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A16),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A16),0.5)</f>
         <v>2.5</v>
       </c>
       <c r="D16" s="114">
@@ -19313,7 +19453,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -19325,7 +19465,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A17),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A17),0.5)</f>
         <v>7</v>
       </c>
       <c r="D17" s="114">
@@ -19337,7 +19477,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -19349,7 +19489,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="114">
-        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A18),0.5)</f>
+        <f>MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A18),0.5)</f>
         <v>0</v>
       </c>
       <c r="D18" s="114">
@@ -19361,7 +19501,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -19373,7 +19513,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A19),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A19),0.5)</f>
         <v>0</v>
       </c>
       <c r="D19" s="114">
@@ -19385,7 +19525,7 @@
         <v>충분</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -19397,7 +19537,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A20),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A20),0.5)</f>
         <v>8</v>
       </c>
       <c r="D20" s="114">
@@ -19409,7 +19549,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -19421,7 +19561,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A21),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A21),0.5)</f>
         <v>8.5</v>
       </c>
       <c r="D21" s="114">
@@ -19433,7 +19573,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -19445,7 +19585,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A22),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A22),0.5)</f>
         <v>3</v>
       </c>
       <c r="D22" s="114">
@@ -19457,7 +19597,7 @@
         <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -19469,7 +19609,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A23),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A23),0.5)</f>
         <v>0</v>
       </c>
       <c r="D23" s="114">
@@ -19481,7 +19621,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -19493,7 +19633,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A24),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A24),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D24" s="114">
@@ -19505,19 +19645,19 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
       <c r="A25" s="114" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B25" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A25)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A25)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A25)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A25)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A25)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A25)</f>
         <v>6</v>
       </c>
       <c r="C25" s="114">
-        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$91,복귀_간접계수맵!$C$7:$C$91,$A25),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A25),0.5)</f>
         <v>0</v>
       </c>
       <c r="D25" s="114">
@@ -19529,7 +19669,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -19552,192 +19692,192 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1347</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1357</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="107" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="123" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60AB3D08-F24F-4970-8076-F8DFB8E99E40}"/>
+  <xr:revisionPtr revIDLastSave="536" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23DB6200-7098-42C0-A00C-AD3043BC03A0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,11 @@
     <sheet name="복귀_화_팔" sheetId="19" r:id="rId19"/>
     <sheet name="복귀_수_하체후면" sheetId="20" r:id="rId20"/>
     <sheet name="복귀_목_수직당기기" sheetId="21" r:id="rId21"/>
-    <sheet name="복귀_증량원칙" sheetId="22" r:id="rId22"/>
-    <sheet name="복귀_간접계수맵" sheetId="23" r:id="rId23"/>
-    <sheet name="복귀_세트검산" sheetId="24" r:id="rId24"/>
+    <sheet name="복귀_캐리" sheetId="25" r:id="rId22"/>
+    <sheet name="복귀_계단" sheetId="26" r:id="rId23"/>
+    <sheet name="복귀_증량원칙" sheetId="22" r:id="rId24"/>
+    <sheet name="복귀_간접계수맵" sheetId="23" r:id="rId25"/>
+    <sheet name="복귀_세트검산" sheetId="24" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="1488">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -3157,9 +3159,6 @@
     <t>135/145/155/165</t>
   </si>
   <si>
-    <t>체스트 서포티드라 척추 부하가 0이다. 바벨 로우로 쓴 기립근을 더 쓰지 않고 수평 볼륨을 쌓는 자리다.</t>
-  </si>
-  <si>
     <t>시티드 케이블 로우 (넓은 그립) / 머신 로우 / 티바 로우</t>
   </si>
   <si>
@@ -3713,9 +3712,6 @@
   </si>
   <si>
     <t>케이블 드래그 컬</t>
-  </si>
-  <si>
-    <t>팔꿈치를 뒤로 끌며 당겨 전면 삼각 개입을 줄인다. 프리쳐(짧아진) · 인클라인(늘어난)과 또 다른 자리다.</t>
   </si>
   <si>
     <t>케이블 컬 (전 구간 장력) / 머신 컬 / 바벨 컬</t>
@@ -4385,17 +4381,1358 @@
   <si>
     <t>약 486분 (8시간 6분)</t>
     <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">https://www.youtube.com/shorts/KGkE5bXQR24, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명치가</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의자</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최상단</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높이에</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞게</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">설정, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>https://www.youtube.com/shorts/W0TMqVIhpcQ</t>
+    </r>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/UerYVESPi_E</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>캐리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>무겁게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>들고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>걷기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>생수배송</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>대비</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · 2026-10-04 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>신설</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>목표: 한 손 36kg(2L 6병 묶음 3팩)을 손에서 놓치지 않고 컨트롤한다. 세트 카운트 · 세트검산에는 넣지 않는다.</t>
+  </si>
+  <si>
+    <t>규칙</t>
+  </si>
+  <si>
+    <t>토 · 수 — 하체 웨이트 끝나고 바로</t>
+  </si>
+  <si>
+    <t>힘든 날은 몰아서 힘들게. 하체 전날(화 · 금)은 피한다</t>
+  </si>
+  <si>
+    <t>파머스 워크(덤벨) / 트랩바 캐리</t>
+  </si>
+  <si>
+    <t>덤벨이 모자라면 트랩바에 원판 — 양손 72kg도 쉽게 만든다</t>
+  </si>
+  <si>
+    <t>양</t>
+  </si>
+  <si>
+    <t>30~40초 걷기 × 4, 휴식 120초</t>
+  </si>
+  <si>
+    <t>트럭 → 현관 구간이 이 길이다</t>
+  </si>
+  <si>
+    <t>시작</t>
+  </si>
+  <si>
+    <t>한 손 24kg</t>
+  </si>
+  <si>
+    <t>데드 80kg이라 드는 힘은 충분하고, 막히는 건 악력이다</t>
+  </si>
+  <si>
+    <t>증량</t>
+  </si>
+  <si>
+    <t>4번 다 안 놓치면 다음 주 한 손 +2kg</t>
+  </si>
+  <si>
+    <t>막힘 없으면 6주 만에 36kg, 현실적으로는 8~10주</t>
+  </si>
+  <si>
+    <t>스트랩</t>
+  </si>
+  <si>
+    <t>금지</t>
+  </si>
+  <si>
+    <t>이 연습의 목적이 악력이다 (계단에서는 허용)</t>
+  </si>
+  <si>
+    <t>무겁게는 주 2회까지</t>
+  </si>
+  <si>
+    <t>악력을 매일 무겁게 쓰면 회복이 안 돼 오히려 안 오른다. 나머지 날은 복귀_계단으로 채운다</t>
+  </si>
+  <si>
+    <t>재검토 조건</t>
+  </si>
+  <si>
+    <t>2주 연속 정체 · 팔꿈치 안쪽/바깥쪽 통증</t>
+  </si>
+  <si>
+    <t>통증이 나면 그날 증량 금지. 리스트컬(전완 24세트)은 이 조건일 때만 다시 꺼낸다</t>
+  </si>
+  <si>
+    <t>순서</t>
+  </si>
+  <si>
+    <t>캐리 → 계단(짧게)</t>
+  </si>
+  <si>
+    <t>악력이 신선할 때 무거운 걸 먼저</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>진행표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>주는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>토요일에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>넘어간다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>주</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>시작</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>손</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(kg)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>양손</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>합계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(kg)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>손</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(kg)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>메모</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>놓침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>통증</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>· 7주차에 36kg이 최선 경로다. 정체 주는 같은 무게를 반복하고 목표 칸을 한 줄씩 아래로 민다.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>계단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>천국의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>계단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>덤벨</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>생수배송</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>대비</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · 2026-10-04 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>신설</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>하루 종일 오르내리는 지구력. 무게는 12~16kg에서 멈춘다 — 36kg은 복귀_캐리 몫. 세트 카운트 · 세트검산에는 넣지 않는다.</t>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>메인 (캐리 뒤)</t>
+  </si>
+  <si>
+    <t>스쿼트 날 — 하체를 이미 쓴 날에 몰기</t>
+  </si>
+  <si>
+    <t>짧게</t>
+  </si>
+  <si>
+    <t>적응용</t>
+  </si>
+  <si>
+    <t>다음 날 데드리프트</t>
+  </si>
+  <si>
+    <t>데드 날 — 하체를 이미 쓴 날에 몰기</t>
+  </si>
+  <si>
+    <t>없음 (휴식)</t>
+  </si>
+  <si>
+    <t>다음 날 스쿼트</t>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>주</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>램프</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>휴식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>전부</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 60</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>초</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>덤벨</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>손</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(kg)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>메인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>분</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>메인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>세트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>짧은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>분</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>짧은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>세트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>메인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>작업분</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>짧은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>작업분</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>주간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>작업분</t>
+    </r>
+  </si>
+  <si>
+    <t>12~14</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>14~16</t>
+  </si>
+  <si>
+    <t>· 시간과 무게를 한 번에 둘 다 올리지 않는다. 범위 칸(12~14 등)은 '시간이 편해진 뒤 무게' 뜻이다.</t>
+  </si>
+  <si>
+    <t>· 다음 주로 넘어가는 기준은 날짜가 아니라 몸: 다음 날 하체 웨이트 중량이 유지되면 넘어가고, 떨어지면 그 주를 반복한다.</t>
+  </si>
+  <si>
+    <t>· 스트랩: 앞 세트는 맨손, 손이 풀리기 시작하면 스트랩. 실제 배달은 맨손 비닐 손잡이다.</t>
+  </si>
+  <si>
+    <t>· 안전: 손잡이를 못 잡으니 속도를 평소보다 1~2단계 낮춘다. 다리가 휘청이거나 덤벨이 미끄러지면 5분을 못 채워도 바로 끊는다.</t>
+  </si>
+  <si>
+    <t>· 아파트 비상계단에 덤벨 들고 오르내릴 수 있으면 그게 가장 실제와 비슷하다 — 내려오는 계단도 다리 부담이 크다.</t>
+  </si>
+  <si>
+    <t>· 4주차(메인 5분 × 6) 이후는 무게를 올리지 말고 유지한다. 배달 일이 시작되면 그 일이 이 시트를 대신한다.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="m\/d"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="63">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4776,8 +6113,53 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4838,6 +6220,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF404040"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -4908,7 +6296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5204,6 +6592,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="61" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -6151,7 +7554,7 @@
         <v>46228</v>
       </c>
       <c r="D59" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -6162,7 +7565,7 @@
         <v>46298</v>
       </c>
       <c r="D60" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -6230,12 +7633,12 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
   </sheetData>
@@ -6922,16 +8325,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="138" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
@@ -6943,16 +8346,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="136" t="s">
         <v>647</v>
       </c>
-      <c r="B4" s="128"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
@@ -9042,7 +10445,7 @@
       <c r="F5" s="53" t="s">
         <v>748</v>
       </c>
-      <c r="G5" s="130" t="s">
+      <c r="G5" s="139" t="s">
         <v>749</v>
       </c>
       <c r="H5" s="56">
@@ -9085,7 +10488,7 @@
       <c r="F6" s="53" t="s">
         <v>750</v>
       </c>
-      <c r="G6" s="131"/>
+      <c r="G6" s="140"/>
       <c r="J6" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>12.6</v>
@@ -9118,7 +10521,7 @@
       <c r="F7" s="53" t="s">
         <v>751</v>
       </c>
-      <c r="G7" s="130" t="s">
+      <c r="G7" s="139" t="s">
         <v>752</v>
       </c>
       <c r="H7" s="56">
@@ -9157,7 +10560,7 @@
       <c r="F8" s="53" t="s">
         <v>753</v>
       </c>
-      <c r="G8" s="131"/>
+      <c r="G8" s="140"/>
       <c r="J8" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>3.9</v>
@@ -9190,7 +10593,7 @@
       <c r="F9" s="53" t="s">
         <v>754</v>
       </c>
-      <c r="G9" s="131"/>
+      <c r="G9" s="140"/>
       <c r="J9" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.5</v>
@@ -9223,7 +10626,7 @@
       <c r="F10" s="53" t="s">
         <v>755</v>
       </c>
-      <c r="G10" s="131"/>
+      <c r="G10" s="140"/>
       <c r="J10" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>14.4</v>
@@ -9461,7 +10864,7 @@
       <c r="F17" s="53" t="s">
         <v>762</v>
       </c>
-      <c r="G17" s="130" t="s">
+      <c r="G17" s="139" t="s">
         <v>386</v>
       </c>
       <c r="H17" s="56">
@@ -9500,7 +10903,7 @@
       <c r="F18" s="53" t="s">
         <v>763</v>
       </c>
-      <c r="G18" s="131"/>
+      <c r="G18" s="140"/>
       <c r="J18" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.1</v>
@@ -10114,7 +11517,7 @@
         <v>124</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>828</v>
@@ -11439,7 +12842,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="G7" s="115" t="s">
         <v>918</v>
@@ -11463,7 +12866,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="114" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G8" s="115" t="s">
         <v>922</v>
@@ -11576,7 +12979,7 @@
         <v>211</v>
       </c>
       <c r="F13" s="116" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="G13" s="119"/>
     </row>
@@ -11717,12 +13120,12 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="126" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="126" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -11787,12 +13190,12 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -11807,7 +13210,7 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -12212,7 +13615,7 @@
         <v>7.7</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="K24" s="115" t="s">
         <v>999</v>
@@ -12253,7 +13656,7 @@
         <v>7.7</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="K25" s="115" t="s">
         <v>1001</v>
@@ -12636,7 +14039,7 @@
         <v>293</v>
       </c>
       <c r="D11" s="114">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E11" s="114">
         <v>4</v>
@@ -12677,7 +14080,7 @@
         <v>293</v>
       </c>
       <c r="D12" s="114">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E12" s="114">
         <v>3</v>
@@ -12695,14 +14098,14 @@
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="J12" s="115" t="s">
+      <c r="J12" s="75" t="s">
+        <v>1423</v>
+      </c>
+      <c r="K12" s="115" t="s">
         <v>1033</v>
       </c>
-      <c r="K12" s="115" t="s">
+      <c r="L12" s="114" t="s">
         <v>1034</v>
-      </c>
-      <c r="L12" s="114" t="s">
-        <v>1035</v>
       </c>
       <c r="M12" s="114"/>
       <c r="N12" s="114"/>
@@ -12712,19 +14115,19 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C13" s="114" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="D13" s="114">
         <v>50</v>
       </c>
       <c r="E13" s="114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="114" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G13" s="114">
         <v>40</v>
@@ -12734,13 +14137,13 @@
       </c>
       <c r="I13" s="114">
         <f t="shared" ref="I13" si="1">IF(E13=0,0,ROUND((E13*(G13+H13)+N13)/60,1))</f>
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J13" s="115" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="K13" s="115" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -12760,7 +14163,7 @@
         <v>25</v>
       </c>
       <c r="E14" s="114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>289</v>
@@ -12773,13 +14176,13 @@
       </c>
       <c r="I14" s="114">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -12796,7 +14199,7 @@
         <v>293</v>
       </c>
       <c r="D15" s="114">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E15" s="114">
         <v>3</v>
@@ -12815,10 +14218,10 @@
         <v>6.8</v>
       </c>
       <c r="J15" s="115" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K15" s="115" t="s">
         <v>1037</v>
-      </c>
-      <c r="K15" s="115" t="s">
-        <v>1038</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -12837,7 +14240,7 @@
         <v>418</v>
       </c>
       <c r="D16" s="114">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" s="114">
         <v>3</v>
@@ -12856,10 +14259,10 @@
         <v>6.5</v>
       </c>
       <c r="J16" s="115" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K16" s="115" t="s">
         <v>1039</v>
-      </c>
-      <c r="K16" s="115" t="s">
-        <v>1040</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -12876,7 +14279,7 @@
         <v>356</v>
       </c>
       <c r="D17" s="114">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E17" s="114">
         <v>3</v>
@@ -12895,10 +14298,10 @@
         <v>6.8</v>
       </c>
       <c r="J17" s="115" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K17" s="115" t="s">
         <v>1041</v>
-      </c>
-      <c r="K17" s="115" t="s">
-        <v>1042</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -12936,10 +14339,10 @@
         <v>6.8</v>
       </c>
       <c r="J18" s="115" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K18" s="115" t="s">
         <v>1043</v>
-      </c>
-      <c r="K18" s="115" t="s">
-        <v>1044</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -12952,13 +14355,13 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>306</v>
       </c>
       <c r="D19" s="114">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="E19" s="114">
         <v>3</v>
@@ -12977,10 +14380,10 @@
         <v>2.5</v>
       </c>
       <c r="J19" s="115" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K19" s="115" t="s">
         <v>1046</v>
-      </c>
-      <c r="K19" s="115" t="s">
-        <v>1047</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114" t="s">
@@ -12999,7 +14402,7 @@
         <v>306</v>
       </c>
       <c r="D20" s="114">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="E20" s="114">
         <v>3</v>
@@ -13018,10 +14421,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="115" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K20" s="115" t="s">
         <v>1048</v>
-      </c>
-      <c r="K20" s="115" t="s">
-        <v>1049</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114" t="s">
@@ -13039,8 +14442,8 @@
       <c r="C21" s="114" t="s">
         <v>324</v>
       </c>
-      <c r="D21" s="114" t="s">
-        <v>294</v>
+      <c r="D21" s="114">
+        <v>20</v>
       </c>
       <c r="E21" s="114">
         <v>3</v>
@@ -13059,10 +14462,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="115" t="s">
+        <v>1049</v>
+      </c>
+      <c r="K21" s="115" t="s">
         <v>1050</v>
-      </c>
-      <c r="K21" s="115" t="s">
-        <v>1051</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114"/>
@@ -13089,52 +14492,52 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="107" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="117" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="107" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="117" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -13144,17 +14547,17 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="117" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="117" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -13164,27 +14567,27 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="117" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -13194,11 +14597,14 @@
     </row>
     <row r="49" spans="3:3">
       <c r="C49" s="118" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="29" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J12" r:id="rId1" display="https://www.youtube.com/shorts/KGkE5bXQR24, 명치가 의자 최상단 높이에 맞게 설정" xr:uid="{FB7A3E7E-E2D3-45DE-85C6-B3A6CD805B29}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13225,7 +14631,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -13399,13 +14805,13 @@
         <v>15.3</v>
       </c>
       <c r="J18" s="113" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K18" s="113" t="s">
         <v>1068</v>
       </c>
-      <c r="K18" s="113" t="s">
+      <c r="L18" s="112" t="s">
         <v>1069</v>
-      </c>
-      <c r="L18" s="112" t="s">
-        <v>1070</v>
       </c>
       <c r="M18" s="112"/>
       <c r="N18" s="112"/>
@@ -13440,10 +14846,10 @@
         <v>9.5</v>
       </c>
       <c r="J19" s="115" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K19" s="115" t="s">
         <v>1071</v>
-      </c>
-      <c r="K19" s="115" t="s">
-        <v>1072</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -13479,10 +14885,10 @@
         <v>7.3</v>
       </c>
       <c r="J20" s="115" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K20" s="115" t="s">
         <v>1073</v>
-      </c>
-      <c r="K20" s="115" t="s">
-        <v>1074</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -13518,13 +14924,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="115" t="s">
+        <v>1074</v>
+      </c>
+      <c r="K21" s="115" t="s">
         <v>1075</v>
       </c>
-      <c r="K21" s="115" t="s">
+      <c r="L21" s="114" t="s">
         <v>1076</v>
-      </c>
-      <c r="L21" s="114" t="s">
-        <v>1077</v>
       </c>
       <c r="M21" s="114"/>
       <c r="N21" s="114"/>
@@ -13534,13 +14940,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="115" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C22" s="114" t="s">
         <v>365</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E22" s="114">
         <v>4</v>
@@ -13559,10 +14965,10 @@
         <v>8</v>
       </c>
       <c r="J22" s="115" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="K22" s="115" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114"/>
@@ -13573,19 +14979,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="115" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C23" s="114" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="E23" s="114">
         <v>3</v>
       </c>
       <c r="F23" s="114" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="G23" s="114">
         <v>60</v>
@@ -13598,10 +15004,10 @@
         <v>6</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -13612,19 +15018,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="115" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C24" s="114" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D24" s="114" t="s">
         <v>1370</v>
-      </c>
-      <c r="C24" s="114" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D24" s="114" t="s">
-        <v>1372</v>
       </c>
       <c r="E24" s="114">
         <v>3</v>
       </c>
       <c r="F24" s="114" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="G24" s="114">
         <v>40</v>
@@ -13637,10 +15043,10 @@
         <v>6</v>
       </c>
       <c r="J24" s="115" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="K24" s="115" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="L24" s="114"/>
       <c r="M24" s="114"/>
@@ -13653,10 +15059,10 @@
         <v>8</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C25" s="114" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D25" s="114">
         <v>30</v>
@@ -13665,7 +15071,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="114" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="G25" s="114">
         <v>40</v>
@@ -13678,10 +15084,10 @@
         <v>3.3</v>
       </c>
       <c r="J25" s="115" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="K25" s="115" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="L25" s="114"/>
       <c r="M25" s="114"/>
@@ -13708,7 +15114,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="107" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -13718,32 +15124,32 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="107" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="117" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="117" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -13753,32 +15159,32 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="117" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="117" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="107" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="117" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="117" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="C46" s="118" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
   </sheetData>
@@ -13809,7 +15215,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -13819,12 +15225,12 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="110" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13911,10 +15317,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" s="115" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K11" s="115" t="s">
         <v>1093</v>
-      </c>
-      <c r="K11" s="115" t="s">
-        <v>1094</v>
       </c>
       <c r="L11" s="114"/>
       <c r="M11" s="114"/>
@@ -13952,10 +15358,10 @@
         <v>5.8</v>
       </c>
       <c r="J12" s="115" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K12" s="115" t="s">
         <v>1095</v>
-      </c>
-      <c r="K12" s="115" t="s">
-        <v>1096</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -13991,10 +15397,10 @@
         <v>5.5</v>
       </c>
       <c r="J13" s="115" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K13" s="115" t="s">
         <v>1097</v>
-      </c>
-      <c r="K13" s="115" t="s">
-        <v>1098</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -14005,7 +15411,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>306</v>
@@ -14030,10 +15436,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114" t="s">
@@ -14071,10 +15477,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="115" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="K15" s="115" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114" t="s">
@@ -14087,7 +15493,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>933</v>
@@ -14112,10 +15518,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="115" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K16" s="115" t="s">
         <v>1102</v>
-      </c>
-      <c r="K16" s="115" t="s">
-        <v>1103</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -14126,7 +15532,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C17" s="114" t="s">
         <v>933</v>
@@ -14151,10 +15557,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="115" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K17" s="115" t="s">
         <v>1105</v>
-      </c>
-      <c r="K17" s="115" t="s">
-        <v>1106</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -14190,10 +15596,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="115" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K18" s="115" t="s">
         <v>1107</v>
-      </c>
-      <c r="K18" s="115" t="s">
-        <v>1108</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -14229,10 +15635,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="115" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K19" s="115" t="s">
         <v>1109</v>
-      </c>
-      <c r="K19" s="115" t="s">
-        <v>1110</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -14259,52 +15665,52 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="107" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="117" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="117" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="117" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="107" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="117" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -14314,37 +15720,37 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="107" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="117" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -14354,22 +15760,22 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -14379,7 +15785,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -15091,7 +16497,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -15172,7 +16578,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="107" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -15248,12 +16654,12 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="107" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="110" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -15263,7 +16669,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="110" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -15351,10 +16757,10 @@
         <v>3.5</v>
       </c>
       <c r="J28" s="113" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K28" s="113" t="s">
         <v>1138</v>
-      </c>
-      <c r="K28" s="113" t="s">
-        <v>1139</v>
       </c>
       <c r="L28" s="112"/>
       <c r="M28" s="112"/>
@@ -15365,7 +16771,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C29" s="114" t="s">
         <v>324</v>
@@ -15391,10 +16797,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="115" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K29" s="115" t="s">
         <v>1141</v>
-      </c>
-      <c r="K29" s="115" t="s">
-        <v>1142</v>
       </c>
       <c r="L29" s="114"/>
       <c r="M29" s="114"/>
@@ -15411,7 +16817,7 @@
         <v>395</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E30" s="114">
         <v>3</v>
@@ -15430,10 +16836,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J30" s="115" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K30" s="115" t="s">
         <v>1144</v>
-      </c>
-      <c r="K30" s="115" t="s">
-        <v>1145</v>
       </c>
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
@@ -15444,7 +16850,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C31" s="114" t="s">
         <v>386</v>
@@ -15469,10 +16875,10 @@
         <v>13</v>
       </c>
       <c r="J31" s="115" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K31" s="115" t="s">
         <v>1147</v>
-      </c>
-      <c r="K31" s="115" t="s">
-        <v>1148</v>
       </c>
       <c r="L31" s="114"/>
       <c r="M31" s="114"/>
@@ -15508,10 +16914,10 @@
         <v>9</v>
       </c>
       <c r="J32" s="115" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K32" s="115" t="s">
         <v>1149</v>
-      </c>
-      <c r="K32" s="115" t="s">
-        <v>1150</v>
       </c>
       <c r="L32" s="114"/>
       <c r="M32" s="114"/>
@@ -15522,7 +16928,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="113" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C33" s="112" t="s">
         <v>440</v>
@@ -15548,10 +16954,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="113" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K33" s="113" t="s">
         <v>1152</v>
-      </c>
-      <c r="K33" s="113" t="s">
-        <v>1153</v>
       </c>
       <c r="L33" s="112" t="s">
         <v>518</v>
@@ -15589,7 +16995,7 @@
         <v>6</v>
       </c>
       <c r="J34" s="115" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K34" s="115" t="s">
         <v>999</v>
@@ -15630,10 +17036,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="115" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K35" s="115" t="s">
         <v>1155</v>
-      </c>
-      <c r="K35" s="115" t="s">
-        <v>1156</v>
       </c>
       <c r="L35" s="114"/>
       <c r="M35" s="114"/>
@@ -15669,10 +17075,10 @@
         <v>8</v>
       </c>
       <c r="J36" s="115" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K36" s="115" t="s">
         <v>1157</v>
-      </c>
-      <c r="K36" s="115" t="s">
-        <v>1158</v>
       </c>
       <c r="L36" s="114"/>
       <c r="M36" s="114"/>
@@ -15708,10 +17114,10 @@
         <v>6.8</v>
       </c>
       <c r="J37" s="115" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K37" s="115" t="s">
         <v>1159</v>
-      </c>
-      <c r="K37" s="115" t="s">
-        <v>1160</v>
       </c>
       <c r="L37" s="114"/>
       <c r="M37" s="114"/>
@@ -15747,7 +17153,7 @@
         <v>3.3</v>
       </c>
       <c r="J38" s="115" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="K38" s="115" t="s">
         <v>1005</v>
@@ -15788,7 +17194,7 @@
         <v>10.7</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="K39" s="115" t="s">
         <v>1007</v>
@@ -15829,10 +17235,10 @@
         <v>11.5</v>
       </c>
       <c r="J40" s="115" t="s">
+        <v>1162</v>
+      </c>
+      <c r="K40" s="115" t="s">
         <v>1163</v>
-      </c>
-      <c r="K40" s="115" t="s">
-        <v>1164</v>
       </c>
       <c r="L40" s="114"/>
       <c r="M40" s="114"/>
@@ -15859,117 +17265,117 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="107" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="117" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="117" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="117" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="117" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="117" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="117" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="107" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="117" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="117" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="117" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="117" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="117" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="107" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="117" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="117" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="117" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="117" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="117" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="107" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="117" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="117" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="117" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -15979,12 +17385,12 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="117" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="117" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -15994,22 +17400,22 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="117" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="117" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="117" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="117" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="79" spans="1:1">
@@ -16019,7 +17425,7 @@
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="118" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
   </sheetData>
@@ -16050,7 +17456,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -16060,7 +17466,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="110" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -16152,10 +17558,10 @@
         <v>12.3</v>
       </c>
       <c r="J11" s="115" t="s">
+        <v>1196</v>
+      </c>
+      <c r="K11" s="115" t="s">
         <v>1197</v>
-      </c>
-      <c r="K11" s="115" t="s">
-        <v>1198</v>
       </c>
       <c r="L11" s="114" t="s">
         <v>1032</v>
@@ -16168,7 +17574,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="115" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>278</v>
@@ -16193,10 +17599,10 @@
         <v>10.7</v>
       </c>
       <c r="J12" s="115" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K12" s="115" t="s">
         <v>1200</v>
-      </c>
-      <c r="K12" s="115" t="s">
-        <v>1201</v>
       </c>
       <c r="L12" s="114"/>
       <c r="M12" s="114"/>
@@ -16207,7 +17613,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>278</v>
@@ -16232,10 +17638,10 @@
         <v>11.7</v>
       </c>
       <c r="J13" s="115" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K13" s="115" t="s">
         <v>1203</v>
-      </c>
-      <c r="K13" s="115" t="s">
-        <v>1204</v>
       </c>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
@@ -16273,10 +17679,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="115" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K14" s="115" t="s">
         <v>1205</v>
-      </c>
-      <c r="K14" s="115" t="s">
-        <v>1206</v>
       </c>
       <c r="L14" s="114"/>
       <c r="M14" s="114"/>
@@ -16312,10 +17718,10 @@
         <v>5.3</v>
       </c>
       <c r="J15" s="115" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K15" s="115" t="s">
         <v>1207</v>
-      </c>
-      <c r="K15" s="115" t="s">
-        <v>1208</v>
       </c>
       <c r="L15" s="114"/>
       <c r="M15" s="114"/>
@@ -16351,10 +17757,10 @@
         <v>9.5</v>
       </c>
       <c r="J16" s="115" t="s">
+        <v>1208</v>
+      </c>
+      <c r="K16" s="115" t="s">
         <v>1209</v>
-      </c>
-      <c r="K16" s="115" t="s">
-        <v>1210</v>
       </c>
       <c r="L16" s="114"/>
       <c r="M16" s="114"/>
@@ -16390,10 +17796,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J17" s="115" t="s">
+        <v>1210</v>
+      </c>
+      <c r="K17" s="115" t="s">
         <v>1211</v>
-      </c>
-      <c r="K17" s="115" t="s">
-        <v>1212</v>
       </c>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -16429,10 +17835,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J18" s="115" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K18" s="115" t="s">
         <v>1213</v>
-      </c>
-      <c r="K18" s="115" t="s">
-        <v>1214</v>
       </c>
       <c r="L18" s="114"/>
       <c r="M18" s="114"/>
@@ -16445,7 +17851,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C19" s="114" t="s">
         <v>356</v>
@@ -16470,10 +17876,10 @@
         <v>5.5</v>
       </c>
       <c r="J19" s="115" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K19" s="115" t="s">
         <v>1216</v>
-      </c>
-      <c r="K19" s="115" t="s">
-        <v>1217</v>
       </c>
       <c r="L19" s="114"/>
       <c r="M19" s="114"/>
@@ -16484,7 +17890,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="115" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>280</v>
@@ -16508,11 +17914,11 @@
         <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="J20" s="115" t="s">
-        <v>1219</v>
+      <c r="J20" s="75" t="s">
+        <v>1424</v>
       </c>
       <c r="K20" s="115" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="L20" s="114"/>
       <c r="M20" s="114"/>
@@ -16523,7 +17929,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="115" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C21" s="114" t="s">
         <v>306</v>
@@ -16548,10 +17954,10 @@
         <v>2.5</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="K21" s="115" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="L21" s="114"/>
       <c r="M21" s="114" t="s">
@@ -16589,10 +17995,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="115" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K22" s="115" t="s">
         <v>1048</v>
-      </c>
-      <c r="K22" s="115" t="s">
-        <v>1049</v>
       </c>
       <c r="L22" s="114"/>
       <c r="M22" s="114" t="s">
@@ -16630,10 +18036,10 @@
         <v>6.7</v>
       </c>
       <c r="J23" s="115" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="K23" s="115" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="L23" s="114"/>
       <c r="M23" s="114"/>
@@ -16660,52 +18066,52 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="107" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="117" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="117" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="117" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="117" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="117" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="107" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="117" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -16715,17 +18121,17 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="117" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="117" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="117" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -16735,27 +18141,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="117" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="117" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="117" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="117" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="117" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -16765,16 +18171,769 @@
     </row>
     <row r="51" spans="1:3">
       <c r="C51" s="118" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="29" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J20" r:id="rId1" xr:uid="{23C18850-0E04-48B0-9034-D4ACB8232A2D}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9284DDD8-3AB2-43B2-A3B8-DBF53736B372}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" style="127" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" style="127" customWidth="1"/>
+    <col min="3" max="5" width="14.7109375" style="127" customWidth="1"/>
+    <col min="6" max="6" width="50.7109375" style="127" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="127"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.75">
+      <c r="A1" s="128" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="127" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15">
+      <c r="A4" s="99" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="129" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="129" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="127" t="s">
+        <v>905</v>
+      </c>
+      <c r="B6" s="135" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="127" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="135" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="127" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="127" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B8" s="135" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="127" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="127" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B9" s="135" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="127" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="127" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B10" s="135" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C10" s="135"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="127" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="127" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B11" s="135" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="127" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="127" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="135" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="127" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="127" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B13" s="135" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="127" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="127" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B14" s="135" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C14" s="135"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="127" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" s="131" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="129" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="129" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C17" s="129" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D17" s="129" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E17" s="129" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F17" s="129" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="132">
+        <v>1</v>
+      </c>
+      <c r="B18" s="133">
+        <v>46298</v>
+      </c>
+      <c r="C18" s="132">
+        <v>24</v>
+      </c>
+      <c r="D18" s="132">
+        <f t="shared" ref="D18:D27" si="0">C18*2</f>
+        <v>48</v>
+      </c>
+      <c r="E18" s="132"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="132">
+        <v>2</v>
+      </c>
+      <c r="B19" s="133">
+        <v>46305</v>
+      </c>
+      <c r="C19" s="132">
+        <v>26</v>
+      </c>
+      <c r="D19" s="132">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="E19" s="132"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="132">
+        <v>3</v>
+      </c>
+      <c r="B20" s="133">
+        <v>46312</v>
+      </c>
+      <c r="C20" s="132">
+        <v>28</v>
+      </c>
+      <c r="D20" s="132">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="E20" s="132"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="132">
+        <v>4</v>
+      </c>
+      <c r="B21" s="133">
+        <v>46319</v>
+      </c>
+      <c r="C21" s="132">
+        <v>30</v>
+      </c>
+      <c r="D21" s="132">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="E21" s="132"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="132">
+        <v>5</v>
+      </c>
+      <c r="B22" s="133">
+        <v>46326</v>
+      </c>
+      <c r="C22" s="132">
+        <v>32</v>
+      </c>
+      <c r="D22" s="132">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="E22" s="132"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="132">
+        <v>6</v>
+      </c>
+      <c r="B23" s="133">
+        <v>46333</v>
+      </c>
+      <c r="C23" s="132">
+        <v>34</v>
+      </c>
+      <c r="D23" s="132">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="E23" s="132"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="132">
+        <v>7</v>
+      </c>
+      <c r="B24" s="133">
+        <v>46340</v>
+      </c>
+      <c r="C24" s="132">
+        <v>36</v>
+      </c>
+      <c r="D24" s="132">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="E24" s="132"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="132">
+        <v>8</v>
+      </c>
+      <c r="B25" s="133">
+        <v>46347</v>
+      </c>
+      <c r="C25" s="132">
+        <v>36</v>
+      </c>
+      <c r="D25" s="132">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="E25" s="132"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="132">
+        <v>9</v>
+      </c>
+      <c r="B26" s="133">
+        <v>46354</v>
+      </c>
+      <c r="C26" s="132">
+        <v>36</v>
+      </c>
+      <c r="D26" s="132">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="E26" s="132"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="132">
+        <v>10</v>
+      </c>
+      <c r="B27" s="133">
+        <v>46361</v>
+      </c>
+      <c r="C27" s="132">
+        <v>36</v>
+      </c>
+      <c r="D27" s="132">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="E27" s="132"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="127" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+  </mergeCells>
+  <phoneticPr fontId="29" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3862FE5C-3816-4CFA-A88D-950DD0B7A491}">
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" style="127" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="127" customWidth="1"/>
+    <col min="3" max="6" width="12.7109375" style="127" customWidth="1"/>
+    <col min="7" max="8" width="13.7109375" style="127" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="127" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="127"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.75">
+      <c r="A1" s="128" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="127" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" s="99" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="129" t="s">
+        <v>905</v>
+      </c>
+      <c r="B5" s="129" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="127" t="s">
+        <v>910</v>
+      </c>
+      <c r="B6" s="135" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="127" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="127" t="s">
+        <v>915</v>
+      </c>
+      <c r="B7" s="135" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="127" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="127" t="s">
+        <v>919</v>
+      </c>
+      <c r="B8" s="135" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="127" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="127" t="s">
+        <v>923</v>
+      </c>
+      <c r="B9" s="135" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="127" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="127" t="s">
+        <v>928</v>
+      </c>
+      <c r="B10" s="135" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C10" s="135"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="127" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="127" t="s">
+        <v>933</v>
+      </c>
+      <c r="B11" s="135" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="127" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="127" t="s">
+        <v>938</v>
+      </c>
+      <c r="B12" s="135" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="127" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" s="131" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="129" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="129" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F15" s="129" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G15" s="129" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H15" s="129" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I15" s="129" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="132">
+        <v>1</v>
+      </c>
+      <c r="B16" s="134" t="s">
+        <v>325</v>
+      </c>
+      <c r="C16" s="132">
+        <v>3</v>
+      </c>
+      <c r="D16" s="132">
+        <v>4</v>
+      </c>
+      <c r="E16" s="132">
+        <v>3</v>
+      </c>
+      <c r="F16" s="132">
+        <v>2</v>
+      </c>
+      <c r="G16" s="132">
+        <f>C16*D16</f>
+        <v>12</v>
+      </c>
+      <c r="H16" s="132">
+        <f>E16*F16</f>
+        <v>6</v>
+      </c>
+      <c r="I16" s="132">
+        <f>G16*2+H16*3</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="132">
+        <v>2</v>
+      </c>
+      <c r="B17" s="134" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C17" s="132">
+        <v>4</v>
+      </c>
+      <c r="D17" s="132">
+        <v>4</v>
+      </c>
+      <c r="E17" s="132">
+        <v>3</v>
+      </c>
+      <c r="F17" s="132">
+        <v>3</v>
+      </c>
+      <c r="G17" s="132">
+        <f>C17*D17</f>
+        <v>16</v>
+      </c>
+      <c r="H17" s="132">
+        <f>E17*F17</f>
+        <v>9</v>
+      </c>
+      <c r="I17" s="132">
+        <f>G17*2+H17*3</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="132">
+        <v>3</v>
+      </c>
+      <c r="B18" s="134" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C18" s="132">
+        <v>5</v>
+      </c>
+      <c r="D18" s="132">
+        <v>5</v>
+      </c>
+      <c r="E18" s="132">
+        <v>4</v>
+      </c>
+      <c r="F18" s="132">
+        <v>3</v>
+      </c>
+      <c r="G18" s="132">
+        <f>C18*D18</f>
+        <v>25</v>
+      </c>
+      <c r="H18" s="132">
+        <f>E18*F18</f>
+        <v>12</v>
+      </c>
+      <c r="I18" s="132">
+        <f>G18*2+H18*3</f>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="132">
+        <v>4</v>
+      </c>
+      <c r="B19" s="134" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C19" s="132">
+        <v>5</v>
+      </c>
+      <c r="D19" s="132">
+        <v>6</v>
+      </c>
+      <c r="E19" s="132">
+        <v>5</v>
+      </c>
+      <c r="F19" s="132">
+        <v>3</v>
+      </c>
+      <c r="G19" s="132">
+        <f>C19*D19</f>
+        <v>30</v>
+      </c>
+      <c r="H19" s="132">
+        <f>E19*F19</f>
+        <v>15</v>
+      </c>
+      <c r="I19" s="132">
+        <f>G19*2+H19*3</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15">
+      <c r="A21" s="99" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="127" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="127" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="127" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="127" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="127" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="127" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+  </mergeCells>
+  <phoneticPr fontId="29" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16845,10 +19004,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D7" s="115" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
@@ -17150,7 +19309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17166,12 +19325,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="119" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -17185,12 +19344,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="119" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B6" s="111" t="s">
         <v>649</v>
@@ -17216,7 +19375,7 @@
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B7" s="115" t="s">
         <v>95</v>
@@ -17239,12 +19398,12 @@
         <v>670</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B8" s="115" t="s">
         <v>528</v>
@@ -17267,12 +19426,12 @@
         <v>670</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B9" s="115" t="s">
         <v>354</v>
@@ -17295,12 +19454,12 @@
         <v>670</v>
       </c>
       <c r="H9" s="115" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>519</v>
@@ -17323,15 +19482,15 @@
         <v>670</v>
       </c>
       <c r="H10" s="115" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.25">
       <c r="A11" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B11" s="115" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>356</v>
@@ -17351,12 +19510,12 @@
         <v>670</v>
       </c>
       <c r="H11" s="115" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B12" s="115" t="s">
         <v>277</v>
@@ -17379,15 +19538,15 @@
         <v>670</v>
       </c>
       <c r="H12" s="115" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B13" s="115" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>280</v>
@@ -17407,15 +19566,15 @@
         <v>670</v>
       </c>
       <c r="H13" s="115" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B14" s="115" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C14" s="114" t="s">
         <v>280</v>
@@ -17435,12 +19594,12 @@
         <v>670</v>
       </c>
       <c r="H14" s="115" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="25.5">
       <c r="A15" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B15" s="115" t="s">
         <v>483</v>
@@ -17453,25 +19612,25 @@
       </c>
       <c r="E15" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="114">
         <f t="shared" ca="1" si="1"/>
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
       <c r="G15" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51">
       <c r="A16" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B16" s="115" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C16" s="114" t="s">
         <v>280</v>
@@ -17481,22 +19640,22 @@
       </c>
       <c r="E16" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="114">
         <f t="shared" ref="F16" ca="1" si="2">IF(ISNUMBER(E16),$D16*E16,0)</f>
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="G16" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H16" s="115" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="25.5">
       <c r="A17" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B17" s="115" t="s">
         <v>1029</v>
@@ -17519,12 +19678,12 @@
         <v>670</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="38.25">
       <c r="A18" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>476</v>
@@ -17547,12 +19706,12 @@
         <v>670</v>
       </c>
       <c r="H18" s="115" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="114" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B19" s="115" t="s">
         <v>450</v>
@@ -17575,12 +19734,12 @@
         <v>670</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="25.5">
       <c r="A20" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B20" s="115" t="s">
         <v>95</v>
@@ -17603,12 +19762,12 @@
         <v>670</v>
       </c>
       <c r="H20" s="115" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B21" s="115" t="s">
         <v>528</v>
@@ -17631,12 +19790,12 @@
         <v>670</v>
       </c>
       <c r="H21" s="115" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B22" s="115" t="s">
         <v>354</v>
@@ -17659,12 +19818,12 @@
         <v>670</v>
       </c>
       <c r="H22" s="115" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B23" s="115" t="s">
         <v>597</v>
@@ -17687,12 +19846,12 @@
         <v>670</v>
       </c>
       <c r="H23" s="115" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B24" s="115" t="s">
         <v>438</v>
@@ -17715,12 +19874,12 @@
         <v>670</v>
       </c>
       <c r="H24" s="115" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5">
       <c r="A25" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B25" s="115" t="s">
         <v>433</v>
@@ -17743,12 +19902,12 @@
         <v>670</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5">
       <c r="A26" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>433</v>
@@ -17771,12 +19930,12 @@
         <v>670</v>
       </c>
       <c r="H26" s="115" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25.5">
       <c r="A27" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B27" s="115" t="s">
         <v>299</v>
@@ -17799,15 +19958,15 @@
         <v>670</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="38.25">
       <c r="A28" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B28" s="115" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>365</v>
@@ -17827,12 +19986,12 @@
         <v>670</v>
       </c>
       <c r="H28" s="115" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="38.25">
       <c r="A29" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B29" s="115" t="s">
         <v>519</v>
@@ -17855,15 +20014,15 @@
         <v>670</v>
       </c>
       <c r="H29" s="115" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="25.5">
       <c r="A30" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B30" s="115" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C30" s="114" t="s">
         <v>380</v>
@@ -17883,12 +20042,12 @@
         <v>670</v>
       </c>
       <c r="H30" s="115" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25.5">
       <c r="A31" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B31" s="115" t="s">
         <v>1029</v>
@@ -17911,12 +20070,12 @@
         <v>670</v>
       </c>
       <c r="H31" s="115" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="25.5">
       <c r="A32" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B32" s="115" t="s">
         <v>476</v>
@@ -17939,12 +20098,12 @@
         <v>670</v>
       </c>
       <c r="H32" s="115" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B33" s="115" t="s">
         <v>93</v>
@@ -17967,15 +20126,15 @@
         <v>670</v>
       </c>
       <c r="H33" s="115" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B34" s="115" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C34" s="114" t="s">
         <v>418</v>
@@ -17995,12 +20154,12 @@
         <v>670</v>
       </c>
       <c r="H34" s="115" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B35" s="115" t="s">
         <v>1029</v>
@@ -18023,12 +20182,12 @@
         <v>670</v>
       </c>
       <c r="H35" s="115" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="25.5">
       <c r="A36" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B36" s="115" t="s">
         <v>93</v>
@@ -18051,12 +20210,12 @@
         <v>670</v>
       </c>
       <c r="H36" s="115" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>277</v>
@@ -18079,15 +20238,15 @@
         <v>670</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C38" s="114" t="s">
         <v>429</v>
@@ -18107,15 +20266,15 @@
         <v>670</v>
       </c>
       <c r="H38" s="115" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C39" s="114" t="s">
         <v>429</v>
@@ -18135,12 +20294,12 @@
         <v>670</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="25.5">
       <c r="A40" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B40" s="115" t="s">
         <v>476</v>
@@ -18163,15 +20322,15 @@
         <v>670</v>
       </c>
       <c r="H40" s="115" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="38.25">
       <c r="A41" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B41" s="115" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C41" s="114" t="s">
         <v>293</v>
@@ -18191,12 +20350,12 @@
         <v>670</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>534</v>
@@ -18219,12 +20378,12 @@
         <v>670</v>
       </c>
       <c r="H42" s="115" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B43" s="115" t="s">
         <v>1000</v>
@@ -18247,12 +20406,12 @@
         <v>670</v>
       </c>
       <c r="H43" s="115" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="25.5">
       <c r="A44" s="114" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B44" s="115" t="s">
         <v>1000</v>
@@ -18275,12 +20434,12 @@
         <v>670</v>
       </c>
       <c r="H44" s="115" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B45" s="115" t="s">
         <v>483</v>
@@ -18293,25 +20452,25 @@
       </c>
       <c r="E45" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="114">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G45" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H45" s="115" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.5">
       <c r="A46" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B46" s="115" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C46" s="114" t="s">
         <v>293</v>
@@ -18321,22 +20480,22 @@
       </c>
       <c r="E46" s="114">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="114">
         <f t="shared" ref="F46" ca="1" si="6">IF(ISNUMBER(E46),$D46*E46,0)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G46" s="114" t="s">
         <v>670</v>
       </c>
       <c r="H46" s="115" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="38.25">
       <c r="A47" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B47" s="115" t="s">
         <v>91</v>
@@ -18359,12 +20518,12 @@
         <v>670</v>
       </c>
       <c r="H47" s="115" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B48" s="115" t="s">
         <v>1029</v>
@@ -18387,12 +20546,12 @@
         <v>670</v>
       </c>
       <c r="H48" s="115" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B49" s="115" t="s">
         <v>428</v>
@@ -18415,12 +20574,12 @@
         <v>670</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="51">
       <c r="A50" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>570</v>
@@ -18443,12 +20602,12 @@
         <v>670</v>
       </c>
       <c r="H50" s="115" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="25.5">
       <c r="A51" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B51" s="115" t="s">
         <v>495</v>
@@ -18471,12 +20630,12 @@
         <v>670</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B52" s="115" t="s">
         <v>91</v>
@@ -18504,7 +20663,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B53" s="115" t="s">
         <v>93</v>
@@ -18527,15 +20686,15 @@
         <v>670</v>
       </c>
       <c r="H53" s="115" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B54" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C54" s="114" t="s">
         <v>386</v>
@@ -18555,12 +20714,12 @@
         <v>670</v>
       </c>
       <c r="H54" s="115" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B55" s="115" t="s">
         <v>385</v>
@@ -18588,7 +20747,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B56" s="115" t="s">
         <v>570</v>
@@ -18611,12 +20770,12 @@
         <v>670</v>
       </c>
       <c r="H56" s="115" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="38.25">
       <c r="A57" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B57" s="115" t="s">
         <v>567</v>
@@ -18639,12 +20798,12 @@
         <v>670</v>
       </c>
       <c r="H57" s="115" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="38.25">
       <c r="A58" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B58" s="115" t="s">
         <v>93</v>
@@ -18667,15 +20826,15 @@
         <v>670</v>
       </c>
       <c r="H58" s="115" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="25.5">
       <c r="A59" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B59" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C59" s="114" t="s">
         <v>395</v>
@@ -18695,15 +20854,15 @@
         <v>670</v>
       </c>
       <c r="H59" s="115" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="51">
       <c r="A60" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B60" s="115" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C60" s="114" t="s">
         <v>395</v>
@@ -18723,12 +20882,12 @@
         <v>670</v>
       </c>
       <c r="H60" s="115" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="38.25">
       <c r="A61" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B61" s="115" t="s">
         <v>91</v>
@@ -18751,12 +20910,12 @@
         <v>670</v>
       </c>
       <c r="H61" s="115" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="25.5">
       <c r="A62" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B62" s="115" t="s">
         <v>385</v>
@@ -18779,15 +20938,15 @@
         <v>670</v>
       </c>
       <c r="H62" s="115" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.5">
       <c r="A63" s="114" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B63" s="115" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C63" s="114" t="s">
         <v>399</v>
@@ -18807,12 +20966,12 @@
         <v>670</v>
       </c>
       <c r="H63" s="115" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="114" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B64" s="115" t="s">
         <v>492</v>
@@ -18840,7 +20999,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="114" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B65" s="115" t="s">
         <v>602</v>
@@ -18868,10 +21027,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B66" s="115" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C66" s="114" t="s">
         <v>306</v>
@@ -18891,12 +21050,12 @@
         <v>670</v>
       </c>
       <c r="H66" s="115" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="38.25">
       <c r="A67" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B67" s="115" t="s">
         <v>95</v>
@@ -18919,12 +21078,12 @@
         <v>670</v>
       </c>
       <c r="H67" s="115" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25.5">
       <c r="A68" s="114" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B68" s="115" t="s">
         <v>438</v>
@@ -18947,12 +21106,12 @@
         <v>670</v>
       </c>
       <c r="H68" s="115" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="25.5">
       <c r="A69" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B69" s="115" t="s">
         <v>528</v>
@@ -18975,12 +21134,12 @@
         <v>670</v>
       </c>
       <c r="H69" s="115" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="114" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B70" s="115" t="s">
         <v>597</v>
@@ -19003,12 +21162,12 @@
         <v>670</v>
       </c>
       <c r="H70" s="115" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B71" s="115" t="s">
         <v>91</v>
@@ -19031,12 +21190,12 @@
         <v>670</v>
       </c>
       <c r="H71" s="115" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="114" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B72" s="115" t="s">
         <v>499</v>
@@ -19059,15 +21218,15 @@
         <v>670</v>
       </c>
       <c r="H72" s="115" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="25.5">
       <c r="A73" s="114" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B73" s="115" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C73" s="114" t="s">
         <v>933</v>
@@ -19087,7 +21246,7 @@
         <v>670</v>
       </c>
       <c r="H73" s="115" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
   </sheetData>
@@ -19096,7 +21255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19112,12 +21271,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="106" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="119" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -19161,7 +21320,7 @@
         <v>하한</v>
       </c>
       <c r="F5" s="115" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>749</v>
@@ -19192,7 +21351,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
@@ -19216,10 +21375,10 @@
         <v>충분</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="I7" s="125">
         <f ca="1">SUM(D7:D10)</f>
@@ -19247,10 +21406,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="H8" s="124" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="I8" s="125">
         <f>SUM(복귀_일_수평당기기!E11:E15,복귀_목_수직당기기!E11:E13)</f>
@@ -19278,7 +21437,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
@@ -19302,7 +21461,7 @@
         <v>충분</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
@@ -19326,7 +21485,7 @@
         <v>충분</v>
       </c>
       <c r="F11" s="115" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1">
@@ -19350,7 +21509,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="115" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1">
@@ -19374,7 +21533,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="115" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1">
@@ -19398,7 +21557,7 @@
         <v>충분</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -19422,10 +21581,10 @@
         <v>충분</v>
       </c>
       <c r="F15" s="115" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="I15" s="125">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -19453,7 +21612,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="115" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -19477,7 +21636,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="115" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -19501,7 +21660,7 @@
         <v>충분</v>
       </c>
       <c r="F18" s="115" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1">
@@ -19525,7 +21684,7 @@
         <v>충분</v>
       </c>
       <c r="F19" s="115" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
@@ -19549,7 +21708,7 @@
         <v>충분</v>
       </c>
       <c r="F20" s="115" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -19573,7 +21732,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="115" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
@@ -19597,7 +21756,7 @@
         <v>과다 점검</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -19621,7 +21780,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" s="115" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -19645,7 +21804,7 @@
         <v>충분</v>
       </c>
       <c r="F24" s="115" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
@@ -19669,7 +21828,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -19692,192 +21851,192 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="123" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="123" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="123" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="123" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="107" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="123" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="123" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="123" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="123" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="123" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="123" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="123" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="123" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="123" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="123" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="107" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="107" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="123" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="123" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="123" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="107" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="123" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="123" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="123" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="123" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="536" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23DB6200-7098-42C0-A00C-AD3043BC03A0}"/>
+  <xr:revisionPtr revIDLastSave="539" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C794C2B3-8359-476C-BCD9-8D67EF25E653}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
     <sheet name="복귀_수_하체후면" sheetId="20" r:id="rId20"/>
     <sheet name="복귀_목_수직당기기" sheetId="21" r:id="rId21"/>
     <sheet name="복귀_캐리" sheetId="25" r:id="rId22"/>
-    <sheet name="복귀_계단" sheetId="26" r:id="rId23"/>
+    <sheet name="복귀_천국의계단" sheetId="26" r:id="rId23"/>
     <sheet name="복귀_증량원칙" sheetId="22" r:id="rId24"/>
     <sheet name="복귀_간접계수맵" sheetId="23" r:id="rId25"/>
     <sheet name="복귀_세트검산" sheetId="24" r:id="rId26"/>
@@ -4731,9 +4731,6 @@
     <t>무겁게는 주 2회까지</t>
   </si>
   <si>
-    <t>악력을 매일 무겁게 쓰면 회복이 안 돼 오히려 안 오른다. 나머지 날은 복귀_계단으로 채운다</t>
-  </si>
-  <si>
     <t>재검토 조건</t>
   </si>
   <si>
@@ -5103,155 +5100,6 @@
   </si>
   <si>
     <t>· 7주차에 36kg이 최선 경로다. 정체 주는 같은 무게를 반복하고 목표 칸을 한 줄씩 아래로 민다.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>계단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> — </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>천국의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>계단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>덤벨</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>생수배송</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>대비</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · 2026-10-04 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>신설</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>하루 종일 오르내리는 지구력. 무게는 12~16kg에서 멈춘다 — 36kg은 복귀_캐리 몫. 세트 카운트 · 세트검산에는 넣지 않는다.</t>
@@ -5721,6 +5569,14 @@
   </si>
   <si>
     <t>· 4주차(메인 5분 × 6) 이후는 무게를 올리지 말고 유지한다. 배달 일이 시작되면 그 일이 이 시트를 대신한다.</t>
+  </si>
+  <si>
+    <t>천국의 계단 + 덤벨 (생수배송 대비 · 2026-10-04 신설)</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>악력을 매일 무겁게 쓰면 회복이 안 돼 오히려 안 오른다. 나머지 날은 복귀_천국의계단으로 채운다</t>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -18319,40 +18175,40 @@
       <c r="D12" s="135"/>
       <c r="E12" s="135"/>
       <c r="F12" s="127" t="s">
-        <v>1445</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="127" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B13" s="135" t="s">
         <v>1446</v>
-      </c>
-      <c r="B13" s="135" t="s">
-        <v>1447</v>
       </c>
       <c r="C13" s="135"/>
       <c r="D13" s="135"/>
       <c r="E13" s="135"/>
       <c r="F13" s="127" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="127" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B14" s="135" t="s">
         <v>1449</v>
-      </c>
-      <c r="B14" s="135" t="s">
-        <v>1450</v>
       </c>
       <c r="C14" s="135"/>
       <c r="D14" s="135"/>
       <c r="E14" s="135"/>
       <c r="F14" s="127" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" s="131" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18360,19 +18216,19 @@
         <v>124</v>
       </c>
       <c r="B17" s="129" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C17" s="129" t="s">
         <v>1453</v>
       </c>
-      <c r="C17" s="129" t="s">
+      <c r="D17" s="129" t="s">
         <v>1454</v>
       </c>
-      <c r="D17" s="129" t="s">
+      <c r="E17" s="129" t="s">
         <v>1455</v>
       </c>
-      <c r="E17" s="129" t="s">
+      <c r="F17" s="129" t="s">
         <v>1456</v>
-      </c>
-      <c r="F17" s="129" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18537,7 +18393,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="127" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
   </sheetData>
@@ -18572,12 +18428,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="128" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="127" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -18590,7 +18446,7 @@
         <v>905</v>
       </c>
       <c r="B5" s="129" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="C5" s="130"/>
       <c r="D5" s="130"/>
@@ -18607,7 +18463,7 @@
         <v>910</v>
       </c>
       <c r="B6" s="135" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C6" s="135"/>
       <c r="D6" s="135"/>
@@ -18616,7 +18472,7 @@
       <c r="G6" s="135"/>
       <c r="H6" s="135"/>
       <c r="I6" s="127" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -18624,7 +18480,7 @@
         <v>915</v>
       </c>
       <c r="B7" s="135" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C7" s="135"/>
       <c r="D7" s="135"/>
@@ -18633,7 +18489,7 @@
       <c r="G7" s="135"/>
       <c r="H7" s="135"/>
       <c r="I7" s="127" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -18641,7 +18497,7 @@
         <v>919</v>
       </c>
       <c r="B8" s="135" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C8" s="135"/>
       <c r="D8" s="135"/>
@@ -18650,7 +18506,7 @@
       <c r="G8" s="135"/>
       <c r="H8" s="135"/>
       <c r="I8" s="127" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -18667,7 +18523,7 @@
       <c r="G9" s="135"/>
       <c r="H9" s="135"/>
       <c r="I9" s="127" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -18675,7 +18531,7 @@
         <v>928</v>
       </c>
       <c r="B10" s="135" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C10" s="135"/>
       <c r="D10" s="135"/>
@@ -18684,7 +18540,7 @@
       <c r="G10" s="135"/>
       <c r="H10" s="135"/>
       <c r="I10" s="127" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -18692,7 +18548,7 @@
         <v>933</v>
       </c>
       <c r="B11" s="135" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C11" s="135"/>
       <c r="D11" s="135"/>
@@ -18701,7 +18557,7 @@
       <c r="G11" s="135"/>
       <c r="H11" s="135"/>
       <c r="I11" s="127" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -18709,7 +18565,7 @@
         <v>938</v>
       </c>
       <c r="B12" s="135" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="C12" s="135"/>
       <c r="D12" s="135"/>
@@ -18718,12 +18574,12 @@
       <c r="G12" s="135"/>
       <c r="H12" s="135"/>
       <c r="I12" s="127" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" s="131" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -18731,28 +18587,28 @@
         <v>124</v>
       </c>
       <c r="B15" s="129" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D15" s="129" t="s">
         <v>1471</v>
       </c>
-      <c r="C15" s="129" t="s">
+      <c r="E15" s="129" t="s">
         <v>1472</v>
       </c>
-      <c r="D15" s="129" t="s">
+      <c r="F15" s="129" t="s">
         <v>1473</v>
       </c>
-      <c r="E15" s="129" t="s">
+      <c r="G15" s="129" t="s">
         <v>1474</v>
       </c>
-      <c r="F15" s="129" t="s">
+      <c r="H15" s="129" t="s">
         <v>1475</v>
       </c>
-      <c r="G15" s="129" t="s">
+      <c r="I15" s="129" t="s">
         <v>1476</v>
-      </c>
-      <c r="H15" s="129" t="s">
-        <v>1477</v>
-      </c>
-      <c r="I15" s="129" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -18792,7 +18648,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="134" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C17" s="132">
         <v>4</v>
@@ -18824,7 +18680,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="134" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="C18" s="132">
         <v>5</v>
@@ -18856,7 +18712,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="134" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="C19" s="132">
         <v>5</v>
@@ -18890,32 +18746,32 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="127" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="127" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="127" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="127" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="127" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="127" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="560" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DA23E97-07E2-4C0A-896D-DC7115BFAE26}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495A3802-4BA8-4695-B2EE-8F9BDFD60A48}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="1489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="1490">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -5531,30 +5531,6 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>[2026-10-04 생수배송 대비 — 일 · 목 3 → 2 · 화 3 → 0(보류)] 캐리 · 천국의 계단이 굴근을 쥐고 버티는 쪽으로 채운다. 늘어난 구간 자극은 캐리가 못 주므로 일 · 목에 2세트를 남겼다. 배달 일을 안 하게 되면 3으로 되돌린다. [2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 17세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>[2026-10-04 생수배송 대비 — 일 · 목 3 → 2 · 화 3 → 0(보류)] 캐리 · 천국의 계단이 굴근을 쥐고 버티는 쪽으로 채운다. 늘어난 구간 자극은 캐리가 못 주므로 일 · 목에 2세트를 남겼다. 배달 일을 안 하게 되면 3으로 되돌린다. 손바닥을 위로 — 손목 굴곡. 전완 앞면(손바닥쪽) 굴근군이다: 요측 · 척측수근굴근 + 장요굴근, 쥐는 동안 심지 · 천지굴근이 보조한다. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다 (2026-10-02).</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>[2026-10-04 생수배송 대비 — 일 · 목 3 → 2 · 화 3 → 0(보류)] 캐리 · 천국의 계단이 굴근을 쥐고 버티는 쪽으로 채운다. 늘어난 구간 자극은 캐리가 못 주므로 일 · 목에 2세트를 남겼다. 배달 일을 안 하게 되면 3으로 되돌린다. [2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 11세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>[2026-10-04] 직접 16: 굴근(손등 아래) 일 2 · 화 0(보류) · 목 2 — 생수배송 대비 캐리 · 계단이 굴근을 채운다. 신근 9 · 리버스컬 3은 그대로. 실질 24.0 → 19. 이전 기록: 직접 21세트: 리스트 컬 굴근 · 신근 슈퍼세트를 팔 하는 날 셋에 각 3+3(일 · 화 · 목) + 화요일 리버스컬 3. 간접 3.0 — 컬 3종 0.33씩. [2026-10-02 사용자 지정 '그냥 다 넣어'] 9 → 21로 올렸고 빈도가 주 1회 → 3회가 됐다. 실질 24.0으로 천장(20)을 넘겨 '과다 점검'이 뜨는 첫 부위다. 굴근은 일 · 목에서 당기기(16 · 11세트) 뒤에 오므로 중량을 7.5로 낮춰 잡았다(화요일 10) — 신근은 세 날 다 같은 중량이다 — 당기기가 신근을 전혀 쓰지 않아 날마다 흔들리지 않는다. 전완은 세 갈래이고 셋을 다 덮는다 — 손목 굴근군(앞면 · 손등 아래 9) · 손목 신근군(뒷면 · 손등 위 9) · 상완요골근(요측 · 팔꿈치를 넘는다 · 리버스컬 3). 리스트 컬 두 개가 가르는 것은 앞/뒤이고, 요측 / 척측(엄지쪽 / 새끼손가락쪽)으로 가르는 종목은 없다. 신근 중량은 7.5로 통일했다 — 굴근의 절반 남짓한 힘이라 같은 10kg을 쓰는 것이 말이 안 됐다(재택도 굴근 15 / 신근 10으로 갈라 둔다). 되돌리려면 일 · 목의 굴근(손등 아래)부터 뺀다 — 순수 그립이 온종일 등척성으로 쓰는 쪽이고, 09-04 규칙상 그 등척성은 계수 0이라 표에 안 보이지만 실제 부하는 있다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>· 전완 24.0 — **'과다 점검'이 뜨는 유일한 부위이고 그게 뜬 첫 사례다**(2026-10-02 사용자 지정). 표가 금지하지는 않는다. 다만 손목 · 팔꿈치가 시큰해지면 가장 먼저 의심할 자리이고, 되돌리는 순서는 일 · 목의 굴근(손등 아래) → 리버스컬이다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다. → [2026-10-04] 이 순서대로 굴근부터 내렸다(일 · 목 3 → 2 · 화 3 → 0 보류, 사용자 결정) — 실질 19. 행은 지우지 않았다.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>약 72분</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>약 43분</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -5570,14 +5546,6 @@
     <t>· ⑬ [2026-10-04] 리스트 컬 손등 아래(굴근) 일 · 목 3 → 2 · 화 3 → 0(보류) — 사용자 결정, 생수배송 대비 캐리 · 천국의 계단이 굴근을 채운다. 화요일은 수요일 캐리 전날이라 0. 행은 남겨 두고 세트만 바꿨다 — 일을 안 하게 되면 3으로 되돌린다. 전완 직접 21 → 16 · 실질 24.0 → 19 · 206세트.</t>
   </si>
   <si>
-    <t>· 목 43세트 98분 · 수 42세트 104분 · 토 41세트 101분 · 일 31세트 72분 · 화 24세트 43분 · 월 25세트 63분.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>206세트</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>화요일 24세트 (삼두 3 · 이두 3 · 전완 6 · 목 6 · 복근 6)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -5590,7 +5558,42 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>통증이 나면 그날 증량 금지. 리스트컬은 2026-10-04에 굴근을 줄였다(전완 실질 24 → 19) — 더 줄이는 건 이 조건일 때만</t>
+    <t>[2026-10-04 생수배송 대비 — 일 3 그대로(같은 날 2로 내렸다가 사용자 결정으로 복귀) · 목 3 → 2 · 화 3 → 0(보류)] 캐리 · 천국의 계단이 굴근을 쥐고 버티는 쪽으로 채운다. 일요일은 다음 캐리(수)까지 이틀이 비어 3세트를 둔다 — 목요일은 토요일 캐리까지 하루뿐이라 2. 배달 일을 안 하게 되면 3으로 되돌린다. [2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 17세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-10-04 생수배송 대비 — 일 3 · 목 3 → 2 · 화 3 → 0(보류)] 캐리 · 천국의 계단이 굴근을 쥐고 버티는 쪽으로 채운다. 늘어난 구간 자극은 캐리가 못 주므로 일 3 · 목 2를 남겼다. 배달 일을 안 하게 되면 3으로 되돌린다. 손바닥을 위로 — 손목 굴곡. 전완 앞면(손바닥쪽) 굴근군이다: 요측 · 척측수근굴근 + 장요굴근, 쥐는 동안 심지 · 천지굴근이 보조한다. 그립과 같은 구획이지만 이 날은 당기기가 없어 온전히 나온다. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다 (2026-10-02).</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-10-04 생수배송 대비 — 일 3 · 목 3 → 2 · 화 3 → 0(보류)] 캐리 · 천국의 계단이 굴근을 쥐고 버티는 쪽으로 채운다. 늘어난 구간 자극은 캐리가 못 주므로 일 3 · 목 2를 남겼다. 배달 일을 안 하게 되면 3으로 되돌린다. [2026-10-02 사용자 지정 — 팔 하는 날마다] 손바닥을 위로 — 손목 굴곡, 전완 앞면 굴근군. 손등 위와 길항근 슈퍼세트 — 그립만 뒤집으므로 휴식 10초가 전환 시간이다. 중량을 화요일(10)보다 낮게 잡았다: 이 날 당기기 11세트가 굴근을 등척성으로 이미 다 썼다. 더블 프로그레션은 날마다 따로 본다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-10-04] 직접 17: 굴근(손등 아래) 일 3 · 화 0(보류) · 목 2 — 생수배송 대비 캐리 · 계단이 굴근을 채운다. 신근 9 · 리버스컬 3은 그대로. 실질 24.0 → 20. 이전 기록: 직접 21세트: 리스트 컬 굴근 · 신근 슈퍼세트를 팔 하는 날 셋에 각 3+3(일 · 화 · 목) + 화요일 리버스컬 3. 간접 3.0 — 컬 3종 0.33씩. [2026-10-02 사용자 지정 '그냥 다 넣어'] 9 → 21로 올렸고 빈도가 주 1회 → 3회가 됐다. 실질 24.0으로 천장(20)을 넘겨 '과다 점검'이 뜨는 첫 부위다. 굴근은 일 · 목에서 당기기(16 · 11세트) 뒤에 오므로 중량을 7.5로 낮춰 잡았다(화요일 10) — 신근은 세 날 다 같은 중량이다 — 당기기가 신근을 전혀 쓰지 않아 날마다 흔들리지 않는다. 전완은 세 갈래이고 셋을 다 덮는다 — 손목 굴근군(앞면 · 손등 아래 9) · 손목 신근군(뒷면 · 손등 위 9) · 상완요골근(요측 · 팔꿈치를 넘는다 · 리버스컬 3). 리스트 컬 두 개가 가르는 것은 앞/뒤이고, 요측 / 척측(엄지쪽 / 새끼손가락쪽)으로 가르는 종목은 없다. 신근 중량은 7.5로 통일했다 — 굴근의 절반 남짓한 힘이라 같은 10kg을 쓰는 것이 말이 안 됐다(재택도 굴근 15 / 신근 10으로 갈라 둔다). 되돌리려면 일 · 목의 굴근(손등 아래)부터 뺀다 — 순수 그립이 온종일 등척성으로 쓰는 쪽이고, 09-04 규칙상 그 등척성은 계수 0이라 표에 안 보이지만 실제 부하는 있다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 전완 24.0 — **'과다 점검'이 뜨는 유일한 부위이고 그게 뜬 첫 사례다**(2026-10-02 사용자 지정). 표가 금지하지는 않는다. 다만 손목 · 팔꿈치가 시큰해지면 가장 먼저 의심할 자리이고, 되돌리는 순서는 일 · 목의 굴근(손등 아래) → 리버스컬이다. 신근은 그립이 전혀 안 쓰는 근육이라 마지막까지 남긴다. → [2026-10-04] 이 순서대로 굴근부터 내렸다(목 3 → 2 · 화 3 → 0 보류, 일은 3 유지 — 사용자 결정) — 실질 20. 행은 지우지 않았다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 73분</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· ⑭ [2026-10-04 같은 날] 일요일 손등 아래 2 → 3으로 되돌렸다 — 사용자 결정. 다음 캐리(수)까지 이틀이 비는 날이라 회복 여유가 있다. 목요일은 토요일 캐리까지 하루뿐이라 2 그대로. 전완 직접 17 · 실질 20 · 207세트.</t>
+  </si>
+  <si>
+    <t>· 목 43세트 98분 · 수 42세트 104분 · 토 41세트 101분 · 일 32세트 73분 · 화 24세트 43분 · 월 25세트 63분.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>207세트</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>통증이 나면 그날 증량 금지. 리스트컬은 2026-10-04에 굴근을 줄였다(전완 실질 24 → 20) — 더 줄이는 건 이 조건일 때만</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
@@ -12621,7 +12624,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -12710,10 +12713,10 @@
       </c>
       <c r="E7" s="121">
         <f>복귀_일_수평당기기!$E$22</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1478</v>
+        <v>1485</v>
       </c>
       <c r="G7" s="115" t="s">
         <v>917</v>
@@ -12761,10 +12764,10 @@
         <v>24</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="G9" s="115" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1">
@@ -12809,7 +12812,7 @@
         <v>43</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="G11" s="115" t="s">
         <v>933</v>
@@ -12847,7 +12850,7 @@
       <c r="D13" s="122"/>
       <c r="E13" s="116">
         <f>SUM(E6:E12)</f>
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F13" s="116" t="s">
         <v>1408</v>
@@ -13001,121 +13004,126 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="126" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="107" t="s">
+      <c r="A46" s="126" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="107" t="s">
         <v>963</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="123" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="123" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="123" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="123" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="123" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="107" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" s="107" t="s">
         <v>968</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="123" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="123" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="123" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="123" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="123" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="123" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="107" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" s="107" t="s">
         <v>974</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="123" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1385</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="123" t="s">
-        <v>975</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="123" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="123" t="s">
-        <v>1407</v>
+        <v>976</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="123" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="123" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="107" t="s">
+    <row r="68" spans="1:1">
+      <c r="A68" s="107" t="s">
         <v>978</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="123" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="123" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="123" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="123" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="123" t="s">
         <v>982</v>
       </c>
     </row>
@@ -14240,7 +14248,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="114">
         <v>15</v>
@@ -14253,10 +14261,10 @@
       </c>
       <c r="I19" s="114">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="K19" s="115" t="s">
         <v>1041</v>
@@ -14356,7 +14364,7 @@
       </c>
       <c r="E22" s="116">
         <f>SUM(E11:E21)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" s="116"/>
       <c r="G22" s="116"/>
@@ -15312,7 +15320,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1474</v>
+        <v>1481</v>
       </c>
       <c r="K14" s="115" t="s">
         <v>1041</v>
@@ -15596,12 +15604,12 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -17830,7 +17838,7 @@
         <v>1.7</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1475</v>
+        <v>1482</v>
       </c>
       <c r="K21" s="115" t="s">
         <v>1041</v>
@@ -18209,7 +18217,7 @@
       <c r="D13" s="135"/>
       <c r="E13" s="135"/>
       <c r="F13" s="127" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -18880,7 +18888,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="D7" s="115" t="s">
         <v>1382</v>
@@ -18964,7 +18972,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="115" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="D13" s="115" t="s">
         <v>36</v>
@@ -21617,7 +21625,7 @@
       </c>
       <c r="B22" s="114">
         <f>SUMIFS(복귀_토_하체전면!$E:$E,복귀_토_하체전면!$C:$C,$A22)+SUMIFS(복귀_일_수평당기기!$E:$E,복귀_일_수평당기기!$C:$C,$A22)+SUMIFS(복귀_월_가슴!$E:$E,복귀_월_가슴!$C:$C,$A22)+SUMIFS(복귀_화_팔!$E:$E,복귀_화_팔!$C:$C,$A22)+SUMIFS(복귀_수_하체후면!$E:$E,복귀_수_하체후면!$C:$C,$A22)+SUMIFS(복귀_목_수직당기기!$E:$E,복귀_목_수직당기기!$C:$C,$A22)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="114">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$93,복귀_간접계수맵!$C$7:$C$93,$A22),0.5)</f>
@@ -21625,14 +21633,14 @@
       </c>
       <c r="D22" s="114">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" s="114" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -21713,11 +21721,11 @@
       </c>
       <c r="B26" s="116">
         <f>SUM(B5:B25)</f>
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D26" s="116">
         <f ca="1">SUM(D5:D25)</f>
-        <v>268.5</v>
+        <v>269.5</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -21862,7 +21870,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="60" spans="1:1">

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495A3802-4BA8-4695-B2EE-8F9BDFD60A48}"/>
+  <xr:revisionPtr revIDLastSave="589" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A545A5EE-3E8E-4F99-B18E-B89B509A7887}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="3" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4671,9 +4671,6 @@
     <t>4번 다 안 놓치면 다음 주 한 손 +2kg</t>
   </si>
   <si>
-    <t>막힘 없으면 6주 만에 36kg, 현실적으로는 8~10주</t>
-  </si>
-  <si>
     <t>스트랩</t>
   </si>
   <si>
@@ -5049,9 +5046,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>· 7주차에 36kg이 최선 경로다. 정체 주는 같은 무게를 반복하고 목표 칸을 한 줄씩 아래로 민다.</t>
   </si>
   <si>
     <t>하루 종일 오르내리는 지구력. 무게는 12~16kg에서 멈춘다 — 36kg은 복귀_캐리 몫. 세트 카운트 · 세트검산에는 넣지 않는다.</t>
@@ -5594,6 +5588,14 @@
   </si>
   <si>
     <t>통증이 나면 그날 증량 금지. 리스트컬은 2026-10-04에 굴근을 줄였다(전완 실질 24 → 20) — 더 줄이는 건 이 조건일 때만</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 3주차(10/17 주)는 프로그램 13주차 디로드라 26kg 그대로 — 웨이트와 같이 한 주 멈춘다. 그래서 36kg은 8주차(11/21 주). 디로드 날짜가 바뀌면 멈추는 줄도 같이 옮긴다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>막힘 없으면 디로드 한 주 포함 7주 만에 36kg(8주차 · 11/21 주)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
@@ -12716,7 +12718,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="G7" s="115" t="s">
         <v>917</v>
@@ -12764,10 +12766,10 @@
         <v>24</v>
       </c>
       <c r="F9" s="114" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G9" s="115" t="s">
         <v>1473</v>
-      </c>
-      <c r="G9" s="115" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1">
@@ -12812,7 +12814,7 @@
         <v>43</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="G11" s="115" t="s">
         <v>933</v>
@@ -13004,12 +13006,12 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="126" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="126" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -13074,7 +13076,7 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="62" spans="1:1">
@@ -14264,7 +14266,7 @@
         <v>2.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K19" s="115" t="s">
         <v>1041</v>
@@ -15320,7 +15322,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="K14" s="115" t="s">
         <v>1041</v>
@@ -15604,12 +15606,12 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -17838,7 +17840,7 @@
         <v>1.7</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="K21" s="115" t="s">
         <v>1041</v>
@@ -18175,21 +18177,21 @@
       <c r="D10" s="135"/>
       <c r="E10" s="135"/>
       <c r="F10" s="127" t="s">
-        <v>1426</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="127" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B11" s="135" t="s">
         <v>1427</v>
-      </c>
-      <c r="B11" s="135" t="s">
-        <v>1428</v>
       </c>
       <c r="C11" s="135"/>
       <c r="D11" s="135"/>
       <c r="E11" s="135"/>
       <c r="F11" s="127" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -18197,46 +18199,46 @@
         <v>9</v>
       </c>
       <c r="B12" s="135" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C12" s="135"/>
       <c r="D12" s="135"/>
       <c r="E12" s="135"/>
       <c r="F12" s="127" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="127" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B13" s="135" t="s">
         <v>1431</v>
-      </c>
-      <c r="B13" s="135" t="s">
-        <v>1432</v>
       </c>
       <c r="C13" s="135"/>
       <c r="D13" s="135"/>
       <c r="E13" s="135"/>
       <c r="F13" s="127" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="127" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B14" s="135" t="s">
         <v>1433</v>
-      </c>
-      <c r="B14" s="135" t="s">
-        <v>1434</v>
       </c>
       <c r="C14" s="135"/>
       <c r="D14" s="135"/>
       <c r="E14" s="135"/>
       <c r="F14" s="127" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" s="131" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18244,19 +18246,19 @@
         <v>123</v>
       </c>
       <c r="B17" s="129" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C17" s="129" t="s">
         <v>1437</v>
       </c>
-      <c r="C17" s="129" t="s">
+      <c r="D17" s="129" t="s">
         <v>1438</v>
       </c>
-      <c r="D17" s="129" t="s">
+      <c r="E17" s="129" t="s">
         <v>1439</v>
       </c>
-      <c r="E17" s="129" t="s">
+      <c r="F17" s="129" t="s">
         <v>1440</v>
-      </c>
-      <c r="F17" s="129" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18299,11 +18301,11 @@
         <v>46312</v>
       </c>
       <c r="C20" s="132">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20" s="132">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E20" s="132"/>
     </row>
@@ -18315,11 +18317,11 @@
         <v>46319</v>
       </c>
       <c r="C21" s="132">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="132">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E21" s="132"/>
     </row>
@@ -18331,11 +18333,11 @@
         <v>46326</v>
       </c>
       <c r="C22" s="132">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" s="132">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E22" s="132"/>
     </row>
@@ -18347,11 +18349,11 @@
         <v>46333</v>
       </c>
       <c r="C23" s="132">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D23" s="132">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E23" s="132"/>
     </row>
@@ -18363,11 +18365,11 @@
         <v>46340</v>
       </c>
       <c r="C24" s="132">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D24" s="132">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E24" s="132"/>
     </row>
@@ -18421,7 +18423,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="127" t="s">
-        <v>1442</v>
+        <v>1488</v>
       </c>
     </row>
   </sheetData>
@@ -18456,12 +18458,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="128" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="127" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -18474,7 +18476,7 @@
         <v>904</v>
       </c>
       <c r="B5" s="129" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="C5" s="130"/>
       <c r="D5" s="130"/>
@@ -18491,7 +18493,7 @@
         <v>909</v>
       </c>
       <c r="B6" s="135" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="C6" s="135"/>
       <c r="D6" s="135"/>
@@ -18500,7 +18502,7 @@
       <c r="G6" s="135"/>
       <c r="H6" s="135"/>
       <c r="I6" s="127" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -18508,7 +18510,7 @@
         <v>914</v>
       </c>
       <c r="B7" s="135" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C7" s="135"/>
       <c r="D7" s="135"/>
@@ -18517,7 +18519,7 @@
       <c r="G7" s="135"/>
       <c r="H7" s="135"/>
       <c r="I7" s="127" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -18525,7 +18527,7 @@
         <v>918</v>
       </c>
       <c r="B8" s="135" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C8" s="135"/>
       <c r="D8" s="135"/>
@@ -18534,7 +18536,7 @@
       <c r="G8" s="135"/>
       <c r="H8" s="135"/>
       <c r="I8" s="127" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -18551,7 +18553,7 @@
       <c r="G9" s="135"/>
       <c r="H9" s="135"/>
       <c r="I9" s="127" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -18559,7 +18561,7 @@
         <v>925</v>
       </c>
       <c r="B10" s="135" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="C10" s="135"/>
       <c r="D10" s="135"/>
@@ -18568,7 +18570,7 @@
       <c r="G10" s="135"/>
       <c r="H10" s="135"/>
       <c r="I10" s="127" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -18576,7 +18578,7 @@
         <v>930</v>
       </c>
       <c r="B11" s="135" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C11" s="135"/>
       <c r="D11" s="135"/>
@@ -18585,7 +18587,7 @@
       <c r="G11" s="135"/>
       <c r="H11" s="135"/>
       <c r="I11" s="127" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -18593,7 +18595,7 @@
         <v>934</v>
       </c>
       <c r="B12" s="135" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="C12" s="135"/>
       <c r="D12" s="135"/>
@@ -18602,12 +18604,12 @@
       <c r="G12" s="135"/>
       <c r="H12" s="135"/>
       <c r="I12" s="127" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" s="131" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -18615,28 +18617,28 @@
         <v>123</v>
       </c>
       <c r="B15" s="129" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D15" s="129" t="s">
         <v>1454</v>
       </c>
-      <c r="C15" s="129" t="s">
+      <c r="E15" s="129" t="s">
         <v>1455</v>
       </c>
-      <c r="D15" s="129" t="s">
+      <c r="F15" s="129" t="s">
         <v>1456</v>
       </c>
-      <c r="E15" s="129" t="s">
+      <c r="G15" s="129" t="s">
         <v>1457</v>
       </c>
-      <c r="F15" s="129" t="s">
+      <c r="H15" s="129" t="s">
         <v>1458</v>
       </c>
-      <c r="G15" s="129" t="s">
+      <c r="I15" s="129" t="s">
         <v>1459</v>
-      </c>
-      <c r="H15" s="129" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I15" s="129" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -18676,7 +18678,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="134" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C17" s="132">
         <v>4</v>
@@ -18708,7 +18710,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="134" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C18" s="132">
         <v>5</v>
@@ -18740,7 +18742,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="134" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C19" s="132">
         <v>5</v>
@@ -18774,32 +18776,32 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="127" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="127" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="127" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="127" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="127" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="127" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
   </sheetData>
@@ -18888,7 +18890,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D7" s="115" t="s">
         <v>1382</v>
@@ -18972,7 +18974,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="115" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="D13" s="115" t="s">
         <v>36</v>
@@ -21640,7 +21642,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -21870,7 +21872,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="60" spans="1:1">

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="596" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BD24385-33DA-4320-AE69-CCE33AD5C958}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A10D329-DA1A-466C-9FD5-A42BE2F690ED}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2817" uniqueCount="1493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2816" uniqueCount="1492">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -5585,28 +5585,27 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 3주차(10/17 주)는 프로그램 13주차 디로드라 26kg 그대로 — 웨이트와 같이 한 주 멈춘다. 그래서 36kg은 8주차(11/21 주). 디로드 날짜가 바뀌면 멈추는 줄도 같이 옮긴다.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>막힘 없으면 디로드 한 주 포함 7주 만에 36kg(8주차 · 11/21 주)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>디로드 주차</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>← 디로드할 프로그램 주차(여럿이면 13, 20처럼 쉼표). 그 주는 앱이 세트를 절반으로 보여 주고 중량을 한 주 멈춘다 — 미루기 안 눌러도 된다. 계획 밖의 쉰 주만 미루기</t>
-  </si>
-  <si>
-    <t>· 계획한 디로드는 위 '디로드 주차'에 적는다 — 앱이 그 주를 알아서 멈추고 세트를 절반으로 보여 준다(2026-10-04). 계획 밖에 통째로 쉰 주만 앱 달력에서 '한 주 미루기'를 누른다 — 중량만 한 주 늦게 올라가고 주차 표시는 그대로다. 영구히 맞추려면 '주차 기준일'을 한 주 뒤로 옮긴다.</t>
+    <t>디로드 시작일</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 디로드 주에는 주차를 올리지 않는다. 시작중량_설정 '디로드 주차'에 적어 두면 앱이 그 주 중량을 멈추고 세트를 위 규칙대로 절반으로 보여 준다(메인은 내림 · 보조는 반올림 · 데드는 0). 그 주는 증량 기록을 적지 않는다.</t>
+    <t>← 디로드 주가 시작되는 토요일(여럿이면 텍스트로 2026-10-17, 2026-12-26). 그 주는 주차로 세지 않고 디로드 주로만 표시된다 — 주차 · 중량 · C4가 전부 그 주에 멈추고, 앱이 세트를 절반으로 보여 준다. 미루기는 누르지 않는다</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 계획한 디로드는 위 '디로드 시작일'에 적는다 — 그 주는 주차로 세지 않고 '디로드 주'로 표시되며, 주차 · 중량 · C4가 같이 멈춘다(2026-10-04 사용자 지정). C4는 디로드 주에 그대로 두고 다음 주에 평소처럼 올린다. 계획 밖에 통째로 쉰 주만 앱 달력에서 '한 주 미루기'를 누른다 — 중량만 한 주 늦게 올라가고 주차 표시는 그대로다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 디로드 주는 주차로 세지 않는다 — 시작중량_설정 '디로드 시작일'에 적어 두면 앱이 그 주를 '디로드 주'로만 표시하고 주차 · 중량 · C4를 같이 멈춘다. 세트는 위 규칙대로 절반으로 보인다(메인은 내림 · 보조는 반올림 · 데드는 0). 그 주는 증량 기록을 적지 않는다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 3번째 줄(10/17 주)은 디로드 주라 26kg 그대로 — 웨이트와 같이 한 주 멈추고, 앱에는 주차 대신 디로드로 뜬다(그 뒤가 3주차). 그래서 36kg은 11/21 주. 디로드 날짜가 바뀌면 멈추는 줄도 같이 옮긴다.</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
@@ -6183,7 +6182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6505,7 +6504,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -7480,13 +7478,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C63" s="100">
+        <v>46312</v>
+      </c>
+      <c r="D63" t="s">
         <v>1488</v>
-      </c>
-      <c r="C63" s="141" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -7517,7 +7515,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -18200,7 +18198,7 @@
       <c r="D10" s="135"/>
       <c r="E10" s="135"/>
       <c r="F10" s="127" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18446,7 +18444,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="127" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
     </row>
   </sheetData>
@@ -19149,7 +19147,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="48" spans="1:1">

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="611" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B8FD4E2-A4BB-4FF2-86F6-D2FAD7D5439A}"/>
+  <xr:revisionPtr revIDLastSave="616" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE455280-6587-4AFB-9A7B-8867B4DC3081}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -4326,144 +4326,6 @@
   </si>
   <si>
     <t>약 486분 (8시간 6분)</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">https://www.youtube.com/shorts/KGkE5bXQR24, </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>명치가</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>의자</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최상단</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>높이에</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맞게</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">설정, </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>https://www.youtube.com/shorts/W0TMqVIhpcQ</t>
-    </r>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
@@ -5613,6 +5475,10 @@
   </si>
   <si>
     <t>· 기본은 증량 6주 + 디로드 1주(7주 덩어리)다 — 시작중량_설정 '디로드 간격(주)' = 7로 앱이 자동 반복한다(2026-10-04 사용자 지정: 10/17 · 12/5 · 1/23 · 3/13 …). 토요일 스쿼트가 2주 연속 안 오르면 그 시점에 앞당기고, 그 토요일을 '디로드 시작일'에 추가한다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>당겼을 때 손잡이가 아래쪽 갈비뼈에서 명치 사이에 닿고, 팔꿈치는 몸통 옆을 지나 뒤로 빠져야 합니다., 패드는 가슴이 패드에서 떨어지지 않는 거리</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
@@ -6189,7 +6055,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6499,7 +6365,8 @@
     <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -6511,7 +6378,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -7486,24 +7353,24 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C63" s="100">
         <v>46312</v>
       </c>
       <c r="D63" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C64" s="135">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
         <v>1490</v>
-      </c>
-      <c r="C64" s="141">
-        <v>7</v>
-      </c>
-      <c r="D64" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -7534,7 +7401,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -8241,16 +8108,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="139" t="s">
         <v>641</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
@@ -8262,16 +8129,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="137" t="s">
         <v>643</v>
       </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
@@ -10361,7 +10228,7 @@
       <c r="F5" s="53" t="s">
         <v>744</v>
       </c>
-      <c r="G5" s="139" t="s">
+      <c r="G5" s="140" t="s">
         <v>745</v>
       </c>
       <c r="H5" s="56">
@@ -10404,7 +10271,7 @@
       <c r="F6" s="53" t="s">
         <v>746</v>
       </c>
-      <c r="G6" s="140"/>
+      <c r="G6" s="141"/>
       <c r="J6" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>12.6</v>
@@ -10437,7 +10304,7 @@
       <c r="F7" s="53" t="s">
         <v>747</v>
       </c>
-      <c r="G7" s="139" t="s">
+      <c r="G7" s="140" t="s">
         <v>748</v>
       </c>
       <c r="H7" s="56">
@@ -10476,7 +10343,7 @@
       <c r="F8" s="53" t="s">
         <v>749</v>
       </c>
-      <c r="G8" s="140"/>
+      <c r="G8" s="141"/>
       <c r="J8" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>3.9</v>
@@ -10509,7 +10376,7 @@
       <c r="F9" s="53" t="s">
         <v>750</v>
       </c>
-      <c r="G9" s="140"/>
+      <c r="G9" s="141"/>
       <c r="J9" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.5</v>
@@ -10542,7 +10409,7 @@
       <c r="F10" s="53" t="s">
         <v>751</v>
       </c>
-      <c r="G10" s="140"/>
+      <c r="G10" s="141"/>
       <c r="J10" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>14.4</v>
@@ -10780,7 +10647,7 @@
       <c r="F17" s="53" t="s">
         <v>758</v>
       </c>
-      <c r="G17" s="139" t="s">
+      <c r="G17" s="140" t="s">
         <v>382</v>
       </c>
       <c r="H17" s="56">
@@ -10819,7 +10686,7 @@
       <c r="F18" s="53" t="s">
         <v>759</v>
       </c>
-      <c r="G18" s="140"/>
+      <c r="G18" s="141"/>
       <c r="J18" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.1</v>
@@ -12758,7 +12625,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="114" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="G7" s="115" t="s">
         <v>914</v>
@@ -12806,10 +12673,10 @@
         <v>24</v>
       </c>
       <c r="F9" s="114" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G9" s="115" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1">
@@ -12854,7 +12721,7 @@
         <v>43</v>
       </c>
       <c r="F11" s="114" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="G11" s="115" t="s">
         <v>930</v>
@@ -13046,12 +12913,12 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="126" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="126" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -13116,7 +12983,7 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="123" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="62" spans="1:1">
@@ -14024,8 +13891,8 @@
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="J12" s="75" t="s">
-        <v>1406</v>
+      <c r="J12" s="136" t="s">
+        <v>1493</v>
       </c>
       <c r="K12" s="115" t="s">
         <v>1026</v>
@@ -14306,7 +14173,7 @@
         <v>2.5</v>
       </c>
       <c r="J19" s="115" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K19" s="115" t="s">
         <v>1038</v>
@@ -15362,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="115" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K14" s="115" t="s">
         <v>1038</v>
@@ -15646,12 +15513,12 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="117" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="117" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -17841,7 +17708,7 @@
         <v>5.8</v>
       </c>
       <c r="J20" s="75" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="K20" s="115" t="s">
         <v>1207</v>
@@ -17880,7 +17747,7 @@
         <v>1.7</v>
       </c>
       <c r="J21" s="115" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K21" s="115" t="s">
         <v>1038</v>
@@ -18123,17 +17990,17 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="128" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="127" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="99" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18154,131 +18021,131 @@
       <c r="A6" s="127" t="s">
         <v>901</v>
       </c>
-      <c r="B6" s="135" t="s">
+      <c r="B6" s="142" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C6" s="142"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="127" t="s">
         <v>1411</v>
-      </c>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="127" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="135" t="s">
+      <c r="B7" s="142" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C7" s="142"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="127" t="s">
         <v>1413</v>
-      </c>
-      <c r="C7" s="135"/>
-      <c r="D7" s="135"/>
-      <c r="E7" s="135"/>
-      <c r="F7" s="127" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="127" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B8" s="142" t="s">
         <v>1415</v>
       </c>
-      <c r="B8" s="135" t="s">
+      <c r="C8" s="142"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="142"/>
+      <c r="F8" s="127" t="s">
         <v>1416</v>
-      </c>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="127" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="127" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B9" s="142" t="s">
         <v>1418</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="C9" s="142"/>
+      <c r="D9" s="142"/>
+      <c r="E9" s="142"/>
+      <c r="F9" s="127" t="s">
         <v>1419</v>
-      </c>
-      <c r="C9" s="135"/>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="127" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="127" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B10" s="142" t="s">
         <v>1421</v>
       </c>
-      <c r="B10" s="135" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C10" s="135"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="142"/>
       <c r="F10" s="127" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="127" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B11" s="142" t="s">
         <v>1423</v>
       </c>
-      <c r="B11" s="135" t="s">
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="127" t="s">
         <v>1424</v>
-      </c>
-      <c r="C11" s="135"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="135"/>
-      <c r="F11" s="127" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="135" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
+      <c r="B12" s="142" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
       <c r="F12" s="127" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="127" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B13" s="142" t="s">
         <v>1427</v>
       </c>
-      <c r="B13" s="135" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
       <c r="F13" s="127" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="127" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B14" s="142" t="s">
         <v>1429</v>
       </c>
-      <c r="B14" s="135" t="s">
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="127" t="s">
         <v>1430</v>
-      </c>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="127" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" s="131" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18286,19 +18153,19 @@
         <v>121</v>
       </c>
       <c r="B17" s="129" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C17" s="129" t="s">
         <v>1433</v>
       </c>
-      <c r="C17" s="129" t="s">
+      <c r="D17" s="129" t="s">
         <v>1434</v>
       </c>
-      <c r="D17" s="129" t="s">
+      <c r="E17" s="129" t="s">
         <v>1435</v>
       </c>
-      <c r="E17" s="129" t="s">
+      <c r="F17" s="129" t="s">
         <v>1436</v>
-      </c>
-      <c r="F17" s="129" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18463,7 +18330,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="127" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
   </sheetData>
@@ -18498,12 +18365,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="128" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="127" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -18516,7 +18383,7 @@
         <v>901</v>
       </c>
       <c r="B5" s="129" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="C5" s="130"/>
       <c r="D5" s="130"/>
@@ -18532,124 +18399,124 @@
       <c r="A6" s="127" t="s">
         <v>906</v>
       </c>
-      <c r="B6" s="135" t="s">
+      <c r="B6" s="142" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C6" s="142"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="142"/>
+      <c r="I6" s="127" t="s">
         <v>1440</v>
-      </c>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="127" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="127" t="s">
         <v>911</v>
       </c>
-      <c r="B7" s="135" t="s">
+      <c r="B7" s="142" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C7" s="142"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="142"/>
+      <c r="H7" s="142"/>
+      <c r="I7" s="127" t="s">
         <v>1442</v>
-      </c>
-      <c r="C7" s="135"/>
-      <c r="D7" s="135"/>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="127" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="127" t="s">
         <v>915</v>
       </c>
-      <c r="B8" s="135" t="s">
+      <c r="B8" s="142" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C8" s="142"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="142"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="127" t="s">
         <v>1442</v>
-      </c>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="135"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="127" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="127" t="s">
         <v>919</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="B9" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="135"/>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="142"/>
+      <c r="E9" s="142"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="142"/>
       <c r="I9" s="127" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="127" t="s">
         <v>922</v>
       </c>
-      <c r="B10" s="135" t="s">
-        <v>1440</v>
-      </c>
-      <c r="C10" s="135"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
+      <c r="B10" s="142" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C10" s="142"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
       <c r="I10" s="127" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="127" t="s">
         <v>927</v>
       </c>
-      <c r="B11" s="135" t="s">
+      <c r="B11" s="142" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="127" t="s">
         <v>1442</v>
-      </c>
-      <c r="C11" s="135"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="135"/>
-      <c r="F11" s="135"/>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="127" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="127" t="s">
         <v>931</v>
       </c>
-      <c r="B12" s="135" t="s">
+      <c r="B12" s="142" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="127" t="s">
         <v>1446</v>
-      </c>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="127" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" s="131" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -18657,28 +18524,28 @@
         <v>121</v>
       </c>
       <c r="B15" s="129" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C15" s="129" t="s">
         <v>1449</v>
       </c>
-      <c r="C15" s="129" t="s">
+      <c r="D15" s="129" t="s">
         <v>1450</v>
       </c>
-      <c r="D15" s="129" t="s">
+      <c r="E15" s="129" t="s">
         <v>1451</v>
       </c>
-      <c r="E15" s="129" t="s">
+      <c r="F15" s="129" t="s">
         <v>1452</v>
       </c>
-      <c r="F15" s="129" t="s">
+      <c r="G15" s="129" t="s">
         <v>1453</v>
       </c>
-      <c r="G15" s="129" t="s">
+      <c r="H15" s="129" t="s">
         <v>1454</v>
       </c>
-      <c r="H15" s="129" t="s">
+      <c r="I15" s="129" t="s">
         <v>1455</v>
-      </c>
-      <c r="I15" s="129" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -18718,7 +18585,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="134" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C17" s="132">
         <v>4</v>
@@ -18750,7 +18617,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="134" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="C18" s="132">
         <v>5</v>
@@ -18782,7 +18649,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="134" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C19" s="132">
         <v>5</v>
@@ -18811,37 +18678,37 @@
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" s="99" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="127" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="127" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="127" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="127" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="127" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="127" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
   </sheetData>
@@ -18930,7 +18797,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D7" s="115" t="s">
         <v>1379</v>
@@ -19014,7 +18881,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="115" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D13" s="115" t="s">
         <v>36</v>
@@ -19161,12 +19028,12 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="123" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="123" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -21682,7 +21549,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="115" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
@@ -21912,7 +21779,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="123" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="60" spans="1:1">

--- a/운동프로그램_주6회_v20.xlsx
+++ b/운동프로그램_주6회_v20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="616" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE455280-6587-4AFB-9A7B-8867B4DC3081}"/>
+  <xr:revisionPtr revIDLastSave="671" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E88B6C2-E753-46D1-AC6E-58733FDE3FBC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2818" uniqueCount="1494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="1501">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -3624,18 +3624,12 @@
     <t>와이드 오버그립 랫풀다운</t>
   </si>
   <si>
-    <t>넓은 엎침 그립 — 팔꿈치가 몸에서 벌어진 경로로 들어온다. 이두 관여가 가장 적은 수직 당기기다.</t>
-  </si>
-  <si>
     <t>오버그립 랫풀다운 (어깨너비 — 어깨가 불편할 때) / 풀업</t>
   </si>
   <si>
     <t>랫풀다운(언더그립 좁게 안쪽으로)</t>
   </si>
   <si>
-    <t>짧고 깊은 쪽 — 뒤침 그립으로 좁게 잡아 어깨 신전 구간을 끝까지 쓴다. 이두 계수 0.5가 붙는 자리다.</t>
-  </si>
-  <si>
     <t>뉴트럴 그립 랫풀다운 / 어시스트 풀업 머신</t>
   </si>
   <si>
@@ -3720,15 +3714,6 @@
     <t>· 팔이 맨 뒤인 이유 — 앞의 18세트가 이두에 간접을 얹고, 가슴 8세트는 플라이라 삼두를 쓰지 않는다. 그래서 V바 푸쉬다운이 온전히 나온다.</t>
   </si>
   <si>
-    <t>· 44세트 · 약 99분. 전완 슈퍼세트 6 + 백 익스텐션 4 + 인클라인 벤치프레스(스미스) 3이 들어오고 언더그립 랫풀다운 3 → 4 · 디클라인 플라이 4 → 3 · 백 익스텐션 3 → 4로 조정됐다 (2026-10-02 사용자 지정).</t>
-  </si>
-  <si>
-    <t>· 메인 리프트가 없으므로 세션 상한 26의 적용 대상이 아니다. 고립 29를 빼면 실질 15다.</t>
-  </si>
-  <si>
-    <t>· 일요일(32세트 74분)과 합쳐 보면 등 블록 둘이 32/44로 갈린다 — 가슴 10세트가 이 날에 묶여 있어서다. 수요일 104분 · 토요일 101분 다음으로 99분이다.</t>
-  </si>
-  <si>
     <t>· 언더그립 랫풀다운 +60초 · 디클라인 케이블 플라이 +60초. 마지막 세트에만 2단.</t>
   </si>
   <si>
@@ -3744,9 +3729,6 @@
     <t>· 페이스풀에도 걸지 않는다. 가벼운 외회전 종목이라 실패 뒤 반복에서 팔꿈치가 먼저 내려온다.</t>
   </si>
   <si>
-    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  일요일을 수평으로 바꿔줘  /  그냥 다 넣어. 팔하는 날에는 슈퍼세트로 묶어서 (전완)  /  목요일 날에 인클라인 벤치프레스 넣어줘. 3세트  /  디클라인 플라이 4 → 3 · 백 익스텐션 3 → 4 (사용자 엑셀 조정)</t>
-  </si>
-  <si>
     <t>복귀판 간접 세트 계수 맵 — 복귀_세트검산 간접 열(C)의 계산 원천</t>
   </si>
   <si>
@@ -3967,9 +3949,6 @@
   </si>
   <si>
     <t>등 중요부위</t>
-  </si>
-  <si>
-    <t>직접 3세트: 목요일(수직) 오버헤드 슈러그 3 — 팔이 머리 위라 수직 날에 맞는다. 간접 2.8 — 친업 · 언더그립 랫풀다운 · 와이드 랫풀다운 · 해머 스트랭스 로우 각 0.2. 팔이 머리 위에 고정된 채 견갑을 내리는 종목이 이것뿐이다</t>
   </si>
   <si>
     <t>직접 10세트: 수요일 데드 톱 1 + 백오프 2 + 일요일 백 익스텐션 3 · 목요일 4(45도 · 맨몸) (재택도 당기기 두 날에 3세트씩 둔다 · 목요일만 4로 올린 것은 사용자 조정). 3 → 10으로 '보완 필요'가 '충분'이 됐다. **척추 신전을 강조해서 해야 이 9세트가 유효하다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근 · 햄스트링이 주동근이 되고 기립근은 버티기만 한다. 그러면 09-04 규칙상 등척성이라 계수 0이고 이 숫자가 거짓이 된다. 중량은 더블 프로그레션 — 맨몸 15회를 채우면 원판 5~10kg을 안는다('맨몸'은 시작값이지 상한이 아니다). 목요일 것도 원판 금지가 아니고, 데드 다음날이라 일요일보다 낮게 나오는 것이 정상이다 — 수요일 데드나 토요일 스쿼트가 2주 연속 안 오르면 그 날 중량을 먼저 의심한다. 간접 1.4 — 스미스 바벨 로우 · 오버헤드 슈러그 각 0.2 + 루마니안 데드 0.5×3. 스쿼트 · 트랩바 슈러그의 등척성 지지는 2026-10-02에 0으로 내렸다 — '버티기만 하는 자극은 세지 않는다'(09-04 규칙). 루마니안만 0.5로 남는 것은 기립근이 등척성이 아니라 동적으로 신전 · 수축하기 때문이다. 허리를 키우는 것은 데드 3세트와 루마니안 3세트뿐이다</t>
@@ -4305,10 +4284,6 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>직접 16세트: 목요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 4 · 언더그립 좁게 4 + 일요일(수평) 시티드 케이블 로우 2 · 원암 케이블 로우 2 (2026-10-02 사용자 조정 4세트 · 2026-10-04 양팔 2 + 원암 2로 분할). 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머 로우 0.5×3(둘 다 일요일). [2026-10-02 정정] 등을 근육군이 아니라 움직임 평면으로 갈라 광배가 두 날에 11/3으로 걸린다 — 그 전에는 한 날에 14였고 '주 1회'로 적혔지만 반대 날 로우가 전부 광배를 쓰고 있었다</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>직접 13세트: 일요일(수평) 스미스 바벨 로우 4 · 해머 스트랭스 로우 3 · 스캡 슈러그 3 + 목요일(수직) 페이스풀 3. 10/3으로 나뉜다 — 페이스풀이 없으면 일요일 주 1회가 되므로 그 자리를 유지한다(재택도 페이스풀을 수직 날에 둔다). 간접 5.0 — 시티드 · 원암 케이블 로우 0.5×(2+2) + 리버스 펙덱 0.33×4 + 케이블 리버스 플라이 0.33×3 + 벤트오버 레터럴 0.33×3 (케이블 리버스 플라이는 경부하 리어델트라 2026-10-02에 0.5 → 0.33)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -4318,14 +4293,6 @@
   </si>
   <si>
     <t>· 32세트 · 약 73분. 전완 슈퍼세트 6 + 백 익스텐션 3이 들어오고 원암 케이블 로우가 3 → 4로 올라 22 → 32가 됐다 (2026-10-02 사용자가 엑셀에서 직접 조정). 복합 11 / 고립 21이다.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>· 주 486분 = 8시간 6분. 주 4회 370분에서 105분 늘었다. 수(104) · 토(101)가 100분을 넘지만 주 4회 시절 일(121)보다는 작다 — 긴 세션 둘이 짧은 넷으로 분산된 것이 이 개편의 실익이다.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>약 486분 (8시간 6분)</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
@@ -5382,10 +5349,6 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>약 98분</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>사용자 지정으로 구성을 그대로 둔 날. 팔이 메인인 유일한 자리라 늘어난 구간 종목을 여기 뒀다. 전완 6(손등 아래는 2026-10-04부터 0 · 보류) · 목 6 · 복근 6이 전부 이 날이고, 리스트 컬 손등 아래 ↔ 위는 슈퍼세트다</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -5432,10 +5395,6 @@
     <t>· ⑭ [2026-10-04 같은 날] 일요일 손등 아래 2 → 3으로 되돌렸다 — 사용자 결정. 다음 캐리(수)까지 이틀이 비는 날이라 회복 여유가 있다. 목요일은 토요일 캐리까지 하루뿐이라 2 그대로. 전완 직접 17 · 실질 20 · 207세트.</t>
   </si>
   <si>
-    <t>· 목 43세트 98분 · 수 42세트 104분 · 토 41세트 101분 · 일 32세트 73분 · 화 24세트 43분 · 월 25세트 63분.</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
     <t>207세트</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
@@ -5479,6 +5438,82 @@
   </si>
   <si>
     <t>당겼을 때 손잡이가 아래쪽 갈비뼈에서 명치 사이에 닿고, 팔꿈치는 몸통 옆을 지나 뒤로 빠져야 합니다., 패드는 가슴이 패드에서 떨어지지 않는 거리</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>넓은 엎침 그립 — 팔꿈치가 몸에서 벌어진 경로로 들어온다. 이두 관여가 가장 적은 수직 당기기다. [2026-10-05 4 → 3] 한 세트를 4번 암풀다운으로 넘겼다 — 사용자 제안.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>짧고 깊은 쪽 — 뒤침 그립으로 좁게 잡아 어깨 신전 구간을 끝까지 쓴다. 이두 계수 0.5가 붙는 자리다. [2026-10-05 4 → 3] 한 세트를 4번 암풀다운으로 넘겼다 — 사용자 제안.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>암풀다운</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>—</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-10-05 사용자 제안 — 와이드 · 언더그립 각 4 → 3, 그 2세트를 여기로] 스트레이트 암 풀다운. 팔꿈치를 살짝만 굽혀 고정하고 머리 위에서 허벅지까지 어깨 신전만 한다 — 이두가 빠지므로 광배가 그립 · 이두보다 먼저 실패한다. 상체를 조금 숙여 맨 위에서 광배가 늘어나게 한다(늘어난 구간 부하 — 랫풀다운 둘이 못 주는 각도). 그래서 넓게 벌린 경로(와이드) · 좁고 깊은 경로(언더그립) · 팔 편 늘어난 위치(이것) 셋이 고르게 3/3/2로 들어간다. 고립이라 다관절 뒤 마무리로 둔다. 같은 케이블 스테이션에서 로프나 일자 바로 바꾸면 된다. 중량은 첫 세션에 12~15회에 맞춰 잡는다.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이블 풀오버 (로프) / 덤벨 풀오버 / 머신 풀오버</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 암풀다운에도 걸지 않는다 — 바로 앞 언더그립 랫풀다운 드롭과 같은 근육이라 겹친다 (2026-10-05).</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>[요청 원문 2026-10-02] 목요일 가슴/등 — 목요일 팔을 세트 후반부에 · 등도 나누고  /  등도 수평/수직으로 재택처럼 나뉘었으면 한다는거야  /  일요일을 수평으로 바꿔줘  /  그냥 다 넣어. 팔하는 날에는 슈퍼세트로 묶어서 (전완)  /  목요일 날에 인클라인 벤치프레스 넣어줘. 3세트  /  디클라인 플라이 4 → 3 · 백 익스텐션 3 → 4 (사용자 엑셀 조정)  /  [2026-10-05] 암풀 다운 넣는게 맞을까? → 언더그립, 와이드그립 각각 3세트씩하고, 암풀다운 2세트 하는거는 어때?</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔을 편 채 끌어내리며 견갑을 내린다 — 랫풀다운 둘과 같은 견갑 하강 개시 관여. 팔꿈치가 고정이라 이두 · 삼두는 0(등척성) (2026-10-05 신설)</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>직접 16세트: 목요일(수직) 친업 4 · 와이드 오버그립 랫풀다운 3 · 언더그립 좁게 3 · 암풀다운 2 (2026-10-05 랫풀다운 둘 4 → 3, 그 2세트를 늘어난 위치 고립으로) + 일요일(수평) 시티드 케이블 로우 2 · 원암 케이블 로우 2 (2026-10-02 사용자 조정 4세트 · 2026-10-04 양팔 2 + 원암 2로 분할). 간접 3.5 — 스미스 바벨 로우 0.5×4 + 해머